--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -596,31 +596,31 @@
         <v>1433</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1725.4</v>
+        <v>1731.8</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4962</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>118.68</v>
+        <v>118.56</v>
       </c>
       <c r="H3" t="n">
-        <v>103.37</v>
+        <v>103.74</v>
       </c>
       <c r="I3" t="n">
-        <v>15.3</v>
+        <v>14.82</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3029</v>
+        <v>0.304</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1528</v>
+        <v>0.1505</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
@@ -641,7 +641,7 @@
         <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>1543.4</v>
+        <v>1552.4</v>
       </c>
     </row>
     <row r="4">
@@ -718,31 +718,31 @@
         <v>1173</v>
       </c>
       <c r="D5" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1681.3</v>
+        <v>1675</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.062</v>
+        <v>-2.7831</v>
       </c>
       <c r="G5" t="n">
-        <v>110.46</v>
+        <v>110.38</v>
       </c>
       <c r="H5" t="n">
-        <v>102.01</v>
+        <v>101.85</v>
       </c>
       <c r="I5" t="n">
-        <v>8.460000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2521</v>
+        <v>0.251</v>
       </c>
       <c r="K5" t="n">
-        <v>0.168</v>
+        <v>0.1711</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>75</v>
@@ -763,7 +763,7 @@
         <v>71</v>
       </c>
       <c r="S5" t="n">
-        <v>1557</v>
+        <v>1553.6</v>
       </c>
     </row>
     <row r="6">
@@ -779,31 +779,31 @@
         <v>1206</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1726.3</v>
+        <v>1707.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2513</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>112.16</v>
+        <v>111.81</v>
       </c>
       <c r="H6" t="n">
-        <v>104.41</v>
+        <v>105.03</v>
       </c>
       <c r="I6" t="n">
-        <v>7.75</v>
+        <v>6.78</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2598</v>
+        <v>0.2621</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1537</v>
+        <v>0.1545</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.2</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>107</v>
@@ -824,7 +824,7 @@
         <v>98</v>
       </c>
       <c r="S6" t="n">
-        <v>1496</v>
+        <v>1505.9</v>
       </c>
     </row>
     <row r="7">
@@ -965,7 +965,7 @@
         <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1456.4</v>
+        <v>1460.7</v>
       </c>
       <c r="F9" t="n">
         <v>0.9714</v>
@@ -1145,31 +1145,31 @@
         <v>1350</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1476.7</v>
+        <v>1471.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2487</v>
+        <v>-0.362</v>
       </c>
       <c r="G12" t="n">
-        <v>111.37</v>
+        <v>110.96</v>
       </c>
       <c r="H12" t="n">
-        <v>108</v>
+        <v>108.02</v>
       </c>
       <c r="I12" t="n">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="J12" t="n">
-        <v>0.241</v>
+        <v>0.2478</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1355</v>
+        <v>0.1345</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>-3.2</v>
       </c>
       <c r="M12" t="n">
         <v>142</v>
@@ -1190,7 +1190,7 @@
         <v>147</v>
       </c>
       <c r="S12" t="n">
-        <v>1505.9</v>
+        <v>1514.2</v>
       </c>
     </row>
     <row r="13">
@@ -2343,31 +2343,31 @@
         <v>1181</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E2" t="n">
-        <v>2166.7</v>
+        <v>2170.1</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9474</v>
+        <v>3.9737</v>
       </c>
       <c r="G2" t="n">
-        <v>122.78</v>
+        <v>123.79</v>
       </c>
       <c r="H2" t="n">
-        <v>92.67</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>30.11</v>
+        <v>30.64</v>
       </c>
       <c r="J2" t="n">
-        <v>0.279</v>
+        <v>0.2823</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1537</v>
+        <v>0.1519</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1691.3</v>
+        <v>1690.2</v>
       </c>
     </row>
     <row r="3">
@@ -2404,31 +2404,31 @@
         <v>1438</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1947.8</v>
+        <v>1951.2</v>
       </c>
       <c r="F3" t="n">
-        <v>14.5268</v>
+        <v>13.9718</v>
       </c>
       <c r="G3" t="n">
-        <v>118.75</v>
+        <v>118.9</v>
       </c>
       <c r="H3" t="n">
-        <v>99.73</v>
+        <v>99.7</v>
       </c>
       <c r="I3" t="n">
-        <v>19.02</v>
+        <v>19.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3173</v>
+        <v>0.3157</v>
       </c>
       <c r="K3" t="n">
         <v>0.1519</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
         <v>17</v>
@@ -2449,7 +2449,7 @@
         <v>14</v>
       </c>
       <c r="S3" t="n">
-        <v>1641</v>
+        <v>1635.2</v>
       </c>
     </row>
     <row r="4">
@@ -2468,7 +2468,7 @@
         <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1761</v>
+        <v>1757.4</v>
       </c>
       <c r="F4" t="n">
         <v>13.1837</v>
@@ -2526,31 +2526,31 @@
         <v>1314</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
         <v>1921.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.539</v>
+        <v>2.4067</v>
       </c>
       <c r="G5" t="n">
-        <v>116.62</v>
+        <v>115.82</v>
       </c>
       <c r="H5" t="n">
-        <v>103.11</v>
+        <v>102.6</v>
       </c>
       <c r="I5" t="n">
-        <v>13.51</v>
+        <v>13.22</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2711</v>
+        <v>0.2692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1371</v>
+        <v>0.1364</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
@@ -2571,7 +2571,7 @@
         <v>25</v>
       </c>
       <c r="S5" t="n">
-        <v>1647.2</v>
+        <v>1655.5</v>
       </c>
     </row>
     <row r="6">
@@ -2587,31 +2587,31 @@
         <v>1155</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1850</v>
+        <v>1839.7</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4896</v>
+        <v>3.0742</v>
       </c>
       <c r="G6" t="n">
-        <v>113.1</v>
+        <v>112.26</v>
       </c>
       <c r="H6" t="n">
-        <v>99.94</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>13.16</v>
+        <v>12.36</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2428</v>
+        <v>0.2417</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1391</v>
+        <v>0.1398</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.2</v>
+        <v>-5</v>
       </c>
       <c r="M6" t="n">
         <v>36</v>
@@ -2632,7 +2632,7 @@
         <v>35</v>
       </c>
       <c r="S6" t="n">
-        <v>1642.5</v>
+        <v>1652.1</v>
       </c>
     </row>
     <row r="7">
@@ -2648,31 +2648,31 @@
         <v>1301</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E7" t="n">
-        <v>1754.7</v>
+        <v>1751.4</v>
       </c>
       <c r="F7" t="n">
-        <v>8.5853</v>
+        <v>8.2582</v>
       </c>
       <c r="G7" t="n">
-        <v>119.4</v>
+        <v>118.51</v>
       </c>
       <c r="H7" t="n">
-        <v>106.58</v>
+        <v>107.99</v>
       </c>
       <c r="I7" t="n">
-        <v>12.82</v>
+        <v>10.52</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2754</v>
+        <v>0.2827</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1284</v>
+        <v>0.1274</v>
       </c>
       <c r="L7" t="n">
-        <v>-10.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>31</v>
@@ -2693,7 +2693,7 @@
         <v>29</v>
       </c>
       <c r="S7" t="n">
-        <v>1655.5</v>
+        <v>1678.8</v>
       </c>
     </row>
     <row r="8">
@@ -2709,31 +2709,31 @@
         <v>1257</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1826.1</v>
+        <v>1830.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.8169</v>
+        <v>-3.7351</v>
       </c>
       <c r="G8" t="n">
-        <v>119.14</v>
+        <v>119.03</v>
       </c>
       <c r="H8" t="n">
-        <v>100.72</v>
+        <v>100.17</v>
       </c>
       <c r="I8" t="n">
-        <v>18.42</v>
+        <v>18.86</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2919</v>
+        <v>0.29</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1608</v>
+        <v>0.1596</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
         <v>19</v>
@@ -2754,7 +2754,7 @@
         <v>17</v>
       </c>
       <c r="S8" t="n">
-        <v>1680.4</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="9">
@@ -3014,31 +3014,31 @@
         <v>1439</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1705.2</v>
+        <v>1718</v>
       </c>
       <c r="F13" t="n">
-        <v>6.7074</v>
+        <v>6.2269</v>
       </c>
       <c r="G13" t="n">
-        <v>112.74</v>
+        <v>112.42</v>
       </c>
       <c r="H13" t="n">
-        <v>107.16</v>
+        <v>106.23</v>
       </c>
       <c r="I13" t="n">
-        <v>5.58</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2962</v>
+        <v>0.2914</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1442</v>
+        <v>0.1461</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="M13" t="n">
         <v>57</v>
@@ -3059,7 +3059,7 @@
         <v>54</v>
       </c>
       <c r="S13" t="n">
-        <v>1661.8</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="14">
@@ -3075,31 +3075,31 @@
         <v>1448</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1653</v>
+        <v>1637.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0919</v>
+        <v>-2.9629</v>
       </c>
       <c r="G14" t="n">
-        <v>112.94</v>
+        <v>112.06</v>
       </c>
       <c r="H14" t="n">
-        <v>110.12</v>
+        <v>109.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2954</v>
+        <v>0.2923</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1494</v>
+        <v>0.1475</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4</v>
+        <v>-2.4</v>
       </c>
       <c r="M14" t="n">
         <v>78</v>
@@ -3120,7 +3120,7 @@
         <v>69</v>
       </c>
       <c r="S14" t="n">
-        <v>1655</v>
+        <v>1669.8</v>
       </c>
     </row>
     <row r="15">
@@ -3136,31 +3136,31 @@
         <v>1393</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>1584.8</v>
+        <v>1593</v>
       </c>
       <c r="F15" t="n">
-        <v>1.43</v>
+        <v>1.2532</v>
       </c>
       <c r="G15" t="n">
-        <v>109.16</v>
+        <v>108.18</v>
       </c>
       <c r="H15" t="n">
-        <v>106.41</v>
+        <v>106.44</v>
       </c>
       <c r="I15" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="J15" t="n">
-        <v>0.277</v>
+        <v>0.2761</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1518</v>
+        <v>0.1528</v>
       </c>
       <c r="L15" t="n">
-        <v>-9.4</v>
+        <v>-13.8</v>
       </c>
       <c r="M15" t="n">
         <v>77</v>
@@ -3181,7 +3181,7 @@
         <v>79</v>
       </c>
       <c r="S15" t="n">
-        <v>1659.3</v>
+        <v>1667.2</v>
       </c>
     </row>
     <row r="16">
@@ -3369,31 +3369,31 @@
         <v>1112</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E2" t="n">
-        <v>2237.1</v>
+        <v>2242.8</v>
       </c>
       <c r="F2" t="n">
-        <v>9.117900000000001</v>
+        <v>8.6394</v>
       </c>
       <c r="G2" t="n">
-        <v>121.31</v>
+        <v>120.84</v>
       </c>
       <c r="H2" t="n">
-        <v>95.70999999999999</v>
+        <v>95.38</v>
       </c>
       <c r="I2" t="n">
-        <v>25.61</v>
+        <v>25.46</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2966</v>
+        <v>0.2935</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1491</v>
+        <v>0.1524</v>
       </c>
       <c r="L2" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -3414,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1737.1</v>
+        <v>1747.2</v>
       </c>
     </row>
     <row r="3">
@@ -3491,31 +3491,31 @@
         <v>1403</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>2060.2</v>
+        <v>2034.5</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6236</v>
+        <v>11.3167</v>
       </c>
       <c r="G4" t="n">
-        <v>119.2</v>
+        <v>118.24</v>
       </c>
       <c r="H4" t="n">
-        <v>105.14</v>
+        <v>105.38</v>
       </c>
       <c r="I4" t="n">
-        <v>14.06</v>
+        <v>12.86</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2931</v>
+        <v>0.2929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1537</v>
+        <v>0.1562</v>
       </c>
       <c r="L4" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="M4" t="n">
         <v>13</v>
@@ -3536,7 +3536,7 @@
         <v>13</v>
       </c>
       <c r="S4" t="n">
-        <v>1755.9</v>
+        <v>1753.9</v>
       </c>
     </row>
     <row r="5">
@@ -3552,31 +3552,31 @@
         <v>1242</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1997.6</v>
+        <v>1972.3</v>
       </c>
       <c r="F5" t="n">
-        <v>11.7834</v>
+        <v>11.3738</v>
       </c>
       <c r="G5" t="n">
-        <v>111.06</v>
+        <v>110.16</v>
       </c>
       <c r="H5" t="n">
-        <v>100.88</v>
+        <v>100.46</v>
       </c>
       <c r="I5" t="n">
-        <v>10.18</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2424</v>
+        <v>0.2509</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1489</v>
+        <v>0.1535</v>
       </c>
       <c r="L5" t="n">
-        <v>-6.4</v>
+        <v>-4.8</v>
       </c>
       <c r="M5" t="n">
         <v>16</v>
@@ -3597,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="S5" t="n">
-        <v>1790.5</v>
+        <v>1777.3</v>
       </c>
     </row>
     <row r="6">
@@ -3613,31 +3613,31 @@
         <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6" t="n">
-        <v>2035.8</v>
+        <v>2030.1</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5611</v>
+        <v>3.0314</v>
       </c>
       <c r="G6" t="n">
-        <v>119.51</v>
+        <v>118.09</v>
       </c>
       <c r="H6" t="n">
-        <v>96.20999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>23.3</v>
+        <v>21.66</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3131</v>
+        <v>0.3174</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1465</v>
+        <v>0.1477</v>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>-3.2</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
@@ -3658,7 +3658,7 @@
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>1671.8</v>
+        <v>1692.3</v>
       </c>
     </row>
     <row r="7">
@@ -3674,28 +3674,28 @@
         <v>1416</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1823</v>
+        <v>1839.8</v>
       </c>
       <c r="F7" t="n">
-        <v>8.086399999999999</v>
+        <v>7.5365</v>
       </c>
       <c r="G7" t="n">
-        <v>115.8</v>
+        <v>115.83</v>
       </c>
       <c r="H7" t="n">
-        <v>109.86</v>
+        <v>110.45</v>
       </c>
       <c r="I7" t="n">
-        <v>5.94</v>
+        <v>5.38</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3088</v>
+        <v>0.3093</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1558</v>
+        <v>0.1541</v>
       </c>
       <c r="L7" t="n">
         <v>3.6</v>
@@ -3719,7 +3719,7 @@
         <v>46</v>
       </c>
       <c r="S7" t="n">
-        <v>1687.1</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="8">
@@ -3735,31 +3735,31 @@
         <v>1395</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1798.4</v>
+        <v>1824.2</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9484</v>
+        <v>6.8019</v>
       </c>
       <c r="G8" t="n">
-        <v>110.3</v>
+        <v>110.58</v>
       </c>
       <c r="H8" t="n">
-        <v>101.19</v>
+        <v>101.35</v>
       </c>
       <c r="I8" t="n">
-        <v>9.109999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3139</v>
+        <v>0.3181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1514</v>
+        <v>0.1536</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
@@ -3780,7 +3780,7 @@
         <v>45</v>
       </c>
       <c r="S8" t="n">
-        <v>1659.6</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="9">
@@ -3796,31 +3796,31 @@
         <v>1452</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1705.2</v>
+        <v>1692.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1432</v>
+        <v>0.3873</v>
       </c>
       <c r="G9" t="n">
-        <v>108.03</v>
+        <v>107.19</v>
       </c>
       <c r="H9" t="n">
-        <v>100.05</v>
+        <v>99.78</v>
       </c>
       <c r="I9" t="n">
-        <v>7.98</v>
+        <v>7.41</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2904</v>
+        <v>0.2944</v>
       </c>
       <c r="K9" t="n">
-        <v>0.164</v>
+        <v>0.1659</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6</v>
+        <v>-2.4</v>
       </c>
       <c r="M9" t="n">
         <v>59</v>
@@ -3841,7 +3841,7 @@
         <v>58</v>
       </c>
       <c r="S9" t="n">
-        <v>1657.7</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="10">
@@ -3857,31 +3857,31 @@
         <v>1140</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1922.8</v>
+        <v>1901.3</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4567</v>
+        <v>2.827</v>
       </c>
       <c r="G10" t="n">
-        <v>118.43</v>
+        <v>117.49</v>
       </c>
       <c r="H10" t="n">
-        <v>105.6</v>
+        <v>106.29</v>
       </c>
       <c r="I10" t="n">
-        <v>12.83</v>
+        <v>11.21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2952</v>
+        <v>0.2953</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1442</v>
+        <v>0.1466</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8</v>
+        <v>-8</v>
       </c>
       <c r="M10" t="n">
         <v>23</v>
@@ -3902,7 +3902,7 @@
         <v>23</v>
       </c>
       <c r="S10" t="n">
-        <v>1711.8</v>
+        <v>1712.1</v>
       </c>
     </row>
     <row r="11">
@@ -3918,31 +3918,31 @@
         <v>1153</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1712.3</v>
+        <v>1733.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0539</v>
+        <v>0.433</v>
       </c>
       <c r="G11" t="n">
-        <v>105.06</v>
+        <v>105.76</v>
       </c>
       <c r="H11" t="n">
-        <v>97.37</v>
+        <v>97.33</v>
       </c>
       <c r="I11" t="n">
-        <v>7.69</v>
+        <v>8.43</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2907</v>
+        <v>0.2897</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1605</v>
+        <v>0.1583</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>10.6</v>
       </c>
       <c r="M11" t="n">
         <v>44</v>
@@ -3963,7 +3963,7 @@
         <v>49</v>
       </c>
       <c r="S11" t="n">
-        <v>1703</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="12">
@@ -3979,31 +3979,31 @@
         <v>1160</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1605.5</v>
+        <v>1613.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7493</v>
+        <v>-4.5669</v>
       </c>
       <c r="G12" t="n">
-        <v>112.74</v>
+        <v>114.63</v>
       </c>
       <c r="H12" t="n">
-        <v>112.94</v>
+        <v>113.03</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.21</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2828</v>
+        <v>0.2808</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1439</v>
+        <v>0.1415</v>
       </c>
       <c r="L12" t="n">
-        <v>-11</v>
+        <v>-1.4</v>
       </c>
       <c r="M12" t="n">
         <v>72</v>
@@ -4024,7 +4024,7 @@
         <v>78</v>
       </c>
       <c r="S12" t="n">
-        <v>1679.2</v>
+        <v>1667.2</v>
       </c>
     </row>
     <row r="13">
@@ -4040,31 +4040,31 @@
         <v>1113</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1664.6</v>
+        <v>1681.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.851</v>
+        <v>-1.7565</v>
       </c>
       <c r="G13" t="n">
-        <v>109.66</v>
+        <v>108.88</v>
       </c>
       <c r="H13" t="n">
-        <v>109.38</v>
+        <v>108.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.28</v>
+        <v>0.61</v>
       </c>
       <c r="J13" t="n">
-        <v>0.282</v>
+        <v>0.2847</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1506</v>
+        <v>0.1535</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
         <v>66</v>
@@ -4085,7 +4085,7 @@
         <v>73</v>
       </c>
       <c r="S13" t="n">
-        <v>1708.5</v>
+        <v>1723.9</v>
       </c>
     </row>
     <row r="14">
@@ -4104,7 +4104,7 @@
         <v>117</v>
       </c>
       <c r="E14" t="n">
-        <v>1712.7</v>
+        <v>1673.5</v>
       </c>
       <c r="F14" t="n">
         <v>-6.3298</v>
@@ -4162,31 +4162,31 @@
         <v>1329</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>1691.1</v>
+        <v>1713.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9325</v>
+        <v>-1.1735</v>
       </c>
       <c r="G15" t="n">
-        <v>109.36</v>
+        <v>110.48</v>
       </c>
       <c r="H15" t="n">
-        <v>108.7</v>
+        <v>109.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.66</v>
+        <v>1.43</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2731</v>
+        <v>0.2757</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1584</v>
+        <v>0.156</v>
       </c>
       <c r="L15" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="M15" t="n">
         <v>74</v>
@@ -4207,7 +4207,7 @@
         <v>84</v>
       </c>
       <c r="S15" t="n">
-        <v>1670</v>
+        <v>1678.3</v>
       </c>
     </row>
     <row r="16">
@@ -4223,31 +4223,31 @@
         <v>1243</v>
       </c>
       <c r="D16" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E16" t="n">
-        <v>1568.4</v>
+        <v>1581</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.3262</v>
+        <v>-5.2381</v>
       </c>
       <c r="G16" t="n">
-        <v>106.72</v>
+        <v>106.53</v>
       </c>
       <c r="H16" t="n">
-        <v>109.48</v>
+        <v>108.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.75</v>
+        <v>-2.37</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2891</v>
+        <v>0.291</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1698</v>
+        <v>0.1721</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.800000000000001</v>
+        <v>-5.6</v>
       </c>
       <c r="M16" t="n">
         <v>102</v>
@@ -4268,7 +4268,7 @@
         <v>102</v>
       </c>
       <c r="S16" t="n">
-        <v>1692.6</v>
+        <v>1691.8</v>
       </c>
     </row>
     <row r="17">
@@ -4284,31 +4284,31 @@
         <v>1428</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>1524.3</v>
+        <v>1525</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.958</v>
+        <v>-4.7872</v>
       </c>
       <c r="G17" t="n">
-        <v>107.81</v>
+        <v>108.53</v>
       </c>
       <c r="H17" t="n">
-        <v>113.45</v>
+        <v>114.69</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.64</v>
+        <v>-6.15</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2774</v>
+        <v>0.2793</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1573</v>
+        <v>0.1575</v>
       </c>
       <c r="L17" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="M17" t="n">
         <v>116</v>
@@ -4329,7 +4329,7 @@
         <v>123</v>
       </c>
       <c r="S17" t="n">
-        <v>1692.4</v>
+        <v>1688.9</v>
       </c>
     </row>
   </sheetData>
@@ -4517,31 +4517,31 @@
         <v>1385</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1953.4</v>
+        <v>1955.3</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6322</v>
+        <v>4.7636</v>
       </c>
       <c r="G3" t="n">
-        <v>114.23</v>
+        <v>113.73</v>
       </c>
       <c r="H3" t="n">
-        <v>98.26000000000001</v>
+        <v>98.58</v>
       </c>
       <c r="I3" t="n">
-        <v>15.97</v>
+        <v>15.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3231</v>
+        <v>0.3268</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1412</v>
+        <v>0.1411</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
@@ -4562,7 +4562,7 @@
         <v>22</v>
       </c>
       <c r="S3" t="n">
-        <v>1685</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="4">
@@ -4639,31 +4639,31 @@
         <v>1371</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1657.5</v>
+        <v>1667.3</v>
       </c>
       <c r="F5" t="n">
-        <v>5.8399</v>
+        <v>5.3395</v>
       </c>
       <c r="G5" t="n">
-        <v>105.28</v>
+        <v>106.11</v>
       </c>
       <c r="H5" t="n">
-        <v>97.08</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3185</v>
+        <v>0.321</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1615</v>
+        <v>0.159</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
         <v>53</v>
@@ -4684,7 +4684,7 @@
         <v>56</v>
       </c>
       <c r="S5" t="n">
-        <v>1629.2</v>
+        <v>1622.1</v>
       </c>
     </row>
     <row r="6">
@@ -4944,31 +4944,31 @@
         <v>1462</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1604.7</v>
+        <v>1594.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5072</v>
+        <v>-2.5518</v>
       </c>
       <c r="G10" t="n">
-        <v>109.11</v>
+        <v>108.69</v>
       </c>
       <c r="H10" t="n">
-        <v>110.45</v>
+        <v>110.81</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.34</v>
+        <v>-2.13</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2628</v>
+        <v>0.2695</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1361</v>
+        <v>0.1378</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6</v>
+        <v>-4</v>
       </c>
       <c r="M10" t="n">
         <v>93</v>
@@ -4989,7 +4989,7 @@
         <v>95</v>
       </c>
       <c r="S10" t="n">
-        <v>1628.3</v>
+        <v>1630.7</v>
       </c>
     </row>
     <row r="11">
@@ -5005,31 +5005,31 @@
         <v>1207</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1553.3</v>
+        <v>1551.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0933</v>
+        <v>-4.9935</v>
       </c>
       <c r="G11" t="n">
-        <v>110.29</v>
+        <v>109.71</v>
       </c>
       <c r="H11" t="n">
-        <v>109.48</v>
+        <v>109.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3082</v>
+        <v>0.3048</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1467</v>
+        <v>0.1487</v>
       </c>
       <c r="L11" t="n">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="M11" t="n">
         <v>90</v>
@@ -5050,7 +5050,7 @@
         <v>99</v>
       </c>
       <c r="S11" t="n">
-        <v>1631.1</v>
+        <v>1645.5</v>
       </c>
     </row>
     <row r="12">
@@ -5299,31 +5299,31 @@
         <v>1304</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>2024.8</v>
+        <v>1990.6</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1666</v>
+        <v>11.3442</v>
       </c>
       <c r="G3" t="n">
-        <v>116.39</v>
+        <v>115.07</v>
       </c>
       <c r="H3" t="n">
-        <v>96.90000000000001</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>19.5</v>
+        <v>17.03</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2407</v>
+        <v>0.2419</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1368</v>
+        <v>0.1401</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -5344,7 +5344,7 @@
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>1652</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4">
@@ -5421,31 +5421,31 @@
         <v>1228</v>
       </c>
       <c r="D5" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1994.4</v>
+        <v>1996.4</v>
       </c>
       <c r="F5" t="n">
-        <v>9.371</v>
+        <v>8.884600000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>125.48</v>
+        <v>125.29</v>
       </c>
       <c r="H5" t="n">
-        <v>103.59</v>
+        <v>102.13</v>
       </c>
       <c r="I5" t="n">
-        <v>21.89</v>
+        <v>23.17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3241</v>
+        <v>0.3216</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1319</v>
+        <v>0.1296</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8</v>
+        <v>13.4</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -5466,7 +5466,7 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1721.9</v>
+        <v>1710.4</v>
       </c>
     </row>
     <row r="6">
@@ -5604,31 +5604,31 @@
         <v>1417</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1821.3</v>
+        <v>1842</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4427</v>
+        <v>2.4672</v>
       </c>
       <c r="G8" t="n">
-        <v>116.64</v>
+        <v>116.51</v>
       </c>
       <c r="H8" t="n">
-        <v>108.06</v>
+        <v>106.69</v>
       </c>
       <c r="I8" t="n">
-        <v>8.59</v>
+        <v>9.82</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2987</v>
+        <v>0.2986</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1299</v>
+        <v>0.1302</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.6</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
         <v>41</v>
@@ -5649,7 +5649,7 @@
         <v>39</v>
       </c>
       <c r="S8" t="n">
-        <v>1672.3</v>
+        <v>1687.7</v>
       </c>
     </row>
     <row r="9">
@@ -5851,7 +5851,7 @@
         <v>117</v>
       </c>
       <c r="E12" t="n">
-        <v>1757.4</v>
+        <v>1770.8</v>
       </c>
       <c r="F12" t="n">
         <v>2.1219</v>
@@ -6153,31 +6153,31 @@
         <v>1332</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>1593.3</v>
+        <v>1591.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.3819</v>
+        <v>-9.7958</v>
       </c>
       <c r="G17" t="n">
-        <v>105.34</v>
+        <v>104.34</v>
       </c>
       <c r="H17" t="n">
-        <v>109.5</v>
+        <v>110.1</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.16</v>
+        <v>-5.77</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3164</v>
+        <v>0.3119</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1755</v>
+        <v>0.172</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>-5.8</v>
       </c>
       <c r="M17" t="n">
         <v>98</v>
@@ -6198,7 +6198,7 @@
         <v>107</v>
       </c>
       <c r="S17" t="n">
-        <v>1721.7</v>
+        <v>1735.8</v>
       </c>
     </row>
     <row r="18">
@@ -6447,31 +6447,31 @@
         <v>1275</v>
       </c>
       <c r="D2" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1773.3</v>
+        <v>1772.7</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2962</v>
+        <v>9.988799999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>120.46</v>
+        <v>120.02</v>
       </c>
       <c r="H2" t="n">
-        <v>103.82</v>
+        <v>103.88</v>
       </c>
       <c r="I2" t="n">
-        <v>16.64</v>
+        <v>16.14</v>
       </c>
       <c r="J2" t="n">
         <v>0.2071</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1391</v>
+        <v>0.1427</v>
       </c>
       <c r="L2" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="M2" t="n">
         <v>87</v>
@@ -6492,7 +6492,7 @@
         <v>52</v>
       </c>
       <c r="S2" t="n">
-        <v>1410.4</v>
+        <v>1413.1</v>
       </c>
     </row>
     <row r="3">
@@ -6508,31 +6508,31 @@
         <v>1103</v>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1711</v>
+        <v>1696.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.32</v>
+        <v>1.4591</v>
       </c>
       <c r="G3" t="n">
-        <v>122.54</v>
+        <v>122.16</v>
       </c>
       <c r="H3" t="n">
-        <v>105.32</v>
+        <v>105</v>
       </c>
       <c r="I3" t="n">
-        <v>17.22</v>
+        <v>17.16</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2878</v>
+        <v>0.2907</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1502</v>
+        <v>0.1511</v>
       </c>
       <c r="L3" t="n">
-        <v>14.6</v>
+        <v>15.8</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
@@ -6553,7 +6553,7 @@
         <v>57</v>
       </c>
       <c r="S3" t="n">
-        <v>1493</v>
+        <v>1484.3</v>
       </c>
     </row>
     <row r="4">
@@ -6569,31 +6569,31 @@
         <v>1245</v>
       </c>
       <c r="D4" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>1586.6</v>
+        <v>1606.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.4251</v>
       </c>
       <c r="G4" t="n">
-        <v>110.79</v>
+        <v>112.27</v>
       </c>
       <c r="H4" t="n">
-        <v>109.57</v>
+        <v>109</v>
       </c>
       <c r="I4" t="n">
-        <v>1.22</v>
+        <v>3.27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3176</v>
+        <v>0.3162</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1841</v>
+        <v>0.181</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>160</v>
@@ -6614,7 +6614,7 @@
         <v>150</v>
       </c>
       <c r="S4" t="n">
-        <v>1485.2</v>
+        <v>1472.9</v>
       </c>
     </row>
     <row r="5">
@@ -6630,31 +6630,31 @@
         <v>1405</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1465.1</v>
+        <v>1453.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6982</v>
+        <v>-0.6704</v>
       </c>
       <c r="G5" t="n">
-        <v>114.13</v>
+        <v>113.63</v>
       </c>
       <c r="H5" t="n">
-        <v>111.31</v>
+        <v>111.29</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2953</v>
+        <v>0.2946</v>
       </c>
       <c r="K5" t="n">
-        <v>0.14</v>
+        <v>0.1412</v>
       </c>
       <c r="L5" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
         <v>145</v>
@@ -6675,7 +6675,7 @@
         <v>153</v>
       </c>
       <c r="S5" t="n">
-        <v>1491.7</v>
+        <v>1505.2</v>
       </c>
     </row>
     <row r="6">
@@ -6691,31 +6691,31 @@
         <v>1325</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1461</v>
+        <v>1466.5</v>
       </c>
       <c r="F6" t="n">
-        <v>2.932</v>
+        <v>2.6633</v>
       </c>
       <c r="G6" t="n">
-        <v>106.87</v>
+        <v>106.96</v>
       </c>
       <c r="H6" t="n">
-        <v>110.83</v>
+        <v>111.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.96</v>
+        <v>-4.34</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2887</v>
+        <v>0.2915</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1481</v>
+        <v>0.1466</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.8</v>
+        <v>-4</v>
       </c>
       <c r="M6" t="n">
         <v>227</v>
@@ -6736,7 +6736,7 @@
         <v>222</v>
       </c>
       <c r="S6" t="n">
-        <v>1502</v>
+        <v>1501.4</v>
       </c>
     </row>
     <row r="7">
@@ -6813,31 +6813,31 @@
         <v>1141</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1348.8</v>
+        <v>1341.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0539</v>
+        <v>-2.8296</v>
       </c>
       <c r="G8" t="n">
-        <v>106.61</v>
+        <v>105.75</v>
       </c>
       <c r="H8" t="n">
-        <v>114.49</v>
+        <v>114.35</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.88</v>
+        <v>-8.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3028</v>
+        <v>0.2991</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1714</v>
+        <v>0.1727</v>
       </c>
       <c r="L8" t="n">
-        <v>9.199999999999999</v>
+        <v>-1.8</v>
       </c>
       <c r="M8" t="n">
         <v>263</v>
@@ -6858,7 +6858,7 @@
         <v>273</v>
       </c>
       <c r="S8" t="n">
-        <v>1465.1</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="9">
@@ -6874,31 +6874,31 @@
         <v>1138</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1380</v>
+        <v>1391.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06</v>
+        <v>-0.2165</v>
       </c>
       <c r="G9" t="n">
-        <v>114.55</v>
+        <v>114.44</v>
       </c>
       <c r="H9" t="n">
-        <v>112.33</v>
+        <v>111.83</v>
       </c>
       <c r="I9" t="n">
-        <v>2.22</v>
+        <v>2.61</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2788</v>
+        <v>0.2726</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1573</v>
+        <v>0.1568</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
       </c>
       <c r="M9" t="n">
         <v>194</v>
@@ -6919,7 +6919,7 @@
         <v>190</v>
       </c>
       <c r="S9" t="n">
-        <v>1461.9</v>
+        <v>1459.5</v>
       </c>
     </row>
   </sheetData>
@@ -7828,31 +7828,31 @@
         <v>1429</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1885.3</v>
+        <v>1864.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.313</v>
+        <v>-0.3251</v>
       </c>
       <c r="G2" t="n">
-        <v>120.72</v>
+        <v>119.66</v>
       </c>
       <c r="H2" t="n">
-        <v>102.92</v>
+        <v>104.27</v>
       </c>
       <c r="I2" t="n">
-        <v>17.79</v>
+        <v>15.38</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3024</v>
+        <v>0.3059</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1489</v>
+        <v>0.1487</v>
       </c>
       <c r="L2" t="n">
-        <v>5.6</v>
+        <v>-4.6</v>
       </c>
       <c r="M2" t="n">
         <v>26</v>
@@ -7873,7 +7873,7 @@
         <v>26</v>
       </c>
       <c r="S2" t="n">
-        <v>1591.1</v>
+        <v>1591.6</v>
       </c>
     </row>
     <row r="3">
@@ -7950,31 +7950,31 @@
         <v>1361</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>1800.1</v>
+        <v>1784.9</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2026</v>
+        <v>5.7312</v>
       </c>
       <c r="G4" t="n">
-        <v>110.14</v>
+        <v>110.23</v>
       </c>
       <c r="H4" t="n">
-        <v>100.16</v>
+        <v>101.11</v>
       </c>
       <c r="I4" t="n">
-        <v>9.98</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2667</v>
+        <v>0.2614</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1658</v>
+        <v>0.1636</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>-3.2</v>
       </c>
       <c r="M4" t="n">
         <v>42</v>
@@ -7995,7 +7995,7 @@
         <v>44</v>
       </c>
       <c r="S4" t="n">
-        <v>1652.3</v>
+        <v>1653.1</v>
       </c>
     </row>
     <row r="5">
@@ -8011,31 +8011,31 @@
         <v>1305</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1728.7</v>
+        <v>1738.9</v>
       </c>
       <c r="F5" t="n">
-        <v>7.7166</v>
+        <v>7.3067</v>
       </c>
       <c r="G5" t="n">
-        <v>112.82</v>
+        <v>112.85</v>
       </c>
       <c r="H5" t="n">
-        <v>106.49</v>
+        <v>107.41</v>
       </c>
       <c r="I5" t="n">
-        <v>6.34</v>
+        <v>5.44</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3074</v>
+        <v>0.305</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1434</v>
+        <v>0.1405</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.4</v>
+        <v>-3.6</v>
       </c>
       <c r="M5" t="n">
         <v>70</v>
@@ -8056,7 +8056,7 @@
         <v>67</v>
       </c>
       <c r="S5" t="n">
-        <v>1619.7</v>
+        <v>1614.5</v>
       </c>
     </row>
     <row r="6">
@@ -8072,31 +8072,31 @@
         <v>1213</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1721.7</v>
+        <v>1722.6</v>
       </c>
       <c r="F6" t="n">
-        <v>6.806</v>
+        <v>6.6005</v>
       </c>
       <c r="G6" t="n">
-        <v>109.04</v>
+        <v>109.82</v>
       </c>
       <c r="H6" t="n">
-        <v>100.39</v>
+        <v>99.62</v>
       </c>
       <c r="I6" t="n">
-        <v>8.65</v>
+        <v>10.21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2801</v>
+        <v>0.2757</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1755</v>
+        <v>0.1736</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="M6" t="n">
         <v>62</v>
@@ -8117,7 +8117,7 @@
         <v>75</v>
       </c>
       <c r="S6" t="n">
-        <v>1596</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="7">
@@ -8136,7 +8136,7 @@
         <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1656.3</v>
+        <v>1651.9</v>
       </c>
       <c r="F7" t="n">
         <v>-5.6123</v>
@@ -8194,31 +8194,31 @@
         <v>1129</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1718</v>
+        <v>1727.7</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4451</v>
+        <v>-2.3169</v>
       </c>
       <c r="G8" t="n">
-        <v>113.04</v>
+        <v>113.86</v>
       </c>
       <c r="H8" t="n">
-        <v>106.38</v>
+        <v>107.08</v>
       </c>
       <c r="I8" t="n">
-        <v>6.66</v>
+        <v>6.78</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2812</v>
+        <v>0.2821</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1555</v>
+        <v>0.1603</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="M8" t="n">
         <v>60</v>
@@ -8239,7 +8239,7 @@
         <v>59</v>
       </c>
       <c r="S8" t="n">
-        <v>1613</v>
+        <v>1623.5</v>
       </c>
     </row>
     <row r="9">
@@ -8255,31 +8255,31 @@
         <v>1424</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1657.8</v>
+        <v>1653.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4625</v>
+        <v>1.5039</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3</v>
+        <v>112.07</v>
       </c>
       <c r="H9" t="n">
-        <v>111.9</v>
+        <v>110.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6</v>
+        <v>1.18</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2995</v>
+        <v>0.294</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1621</v>
+        <v>0.1616</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="M9" t="n">
         <v>120</v>
@@ -8300,7 +8300,7 @@
         <v>126</v>
       </c>
       <c r="S9" t="n">
-        <v>1610.1</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="10">
@@ -8316,31 +8316,31 @@
         <v>1461</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1511.1</v>
+        <v>1524.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4101</v>
+        <v>-0.385</v>
       </c>
       <c r="G10" t="n">
-        <v>111.78</v>
+        <v>112.57</v>
       </c>
       <c r="H10" t="n">
-        <v>107.92</v>
+        <v>108.22</v>
       </c>
       <c r="I10" t="n">
-        <v>3.86</v>
+        <v>4.35</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3255</v>
+        <v>0.3147</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1565</v>
+        <v>0.1573</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4</v>
+        <v>3.8</v>
       </c>
       <c r="M10" t="n">
         <v>101</v>
@@ -8361,7 +8361,7 @@
         <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>1557.3</v>
+        <v>1569.8</v>
       </c>
     </row>
     <row r="11">
@@ -8377,31 +8377,31 @@
         <v>1201</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1415.9</v>
+        <v>1423.4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6524</v>
+        <v>2.4993</v>
       </c>
       <c r="G11" t="n">
-        <v>104.69</v>
+        <v>105.7</v>
       </c>
       <c r="H11" t="n">
-        <v>106.09</v>
+        <v>105.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4</v>
+        <v>0.02</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2612</v>
+        <v>0.2618</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1714</v>
+        <v>0.1679</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4</v>
+        <v>-3.6</v>
       </c>
       <c r="M11" t="n">
         <v>126</v>
@@ -8422,7 +8422,7 @@
         <v>139</v>
       </c>
       <c r="S11" t="n">
-        <v>1593.9</v>
+        <v>1581.4</v>
       </c>
     </row>
     <row r="12">
@@ -8438,31 +8438,31 @@
         <v>1363</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1362.7</v>
+        <v>1365.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4644</v>
+        <v>-3.3076</v>
       </c>
       <c r="G12" t="n">
-        <v>106.25</v>
+        <v>105.89</v>
       </c>
       <c r="H12" t="n">
-        <v>119.5</v>
+        <v>119.41</v>
       </c>
       <c r="I12" t="n">
-        <v>-13.25</v>
+        <v>-13.52</v>
       </c>
       <c r="J12" t="n">
-        <v>0.329</v>
+        <v>0.3273</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1457</v>
+        <v>0.1431</v>
       </c>
       <c r="L12" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="M12" t="n">
         <v>234</v>
@@ -8483,7 +8483,7 @@
         <v>256</v>
       </c>
       <c r="S12" t="n">
-        <v>1595</v>
+        <v>1586.5</v>
       </c>
     </row>
     <row r="13">
@@ -8499,31 +8499,31 @@
         <v>1102</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1257.5</v>
+        <v>1257.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4208</v>
+        <v>-2.3848</v>
       </c>
       <c r="G13" t="n">
-        <v>93.75</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>120.08</v>
+        <v>120.68</v>
       </c>
       <c r="I13" t="n">
-        <v>-26.33</v>
+        <v>-27.22</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2311</v>
+        <v>0.2242</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2089</v>
+        <v>0.2077</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.4</v>
+        <v>-19.6</v>
       </c>
       <c r="M13" t="n">
         <v>346</v>
@@ -8544,7 +8544,7 @@
         <v>349</v>
       </c>
       <c r="S13" t="n">
-        <v>1554.6</v>
+        <v>1563.3</v>
       </c>
     </row>
   </sheetData>
@@ -8671,31 +8671,31 @@
         <v>1196</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1991</v>
+        <v>1993.6</v>
       </c>
       <c r="F2" t="n">
-        <v>4.005</v>
+        <v>4.3059</v>
       </c>
       <c r="G2" t="n">
-        <v>120.45</v>
+        <v>121.4</v>
       </c>
       <c r="H2" t="n">
-        <v>98.51000000000001</v>
+        <v>98.63</v>
       </c>
       <c r="I2" t="n">
-        <v>21.94</v>
+        <v>22.77</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3301</v>
+        <v>0.3333</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1588</v>
+        <v>0.1547</v>
       </c>
       <c r="L2" t="n">
-        <v>17.8</v>
+        <v>22.8</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -8716,7 +8716,7 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1706.1</v>
+        <v>1699.9</v>
       </c>
     </row>
     <row r="3">
@@ -8732,31 +8732,31 @@
         <v>1104</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1987.5</v>
+        <v>1966.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.936</v>
+        <v>-1.6248</v>
       </c>
       <c r="G3" t="n">
-        <v>121.38</v>
+        <v>121.39</v>
       </c>
       <c r="H3" t="n">
-        <v>109.56</v>
+        <v>110.58</v>
       </c>
       <c r="I3" t="n">
-        <v>11.82</v>
+        <v>10.81</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2753</v>
+        <v>0.279</v>
       </c>
       <c r="K3" t="n">
         <v>0.1296</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -8777,7 +8777,7 @@
         <v>16</v>
       </c>
       <c r="S3" t="n">
-        <v>1770.3</v>
+        <v>1769.4</v>
       </c>
     </row>
     <row r="4">
@@ -8854,31 +8854,31 @@
         <v>1281</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1783.2</v>
+        <v>1768.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.3477</v>
+        <v>-2.8893</v>
       </c>
       <c r="G5" t="n">
-        <v>116.22</v>
+        <v>115.23</v>
       </c>
       <c r="H5" t="n">
-        <v>108.21</v>
+        <v>109.22</v>
       </c>
       <c r="I5" t="n">
-        <v>8.01</v>
+        <v>6.01</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2999</v>
+        <v>0.3029</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1675</v>
+        <v>0.1713</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>47</v>
@@ -8899,7 +8899,7 @@
         <v>53</v>
       </c>
       <c r="S5" t="n">
-        <v>1636.2</v>
+        <v>1637.7</v>
       </c>
     </row>
     <row r="6">
@@ -8915,31 +8915,31 @@
         <v>1246</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1910.2</v>
+        <v>1893.4</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1328</v>
+        <v>6.006</v>
       </c>
       <c r="G6" t="n">
-        <v>117.29</v>
+        <v>116.85</v>
       </c>
       <c r="H6" t="n">
-        <v>104.88</v>
+        <v>105.78</v>
       </c>
       <c r="I6" t="n">
-        <v>12.41</v>
+        <v>11.07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3083</v>
+        <v>0.3101</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1456</v>
+        <v>0.1466</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
         <v>25</v>
@@ -8960,7 +8960,7 @@
         <v>27</v>
       </c>
       <c r="S6" t="n">
-        <v>1715.2</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="7">
@@ -8976,31 +8976,31 @@
         <v>1397</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1909.3</v>
+        <v>1912.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9652</v>
+        <v>-1.7463</v>
       </c>
       <c r="G7" t="n">
-        <v>116.77</v>
+        <v>117.37</v>
       </c>
       <c r="H7" t="n">
-        <v>101.52</v>
+        <v>101.08</v>
       </c>
       <c r="I7" t="n">
-        <v>15.26</v>
+        <v>16.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3579</v>
+        <v>0.3535</v>
       </c>
       <c r="K7" t="n">
-        <v>0.169</v>
+        <v>0.1667</v>
       </c>
       <c r="L7" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
         <v>18</v>
@@ -9021,7 +9021,7 @@
         <v>20</v>
       </c>
       <c r="S7" t="n">
-        <v>1704.1</v>
+        <v>1692.2</v>
       </c>
     </row>
     <row r="8">
@@ -9040,7 +9040,7 @@
         <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>1818.7</v>
+        <v>1785.1</v>
       </c>
       <c r="F8" t="n">
         <v>2.0552</v>
@@ -9098,31 +9098,31 @@
         <v>1435</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1914.8</v>
+        <v>1921</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5315</v>
+        <v>1.9274</v>
       </c>
       <c r="G9" t="n">
-        <v>121.92</v>
+        <v>121.87</v>
       </c>
       <c r="H9" t="n">
-        <v>105.39</v>
+        <v>105.42</v>
       </c>
       <c r="I9" t="n">
-        <v>16.53</v>
+        <v>16.45</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2752</v>
+        <v>0.2854</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1255</v>
+        <v>0.1247</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="M9" t="n">
         <v>14</v>
@@ -9143,7 +9143,7 @@
         <v>18</v>
       </c>
       <c r="S9" t="n">
-        <v>1688.9</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="10">
@@ -9159,31 +9159,31 @@
         <v>1401</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1786.5</v>
+        <v>1836.9</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8041</v>
+        <v>4.4256</v>
       </c>
       <c r="G10" t="n">
-        <v>117.75</v>
+        <v>118.62</v>
       </c>
       <c r="H10" t="n">
-        <v>106.35</v>
+        <v>106.73</v>
       </c>
       <c r="I10" t="n">
-        <v>11.4</v>
+        <v>11.89</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3057</v>
+        <v>0.3028</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1422</v>
+        <v>0.1406</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.4</v>
+        <v>-0.6</v>
       </c>
       <c r="M10" t="n">
         <v>38</v>
@@ -9204,7 +9204,7 @@
         <v>43</v>
       </c>
       <c r="S10" t="n">
-        <v>1644.3</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="11">
@@ -9220,31 +9220,31 @@
         <v>1208</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1795.5</v>
+        <v>1810.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.8284</v>
       </c>
       <c r="G11" t="n">
-        <v>120.49</v>
+        <v>120.8</v>
       </c>
       <c r="H11" t="n">
-        <v>105.83</v>
+        <v>106.43</v>
       </c>
       <c r="I11" t="n">
-        <v>14.66</v>
+        <v>14.38</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3208</v>
+        <v>0.3238</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1349</v>
+        <v>0.1381</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>33</v>
@@ -9265,7 +9265,7 @@
         <v>31</v>
       </c>
       <c r="S11" t="n">
-        <v>1628.9</v>
+        <v>1647.3</v>
       </c>
     </row>
     <row r="12">
@@ -9281,31 +9281,31 @@
         <v>1120</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1830.2</v>
+        <v>1835.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.3155</v>
+        <v>-7.2849</v>
       </c>
       <c r="G12" t="n">
-        <v>118.8</v>
+        <v>119.39</v>
       </c>
       <c r="H12" t="n">
-        <v>114.33</v>
+        <v>113.99</v>
       </c>
       <c r="I12" t="n">
-        <v>4.47</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3515</v>
+        <v>0.3508</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1455</v>
+        <v>0.1441</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.2</v>
+        <v>-1.8</v>
       </c>
       <c r="M12" t="n">
         <v>40</v>
@@ -9326,7 +9326,7 @@
         <v>38</v>
       </c>
       <c r="S12" t="n">
-        <v>1748</v>
+        <v>1745.4</v>
       </c>
     </row>
     <row r="13">
@@ -9342,31 +9342,31 @@
         <v>1280</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1635.9</v>
+        <v>1633.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3161</v>
+        <v>-2.2844</v>
       </c>
       <c r="G13" t="n">
-        <v>107.19</v>
+        <v>106.96</v>
       </c>
       <c r="H13" t="n">
-        <v>110.91</v>
+        <v>112.13</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.71</v>
+        <v>-5.17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2815</v>
+        <v>0.279</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1545</v>
+        <v>0.1541</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.8</v>
+        <v>-17</v>
       </c>
       <c r="M13" t="n">
         <v>96</v>
@@ -9387,7 +9387,7 @@
         <v>104</v>
       </c>
       <c r="S13" t="n">
-        <v>1689.9</v>
+        <v>1702.1</v>
       </c>
     </row>
     <row r="14">
@@ -9403,28 +9403,28 @@
         <v>1328</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1672.3</v>
+        <v>1687.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3858</v>
+        <v>-3.1749</v>
       </c>
       <c r="G14" t="n">
-        <v>119.53</v>
+        <v>119.85</v>
       </c>
       <c r="H14" t="n">
-        <v>111.93</v>
+        <v>111.64</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3161</v>
+        <v>0.3131</v>
       </c>
       <c r="K14" t="n">
-        <v>0.138</v>
+        <v>0.1429</v>
       </c>
       <c r="L14" t="n">
         <v>3.4</v>
@@ -9448,7 +9448,7 @@
         <v>62</v>
       </c>
       <c r="S14" t="n">
-        <v>1653.7</v>
+        <v>1659.4</v>
       </c>
     </row>
     <row r="15">
@@ -9464,31 +9464,31 @@
         <v>1279</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>1641.6</v>
+        <v>1635.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.7805</v>
+        <v>-8.315899999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>109.63</v>
+        <v>109.52</v>
       </c>
       <c r="H15" t="n">
-        <v>110.03</v>
+        <v>110.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2839</v>
+        <v>0.2845</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1304</v>
+        <v>0.1345</v>
       </c>
       <c r="L15" t="n">
-        <v>-7</v>
+        <v>-5.2</v>
       </c>
       <c r="M15" t="n">
         <v>79</v>
@@ -9509,7 +9509,7 @@
         <v>91</v>
       </c>
       <c r="S15" t="n">
-        <v>1690.6</v>
+        <v>1698.7</v>
       </c>
     </row>
     <row r="16">
@@ -9525,31 +9525,31 @@
         <v>1261</v>
       </c>
       <c r="D16" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E16" t="n">
-        <v>1653.5</v>
+        <v>1647.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7588</v>
+        <v>-1.0692</v>
       </c>
       <c r="G16" t="n">
-        <v>116.18</v>
+        <v>116.12</v>
       </c>
       <c r="H16" t="n">
-        <v>111.22</v>
+        <v>111.97</v>
       </c>
       <c r="I16" t="n">
-        <v>4.96</v>
+        <v>4.16</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3055</v>
+        <v>0.2988</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1474</v>
+        <v>0.1514</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.8</v>
+        <v>-6.6</v>
       </c>
       <c r="M16" t="n">
         <v>58</v>
@@ -9570,7 +9570,7 @@
         <v>70</v>
       </c>
       <c r="S16" t="n">
-        <v>1646.4</v>
+        <v>1654.3</v>
       </c>
     </row>
     <row r="17">
@@ -9586,31 +9586,31 @@
         <v>1376</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>1536.5</v>
+        <v>1538.7</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7826</v>
+        <v>-2.644</v>
       </c>
       <c r="G17" t="n">
-        <v>109.92</v>
+        <v>109.32</v>
       </c>
       <c r="H17" t="n">
-        <v>111.02</v>
+        <v>111.39</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1</v>
+        <v>-2.08</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2622</v>
+        <v>0.2639</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1333</v>
+        <v>0.1357</v>
       </c>
       <c r="L17" t="n">
-        <v>-9.6</v>
+        <v>-10.6</v>
       </c>
       <c r="M17" t="n">
         <v>94</v>
@@ -9631,7 +9631,7 @@
         <v>108</v>
       </c>
       <c r="S17" t="n">
-        <v>1647.1</v>
+        <v>1657.2</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -26,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +54,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,97 +438,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -1391,97 +1403,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2234,97 +2246,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -3260,97 +3272,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4347,97 +4359,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5129,97 +5141,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6338,97 +6350,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6937,97 +6949,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7719,97 +7731,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8562,97 +8574,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -26,16 +26,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +51,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,97 +426,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -547,31 +535,31 @@
         <v>1387</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E2" t="n">
-        <v>1828.2</v>
+        <v>1825.9</v>
       </c>
       <c r="F2" t="n">
-        <v>11.0707</v>
+        <v>10.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>121.57</v>
+        <v>122</v>
       </c>
       <c r="H2" t="n">
-        <v>96.51000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="I2" t="n">
-        <v>25.06</v>
+        <v>25.05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2343</v>
+        <v>0.2326</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1691</v>
+        <v>0.167</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="M2" t="n">
         <v>27</v>
@@ -592,7 +580,7 @@
         <v>24</v>
       </c>
       <c r="S2" t="n">
-        <v>1506.9</v>
+        <v>1501.8</v>
       </c>
     </row>
     <row r="3">
@@ -669,31 +657,31 @@
         <v>1386</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1618.4</v>
+        <v>1610.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2798</v>
+        <v>0.6493</v>
       </c>
       <c r="G4" t="n">
-        <v>104.61</v>
+        <v>104.92</v>
       </c>
       <c r="H4" t="n">
-        <v>102.08</v>
+        <v>102.36</v>
       </c>
       <c r="I4" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2886</v>
+        <v>0.2837</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1617</v>
+        <v>0.1632</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="M4" t="n">
         <v>132</v>
@@ -714,7 +702,7 @@
         <v>132</v>
       </c>
       <c r="S4" t="n">
-        <v>1511.9</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="5">
@@ -852,31 +840,31 @@
         <v>1172</v>
       </c>
       <c r="D7" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1534.8</v>
+        <v>1523</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9764</v>
+        <v>-2.809</v>
       </c>
       <c r="G7" t="n">
-        <v>109.14</v>
+        <v>108.88</v>
       </c>
       <c r="H7" t="n">
-        <v>105.34</v>
+        <v>105.54</v>
       </c>
       <c r="I7" t="n">
-        <v>3.79</v>
+        <v>3.34</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2905</v>
+        <v>0.2845</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1611</v>
+        <v>0.1555</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
         <v>106</v>
@@ -897,7 +885,7 @@
         <v>105</v>
       </c>
       <c r="S7" t="n">
-        <v>1538.2</v>
+        <v>1542.6</v>
       </c>
     </row>
     <row r="8">
@@ -913,31 +901,31 @@
         <v>1182</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>1477.4</v>
+        <v>1476.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5766</v>
+        <v>-2.3487</v>
       </c>
       <c r="G8" t="n">
-        <v>109.56</v>
+        <v>108.08</v>
       </c>
       <c r="H8" t="n">
-        <v>107.88</v>
+        <v>107.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2809</v>
+        <v>0.2829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1707</v>
+        <v>0.1768</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.4</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>125</v>
@@ -958,7 +946,7 @@
         <v>131</v>
       </c>
       <c r="S8" t="n">
-        <v>1544.2</v>
+        <v>1541.8</v>
       </c>
     </row>
     <row r="9">
@@ -967,59 +955,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>G Washington</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1460.7</v>
+        <v>1540.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9714</v>
+        <v>-4.3148</v>
       </c>
       <c r="G9" t="n">
-        <v>103.92</v>
+        <v>116.28</v>
       </c>
       <c r="H9" t="n">
-        <v>102.4</v>
+        <v>105.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>10.88</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3108</v>
+        <v>0.3229</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1628</v>
+        <v>0.1749</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="N9" t="n">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="Q9" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="R9" t="n">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="S9" t="n">
-        <v>1502.1</v>
+        <v>1537.4</v>
       </c>
     </row>
     <row r="10">
@@ -1028,59 +1016,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G Washington</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="D10" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E10" t="n">
-        <v>1511.5</v>
+        <v>1456.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4633</v>
+        <v>1.1066</v>
       </c>
       <c r="G10" t="n">
-        <v>115.96</v>
+        <v>105.16</v>
       </c>
       <c r="H10" t="n">
-        <v>105.35</v>
+        <v>103.59</v>
       </c>
       <c r="I10" t="n">
-        <v>10.61</v>
+        <v>1.57</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3232</v>
+        <v>0.3183</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1782</v>
+        <v>0.1588</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>-2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="N10" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="O10" t="n">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="P10" t="n">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="Q10" t="n">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="R10" t="n">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="S10" t="n">
-        <v>1539</v>
+        <v>1494.5</v>
       </c>
     </row>
     <row r="11">
@@ -1096,31 +1084,31 @@
         <v>1348</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1553.4</v>
+        <v>1573.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.859</v>
+        <v>0.7869</v>
       </c>
       <c r="G11" t="n">
-        <v>105.72</v>
+        <v>105.82</v>
       </c>
       <c r="H11" t="n">
-        <v>102.88</v>
+        <v>102.05</v>
       </c>
       <c r="I11" t="n">
-        <v>2.85</v>
+        <v>3.77</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3066</v>
+        <v>0.3055</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1764</v>
+        <v>0.1789</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.2</v>
+        <v>-4</v>
       </c>
       <c r="M11" t="n">
         <v>137</v>
@@ -1141,7 +1129,7 @@
         <v>141</v>
       </c>
       <c r="S11" t="n">
-        <v>1521.9</v>
+        <v>1518.9</v>
       </c>
     </row>
     <row r="12">
@@ -1218,31 +1206,31 @@
         <v>1247</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E13" t="n">
-        <v>1392.1</v>
+        <v>1400.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3737</v>
+        <v>-2.1985</v>
       </c>
       <c r="G13" t="n">
-        <v>98.06</v>
+        <v>99.5</v>
       </c>
       <c r="H13" t="n">
-        <v>109.65</v>
+        <v>110.35</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.59</v>
+        <v>-10.85</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3245</v>
+        <v>0.3276</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1807</v>
+        <v>0.1795</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.2</v>
+        <v>-3.8</v>
       </c>
       <c r="M13" t="n">
         <v>229</v>
@@ -1263,7 +1251,7 @@
         <v>239</v>
       </c>
       <c r="S13" t="n">
-        <v>1566.7</v>
+        <v>1562.2</v>
       </c>
     </row>
     <row r="14">
@@ -1279,31 +1267,31 @@
         <v>1382</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E14" t="n">
-        <v>1541.7</v>
+        <v>1531.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.021100000000001</v>
+        <v>-8.8443</v>
       </c>
       <c r="G14" t="n">
-        <v>111.7</v>
+        <v>111.57</v>
       </c>
       <c r="H14" t="n">
-        <v>110.92</v>
+        <v>111.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.78</v>
+        <v>0.52</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3187</v>
+        <v>0.3194</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1608</v>
+        <v>0.1633</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="M14" t="n">
         <v>150</v>
@@ -1324,7 +1312,7 @@
         <v>149</v>
       </c>
       <c r="S14" t="n">
-        <v>1535.2</v>
+        <v>1532.1</v>
       </c>
     </row>
     <row r="15">
@@ -1340,31 +1328,31 @@
         <v>1260</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E15" t="n">
-        <v>1392</v>
+        <v>1390.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.4275</v>
+        <v>-4.2873</v>
       </c>
       <c r="G15" t="n">
-        <v>99.75</v>
+        <v>100.15</v>
       </c>
       <c r="H15" t="n">
-        <v>114.41</v>
+        <v>115.52</v>
       </c>
       <c r="I15" t="n">
-        <v>-14.66</v>
+        <v>-15.37</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2838</v>
+        <v>0.2854</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1903</v>
+        <v>0.1902</v>
       </c>
       <c r="L15" t="n">
-        <v>-12.2</v>
+        <v>-11</v>
       </c>
       <c r="M15" t="n">
         <v>306</v>
@@ -1385,7 +1373,7 @@
         <v>303</v>
       </c>
       <c r="S15" t="n">
-        <v>1548.6</v>
+        <v>1562.8</v>
       </c>
     </row>
   </sheetData>
@@ -1403,97 +1391,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2246,97 +2234,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2477,31 +2465,31 @@
         <v>1274</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1757.4</v>
+        <v>1773.8</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1837</v>
+        <v>12.7945</v>
       </c>
       <c r="G4" t="n">
-        <v>117.38</v>
+        <v>117.09</v>
       </c>
       <c r="H4" t="n">
-        <v>99.64</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>17.74</v>
+        <v>17.19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3063</v>
+        <v>0.3061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1591</v>
+        <v>0.1624</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
@@ -2522,7 +2510,7 @@
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>1596.7</v>
+        <v>1607.1</v>
       </c>
     </row>
     <row r="5">
@@ -2653,59 +2641,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1301</v>
+        <v>1257</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1751.4</v>
+        <v>1830.2</v>
       </c>
       <c r="F7" t="n">
-        <v>8.2582</v>
+        <v>-3.7351</v>
       </c>
       <c r="G7" t="n">
-        <v>118.51</v>
+        <v>119.03</v>
       </c>
       <c r="H7" t="n">
-        <v>107.99</v>
+        <v>100.17</v>
       </c>
       <c r="I7" t="n">
-        <v>10.52</v>
+        <v>18.86</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2827</v>
+        <v>0.29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1274</v>
+        <v>0.1596</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="P7" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R7" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="S7" t="n">
-        <v>1678.8</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="8">
@@ -2714,59 +2702,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1257</v>
+        <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" t="n">
-        <v>1830.2</v>
+        <v>1751.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.7351</v>
+        <v>8.2582</v>
       </c>
       <c r="G8" t="n">
-        <v>119.03</v>
+        <v>118.51</v>
       </c>
       <c r="H8" t="n">
-        <v>100.17</v>
+        <v>107.99</v>
       </c>
       <c r="I8" t="n">
-        <v>18.86</v>
+        <v>10.52</v>
       </c>
       <c r="J8" t="n">
-        <v>0.29</v>
+        <v>0.2827</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1596</v>
+        <v>0.1274</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N8" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="S8" t="n">
-        <v>1675</v>
+        <v>1678.8</v>
       </c>
     </row>
     <row r="9">
@@ -2775,59 +2763,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Florida St</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1143</v>
+        <v>1199</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1697.1</v>
+        <v>1606</v>
       </c>
       <c r="F9" t="n">
-        <v>8.4321</v>
+        <v>-1.2483</v>
       </c>
       <c r="G9" t="n">
-        <v>109.39</v>
+        <v>110.66</v>
       </c>
       <c r="H9" t="n">
-        <v>103.55</v>
+        <v>107.46</v>
       </c>
       <c r="I9" t="n">
-        <v>5.84</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2286</v>
+        <v>0.3177</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1474</v>
+        <v>0.1509</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N9" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="O9" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P9" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q9" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="R9" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="S9" t="n">
-        <v>1603.7</v>
+        <v>1647.5</v>
       </c>
     </row>
     <row r="10">
@@ -2836,59 +2824,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>California</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1374</v>
+        <v>1143</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E10" t="n">
-        <v>1770.1</v>
+        <v>1728.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6059</v>
+        <v>8.044</v>
       </c>
       <c r="G10" t="n">
-        <v>119.38</v>
+        <v>109.41</v>
       </c>
       <c r="H10" t="n">
-        <v>110.1</v>
+        <v>102.71</v>
       </c>
       <c r="I10" t="n">
-        <v>9.279999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3004</v>
+        <v>0.227</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1491</v>
+        <v>0.1448</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M10" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
+        <v>66</v>
+      </c>
+      <c r="O10" t="n">
+        <v>71</v>
+      </c>
+      <c r="P10" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q10" t="n">
         <v>45</v>
       </c>
-      <c r="O10" t="n">
-        <v>37</v>
-      </c>
-      <c r="P10" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>38</v>
-      </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="S10" t="n">
-        <v>1642.4</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="11">
@@ -2897,59 +2885,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Florida St</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1199</v>
+        <v>1390</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1599</v>
+        <v>1733.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7495</v>
+        <v>2.8143</v>
       </c>
       <c r="G11" t="n">
-        <v>110.62</v>
+        <v>111.86</v>
       </c>
       <c r="H11" t="n">
-        <v>107.19</v>
+        <v>106.91</v>
       </c>
       <c r="I11" t="n">
-        <v>3.43</v>
+        <v>4.95</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3205</v>
+        <v>0.3137</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1501</v>
+        <v>0.1439</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N11" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="O11" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="Q11" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R11" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="S11" t="n">
-        <v>1651.4</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="12">
@@ -2958,59 +2946,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1390</v>
+        <v>1374</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E12" t="n">
-        <v>1726</v>
+        <v>1753.7</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1148</v>
+        <v>1.2979</v>
       </c>
       <c r="G12" t="n">
-        <v>111.23</v>
+        <v>118.53</v>
       </c>
       <c r="H12" t="n">
-        <v>106.28</v>
+        <v>109.67</v>
       </c>
       <c r="I12" t="n">
-        <v>4.95</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.316</v>
+        <v>0.3029</v>
       </c>
       <c r="K12" t="n">
-        <v>0.145</v>
+        <v>0.1516</v>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="N12" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="P12" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="R12" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="S12" t="n">
-        <v>1626.4</v>
+        <v>1646.7</v>
       </c>
     </row>
     <row r="13">
@@ -3209,31 +3197,31 @@
         <v>1338</v>
       </c>
       <c r="D16" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>1544.7</v>
+        <v>1510.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.8166</v>
+        <v>-5.4673</v>
       </c>
       <c r="G16" t="n">
-        <v>106.44</v>
+        <v>106.74</v>
       </c>
       <c r="H16" t="n">
-        <v>108.57</v>
+        <v>109.24</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.13</v>
+        <v>-2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3221</v>
+        <v>0.3257</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1696</v>
+        <v>0.1677</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M16" t="n">
         <v>99</v>
@@ -3254,7 +3242,7 @@
         <v>110</v>
       </c>
       <c r="S16" t="n">
-        <v>1665.2</v>
+        <v>1660.9</v>
       </c>
     </row>
   </sheetData>
@@ -3272,97 +3260,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -3442,31 +3430,31 @@
         <v>1222</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>2083.1</v>
+        <v>2085.1</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0302</v>
+        <v>2.67</v>
       </c>
       <c r="G3" t="n">
-        <v>118.12</v>
+        <v>117.81</v>
       </c>
       <c r="H3" t="n">
-        <v>94.48</v>
+        <v>94.78</v>
       </c>
       <c r="I3" t="n">
-        <v>23.64</v>
+        <v>23.03</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3382</v>
+        <v>0.3414</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1188</v>
+        <v>0.1193</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -3487,7 +3475,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1703.5</v>
+        <v>1703.4</v>
       </c>
     </row>
     <row r="4">
@@ -3557,59 +3545,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E5" t="n">
-        <v>1972.3</v>
+        <v>2030.1</v>
       </c>
       <c r="F5" t="n">
-        <v>11.3738</v>
+        <v>3.0314</v>
       </c>
       <c r="G5" t="n">
-        <v>110.16</v>
+        <v>118.09</v>
       </c>
       <c r="H5" t="n">
-        <v>100.46</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>9.699999999999999</v>
+        <v>21.66</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2509</v>
+        <v>0.3174</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1535</v>
+        <v>0.1477</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.8</v>
+        <v>-3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>1777.3</v>
+        <v>1692.3</v>
       </c>
     </row>
     <row r="6">
@@ -3618,59 +3606,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>2030.1</v>
+        <v>1972.3</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0314</v>
+        <v>11.3738</v>
       </c>
       <c r="G6" t="n">
-        <v>118.09</v>
+        <v>110.16</v>
       </c>
       <c r="H6" t="n">
-        <v>96.43000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="I6" t="n">
-        <v>21.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3174</v>
+        <v>0.2509</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1477</v>
+        <v>0.1535</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.2</v>
+        <v>-4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S6" t="n">
-        <v>1692.3</v>
+        <v>1777.3</v>
       </c>
     </row>
     <row r="7">
@@ -3679,59 +3667,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1416</v>
+        <v>1395</v>
       </c>
       <c r="D7" t="n">
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1839.8</v>
+        <v>1824.2</v>
       </c>
       <c r="F7" t="n">
-        <v>7.5365</v>
+        <v>6.8019</v>
       </c>
       <c r="G7" t="n">
-        <v>115.83</v>
+        <v>110.58</v>
       </c>
       <c r="H7" t="n">
-        <v>110.45</v>
+        <v>101.35</v>
       </c>
       <c r="I7" t="n">
-        <v>5.38</v>
+        <v>9.23</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3093</v>
+        <v>0.3181</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1541</v>
+        <v>0.1536</v>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P7" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
-        <v>1687.9</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="8">
@@ -3740,59 +3728,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1395</v>
+        <v>1416</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1824.2</v>
+        <v>1839.8</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8019</v>
+        <v>7.5365</v>
       </c>
       <c r="G8" t="n">
-        <v>110.58</v>
+        <v>115.83</v>
       </c>
       <c r="H8" t="n">
-        <v>101.35</v>
+        <v>110.45</v>
       </c>
       <c r="I8" t="n">
-        <v>9.23</v>
+        <v>5.38</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3181</v>
+        <v>0.3093</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1536</v>
+        <v>0.1541</v>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N8" t="n">
+        <v>39</v>
+      </c>
+      <c r="O8" t="n">
+        <v>48</v>
+      </c>
+      <c r="P8" t="n">
         <v>42</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
+        <v>28</v>
+      </c>
+      <c r="R8" t="n">
         <v>46</v>
       </c>
-      <c r="P8" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>47</v>
-      </c>
-      <c r="R8" t="n">
-        <v>45</v>
-      </c>
       <c r="S8" t="n">
-        <v>1678</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="9">
@@ -3801,59 +3789,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1452</v>
+        <v>1153</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1692.7</v>
+        <v>1733.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3873</v>
+        <v>0.433</v>
       </c>
       <c r="G9" t="n">
-        <v>107.19</v>
+        <v>105.76</v>
       </c>
       <c r="H9" t="n">
-        <v>99.78</v>
+        <v>97.33</v>
       </c>
       <c r="I9" t="n">
-        <v>7.41</v>
+        <v>8.43</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2944</v>
+        <v>0.2897</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1659</v>
+        <v>0.1583</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4</v>
+        <v>10.6</v>
       </c>
       <c r="M9" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="P9" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R9" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="S9" t="n">
-        <v>1649.8</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="10">
@@ -3862,59 +3850,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1140</v>
+        <v>1452</v>
       </c>
       <c r="D10" t="n">
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1901.3</v>
+        <v>1692.7</v>
       </c>
       <c r="F10" t="n">
-        <v>2.827</v>
+        <v>0.3873</v>
       </c>
       <c r="G10" t="n">
-        <v>117.49</v>
+        <v>107.19</v>
       </c>
       <c r="H10" t="n">
-        <v>106.29</v>
+        <v>99.78</v>
       </c>
       <c r="I10" t="n">
-        <v>11.21</v>
+        <v>7.41</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2953</v>
+        <v>0.2944</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1466</v>
+        <v>0.1659</v>
       </c>
       <c r="L10" t="n">
-        <v>-8</v>
+        <v>-2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="N10" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="O10" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="R10" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="S10" t="n">
-        <v>1712.1</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="11">
@@ -3923,59 +3911,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1153</v>
+        <v>1140</v>
       </c>
       <c r="D11" t="n">
         <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1733.8</v>
+        <v>1901.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.433</v>
+        <v>2.827</v>
       </c>
       <c r="G11" t="n">
-        <v>105.76</v>
+        <v>117.49</v>
       </c>
       <c r="H11" t="n">
-        <v>97.33</v>
+        <v>106.29</v>
       </c>
       <c r="I11" t="n">
-        <v>8.43</v>
+        <v>11.21</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2897</v>
+        <v>0.2953</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1583</v>
+        <v>0.1466</v>
       </c>
       <c r="L11" t="n">
-        <v>10.6</v>
+        <v>-8</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="O11" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="P11" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="R11" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="S11" t="n">
-        <v>1713</v>
+        <v>1712.1</v>
       </c>
     </row>
     <row r="12">
@@ -4106,59 +4094,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Oklahoma St</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1124</v>
+        <v>1329</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1673.5</v>
+        <v>1713.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.3298</v>
+        <v>-1.1735</v>
       </c>
       <c r="G14" t="n">
-        <v>115.76</v>
+        <v>110.48</v>
       </c>
       <c r="H14" t="n">
-        <v>111.17</v>
+        <v>109.05</v>
       </c>
       <c r="I14" t="n">
-        <v>4.59</v>
+        <v>1.43</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3248</v>
+        <v>0.2757</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1611</v>
+        <v>0.156</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.6</v>
+        <v>-7</v>
       </c>
       <c r="M14" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="N14" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O14" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="P14" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="R14" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="S14" t="n">
-        <v>1725.5</v>
+        <v>1678.3</v>
       </c>
     </row>
     <row r="15">
@@ -4167,59 +4155,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oklahoma St</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1329</v>
+        <v>1124</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E15" t="n">
-        <v>1713.4</v>
+        <v>1671.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1735</v>
+        <v>-6.0193</v>
       </c>
       <c r="G15" t="n">
-        <v>110.48</v>
+        <v>114.76</v>
       </c>
       <c r="H15" t="n">
-        <v>109.05</v>
+        <v>111.24</v>
       </c>
       <c r="I15" t="n">
-        <v>1.43</v>
+        <v>3.51</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2757</v>
+        <v>0.3244</v>
       </c>
       <c r="K15" t="n">
-        <v>0.156</v>
+        <v>0.1668</v>
       </c>
       <c r="L15" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="M15" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="N15" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O15" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="P15" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="R15" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="S15" t="n">
-        <v>1678.3</v>
+        <v>1739.8</v>
       </c>
     </row>
     <row r="16">
@@ -4359,97 +4347,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4590,31 +4578,31 @@
         <v>1437</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1813.5</v>
+        <v>1820.1</v>
       </c>
       <c r="F4" t="n">
-        <v>6.893</v>
+        <v>6.5295</v>
       </c>
       <c r="G4" t="n">
-        <v>114.62</v>
+        <v>114.74</v>
       </c>
       <c r="H4" t="n">
-        <v>105.11</v>
+        <v>103.88</v>
       </c>
       <c r="I4" t="n">
-        <v>9.51</v>
+        <v>10.87</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3173</v>
+        <v>0.3148</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1412</v>
+        <v>0.141</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.8</v>
+        <v>-2.2</v>
       </c>
       <c r="M4" t="n">
         <v>34</v>
@@ -4635,7 +4623,7 @@
         <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>1649.2</v>
+        <v>1643.5</v>
       </c>
     </row>
     <row r="5">
@@ -4705,59 +4693,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1605.1</v>
+        <v>1672.5</v>
       </c>
       <c r="F6" t="n">
-        <v>5.8136</v>
+        <v>-1.8294</v>
       </c>
       <c r="G6" t="n">
-        <v>105.51</v>
+        <v>110.12</v>
       </c>
       <c r="H6" t="n">
-        <v>102.59</v>
+        <v>109.57</v>
       </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>0.55</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2994</v>
+        <v>0.2481</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1703</v>
+        <v>0.1544</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="N6" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q6" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="R6" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="S6" t="n">
-        <v>1597</v>
+        <v>1663.7</v>
       </c>
     </row>
     <row r="7">
@@ -4766,59 +4754,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1166</v>
+        <v>1177</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1661.7</v>
+        <v>1586.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7577</v>
+        <v>5.744</v>
       </c>
       <c r="G7" t="n">
-        <v>110.25</v>
+        <v>104.54</v>
       </c>
       <c r="H7" t="n">
-        <v>110.82</v>
+        <v>103.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.57</v>
+        <v>1.34</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2489</v>
+        <v>0.2937</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1555</v>
+        <v>0.1724</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.4</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="O7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q7" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R7" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="S7" t="n">
-        <v>1664.2</v>
+        <v>1607.9</v>
       </c>
     </row>
     <row r="8">
@@ -4834,31 +4822,31 @@
         <v>1344</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>1578.5</v>
+        <v>1568.8</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8443</v>
+        <v>1.8893</v>
       </c>
       <c r="G8" t="n">
-        <v>116.46</v>
+        <v>114.76</v>
       </c>
       <c r="H8" t="n">
-        <v>112.82</v>
+        <v>112.81</v>
       </c>
       <c r="I8" t="n">
-        <v>3.64</v>
+        <v>1.94</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2564</v>
+        <v>0.2627</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1547</v>
+        <v>0.1612</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2</v>
+        <v>-3.2</v>
       </c>
       <c r="M8" t="n">
         <v>63</v>
@@ -4879,7 +4867,7 @@
         <v>74</v>
       </c>
       <c r="S8" t="n">
-        <v>1644.9</v>
+        <v>1637.9</v>
       </c>
     </row>
     <row r="9">
@@ -4895,31 +4883,31 @@
         <v>1139</v>
       </c>
       <c r="D9" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1626.7</v>
+        <v>1616</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2252</v>
+        <v>1.0517</v>
       </c>
       <c r="G9" t="n">
-        <v>111.73</v>
+        <v>110.53</v>
       </c>
       <c r="H9" t="n">
-        <v>108.99</v>
+        <v>108.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.74</v>
+        <v>1.73</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3088</v>
+        <v>0.3033</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1503</v>
+        <v>0.1524</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="M9" t="n">
         <v>83</v>
@@ -4940,7 +4928,7 @@
         <v>80</v>
       </c>
       <c r="S9" t="n">
-        <v>1624.5</v>
+        <v>1623.7</v>
       </c>
     </row>
     <row r="10">
@@ -5010,59 +4998,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1207</v>
+        <v>1266</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1551.4</v>
+        <v>1517.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9935</v>
+        <v>-8.0067</v>
       </c>
       <c r="G11" t="n">
-        <v>109.71</v>
+        <v>104.9</v>
       </c>
       <c r="H11" t="n">
-        <v>109.01</v>
+        <v>105.24</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>-0.35</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3048</v>
+        <v>0.2997</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1487</v>
+        <v>0.1579</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.8</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
         <v>90</v>
       </c>
-      <c r="N11" t="n">
-        <v>95</v>
-      </c>
       <c r="O11" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="P11" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="Q11" t="n">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="R11" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="S11" t="n">
-        <v>1645.5</v>
+        <v>1658.7</v>
       </c>
     </row>
     <row r="12">
@@ -5071,59 +5059,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1266</v>
+        <v>1207</v>
       </c>
       <c r="D12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1496.1</v>
+        <v>1551.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.5199</v>
+        <v>-4.9935</v>
       </c>
       <c r="G12" t="n">
-        <v>104.29</v>
+        <v>109.71</v>
       </c>
       <c r="H12" t="n">
-        <v>106.45</v>
+        <v>109.01</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.16</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3007</v>
+        <v>0.3048</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1568</v>
+        <v>0.1487</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.4</v>
+        <v>-6.8</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O12" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P12" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="R12" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="S12" t="n">
-        <v>1661.5</v>
+        <v>1645.5</v>
       </c>
     </row>
   </sheetData>
@@ -5141,97 +5129,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5304,59 +5292,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1304</v>
+        <v>1277</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E3" t="n">
-        <v>1990.6</v>
+        <v>2050.3</v>
       </c>
       <c r="F3" t="n">
-        <v>11.3442</v>
+        <v>0.5431</v>
       </c>
       <c r="G3" t="n">
-        <v>115.07</v>
+        <v>116.95</v>
       </c>
       <c r="H3" t="n">
-        <v>98.04000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="I3" t="n">
-        <v>17.03</v>
+        <v>17.97</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2419</v>
+        <v>0.2979</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1401</v>
+        <v>0.1625</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>14</v>
+      </c>
+      <c r="R3" t="n">
         <v>11</v>
       </c>
-      <c r="N3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O3" t="n">
-        <v>12</v>
-      </c>
-      <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12</v>
-      </c>
       <c r="S3" t="n">
-        <v>1658</v>
+        <v>1712.3</v>
       </c>
     </row>
     <row r="4">
@@ -5365,59 +5353,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1277</v>
+        <v>1304</v>
       </c>
       <c r="D4" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>2050.3</v>
+        <v>1990.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5431</v>
+        <v>11.3442</v>
       </c>
       <c r="G4" t="n">
-        <v>116.95</v>
+        <v>115.07</v>
       </c>
       <c r="H4" t="n">
-        <v>98.98</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>17.97</v>
+        <v>17.03</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2979</v>
+        <v>0.2419</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1625</v>
+        <v>0.1401</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
-      <c r="N4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>14</v>
-      </c>
       <c r="R4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S4" t="n">
-        <v>1712.3</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="5">
@@ -5494,31 +5482,31 @@
         <v>1345</v>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1972.2</v>
+        <v>1976</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3222</v>
+        <v>0.8268</v>
       </c>
       <c r="G6" t="n">
-        <v>124.01</v>
+        <v>123.88</v>
       </c>
       <c r="H6" t="n">
-        <v>105.95</v>
+        <v>105.93</v>
       </c>
       <c r="I6" t="n">
-        <v>18.06</v>
+        <v>17.95</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2978</v>
+        <v>0.2977</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1321</v>
+        <v>0.1374</v>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
@@ -5539,7 +5527,7 @@
         <v>9</v>
       </c>
       <c r="S6" t="n">
-        <v>1747.3</v>
+        <v>1740.2</v>
       </c>
     </row>
     <row r="7">
@@ -5555,31 +5543,31 @@
         <v>1458</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1833.6</v>
+        <v>1837.7</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5562</v>
+        <v>0.7673</v>
       </c>
       <c r="G7" t="n">
-        <v>117.74</v>
+        <v>118.38</v>
       </c>
       <c r="H7" t="n">
-        <v>107.72</v>
+        <v>106.47</v>
       </c>
       <c r="I7" t="n">
-        <v>10.02</v>
+        <v>11.91</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2772</v>
+        <v>0.2733</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1264</v>
+        <v>0.1236</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="M7" t="n">
         <v>30</v>
@@ -5600,7 +5588,7 @@
         <v>32</v>
       </c>
       <c r="S7" t="n">
-        <v>1689.3</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="8">
@@ -5670,59 +5658,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1234</v>
+        <v>1326</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1821.4</v>
+        <v>1787.4</v>
       </c>
       <c r="F9" t="n">
-        <v>4.8208</v>
+        <v>1.3307</v>
       </c>
       <c r="G9" t="n">
-        <v>119.88</v>
+        <v>118.28</v>
       </c>
       <c r="H9" t="n">
-        <v>103.67</v>
+        <v>107.42</v>
       </c>
       <c r="I9" t="n">
-        <v>16.21</v>
+        <v>10.87</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2891</v>
+        <v>0.255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1416</v>
+        <v>0.1501</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.8</v>
+        <v>6.8</v>
       </c>
       <c r="M9" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="R9" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S9" t="n">
-        <v>1682.5</v>
+        <v>1694.2</v>
       </c>
     </row>
     <row r="10">
@@ -5731,59 +5719,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1326</v>
+        <v>1234</v>
       </c>
       <c r="D10" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" t="n">
-        <v>1782.1</v>
+        <v>1855.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1828</v>
+        <v>4.8208</v>
       </c>
       <c r="G10" t="n">
-        <v>117.32</v>
+        <v>119.88</v>
       </c>
       <c r="H10" t="n">
-        <v>108.16</v>
+        <v>103.67</v>
       </c>
       <c r="I10" t="n">
-        <v>9.16</v>
+        <v>16.21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2601</v>
+        <v>0.2891</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1481</v>
+        <v>0.1416</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4</v>
+        <v>-2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1704.7</v>
+        <v>1682.5</v>
       </c>
     </row>
     <row r="11">
@@ -5799,31 +5787,31 @@
         <v>1231</v>
       </c>
       <c r="D11" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1746.4</v>
+        <v>1752.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8012</v>
+        <v>-2.7312</v>
       </c>
       <c r="G11" t="n">
-        <v>115.78</v>
+        <v>116.39</v>
       </c>
       <c r="H11" t="n">
-        <v>107.65</v>
+        <v>106.14</v>
       </c>
       <c r="I11" t="n">
-        <v>8.130000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="J11" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1402</v>
+        <v>0.1415</v>
       </c>
       <c r="L11" t="n">
-        <v>-9.6</v>
+        <v>-7.2</v>
       </c>
       <c r="M11" t="n">
         <v>43</v>
@@ -5844,7 +5832,7 @@
         <v>41</v>
       </c>
       <c r="S11" t="n">
-        <v>1703.1</v>
+        <v>1695.9</v>
       </c>
     </row>
     <row r="12">
@@ -5853,59 +5841,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1425</v>
+        <v>1449</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E12" t="n">
-        <v>1770.8</v>
+        <v>1654.2</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1219</v>
+        <v>2.1014</v>
       </c>
       <c r="G12" t="n">
-        <v>108.37</v>
+        <v>111.56</v>
       </c>
       <c r="H12" t="n">
-        <v>107.72</v>
+        <v>105.96</v>
       </c>
       <c r="I12" t="n">
-        <v>0.64</v>
+        <v>5.61</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2924</v>
+        <v>0.3009</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1722</v>
+        <v>0.1501</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.6</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O12" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="P12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="R12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S12" t="n">
-        <v>1691.4</v>
+        <v>1689.2</v>
       </c>
     </row>
     <row r="13">
@@ -5914,59 +5902,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1278</v>
+        <v>1425</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E13" t="n">
-        <v>1623.1</v>
+        <v>1755.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0378</v>
+        <v>1.5224</v>
       </c>
       <c r="G13" t="n">
-        <v>111.88</v>
+        <v>107.92</v>
       </c>
       <c r="H13" t="n">
-        <v>107.72</v>
+        <v>108.19</v>
       </c>
       <c r="I13" t="n">
-        <v>4.16</v>
+        <v>-0.27</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2422</v>
+        <v>0.2952</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1542</v>
+        <v>0.1712</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8</v>
+        <v>-18</v>
       </c>
       <c r="M13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N13" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="O13" t="n">
+        <v>82</v>
+      </c>
+      <c r="P13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>52</v>
+      </c>
+      <c r="R13" t="n">
         <v>63</v>
       </c>
-      <c r="P13" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>96</v>
-      </c>
-      <c r="R13" t="n">
-        <v>68</v>
-      </c>
       <c r="S13" t="n">
-        <v>1677.8</v>
+        <v>1684.4</v>
       </c>
     </row>
     <row r="14">
@@ -5975,59 +5963,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1449</v>
+        <v>1278</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E14" t="n">
-        <v>1639.3</v>
+        <v>1616.9</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3162</v>
+        <v>0.1308</v>
       </c>
       <c r="G14" t="n">
-        <v>111.08</v>
+        <v>109.88</v>
       </c>
       <c r="H14" t="n">
-        <v>106.69</v>
+        <v>108.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.39</v>
+        <v>1.68</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2953</v>
+        <v>0.2483</v>
       </c>
       <c r="K14" t="n">
-        <v>0.15</v>
+        <v>0.1566</v>
       </c>
       <c r="L14" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N14" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="O14" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P14" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="R14" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="S14" t="n">
-        <v>1687.1</v>
+        <v>1678.8</v>
       </c>
     </row>
     <row r="15">
@@ -6104,31 +6092,31 @@
         <v>1321</v>
       </c>
       <c r="D16" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>1595.5</v>
+        <v>1591.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.1956</v>
+        <v>-4.6981</v>
       </c>
       <c r="G16" t="n">
-        <v>110.12</v>
+        <v>110.63</v>
       </c>
       <c r="H16" t="n">
-        <v>108.88</v>
+        <v>109.75</v>
       </c>
       <c r="I16" t="n">
-        <v>1.24</v>
+        <v>0.87</v>
       </c>
       <c r="J16" t="n">
-        <v>0.273</v>
+        <v>0.2719</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1275</v>
+        <v>0.1268</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.4</v>
+        <v>-2.8</v>
       </c>
       <c r="M16" t="n">
         <v>68</v>
@@ -6149,7 +6137,7 @@
         <v>72</v>
       </c>
       <c r="S16" t="n">
-        <v>1692.6</v>
+        <v>1705.7</v>
       </c>
     </row>
     <row r="17">
@@ -6226,31 +6214,31 @@
         <v>1268</v>
       </c>
       <c r="D18" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E18" t="n">
-        <v>1584.4</v>
+        <v>1598.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.259399999999999</v>
+        <v>-7.9559</v>
       </c>
       <c r="G18" t="n">
-        <v>103.79</v>
+        <v>102.77</v>
       </c>
       <c r="H18" t="n">
-        <v>113.48</v>
+        <v>114.81</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.69</v>
+        <v>-12.04</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3183</v>
+        <v>0.3181</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1789</v>
+        <v>0.1773</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.6</v>
+        <v>-10</v>
       </c>
       <c r="M18" t="n">
         <v>130</v>
@@ -6271,7 +6259,7 @@
         <v>146</v>
       </c>
       <c r="S18" t="n">
-        <v>1703.6</v>
+        <v>1712.3</v>
       </c>
     </row>
     <row r="19">
@@ -6287,31 +6275,31 @@
         <v>1336</v>
       </c>
       <c r="D19" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E19" t="n">
-        <v>1570.6</v>
+        <v>1531.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.9364</v>
+        <v>-7.5446</v>
       </c>
       <c r="G19" t="n">
-        <v>110.93</v>
+        <v>110.14</v>
       </c>
       <c r="H19" t="n">
-        <v>117.12</v>
+        <v>118.59</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.19</v>
+        <v>-8.44</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2682</v>
+        <v>0.2617</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1505</v>
+        <v>0.1492</v>
       </c>
       <c r="L19" t="n">
-        <v>-8.4</v>
+        <v>-15.4</v>
       </c>
       <c r="M19" t="n">
         <v>128</v>
@@ -6332,7 +6320,7 @@
         <v>125</v>
       </c>
       <c r="S19" t="n">
-        <v>1667.7</v>
+        <v>1669.9</v>
       </c>
     </row>
   </sheetData>
@@ -6350,97 +6338,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6818,59 +6806,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C Michigan</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1341.3</v>
+        <v>1391.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8296</v>
+        <v>-0.2165</v>
       </c>
       <c r="G8" t="n">
-        <v>105.75</v>
+        <v>114.44</v>
       </c>
       <c r="H8" t="n">
-        <v>114.35</v>
+        <v>111.83</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.6</v>
+        <v>2.61</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2991</v>
+        <v>0.2726</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1727</v>
+        <v>0.1568</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="N8" t="n">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="O8" t="n">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="P8" t="n">
-        <v>274</v>
+        <v>194</v>
       </c>
       <c r="Q8" t="n">
-        <v>301</v>
+        <v>178</v>
       </c>
       <c r="R8" t="n">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="S8" t="n">
-        <v>1477</v>
+        <v>1459.5</v>
       </c>
     </row>
     <row r="9">
@@ -6879,59 +6867,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1138</v>
+        <v>1269</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1391.4</v>
+        <v>1478.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2165</v>
+        <v>1.0696</v>
       </c>
       <c r="G9" t="n">
-        <v>114.44</v>
+        <v>109.4</v>
       </c>
       <c r="H9" t="n">
-        <v>111.83</v>
+        <v>107.53</v>
       </c>
       <c r="I9" t="n">
-        <v>2.61</v>
+        <v>1.87</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2726</v>
+        <v>0.2938</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1568</v>
+        <v>0.1727</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4</v>
+        <v>-4.2</v>
       </c>
       <c r="M9" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="N9" t="n">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="O9" t="n">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="P9" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Q9" t="n">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="R9" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="S9" t="n">
-        <v>1459.5</v>
+        <v>1451.7</v>
       </c>
     </row>
   </sheetData>
@@ -6949,97 +6937,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7731,97 +7719,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7901,31 +7889,31 @@
         <v>1307</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>1847</v>
+        <v>1825.3</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3818</v>
+        <v>4.1386</v>
       </c>
       <c r="G3" t="n">
-        <v>114.73</v>
+        <v>114.16</v>
       </c>
       <c r="H3" t="n">
-        <v>100.98</v>
+        <v>101.47</v>
       </c>
       <c r="I3" t="n">
-        <v>13.75</v>
+        <v>12.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2694</v>
+        <v>0.2721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.143</v>
+        <v>0.1448</v>
       </c>
       <c r="L3" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
         <v>46</v>
@@ -7946,7 +7934,7 @@
         <v>42</v>
       </c>
       <c r="S3" t="n">
-        <v>1589.8</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="4">
@@ -8016,59 +8004,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Grand Canyon</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1305</v>
+        <v>1213</v>
       </c>
       <c r="D5" t="n">
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1738.9</v>
+        <v>1722.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3067</v>
+        <v>6.6005</v>
       </c>
       <c r="G5" t="n">
-        <v>112.85</v>
+        <v>109.82</v>
       </c>
       <c r="H5" t="n">
-        <v>107.41</v>
+        <v>99.62</v>
       </c>
       <c r="I5" t="n">
-        <v>5.44</v>
+        <v>10.21</v>
       </c>
       <c r="J5" t="n">
-        <v>0.305</v>
+        <v>0.2757</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1405</v>
+        <v>0.1736</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.6</v>
+        <v>7.8</v>
       </c>
       <c r="M5" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="N5" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="O5" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="P5" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="R5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>1614.5</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="6">
@@ -8077,59 +8065,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grand Canyon</t>
+          <t>Colorado St</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1213</v>
+        <v>1161</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1722.6</v>
+        <v>1673.6</v>
       </c>
       <c r="F6" t="n">
-        <v>6.6005</v>
+        <v>-5.2938</v>
       </c>
       <c r="G6" t="n">
-        <v>109.82</v>
+        <v>119.56</v>
       </c>
       <c r="H6" t="n">
-        <v>99.62</v>
+        <v>112.77</v>
       </c>
       <c r="I6" t="n">
-        <v>10.21</v>
+        <v>6.79</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2757</v>
+        <v>0.256</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1736</v>
+        <v>0.1771</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="N6" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O6" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="P6" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R6" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="S6" t="n">
-        <v>1577</v>
+        <v>1559.4</v>
       </c>
     </row>
     <row r="7">
@@ -8138,59 +8126,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1161</v>
+        <v>1129</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1651.9</v>
+        <v>1727.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.6123</v>
+        <v>-2.3169</v>
       </c>
       <c r="G7" t="n">
-        <v>120.05</v>
+        <v>113.86</v>
       </c>
       <c r="H7" t="n">
-        <v>113.29</v>
+        <v>107.08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2615</v>
+        <v>0.2821</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1721</v>
+        <v>0.1603</v>
       </c>
       <c r="L7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="M7" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="N7" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="O7" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="P7" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="R7" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="S7" t="n">
-        <v>1542.5</v>
+        <v>1623.5</v>
       </c>
     </row>
     <row r="8">
@@ -8199,59 +8187,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1129</v>
+        <v>1305</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1727.7</v>
+        <v>1738.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3169</v>
+        <v>7.3067</v>
       </c>
       <c r="G8" t="n">
-        <v>113.86</v>
+        <v>112.85</v>
       </c>
       <c r="H8" t="n">
-        <v>107.08</v>
+        <v>107.41</v>
       </c>
       <c r="I8" t="n">
-        <v>6.78</v>
+        <v>5.44</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2821</v>
+        <v>0.305</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1603</v>
+        <v>0.1405</v>
       </c>
       <c r="L8" t="n">
-        <v>6.2</v>
+        <v>-3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O8" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P8" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="S8" t="n">
-        <v>1623.5</v>
+        <v>1614.5</v>
       </c>
     </row>
     <row r="9">
@@ -8574,97 +8562,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8805,31 +8793,31 @@
         <v>1116</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1925.2</v>
+        <v>1932.7</v>
       </c>
       <c r="F4" t="n">
-        <v>7.1116</v>
+        <v>6.7834</v>
       </c>
       <c r="G4" t="n">
-        <v>122.37</v>
+        <v>123.18</v>
       </c>
       <c r="H4" t="n">
-        <v>109.06</v>
+        <v>108.72</v>
       </c>
       <c r="I4" t="n">
-        <v>13.31</v>
+        <v>14.46</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3062</v>
+        <v>0.2975</v>
       </c>
       <c r="K4" t="n">
-        <v>0.119</v>
+        <v>0.1194</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>20</v>
@@ -8850,7 +8838,7 @@
         <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>1726.1</v>
+        <v>1725.9</v>
       </c>
     </row>
     <row r="5">
@@ -8859,59 +8847,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1281</v>
+        <v>1397</v>
       </c>
       <c r="D5" t="n">
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1768.2</v>
+        <v>1912.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8893</v>
+        <v>-1.7463</v>
       </c>
       <c r="G5" t="n">
-        <v>115.23</v>
+        <v>117.37</v>
       </c>
       <c r="H5" t="n">
-        <v>109.22</v>
+        <v>101.08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.01</v>
+        <v>16.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3029</v>
+        <v>0.3535</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1713</v>
+        <v>0.1667</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="N5" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="S5" t="n">
-        <v>1637.7</v>
+        <v>1692.2</v>
       </c>
     </row>
     <row r="6">
@@ -8920,59 +8908,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1246</v>
+        <v>1281</v>
       </c>
       <c r="D6" t="n">
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1893.4</v>
+        <v>1768.2</v>
       </c>
       <c r="F6" t="n">
-        <v>6.006</v>
+        <v>-2.8893</v>
       </c>
       <c r="G6" t="n">
-        <v>116.85</v>
+        <v>115.23</v>
       </c>
       <c r="H6" t="n">
-        <v>105.78</v>
+        <v>109.22</v>
       </c>
       <c r="I6" t="n">
-        <v>11.07</v>
+        <v>6.01</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3101</v>
+        <v>0.3029</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1466</v>
+        <v>0.1713</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O6" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="S6" t="n">
-        <v>1717.2</v>
+        <v>1637.7</v>
       </c>
     </row>
     <row r="7">
@@ -8981,59 +8969,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1397</v>
+        <v>1435</v>
       </c>
       <c r="D7" t="n">
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1912.8</v>
+        <v>1921</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7463</v>
+        <v>1.9274</v>
       </c>
       <c r="G7" t="n">
-        <v>117.37</v>
+        <v>121.87</v>
       </c>
       <c r="H7" t="n">
-        <v>101.08</v>
+        <v>105.42</v>
       </c>
       <c r="I7" t="n">
-        <v>16.3</v>
+        <v>16.45</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3535</v>
+        <v>0.2854</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1667</v>
+        <v>0.1247</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>-1.6</v>
       </c>
       <c r="M7" t="n">
+        <v>14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" t="n">
         <v>18</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>16</v>
       </c>
-      <c r="O7" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" t="n">
-        <v>20</v>
-      </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>1692.2</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="8">
@@ -9042,59 +9030,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1785.1</v>
+        <v>1836.9</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0552</v>
+        <v>4.4256</v>
       </c>
       <c r="G8" t="n">
-        <v>121.1</v>
+        <v>118.62</v>
       </c>
       <c r="H8" t="n">
-        <v>110.26</v>
+        <v>106.73</v>
       </c>
       <c r="I8" t="n">
-        <v>10.85</v>
+        <v>11.89</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3116</v>
+        <v>0.3028</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1505</v>
+        <v>0.1406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="R8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
-        <v>1691.9</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="9">
@@ -9103,59 +9091,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1435</v>
+        <v>1246</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1921</v>
+        <v>1893.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9274</v>
+        <v>6.006</v>
       </c>
       <c r="G9" t="n">
-        <v>121.87</v>
+        <v>116.85</v>
       </c>
       <c r="H9" t="n">
-        <v>105.42</v>
+        <v>105.78</v>
       </c>
       <c r="I9" t="n">
-        <v>16.45</v>
+        <v>11.07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2854</v>
+        <v>0.3101</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1247</v>
+        <v>0.1466</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="R9" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="S9" t="n">
-        <v>1684</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="10">
@@ -9164,59 +9152,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1401</v>
+        <v>1208</v>
       </c>
       <c r="D10" t="n">
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1836.9</v>
+        <v>1810.7</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4256</v>
+        <v>-0.8284</v>
       </c>
       <c r="G10" t="n">
-        <v>118.62</v>
+        <v>120.8</v>
       </c>
       <c r="H10" t="n">
-        <v>106.73</v>
+        <v>106.43</v>
       </c>
       <c r="I10" t="n">
-        <v>11.89</v>
+        <v>14.38</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3028</v>
+        <v>0.3238</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1406</v>
+        <v>0.1381</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="n">
         <v>39</v>
       </c>
-      <c r="Q10" t="n">
-        <v>41</v>
-      </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="S10" t="n">
-        <v>1655.1</v>
+        <v>1647.3</v>
       </c>
     </row>
     <row r="11">
@@ -9225,59 +9213,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1208</v>
+        <v>1400</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1810.7</v>
+        <v>1777.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8284</v>
+        <v>2.2904</v>
       </c>
       <c r="G11" t="n">
-        <v>120.8</v>
+        <v>120.67</v>
       </c>
       <c r="H11" t="n">
-        <v>106.43</v>
+        <v>111.46</v>
       </c>
       <c r="I11" t="n">
-        <v>14.38</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3238</v>
+        <v>0.3123</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1381</v>
+        <v>0.1488</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>-7</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="S11" t="n">
-        <v>1647.3</v>
+        <v>1700.7</v>
       </c>
     </row>
     <row r="12">
@@ -9347,59 +9335,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mississippi St</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1280</v>
+        <v>1328</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1633.2</v>
+        <v>1687.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2844</v>
+        <v>-3.1749</v>
       </c>
       <c r="G13" t="n">
-        <v>106.96</v>
+        <v>119.85</v>
       </c>
       <c r="H13" t="n">
-        <v>112.13</v>
+        <v>111.64</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.279</v>
+        <v>0.3131</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1541</v>
+        <v>0.1429</v>
       </c>
       <c r="L13" t="n">
-        <v>-17</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O13" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="Q13" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="R13" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="S13" t="n">
-        <v>1702.1</v>
+        <v>1659.4</v>
       </c>
     </row>
     <row r="14">
@@ -9408,59 +9396,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Mississippi St</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1328</v>
+        <v>1280</v>
       </c>
       <c r="D14" t="n">
         <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1687.4</v>
+        <v>1633.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1749</v>
+        <v>-2.2844</v>
       </c>
       <c r="G14" t="n">
-        <v>119.85</v>
+        <v>106.96</v>
       </c>
       <c r="H14" t="n">
-        <v>111.64</v>
+        <v>112.13</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3131</v>
+        <v>0.279</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1429</v>
+        <v>0.1541</v>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>-17</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="N14" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="O14" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="P14" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="R14" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="S14" t="n">
-        <v>1659.4</v>
+        <v>1702.1</v>
       </c>
     </row>
     <row r="15">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -26,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +54,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,97 +438,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -535,31 +547,31 @@
         <v>1387</v>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>1825.9</v>
+        <v>1828.2</v>
       </c>
       <c r="F2" t="n">
-        <v>10.4518</v>
+        <v>11.0707</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>121.57</v>
       </c>
       <c r="H2" t="n">
-        <v>96.95</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2326</v>
+        <v>0.2343</v>
       </c>
       <c r="K2" t="n">
-        <v>0.167</v>
+        <v>0.1691</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>27</v>
@@ -580,7 +592,7 @@
         <v>24</v>
       </c>
       <c r="S2" t="n">
-        <v>1501.8</v>
+        <v>1506.9</v>
       </c>
     </row>
     <row r="3">
@@ -657,31 +669,31 @@
         <v>1386</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1610.2</v>
+        <v>1618.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6493</v>
+        <v>0.2798</v>
       </c>
       <c r="G4" t="n">
-        <v>104.92</v>
+        <v>104.61</v>
       </c>
       <c r="H4" t="n">
-        <v>102.36</v>
+        <v>102.08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2837</v>
+        <v>0.2886</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1632</v>
+        <v>0.1617</v>
       </c>
       <c r="L4" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>132</v>
@@ -702,7 +714,7 @@
         <v>132</v>
       </c>
       <c r="S4" t="n">
-        <v>1512.1</v>
+        <v>1511.9</v>
       </c>
     </row>
     <row r="5">
@@ -840,31 +852,31 @@
         <v>1172</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E7" t="n">
-        <v>1523</v>
+        <v>1534.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.809</v>
+        <v>-2.9764</v>
       </c>
       <c r="G7" t="n">
-        <v>108.88</v>
+        <v>109.14</v>
       </c>
       <c r="H7" t="n">
-        <v>105.54</v>
+        <v>105.34</v>
       </c>
       <c r="I7" t="n">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2845</v>
+        <v>0.2905</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1555</v>
+        <v>0.1611</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>106</v>
@@ -885,7 +897,7 @@
         <v>105</v>
       </c>
       <c r="S7" t="n">
-        <v>1542.6</v>
+        <v>1538.2</v>
       </c>
     </row>
     <row r="8">
@@ -901,31 +913,31 @@
         <v>1182</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>1476.6</v>
+        <v>1477.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3487</v>
+        <v>-2.5766</v>
       </c>
       <c r="G8" t="n">
-        <v>108.08</v>
+        <v>109.56</v>
       </c>
       <c r="H8" t="n">
-        <v>107.04</v>
+        <v>107.88</v>
       </c>
       <c r="I8" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2829</v>
+        <v>0.2809</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1768</v>
+        <v>0.1707</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.800000000000001</v>
+        <v>-6.4</v>
       </c>
       <c r="M8" t="n">
         <v>125</v>
@@ -946,7 +958,7 @@
         <v>131</v>
       </c>
       <c r="S8" t="n">
-        <v>1541.8</v>
+        <v>1544.2</v>
       </c>
     </row>
     <row r="9">
@@ -955,59 +967,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G Washington</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1540.4</v>
+        <v>1460.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3148</v>
+        <v>0.9714</v>
       </c>
       <c r="G9" t="n">
-        <v>116.28</v>
+        <v>103.92</v>
       </c>
       <c r="H9" t="n">
-        <v>105.4</v>
+        <v>102.4</v>
       </c>
       <c r="I9" t="n">
-        <v>10.88</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3229</v>
+        <v>0.3108</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1749</v>
+        <v>0.1628</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>-0.8</v>
       </c>
       <c r="M9" t="n">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="N9" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="O9" t="n">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="Q9" t="n">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="R9" t="n">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="S9" t="n">
-        <v>1537.4</v>
+        <v>1502.1</v>
       </c>
     </row>
     <row r="10">
@@ -1016,59 +1028,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>G Washington</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E10" t="n">
-        <v>1456.7</v>
+        <v>1511.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1066</v>
+        <v>-4.4633</v>
       </c>
       <c r="G10" t="n">
-        <v>105.16</v>
+        <v>115.96</v>
       </c>
       <c r="H10" t="n">
-        <v>103.59</v>
+        <v>105.35</v>
       </c>
       <c r="I10" t="n">
-        <v>1.57</v>
+        <v>10.61</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3183</v>
+        <v>0.3232</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1588</v>
+        <v>0.1782</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="N10" t="n">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="O10" t="n">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="P10" t="n">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="R10" t="n">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="S10" t="n">
-        <v>1494.5</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="11">
@@ -1084,31 +1096,31 @@
         <v>1348</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E11" t="n">
-        <v>1573.4</v>
+        <v>1553.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7869</v>
+        <v>0.859</v>
       </c>
       <c r="G11" t="n">
-        <v>105.82</v>
+        <v>105.72</v>
       </c>
       <c r="H11" t="n">
-        <v>102.05</v>
+        <v>102.88</v>
       </c>
       <c r="I11" t="n">
-        <v>3.77</v>
+        <v>2.85</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3055</v>
+        <v>0.3066</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1789</v>
+        <v>0.1764</v>
       </c>
       <c r="L11" t="n">
-        <v>-4</v>
+        <v>-7.2</v>
       </c>
       <c r="M11" t="n">
         <v>137</v>
@@ -1129,7 +1141,7 @@
         <v>141</v>
       </c>
       <c r="S11" t="n">
-        <v>1518.9</v>
+        <v>1521.9</v>
       </c>
     </row>
     <row r="12">
@@ -1206,31 +1218,31 @@
         <v>1247</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E13" t="n">
-        <v>1400.4</v>
+        <v>1392.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1985</v>
+        <v>-2.3737</v>
       </c>
       <c r="G13" t="n">
-        <v>99.5</v>
+        <v>98.06</v>
       </c>
       <c r="H13" t="n">
-        <v>110.35</v>
+        <v>109.65</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.85</v>
+        <v>-11.59</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3276</v>
+        <v>0.3245</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1795</v>
+        <v>0.1807</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.8</v>
+        <v>-6.2</v>
       </c>
       <c r="M13" t="n">
         <v>229</v>
@@ -1251,7 +1263,7 @@
         <v>239</v>
       </c>
       <c r="S13" t="n">
-        <v>1562.2</v>
+        <v>1566.7</v>
       </c>
     </row>
     <row r="14">
@@ -1267,31 +1279,31 @@
         <v>1382</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E14" t="n">
-        <v>1531.8</v>
+        <v>1541.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.8443</v>
+        <v>-9.021100000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>111.57</v>
+        <v>111.7</v>
       </c>
       <c r="H14" t="n">
-        <v>111.05</v>
+        <v>110.92</v>
       </c>
       <c r="I14" t="n">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3194</v>
+        <v>0.3187</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1633</v>
+        <v>0.1608</v>
       </c>
       <c r="L14" t="n">
-        <v>-3</v>
+        <v>-2.2</v>
       </c>
       <c r="M14" t="n">
         <v>150</v>
@@ -1312,7 +1324,7 @@
         <v>149</v>
       </c>
       <c r="S14" t="n">
-        <v>1532.1</v>
+        <v>1535.2</v>
       </c>
     </row>
     <row r="15">
@@ -1328,31 +1340,31 @@
         <v>1260</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E15" t="n">
-        <v>1390.9</v>
+        <v>1392</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.2873</v>
+        <v>-4.4275</v>
       </c>
       <c r="G15" t="n">
-        <v>100.15</v>
+        <v>99.75</v>
       </c>
       <c r="H15" t="n">
-        <v>115.52</v>
+        <v>114.41</v>
       </c>
       <c r="I15" t="n">
-        <v>-15.37</v>
+        <v>-14.66</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2854</v>
+        <v>0.2838</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1902</v>
+        <v>0.1903</v>
       </c>
       <c r="L15" t="n">
-        <v>-11</v>
+        <v>-12.2</v>
       </c>
       <c r="M15" t="n">
         <v>306</v>
@@ -1373,7 +1385,7 @@
         <v>303</v>
       </c>
       <c r="S15" t="n">
-        <v>1562.8</v>
+        <v>1548.6</v>
       </c>
     </row>
   </sheetData>
@@ -1391,97 +1403,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2234,97 +2246,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2465,31 +2477,31 @@
         <v>1274</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1773.8</v>
+        <v>1757.4</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7945</v>
+        <v>13.1837</v>
       </c>
       <c r="G4" t="n">
-        <v>117.09</v>
+        <v>117.38</v>
       </c>
       <c r="H4" t="n">
-        <v>99.90000000000001</v>
+        <v>99.64</v>
       </c>
       <c r="I4" t="n">
-        <v>17.19</v>
+        <v>17.74</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3061</v>
+        <v>0.3063</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1624</v>
+        <v>0.1591</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
@@ -2510,7 +2522,7 @@
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>1607.1</v>
+        <v>1596.7</v>
       </c>
     </row>
     <row r="5">
@@ -2641,59 +2653,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1257</v>
+        <v>1301</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" t="n">
-        <v>1830.2</v>
+        <v>1751.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.7351</v>
+        <v>8.2582</v>
       </c>
       <c r="G7" t="n">
-        <v>119.03</v>
+        <v>118.51</v>
       </c>
       <c r="H7" t="n">
-        <v>100.17</v>
+        <v>107.99</v>
       </c>
       <c r="I7" t="n">
-        <v>18.86</v>
+        <v>10.52</v>
       </c>
       <c r="J7" t="n">
-        <v>0.29</v>
+        <v>0.2827</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1596</v>
+        <v>0.1274</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="O7" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="S7" t="n">
-        <v>1675</v>
+        <v>1678.8</v>
       </c>
     </row>
     <row r="8">
@@ -2702,59 +2714,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1301</v>
+        <v>1257</v>
       </c>
       <c r="D8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1751.4</v>
+        <v>1830.2</v>
       </c>
       <c r="F8" t="n">
-        <v>8.2582</v>
+        <v>-3.7351</v>
       </c>
       <c r="G8" t="n">
-        <v>118.51</v>
+        <v>119.03</v>
       </c>
       <c r="H8" t="n">
-        <v>107.99</v>
+        <v>100.17</v>
       </c>
       <c r="I8" t="n">
-        <v>10.52</v>
+        <v>18.86</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2827</v>
+        <v>0.29</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1274</v>
+        <v>0.1596</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O8" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="S8" t="n">
-        <v>1678.8</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="9">
@@ -2763,59 +2775,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Florida St</t>
+          <t>California</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1199</v>
+        <v>1143</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1606</v>
+        <v>1697.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2483</v>
+        <v>8.4321</v>
       </c>
       <c r="G9" t="n">
-        <v>110.66</v>
+        <v>109.39</v>
       </c>
       <c r="H9" t="n">
-        <v>107.46</v>
+        <v>103.55</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>5.84</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3177</v>
+        <v>0.2286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1509</v>
+        <v>0.1474</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>-0.4</v>
       </c>
       <c r="M9" t="n">
+        <v>73</v>
+      </c>
+      <c r="N9" t="n">
+        <v>66</v>
+      </c>
+      <c r="O9" t="n">
         <v>71</v>
       </c>
-      <c r="N9" t="n">
-        <v>80</v>
-      </c>
-      <c r="O9" t="n">
-        <v>74</v>
-      </c>
       <c r="P9" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q9" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="R9" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="S9" t="n">
-        <v>1647.5</v>
+        <v>1603.7</v>
       </c>
     </row>
     <row r="10">
@@ -2824,59 +2836,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1143</v>
+        <v>1374</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E10" t="n">
-        <v>1728.5</v>
+        <v>1770.1</v>
       </c>
       <c r="F10" t="n">
-        <v>8.044</v>
+        <v>1.6059</v>
       </c>
       <c r="G10" t="n">
-        <v>109.41</v>
+        <v>119.38</v>
       </c>
       <c r="H10" t="n">
-        <v>102.71</v>
+        <v>110.1</v>
       </c>
       <c r="I10" t="n">
-        <v>6.7</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.227</v>
+        <v>0.3004</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1448</v>
+        <v>0.1491</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="N10" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="O10" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="P10" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="R10" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="S10" t="n">
-        <v>1599.2</v>
+        <v>1642.4</v>
       </c>
     </row>
     <row r="11">
@@ -2885,59 +2897,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Florida St</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1390</v>
+        <v>1199</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E11" t="n">
-        <v>1733.6</v>
+        <v>1599</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8143</v>
+        <v>-1.7495</v>
       </c>
       <c r="G11" t="n">
-        <v>111.86</v>
+        <v>110.62</v>
       </c>
       <c r="H11" t="n">
-        <v>106.91</v>
+        <v>107.19</v>
       </c>
       <c r="I11" t="n">
-        <v>4.95</v>
+        <v>3.43</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3137</v>
+        <v>0.3205</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1439</v>
+        <v>0.1501</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="O11" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="P11" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="R11" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S11" t="n">
-        <v>1622</v>
+        <v>1651.4</v>
       </c>
     </row>
     <row r="12">
@@ -2946,59 +2958,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1374</v>
+        <v>1390</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E12" t="n">
-        <v>1753.7</v>
+        <v>1726</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2979</v>
+        <v>3.1148</v>
       </c>
       <c r="G12" t="n">
-        <v>118.53</v>
+        <v>111.23</v>
       </c>
       <c r="H12" t="n">
-        <v>109.67</v>
+        <v>106.28</v>
       </c>
       <c r="I12" t="n">
-        <v>8.859999999999999</v>
+        <v>4.95</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3029</v>
+        <v>0.316</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1516</v>
+        <v>0.145</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="N12" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="O12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="R12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="S12" t="n">
-        <v>1646.7</v>
+        <v>1626.4</v>
       </c>
     </row>
     <row r="13">
@@ -3197,31 +3209,31 @@
         <v>1338</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E16" t="n">
-        <v>1510.7</v>
+        <v>1544.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.4673</v>
+        <v>-5.8166</v>
       </c>
       <c r="G16" t="n">
-        <v>106.74</v>
+        <v>106.44</v>
       </c>
       <c r="H16" t="n">
-        <v>109.24</v>
+        <v>108.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5</v>
+        <v>-2.13</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3257</v>
+        <v>0.3221</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1677</v>
+        <v>0.1696</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4</v>
+        <v>-3.4</v>
       </c>
       <c r="M16" t="n">
         <v>99</v>
@@ -3242,7 +3254,7 @@
         <v>110</v>
       </c>
       <c r="S16" t="n">
-        <v>1660.9</v>
+        <v>1665.2</v>
       </c>
     </row>
   </sheetData>
@@ -3260,97 +3272,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -3430,31 +3442,31 @@
         <v>1222</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>2085.1</v>
+        <v>2083.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.67</v>
+        <v>3.0302</v>
       </c>
       <c r="G3" t="n">
-        <v>117.81</v>
+        <v>118.12</v>
       </c>
       <c r="H3" t="n">
-        <v>94.78</v>
+        <v>94.48</v>
       </c>
       <c r="I3" t="n">
-        <v>23.03</v>
+        <v>23.64</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3414</v>
+        <v>0.3382</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1193</v>
+        <v>0.1188</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -3475,7 +3487,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1703.4</v>
+        <v>1703.5</v>
       </c>
     </row>
     <row r="4">
@@ -3545,59 +3557,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="D5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>2030.1</v>
+        <v>1972.3</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0314</v>
+        <v>11.3738</v>
       </c>
       <c r="G5" t="n">
-        <v>118.09</v>
+        <v>110.16</v>
       </c>
       <c r="H5" t="n">
-        <v>96.43000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="I5" t="n">
-        <v>21.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3174</v>
+        <v>0.2509</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1477</v>
+        <v>0.1535</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.2</v>
+        <v>-4.8</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S5" t="n">
-        <v>1692.3</v>
+        <v>1777.3</v>
       </c>
     </row>
     <row r="6">
@@ -3606,59 +3618,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6" t="n">
-        <v>1972.3</v>
+        <v>2030.1</v>
       </c>
       <c r="F6" t="n">
-        <v>11.3738</v>
+        <v>3.0314</v>
       </c>
       <c r="G6" t="n">
-        <v>110.16</v>
+        <v>118.09</v>
       </c>
       <c r="H6" t="n">
-        <v>100.46</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>9.699999999999999</v>
+        <v>21.66</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2509</v>
+        <v>0.3174</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1535</v>
+        <v>0.1477</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.8</v>
+        <v>-3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>1777.3</v>
+        <v>1692.3</v>
       </c>
     </row>
     <row r="7">
@@ -3667,59 +3679,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1395</v>
+        <v>1416</v>
       </c>
       <c r="D7" t="n">
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1824.2</v>
+        <v>1839.8</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8019</v>
+        <v>7.5365</v>
       </c>
       <c r="G7" t="n">
-        <v>110.58</v>
+        <v>115.83</v>
       </c>
       <c r="H7" t="n">
-        <v>101.35</v>
+        <v>110.45</v>
       </c>
       <c r="I7" t="n">
-        <v>9.23</v>
+        <v>5.38</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3181</v>
+        <v>0.3093</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1536</v>
+        <v>0.1541</v>
       </c>
       <c r="L7" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N7" t="n">
+        <v>39</v>
+      </c>
+      <c r="O7" t="n">
+        <v>48</v>
+      </c>
+      <c r="P7" t="n">
         <v>42</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
+        <v>28</v>
+      </c>
+      <c r="R7" t="n">
         <v>46</v>
       </c>
-      <c r="P7" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>47</v>
-      </c>
-      <c r="R7" t="n">
-        <v>45</v>
-      </c>
       <c r="S7" t="n">
-        <v>1678</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="8">
@@ -3728,59 +3740,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>1395</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1839.8</v>
+        <v>1824.2</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5365</v>
+        <v>6.8019</v>
       </c>
       <c r="G8" t="n">
-        <v>115.83</v>
+        <v>110.58</v>
       </c>
       <c r="H8" t="n">
-        <v>110.45</v>
+        <v>101.35</v>
       </c>
       <c r="I8" t="n">
-        <v>5.38</v>
+        <v>9.23</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3093</v>
+        <v>0.3181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1541</v>
+        <v>0.1536</v>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S8" t="n">
-        <v>1687.9</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="9">
@@ -3789,59 +3801,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1153</v>
+        <v>1452</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1733.8</v>
+        <v>1692.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.433</v>
+        <v>0.3873</v>
       </c>
       <c r="G9" t="n">
-        <v>105.76</v>
+        <v>107.19</v>
       </c>
       <c r="H9" t="n">
-        <v>97.33</v>
+        <v>99.78</v>
       </c>
       <c r="I9" t="n">
-        <v>8.43</v>
+        <v>7.41</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2897</v>
+        <v>0.2944</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1583</v>
+        <v>0.1659</v>
       </c>
       <c r="L9" t="n">
-        <v>10.6</v>
+        <v>-2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q9" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R9" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S9" t="n">
-        <v>1713</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="10">
@@ -3850,59 +3862,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1452</v>
+        <v>1140</v>
       </c>
       <c r="D10" t="n">
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1692.7</v>
+        <v>1901.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3873</v>
+        <v>2.827</v>
       </c>
       <c r="G10" t="n">
-        <v>107.19</v>
+        <v>117.49</v>
       </c>
       <c r="H10" t="n">
-        <v>99.78</v>
+        <v>106.29</v>
       </c>
       <c r="I10" t="n">
-        <v>7.41</v>
+        <v>11.21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2944</v>
+        <v>0.2953</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1659</v>
+        <v>0.1466</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4</v>
+        <v>-8</v>
       </c>
       <c r="M10" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="N10" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="O10" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="P10" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="S10" t="n">
-        <v>1649.8</v>
+        <v>1712.1</v>
       </c>
     </row>
     <row r="11">
@@ -3911,59 +3923,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="D11" t="n">
         <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1901.3</v>
+        <v>1733.8</v>
       </c>
       <c r="F11" t="n">
-        <v>2.827</v>
+        <v>0.433</v>
       </c>
       <c r="G11" t="n">
-        <v>117.49</v>
+        <v>105.76</v>
       </c>
       <c r="H11" t="n">
-        <v>106.29</v>
+        <v>97.33</v>
       </c>
       <c r="I11" t="n">
-        <v>11.21</v>
+        <v>8.43</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2953</v>
+        <v>0.2897</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1466</v>
+        <v>0.1583</v>
       </c>
       <c r="L11" t="n">
-        <v>-8</v>
+        <v>10.6</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="O11" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="R11" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="S11" t="n">
-        <v>1712.1</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="12">
@@ -4094,59 +4106,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oklahoma St</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1329</v>
+        <v>1124</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E14" t="n">
-        <v>1713.4</v>
+        <v>1673.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1735</v>
+        <v>-6.3298</v>
       </c>
       <c r="G14" t="n">
-        <v>110.48</v>
+        <v>115.76</v>
       </c>
       <c r="H14" t="n">
-        <v>109.05</v>
+        <v>111.17</v>
       </c>
       <c r="I14" t="n">
-        <v>1.43</v>
+        <v>4.59</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2757</v>
+        <v>0.3248</v>
       </c>
       <c r="K14" t="n">
-        <v>0.156</v>
+        <v>0.1611</v>
       </c>
       <c r="L14" t="n">
-        <v>-7</v>
+        <v>-5.6</v>
       </c>
       <c r="M14" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="N14" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="P14" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="R14" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="S14" t="n">
-        <v>1678.3</v>
+        <v>1725.5</v>
       </c>
     </row>
     <row r="15">
@@ -4155,59 +4167,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Oklahoma St</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1124</v>
+        <v>1329</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>1671.5</v>
+        <v>1713.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.0193</v>
+        <v>-1.1735</v>
       </c>
       <c r="G15" t="n">
-        <v>114.76</v>
+        <v>110.48</v>
       </c>
       <c r="H15" t="n">
-        <v>111.24</v>
+        <v>109.05</v>
       </c>
       <c r="I15" t="n">
-        <v>3.51</v>
+        <v>1.43</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3244</v>
+        <v>0.2757</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1668</v>
+        <v>0.156</v>
       </c>
       <c r="L15" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M15" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="N15" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O15" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="P15" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q15" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="R15" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="S15" t="n">
-        <v>1739.8</v>
+        <v>1678.3</v>
       </c>
     </row>
     <row r="16">
@@ -4347,97 +4359,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4578,31 +4590,31 @@
         <v>1437</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1820.1</v>
+        <v>1813.5</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5295</v>
+        <v>6.893</v>
       </c>
       <c r="G4" t="n">
-        <v>114.74</v>
+        <v>114.62</v>
       </c>
       <c r="H4" t="n">
-        <v>103.88</v>
+        <v>105.11</v>
       </c>
       <c r="I4" t="n">
-        <v>10.87</v>
+        <v>9.51</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3148</v>
+        <v>0.3173</v>
       </c>
       <c r="K4" t="n">
-        <v>0.141</v>
+        <v>0.1412</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="M4" t="n">
         <v>34</v>
@@ -4623,7 +4635,7 @@
         <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>1643.5</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="5">
@@ -4693,59 +4705,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1166</v>
+        <v>1177</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>1672.5</v>
+        <v>1605.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8294</v>
+        <v>5.8136</v>
       </c>
       <c r="G6" t="n">
-        <v>110.12</v>
+        <v>105.51</v>
       </c>
       <c r="H6" t="n">
-        <v>109.57</v>
+        <v>102.59</v>
       </c>
       <c r="I6" t="n">
-        <v>0.55</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2481</v>
+        <v>0.2994</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1544</v>
+        <v>0.1703</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8</v>
+        <v>4.4</v>
       </c>
       <c r="M6" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="O6" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R6" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="S6" t="n">
-        <v>1663.7</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="7">
@@ -4754,59 +4766,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1586.7</v>
+        <v>1661.7</v>
       </c>
       <c r="F7" t="n">
-        <v>5.744</v>
+        <v>-1.7577</v>
       </c>
       <c r="G7" t="n">
-        <v>104.54</v>
+        <v>110.25</v>
       </c>
       <c r="H7" t="n">
-        <v>103.2</v>
+        <v>110.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.34</v>
+        <v>-0.57</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2937</v>
+        <v>0.2489</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1724</v>
+        <v>0.1555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>-7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="N7" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="O7" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q7" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="S7" t="n">
-        <v>1607.9</v>
+        <v>1664.2</v>
       </c>
     </row>
     <row r="8">
@@ -4822,31 +4834,31 @@
         <v>1344</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>1568.8</v>
+        <v>1578.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8893</v>
+        <v>1.8443</v>
       </c>
       <c r="G8" t="n">
-        <v>114.76</v>
+        <v>116.46</v>
       </c>
       <c r="H8" t="n">
-        <v>112.81</v>
+        <v>112.82</v>
       </c>
       <c r="I8" t="n">
-        <v>1.94</v>
+        <v>3.64</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2627</v>
+        <v>0.2564</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1612</v>
+        <v>0.1547</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2</v>
+        <v>-0.2</v>
       </c>
       <c r="M8" t="n">
         <v>63</v>
@@ -4867,7 +4879,7 @@
         <v>74</v>
       </c>
       <c r="S8" t="n">
-        <v>1637.9</v>
+        <v>1644.9</v>
       </c>
     </row>
     <row r="9">
@@ -4883,31 +4895,31 @@
         <v>1139</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E9" t="n">
-        <v>1616</v>
+        <v>1626.7</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0517</v>
+        <v>1.2252</v>
       </c>
       <c r="G9" t="n">
-        <v>110.53</v>
+        <v>111.73</v>
       </c>
       <c r="H9" t="n">
-        <v>108.8</v>
+        <v>108.99</v>
       </c>
       <c r="I9" t="n">
-        <v>1.73</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3033</v>
+        <v>0.3088</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1524</v>
+        <v>0.1503</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.8</v>
+        <v>-3.4</v>
       </c>
       <c r="M9" t="n">
         <v>83</v>
@@ -4928,7 +4940,7 @@
         <v>80</v>
       </c>
       <c r="S9" t="n">
-        <v>1623.7</v>
+        <v>1624.5</v>
       </c>
     </row>
     <row r="10">
@@ -4998,59 +5010,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1266</v>
+        <v>1207</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1517.6</v>
+        <v>1551.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.0067</v>
+        <v>-4.9935</v>
       </c>
       <c r="G11" t="n">
-        <v>104.9</v>
+        <v>109.71</v>
       </c>
       <c r="H11" t="n">
-        <v>105.24</v>
+        <v>109.01</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.35</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2997</v>
+        <v>0.3048</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1579</v>
+        <v>0.1487</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>-6.8</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O11" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P11" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="Q11" t="n">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="R11" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="S11" t="n">
-        <v>1658.7</v>
+        <v>1645.5</v>
       </c>
     </row>
     <row r="12">
@@ -5059,59 +5071,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1207</v>
+        <v>1266</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E12" t="n">
-        <v>1551.4</v>
+        <v>1496.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9935</v>
+        <v>-8.5199</v>
       </c>
       <c r="G12" t="n">
-        <v>109.71</v>
+        <v>104.29</v>
       </c>
       <c r="H12" t="n">
-        <v>109.01</v>
+        <v>106.45</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>-2.16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3048</v>
+        <v>0.3007</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1487</v>
+        <v>0.1568</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.8</v>
+        <v>-2.4</v>
       </c>
       <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
         <v>90</v>
       </c>
-      <c r="N12" t="n">
-        <v>95</v>
-      </c>
       <c r="O12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="P12" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="n">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="R12" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="S12" t="n">
-        <v>1645.5</v>
+        <v>1661.5</v>
       </c>
     </row>
   </sheetData>
@@ -5129,97 +5141,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5292,59 +5304,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1277</v>
+        <v>1304</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>2050.3</v>
+        <v>1990.6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5431</v>
+        <v>11.3442</v>
       </c>
       <c r="G3" t="n">
-        <v>116.95</v>
+        <v>115.07</v>
       </c>
       <c r="H3" t="n">
-        <v>98.98</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>17.97</v>
+        <v>17.03</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2979</v>
+        <v>0.2419</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1625</v>
+        <v>0.1401</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
         <v>9</v>
       </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>14</v>
-      </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>1712.3</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4">
@@ -5353,59 +5365,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1304</v>
+        <v>1277</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E4" t="n">
-        <v>1990.6</v>
+        <v>2050.3</v>
       </c>
       <c r="F4" t="n">
-        <v>11.3442</v>
+        <v>0.5431</v>
       </c>
       <c r="G4" t="n">
-        <v>115.07</v>
+        <v>116.95</v>
       </c>
       <c r="H4" t="n">
-        <v>98.04000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="I4" t="n">
-        <v>17.03</v>
+        <v>17.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2419</v>
+        <v>0.2979</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1401</v>
+        <v>0.1625</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R4" t="n">
         <v>11</v>
       </c>
-      <c r="N4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>12</v>
-      </c>
       <c r="S4" t="n">
-        <v>1658</v>
+        <v>1712.3</v>
       </c>
     </row>
     <row r="5">
@@ -5482,31 +5494,31 @@
         <v>1345</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>1976</v>
+        <v>1972.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8268</v>
+        <v>1.3222</v>
       </c>
       <c r="G6" t="n">
-        <v>123.88</v>
+        <v>124.01</v>
       </c>
       <c r="H6" t="n">
-        <v>105.93</v>
+        <v>105.95</v>
       </c>
       <c r="I6" t="n">
-        <v>17.95</v>
+        <v>18.06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2977</v>
+        <v>0.2978</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1374</v>
+        <v>0.1321</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
@@ -5527,7 +5539,7 @@
         <v>9</v>
       </c>
       <c r="S6" t="n">
-        <v>1740.2</v>
+        <v>1747.3</v>
       </c>
     </row>
     <row r="7">
@@ -5543,31 +5555,31 @@
         <v>1458</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1837.7</v>
+        <v>1833.6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7673</v>
+        <v>0.5562</v>
       </c>
       <c r="G7" t="n">
-        <v>118.38</v>
+        <v>117.74</v>
       </c>
       <c r="H7" t="n">
-        <v>106.47</v>
+        <v>107.72</v>
       </c>
       <c r="I7" t="n">
-        <v>11.91</v>
+        <v>10.02</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2733</v>
+        <v>0.2772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1236</v>
+        <v>0.1264</v>
       </c>
       <c r="L7" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
         <v>30</v>
@@ -5588,7 +5600,7 @@
         <v>32</v>
       </c>
       <c r="S7" t="n">
-        <v>1686</v>
+        <v>1689.3</v>
       </c>
     </row>
     <row r="8">
@@ -5658,59 +5670,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1326</v>
+        <v>1234</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1787.4</v>
+        <v>1821.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3307</v>
+        <v>4.8208</v>
       </c>
       <c r="G9" t="n">
-        <v>118.28</v>
+        <v>119.88</v>
       </c>
       <c r="H9" t="n">
-        <v>107.42</v>
+        <v>103.67</v>
       </c>
       <c r="I9" t="n">
-        <v>10.87</v>
+        <v>16.21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.255</v>
+        <v>0.2891</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1501</v>
+        <v>0.1416</v>
       </c>
       <c r="L9" t="n">
-        <v>6.8</v>
+        <v>-2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S9" t="n">
-        <v>1694.2</v>
+        <v>1682.5</v>
       </c>
     </row>
     <row r="10">
@@ -5719,59 +5731,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1234</v>
+        <v>1326</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E10" t="n">
-        <v>1855.3</v>
+        <v>1782.1</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8208</v>
+        <v>1.1828</v>
       </c>
       <c r="G10" t="n">
-        <v>119.88</v>
+        <v>117.32</v>
       </c>
       <c r="H10" t="n">
-        <v>103.67</v>
+        <v>108.16</v>
       </c>
       <c r="I10" t="n">
-        <v>16.21</v>
+        <v>9.16</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2891</v>
+        <v>0.2601</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1416</v>
+        <v>0.1481</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8</v>
+        <v>-0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S10" t="n">
-        <v>1682.5</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="11">
@@ -5787,31 +5799,31 @@
         <v>1231</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E11" t="n">
-        <v>1752.7</v>
+        <v>1746.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7312</v>
+        <v>-2.8012</v>
       </c>
       <c r="G11" t="n">
-        <v>116.39</v>
+        <v>115.78</v>
       </c>
       <c r="H11" t="n">
-        <v>106.14</v>
+        <v>107.65</v>
       </c>
       <c r="I11" t="n">
-        <v>10.26</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1415</v>
+        <v>0.1402</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.2</v>
+        <v>-9.6</v>
       </c>
       <c r="M11" t="n">
         <v>43</v>
@@ -5832,7 +5844,7 @@
         <v>41</v>
       </c>
       <c r="S11" t="n">
-        <v>1695.9</v>
+        <v>1703.1</v>
       </c>
     </row>
     <row r="12">
@@ -5841,59 +5853,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1449</v>
+        <v>1425</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E12" t="n">
-        <v>1654.2</v>
+        <v>1770.8</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1014</v>
+        <v>2.1219</v>
       </c>
       <c r="G12" t="n">
-        <v>111.56</v>
+        <v>108.37</v>
       </c>
       <c r="H12" t="n">
-        <v>105.96</v>
+        <v>107.72</v>
       </c>
       <c r="I12" t="n">
-        <v>5.61</v>
+        <v>0.64</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3009</v>
+        <v>0.2924</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1501</v>
+        <v>0.1722</v>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>-15.6</v>
       </c>
       <c r="M12" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q12" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="R12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S12" t="n">
-        <v>1689.2</v>
+        <v>1691.4</v>
       </c>
     </row>
     <row r="13">
@@ -5902,59 +5914,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1425</v>
+        <v>1278</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E13" t="n">
-        <v>1755.8</v>
+        <v>1623.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5224</v>
+        <v>-0.0378</v>
       </c>
       <c r="G13" t="n">
-        <v>107.92</v>
+        <v>111.88</v>
       </c>
       <c r="H13" t="n">
-        <v>108.19</v>
+        <v>107.72</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.27</v>
+        <v>4.16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2952</v>
+        <v>0.2422</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1712</v>
+        <v>0.1542</v>
       </c>
       <c r="L13" t="n">
-        <v>-18</v>
+        <v>3.8</v>
       </c>
       <c r="M13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="O13" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="R13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="S13" t="n">
-        <v>1684.4</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="14">
@@ -5963,59 +5975,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1278</v>
+        <v>1449</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E14" t="n">
-        <v>1616.9</v>
+        <v>1639.3</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1308</v>
+        <v>2.3162</v>
       </c>
       <c r="G14" t="n">
-        <v>109.88</v>
+        <v>111.08</v>
       </c>
       <c r="H14" t="n">
-        <v>108.2</v>
+        <v>106.69</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>4.39</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2483</v>
+        <v>0.2953</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1566</v>
+        <v>0.15</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N14" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="O14" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="P14" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="Q14" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R14" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="S14" t="n">
-        <v>1678.8</v>
+        <v>1687.1</v>
       </c>
     </row>
     <row r="15">
@@ -6092,31 +6104,31 @@
         <v>1321</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E16" t="n">
-        <v>1591.7</v>
+        <v>1595.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.6981</v>
+        <v>-5.1956</v>
       </c>
       <c r="G16" t="n">
-        <v>110.63</v>
+        <v>110.12</v>
       </c>
       <c r="H16" t="n">
-        <v>109.75</v>
+        <v>108.88</v>
       </c>
       <c r="I16" t="n">
-        <v>0.87</v>
+        <v>1.24</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2719</v>
+        <v>0.273</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1268</v>
+        <v>0.1275</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.8</v>
+        <v>-4.4</v>
       </c>
       <c r="M16" t="n">
         <v>68</v>
@@ -6137,7 +6149,7 @@
         <v>72</v>
       </c>
       <c r="S16" t="n">
-        <v>1705.7</v>
+        <v>1692.6</v>
       </c>
     </row>
     <row r="17">
@@ -6214,31 +6226,31 @@
         <v>1268</v>
       </c>
       <c r="D18" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E18" t="n">
-        <v>1598.8</v>
+        <v>1584.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.9559</v>
+        <v>-8.259399999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>102.77</v>
+        <v>103.79</v>
       </c>
       <c r="H18" t="n">
-        <v>114.81</v>
+        <v>113.48</v>
       </c>
       <c r="I18" t="n">
-        <v>-12.04</v>
+        <v>-9.69</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3181</v>
+        <v>0.3183</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1773</v>
+        <v>0.1789</v>
       </c>
       <c r="L18" t="n">
-        <v>-10</v>
+        <v>-5.6</v>
       </c>
       <c r="M18" t="n">
         <v>130</v>
@@ -6259,7 +6271,7 @@
         <v>146</v>
       </c>
       <c r="S18" t="n">
-        <v>1712.3</v>
+        <v>1703.6</v>
       </c>
     </row>
     <row r="19">
@@ -6275,31 +6287,31 @@
         <v>1336</v>
       </c>
       <c r="D19" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E19" t="n">
-        <v>1531.4</v>
+        <v>1570.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.5446</v>
+        <v>-7.9364</v>
       </c>
       <c r="G19" t="n">
-        <v>110.14</v>
+        <v>110.93</v>
       </c>
       <c r="H19" t="n">
-        <v>118.59</v>
+        <v>117.12</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.44</v>
+        <v>-6.19</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2617</v>
+        <v>0.2682</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1492</v>
+        <v>0.1505</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.4</v>
+        <v>-8.4</v>
       </c>
       <c r="M19" t="n">
         <v>128</v>
@@ -6320,7 +6332,7 @@
         <v>125</v>
       </c>
       <c r="S19" t="n">
-        <v>1669.9</v>
+        <v>1667.7</v>
       </c>
     </row>
   </sheetData>
@@ -6338,97 +6350,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6806,59 +6818,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>C Michigan</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1391.4</v>
+        <v>1341.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2165</v>
+        <v>-2.8296</v>
       </c>
       <c r="G8" t="n">
-        <v>114.44</v>
+        <v>105.75</v>
       </c>
       <c r="H8" t="n">
-        <v>111.83</v>
+        <v>114.35</v>
       </c>
       <c r="I8" t="n">
-        <v>2.61</v>
+        <v>-8.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2726</v>
+        <v>0.2991</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1568</v>
+        <v>0.1727</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.4</v>
+        <v>-1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="N8" t="n">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="O8" t="n">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="P8" t="n">
-        <v>194</v>
+        <v>274</v>
       </c>
       <c r="Q8" t="n">
-        <v>178</v>
+        <v>301</v>
       </c>
       <c r="R8" t="n">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="S8" t="n">
-        <v>1459.5</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="9">
@@ -6867,59 +6879,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1269</v>
+        <v>1138</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1478.7</v>
+        <v>1391.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0696</v>
+        <v>-0.2165</v>
       </c>
       <c r="G9" t="n">
-        <v>109.4</v>
+        <v>114.44</v>
       </c>
       <c r="H9" t="n">
-        <v>107.53</v>
+        <v>111.83</v>
       </c>
       <c r="I9" t="n">
-        <v>1.87</v>
+        <v>2.61</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2938</v>
+        <v>0.2726</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1727</v>
+        <v>0.1568</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.2</v>
+        <v>-2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="N9" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="O9" t="n">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="P9" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>178</v>
+      </c>
+      <c r="R9" t="n">
         <v>190</v>
       </c>
-      <c r="Q9" t="n">
-        <v>204</v>
-      </c>
-      <c r="R9" t="n">
-        <v>204</v>
-      </c>
       <c r="S9" t="n">
-        <v>1451.7</v>
+        <v>1459.5</v>
       </c>
     </row>
   </sheetData>
@@ -6937,97 +6949,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7719,97 +7731,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7889,31 +7901,31 @@
         <v>1307</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>1825.3</v>
+        <v>1847</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1386</v>
+        <v>4.3818</v>
       </c>
       <c r="G3" t="n">
-        <v>114.16</v>
+        <v>114.73</v>
       </c>
       <c r="H3" t="n">
-        <v>101.47</v>
+        <v>100.98</v>
       </c>
       <c r="I3" t="n">
-        <v>12.7</v>
+        <v>13.75</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2721</v>
+        <v>0.2694</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1448</v>
+        <v>0.143</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="M3" t="n">
         <v>46</v>
@@ -7934,7 +7946,7 @@
         <v>42</v>
       </c>
       <c r="S3" t="n">
-        <v>1590</v>
+        <v>1589.8</v>
       </c>
     </row>
     <row r="4">
@@ -8004,59 +8016,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grand Canyon</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1213</v>
+        <v>1305</v>
       </c>
       <c r="D5" t="n">
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1722.6</v>
+        <v>1738.9</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6005</v>
+        <v>7.3067</v>
       </c>
       <c r="G5" t="n">
-        <v>109.82</v>
+        <v>112.85</v>
       </c>
       <c r="H5" t="n">
-        <v>99.62</v>
+        <v>107.41</v>
       </c>
       <c r="I5" t="n">
-        <v>10.21</v>
+        <v>5.44</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2757</v>
+        <v>0.305</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1736</v>
+        <v>0.1405</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8</v>
+        <v>-3.6</v>
       </c>
       <c r="M5" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="O5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="P5" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="R5" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="S5" t="n">
-        <v>1577</v>
+        <v>1614.5</v>
       </c>
     </row>
     <row r="6">
@@ -8065,59 +8077,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Grand Canyon</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1161</v>
+        <v>1213</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1673.6</v>
+        <v>1722.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.2938</v>
+        <v>6.6005</v>
       </c>
       <c r="G6" t="n">
-        <v>119.56</v>
+        <v>109.82</v>
       </c>
       <c r="H6" t="n">
-        <v>112.77</v>
+        <v>99.62</v>
       </c>
       <c r="I6" t="n">
-        <v>6.79</v>
+        <v>10.21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.256</v>
+        <v>0.2757</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1771</v>
+        <v>0.1736</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M6" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="N6" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O6" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="P6" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="S6" t="n">
-        <v>1559.4</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="7">
@@ -8126,59 +8138,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Colorado St</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1129</v>
+        <v>1161</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1727.7</v>
+        <v>1651.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3169</v>
+        <v>-5.6123</v>
       </c>
       <c r="G7" t="n">
-        <v>113.86</v>
+        <v>120.05</v>
       </c>
       <c r="H7" t="n">
-        <v>107.08</v>
+        <v>113.29</v>
       </c>
       <c r="I7" t="n">
-        <v>6.78</v>
+        <v>6.76</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2821</v>
+        <v>0.2615</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1603</v>
+        <v>0.1721</v>
       </c>
       <c r="L7" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="N7" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="O7" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="P7" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q7" t="n">
         <v>78</v>
       </c>
-      <c r="Q7" t="n">
-        <v>63</v>
-      </c>
       <c r="R7" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="S7" t="n">
-        <v>1623.5</v>
+        <v>1542.5</v>
       </c>
     </row>
     <row r="8">
@@ -8187,59 +8199,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1305</v>
+        <v>1129</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1738.9</v>
+        <v>1727.7</v>
       </c>
       <c r="F8" t="n">
-        <v>7.3067</v>
+        <v>-2.3169</v>
       </c>
       <c r="G8" t="n">
-        <v>112.85</v>
+        <v>113.86</v>
       </c>
       <c r="H8" t="n">
-        <v>107.41</v>
+        <v>107.08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.44</v>
+        <v>6.78</v>
       </c>
       <c r="J8" t="n">
-        <v>0.305</v>
+        <v>0.2821</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1405</v>
+        <v>0.1603</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.6</v>
+        <v>6.2</v>
       </c>
       <c r="M8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O8" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="R8" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="S8" t="n">
-        <v>1614.5</v>
+        <v>1623.5</v>
       </c>
     </row>
     <row r="9">
@@ -8562,97 +8574,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8793,31 +8805,31 @@
         <v>1116</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1932.7</v>
+        <v>1925.2</v>
       </c>
       <c r="F4" t="n">
-        <v>6.7834</v>
+        <v>7.1116</v>
       </c>
       <c r="G4" t="n">
-        <v>123.18</v>
+        <v>122.37</v>
       </c>
       <c r="H4" t="n">
-        <v>108.72</v>
+        <v>109.06</v>
       </c>
       <c r="I4" t="n">
-        <v>14.46</v>
+        <v>13.31</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2975</v>
+        <v>0.3062</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1194</v>
+        <v>0.119</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>20</v>
@@ -8838,7 +8850,7 @@
         <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>1725.9</v>
+        <v>1726.1</v>
       </c>
     </row>
     <row r="5">
@@ -8847,59 +8859,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1397</v>
+        <v>1281</v>
       </c>
       <c r="D5" t="n">
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1912.8</v>
+        <v>1768.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7463</v>
+        <v>-2.8893</v>
       </c>
       <c r="G5" t="n">
-        <v>117.37</v>
+        <v>115.23</v>
       </c>
       <c r="H5" t="n">
-        <v>101.08</v>
+        <v>109.22</v>
       </c>
       <c r="I5" t="n">
-        <v>16.3</v>
+        <v>6.01</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3535</v>
+        <v>0.3029</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1667</v>
+        <v>0.1713</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="P5" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="R5" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="S5" t="n">
-        <v>1692.2</v>
+        <v>1637.7</v>
       </c>
     </row>
     <row r="6">
@@ -8908,59 +8920,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1281</v>
+        <v>1246</v>
       </c>
       <c r="D6" t="n">
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1768.2</v>
+        <v>1893.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8893</v>
+        <v>6.006</v>
       </c>
       <c r="G6" t="n">
-        <v>115.23</v>
+        <v>116.85</v>
       </c>
       <c r="H6" t="n">
-        <v>109.22</v>
+        <v>105.78</v>
       </c>
       <c r="I6" t="n">
-        <v>6.01</v>
+        <v>11.07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3029</v>
+        <v>0.3101</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1713</v>
+        <v>0.1466</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R6" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="S6" t="n">
-        <v>1637.7</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="7">
@@ -8969,59 +8981,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1435</v>
+        <v>1397</v>
       </c>
       <c r="D7" t="n">
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1921</v>
+        <v>1912.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9274</v>
+        <v>-1.7463</v>
       </c>
       <c r="G7" t="n">
-        <v>121.87</v>
+        <v>117.37</v>
       </c>
       <c r="H7" t="n">
-        <v>105.42</v>
+        <v>101.08</v>
       </c>
       <c r="I7" t="n">
-        <v>16.45</v>
+        <v>16.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2854</v>
+        <v>0.3535</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1247</v>
+        <v>0.1667</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" t="n">
         <v>20</v>
       </c>
-      <c r="O7" t="n">
-        <v>18</v>
-      </c>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S7" t="n">
-        <v>1684</v>
+        <v>1692.2</v>
       </c>
     </row>
     <row r="8">
@@ -9030,59 +9042,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>1836.9</v>
+        <v>1785.1</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4256</v>
+        <v>2.0552</v>
       </c>
       <c r="G8" t="n">
-        <v>118.62</v>
+        <v>121.1</v>
       </c>
       <c r="H8" t="n">
-        <v>106.73</v>
+        <v>110.26</v>
       </c>
       <c r="I8" t="n">
-        <v>11.89</v>
+        <v>10.85</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3028</v>
+        <v>0.3116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1406</v>
+        <v>0.1505</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
+        <v>29</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" t="n">
+        <v>34</v>
+      </c>
+      <c r="P8" t="n">
         <v>38</v>
       </c>
-      <c r="N8" t="n">
-        <v>34</v>
-      </c>
-      <c r="O8" t="n">
-        <v>36</v>
-      </c>
-      <c r="P8" t="n">
-        <v>39</v>
-      </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="S8" t="n">
-        <v>1655.1</v>
+        <v>1691.9</v>
       </c>
     </row>
     <row r="9">
@@ -9091,59 +9103,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1246</v>
+        <v>1435</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1893.4</v>
+        <v>1921</v>
       </c>
       <c r="F9" t="n">
-        <v>6.006</v>
+        <v>1.9274</v>
       </c>
       <c r="G9" t="n">
-        <v>116.85</v>
+        <v>121.87</v>
       </c>
       <c r="H9" t="n">
-        <v>105.78</v>
+        <v>105.42</v>
       </c>
       <c r="I9" t="n">
-        <v>11.07</v>
+        <v>16.45</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3101</v>
+        <v>0.2854</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1466</v>
+        <v>0.1247</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="S9" t="n">
-        <v>1717.2</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="10">
@@ -9152,59 +9164,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1208</v>
+        <v>1401</v>
       </c>
       <c r="D10" t="n">
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1810.7</v>
+        <v>1836.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8284</v>
+        <v>4.4256</v>
       </c>
       <c r="G10" t="n">
-        <v>120.8</v>
+        <v>118.62</v>
       </c>
       <c r="H10" t="n">
-        <v>106.43</v>
+        <v>106.73</v>
       </c>
       <c r="I10" t="n">
-        <v>14.38</v>
+        <v>11.89</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3238</v>
+        <v>0.3028</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1381</v>
+        <v>0.1406</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>-0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P10" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R10" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
-        <v>1647.3</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="11">
@@ -9213,59 +9225,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1400</v>
+        <v>1208</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1777.5</v>
+        <v>1810.7</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2904</v>
+        <v>-0.8284</v>
       </c>
       <c r="G11" t="n">
-        <v>120.67</v>
+        <v>120.8</v>
       </c>
       <c r="H11" t="n">
-        <v>111.46</v>
+        <v>106.43</v>
       </c>
       <c r="I11" t="n">
-        <v>9.210000000000001</v>
+        <v>14.38</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3123</v>
+        <v>0.3238</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1488</v>
+        <v>0.1381</v>
       </c>
       <c r="L11" t="n">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N11" t="n">
+        <v>31</v>
+      </c>
+      <c r="O11" t="n">
         <v>30</v>
       </c>
-      <c r="O11" t="n">
-        <v>34</v>
-      </c>
       <c r="P11" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="Q11" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="R11" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="S11" t="n">
-        <v>1700.7</v>
+        <v>1647.3</v>
       </c>
     </row>
     <row r="12">
@@ -9335,59 +9347,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Mississippi St</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1328</v>
+        <v>1280</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1687.4</v>
+        <v>1633.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1749</v>
+        <v>-2.2844</v>
       </c>
       <c r="G13" t="n">
-        <v>119.85</v>
+        <v>106.96</v>
       </c>
       <c r="H13" t="n">
-        <v>111.64</v>
+        <v>112.13</v>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3131</v>
+        <v>0.279</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1429</v>
+        <v>0.1541</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>-17</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="N13" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="O13" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="P13" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="R13" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="S13" t="n">
-        <v>1659.4</v>
+        <v>1702.1</v>
       </c>
     </row>
     <row r="14">
@@ -9396,59 +9408,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mississippi St</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1280</v>
+        <v>1328</v>
       </c>
       <c r="D14" t="n">
         <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1633.2</v>
+        <v>1687.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2844</v>
+        <v>-3.1749</v>
       </c>
       <c r="G14" t="n">
-        <v>106.96</v>
+        <v>119.85</v>
       </c>
       <c r="H14" t="n">
-        <v>112.13</v>
+        <v>111.64</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.279</v>
+        <v>0.3131</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1541</v>
+        <v>0.1429</v>
       </c>
       <c r="L14" t="n">
-        <v>-17</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O14" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="Q14" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="S14" t="n">
-        <v>1702.1</v>
+        <v>1659.4</v>
       </c>
     </row>
     <row r="15">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -1988,31 +1988,31 @@
         <v>1339</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1410.8</v>
+        <v>1412.6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4251</v>
+        <v>1.453</v>
       </c>
       <c r="G10" t="n">
-        <v>102.32</v>
+        <v>102.44</v>
       </c>
       <c r="H10" t="n">
-        <v>111.88</v>
+        <v>111.35</v>
       </c>
       <c r="I10" t="n">
-        <v>-9.56</v>
+        <v>-8.91</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2621</v>
+        <v>0.2631</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1897</v>
+        <v>0.1902</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.2</v>
+        <v>-7.8</v>
       </c>
       <c r="M10" t="n">
         <v>204</v>
@@ -2033,7 +2033,7 @@
         <v>227</v>
       </c>
       <c r="S10" t="n">
-        <v>1540.4</v>
+        <v>1532.3</v>
       </c>
     </row>
     <row r="11">
@@ -2049,31 +2049,31 @@
         <v>1258</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E11" t="n">
-        <v>1477.4</v>
+        <v>1472.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.9616</v>
+        <v>-5.7748</v>
       </c>
       <c r="G11" t="n">
-        <v>105.32</v>
+        <v>105.07</v>
       </c>
       <c r="H11" t="n">
-        <v>105.5</v>
+        <v>105.42</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.18</v>
+        <v>-0.35</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2501</v>
+        <v>0.2548</v>
       </c>
       <c r="K11" t="n">
-        <v>0.165</v>
+        <v>0.1644</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
         <v>148</v>
@@ -2094,7 +2094,7 @@
         <v>166</v>
       </c>
       <c r="S11" t="n">
-        <v>1524</v>
+        <v>1516.2</v>
       </c>
     </row>
     <row r="12">
@@ -2110,31 +2110,31 @@
         <v>1360</v>
       </c>
       <c r="D12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E12" t="n">
-        <v>1358.3</v>
+        <v>1363</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9934</v>
+        <v>1.825</v>
       </c>
       <c r="G12" t="n">
-        <v>104.8</v>
+        <v>104.99</v>
       </c>
       <c r="H12" t="n">
-        <v>113.93</v>
+        <v>113.39</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.130000000000001</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3015</v>
+        <v>0.3057</v>
       </c>
       <c r="K12" t="n">
-        <v>0.169</v>
+        <v>0.1671</v>
       </c>
       <c r="L12" t="n">
-        <v>-7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>235</v>
@@ -2155,7 +2155,7 @@
         <v>244</v>
       </c>
       <c r="S12" t="n">
-        <v>1529.1</v>
+        <v>1528.1</v>
       </c>
     </row>
     <row r="13">
@@ -2171,31 +2171,31 @@
         <v>1337</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E13" t="n">
-        <v>1310.8</v>
+        <v>1308.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9603</v>
+        <v>-1.8402</v>
       </c>
       <c r="G13" t="n">
-        <v>100.83</v>
+        <v>100.55</v>
       </c>
       <c r="H13" t="n">
-        <v>114.02</v>
+        <v>114.01</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.19</v>
+        <v>-13.46</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2842</v>
+        <v>0.2898</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1739</v>
+        <v>0.1727</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="M13" t="n">
         <v>260</v>
@@ -2216,7 +2216,7 @@
         <v>270</v>
       </c>
       <c r="S13" t="n">
-        <v>1527</v>
+        <v>1522.7</v>
       </c>
     </row>
   </sheetData>
@@ -5238,31 +5238,31 @@
         <v>1276</v>
       </c>
       <c r="D2" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>2167</v>
+        <v>2172.4</v>
       </c>
       <c r="F2" t="n">
-        <v>8.613799999999999</v>
+        <v>8.183400000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>122.15</v>
+        <v>121.54</v>
       </c>
       <c r="H2" t="n">
-        <v>94.92</v>
+        <v>95.23</v>
       </c>
       <c r="I2" t="n">
-        <v>27.23</v>
+        <v>26.31</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2673</v>
+        <v>0.2642</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1627</v>
+        <v>0.1678</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -5283,7 +5283,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1754.5</v>
+        <v>1756.1</v>
       </c>
     </row>
     <row r="3">
@@ -5299,31 +5299,31 @@
         <v>1277</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>2050.3</v>
+        <v>2051.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5431</v>
+        <v>0.5706</v>
       </c>
       <c r="G3" t="n">
-        <v>116.95</v>
+        <v>117.41</v>
       </c>
       <c r="H3" t="n">
-        <v>98.98</v>
+        <v>100.06</v>
       </c>
       <c r="I3" t="n">
-        <v>17.97</v>
+        <v>17.36</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2979</v>
+        <v>0.2989</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1625</v>
+        <v>0.165</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -5344,7 +5344,7 @@
         <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>1712.3</v>
+        <v>1704.4</v>
       </c>
     </row>
     <row r="4">
@@ -5726,31 +5726,31 @@
         <v>1234</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1855.3</v>
+        <v>1849.8</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8208</v>
+        <v>4.4435</v>
       </c>
       <c r="G10" t="n">
-        <v>119.88</v>
+        <v>119.28</v>
       </c>
       <c r="H10" t="n">
-        <v>103.67</v>
+        <v>103.76</v>
       </c>
       <c r="I10" t="n">
-        <v>16.21</v>
+        <v>15.52</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2891</v>
+        <v>0.2925</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1416</v>
+        <v>0.1388</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
         <v>24</v>
@@ -5771,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1682.5</v>
+        <v>1706.7</v>
       </c>
     </row>
     <row r="11">
@@ -6031,31 +6031,31 @@
         <v>1353</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>1570.5</v>
+        <v>1550.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2938</v>
+        <v>-3.1151</v>
       </c>
       <c r="G15" t="n">
-        <v>104.1</v>
+        <v>104.86</v>
       </c>
       <c r="H15" t="n">
-        <v>111.98</v>
+        <v>112.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.89</v>
+        <v>-7.98</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3198</v>
+        <v>0.3247</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1478</v>
+        <v>0.1469</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4</v>
+        <v>-2.6</v>
       </c>
       <c r="M15" t="n">
         <v>144</v>
@@ -6076,7 +6076,7 @@
         <v>158</v>
       </c>
       <c r="S15" t="n">
-        <v>1676.4</v>
+        <v>1695.2</v>
       </c>
     </row>
     <row r="16">
@@ -7351,31 +7351,31 @@
         <v>1320</v>
       </c>
       <c r="D7" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E7" t="n">
-        <v>1546.3</v>
+        <v>1548.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.5639</v>
+        <v>-4.3824</v>
       </c>
       <c r="G7" t="n">
-        <v>106.62</v>
+        <v>106.65</v>
       </c>
       <c r="H7" t="n">
-        <v>96.51000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.201</v>
+        <v>0.2059</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1381</v>
+        <v>0.1354</v>
       </c>
       <c r="L7" t="n">
-        <v>12.6</v>
+        <v>9.6</v>
       </c>
       <c r="M7" t="n">
         <v>80</v>
@@ -7396,7 +7396,7 @@
         <v>81</v>
       </c>
       <c r="S7" t="n">
-        <v>1515.6</v>
+        <v>1508.1</v>
       </c>
     </row>
     <row r="8">
@@ -7412,28 +7412,28 @@
         <v>1434</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E8" t="n">
-        <v>1458.2</v>
+        <v>1462.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6655</v>
+        <v>0.7974</v>
       </c>
       <c r="G8" t="n">
-        <v>106.02</v>
+        <v>105.92</v>
       </c>
       <c r="H8" t="n">
-        <v>106.35</v>
+        <v>106.15</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3035</v>
+        <v>0.3118</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1462</v>
+        <v>0.1465</v>
       </c>
       <c r="L8" t="n">
         <v>2.8</v>
@@ -7457,7 +7457,7 @@
         <v>155</v>
       </c>
       <c r="S8" t="n">
-        <v>1520.9</v>
+        <v>1519.4</v>
       </c>
     </row>
     <row r="9">
@@ -7473,31 +7473,31 @@
         <v>1356</v>
       </c>
       <c r="D9" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E9" t="n">
-        <v>1480.3</v>
+        <v>1474.9</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7056</v>
+        <v>0.7808</v>
       </c>
       <c r="G9" t="n">
-        <v>103.07</v>
+        <v>102.61</v>
       </c>
       <c r="H9" t="n">
-        <v>99.23</v>
+        <v>99.38</v>
       </c>
       <c r="I9" t="n">
-        <v>3.84</v>
+        <v>3.23</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2772</v>
+        <v>0.2771</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1668</v>
+        <v>0.1671</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="M9" t="n">
         <v>114</v>
@@ -7518,7 +7518,7 @@
         <v>113</v>
       </c>
       <c r="S9" t="n">
-        <v>1517.9</v>
+        <v>1518.9</v>
       </c>
     </row>
     <row r="10">
@@ -7534,31 +7534,31 @@
         <v>1179</v>
       </c>
       <c r="D10" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1496.3</v>
+        <v>1501.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.6733</v>
+        <v>-7.4324</v>
       </c>
       <c r="G10" t="n">
-        <v>107.6</v>
+        <v>107.72</v>
       </c>
       <c r="H10" t="n">
-        <v>112.05</v>
+        <v>111.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.45</v>
+        <v>-3.64</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2667</v>
+        <v>0.2728</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1455</v>
+        <v>0.1449</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.8</v>
+        <v>-10</v>
       </c>
       <c r="M10" t="n">
         <v>213</v>
@@ -7579,7 +7579,7 @@
         <v>206</v>
       </c>
       <c r="S10" t="n">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="11">
@@ -7595,28 +7595,28 @@
         <v>1232</v>
       </c>
       <c r="D11" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E11" t="n">
-        <v>1432.5</v>
+        <v>1428.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2563</v>
+        <v>-3.2579</v>
       </c>
       <c r="G11" t="n">
-        <v>102.56</v>
+        <v>102.44</v>
       </c>
       <c r="H11" t="n">
-        <v>106.68</v>
+        <v>106.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.12</v>
+        <v>-4.32</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2336</v>
+        <v>0.2378</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1865</v>
+        <v>0.1878</v>
       </c>
       <c r="L11" t="n">
         <v>-6.8</v>
@@ -7640,7 +7640,7 @@
         <v>216</v>
       </c>
       <c r="S11" t="n">
-        <v>1526.5</v>
+        <v>1523.5</v>
       </c>
     </row>
     <row r="12">
@@ -7656,31 +7656,31 @@
         <v>1191</v>
       </c>
       <c r="D12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E12" t="n">
-        <v>1331.7</v>
+        <v>1329.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1084</v>
+        <v>-2.036</v>
       </c>
       <c r="G12" t="n">
-        <v>97.31999999999999</v>
+        <v>97.12</v>
       </c>
       <c r="H12" t="n">
-        <v>116.3</v>
+        <v>115.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-18.98</v>
+        <v>-18.77</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2361</v>
+        <v>0.2369</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1832</v>
+        <v>0.1852</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.6</v>
+        <v>-13.8</v>
       </c>
       <c r="M12" t="n">
         <v>310</v>
@@ -7701,7 +7701,7 @@
         <v>304</v>
       </c>
       <c r="S12" t="n">
-        <v>1568.3</v>
+        <v>1568.2</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -545,10 +545,10 @@
         <v>121</v>
       </c>
       <c r="E2" t="n">
-        <v>1825.9</v>
+        <v>1824.5</v>
       </c>
       <c r="F2" t="n">
-        <v>10.4518</v>
+        <v>10.3996</v>
       </c>
       <c r="G2" t="n">
         <v>122</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="S2" t="n">
-        <v>1501.8</v>
+        <v>1501.2</v>
       </c>
     </row>
     <row r="3">
@@ -606,10 +606,10 @@
         <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1731.8</v>
+        <v>1727.9</v>
       </c>
       <c r="F3" t="n">
-        <v>2.54</v>
+        <v>2.9027</v>
       </c>
       <c r="G3" t="n">
         <v>118.56</v>
@@ -648,7 +648,7 @@
         <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>1552.4</v>
+        <v>1551.3</v>
       </c>
     </row>
     <row r="4">
@@ -667,10 +667,10 @@
         <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1610.2</v>
+        <v>1609.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6493</v>
+        <v>0.6471</v>
       </c>
       <c r="G4" t="n">
         <v>104.92</v>
@@ -709,7 +709,7 @@
         <v>132</v>
       </c>
       <c r="S4" t="n">
-        <v>1512.1</v>
+        <v>1511.8</v>
       </c>
     </row>
     <row r="5">
@@ -728,10 +728,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1675</v>
+        <v>1675.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7831</v>
+        <v>-2.825</v>
       </c>
       <c r="G5" t="n">
         <v>110.38</v>
@@ -770,7 +770,7 @@
         <v>71</v>
       </c>
       <c r="S5" t="n">
-        <v>1553.6</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="6">
@@ -789,10 +789,10 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1707.9</v>
+        <v>1707.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6563</v>
       </c>
       <c r="G6" t="n">
         <v>111.81</v>
@@ -831,7 +831,7 @@
         <v>98</v>
       </c>
       <c r="S6" t="n">
-        <v>1505.9</v>
+        <v>1505.6</v>
       </c>
     </row>
     <row r="7">
@@ -850,10 +850,10 @@
         <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1523</v>
+        <v>1522.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.809</v>
+        <v>-2.8164</v>
       </c>
       <c r="G7" t="n">
         <v>108.88</v>
@@ -892,7 +892,7 @@
         <v>105</v>
       </c>
       <c r="S7" t="n">
-        <v>1542.6</v>
+        <v>1541.6</v>
       </c>
     </row>
     <row r="8">
@@ -911,10 +911,10 @@
         <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>1476.6</v>
+        <v>1477.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3487</v>
+        <v>-2.429</v>
       </c>
       <c r="G8" t="n">
         <v>108.08</v>
@@ -953,7 +953,7 @@
         <v>131</v>
       </c>
       <c r="S8" t="n">
-        <v>1541.8</v>
+        <v>1541.5</v>
       </c>
     </row>
     <row r="9">
@@ -972,10 +972,10 @@
         <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1540.4</v>
+        <v>1541.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3148</v>
+        <v>-4.2526</v>
       </c>
       <c r="G9" t="n">
         <v>116.28</v>
@@ -1014,7 +1014,7 @@
         <v>86</v>
       </c>
       <c r="S9" t="n">
-        <v>1537.4</v>
+        <v>1538.6</v>
       </c>
     </row>
     <row r="10">
@@ -1033,10 +1033,10 @@
         <v>121</v>
       </c>
       <c r="E10" t="n">
-        <v>1456.7</v>
+        <v>1457.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1066</v>
+        <v>1.0971</v>
       </c>
       <c r="G10" t="n">
         <v>105.16</v>
@@ -1075,7 +1075,7 @@
         <v>181</v>
       </c>
       <c r="S10" t="n">
-        <v>1494.5</v>
+        <v>1494.4</v>
       </c>
     </row>
     <row r="11">
@@ -1094,10 +1094,10 @@
         <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1573.4</v>
+        <v>1573.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7869</v>
+        <v>0.7973</v>
       </c>
       <c r="G11" t="n">
         <v>105.82</v>
@@ -1136,7 +1136,7 @@
         <v>141</v>
       </c>
       <c r="S11" t="n">
-        <v>1518.9</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="12">
@@ -1155,10 +1155,10 @@
         <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1471.7</v>
+        <v>1471.3</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.362</v>
+        <v>-0.3741</v>
       </c>
       <c r="G12" t="n">
         <v>110.96</v>
@@ -1197,7 +1197,7 @@
         <v>147</v>
       </c>
       <c r="S12" t="n">
-        <v>1514.2</v>
+        <v>1513.8</v>
       </c>
     </row>
     <row r="13">
@@ -1216,10 +1216,10 @@
         <v>121</v>
       </c>
       <c r="E13" t="n">
-        <v>1400.4</v>
+        <v>1400.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1985</v>
+        <v>-2.2046</v>
       </c>
       <c r="G13" t="n">
         <v>99.5</v>
@@ -1258,7 +1258,7 @@
         <v>239</v>
       </c>
       <c r="S13" t="n">
-        <v>1562.2</v>
+        <v>1562.7</v>
       </c>
     </row>
     <row r="14">
@@ -1277,10 +1277,10 @@
         <v>121</v>
       </c>
       <c r="E14" t="n">
-        <v>1531.8</v>
+        <v>1531.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.8443</v>
+        <v>-8.8599</v>
       </c>
       <c r="G14" t="n">
         <v>111.57</v>
@@ -1319,7 +1319,7 @@
         <v>149</v>
       </c>
       <c r="S14" t="n">
-        <v>1532.1</v>
+        <v>1531.6</v>
       </c>
     </row>
     <row r="15">
@@ -1338,10 +1338,10 @@
         <v>121</v>
       </c>
       <c r="E15" t="n">
-        <v>1390.9</v>
+        <v>1391.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.2873</v>
+        <v>-4.2997</v>
       </c>
       <c r="G15" t="n">
         <v>100.15</v>
@@ -1380,7 +1380,7 @@
         <v>303</v>
       </c>
       <c r="S15" t="n">
-        <v>1562.8</v>
+        <v>1562.7</v>
       </c>
     </row>
   </sheetData>
@@ -1510,10 +1510,10 @@
         <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1772.7</v>
+        <v>1771.7</v>
       </c>
       <c r="F2" t="n">
-        <v>9.988799999999999</v>
+        <v>9.957599999999999</v>
       </c>
       <c r="G2" t="n">
         <v>120.02</v>
@@ -1552,7 +1552,7 @@
         <v>52</v>
       </c>
       <c r="S2" t="n">
-        <v>1413.1</v>
+        <v>1412.7</v>
       </c>
     </row>
     <row r="3">
@@ -1571,10 +1571,10 @@
         <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1696.6</v>
+        <v>1693.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4591</v>
+        <v>1.6325</v>
       </c>
       <c r="G3" t="n">
         <v>122.16</v>
@@ -1613,7 +1613,7 @@
         <v>57</v>
       </c>
       <c r="S3" t="n">
-        <v>1484.3</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="4">
@@ -1632,10 +1632,10 @@
         <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>1606.9</v>
+        <v>1605.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4251</v>
+        <v>0.4681</v>
       </c>
       <c r="G4" t="n">
         <v>112.27</v>
@@ -1674,7 +1674,7 @@
         <v>150</v>
       </c>
       <c r="S4" t="n">
-        <v>1472.9</v>
+        <v>1472.1</v>
       </c>
     </row>
     <row r="5">
@@ -1693,10 +1693,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1453.1</v>
+        <v>1452.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6704</v>
+        <v>-0.6824</v>
       </c>
       <c r="G5" t="n">
         <v>113.63</v>
@@ -1735,7 +1735,7 @@
         <v>153</v>
       </c>
       <c r="S5" t="n">
-        <v>1505.2</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="6">
@@ -1754,10 +1754,10 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1466.5</v>
+        <v>1466.1</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6633</v>
+        <v>2.6549</v>
       </c>
       <c r="G6" t="n">
         <v>106.96</v>
@@ -1796,7 +1796,7 @@
         <v>222</v>
       </c>
       <c r="S6" t="n">
-        <v>1501.4</v>
+        <v>1500.7</v>
       </c>
     </row>
     <row r="7">
@@ -1815,10 +1815,10 @@
         <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1419.3</v>
+        <v>1418.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3365</v>
+        <v>1.305</v>
       </c>
       <c r="G7" t="n">
         <v>108.75</v>
@@ -1857,7 +1857,7 @@
         <v>157</v>
       </c>
       <c r="S7" t="n">
-        <v>1468</v>
+        <v>1467.4</v>
       </c>
     </row>
     <row r="8">
@@ -1876,10 +1876,10 @@
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1391.4</v>
+        <v>1391</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2165</v>
+        <v>-0.2206</v>
       </c>
       <c r="G8" t="n">
         <v>114.44</v>
@@ -1918,7 +1918,7 @@
         <v>190</v>
       </c>
       <c r="S8" t="n">
-        <v>1459.5</v>
+        <v>1458.9</v>
       </c>
     </row>
     <row r="9">
@@ -1937,10 +1937,10 @@
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1478.7</v>
+        <v>1478.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0696</v>
+        <v>1.058</v>
       </c>
       <c r="G9" t="n">
         <v>109.4</v>
@@ -1979,7 +1979,7 @@
         <v>204</v>
       </c>
       <c r="S9" t="n">
-        <v>1451.7</v>
+        <v>1451.3</v>
       </c>
     </row>
   </sheetData>
@@ -2109,10 +2109,10 @@
         <v>118</v>
       </c>
       <c r="E2" t="n">
-        <v>1753.8</v>
+        <v>1752.3</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6074</v>
+        <v>5.5868</v>
       </c>
       <c r="G2" t="n">
         <v>118.84</v>
@@ -2151,7 +2151,7 @@
         <v>55</v>
       </c>
       <c r="S2" t="n">
-        <v>1487.2</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="3">
@@ -2170,10 +2170,10 @@
         <v>118</v>
       </c>
       <c r="E3" t="n">
-        <v>1625.8</v>
+        <v>1623.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4157</v>
+        <v>1.3833</v>
       </c>
       <c r="G3" t="n">
         <v>111.03</v>
@@ -2212,7 +2212,7 @@
         <v>112</v>
       </c>
       <c r="S3" t="n">
-        <v>1527.8</v>
+        <v>1526.1</v>
       </c>
     </row>
     <row r="4">
@@ -2231,10 +2231,10 @@
         <v>118</v>
       </c>
       <c r="E4" t="n">
-        <v>1591.6</v>
+        <v>1589.7</v>
       </c>
       <c r="F4" t="n">
-        <v>2.307</v>
+        <v>2.2669</v>
       </c>
       <c r="G4" t="n">
         <v>110.94</v>
@@ -2273,7 +2273,7 @@
         <v>90</v>
       </c>
       <c r="S4" t="n">
-        <v>1507.2</v>
+        <v>1505.7</v>
       </c>
     </row>
     <row r="5">
@@ -2292,10 +2292,10 @@
         <v>118</v>
       </c>
       <c r="E5" t="n">
-        <v>1583</v>
+        <v>1581.7</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7153</v>
+        <v>4.703</v>
       </c>
       <c r="G5" t="n">
         <v>116.24</v>
@@ -2334,7 +2334,7 @@
         <v>101</v>
       </c>
       <c r="S5" t="n">
-        <v>1505.6</v>
+        <v>1504.9</v>
       </c>
     </row>
     <row r="6">
@@ -2353,10 +2353,10 @@
         <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>1521.6</v>
+        <v>1520.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8755</v>
+        <v>1.8071</v>
       </c>
       <c r="G6" t="n">
         <v>107.6</v>
@@ -2395,7 +2395,7 @@
         <v>116</v>
       </c>
       <c r="S6" t="n">
-        <v>1504.2</v>
+        <v>1502.8</v>
       </c>
     </row>
     <row r="7">
@@ -2414,10 +2414,10 @@
         <v>122</v>
       </c>
       <c r="E7" t="n">
-        <v>1548.2</v>
+        <v>1547.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3824</v>
+        <v>-4.3733</v>
       </c>
       <c r="G7" t="n">
         <v>106.65</v>
@@ -2456,7 +2456,7 @@
         <v>81</v>
       </c>
       <c r="S7" t="n">
-        <v>1508.1</v>
+        <v>1507.2</v>
       </c>
     </row>
     <row r="8">
@@ -2475,10 +2475,10 @@
         <v>122</v>
       </c>
       <c r="E8" t="n">
-        <v>1462.3</v>
+        <v>1460.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7974</v>
+        <v>0.7665</v>
       </c>
       <c r="G8" t="n">
         <v>105.92</v>
@@ -2517,7 +2517,7 @@
         <v>155</v>
       </c>
       <c r="S8" t="n">
-        <v>1519.4</v>
+        <v>1518.4</v>
       </c>
     </row>
     <row r="9">
@@ -2536,10 +2536,10 @@
         <v>122</v>
       </c>
       <c r="E9" t="n">
-        <v>1474.9</v>
+        <v>1473.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7808</v>
+        <v>0.7702</v>
       </c>
       <c r="G9" t="n">
         <v>102.61</v>
@@ -2578,7 +2578,7 @@
         <v>113</v>
       </c>
       <c r="S9" t="n">
-        <v>1518.9</v>
+        <v>1517.4</v>
       </c>
     </row>
     <row r="10">
@@ -2597,10 +2597,10 @@
         <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1501.7</v>
+        <v>1499.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.4324</v>
+        <v>-7.1954</v>
       </c>
       <c r="G10" t="n">
         <v>107.72</v>
@@ -2639,7 +2639,7 @@
         <v>206</v>
       </c>
       <c r="S10" t="n">
-        <v>1522</v>
+        <v>1520.7</v>
       </c>
     </row>
     <row r="11">
@@ -2658,10 +2658,10 @@
         <v>122</v>
       </c>
       <c r="E11" t="n">
-        <v>1428.5</v>
+        <v>1427.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2579</v>
+        <v>-3.2441</v>
       </c>
       <c r="G11" t="n">
         <v>102.44</v>
@@ -2700,7 +2700,7 @@
         <v>216</v>
       </c>
       <c r="S11" t="n">
-        <v>1523.5</v>
+        <v>1522.9</v>
       </c>
     </row>
     <row r="12">
@@ -2719,10 +2719,10 @@
         <v>122</v>
       </c>
       <c r="E12" t="n">
-        <v>1329.8</v>
+        <v>1329.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.036</v>
+        <v>-2.0436</v>
       </c>
       <c r="G12" t="n">
         <v>97.12</v>
@@ -2761,7 +2761,7 @@
         <v>304</v>
       </c>
       <c r="S12" t="n">
-        <v>1568.2</v>
+        <v>1566.8</v>
       </c>
     </row>
   </sheetData>
@@ -2891,10 +2891,10 @@
         <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1864.3</v>
+        <v>1858.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3251</v>
+        <v>0.4232</v>
       </c>
       <c r="G2" t="n">
         <v>119.66</v>
@@ -2933,7 +2933,7 @@
         <v>26</v>
       </c>
       <c r="S2" t="n">
-        <v>1591.6</v>
+        <v>1589.9</v>
       </c>
     </row>
     <row r="3">
@@ -2952,10 +2952,10 @@
         <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>1825.3</v>
+        <v>1822.6</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1386</v>
+        <v>3.8299</v>
       </c>
       <c r="G3" t="n">
         <v>114.16</v>
@@ -2994,7 +2994,7 @@
         <v>42</v>
       </c>
       <c r="S3" t="n">
-        <v>1590</v>
+        <v>1587.8</v>
       </c>
     </row>
     <row r="4">
@@ -3013,10 +3013,10 @@
         <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>1784.9</v>
+        <v>1781.6</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7312</v>
+        <v>6.1342</v>
       </c>
       <c r="G4" t="n">
         <v>110.23</v>
@@ -3055,7 +3055,7 @@
         <v>44</v>
       </c>
       <c r="S4" t="n">
-        <v>1653.1</v>
+        <v>1653.2</v>
       </c>
     </row>
     <row r="5">
@@ -3074,10 +3074,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1722.6</v>
+        <v>1718.4</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6005</v>
+        <v>6.6944</v>
       </c>
       <c r="G5" t="n">
         <v>109.82</v>
@@ -3116,7 +3116,7 @@
         <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>1577</v>
+        <v>1575.6</v>
       </c>
     </row>
     <row r="6">
@@ -3135,10 +3135,10 @@
         <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1673.6</v>
+        <v>1673.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.2938</v>
+        <v>-5.7426</v>
       </c>
       <c r="G6" t="n">
         <v>119.56</v>
@@ -3177,7 +3177,7 @@
         <v>88</v>
       </c>
       <c r="S6" t="n">
-        <v>1559.4</v>
+        <v>1557.5</v>
       </c>
     </row>
     <row r="7">
@@ -3196,10 +3196,10 @@
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1727.7</v>
+        <v>1725.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3169</v>
+        <v>-2.372</v>
       </c>
       <c r="G7" t="n">
         <v>113.86</v>
@@ -3238,7 +3238,7 @@
         <v>59</v>
       </c>
       <c r="S7" t="n">
-        <v>1623.5</v>
+        <v>1621.6</v>
       </c>
     </row>
     <row r="8">
@@ -3257,10 +3257,10 @@
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1738.9</v>
+        <v>1735.9</v>
       </c>
       <c r="F8" t="n">
-        <v>7.3067</v>
+        <v>7.2596</v>
       </c>
       <c r="G8" t="n">
         <v>112.85</v>
@@ -3299,7 +3299,7 @@
         <v>67</v>
       </c>
       <c r="S8" t="n">
-        <v>1614.5</v>
+        <v>1612.8</v>
       </c>
     </row>
     <row r="9">
@@ -3318,10 +3318,10 @@
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1653.5</v>
+        <v>1651.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5039</v>
+        <v>1.4503</v>
       </c>
       <c r="G9" t="n">
         <v>112.07</v>
@@ -3360,7 +3360,7 @@
         <v>126</v>
       </c>
       <c r="S9" t="n">
-        <v>1621</v>
+        <v>1619.2</v>
       </c>
     </row>
     <row r="10">
@@ -3379,10 +3379,10 @@
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1524.7</v>
+        <v>1523.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.385</v>
+        <v>-0.3879</v>
       </c>
       <c r="G10" t="n">
         <v>112.57</v>
@@ -3421,7 +3421,7 @@
         <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>1569.8</v>
+        <v>1568.9</v>
       </c>
     </row>
     <row r="11">
@@ -3440,10 +3440,10 @@
         <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1423.4</v>
+        <v>1422.5</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4993</v>
+        <v>2.4973</v>
       </c>
       <c r="G11" t="n">
         <v>105.7</v>
@@ -3482,7 +3482,7 @@
         <v>139</v>
       </c>
       <c r="S11" t="n">
-        <v>1581.4</v>
+        <v>1579.9</v>
       </c>
     </row>
     <row r="12">
@@ -3501,10 +3501,10 @@
         <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1365.1</v>
+        <v>1364.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3076</v>
+        <v>-3.3087</v>
       </c>
       <c r="G12" t="n">
         <v>105.89</v>
@@ -3543,7 +3543,7 @@
         <v>256</v>
       </c>
       <c r="S12" t="n">
-        <v>1586.5</v>
+        <v>1585.4</v>
       </c>
     </row>
     <row r="13">
@@ -3562,10 +3562,10 @@
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1257.8</v>
+        <v>1257.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3848</v>
+        <v>-2.4029</v>
       </c>
       <c r="G13" t="n">
         <v>93.45999999999999</v>
@@ -3604,7 +3604,7 @@
         <v>349</v>
       </c>
       <c r="S13" t="n">
-        <v>1563.3</v>
+        <v>1561.6</v>
       </c>
     </row>
   </sheetData>
@@ -3734,10 +3734,10 @@
         <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>1430.5</v>
+        <v>1430.4</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2584</v>
+        <v>3.2549</v>
       </c>
       <c r="G2" t="n">
         <v>113.28</v>
@@ -3776,7 +3776,7 @@
         <v>127</v>
       </c>
       <c r="S2" t="n">
-        <v>1375.7</v>
+        <v>1375.2</v>
       </c>
     </row>
     <row r="3">
@@ -3795,10 +3795,10 @@
         <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>1319.8</v>
+        <v>1320.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6937</v>
+        <v>-0.7048</v>
       </c>
       <c r="G3" t="n">
         <v>104.37</v>
@@ -3837,7 +3837,7 @@
         <v>290</v>
       </c>
       <c r="S3" t="n">
-        <v>1397.9</v>
+        <v>1399.1</v>
       </c>
     </row>
     <row r="4">
@@ -3856,10 +3856,10 @@
         <v>122</v>
       </c>
       <c r="E4" t="n">
-        <v>1421.4</v>
+        <v>1421.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1948</v>
+        <v>0.2169</v>
       </c>
       <c r="G4" t="n">
         <v>111.41</v>
@@ -3898,7 +3898,7 @@
         <v>228</v>
       </c>
       <c r="S4" t="n">
-        <v>1420.4</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="5">
@@ -3917,10 +3917,10 @@
         <v>122</v>
       </c>
       <c r="E5" t="n">
-        <v>1343</v>
+        <v>1343.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6521</v>
+        <v>-2.6522</v>
       </c>
       <c r="G5" t="n">
         <v>115.3</v>
@@ -4089,10 +4089,10 @@
         <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1993.6</v>
+        <v>2002.2</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3059</v>
+        <v>2.5717</v>
       </c>
       <c r="G2" t="n">
         <v>121.4</v>
@@ -4131,7 +4131,7 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1699.9</v>
+        <v>1700.4</v>
       </c>
     </row>
     <row r="3">
@@ -4150,10 +4150,10 @@
         <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1966.5</v>
+        <v>1967.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6248</v>
+        <v>-1.6145</v>
       </c>
       <c r="G3" t="n">
         <v>121.39</v>
@@ -4211,10 +4211,10 @@
         <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1932.7</v>
+        <v>1940.1</v>
       </c>
       <c r="F4" t="n">
-        <v>6.7834</v>
+        <v>5.7735</v>
       </c>
       <c r="G4" t="n">
         <v>123.18</v>
@@ -4253,7 +4253,7 @@
         <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>1725.9</v>
+        <v>1727.6</v>
       </c>
     </row>
     <row r="5">
@@ -4272,10 +4272,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1912.8</v>
+        <v>1915.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7463</v>
+        <v>-1.8805</v>
       </c>
       <c r="G5" t="n">
         <v>117.37</v>
@@ -4314,7 +4314,7 @@
         <v>20</v>
       </c>
       <c r="S5" t="n">
-        <v>1692.2</v>
+        <v>1693.7</v>
       </c>
     </row>
     <row r="6">
@@ -4333,10 +4333,10 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1768.2</v>
+        <v>1767.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8893</v>
+        <v>-2.184</v>
       </c>
       <c r="G6" t="n">
         <v>115.23</v>
@@ -4375,7 +4375,7 @@
         <v>53</v>
       </c>
       <c r="S6" t="n">
-        <v>1637.7</v>
+        <v>1638.6</v>
       </c>
     </row>
     <row r="7">
@@ -4394,10 +4394,10 @@
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1921</v>
+        <v>1918.7</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9274</v>
+        <v>2.6895</v>
       </c>
       <c r="G7" t="n">
         <v>121.87</v>
@@ -4436,7 +4436,7 @@
         <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>1684</v>
+        <v>1684.4</v>
       </c>
     </row>
     <row r="8">
@@ -4455,10 +4455,10 @@
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1836.9</v>
+        <v>1835.2</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4256</v>
+        <v>4.7779</v>
       </c>
       <c r="G8" t="n">
         <v>118.62</v>
@@ -4516,10 +4516,10 @@
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1893.4</v>
+        <v>1894.4</v>
       </c>
       <c r="F9" t="n">
-        <v>6.006</v>
+        <v>5.7232</v>
       </c>
       <c r="G9" t="n">
         <v>116.85</v>
@@ -4577,10 +4577,10 @@
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1810.7</v>
+        <v>1808.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8284</v>
+        <v>0.1677</v>
       </c>
       <c r="G10" t="n">
         <v>120.8</v>
@@ -4619,7 +4619,7 @@
         <v>31</v>
       </c>
       <c r="S10" t="n">
-        <v>1647.3</v>
+        <v>1648.7</v>
       </c>
     </row>
     <row r="11">
@@ -4638,10 +4638,10 @@
         <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1777.5</v>
+        <v>1775.6</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2904</v>
+        <v>2.7602</v>
       </c>
       <c r="G11" t="n">
         <v>120.67</v>
@@ -4680,7 +4680,7 @@
         <v>37</v>
       </c>
       <c r="S11" t="n">
-        <v>1700.7</v>
+        <v>1702.7</v>
       </c>
     </row>
     <row r="12">
@@ -4699,10 +4699,10 @@
         <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1835.8</v>
+        <v>1839.6</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.2849</v>
+        <v>-7.8485</v>
       </c>
       <c r="G12" t="n">
         <v>119.39</v>
@@ -4741,7 +4741,7 @@
         <v>38</v>
       </c>
       <c r="S12" t="n">
-        <v>1745.4</v>
+        <v>1747.7</v>
       </c>
     </row>
     <row r="13">
@@ -4760,10 +4760,10 @@
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1687.4</v>
+        <v>1685.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1749</v>
+        <v>-2.7727</v>
       </c>
       <c r="G13" t="n">
         <v>119.85</v>
@@ -4802,7 +4802,7 @@
         <v>62</v>
       </c>
       <c r="S13" t="n">
-        <v>1659.4</v>
+        <v>1660.1</v>
       </c>
     </row>
     <row r="14">
@@ -4821,10 +4821,10 @@
         <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1633.2</v>
+        <v>1629.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2844</v>
+        <v>-1.5728</v>
       </c>
       <c r="G14" t="n">
         <v>106.96</v>
@@ -4863,7 +4863,7 @@
         <v>104</v>
       </c>
       <c r="S14" t="n">
-        <v>1702.1</v>
+        <v>1701.8</v>
       </c>
     </row>
     <row r="15">
@@ -4882,10 +4882,10 @@
         <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>1635.4</v>
+        <v>1636.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.315899999999999</v>
+        <v>-8.902100000000001</v>
       </c>
       <c r="G15" t="n">
         <v>109.52</v>
@@ -4924,7 +4924,7 @@
         <v>91</v>
       </c>
       <c r="S15" t="n">
-        <v>1698.7</v>
+        <v>1697.7</v>
       </c>
     </row>
     <row r="16">
@@ -4943,10 +4943,10 @@
         <v>120</v>
       </c>
       <c r="E16" t="n">
-        <v>1647.8</v>
+        <v>1648.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0692</v>
+        <v>-0.9809</v>
       </c>
       <c r="G16" t="n">
         <v>116.12</v>
@@ -4985,7 +4985,7 @@
         <v>70</v>
       </c>
       <c r="S16" t="n">
-        <v>1654.3</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="17">
@@ -5004,10 +5004,10 @@
         <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>1538.7</v>
+        <v>1537.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.644</v>
+        <v>-2.6339</v>
       </c>
       <c r="G17" t="n">
         <v>109.32</v>
@@ -5046,7 +5046,7 @@
         <v>108</v>
       </c>
       <c r="S17" t="n">
-        <v>1657.2</v>
+        <v>1657.5</v>
       </c>
     </row>
   </sheetData>
@@ -5176,10 +5176,10 @@
         <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>1515</v>
+        <v>1514.8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5934</v>
+        <v>0.598</v>
       </c>
       <c r="G2" t="n">
         <v>116.43</v>
@@ -5218,7 +5218,7 @@
         <v>128</v>
       </c>
       <c r="S2" t="n">
-        <v>1424.7</v>
+        <v>1424.6</v>
       </c>
     </row>
     <row r="3">
@@ -5237,10 +5237,10 @@
         <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>1455.6</v>
+        <v>1454.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.903</v>
+        <v>0.8914</v>
       </c>
       <c r="G3" t="n">
         <v>115.27</v>
@@ -5279,7 +5279,7 @@
         <v>171</v>
       </c>
       <c r="S3" t="n">
-        <v>1455.6</v>
+        <v>1455.1</v>
       </c>
     </row>
     <row r="4">
@@ -5298,10 +5298,10 @@
         <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1487</v>
+        <v>1486.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4064</v>
+        <v>0.4187</v>
       </c>
       <c r="G4" t="n">
         <v>114.27</v>
@@ -5340,7 +5340,7 @@
         <v>240</v>
       </c>
       <c r="S4" t="n">
-        <v>1425.7</v>
+        <v>1426.2</v>
       </c>
     </row>
     <row r="5">
@@ -5359,10 +5359,10 @@
         <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>1444.7</v>
+        <v>1444.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0916</v>
+        <v>-4.0824</v>
       </c>
       <c r="G5" t="n">
         <v>112.06</v>
@@ -5401,7 +5401,7 @@
         <v>213</v>
       </c>
       <c r="S5" t="n">
-        <v>1433.3</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="6">
@@ -5420,10 +5420,10 @@
         <v>117</v>
       </c>
       <c r="E6" t="n">
-        <v>1377.5</v>
+        <v>1377.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0451</v>
+        <v>-0.0597</v>
       </c>
       <c r="G6" t="n">
         <v>110.79</v>
@@ -5462,7 +5462,7 @@
         <v>235</v>
       </c>
       <c r="S6" t="n">
-        <v>1473.2</v>
+        <v>1472.9</v>
       </c>
     </row>
     <row r="7">
@@ -5484,7 +5484,7 @@
         <v>1529.5</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1789</v>
+        <v>1.1809</v>
       </c>
       <c r="G7" t="n">
         <v>110.54</v>
@@ -5523,7 +5523,7 @@
         <v>198</v>
       </c>
       <c r="S7" t="n">
-        <v>1418.9</v>
+        <v>1418.3</v>
       </c>
     </row>
     <row r="8">
@@ -5545,7 +5545,7 @@
         <v>1366.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.834</v>
+        <v>-2.841</v>
       </c>
       <c r="G8" t="n">
         <v>109.54</v>
@@ -5584,7 +5584,7 @@
         <v>298</v>
       </c>
       <c r="S8" t="n">
-        <v>1427.6</v>
+        <v>1427.7</v>
       </c>
     </row>
     <row r="9">
@@ -5603,10 +5603,10 @@
         <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1392</v>
+        <v>1392.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0171</v>
+        <v>-4.0162</v>
       </c>
       <c r="G9" t="n">
         <v>109.83</v>
@@ -5645,7 +5645,7 @@
         <v>286</v>
       </c>
       <c r="S9" t="n">
-        <v>1428.5</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="10">
@@ -5664,10 +5664,10 @@
         <v>117</v>
       </c>
       <c r="E10" t="n">
-        <v>1232.1</v>
+        <v>1231.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1473</v>
+        <v>-0.1472</v>
       </c>
       <c r="G10" t="n">
         <v>100.86</v>
@@ -5706,7 +5706,7 @@
         <v>350</v>
       </c>
       <c r="S10" t="n">
-        <v>1417.6</v>
+        <v>1417.3</v>
       </c>
     </row>
     <row r="11">
@@ -5725,10 +5725,10 @@
         <v>117</v>
       </c>
       <c r="E11" t="n">
-        <v>1237</v>
+        <v>1236.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5951</v>
+        <v>-3.5993</v>
       </c>
       <c r="G11" t="n">
         <v>101.54</v>
@@ -5767,7 +5767,7 @@
         <v>358</v>
       </c>
       <c r="S11" t="n">
-        <v>1432.7</v>
+        <v>1431.8</v>
       </c>
     </row>
   </sheetData>
@@ -5900,7 +5900,7 @@
         <v>1563.2</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2331</v>
+        <v>3.2741</v>
       </c>
       <c r="G2" t="n">
         <v>113.58</v>
@@ -5939,7 +5939,7 @@
         <v>85</v>
       </c>
       <c r="S2" t="n">
-        <v>1382.6</v>
+        <v>1383.2</v>
       </c>
     </row>
     <row r="3">
@@ -5958,10 +5958,10 @@
         <v>119</v>
       </c>
       <c r="E3" t="n">
-        <v>1710.3</v>
+        <v>1718.7</v>
       </c>
       <c r="F3" t="n">
-        <v>3.285</v>
+        <v>2.9617</v>
       </c>
       <c r="G3" t="n">
         <v>115.41</v>
@@ -6000,7 +6000,7 @@
         <v>60</v>
       </c>
       <c r="S3" t="n">
-        <v>1422.9</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="4">
@@ -6019,10 +6019,10 @@
         <v>119</v>
       </c>
       <c r="E4" t="n">
-        <v>1394.2</v>
+        <v>1395</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5557</v>
+        <v>1.606</v>
       </c>
       <c r="G4" t="n">
         <v>109.77</v>
@@ -6061,7 +6061,7 @@
         <v>137</v>
       </c>
       <c r="S4" t="n">
-        <v>1425</v>
+        <v>1426.5</v>
       </c>
     </row>
     <row r="5">
@@ -6080,10 +6080,10 @@
         <v>119</v>
       </c>
       <c r="E5" t="n">
-        <v>1376.6</v>
+        <v>1376.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4682</v>
+        <v>-0.451</v>
       </c>
       <c r="G5" t="n">
         <v>102.17</v>
@@ -6141,10 +6141,10 @@
         <v>119</v>
       </c>
       <c r="E6" t="n">
-        <v>1340.2</v>
+        <v>1339.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5172</v>
+        <v>0.5343</v>
       </c>
       <c r="G6" t="n">
         <v>106.23</v>
@@ -6183,7 +6183,7 @@
         <v>203</v>
       </c>
       <c r="S6" t="n">
-        <v>1457.9</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="7">
@@ -6205,7 +6205,7 @@
         <v>1362.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5288</v>
+        <v>-1.5128</v>
       </c>
       <c r="G7" t="n">
         <v>104.43</v>
@@ -6244,7 +6244,7 @@
         <v>251</v>
       </c>
       <c r="S7" t="n">
-        <v>1433.8</v>
+        <v>1434.9</v>
       </c>
     </row>
     <row r="8">
@@ -6266,7 +6266,7 @@
         <v>1276.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.832</v>
+        <v>-0.8273</v>
       </c>
       <c r="G8" t="n">
         <v>103.46</v>
@@ -6305,7 +6305,7 @@
         <v>301</v>
       </c>
       <c r="S8" t="n">
-        <v>1424.5</v>
+        <v>1424.2</v>
       </c>
     </row>
     <row r="9">
@@ -6324,10 +6324,10 @@
         <v>119</v>
       </c>
       <c r="E9" t="n">
-        <v>1288.3</v>
+        <v>1288.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6901</v>
+        <v>-1.681</v>
       </c>
       <c r="G9" t="n">
         <v>102.39</v>
@@ -6366,7 +6366,7 @@
         <v>294</v>
       </c>
       <c r="S9" t="n">
-        <v>1441.9</v>
+        <v>1441.7</v>
       </c>
     </row>
   </sheetData>
@@ -6496,10 +6496,10 @@
         <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>2055.1</v>
+        <v>2061.6</v>
       </c>
       <c r="F2" t="n">
-        <v>6.9647</v>
+        <v>6.7538</v>
       </c>
       <c r="G2" t="n">
         <v>120.35</v>
@@ -6538,7 +6538,7 @@
         <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>1597.1</v>
+        <v>1597.9</v>
       </c>
     </row>
     <row r="3">
@@ -6560,7 +6560,7 @@
         <v>1877.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2467</v>
+        <v>-0.5286</v>
       </c>
       <c r="G3" t="n">
         <v>118.87</v>
@@ -6599,7 +6599,7 @@
         <v>21</v>
       </c>
       <c r="S3" t="n">
-        <v>1595.8</v>
+        <v>1595.3</v>
       </c>
     </row>
     <row r="4">
@@ -6618,10 +6618,10 @@
         <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1765.3</v>
+        <v>1765.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5462</v>
+        <v>-0.7176</v>
       </c>
       <c r="G4" t="n">
         <v>117.4</v>
@@ -6660,7 +6660,7 @@
         <v>40</v>
       </c>
       <c r="S4" t="n">
-        <v>1571</v>
+        <v>1571.8</v>
       </c>
     </row>
     <row r="5">
@@ -6679,10 +6679,10 @@
         <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>1544.1</v>
+        <v>1543.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0583</v>
+        <v>-3.0737</v>
       </c>
       <c r="G5" t="n">
         <v>106.94</v>
@@ -6721,7 +6721,7 @@
         <v>175</v>
       </c>
       <c r="S5" t="n">
-        <v>1540</v>
+        <v>1539.5</v>
       </c>
     </row>
     <row r="6">
@@ -6740,10 +6740,10 @@
         <v>117</v>
       </c>
       <c r="E6" t="n">
-        <v>1566.3</v>
+        <v>1564.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.2596</v>
+        <v>-4.1724</v>
       </c>
       <c r="G6" t="n">
         <v>108.93</v>
@@ -6782,7 +6782,7 @@
         <v>122</v>
       </c>
       <c r="S6" t="n">
-        <v>1574.8</v>
+        <v>1573.6</v>
       </c>
     </row>
     <row r="7">
@@ -6801,10 +6801,10 @@
         <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1433</v>
+        <v>1432.7</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1251</v>
+        <v>4.1195</v>
       </c>
       <c r="G7" t="n">
         <v>108.15</v>
@@ -6843,7 +6843,7 @@
         <v>115</v>
       </c>
       <c r="S7" t="n">
-        <v>1522.5</v>
+        <v>1522.4</v>
       </c>
     </row>
     <row r="8">
@@ -6862,10 +6862,10 @@
         <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>1553.4</v>
+        <v>1553.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7641</v>
+        <v>2.7763</v>
       </c>
       <c r="G8" t="n">
         <v>101.85</v>
@@ -6904,7 +6904,7 @@
         <v>118</v>
       </c>
       <c r="S8" t="n">
-        <v>1530.4</v>
+        <v>1530.5</v>
       </c>
     </row>
     <row r="9">
@@ -6923,10 +6923,10 @@
         <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1458.7</v>
+        <v>1458.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9786</v>
+        <v>-1.9961</v>
       </c>
       <c r="G9" t="n">
         <v>109.85</v>
@@ -6965,7 +6965,7 @@
         <v>135</v>
       </c>
       <c r="S9" t="n">
-        <v>1567.7</v>
+        <v>1567.6</v>
       </c>
     </row>
     <row r="10">
@@ -6984,10 +6984,10 @@
         <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1412.6</v>
+        <v>1412.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.453</v>
+        <v>1.4459</v>
       </c>
       <c r="G10" t="n">
         <v>102.44</v>
@@ -7026,7 +7026,7 @@
         <v>227</v>
       </c>
       <c r="S10" t="n">
-        <v>1532.3</v>
+        <v>1532.4</v>
       </c>
     </row>
     <row r="11">
@@ -7045,10 +7045,10 @@
         <v>122</v>
       </c>
       <c r="E11" t="n">
-        <v>1472.7</v>
+        <v>1471.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.7748</v>
+        <v>-5.748</v>
       </c>
       <c r="G11" t="n">
         <v>105.07</v>
@@ -7087,7 +7087,7 @@
         <v>166</v>
       </c>
       <c r="S11" t="n">
-        <v>1516.2</v>
+        <v>1515.5</v>
       </c>
     </row>
     <row r="12">
@@ -7106,10 +7106,10 @@
         <v>122</v>
       </c>
       <c r="E12" t="n">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F12" t="n">
-        <v>1.825</v>
+        <v>1.7876</v>
       </c>
       <c r="G12" t="n">
         <v>104.99</v>
@@ -7148,7 +7148,7 @@
         <v>244</v>
       </c>
       <c r="S12" t="n">
-        <v>1528.1</v>
+        <v>1527.7</v>
       </c>
     </row>
     <row r="13">
@@ -7167,10 +7167,10 @@
         <v>122</v>
       </c>
       <c r="E13" t="n">
-        <v>1308.9</v>
+        <v>1308.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8402</v>
+        <v>-1.8484</v>
       </c>
       <c r="G13" t="n">
         <v>100.55</v>
@@ -7209,7 +7209,7 @@
         <v>270</v>
       </c>
       <c r="S13" t="n">
-        <v>1522.7</v>
+        <v>1523.1</v>
       </c>
     </row>
   </sheetData>
@@ -7339,10 +7339,10 @@
         <v>119</v>
       </c>
       <c r="E2" t="n">
-        <v>2170.1</v>
+        <v>2179.5</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9737</v>
+        <v>3.6659</v>
       </c>
       <c r="G2" t="n">
         <v>123.79</v>
@@ -7381,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1690.2</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="3">
@@ -7400,10 +7400,10 @@
         <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>1951.2</v>
+        <v>1951.6</v>
       </c>
       <c r="F3" t="n">
-        <v>13.9718</v>
+        <v>14.014</v>
       </c>
       <c r="G3" t="n">
         <v>118.9</v>
@@ -7442,7 +7442,7 @@
         <v>14</v>
       </c>
       <c r="S3" t="n">
-        <v>1635.2</v>
+        <v>1635.8</v>
       </c>
     </row>
     <row r="4">
@@ -7461,10 +7461,10 @@
         <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1773.8</v>
+        <v>1775.8</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7945</v>
+        <v>12.7773</v>
       </c>
       <c r="G4" t="n">
         <v>117.09</v>
@@ -7503,7 +7503,7 @@
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>1607.1</v>
+        <v>1609.3</v>
       </c>
     </row>
     <row r="5">
@@ -7522,10 +7522,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1921.2</v>
+        <v>1921.9</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4067</v>
+        <v>2.4321</v>
       </c>
       <c r="G5" t="n">
         <v>115.82</v>
@@ -7564,7 +7564,7 @@
         <v>25</v>
       </c>
       <c r="S5" t="n">
-        <v>1655.5</v>
+        <v>1655.6</v>
       </c>
     </row>
     <row r="6">
@@ -7583,10 +7583,10 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1839.7</v>
+        <v>1836.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0742</v>
+        <v>3.8425</v>
       </c>
       <c r="G6" t="n">
         <v>112.26</v>
@@ -7625,7 +7625,7 @@
         <v>35</v>
       </c>
       <c r="S6" t="n">
-        <v>1652.1</v>
+        <v>1652.4</v>
       </c>
     </row>
     <row r="7">
@@ -7644,10 +7644,10 @@
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1830.2</v>
+        <v>1830.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.7351</v>
+        <v>-3.0745</v>
       </c>
       <c r="G7" t="n">
         <v>119.03</v>
@@ -7686,7 +7686,7 @@
         <v>17</v>
       </c>
       <c r="S7" t="n">
-        <v>1675</v>
+        <v>1677.2</v>
       </c>
     </row>
     <row r="8">
@@ -7705,10 +7705,10 @@
         <v>119</v>
       </c>
       <c r="E8" t="n">
-        <v>1751.4</v>
+        <v>1751.7</v>
       </c>
       <c r="F8" t="n">
-        <v>8.2582</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="G8" t="n">
         <v>118.51</v>
@@ -7747,7 +7747,7 @@
         <v>29</v>
       </c>
       <c r="S8" t="n">
-        <v>1678.8</v>
+        <v>1678.3</v>
       </c>
     </row>
     <row r="9">
@@ -7766,10 +7766,10 @@
         <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1606</v>
+        <v>1607.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2483</v>
+        <v>-1.2916</v>
       </c>
       <c r="G9" t="n">
         <v>110.66</v>
@@ -7808,7 +7808,7 @@
         <v>77</v>
       </c>
       <c r="S9" t="n">
-        <v>1647.5</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="10">
@@ -7827,10 +7827,10 @@
         <v>121</v>
       </c>
       <c r="E10" t="n">
-        <v>1728.5</v>
+        <v>1730.3</v>
       </c>
       <c r="F10" t="n">
-        <v>8.044</v>
+        <v>8.0456</v>
       </c>
       <c r="G10" t="n">
         <v>109.41</v>
@@ -7869,7 +7869,7 @@
         <v>64</v>
       </c>
       <c r="S10" t="n">
-        <v>1599.2</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11">
@@ -7888,10 +7888,10 @@
         <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1733.6</v>
+        <v>1734.2</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8143</v>
+        <v>2.838</v>
       </c>
       <c r="G11" t="n">
         <v>111.86</v>
@@ -7930,7 +7930,7 @@
         <v>65</v>
       </c>
       <c r="S11" t="n">
-        <v>1622</v>
+        <v>1622.2</v>
       </c>
     </row>
     <row r="12">
@@ -7949,10 +7949,10 @@
         <v>121</v>
       </c>
       <c r="E12" t="n">
-        <v>1753.7</v>
+        <v>1752.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2979</v>
+        <v>1.268</v>
       </c>
       <c r="G12" t="n">
         <v>118.53</v>
@@ -7991,7 +7991,7 @@
         <v>36</v>
       </c>
       <c r="S12" t="n">
-        <v>1646.7</v>
+        <v>1646.2</v>
       </c>
     </row>
     <row r="13">
@@ -8010,10 +8010,10 @@
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1718</v>
+        <v>1718.5</v>
       </c>
       <c r="F13" t="n">
-        <v>6.2269</v>
+        <v>6.1973</v>
       </c>
       <c r="G13" t="n">
         <v>112.42</v>
@@ -8052,7 +8052,7 @@
         <v>54</v>
       </c>
       <c r="S13" t="n">
-        <v>1648</v>
+        <v>1648.5</v>
       </c>
     </row>
     <row r="14">
@@ -8071,10 +8071,10 @@
         <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1637.3</v>
+        <v>1637.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9629</v>
+        <v>-3.1375</v>
       </c>
       <c r="G14" t="n">
         <v>112.06</v>
@@ -8113,7 +8113,7 @@
         <v>69</v>
       </c>
       <c r="S14" t="n">
-        <v>1669.8</v>
+        <v>1670.9</v>
       </c>
     </row>
     <row r="15">
@@ -8132,10 +8132,10 @@
         <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>1593</v>
+        <v>1593.4</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2532</v>
+        <v>1.2389</v>
       </c>
       <c r="G15" t="n">
         <v>108.18</v>
@@ -8174,7 +8174,7 @@
         <v>79</v>
       </c>
       <c r="S15" t="n">
-        <v>1667.2</v>
+        <v>1667.8</v>
       </c>
     </row>
     <row r="16">
@@ -8196,7 +8196,7 @@
         <v>1510.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.4673</v>
+        <v>-5.4665</v>
       </c>
       <c r="G16" t="n">
         <v>106.74</v>
@@ -8365,10 +8365,10 @@
         <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>1713.4</v>
+        <v>1709.5</v>
       </c>
       <c r="F2" t="n">
-        <v>9.475099999999999</v>
+        <v>9.3651</v>
       </c>
       <c r="G2" t="n">
         <v>115.67</v>
@@ -8407,7 +8407,7 @@
         <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>1560.8</v>
+        <v>1558.8</v>
       </c>
     </row>
     <row r="3">
@@ -8426,10 +8426,10 @@
         <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>1677.6</v>
+        <v>1676.2</v>
       </c>
       <c r="F3" t="n">
-        <v>9.6843</v>
+        <v>9.632899999999999</v>
       </c>
       <c r="G3" t="n">
         <v>122.85</v>
@@ -8468,7 +8468,7 @@
         <v>50</v>
       </c>
       <c r="S3" t="n">
-        <v>1503.6</v>
+        <v>1502.5</v>
       </c>
     </row>
     <row r="4">
@@ -8487,10 +8487,10 @@
         <v>118</v>
       </c>
       <c r="E4" t="n">
-        <v>1614.6</v>
+        <v>1613.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3875</v>
+        <v>1.3577</v>
       </c>
       <c r="G4" t="n">
         <v>112.04</v>
@@ -8529,7 +8529,7 @@
         <v>83</v>
       </c>
       <c r="S4" t="n">
-        <v>1530.2</v>
+        <v>1529.6</v>
       </c>
     </row>
     <row r="5">
@@ -8548,10 +8548,10 @@
         <v>121</v>
       </c>
       <c r="E5" t="n">
-        <v>1599.9</v>
+        <v>1597.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5599</v>
+        <v>0.5946</v>
       </c>
       <c r="G5" t="n">
         <v>108.59</v>
@@ -8590,7 +8590,7 @@
         <v>114</v>
       </c>
       <c r="S5" t="n">
-        <v>1505.6</v>
+        <v>1504.4</v>
       </c>
     </row>
     <row r="6">
@@ -8609,10 +8609,10 @@
         <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>1579.4</v>
+        <v>1577.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2688</v>
+        <v>-1.2377</v>
       </c>
       <c r="G6" t="n">
         <v>109.09</v>
@@ -8651,7 +8651,7 @@
         <v>121</v>
       </c>
       <c r="S6" t="n">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7">
@@ -8670,10 +8670,10 @@
         <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1440.4</v>
+        <v>1439.3</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3894</v>
+        <v>1.3639</v>
       </c>
       <c r="G7" t="n">
         <v>112.74</v>
@@ -8712,7 +8712,7 @@
         <v>169</v>
       </c>
       <c r="S7" t="n">
-        <v>1493.2</v>
+        <v>1491.9</v>
       </c>
     </row>
     <row r="8">
@@ -8731,10 +8731,10 @@
         <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>1537.2</v>
+        <v>1536.7</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.3054</v>
+        <v>-5.3186</v>
       </c>
       <c r="G8" t="n">
         <v>104.14</v>
@@ -8773,7 +8773,7 @@
         <v>143</v>
       </c>
       <c r="S8" t="n">
-        <v>1505.6</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="9">
@@ -8792,10 +8792,10 @@
         <v>122</v>
       </c>
       <c r="E9" t="n">
-        <v>1495.3</v>
+        <v>1493.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8165</v>
+        <v>-1.8307</v>
       </c>
       <c r="G9" t="n">
         <v>104.53</v>
@@ -8834,7 +8834,7 @@
         <v>197</v>
       </c>
       <c r="S9" t="n">
-        <v>1532.1</v>
+        <v>1529.8</v>
       </c>
     </row>
     <row r="10">
@@ -8853,10 +8853,10 @@
         <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1509.4</v>
+        <v>1508.2</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.64</v>
+        <v>-1.6583</v>
       </c>
       <c r="G10" t="n">
         <v>111.93</v>
@@ -8895,7 +8895,7 @@
         <v>177</v>
       </c>
       <c r="S10" t="n">
-        <v>1493.4</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="11">
@@ -8914,10 +8914,10 @@
         <v>122</v>
       </c>
       <c r="E11" t="n">
-        <v>1562.9</v>
+        <v>1560.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.6224</v>
+        <v>-5.242</v>
       </c>
       <c r="G11" t="n">
         <v>103.89</v>
@@ -8956,7 +8956,7 @@
         <v>130</v>
       </c>
       <c r="S11" t="n">
-        <v>1613.5</v>
+        <v>1612.9</v>
       </c>
     </row>
   </sheetData>
@@ -9086,10 +9086,10 @@
         <v>119</v>
       </c>
       <c r="E2" t="n">
-        <v>2242.8</v>
+        <v>2252.6</v>
       </c>
       <c r="F2" t="n">
-        <v>8.6394</v>
+        <v>8.169700000000001</v>
       </c>
       <c r="G2" t="n">
         <v>120.84</v>
@@ -9128,7 +9128,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1747.2</v>
+        <v>1751.1</v>
       </c>
     </row>
     <row r="3">
@@ -9147,10 +9147,10 @@
         <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>2085.1</v>
+        <v>2099.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2.67</v>
+        <v>1.9173</v>
       </c>
       <c r="G3" t="n">
         <v>117.81</v>
@@ -9189,7 +9189,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1703.4</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="4">
@@ -9208,10 +9208,10 @@
         <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>2034.5</v>
+        <v>2044.2</v>
       </c>
       <c r="F4" t="n">
-        <v>11.3167</v>
+        <v>10.5951</v>
       </c>
       <c r="G4" t="n">
         <v>118.24</v>
@@ -9250,7 +9250,7 @@
         <v>13</v>
       </c>
       <c r="S4" t="n">
-        <v>1753.9</v>
+        <v>1756.8</v>
       </c>
     </row>
     <row r="5">
@@ -9269,10 +9269,10 @@
         <v>119</v>
       </c>
       <c r="E5" t="n">
-        <v>2030.1</v>
+        <v>2024.5</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0314</v>
+        <v>3.6605</v>
       </c>
       <c r="G5" t="n">
         <v>118.09</v>
@@ -9311,7 +9311,7 @@
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>1692.3</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="6">
@@ -9330,10 +9330,10 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1972.3</v>
+        <v>1971.6</v>
       </c>
       <c r="F6" t="n">
-        <v>11.3738</v>
+        <v>11.9283</v>
       </c>
       <c r="G6" t="n">
         <v>110.16</v>
@@ -9372,7 +9372,7 @@
         <v>15</v>
       </c>
       <c r="S6" t="n">
-        <v>1777.3</v>
+        <v>1779.6</v>
       </c>
     </row>
     <row r="7">
@@ -9391,10 +9391,10 @@
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1824.2</v>
+        <v>1827.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8019</v>
+        <v>6.8987</v>
       </c>
       <c r="G7" t="n">
         <v>110.58</v>
@@ -9433,7 +9433,7 @@
         <v>45</v>
       </c>
       <c r="S7" t="n">
-        <v>1678</v>
+        <v>1681.1</v>
       </c>
     </row>
     <row r="8">
@@ -9452,10 +9452,10 @@
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1839.8</v>
+        <v>1838.2</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5365</v>
+        <v>7.6713</v>
       </c>
       <c r="G8" t="n">
         <v>115.83</v>
@@ -9494,7 +9494,7 @@
         <v>46</v>
       </c>
       <c r="S8" t="n">
-        <v>1687.9</v>
+        <v>1687.7</v>
       </c>
     </row>
     <row r="9">
@@ -9513,10 +9513,10 @@
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1733.8</v>
+        <v>1733</v>
       </c>
       <c r="F9" t="n">
-        <v>0.433</v>
+        <v>0.4193</v>
       </c>
       <c r="G9" t="n">
         <v>105.76</v>
@@ -9555,7 +9555,7 @@
         <v>49</v>
       </c>
       <c r="S9" t="n">
-        <v>1713</v>
+        <v>1713.8</v>
       </c>
     </row>
     <row r="10">
@@ -9574,10 +9574,10 @@
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1692.7</v>
+        <v>1692.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3873</v>
+        <v>0.3731</v>
       </c>
       <c r="G10" t="n">
         <v>107.19</v>
@@ -9616,7 +9616,7 @@
         <v>58</v>
       </c>
       <c r="S10" t="n">
-        <v>1649.8</v>
+        <v>1650.7</v>
       </c>
     </row>
     <row r="11">
@@ -9635,10 +9635,10 @@
         <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1901.3</v>
+        <v>1905.8</v>
       </c>
       <c r="F11" t="n">
-        <v>2.827</v>
+        <v>2.2762</v>
       </c>
       <c r="G11" t="n">
         <v>117.49</v>
@@ -9677,7 +9677,7 @@
         <v>23</v>
       </c>
       <c r="S11" t="n">
-        <v>1712.1</v>
+        <v>1713.1</v>
       </c>
     </row>
     <row r="12">
@@ -9696,10 +9696,10 @@
         <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1613.1</v>
+        <v>1614.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5669</v>
+        <v>-4.609</v>
       </c>
       <c r="G12" t="n">
         <v>114.63</v>
@@ -9738,7 +9738,7 @@
         <v>78</v>
       </c>
       <c r="S12" t="n">
-        <v>1667.2</v>
+        <v>1668.4</v>
       </c>
     </row>
     <row r="13">
@@ -9757,10 +9757,10 @@
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1681.6</v>
+        <v>1681.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7565</v>
+        <v>-1.7205</v>
       </c>
       <c r="G13" t="n">
         <v>108.88</v>
@@ -9799,7 +9799,7 @@
         <v>73</v>
       </c>
       <c r="S13" t="n">
-        <v>1723.9</v>
+        <v>1725.8</v>
       </c>
     </row>
     <row r="14">
@@ -9818,10 +9818,10 @@
         <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1713.4</v>
+        <v>1711.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1735</v>
+        <v>-1.0529</v>
       </c>
       <c r="G14" t="n">
         <v>110.48</v>
@@ -9860,7 +9860,7 @@
         <v>84</v>
       </c>
       <c r="S14" t="n">
-        <v>1678.3</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="15">
@@ -9879,10 +9879,10 @@
         <v>121</v>
       </c>
       <c r="E15" t="n">
-        <v>1671.5</v>
+        <v>1674.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.0193</v>
+        <v>-6.5504</v>
       </c>
       <c r="G15" t="n">
         <v>114.76</v>
@@ -9921,7 +9921,7 @@
         <v>51</v>
       </c>
       <c r="S15" t="n">
-        <v>1739.8</v>
+        <v>1740.6</v>
       </c>
     </row>
     <row r="16">
@@ -9940,10 +9940,10 @@
         <v>120</v>
       </c>
       <c r="E16" t="n">
-        <v>1581</v>
+        <v>1579.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.2381</v>
+        <v>-5.1262</v>
       </c>
       <c r="G16" t="n">
         <v>106.53</v>
@@ -9982,7 +9982,7 @@
         <v>102</v>
       </c>
       <c r="S16" t="n">
-        <v>1691.8</v>
+        <v>1692.2</v>
       </c>
     </row>
     <row r="17">
@@ -10001,10 +10001,10 @@
         <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>1525</v>
+        <v>1525.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.7872</v>
+        <v>-4.671</v>
       </c>
       <c r="G17" t="n">
         <v>108.53</v>
@@ -10043,7 +10043,7 @@
         <v>123</v>
       </c>
       <c r="S17" t="n">
-        <v>1688.9</v>
+        <v>1690.3</v>
       </c>
     </row>
   </sheetData>
@@ -10173,10 +10173,10 @@
         <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>2083.8</v>
+        <v>2092.8</v>
       </c>
       <c r="F2" t="n">
-        <v>9.8756</v>
+        <v>9.4907</v>
       </c>
       <c r="G2" t="n">
         <v>117.38</v>
@@ -10215,7 +10215,7 @@
         <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>1664.7</v>
+        <v>1667.4</v>
       </c>
     </row>
     <row r="3">
@@ -10237,7 +10237,7 @@
         <v>1955.3</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7636</v>
+        <v>5.539</v>
       </c>
       <c r="G3" t="n">
         <v>113.73</v>
@@ -10276,7 +10276,7 @@
         <v>22</v>
       </c>
       <c r="S3" t="n">
-        <v>1677.8</v>
+        <v>1679.7</v>
       </c>
     </row>
     <row r="4">
@@ -10295,10 +10295,10 @@
         <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1820.1</v>
+        <v>1821.5</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5295</v>
+        <v>6.4146</v>
       </c>
       <c r="G4" t="n">
         <v>114.74</v>
@@ -10337,7 +10337,7 @@
         <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>1643.5</v>
+        <v>1645.7</v>
       </c>
     </row>
     <row r="5">
@@ -10356,10 +10356,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1667.3</v>
+        <v>1668.1</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3395</v>
+        <v>5.3546</v>
       </c>
       <c r="G5" t="n">
         <v>106.11</v>
@@ -10398,7 +10398,7 @@
         <v>56</v>
       </c>
       <c r="S5" t="n">
-        <v>1622.1</v>
+        <v>1623.2</v>
       </c>
     </row>
     <row r="6">
@@ -10417,10 +10417,10 @@
         <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1672.5</v>
+        <v>1675</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8294</v>
+        <v>-2.3235</v>
       </c>
       <c r="G6" t="n">
         <v>110.12</v>
@@ -10459,7 +10459,7 @@
         <v>87</v>
       </c>
       <c r="S6" t="n">
-        <v>1663.7</v>
+        <v>1664.3</v>
       </c>
     </row>
     <row r="7">
@@ -10478,10 +10478,10 @@
         <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1586.7</v>
+        <v>1587.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5.744</v>
+        <v>5.7347</v>
       </c>
       <c r="G7" t="n">
         <v>104.54</v>
@@ -10520,7 +10520,7 @@
         <v>97</v>
       </c>
       <c r="S7" t="n">
-        <v>1607.9</v>
+        <v>1608.9</v>
       </c>
     </row>
     <row r="8">
@@ -10539,10 +10539,10 @@
         <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>1568.8</v>
+        <v>1570.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8893</v>
+        <v>1.9346</v>
       </c>
       <c r="G8" t="n">
         <v>114.76</v>
@@ -10581,7 +10581,7 @@
         <v>74</v>
       </c>
       <c r="S8" t="n">
-        <v>1637.9</v>
+        <v>1639.9</v>
       </c>
     </row>
     <row r="9">
@@ -10600,10 +10600,10 @@
         <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1616</v>
+        <v>1616.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0517</v>
+        <v>1.0682</v>
       </c>
       <c r="G9" t="n">
         <v>110.53</v>
@@ -10642,7 +10642,7 @@
         <v>80</v>
       </c>
       <c r="S9" t="n">
-        <v>1623.7</v>
+        <v>1624.9</v>
       </c>
     </row>
     <row r="10">
@@ -10661,10 +10661,10 @@
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1594.9</v>
+        <v>1595.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5518</v>
+        <v>-2.7714</v>
       </c>
       <c r="G10" t="n">
         <v>108.69</v>
@@ -10703,7 +10703,7 @@
         <v>95</v>
       </c>
       <c r="S10" t="n">
-        <v>1630.7</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="11">
@@ -10722,10 +10722,10 @@
         <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1517.6</v>
+        <v>1515.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.0067</v>
+        <v>-7.4748</v>
       </c>
       <c r="G11" t="n">
         <v>104.9</v>
@@ -10764,7 +10764,7 @@
         <v>109</v>
       </c>
       <c r="S11" t="n">
-        <v>1658.7</v>
+        <v>1659.8</v>
       </c>
     </row>
     <row r="12">
@@ -10783,10 +10783,10 @@
         <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1551.4</v>
+        <v>1551.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9935</v>
+        <v>-5.0089</v>
       </c>
       <c r="G12" t="n">
         <v>109.71</v>
@@ -10825,7 +10825,7 @@
         <v>99</v>
       </c>
       <c r="S12" t="n">
-        <v>1645.5</v>
+        <v>1646.4</v>
       </c>
     </row>
   </sheetData>
@@ -10955,10 +10955,10 @@
         <v>115</v>
       </c>
       <c r="E2" t="n">
-        <v>1623.3</v>
+        <v>1620.8</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5579</v>
+        <v>-1.4038</v>
       </c>
       <c r="G2" t="n">
         <v>121.64</v>
@@ -11016,10 +11016,10 @@
         <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>1492</v>
+        <v>1492.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7239</v>
+        <v>1.7375</v>
       </c>
       <c r="G3" t="n">
         <v>113.5</v>
@@ -11058,7 +11058,7 @@
         <v>129</v>
       </c>
       <c r="S3" t="n">
-        <v>1432.7</v>
+        <v>1433.9</v>
       </c>
     </row>
     <row r="4">
@@ -11077,10 +11077,10 @@
         <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>1373.3</v>
+        <v>1373.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7029</v>
+        <v>-1.7201</v>
       </c>
       <c r="G4" t="n">
         <v>107.9</v>
@@ -11119,7 +11119,7 @@
         <v>250</v>
       </c>
       <c r="S4" t="n">
-        <v>1424.1</v>
+        <v>1423.5</v>
       </c>
     </row>
     <row r="5">
@@ -11138,10 +11138,10 @@
         <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>1375.2</v>
+        <v>1374.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.3006</v>
+        <v>-4.2989</v>
       </c>
       <c r="G5" t="n">
         <v>106.52</v>
@@ -11180,7 +11180,7 @@
         <v>242</v>
       </c>
       <c r="S5" t="n">
-        <v>1419.4</v>
+        <v>1418.9</v>
       </c>
     </row>
     <row r="6">
@@ -11199,10 +11199,10 @@
         <v>117</v>
       </c>
       <c r="E6" t="n">
-        <v>1400</v>
+        <v>1399.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9885</v>
+        <v>-2.9584</v>
       </c>
       <c r="G6" t="n">
         <v>106.84</v>
@@ -11241,7 +11241,7 @@
         <v>264</v>
       </c>
       <c r="S6" t="n">
-        <v>1389.8</v>
+        <v>1389.7</v>
       </c>
     </row>
     <row r="7">
@@ -11260,10 +11260,10 @@
         <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>1327.6</v>
+        <v>1327.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9623</v>
+        <v>-0.9686</v>
       </c>
       <c r="G7" t="n">
         <v>104.64</v>
@@ -11302,7 +11302,7 @@
         <v>266</v>
       </c>
       <c r="S7" t="n">
-        <v>1410.6</v>
+        <v>1410.8</v>
       </c>
     </row>
     <row r="8">
@@ -11324,7 +11324,7 @@
         <v>1330.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0665</v>
+        <v>1.0554</v>
       </c>
       <c r="G8" t="n">
         <v>107.63</v>
@@ -11363,7 +11363,7 @@
         <v>241</v>
       </c>
       <c r="S8" t="n">
-        <v>1390.3</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="9">
@@ -11382,10 +11382,10 @@
         <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1285.2</v>
+        <v>1285.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3166</v>
+        <v>0.3056</v>
       </c>
       <c r="G9" t="n">
         <v>99.63</v>
@@ -11424,7 +11424,7 @@
         <v>292</v>
       </c>
       <c r="S9" t="n">
-        <v>1417.8</v>
+        <v>1417.1</v>
       </c>
     </row>
     <row r="10">
@@ -11443,10 +11443,10 @@
         <v>121</v>
       </c>
       <c r="E10" t="n">
-        <v>1247</v>
+        <v>1246.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.7199</v>
+        <v>-4.7167</v>
       </c>
       <c r="G10" t="n">
         <v>93.64</v>
@@ -11485,7 +11485,7 @@
         <v>361</v>
       </c>
       <c r="S10" t="n">
-        <v>1444.4</v>
+        <v>1443.2</v>
       </c>
     </row>
   </sheetData>
@@ -11615,10 +11615,10 @@
         <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>2172.4</v>
+        <v>2181.2</v>
       </c>
       <c r="F2" t="n">
-        <v>8.183400000000001</v>
+        <v>7.6139</v>
       </c>
       <c r="G2" t="n">
         <v>121.54</v>
@@ -11657,7 +11657,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1756.1</v>
+        <v>1758.2</v>
       </c>
     </row>
     <row r="3">
@@ -11676,10 +11676,10 @@
         <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>2051.5</v>
+        <v>2057.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5706</v>
+        <v>0.2001</v>
       </c>
       <c r="G3" t="n">
         <v>117.41</v>
@@ -11718,7 +11718,7 @@
         <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>1704.4</v>
+        <v>1707.1</v>
       </c>
     </row>
     <row r="4">
@@ -11737,10 +11737,10 @@
         <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>1990.6</v>
+        <v>1992.1</v>
       </c>
       <c r="F4" t="n">
-        <v>11.3442</v>
+        <v>11.5554</v>
       </c>
       <c r="G4" t="n">
         <v>115.07</v>
@@ -11779,7 +11779,7 @@
         <v>12</v>
       </c>
       <c r="S4" t="n">
-        <v>1658</v>
+        <v>1659.3</v>
       </c>
     </row>
     <row r="5">
@@ -11798,10 +11798,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1996.4</v>
+        <v>1999.8</v>
       </c>
       <c r="F5" t="n">
-        <v>8.884600000000001</v>
+        <v>8.6837</v>
       </c>
       <c r="G5" t="n">
         <v>125.29</v>
@@ -11840,7 +11840,7 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1710.4</v>
+        <v>1712.9</v>
       </c>
     </row>
     <row r="6">
@@ -11859,10 +11859,10 @@
         <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1976</v>
+        <v>1978.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8268</v>
+        <v>0.7736</v>
       </c>
       <c r="G6" t="n">
         <v>123.88</v>
@@ -11901,7 +11901,7 @@
         <v>9</v>
       </c>
       <c r="S6" t="n">
-        <v>1740.2</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="7">
@@ -11920,10 +11920,10 @@
         <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1837.7</v>
+        <v>1837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7673</v>
+        <v>1.4688</v>
       </c>
       <c r="G7" t="n">
         <v>118.38</v>
@@ -11962,7 +11962,7 @@
         <v>32</v>
       </c>
       <c r="S7" t="n">
-        <v>1686</v>
+        <v>1688.3</v>
       </c>
     </row>
     <row r="8">
@@ -11981,10 +11981,10 @@
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1842</v>
+        <v>1845.8</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4672</v>
+        <v>2.0997</v>
       </c>
       <c r="G8" t="n">
         <v>116.51</v>
@@ -12023,7 +12023,7 @@
         <v>39</v>
       </c>
       <c r="S8" t="n">
-        <v>1687.7</v>
+        <v>1689.8</v>
       </c>
     </row>
     <row r="9">
@@ -12042,10 +12042,10 @@
         <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>1787.4</v>
+        <v>1789.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3307</v>
+        <v>1.4042</v>
       </c>
       <c r="G9" t="n">
         <v>118.28</v>
@@ -12084,7 +12084,7 @@
         <v>34</v>
       </c>
       <c r="S9" t="n">
-        <v>1694.2</v>
+        <v>1696.1</v>
       </c>
     </row>
     <row r="10">
@@ -12103,10 +12103,10 @@
         <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1849.8</v>
+        <v>1851.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4435</v>
+        <v>4.4379</v>
       </c>
       <c r="G10" t="n">
         <v>119.28</v>
@@ -12145,7 +12145,7 @@
         <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1706.7</v>
+        <v>1708.5</v>
       </c>
     </row>
     <row r="11">
@@ -12164,10 +12164,10 @@
         <v>121</v>
       </c>
       <c r="E11" t="n">
-        <v>1752.7</v>
+        <v>1752.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7312</v>
+        <v>-2.4765</v>
       </c>
       <c r="G11" t="n">
         <v>116.39</v>
@@ -12206,7 +12206,7 @@
         <v>41</v>
       </c>
       <c r="S11" t="n">
-        <v>1695.9</v>
+        <v>1696.5</v>
       </c>
     </row>
     <row r="12">
@@ -12225,10 +12225,10 @@
         <v>121</v>
       </c>
       <c r="E12" t="n">
-        <v>1654.2</v>
+        <v>1655.8</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1014</v>
+        <v>2.1181</v>
       </c>
       <c r="G12" t="n">
         <v>111.56</v>
@@ -12267,7 +12267,7 @@
         <v>61</v>
       </c>
       <c r="S12" t="n">
-        <v>1689.2</v>
+        <v>1691.3</v>
       </c>
     </row>
     <row r="13">
@@ -12286,10 +12286,10 @@
         <v>121</v>
       </c>
       <c r="E13" t="n">
-        <v>1755.8</v>
+        <v>1756.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5224</v>
+        <v>1.6277</v>
       </c>
       <c r="G13" t="n">
         <v>107.92</v>
@@ -12328,7 +12328,7 @@
         <v>63</v>
       </c>
       <c r="S13" t="n">
-        <v>1684.4</v>
+        <v>1685.7</v>
       </c>
     </row>
     <row r="14">
@@ -12350,7 +12350,7 @@
         <v>1616.9</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1308</v>
+        <v>0.1361</v>
       </c>
       <c r="G14" t="n">
         <v>109.88</v>
@@ -12389,7 +12389,7 @@
         <v>68</v>
       </c>
       <c r="S14" t="n">
-        <v>1678.8</v>
+        <v>1679.2</v>
       </c>
     </row>
     <row r="15">
@@ -12408,10 +12408,10 @@
         <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>1550.6</v>
+        <v>1551.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1151</v>
+        <v>-3.1062</v>
       </c>
       <c r="G15" t="n">
         <v>104.86</v>
@@ -12450,7 +12450,7 @@
         <v>158</v>
       </c>
       <c r="S15" t="n">
-        <v>1695.2</v>
+        <v>1697.1</v>
       </c>
     </row>
     <row r="16">
@@ -12469,10 +12469,10 @@
         <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>1591.7</v>
+        <v>1592.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.6981</v>
+        <v>-4.7578</v>
       </c>
       <c r="G16" t="n">
         <v>110.63</v>
@@ -12511,7 +12511,7 @@
         <v>72</v>
       </c>
       <c r="S16" t="n">
-        <v>1705.7</v>
+        <v>1706.7</v>
       </c>
     </row>
     <row r="17">
@@ -12530,10 +12530,10 @@
         <v>120</v>
       </c>
       <c r="E17" t="n">
-        <v>1591.3</v>
+        <v>1593.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.7958</v>
+        <v>-9.597300000000001</v>
       </c>
       <c r="G17" t="n">
         <v>104.34</v>
@@ -12572,7 +12572,7 @@
         <v>107</v>
       </c>
       <c r="S17" t="n">
-        <v>1735.8</v>
+        <v>1738.3</v>
       </c>
     </row>
     <row r="18">
@@ -12591,10 +12591,10 @@
         <v>121</v>
       </c>
       <c r="E18" t="n">
-        <v>1598.8</v>
+        <v>1601.6</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.9559</v>
+        <v>-8.364800000000001</v>
       </c>
       <c r="G18" t="n">
         <v>102.77</v>
@@ -12633,7 +12633,7 @@
         <v>146</v>
       </c>
       <c r="S18" t="n">
-        <v>1712.3</v>
+        <v>1713.6</v>
       </c>
     </row>
     <row r="19">
@@ -12652,10 +12652,10 @@
         <v>121</v>
       </c>
       <c r="E19" t="n">
-        <v>1531.4</v>
+        <v>1532.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.5446</v>
+        <v>-7.5578</v>
       </c>
       <c r="G19" t="n">
         <v>110.14</v>
@@ -12694,7 +12694,7 @@
         <v>125</v>
       </c>
       <c r="S19" t="n">
-        <v>1669.9</v>
+        <v>1671.8</v>
       </c>
     </row>
   </sheetData>
@@ -12824,10 +12824,10 @@
         <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>1685.2</v>
+        <v>1681</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8461</v>
+        <v>2.0383</v>
       </c>
       <c r="G2" t="n">
         <v>115.35</v>
@@ -12866,7 +12866,7 @@
         <v>93</v>
       </c>
       <c r="S2" t="n">
-        <v>1429.5</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="3">
@@ -12885,10 +12885,10 @@
         <v>118</v>
       </c>
       <c r="E3" t="n">
-        <v>1580.3</v>
+        <v>1578.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5895</v>
+        <v>1.6342</v>
       </c>
       <c r="G3" t="n">
         <v>109.21</v>
@@ -12927,7 +12927,7 @@
         <v>145</v>
       </c>
       <c r="S3" t="n">
-        <v>1483.9</v>
+        <v>1482.2</v>
       </c>
     </row>
     <row r="4">
@@ -12946,10 +12946,10 @@
         <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>1568.2</v>
+        <v>1567.8</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0091</v>
+        <v>4.0005</v>
       </c>
       <c r="G4" t="n">
         <v>112.7</v>
@@ -12988,7 +12988,7 @@
         <v>92</v>
       </c>
       <c r="S4" t="n">
-        <v>1479.4</v>
+        <v>1478.9</v>
       </c>
     </row>
     <row r="5">
@@ -13007,10 +13007,10 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>1444.5</v>
+        <v>1443.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1442</v>
+        <v>1.1405</v>
       </c>
       <c r="G5" t="n">
         <v>106.98</v>
@@ -13049,7 +13049,7 @@
         <v>179</v>
       </c>
       <c r="S5" t="n">
-        <v>1459.6</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="6">
@@ -13068,10 +13068,10 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1421</v>
+        <v>1420.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0515</v>
+        <v>-0.0564</v>
       </c>
       <c r="G6" t="n">
         <v>103.41</v>
@@ -13110,7 +13110,7 @@
         <v>211</v>
       </c>
       <c r="S6" t="n">
-        <v>1440.1</v>
+        <v>1439.6</v>
       </c>
     </row>
     <row r="7">
@@ -13129,10 +13129,10 @@
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1526.7</v>
+        <v>1525.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9316</v>
+        <v>2.8777</v>
       </c>
       <c r="G7" t="n">
         <v>112.99</v>
@@ -13171,7 +13171,7 @@
         <v>124</v>
       </c>
       <c r="S7" t="n">
-        <v>1464</v>
+        <v>1462.6</v>
       </c>
     </row>
     <row r="8">
@@ -13190,10 +13190,10 @@
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1547.9</v>
+        <v>1546.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8805</v>
+        <v>-2.9255</v>
       </c>
       <c r="G8" t="n">
         <v>102.64</v>
@@ -13232,7 +13232,7 @@
         <v>180</v>
       </c>
       <c r="S8" t="n">
-        <v>1527.3</v>
+        <v>1527.1</v>
       </c>
     </row>
     <row r="9">
@@ -13251,10 +13251,10 @@
         <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>1447.5</v>
+        <v>1447.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3213</v>
+        <v>3.303</v>
       </c>
       <c r="G9" t="n">
         <v>102.98</v>
@@ -13293,7 +13293,7 @@
         <v>219</v>
       </c>
       <c r="S9" t="n">
-        <v>1464.4</v>
+        <v>1463.7</v>
       </c>
     </row>
     <row r="10">
@@ -13312,10 +13312,10 @@
         <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1389.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1499</v>
+        <v>0.1605</v>
       </c>
       <c r="G10" t="n">
         <v>108.08</v>
@@ -13354,7 +13354,7 @@
         <v>208</v>
       </c>
       <c r="S10" t="n">
-        <v>1517.7</v>
+        <v>1516.7</v>
       </c>
     </row>
     <row r="11">
@@ -13373,10 +13373,10 @@
         <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>1351.3</v>
+        <v>1350.9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4097</v>
+        <v>0.3858</v>
       </c>
       <c r="G11" t="n">
         <v>101.86</v>
@@ -13415,7 +13415,7 @@
         <v>268</v>
       </c>
       <c r="S11" t="n">
-        <v>1452</v>
+        <v>1451.2</v>
       </c>
     </row>
     <row r="12">
@@ -13434,10 +13434,10 @@
         <v>120</v>
       </c>
       <c r="E12" t="n">
-        <v>1465</v>
+        <v>1464.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9038</v>
+        <v>0.8972</v>
       </c>
       <c r="G12" t="n">
         <v>111.77</v>
@@ -13476,7 +13476,7 @@
         <v>210</v>
       </c>
       <c r="S12" t="n">
-        <v>1490</v>
+        <v>1489.3</v>
       </c>
     </row>
     <row r="13">
@@ -13495,10 +13495,10 @@
         <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>1328.7</v>
+        <v>1328.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1764</v>
+        <v>1.1591</v>
       </c>
       <c r="G13" t="n">
         <v>107.08</v>
@@ -13537,7 +13537,7 @@
         <v>267</v>
       </c>
       <c r="S13" t="n">
-        <v>1454.5</v>
+        <v>1453.6</v>
       </c>
     </row>
     <row r="14">
@@ -13556,10 +13556,10 @@
         <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>1359.6</v>
+        <v>1359.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.5538</v>
+        <v>-3.5632</v>
       </c>
       <c r="G14" t="n">
         <v>105.8</v>
@@ -13598,7 +13598,7 @@
         <v>288</v>
       </c>
       <c r="S14" t="n">
-        <v>1484.3</v>
+        <v>1483.9</v>
       </c>
     </row>
   </sheetData>
@@ -13728,10 +13728,10 @@
         <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>1732.5</v>
+        <v>1729</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2122</v>
+        <v>3.4996</v>
       </c>
       <c r="G2" t="n">
         <v>117.41</v>
@@ -13770,7 +13770,7 @@
         <v>94</v>
       </c>
       <c r="S2" t="n">
-        <v>1483.4</v>
+        <v>1482.9</v>
       </c>
     </row>
     <row r="3">
@@ -13789,10 +13789,10 @@
         <v>122</v>
       </c>
       <c r="E3" t="n">
-        <v>1545.2</v>
+        <v>1544.3</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7891</v>
+        <v>4.758</v>
       </c>
       <c r="G3" t="n">
         <v>113.42</v>
@@ -13831,7 +13831,7 @@
         <v>96</v>
       </c>
       <c r="S3" t="n">
-        <v>1490.8</v>
+        <v>1491.4</v>
       </c>
     </row>
     <row r="4">
@@ -13850,10 +13850,10 @@
         <v>122</v>
       </c>
       <c r="E4" t="n">
-        <v>1489.1</v>
+        <v>1487.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.6149</v>
+        <v>-3.5819</v>
       </c>
       <c r="G4" t="n">
         <v>108.56</v>
@@ -13892,7 +13892,7 @@
         <v>133</v>
       </c>
       <c r="S4" t="n">
-        <v>1487.7</v>
+        <v>1486.4</v>
       </c>
     </row>
     <row r="5">
@@ -13911,10 +13911,10 @@
         <v>122</v>
       </c>
       <c r="E5" t="n">
-        <v>1485.7</v>
+        <v>1485.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0304</v>
+        <v>-4.0291</v>
       </c>
       <c r="G5" t="n">
         <v>107.77</v>
@@ -13953,7 +13953,7 @@
         <v>161</v>
       </c>
       <c r="S5" t="n">
-        <v>1526.5</v>
+        <v>1528.1</v>
       </c>
     </row>
     <row r="6">
@@ -13972,10 +13972,10 @@
         <v>122</v>
       </c>
       <c r="E6" t="n">
-        <v>1508.2</v>
+        <v>1507.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4067</v>
+        <v>-0.4075</v>
       </c>
       <c r="G6" t="n">
         <v>110.23</v>
@@ -14014,7 +14014,7 @@
         <v>160</v>
       </c>
       <c r="S6" t="n">
-        <v>1470.2</v>
+        <v>1469.7</v>
       </c>
     </row>
     <row r="7">
@@ -14033,10 +14033,10 @@
         <v>122</v>
       </c>
       <c r="E7" t="n">
-        <v>1503.4</v>
+        <v>1502.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0097</v>
+        <v>-2.0079</v>
       </c>
       <c r="G7" t="n">
         <v>101.77</v>
@@ -14075,7 +14075,7 @@
         <v>248</v>
       </c>
       <c r="S7" t="n">
-        <v>1471.5</v>
+        <v>1470.5</v>
       </c>
     </row>
     <row r="8">
@@ -14094,10 +14094,10 @@
         <v>122</v>
       </c>
       <c r="E8" t="n">
-        <v>1459.7</v>
+        <v>1459.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0609</v>
+        <v>-0.0599</v>
       </c>
       <c r="G8" t="n">
         <v>106.71</v>
@@ -14136,7 +14136,7 @@
         <v>214</v>
       </c>
       <c r="S8" t="n">
-        <v>1469.9</v>
+        <v>1469.2</v>
       </c>
     </row>
     <row r="9">
@@ -14155,10 +14155,10 @@
         <v>122</v>
       </c>
       <c r="E9" t="n">
-        <v>1399.2</v>
+        <v>1398.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4398</v>
+        <v>1.4406</v>
       </c>
       <c r="G9" t="n">
         <v>108.1</v>
@@ -14197,7 +14197,7 @@
         <v>218</v>
       </c>
       <c r="S9" t="n">
-        <v>1474.7</v>
+        <v>1474.3</v>
       </c>
     </row>
     <row r="10">
@@ -14216,10 +14216,10 @@
         <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>1381.1</v>
+        <v>1380.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3949</v>
+        <v>1.3979</v>
       </c>
       <c r="G10" t="n">
         <v>106.61</v>
@@ -14258,7 +14258,7 @@
         <v>200</v>
       </c>
       <c r="S10" t="n">
-        <v>1494.9</v>
+        <v>1494.4</v>
       </c>
     </row>
     <row r="11">
@@ -14277,10 +14277,10 @@
         <v>122</v>
       </c>
       <c r="E11" t="n">
-        <v>1456.1</v>
+        <v>1456</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.1471</v>
+        <v>-8.1896</v>
       </c>
       <c r="G11" t="n">
         <v>108.64</v>
@@ -14319,7 +14319,7 @@
         <v>186</v>
       </c>
       <c r="S11" t="n">
-        <v>1487.6</v>
+        <v>1487.2</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -603,31 +603,31 @@
         <v>1433</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E3" t="n">
-        <v>1727.9</v>
+        <v>1739.9</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9027</v>
+        <v>2.9764</v>
       </c>
       <c r="G3" t="n">
-        <v>118.56</v>
+        <v>118.46</v>
       </c>
       <c r="H3" t="n">
-        <v>103.74</v>
+        <v>103.76</v>
       </c>
       <c r="I3" t="n">
-        <v>14.82</v>
+        <v>14.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.304</v>
+        <v>0.2979</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1505</v>
+        <v>0.1497</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
@@ -648,7 +648,7 @@
         <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>1551.3</v>
+        <v>1554.6</v>
       </c>
     </row>
     <row r="4">
@@ -725,31 +725,31 @@
         <v>1173</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E5" t="n">
-        <v>1675.3</v>
+        <v>1663.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.825</v>
+        <v>-2.5466</v>
       </c>
       <c r="G5" t="n">
-        <v>110.38</v>
+        <v>109.99</v>
       </c>
       <c r="H5" t="n">
-        <v>101.85</v>
+        <v>102.29</v>
       </c>
       <c r="I5" t="n">
-        <v>8.529999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.251</v>
+        <v>0.2531</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1711</v>
+        <v>0.1686</v>
       </c>
       <c r="L5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
         <v>75</v>
@@ -770,7 +770,7 @@
         <v>71</v>
       </c>
       <c r="S5" t="n">
-        <v>1553.3</v>
+        <v>1562.3</v>
       </c>
     </row>
     <row r="6">
@@ -1507,31 +1507,31 @@
         <v>1275</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>1771.7</v>
+        <v>1775.2</v>
       </c>
       <c r="F2" t="n">
-        <v>9.957599999999999</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>120.02</v>
+        <v>120.89</v>
       </c>
       <c r="H2" t="n">
-        <v>103.88</v>
+        <v>105.23</v>
       </c>
       <c r="I2" t="n">
-        <v>16.14</v>
+        <v>15.66</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2071</v>
+        <v>0.2107</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1427</v>
+        <v>0.1402</v>
       </c>
       <c r="L2" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>87</v>
@@ -1552,7 +1552,7 @@
         <v>52</v>
       </c>
       <c r="S2" t="n">
-        <v>1412.7</v>
+        <v>1414.6</v>
       </c>
     </row>
     <row r="3">
@@ -1568,31 +1568,31 @@
         <v>1103</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E3" t="n">
-        <v>1693.7</v>
+        <v>1694.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6325</v>
+        <v>1.739</v>
       </c>
       <c r="G3" t="n">
-        <v>122.16</v>
+        <v>123.02</v>
       </c>
       <c r="H3" t="n">
-        <v>105</v>
+        <v>104.03</v>
       </c>
       <c r="I3" t="n">
-        <v>17.16</v>
+        <v>18.98</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2907</v>
+        <v>0.2846</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1511</v>
+        <v>0.152</v>
       </c>
       <c r="L3" t="n">
-        <v>15.8</v>
+        <v>20.2</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
@@ -1613,7 +1613,7 @@
         <v>57</v>
       </c>
       <c r="S3" t="n">
-        <v>1484</v>
+        <v>1476.4</v>
       </c>
     </row>
     <row r="4">
@@ -1629,31 +1629,31 @@
         <v>1245</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
-        <v>1605.5</v>
+        <v>1604.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4681</v>
+        <v>0.3083</v>
       </c>
       <c r="G4" t="n">
-        <v>112.27</v>
+        <v>112.38</v>
       </c>
       <c r="H4" t="n">
-        <v>109</v>
+        <v>109.12</v>
       </c>
       <c r="I4" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3162</v>
+        <v>0.3198</v>
       </c>
       <c r="K4" t="n">
-        <v>0.181</v>
+        <v>0.1818</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
         <v>160</v>
@@ -1674,7 +1674,7 @@
         <v>150</v>
       </c>
       <c r="S4" t="n">
-        <v>1472.1</v>
+        <v>1468.3</v>
       </c>
     </row>
     <row r="5">
@@ -1690,31 +1690,31 @@
         <v>1405</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E5" t="n">
-        <v>1452.4</v>
+        <v>1454.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6824</v>
+        <v>-0.6694</v>
       </c>
       <c r="G5" t="n">
-        <v>113.63</v>
+        <v>115.34</v>
       </c>
       <c r="H5" t="n">
-        <v>111.29</v>
+        <v>111.66</v>
       </c>
       <c r="I5" t="n">
-        <v>2.34</v>
+        <v>3.68</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2946</v>
+        <v>0.2982</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1412</v>
+        <v>0.1389</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>11.8</v>
       </c>
       <c r="M5" t="n">
         <v>145</v>
@@ -1735,7 +1735,7 @@
         <v>153</v>
       </c>
       <c r="S5" t="n">
-        <v>1505</v>
+        <v>1496.5</v>
       </c>
     </row>
     <row r="6">
@@ -1744,59 +1744,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Bowling Green</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1325</v>
+        <v>1132</v>
       </c>
       <c r="D6" t="n">
+        <v>123</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="G6" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>149</v>
+      </c>
+      <c r="N6" t="n">
+        <v>186</v>
+      </c>
+      <c r="O6" t="n">
         <v>120</v>
       </c>
-      <c r="E6" t="n">
-        <v>1466.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.6549</v>
-      </c>
-      <c r="G6" t="n">
-        <v>106.96</v>
-      </c>
-      <c r="H6" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.2915</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1466</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>227</v>
-      </c>
-      <c r="N6" t="n">
-        <v>190</v>
-      </c>
-      <c r="O6" t="n">
-        <v>241</v>
-      </c>
       <c r="P6" t="n">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="Q6" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="R6" t="n">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="S6" t="n">
-        <v>1500.7</v>
+        <v>1462.9</v>
       </c>
     </row>
     <row r="7">
@@ -1805,59 +1805,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bowling Green</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1132</v>
+        <v>1325</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
-        <v>1418.6</v>
+        <v>1462.5</v>
       </c>
       <c r="F7" t="n">
-        <v>1.305</v>
+        <v>2.3882</v>
       </c>
       <c r="G7" t="n">
-        <v>108.75</v>
+        <v>107.94</v>
       </c>
       <c r="H7" t="n">
-        <v>101.71</v>
+        <v>112.06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.04</v>
+        <v>-4.11</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2687</v>
+        <v>0.2911</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1604</v>
+        <v>0.1442</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="N7" t="n">
+        <v>190</v>
+      </c>
+      <c r="O7" t="n">
+        <v>241</v>
+      </c>
+      <c r="P7" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q7" t="n">
         <v>186</v>
       </c>
-      <c r="O7" t="n">
-        <v>120</v>
-      </c>
-      <c r="P7" t="n">
-        <v>149</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>198</v>
-      </c>
       <c r="R7" t="n">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="S7" t="n">
-        <v>1467.4</v>
+        <v>1513.3</v>
       </c>
     </row>
     <row r="8">
@@ -1873,31 +1873,31 @@
         <v>1138</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1391</v>
+        <v>1384.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2206</v>
+        <v>-0.3277</v>
       </c>
       <c r="G8" t="n">
-        <v>114.44</v>
+        <v>115.04</v>
       </c>
       <c r="H8" t="n">
-        <v>111.83</v>
+        <v>114.08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.61</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2726</v>
+        <v>0.2767</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1568</v>
+        <v>0.158</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="M8" t="n">
         <v>194</v>
@@ -1918,7 +1918,7 @@
         <v>190</v>
       </c>
       <c r="S8" t="n">
-        <v>1458.9</v>
+        <v>1459.6</v>
       </c>
     </row>
     <row r="9">
@@ -2106,31 +2106,31 @@
         <v>1125</v>
       </c>
       <c r="D2" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>1752.3</v>
+        <v>1736.4</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5868</v>
+        <v>5.3442</v>
       </c>
       <c r="G2" t="n">
-        <v>118.84</v>
+        <v>118.57</v>
       </c>
       <c r="H2" t="n">
-        <v>104.39</v>
+        <v>105.72</v>
       </c>
       <c r="I2" t="n">
-        <v>14.44</v>
+        <v>12.85</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2389</v>
+        <v>0.2328</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1756</v>
+        <v>0.1733</v>
       </c>
       <c r="L2" t="n">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
         <v>55</v>
@@ -2151,7 +2151,7 @@
         <v>55</v>
       </c>
       <c r="S2" t="n">
-        <v>1486</v>
+        <v>1485.7</v>
       </c>
     </row>
     <row r="3">
@@ -2167,31 +2167,31 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E3" t="n">
-        <v>1623.6</v>
+        <v>1627.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3833</v>
+        <v>1.2831</v>
       </c>
       <c r="G3" t="n">
-        <v>111.03</v>
+        <v>110.42</v>
       </c>
       <c r="H3" t="n">
-        <v>106.13</v>
+        <v>105.54</v>
       </c>
       <c r="I3" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="J3" t="n">
         <v>0.2732</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1331</v>
+        <v>0.1327</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>123</v>
@@ -2212,7 +2212,7 @@
         <v>112</v>
       </c>
       <c r="S3" t="n">
-        <v>1526.1</v>
+        <v>1522.2</v>
       </c>
     </row>
     <row r="4">
@@ -2228,31 +2228,31 @@
         <v>1229</v>
       </c>
       <c r="D4" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
-        <v>1589.7</v>
+        <v>1580.6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2669</v>
+        <v>2.2563</v>
       </c>
       <c r="G4" t="n">
-        <v>110.94</v>
+        <v>109.57</v>
       </c>
       <c r="H4" t="n">
-        <v>101.68</v>
+        <v>102.17</v>
       </c>
       <c r="I4" t="n">
-        <v>9.26</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2598</v>
+        <v>0.2579</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1625</v>
+        <v>0.1639</v>
       </c>
       <c r="L4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M4" t="n">
         <v>97</v>
@@ -2273,7 +2273,7 @@
         <v>90</v>
       </c>
       <c r="S4" t="n">
-        <v>1505.7</v>
+        <v>1504.8</v>
       </c>
     </row>
     <row r="5">
@@ -2289,31 +2289,31 @@
         <v>1293</v>
       </c>
       <c r="D5" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E5" t="n">
-        <v>1581.7</v>
+        <v>1572.9</v>
       </c>
       <c r="F5" t="n">
-        <v>4.703</v>
+        <v>4.2807</v>
       </c>
       <c r="G5" t="n">
-        <v>116.24</v>
+        <v>115.54</v>
       </c>
       <c r="H5" t="n">
-        <v>111.31</v>
+        <v>111.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.93</v>
+        <v>4.24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.312</v>
+        <v>0.3089</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1601</v>
+        <v>0.1611</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.6</v>
+        <v>-8.6</v>
       </c>
       <c r="M5" t="n">
         <v>117</v>
@@ -2334,7 +2334,7 @@
         <v>101</v>
       </c>
       <c r="S5" t="n">
-        <v>1504.9</v>
+        <v>1504.1</v>
       </c>
     </row>
     <row r="6">
@@ -2350,31 +2350,31 @@
         <v>1227</v>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E6" t="n">
-        <v>1520.2</v>
+        <v>1529.1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8071</v>
+        <v>1.9462</v>
       </c>
       <c r="G6" t="n">
-        <v>107.6</v>
+        <v>108.2</v>
       </c>
       <c r="H6" t="n">
-        <v>103.45</v>
+        <v>103.26</v>
       </c>
       <c r="I6" t="n">
-        <v>4.15</v>
+        <v>4.93</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3478</v>
+        <v>0.3454</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1686</v>
+        <v>0.1649</v>
       </c>
       <c r="L6" t="n">
-        <v>10.4</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
         <v>110</v>
@@ -2395,7 +2395,7 @@
         <v>116</v>
       </c>
       <c r="S6" t="n">
-        <v>1502.8</v>
+        <v>1506.7</v>
       </c>
     </row>
     <row r="7">
@@ -2411,31 +2411,31 @@
         <v>1320</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
-        <v>1547.5</v>
+        <v>1556.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3733</v>
+        <v>-4.1888</v>
       </c>
       <c r="G7" t="n">
-        <v>106.65</v>
+        <v>107.26</v>
       </c>
       <c r="H7" t="n">
-        <v>96.59999999999999</v>
+        <v>96.19</v>
       </c>
       <c r="I7" t="n">
-        <v>10.05</v>
+        <v>11.06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2059</v>
+        <v>0.2089</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1354</v>
+        <v>0.1373</v>
       </c>
       <c r="L7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>80</v>
@@ -2456,7 +2456,7 @@
         <v>81</v>
       </c>
       <c r="S7" t="n">
-        <v>1507.2</v>
+        <v>1512.2</v>
       </c>
     </row>
     <row r="8">
@@ -2472,31 +2472,31 @@
         <v>1434</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1460.9</v>
+        <v>1456.8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7665</v>
+        <v>0.8941</v>
       </c>
       <c r="G8" t="n">
-        <v>105.92</v>
+        <v>105.55</v>
       </c>
       <c r="H8" t="n">
-        <v>106.15</v>
+        <v>106.08</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.23</v>
+        <v>-0.53</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3118</v>
+        <v>0.3091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1465</v>
+        <v>0.1496</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
         <v>152</v>
@@ -2517,7 +2517,7 @@
         <v>155</v>
       </c>
       <c r="S8" t="n">
-        <v>1518.4</v>
+        <v>1523.8</v>
       </c>
     </row>
     <row r="9">
@@ -2594,31 +2594,31 @@
         <v>1179</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" t="n">
-        <v>1499.5</v>
+        <v>1515.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.1954</v>
+        <v>-6.9278</v>
       </c>
       <c r="G10" t="n">
-        <v>107.72</v>
+        <v>108.97</v>
       </c>
       <c r="H10" t="n">
         <v>111.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.64</v>
+        <v>-2.39</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2728</v>
+        <v>0.2741</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1449</v>
+        <v>0.1451</v>
       </c>
       <c r="L10" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="M10" t="n">
         <v>213</v>
@@ -2639,7 +2639,7 @@
         <v>206</v>
       </c>
       <c r="S10" t="n">
-        <v>1520.7</v>
+        <v>1530.8</v>
       </c>
     </row>
     <row r="11">
@@ -2942,59 +2942,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>San Diego St</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1307</v>
+        <v>1361</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E3" t="n">
-        <v>1822.6</v>
+        <v>1788.2</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8299</v>
+        <v>5.5794</v>
       </c>
       <c r="G3" t="n">
-        <v>114.16</v>
+        <v>110.7</v>
       </c>
       <c r="H3" t="n">
-        <v>101.47</v>
+        <v>101.58</v>
       </c>
       <c r="I3" t="n">
-        <v>12.7</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2721</v>
+        <v>0.2605</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1448</v>
+        <v>0.1642</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>-0.6</v>
       </c>
       <c r="M3" t="n">
+        <v>42</v>
+      </c>
+      <c r="N3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O3" t="n">
+        <v>52</v>
+      </c>
+      <c r="P3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="n">
         <v>46</v>
       </c>
-      <c r="N3" t="n">
-        <v>47</v>
-      </c>
-      <c r="O3" t="n">
-        <v>50</v>
-      </c>
-      <c r="P3" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>44</v>
       </c>
-      <c r="R3" t="n">
-        <v>42</v>
-      </c>
       <c r="S3" t="n">
-        <v>1587.8</v>
+        <v>1652.6</v>
       </c>
     </row>
     <row r="4">
@@ -3003,59 +3003,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Diego St</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1361</v>
+        <v>1307</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>1781.6</v>
+        <v>1822.6</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1342</v>
+        <v>3.8299</v>
       </c>
       <c r="G4" t="n">
-        <v>110.23</v>
+        <v>114.16</v>
       </c>
       <c r="H4" t="n">
-        <v>101.11</v>
+        <v>101.47</v>
       </c>
       <c r="I4" t="n">
-        <v>9.119999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2614</v>
+        <v>0.2721</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1636</v>
+        <v>0.1448</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.2</v>
+        <v>5.8</v>
       </c>
       <c r="M4" t="n">
+        <v>46</v>
+      </c>
+      <c r="N4" t="n">
+        <v>47</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>44</v>
+      </c>
+      <c r="R4" t="n">
         <v>42</v>
       </c>
-      <c r="N4" t="n">
-        <v>48</v>
-      </c>
-      <c r="O4" t="n">
-        <v>52</v>
-      </c>
-      <c r="P4" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>46</v>
-      </c>
-      <c r="R4" t="n">
-        <v>44</v>
-      </c>
       <c r="S4" t="n">
-        <v>1653.2</v>
+        <v>1587.8</v>
       </c>
     </row>
     <row r="5">
@@ -3125,59 +3125,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1161</v>
+        <v>1129</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>1673.2</v>
+        <v>1725.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.7426</v>
+        <v>-2.372</v>
       </c>
       <c r="G6" t="n">
-        <v>119.56</v>
+        <v>113.86</v>
       </c>
       <c r="H6" t="n">
-        <v>112.77</v>
+        <v>107.08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
       <c r="J6" t="n">
-        <v>0.256</v>
+        <v>0.2821</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1771</v>
+        <v>0.1603</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="M6" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="N6" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="O6" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="P6" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q6" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="R6" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="S6" t="n">
-        <v>1557.5</v>
+        <v>1621.6</v>
       </c>
     </row>
     <row r="7">
@@ -3186,59 +3186,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1129</v>
+        <v>1305</v>
       </c>
       <c r="D7" t="n">
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>1725.6</v>
+        <v>1735.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.372</v>
+        <v>7.2596</v>
       </c>
       <c r="G7" t="n">
-        <v>113.86</v>
+        <v>112.85</v>
       </c>
       <c r="H7" t="n">
-        <v>107.08</v>
+        <v>107.41</v>
       </c>
       <c r="I7" t="n">
-        <v>6.78</v>
+        <v>5.44</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2821</v>
+        <v>0.305</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1603</v>
+        <v>0.1405</v>
       </c>
       <c r="L7" t="n">
-        <v>6.2</v>
+        <v>-3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O7" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P7" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="S7" t="n">
-        <v>1621.6</v>
+        <v>1612.8</v>
       </c>
     </row>
     <row r="8">
@@ -3247,59 +3247,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Colorado St</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1305</v>
+        <v>1161</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>1735.9</v>
+        <v>1673.2</v>
       </c>
       <c r="F8" t="n">
-        <v>7.2596</v>
+        <v>-5.7426</v>
       </c>
       <c r="G8" t="n">
-        <v>112.85</v>
+        <v>119.56</v>
       </c>
       <c r="H8" t="n">
-        <v>107.41</v>
+        <v>112.77</v>
       </c>
       <c r="I8" t="n">
-        <v>5.44</v>
+        <v>6.79</v>
       </c>
       <c r="J8" t="n">
-        <v>0.305</v>
+        <v>0.256</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1405</v>
+        <v>0.1771</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.6</v>
+        <v>7.6</v>
       </c>
       <c r="M8" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="N8" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="O8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P8" t="n">
         <v>84</v>
       </c>
-      <c r="P8" t="n">
-        <v>70</v>
-      </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="R8" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="S8" t="n">
-        <v>1612.8</v>
+        <v>1557.5</v>
       </c>
     </row>
     <row r="9">
@@ -3315,31 +3315,31 @@
         <v>1424</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E9" t="n">
-        <v>1651.1</v>
+        <v>1644.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4503</v>
+        <v>1.6162</v>
       </c>
       <c r="G9" t="n">
-        <v>112.07</v>
+        <v>112.14</v>
       </c>
       <c r="H9" t="n">
-        <v>110.89</v>
+        <v>111.68</v>
       </c>
       <c r="I9" t="n">
-        <v>1.18</v>
+        <v>0.46</v>
       </c>
       <c r="J9" t="n">
         <v>0.294</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1616</v>
+        <v>0.1598</v>
       </c>
       <c r="L9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
         <v>120</v>
@@ -3360,7 +3360,7 @@
         <v>126</v>
       </c>
       <c r="S9" t="n">
-        <v>1619.2</v>
+        <v>1623.2</v>
       </c>
     </row>
     <row r="10">
@@ -5539,31 +5539,31 @@
         <v>1422</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1366.3</v>
+        <v>1371.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.841</v>
+        <v>-2.6983</v>
       </c>
       <c r="G8" t="n">
-        <v>109.54</v>
+        <v>110.38</v>
       </c>
       <c r="H8" t="n">
-        <v>118.14</v>
+        <v>117.51</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.267</v>
+        <v>0.2724</v>
       </c>
       <c r="K8" t="n">
-        <v>0.144</v>
+        <v>0.1441</v>
       </c>
       <c r="L8" t="n">
-        <v>-4</v>
+        <v>-3.2</v>
       </c>
       <c r="M8" t="n">
         <v>304</v>
@@ -5584,7 +5584,7 @@
         <v>298</v>
       </c>
       <c r="S8" t="n">
-        <v>1427.7</v>
+        <v>1418.4</v>
       </c>
     </row>
     <row r="9">
@@ -5600,31 +5600,31 @@
         <v>1151</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E9" t="n">
-        <v>1392.1</v>
+        <v>1388.3</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0162</v>
+        <v>-3.8474</v>
       </c>
       <c r="G9" t="n">
-        <v>109.83</v>
+        <v>110.7</v>
       </c>
       <c r="H9" t="n">
-        <v>115.43</v>
+        <v>116.42</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.6</v>
+        <v>-5.73</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2055</v>
+        <v>0.2079</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1411</v>
+        <v>0.1402</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
         <v>298</v>
@@ -5645,7 +5645,7 @@
         <v>286</v>
       </c>
       <c r="S9" t="n">
-        <v>1429</v>
+        <v>1422.3</v>
       </c>
     </row>
     <row r="10">
@@ -5661,31 +5661,31 @@
         <v>1154</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E10" t="n">
-        <v>1231.8</v>
+        <v>1235.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1472</v>
+        <v>-0.0387</v>
       </c>
       <c r="G10" t="n">
-        <v>100.86</v>
+        <v>102.25</v>
       </c>
       <c r="H10" t="n">
-        <v>118.13</v>
+        <v>118.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-17.28</v>
+        <v>-16.53</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2962</v>
+        <v>0.2933</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1573</v>
+        <v>0.1554</v>
       </c>
       <c r="L10" t="n">
-        <v>-11.6</v>
+        <v>-7.8</v>
       </c>
       <c r="M10" t="n">
         <v>351</v>
@@ -5706,7 +5706,7 @@
         <v>350</v>
       </c>
       <c r="S10" t="n">
-        <v>1417.3</v>
+        <v>1415.5</v>
       </c>
     </row>
     <row r="11">
@@ -5722,31 +5722,31 @@
         <v>1440</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E11" t="n">
-        <v>1236.9</v>
+        <v>1235.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5993</v>
+        <v>-3.5074</v>
       </c>
       <c r="G11" t="n">
-        <v>101.54</v>
+        <v>101.27</v>
       </c>
       <c r="H11" t="n">
-        <v>123.37</v>
+        <v>123.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-21.83</v>
+        <v>-21.93</v>
       </c>
       <c r="J11" t="n">
-        <v>0.296</v>
+        <v>0.2984</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1405</v>
+        <v>0.1433</v>
       </c>
       <c r="L11" t="n">
-        <v>-13.8</v>
+        <v>-13</v>
       </c>
       <c r="M11" t="n">
         <v>360</v>
@@ -5767,7 +5767,7 @@
         <v>358</v>
       </c>
       <c r="S11" t="n">
-        <v>1431.8</v>
+        <v>1429.4</v>
       </c>
     </row>
   </sheetData>
@@ -6859,31 +6859,31 @@
         <v>1370</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1553.5</v>
+        <v>1555.8</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7763</v>
+        <v>2.5588</v>
       </c>
       <c r="G8" t="n">
-        <v>101.85</v>
+        <v>101.35</v>
       </c>
       <c r="H8" t="n">
-        <v>98.97</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2564</v>
+        <v>0.2553</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1662</v>
+        <v>0.1673</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
         <v>115</v>
@@ -6904,7 +6904,7 @@
         <v>118</v>
       </c>
       <c r="S8" t="n">
-        <v>1530.5</v>
+        <v>1523.7</v>
       </c>
     </row>
     <row r="9">
@@ -6920,31 +6920,31 @@
         <v>1450</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E9" t="n">
-        <v>1458.2</v>
+        <v>1453.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9961</v>
+        <v>-1.9312</v>
       </c>
       <c r="G9" t="n">
-        <v>109.85</v>
+        <v>109.46</v>
       </c>
       <c r="H9" t="n">
-        <v>112.21</v>
+        <v>111.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.36</v>
+        <v>-2.52</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2659</v>
+        <v>0.259</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1829</v>
+        <v>0.1813</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.8</v>
+        <v>-3</v>
       </c>
       <c r="M9" t="n">
         <v>134</v>
@@ -6965,7 +6965,7 @@
         <v>135</v>
       </c>
       <c r="S9" t="n">
-        <v>1567.6</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="10">
@@ -6981,31 +6981,31 @@
         <v>1339</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" t="n">
-        <v>1412.3</v>
+        <v>1416.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4459</v>
+        <v>1.4725</v>
       </c>
       <c r="G10" t="n">
-        <v>102.44</v>
+        <v>102.47</v>
       </c>
       <c r="H10" t="n">
-        <v>111.35</v>
+        <v>110.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.91</v>
+        <v>-8.42</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2631</v>
+        <v>0.2615</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1902</v>
+        <v>0.1865</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.8</v>
+        <v>-5</v>
       </c>
       <c r="M10" t="n">
         <v>204</v>
@@ -7026,7 +7026,7 @@
         <v>227</v>
       </c>
       <c r="S10" t="n">
-        <v>1532.4</v>
+        <v>1531.8</v>
       </c>
     </row>
     <row r="11">
@@ -7103,31 +7103,31 @@
         <v>1360</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="n">
-        <v>1362</v>
+        <v>1359.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7876</v>
+        <v>1.6714</v>
       </c>
       <c r="G12" t="n">
-        <v>104.99</v>
+        <v>104.54</v>
       </c>
       <c r="H12" t="n">
-        <v>113.39</v>
+        <v>112.86</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.32</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3057</v>
+        <v>0.3035</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1671</v>
+        <v>0.1702</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.800000000000001</v>
+        <v>-6.6</v>
       </c>
       <c r="M12" t="n">
         <v>235</v>
@@ -7148,7 +7148,7 @@
         <v>244</v>
       </c>
       <c r="S12" t="n">
-        <v>1527.7</v>
+        <v>1529.1</v>
       </c>
     </row>
     <row r="13">
@@ -9442,59 +9442,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>1153</v>
       </c>
       <c r="D8" t="n">
         <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>1838.2</v>
+        <v>1733</v>
       </c>
       <c r="F8" t="n">
-        <v>7.6713</v>
+        <v>0.4193</v>
       </c>
       <c r="G8" t="n">
-        <v>115.83</v>
+        <v>105.76</v>
       </c>
       <c r="H8" t="n">
-        <v>110.45</v>
+        <v>97.33</v>
       </c>
       <c r="I8" t="n">
-        <v>5.38</v>
+        <v>8.43</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3093</v>
+        <v>0.2897</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1541</v>
+        <v>0.1583</v>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>10.6</v>
       </c>
       <c r="M8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S8" t="n">
-        <v>1687.7</v>
+        <v>1713.8</v>
       </c>
     </row>
     <row r="9">
@@ -9503,59 +9503,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1153</v>
+        <v>1452</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E9" t="n">
-        <v>1733</v>
+        <v>1710.3</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4193</v>
+        <v>0.4911</v>
       </c>
       <c r="G9" t="n">
-        <v>105.76</v>
+        <v>107.75</v>
       </c>
       <c r="H9" t="n">
-        <v>97.33</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>8.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2897</v>
+        <v>0.2866</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1583</v>
+        <v>0.163</v>
       </c>
       <c r="L9" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q9" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R9" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S9" t="n">
-        <v>1713.8</v>
+        <v>1659.8</v>
       </c>
     </row>
     <row r="10">
@@ -9564,59 +9564,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1452</v>
+        <v>1416</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E10" t="n">
-        <v>1692.6</v>
+        <v>1820.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3731</v>
+        <v>7.025</v>
       </c>
       <c r="G10" t="n">
-        <v>107.19</v>
+        <v>114.77</v>
       </c>
       <c r="H10" t="n">
-        <v>99.78</v>
+        <v>110.49</v>
       </c>
       <c r="I10" t="n">
-        <v>7.41</v>
+        <v>4.28</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2944</v>
+        <v>0.3115</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1659</v>
+        <v>0.1546</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4</v>
+        <v>-1.6</v>
       </c>
       <c r="M10" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O10" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P10" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
-        <v>1650.7</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="11">
@@ -10163,59 +10163,59 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1163</v>
+        <v>1385</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>2092.8</v>
+        <v>1961.4</v>
       </c>
       <c r="F2" t="n">
-        <v>9.4907</v>
+        <v>5.5897</v>
       </c>
       <c r="G2" t="n">
-        <v>117.38</v>
+        <v>113.79</v>
       </c>
       <c r="H2" t="n">
-        <v>97.34999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="I2" t="n">
-        <v>20.03</v>
+        <v>15.09</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2903</v>
+        <v>0.3238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1532</v>
+        <v>0.1418</v>
       </c>
       <c r="L2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="M2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17</v>
+      </c>
+      <c r="O2" t="n">
         <v>10</v>
       </c>
-      <c r="N2" t="n">
-        <v>4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>16</v>
-      </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="S2" t="n">
-        <v>1667.4</v>
+        <v>1680.5</v>
       </c>
     </row>
     <row r="3">
@@ -10224,59 +10224,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1385</v>
+        <v>1163</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>1955.3</v>
+        <v>2092.8</v>
       </c>
       <c r="F3" t="n">
-        <v>5.539</v>
+        <v>9.4907</v>
       </c>
       <c r="G3" t="n">
-        <v>113.73</v>
+        <v>117.38</v>
       </c>
       <c r="H3" t="n">
-        <v>98.58</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>15.15</v>
+        <v>20.03</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3268</v>
+        <v>0.2903</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1411</v>
+        <v>0.1532</v>
       </c>
       <c r="L3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>1679.7</v>
+        <v>1667.4</v>
       </c>
     </row>
     <row r="4">
@@ -10353,31 +10353,31 @@
         <v>1371</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E5" t="n">
-        <v>1668.1</v>
+        <v>1662</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3546</v>
+        <v>4.9773</v>
       </c>
       <c r="G5" t="n">
-        <v>106.11</v>
+        <v>105.77</v>
       </c>
       <c r="H5" t="n">
-        <v>97.43000000000001</v>
+        <v>98.03</v>
       </c>
       <c r="I5" t="n">
-        <v>8.67</v>
+        <v>7.74</v>
       </c>
       <c r="J5" t="n">
-        <v>0.321</v>
+        <v>0.3233</v>
       </c>
       <c r="K5" t="n">
-        <v>0.159</v>
+        <v>0.1586</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>-2</v>
       </c>
       <c r="M5" t="n">
         <v>53</v>
@@ -10398,7 +10398,7 @@
         <v>56</v>
       </c>
       <c r="S5" t="n">
-        <v>1623.2</v>
+        <v>1637.8</v>
       </c>
     </row>
     <row r="6">
@@ -10952,31 +10952,31 @@
         <v>1219</v>
       </c>
       <c r="D2" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>1620.8</v>
+        <v>1618</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4038</v>
+        <v>-1.2011</v>
       </c>
       <c r="G2" t="n">
-        <v>121.64</v>
+        <v>121.43</v>
       </c>
       <c r="H2" t="n">
-        <v>100.61</v>
+        <v>99.78</v>
       </c>
       <c r="I2" t="n">
-        <v>21.04</v>
+        <v>21.65</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3121</v>
+        <v>0.3136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1266</v>
+        <v>0.1281</v>
       </c>
       <c r="L2" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="M2" t="n">
         <v>91</v>
@@ -10997,7 +10997,7 @@
         <v>76</v>
       </c>
       <c r="S2" t="n">
-        <v>1381.5</v>
+        <v>1375.9</v>
       </c>
     </row>
     <row r="3">
@@ -11013,31 +11013,31 @@
         <v>1457</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E3" t="n">
-        <v>1492.7</v>
+        <v>1494.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7375</v>
+        <v>1.7613</v>
       </c>
       <c r="G3" t="n">
-        <v>113.5</v>
+        <v>113.46</v>
       </c>
       <c r="H3" t="n">
-        <v>107.2</v>
+        <v>107.15</v>
       </c>
       <c r="I3" t="n">
-        <v>6.3</v>
+        <v>6.32</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3166</v>
+        <v>0.3148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1408</v>
+        <v>0.1389</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
         <v>141</v>
@@ -11058,7 +11058,7 @@
         <v>129</v>
       </c>
       <c r="S3" t="n">
-        <v>1433.9</v>
+        <v>1430.2</v>
       </c>
     </row>
     <row r="4">
@@ -11074,31 +11074,31 @@
         <v>1347</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
-        <v>1373.1</v>
+        <v>1373.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7201</v>
+        <v>-1.6094</v>
       </c>
       <c r="G4" t="n">
-        <v>107.9</v>
+        <v>107.89</v>
       </c>
       <c r="H4" t="n">
-        <v>108.68</v>
+        <v>108.72</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.78</v>
+        <v>-0.83</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2779</v>
+        <v>0.276</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1661</v>
+        <v>0.1671</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
         <v>255</v>
@@ -11119,7 +11119,7 @@
         <v>250</v>
       </c>
       <c r="S4" t="n">
-        <v>1423.5</v>
+        <v>1419.6</v>
       </c>
     </row>
     <row r="5">
@@ -11135,31 +11135,31 @@
         <v>1421</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E5" t="n">
-        <v>1374.9</v>
+        <v>1383.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.2989</v>
+        <v>-4.0778</v>
       </c>
       <c r="G5" t="n">
-        <v>106.52</v>
+        <v>106.7</v>
       </c>
       <c r="H5" t="n">
-        <v>110.31</v>
+        <v>109.86</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.8</v>
+        <v>-3.16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2887</v>
+        <v>0.2837</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1596</v>
+        <v>0.1605</v>
       </c>
       <c r="L5" t="n">
-        <v>-7.4</v>
+        <v>-6.6</v>
       </c>
       <c r="M5" t="n">
         <v>253</v>
@@ -11180,7 +11180,7 @@
         <v>242</v>
       </c>
       <c r="S5" t="n">
-        <v>1418.9</v>
+        <v>1419.1</v>
       </c>
     </row>
     <row r="6">
@@ -11196,31 +11196,31 @@
         <v>1255</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E6" t="n">
-        <v>1399.7</v>
+        <v>1393.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9584</v>
+        <v>-2.8101</v>
       </c>
       <c r="G6" t="n">
-        <v>106.84</v>
+        <v>106.82</v>
       </c>
       <c r="H6" t="n">
-        <v>107.17</v>
+        <v>107.64</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.33</v>
+        <v>-0.82</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3194</v>
+        <v>0.3237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1894</v>
+        <v>0.1864</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="M6" t="n">
         <v>272</v>
@@ -11241,7 +11241,7 @@
         <v>264</v>
       </c>
       <c r="S6" t="n">
-        <v>1389.7</v>
+        <v>1389.4</v>
       </c>
     </row>
     <row r="7">
@@ -11257,31 +11257,31 @@
         <v>1342</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
-        <v>1327.7</v>
+        <v>1333.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9686</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>104.64</v>
+        <v>105.31</v>
       </c>
       <c r="H7" t="n">
-        <v>109.5</v>
+        <v>109.56</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.86</v>
+        <v>-4.25</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2983</v>
+        <v>0.3092</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1853</v>
+        <v>0.1832</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
         <v>278</v>
@@ -11302,7 +11302,7 @@
         <v>266</v>
       </c>
       <c r="S7" t="n">
-        <v>1410.8</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="8">
@@ -11318,31 +11318,31 @@
         <v>1149</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1330.5</v>
+        <v>1319.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0554</v>
+        <v>0.9741</v>
       </c>
       <c r="G8" t="n">
-        <v>107.63</v>
+        <v>107.28</v>
       </c>
       <c r="H8" t="n">
-        <v>106.83</v>
+        <v>107.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2642</v>
+        <v>0.2613</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1832</v>
+        <v>0.1772</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
         <v>244</v>
@@ -11363,7 +11363,7 @@
         <v>241</v>
       </c>
       <c r="S8" t="n">
-        <v>1390</v>
+        <v>1394.8</v>
       </c>
     </row>
     <row r="9">
@@ -11440,31 +11440,31 @@
         <v>1205</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E10" t="n">
-        <v>1246.6</v>
+        <v>1245.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.7167</v>
+        <v>-4.5195</v>
       </c>
       <c r="G10" t="n">
-        <v>93.64</v>
+        <v>93.22</v>
       </c>
       <c r="H10" t="n">
-        <v>121.61</v>
+        <v>121.76</v>
       </c>
       <c r="I10" t="n">
-        <v>-27.96</v>
+        <v>-28.54</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2472</v>
+        <v>0.2487</v>
       </c>
       <c r="K10" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>361</v>
@@ -11485,7 +11485,7 @@
         <v>361</v>
       </c>
       <c r="S10" t="n">
-        <v>1443.2</v>
+        <v>1453.1</v>
       </c>
     </row>
   </sheetData>
@@ -13492,31 +13492,31 @@
         <v>1299</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E13" t="n">
-        <v>1328.3</v>
+        <v>1326</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1591</v>
+        <v>1.0955</v>
       </c>
       <c r="G13" t="n">
-        <v>107.08</v>
+        <v>106.8</v>
       </c>
       <c r="H13" t="n">
-        <v>113.61</v>
+        <v>113.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.53</v>
+        <v>-7.05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2719</v>
+        <v>0.2733</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1755</v>
+        <v>0.1743</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.4</v>
+        <v>-8</v>
       </c>
       <c r="M13" t="n">
         <v>274</v>
@@ -13537,7 +13537,7 @@
         <v>267</v>
       </c>
       <c r="S13" t="n">
-        <v>1453.6</v>
+        <v>1450.1</v>
       </c>
     </row>
     <row r="14">
@@ -13553,31 +13553,31 @@
         <v>1318</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E14" t="n">
-        <v>1359.9</v>
+        <v>1362.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.5632</v>
+        <v>-3.5491</v>
       </c>
       <c r="G14" t="n">
-        <v>105.8</v>
+        <v>106.52</v>
       </c>
       <c r="H14" t="n">
-        <v>115.61</v>
+        <v>114.9</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.800000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2758</v>
+        <v>0.28</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1575</v>
+        <v>0.1592</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.4</v>
+        <v>-4.4</v>
       </c>
       <c r="M14" t="n">
         <v>288</v>
@@ -13598,7 +13598,7 @@
         <v>288</v>
       </c>
       <c r="S14" t="n">
-        <v>1483.9</v>
+        <v>1477.6</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -542,31 +542,31 @@
         <v>1387</v>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>1824.5</v>
+        <v>1807.8</v>
       </c>
       <c r="F2" t="n">
-        <v>10.3996</v>
+        <v>9.839</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>120.36</v>
       </c>
       <c r="H2" t="n">
-        <v>96.95</v>
+        <v>98.52</v>
       </c>
       <c r="I2" t="n">
-        <v>25.05</v>
+        <v>21.84</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2326</v>
+        <v>0.2436</v>
       </c>
       <c r="K2" t="n">
-        <v>0.167</v>
+        <v>0.1686</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M2" t="n">
         <v>27</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="S2" t="n">
-        <v>1501.2</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="3">
@@ -664,31 +664,31 @@
         <v>1386</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1609.8</v>
+        <v>1612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6471</v>
+        <v>0.9935</v>
       </c>
       <c r="G4" t="n">
-        <v>104.92</v>
+        <v>105.94</v>
       </c>
       <c r="H4" t="n">
-        <v>102.36</v>
+        <v>102.75</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2837</v>
+        <v>0.2842</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1632</v>
+        <v>0.1621</v>
       </c>
       <c r="L4" t="n">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="M4" t="n">
         <v>132</v>
@@ -709,7 +709,7 @@
         <v>132</v>
       </c>
       <c r="S4" t="n">
-        <v>1511.8</v>
+        <v>1506.8</v>
       </c>
     </row>
     <row r="5">
@@ -786,31 +786,31 @@
         <v>1206</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1707.5</v>
+        <v>1724.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6563</v>
+        <v>-1.0204</v>
       </c>
       <c r="G6" t="n">
-        <v>111.81</v>
+        <v>113.12</v>
       </c>
       <c r="H6" t="n">
-        <v>105.03</v>
+        <v>104.31</v>
       </c>
       <c r="I6" t="n">
-        <v>6.78</v>
+        <v>8.81</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2621</v>
+        <v>0.2641</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1545</v>
+        <v>0.1547</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
         <v>107</v>
@@ -831,7 +831,7 @@
         <v>98</v>
       </c>
       <c r="S6" t="n">
-        <v>1505.6</v>
+        <v>1517.3</v>
       </c>
     </row>
     <row r="7">
@@ -847,31 +847,31 @@
         <v>1172</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1522.3</v>
+        <v>1530.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8164</v>
+        <v>-2.7149</v>
       </c>
       <c r="G7" t="n">
-        <v>108.88</v>
+        <v>108.86</v>
       </c>
       <c r="H7" t="n">
-        <v>105.54</v>
+        <v>105.24</v>
       </c>
       <c r="I7" t="n">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2845</v>
+        <v>0.2859</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1555</v>
+        <v>0.1553</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
         <v>106</v>
@@ -892,7 +892,7 @@
         <v>105</v>
       </c>
       <c r="S7" t="n">
-        <v>1541.6</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="8">
@@ -908,31 +908,31 @@
         <v>1182</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1477.1</v>
+        <v>1481.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.429</v>
+        <v>-2.2564</v>
       </c>
       <c r="G8" t="n">
-        <v>108.08</v>
+        <v>108.87</v>
       </c>
       <c r="H8" t="n">
-        <v>107.04</v>
+        <v>107.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2829</v>
+        <v>0.2905</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1768</v>
+        <v>0.1742</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="M8" t="n">
         <v>125</v>
@@ -953,7 +953,7 @@
         <v>131</v>
       </c>
       <c r="S8" t="n">
-        <v>1541.5</v>
+        <v>1537.9</v>
       </c>
     </row>
     <row r="9">
@@ -962,59 +962,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G Washington</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1541.7</v>
+        <v>1464.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.2526</v>
+        <v>1.1637</v>
       </c>
       <c r="G9" t="n">
-        <v>116.28</v>
+        <v>104.6</v>
       </c>
       <c r="H9" t="n">
-        <v>105.4</v>
+        <v>102.16</v>
       </c>
       <c r="I9" t="n">
-        <v>10.88</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3229</v>
+        <v>0.3135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1749</v>
+        <v>0.1649</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>-0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="N9" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="O9" t="n">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="Q9" t="n">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="R9" t="n">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="S9" t="n">
-        <v>1538.6</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="10">
@@ -1023,59 +1023,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>G Washington</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1457.2</v>
+        <v>1524.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0971</v>
+        <v>-4.0633</v>
       </c>
       <c r="G10" t="n">
-        <v>105.16</v>
+        <v>115.25</v>
       </c>
       <c r="H10" t="n">
-        <v>103.59</v>
+        <v>105.33</v>
       </c>
       <c r="I10" t="n">
-        <v>1.57</v>
+        <v>9.92</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3183</v>
+        <v>0.3298</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1588</v>
+        <v>0.1749</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="N10" t="n">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="O10" t="n">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="P10" t="n">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="R10" t="n">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="S10" t="n">
-        <v>1494.4</v>
+        <v>1531.5</v>
       </c>
     </row>
     <row r="11">
@@ -1091,31 +1091,31 @@
         <v>1348</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1573.1</v>
+        <v>1565.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7973</v>
+        <v>0.7602</v>
       </c>
       <c r="G11" t="n">
-        <v>105.82</v>
+        <v>104.48</v>
       </c>
       <c r="H11" t="n">
-        <v>102.05</v>
+        <v>101.92</v>
       </c>
       <c r="I11" t="n">
-        <v>3.77</v>
+        <v>2.56</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3055</v>
+        <v>0.3041</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1789</v>
+        <v>0.181</v>
       </c>
       <c r="L11" t="n">
-        <v>-4</v>
+        <v>-7.4</v>
       </c>
       <c r="M11" t="n">
         <v>137</v>
@@ -1136,7 +1136,7 @@
         <v>141</v>
       </c>
       <c r="S11" t="n">
-        <v>1519</v>
+        <v>1516.7</v>
       </c>
     </row>
     <row r="12">
@@ -1152,31 +1152,31 @@
         <v>1350</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1471.3</v>
+        <v>1466.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3741</v>
+        <v>-0.4968</v>
       </c>
       <c r="G12" t="n">
-        <v>110.96</v>
+        <v>111.48</v>
       </c>
       <c r="H12" t="n">
-        <v>108.02</v>
+        <v>108.68</v>
       </c>
       <c r="I12" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2478</v>
+        <v>0.2419</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1345</v>
+        <v>0.1397</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.2</v>
+        <v>-1.4</v>
       </c>
       <c r="M12" t="n">
         <v>142</v>
@@ -1197,7 +1197,7 @@
         <v>147</v>
       </c>
       <c r="S12" t="n">
-        <v>1513.8</v>
+        <v>1510.8</v>
       </c>
     </row>
     <row r="13">
@@ -1213,31 +1213,31 @@
         <v>1247</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>1400.6</v>
+        <v>1398.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2046</v>
+        <v>-2.0204</v>
       </c>
       <c r="G13" t="n">
-        <v>99.5</v>
+        <v>99.75</v>
       </c>
       <c r="H13" t="n">
-        <v>110.35</v>
+        <v>111.11</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.85</v>
+        <v>-11.36</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3276</v>
+        <v>0.3303</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1795</v>
+        <v>0.1752</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.8</v>
+        <v>-6</v>
       </c>
       <c r="M13" t="n">
         <v>229</v>
@@ -1258,7 +1258,7 @@
         <v>239</v>
       </c>
       <c r="S13" t="n">
-        <v>1562.7</v>
+        <v>1566.1</v>
       </c>
     </row>
     <row r="14">
@@ -1274,31 +1274,31 @@
         <v>1382</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>1531.3</v>
+        <v>1533.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.8599</v>
+        <v>-8.699299999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>111.57</v>
+        <v>111.12</v>
       </c>
       <c r="H14" t="n">
-        <v>111.05</v>
+        <v>110.83</v>
       </c>
       <c r="I14" t="n">
-        <v>0.52</v>
+        <v>0.29</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3194</v>
+        <v>0.3183</v>
       </c>
       <c r="K14" t="n">
         <v>0.1633</v>
       </c>
       <c r="L14" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="M14" t="n">
         <v>150</v>
@@ -1319,7 +1319,7 @@
         <v>149</v>
       </c>
       <c r="S14" t="n">
-        <v>1531.6</v>
+        <v>1531.2</v>
       </c>
     </row>
     <row r="15">
@@ -1335,31 +1335,31 @@
         <v>1260</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E15" t="n">
-        <v>1391.4</v>
+        <v>1397.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.2997</v>
+        <v>-4.1654</v>
       </c>
       <c r="G15" t="n">
-        <v>100.15</v>
+        <v>100.55</v>
       </c>
       <c r="H15" t="n">
-        <v>115.52</v>
+        <v>114.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-15.37</v>
+        <v>-14.11</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2854</v>
+        <v>0.2832</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1902</v>
+        <v>0.1903</v>
       </c>
       <c r="L15" t="n">
-        <v>-11</v>
+        <v>-4.4</v>
       </c>
       <c r="M15" t="n">
         <v>306</v>
@@ -1380,7 +1380,7 @@
         <v>303</v>
       </c>
       <c r="S15" t="n">
-        <v>1562.7</v>
+        <v>1557.5</v>
       </c>
     </row>
   </sheetData>
@@ -2167,31 +2167,31 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1627.7</v>
+        <v>1617.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2831</v>
+        <v>1.2181</v>
       </c>
       <c r="G3" t="n">
         <v>110.42</v>
       </c>
       <c r="H3" t="n">
-        <v>105.54</v>
+        <v>106.06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.88</v>
+        <v>4.36</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2732</v>
+        <v>0.2631</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1327</v>
+        <v>0.1366</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="M3" t="n">
         <v>123</v>
@@ -2212,7 +2212,7 @@
         <v>112</v>
       </c>
       <c r="S3" t="n">
-        <v>1522.2</v>
+        <v>1524.5</v>
       </c>
     </row>
     <row r="4">
@@ -2350,31 +2350,31 @@
         <v>1227</v>
       </c>
       <c r="D6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1529.1</v>
+        <v>1535.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9462</v>
+        <v>2.1038</v>
       </c>
       <c r="G6" t="n">
-        <v>108.2</v>
+        <v>108.47</v>
       </c>
       <c r="H6" t="n">
-        <v>103.26</v>
+        <v>102.47</v>
       </c>
       <c r="I6" t="n">
-        <v>4.93</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3454</v>
+        <v>0.3429</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1649</v>
+        <v>0.1641</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="M6" t="n">
         <v>110</v>
@@ -2395,7 +2395,7 @@
         <v>116</v>
       </c>
       <c r="S6" t="n">
-        <v>1506.7</v>
+        <v>1506.5</v>
       </c>
     </row>
     <row r="7">
@@ -2411,31 +2411,31 @@
         <v>1320</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1556.5</v>
+        <v>1567</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.1888</v>
+        <v>-3.9617</v>
       </c>
       <c r="G7" t="n">
-        <v>107.26</v>
+        <v>107.53</v>
       </c>
       <c r="H7" t="n">
-        <v>96.19</v>
+        <v>96.87</v>
       </c>
       <c r="I7" t="n">
-        <v>11.06</v>
+        <v>10.66</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2089</v>
+        <v>0.214</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1373</v>
+        <v>0.1374</v>
       </c>
       <c r="L7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>80</v>
@@ -2456,7 +2456,7 @@
         <v>81</v>
       </c>
       <c r="S7" t="n">
-        <v>1512.2</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="8">
@@ -2594,31 +2594,31 @@
         <v>1179</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1515.3</v>
+        <v>1508.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.9278</v>
+        <v>-6.5709</v>
       </c>
       <c r="G10" t="n">
-        <v>108.97</v>
+        <v>107.64</v>
       </c>
       <c r="H10" t="n">
-        <v>111.36</v>
+        <v>111.59</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.39</v>
+        <v>-3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2741</v>
+        <v>0.2753</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1451</v>
+        <v>0.1457</v>
       </c>
       <c r="L10" t="n">
-        <v>-1</v>
+        <v>-4.2</v>
       </c>
       <c r="M10" t="n">
         <v>213</v>
@@ -2639,7 +2639,7 @@
         <v>206</v>
       </c>
       <c r="S10" t="n">
-        <v>1530.8</v>
+        <v>1528.6</v>
       </c>
     </row>
     <row r="11">
@@ -2888,31 +2888,31 @@
         <v>1429</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>1858.4</v>
+        <v>1869.8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4232</v>
+        <v>0.2419</v>
       </c>
       <c r="G2" t="n">
-        <v>119.66</v>
+        <v>120.49</v>
       </c>
       <c r="H2" t="n">
-        <v>104.27</v>
+        <v>105.01</v>
       </c>
       <c r="I2" t="n">
-        <v>15.38</v>
+        <v>15.48</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3059</v>
+        <v>0.3065</v>
       </c>
       <c r="K2" t="n">
         <v>0.1487</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.6</v>
+        <v>-7.6</v>
       </c>
       <c r="M2" t="n">
         <v>26</v>
@@ -2933,7 +2933,7 @@
         <v>26</v>
       </c>
       <c r="S2" t="n">
-        <v>1589.9</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="3">
@@ -3010,31 +3010,31 @@
         <v>1307</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1822.6</v>
+        <v>1811.2</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8299</v>
+        <v>3.4739</v>
       </c>
       <c r="G4" t="n">
-        <v>114.16</v>
+        <v>115.21</v>
       </c>
       <c r="H4" t="n">
-        <v>101.47</v>
+        <v>103.06</v>
       </c>
       <c r="I4" t="n">
-        <v>12.7</v>
+        <v>12.14</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2721</v>
+        <v>0.2768</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1448</v>
+        <v>0.1435</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8</v>
+        <v>-2.4</v>
       </c>
       <c r="M4" t="n">
         <v>46</v>
@@ -3055,7 +3055,7 @@
         <v>42</v>
       </c>
       <c r="S4" t="n">
-        <v>1587.8</v>
+        <v>1598.9</v>
       </c>
     </row>
     <row r="5">
@@ -3071,31 +3071,31 @@
         <v>1213</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1718.4</v>
+        <v>1720.3</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6944</v>
+        <v>6.4863</v>
       </c>
       <c r="G5" t="n">
-        <v>109.82</v>
+        <v>110.07</v>
       </c>
       <c r="H5" t="n">
-        <v>99.62</v>
+        <v>99.11</v>
       </c>
       <c r="I5" t="n">
-        <v>10.21</v>
+        <v>10.96</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2757</v>
+        <v>0.275</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1736</v>
+        <v>0.1725</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
       <c r="M5" t="n">
         <v>62</v>
@@ -3116,7 +3116,7 @@
         <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>1575.6</v>
+        <v>1572.8</v>
       </c>
     </row>
     <row r="6">
@@ -3132,31 +3132,31 @@
         <v>1129</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1725.6</v>
+        <v>1737.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.372</v>
+        <v>-2.1403</v>
       </c>
       <c r="G6" t="n">
-        <v>113.86</v>
+        <v>114.39</v>
       </c>
       <c r="H6" t="n">
-        <v>107.08</v>
+        <v>107.18</v>
       </c>
       <c r="I6" t="n">
-        <v>6.78</v>
+        <v>7.21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2821</v>
+        <v>0.2847</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1603</v>
+        <v>0.1604</v>
       </c>
       <c r="L6" t="n">
-        <v>6.2</v>
+        <v>12.2</v>
       </c>
       <c r="M6" t="n">
         <v>60</v>
@@ -3177,7 +3177,7 @@
         <v>59</v>
       </c>
       <c r="S6" t="n">
-        <v>1621.6</v>
+        <v>1622.1</v>
       </c>
     </row>
     <row r="7">
@@ -3193,31 +3193,31 @@
         <v>1305</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1735.9</v>
+        <v>1736.5</v>
       </c>
       <c r="F7" t="n">
-        <v>7.2596</v>
+        <v>6.7862</v>
       </c>
       <c r="G7" t="n">
-        <v>112.85</v>
+        <v>112.99</v>
       </c>
       <c r="H7" t="n">
-        <v>107.41</v>
+        <v>106.43</v>
       </c>
       <c r="I7" t="n">
-        <v>5.44</v>
+        <v>6.56</v>
       </c>
       <c r="J7" t="n">
-        <v>0.305</v>
+        <v>0.3038</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1405</v>
+        <v>0.1419</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
         <v>70</v>
@@ -3238,7 +3238,7 @@
         <v>67</v>
       </c>
       <c r="S7" t="n">
-        <v>1612.8</v>
+        <v>1598.1</v>
       </c>
     </row>
     <row r="8">
@@ -3254,31 +3254,31 @@
         <v>1161</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1673.2</v>
+        <v>1661.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.7426</v>
+        <v>-5.2805</v>
       </c>
       <c r="G8" t="n">
-        <v>119.56</v>
+        <v>119.17</v>
       </c>
       <c r="H8" t="n">
-        <v>112.77</v>
+        <v>113.56</v>
       </c>
       <c r="I8" t="n">
-        <v>6.79</v>
+        <v>5.61</v>
       </c>
       <c r="J8" t="n">
-        <v>0.256</v>
+        <v>0.2593</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1771</v>
+        <v>0.1744</v>
       </c>
       <c r="L8" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="M8" t="n">
         <v>86</v>
@@ -3299,7 +3299,7 @@
         <v>88</v>
       </c>
       <c r="S8" t="n">
-        <v>1557.5</v>
+        <v>1561.4</v>
       </c>
     </row>
     <row r="9">
@@ -3376,28 +3376,28 @@
         <v>1461</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1523.8</v>
+        <v>1526.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3879</v>
+        <v>-0.2647</v>
       </c>
       <c r="G10" t="n">
-        <v>112.57</v>
+        <v>113.84</v>
       </c>
       <c r="H10" t="n">
-        <v>108.22</v>
+        <v>109.09</v>
       </c>
       <c r="I10" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3147</v>
+        <v>0.3231</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1573</v>
+        <v>0.159</v>
       </c>
       <c r="L10" t="n">
         <v>3.8</v>
@@ -3421,7 +3421,7 @@
         <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>1568.9</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="11">
@@ -3437,31 +3437,31 @@
         <v>1201</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1422.5</v>
+        <v>1420.6</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4973</v>
+        <v>2.37</v>
       </c>
       <c r="G11" t="n">
-        <v>105.7</v>
+        <v>104.39</v>
       </c>
       <c r="H11" t="n">
-        <v>105.68</v>
+        <v>106.19</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02</v>
+        <v>-1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2618</v>
+        <v>0.2609</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1679</v>
+        <v>0.17</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="M11" t="n">
         <v>126</v>
@@ -3482,7 +3482,7 @@
         <v>139</v>
       </c>
       <c r="S11" t="n">
-        <v>1579.9</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="12">
@@ -3498,31 +3498,31 @@
         <v>1363</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1364.4</v>
+        <v>1361.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3087</v>
+        <v>-3.1738</v>
       </c>
       <c r="G12" t="n">
-        <v>105.89</v>
+        <v>107.12</v>
       </c>
       <c r="H12" t="n">
-        <v>119.41</v>
+        <v>120.72</v>
       </c>
       <c r="I12" t="n">
-        <v>-13.52</v>
+        <v>-13.59</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3273</v>
+        <v>0.3383</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1431</v>
+        <v>0.1413</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8</v>
+        <v>-9</v>
       </c>
       <c r="M12" t="n">
         <v>234</v>
@@ -3543,7 +3543,7 @@
         <v>256</v>
       </c>
       <c r="S12" t="n">
-        <v>1585.4</v>
+        <v>1584.5</v>
       </c>
     </row>
     <row r="13">
@@ -3559,31 +3559,31 @@
         <v>1102</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>1257.1</v>
+        <v>1256.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4029</v>
+        <v>-2.3635</v>
       </c>
       <c r="G13" t="n">
-        <v>93.45999999999999</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>120.68</v>
+        <v>120.31</v>
       </c>
       <c r="I13" t="n">
-        <v>-27.22</v>
+        <v>-26.88</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2242</v>
+        <v>0.2222</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2077</v>
+        <v>0.2048</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.6</v>
+        <v>-15.2</v>
       </c>
       <c r="M13" t="n">
         <v>346</v>
@@ -3604,7 +3604,7 @@
         <v>349</v>
       </c>
       <c r="S13" t="n">
-        <v>1561.6</v>
+        <v>1567.3</v>
       </c>
     </row>
   </sheetData>
@@ -4086,31 +4086,31 @@
         <v>1196</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>2002.2</v>
+        <v>2014.8</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5717</v>
+        <v>2.8716</v>
       </c>
       <c r="G2" t="n">
-        <v>121.4</v>
+        <v>120.95</v>
       </c>
       <c r="H2" t="n">
-        <v>98.63</v>
+        <v>99.02</v>
       </c>
       <c r="I2" t="n">
-        <v>22.77</v>
+        <v>21.92</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3333</v>
+        <v>0.3329</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1547</v>
+        <v>0.1552</v>
       </c>
       <c r="L2" t="n">
-        <v>22.8</v>
+        <v>21.4</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -4131,7 +4131,7 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1700.4</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="3">
@@ -4147,31 +4147,31 @@
         <v>1104</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1967.1</v>
+        <v>1975.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6145</v>
+        <v>-1.4869</v>
       </c>
       <c r="G3" t="n">
-        <v>121.39</v>
+        <v>122.11</v>
       </c>
       <c r="H3" t="n">
-        <v>110.58</v>
+        <v>110.78</v>
       </c>
       <c r="I3" t="n">
-        <v>10.81</v>
+        <v>11.33</v>
       </c>
       <c r="J3" t="n">
-        <v>0.279</v>
+        <v>0.2853</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1296</v>
+        <v>0.1289</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -4192,7 +4192,7 @@
         <v>16</v>
       </c>
       <c r="S3" t="n">
-        <v>1769.4</v>
+        <v>1772.1</v>
       </c>
     </row>
     <row r="4">
@@ -4208,31 +4208,31 @@
         <v>1116</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1940.1</v>
+        <v>1950</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7735</v>
+        <v>5.5428</v>
       </c>
       <c r="G4" t="n">
-        <v>123.18</v>
+        <v>122.85</v>
       </c>
       <c r="H4" t="n">
-        <v>108.72</v>
+        <v>108.88</v>
       </c>
       <c r="I4" t="n">
-        <v>14.46</v>
+        <v>13.96</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2975</v>
+        <v>0.3009</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1194</v>
+        <v>0.1205</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
         <v>20</v>
@@ -4253,7 +4253,7 @@
         <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>1727.6</v>
+        <v>1728.7</v>
       </c>
     </row>
     <row r="5">
@@ -4262,59 +4262,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1397</v>
+        <v>1435</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1915.6</v>
+        <v>1935.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8805</v>
+        <v>2.1989</v>
       </c>
       <c r="G5" t="n">
-        <v>117.37</v>
+        <v>121.8</v>
       </c>
       <c r="H5" t="n">
-        <v>101.08</v>
+        <v>105.67</v>
       </c>
       <c r="I5" t="n">
-        <v>16.3</v>
+        <v>16.12</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3535</v>
+        <v>0.2802</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1667</v>
+        <v>0.1278</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>-0.6</v>
       </c>
       <c r="M5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" t="n">
         <v>18</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>16</v>
       </c>
-      <c r="O5" t="n">
-        <v>20</v>
-      </c>
-      <c r="P5" t="n">
-        <v>20</v>
-      </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S5" t="n">
-        <v>1693.7</v>
+        <v>1694.9</v>
       </c>
     </row>
     <row r="6">
@@ -4323,59 +4323,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1281</v>
+        <v>1397</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1767.4</v>
+        <v>1898.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.184</v>
+        <v>-1.6704</v>
       </c>
       <c r="G6" t="n">
-        <v>115.23</v>
+        <v>117.06</v>
       </c>
       <c r="H6" t="n">
-        <v>109.22</v>
+        <v>101.96</v>
       </c>
       <c r="I6" t="n">
-        <v>6.01</v>
+        <v>15.09</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3029</v>
+        <v>0.3583</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1713</v>
+        <v>0.1671</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="S6" t="n">
-        <v>1638.6</v>
+        <v>1706.1</v>
       </c>
     </row>
     <row r="7">
@@ -4384,59 +4384,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1435</v>
+        <v>1401</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1918.7</v>
+        <v>1843.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6895</v>
+        <v>4.536</v>
       </c>
       <c r="G7" t="n">
-        <v>121.87</v>
+        <v>117.79</v>
       </c>
       <c r="H7" t="n">
-        <v>105.42</v>
+        <v>106.34</v>
       </c>
       <c r="I7" t="n">
-        <v>16.45</v>
+        <v>11.45</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2854</v>
+        <v>0.3067</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1247</v>
+        <v>0.1399</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6</v>
+        <v>-0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="R7" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
-        <v>1684.4</v>
+        <v>1651.1</v>
       </c>
     </row>
     <row r="8">
@@ -4445,59 +4445,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1401</v>
+        <v>1208</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1835.2</v>
+        <v>1816.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7779</v>
+        <v>0.2065</v>
       </c>
       <c r="G8" t="n">
-        <v>118.62</v>
+        <v>121.14</v>
       </c>
       <c r="H8" t="n">
-        <v>106.73</v>
+        <v>107.06</v>
       </c>
       <c r="I8" t="n">
-        <v>11.89</v>
+        <v>14.09</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3028</v>
+        <v>0.3227</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1406</v>
+        <v>0.1388</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6</v>
+        <v>7.6</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P8" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="n">
         <v>39</v>
       </c>
-      <c r="Q8" t="n">
-        <v>41</v>
-      </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="S8" t="n">
-        <v>1655.1</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="9">
@@ -4506,59 +4506,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1246</v>
+        <v>1281</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1894.4</v>
+        <v>1757.5</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7232</v>
+        <v>-1.923</v>
       </c>
       <c r="G9" t="n">
-        <v>116.85</v>
+        <v>115.19</v>
       </c>
       <c r="H9" t="n">
-        <v>105.78</v>
+        <v>109.25</v>
       </c>
       <c r="I9" t="n">
-        <v>11.07</v>
+        <v>5.95</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3101</v>
+        <v>0.3014</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1466</v>
+        <v>0.1701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O9" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="S9" t="n">
-        <v>1717.2</v>
+        <v>1651.9</v>
       </c>
     </row>
     <row r="10">
@@ -4567,59 +4567,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1208</v>
+        <v>1246</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1808.8</v>
+        <v>1881.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1677</v>
+        <v>5.4881</v>
       </c>
       <c r="G10" t="n">
-        <v>120.8</v>
+        <v>116.58</v>
       </c>
       <c r="H10" t="n">
-        <v>106.43</v>
+        <v>106.11</v>
       </c>
       <c r="I10" t="n">
-        <v>14.38</v>
+        <v>10.47</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3238</v>
+        <v>0.3117</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1381</v>
+        <v>0.1455</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
+        <v>25</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q10" t="n">
         <v>33</v>
       </c>
-      <c r="N10" t="n">
-        <v>31</v>
-      </c>
-      <c r="O10" t="n">
-        <v>30</v>
-      </c>
-      <c r="P10" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>39</v>
-      </c>
       <c r="R10" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S10" t="n">
-        <v>1648.7</v>
+        <v>1728.4</v>
       </c>
     </row>
     <row r="11">
@@ -4635,31 +4635,31 @@
         <v>1400</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1775.6</v>
+        <v>1757.7</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7602</v>
+        <v>2.865</v>
       </c>
       <c r="G11" t="n">
-        <v>120.67</v>
+        <v>120.37</v>
       </c>
       <c r="H11" t="n">
-        <v>111.46</v>
+        <v>111.34</v>
       </c>
       <c r="I11" t="n">
-        <v>9.210000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3123</v>
+        <v>0.3098</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1488</v>
+        <v>0.1494</v>
       </c>
       <c r="L11" t="n">
-        <v>-7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>29</v>
@@ -4680,7 +4680,7 @@
         <v>37</v>
       </c>
       <c r="S11" t="n">
-        <v>1702.7</v>
+        <v>1699.4</v>
       </c>
     </row>
     <row r="12">
@@ -4689,59 +4689,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1120</v>
+        <v>1328</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1839.6</v>
+        <v>1703.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.8485</v>
+        <v>-2.4994</v>
       </c>
       <c r="G12" t="n">
-        <v>119.39</v>
+        <v>119.56</v>
       </c>
       <c r="H12" t="n">
-        <v>113.99</v>
+        <v>111.75</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3508</v>
+        <v>0.3111</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1441</v>
+        <v>0.1412</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8</v>
+        <v>8.6</v>
       </c>
       <c r="M12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="O12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="S12" t="n">
-        <v>1747.7</v>
+        <v>1663.6</v>
       </c>
     </row>
     <row r="13">
@@ -4750,59 +4750,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1328</v>
+        <v>1120</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>1685.9</v>
+        <v>1831.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7727</v>
+        <v>-7.7196</v>
       </c>
       <c r="G13" t="n">
-        <v>119.85</v>
+        <v>119.16</v>
       </c>
       <c r="H13" t="n">
-        <v>111.64</v>
+        <v>114.92</v>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>4.25</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3131</v>
+        <v>0.3497</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1429</v>
+        <v>0.1459</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>-3</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
+        <v>29</v>
+      </c>
+      <c r="O13" t="n">
+        <v>42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q13" t="n">
         <v>49</v>
       </c>
-      <c r="O13" t="n">
-        <v>51</v>
-      </c>
-      <c r="P13" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>82</v>
-      </c>
       <c r="R13" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>1660.1</v>
+        <v>1758.3</v>
       </c>
     </row>
     <row r="14">
@@ -4818,31 +4818,31 @@
         <v>1280</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>1629.7</v>
+        <v>1621.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5728</v>
+        <v>-1.5779</v>
       </c>
       <c r="G14" t="n">
-        <v>106.96</v>
+        <v>107.61</v>
       </c>
       <c r="H14" t="n">
-        <v>112.13</v>
+        <v>112.47</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.17</v>
+        <v>-4.86</v>
       </c>
       <c r="J14" t="n">
-        <v>0.279</v>
+        <v>0.2773</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1541</v>
+        <v>0.1559</v>
       </c>
       <c r="L14" t="n">
-        <v>-17</v>
+        <v>-19.4</v>
       </c>
       <c r="M14" t="n">
         <v>96</v>
@@ -4863,7 +4863,7 @@
         <v>104</v>
       </c>
       <c r="S14" t="n">
-        <v>1701.8</v>
+        <v>1703.2</v>
       </c>
     </row>
     <row r="15">
@@ -4872,59 +4872,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1279</v>
+        <v>1376</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E15" t="n">
-        <v>1636.6</v>
+        <v>1550</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.902100000000001</v>
+        <v>-2.5273</v>
       </c>
       <c r="G15" t="n">
-        <v>109.52</v>
+        <v>108.93</v>
       </c>
       <c r="H15" t="n">
-        <v>110.2</v>
+        <v>110.37</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.68</v>
+        <v>-1.44</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2845</v>
+        <v>0.2616</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1345</v>
+        <v>0.1372</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.2</v>
+        <v>-7.2</v>
       </c>
       <c r="M15" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="N15" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="O15" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Q15" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="R15" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="S15" t="n">
-        <v>1697.7</v>
+        <v>1653.5</v>
       </c>
     </row>
     <row r="16">
@@ -4933,59 +4933,59 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1261</v>
+        <v>1279</v>
       </c>
       <c r="D16" t="n">
+        <v>124</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1624.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-8.4802</v>
+      </c>
+      <c r="G16" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>109.59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>79</v>
+      </c>
+      <c r="N16" t="n">
+        <v>71</v>
+      </c>
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q16" t="n">
         <v>120</v>
       </c>
-      <c r="E16" t="n">
-        <v>1648.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.9809</v>
-      </c>
-      <c r="G16" t="n">
-        <v>116.12</v>
-      </c>
-      <c r="H16" t="n">
-        <v>111.97</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.2988</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.1514</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>58</v>
-      </c>
-      <c r="N16" t="n">
-        <v>62</v>
-      </c>
-      <c r="O16" t="n">
-        <v>68</v>
-      </c>
-      <c r="P16" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>80</v>
-      </c>
       <c r="R16" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="S16" t="n">
-        <v>1655</v>
+        <v>1688.2</v>
       </c>
     </row>
     <row r="17">
@@ -4994,59 +4994,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1376</v>
+        <v>1261</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E17" t="n">
-        <v>1537.9</v>
+        <v>1640.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6339</v>
+        <v>-1.2644</v>
       </c>
       <c r="G17" t="n">
-        <v>109.32</v>
+        <v>115.45</v>
       </c>
       <c r="H17" t="n">
-        <v>111.39</v>
+        <v>111.34</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.08</v>
+        <v>4.11</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2639</v>
+        <v>0.2976</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1357</v>
+        <v>0.1541</v>
       </c>
       <c r="L17" t="n">
-        <v>-10.6</v>
+        <v>-6.6</v>
       </c>
       <c r="M17" t="n">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="N17" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="O17" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="P17" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="Q17" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="R17" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="S17" t="n">
-        <v>1657.5</v>
+        <v>1660.6</v>
       </c>
     </row>
   </sheetData>
@@ -5173,31 +5173,31 @@
         <v>1190</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>1514.8</v>
+        <v>1515.6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.598</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>116.43</v>
+        <v>116.98</v>
       </c>
       <c r="H2" t="n">
-        <v>105.39</v>
+        <v>105.72</v>
       </c>
       <c r="I2" t="n">
-        <v>11.04</v>
+        <v>11.26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2692</v>
+        <v>0.2696</v>
       </c>
       <c r="K2" t="n">
         <v>0.1444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
         <v>140</v>
@@ -5218,7 +5218,7 @@
         <v>128</v>
       </c>
       <c r="S2" t="n">
-        <v>1424.6</v>
+        <v>1416.1</v>
       </c>
     </row>
     <row r="3">
@@ -5234,31 +5234,31 @@
         <v>1273</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1454.9</v>
+        <v>1450.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8914</v>
+        <v>0.8818</v>
       </c>
       <c r="G3" t="n">
-        <v>115.27</v>
+        <v>114.82</v>
       </c>
       <c r="H3" t="n">
-        <v>111.22</v>
+        <v>111.29</v>
       </c>
       <c r="I3" t="n">
-        <v>4.05</v>
+        <v>3.53</v>
       </c>
       <c r="J3" t="n">
-        <v>0.306</v>
+        <v>0.3138</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1492</v>
+        <v>0.152</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>-0.6</v>
       </c>
       <c r="M3" t="n">
         <v>182</v>
@@ -5279,7 +5279,7 @@
         <v>171</v>
       </c>
       <c r="S3" t="n">
-        <v>1455.1</v>
+        <v>1450.7</v>
       </c>
     </row>
     <row r="4">
@@ -5295,31 +5295,31 @@
         <v>1459</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1486.8</v>
+        <v>1481.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4187</v>
+        <v>0.4047</v>
       </c>
       <c r="G4" t="n">
-        <v>114.27</v>
+        <v>114.07</v>
       </c>
       <c r="H4" t="n">
-        <v>114.42</v>
+        <v>114.38</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.15</v>
+        <v>-0.31</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2941</v>
+        <v>0.2903</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1302</v>
+        <v>0.1301</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6</v>
+        <v>-1.2</v>
       </c>
       <c r="M4" t="n">
         <v>248</v>
@@ -5340,7 +5340,7 @@
         <v>240</v>
       </c>
       <c r="S4" t="n">
-        <v>1426.2</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="5">
@@ -5356,31 +5356,31 @@
         <v>1359</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1444.9</v>
+        <v>1437.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0824</v>
+        <v>-3.8054</v>
       </c>
       <c r="G5" t="n">
-        <v>112.06</v>
+        <v>112.22</v>
       </c>
       <c r="H5" t="n">
-        <v>110.06</v>
+        <v>110.83</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="J5" t="n">
-        <v>0.237</v>
+        <v>0.2391</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1263</v>
+        <v>0.1241</v>
       </c>
       <c r="L5" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
         <v>209</v>
@@ -5401,7 +5401,7 @@
         <v>213</v>
       </c>
       <c r="S5" t="n">
-        <v>1434</v>
+        <v>1439.5</v>
       </c>
     </row>
     <row r="6">
@@ -5417,31 +5417,31 @@
         <v>1441</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1377.3</v>
+        <v>1381.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0597</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>110.79</v>
+        <v>110.75</v>
       </c>
       <c r="H6" t="n">
-        <v>113.15</v>
+        <v>113.08</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.36</v>
+        <v>-2.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.326</v>
+        <v>0.3281</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1512</v>
+        <v>0.1487</v>
       </c>
       <c r="L6" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
         <v>236</v>
@@ -5462,7 +5462,7 @@
         <v>235</v>
       </c>
       <c r="S6" t="n">
-        <v>1472.9</v>
+        <v>1471.4</v>
       </c>
     </row>
     <row r="7">
@@ -5478,31 +5478,31 @@
         <v>1202</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1529.5</v>
+        <v>1533.7</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1809</v>
+        <v>1.0135</v>
       </c>
       <c r="G7" t="n">
-        <v>110.54</v>
+        <v>111.25</v>
       </c>
       <c r="H7" t="n">
-        <v>107.27</v>
+        <v>107.48</v>
       </c>
       <c r="I7" t="n">
-        <v>3.27</v>
+        <v>3.77</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2582</v>
+        <v>0.2564</v>
       </c>
       <c r="K7" t="n">
-        <v>0.171</v>
+        <v>0.1709</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>200</v>
@@ -5523,7 +5523,7 @@
         <v>198</v>
       </c>
       <c r="S7" t="n">
-        <v>1418.3</v>
+        <v>1419.8</v>
       </c>
     </row>
     <row r="8">
@@ -5539,31 +5539,31 @@
         <v>1422</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1371.5</v>
+        <v>1376.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6983</v>
+        <v>-2.5542</v>
       </c>
       <c r="G8" t="n">
-        <v>110.38</v>
+        <v>110.35</v>
       </c>
       <c r="H8" t="n">
-        <v>117.51</v>
+        <v>117.35</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.13</v>
+        <v>-7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2724</v>
+        <v>0.272</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1441</v>
+        <v>0.1391</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
         <v>304</v>
@@ -5584,7 +5584,7 @@
         <v>298</v>
       </c>
       <c r="S8" t="n">
-        <v>1418.4</v>
+        <v>1424.1</v>
       </c>
     </row>
     <row r="9">
@@ -5661,31 +5661,31 @@
         <v>1154</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1235.6</v>
+        <v>1234.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0387</v>
+        <v>0.075</v>
       </c>
       <c r="G10" t="n">
-        <v>102.25</v>
+        <v>102.55</v>
       </c>
       <c r="H10" t="n">
-        <v>118.78</v>
+        <v>119.03</v>
       </c>
       <c r="I10" t="n">
-        <v>-16.53</v>
+        <v>-16.48</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2933</v>
+        <v>0.2969</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1554</v>
+        <v>0.1551</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.8</v>
+        <v>-8.6</v>
       </c>
       <c r="M10" t="n">
         <v>351</v>
@@ -5706,7 +5706,7 @@
         <v>350</v>
       </c>
       <c r="S10" t="n">
-        <v>1415.5</v>
+        <v>1419.9</v>
       </c>
     </row>
     <row r="11">
@@ -6737,31 +6737,31 @@
         <v>1362</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1564.7</v>
+        <v>1568.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1724</v>
+        <v>-4.0664</v>
       </c>
       <c r="G6" t="n">
-        <v>108.93</v>
+        <v>109.57</v>
       </c>
       <c r="H6" t="n">
-        <v>109.17</v>
+        <v>108.89</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.23</v>
+        <v>0.68</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2663</v>
+        <v>0.2747</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1568</v>
+        <v>0.1548</v>
       </c>
       <c r="L6" t="n">
-        <v>-9</v>
+        <v>-0.2</v>
       </c>
       <c r="M6" t="n">
         <v>122</v>
@@ -6782,7 +6782,7 @@
         <v>122</v>
       </c>
       <c r="S6" t="n">
-        <v>1573.6</v>
+        <v>1568.4</v>
       </c>
     </row>
     <row r="7">
@@ -6798,31 +6798,31 @@
         <v>1334</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1432.7</v>
+        <v>1440.5</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1195</v>
+        <v>3.9361</v>
       </c>
       <c r="G7" t="n">
-        <v>108.15</v>
+        <v>107.78</v>
       </c>
       <c r="H7" t="n">
-        <v>105.42</v>
+        <v>104.75</v>
       </c>
       <c r="I7" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="J7" t="n">
         <v>0.2727</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1889</v>
+        <v>0.189</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.4</v>
+        <v>-9</v>
       </c>
       <c r="M7" t="n">
         <v>112</v>
@@ -6843,7 +6843,7 @@
         <v>115</v>
       </c>
       <c r="S7" t="n">
-        <v>1522.4</v>
+        <v>1523.4</v>
       </c>
     </row>
     <row r="8">
@@ -6859,31 +6859,31 @@
         <v>1370</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1555.8</v>
+        <v>1548</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5588</v>
+        <v>2.3807</v>
       </c>
       <c r="G8" t="n">
-        <v>101.35</v>
+        <v>100.95</v>
       </c>
       <c r="H8" t="n">
-        <v>98.51000000000001</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2553</v>
+        <v>0.2559</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1673</v>
+        <v>0.1686</v>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="M8" t="n">
         <v>115</v>
@@ -6904,7 +6904,7 @@
         <v>118</v>
       </c>
       <c r="S8" t="n">
-        <v>1523.7</v>
+        <v>1521.6</v>
       </c>
     </row>
     <row r="9">
@@ -6981,31 +6981,31 @@
         <v>1339</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1416.8</v>
+        <v>1413.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4725</v>
+        <v>1.5131</v>
       </c>
       <c r="G10" t="n">
-        <v>102.47</v>
+        <v>102.18</v>
       </c>
       <c r="H10" t="n">
-        <v>110.89</v>
+        <v>111.49</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.42</v>
+        <v>-9.31</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2615</v>
+        <v>0.2652</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1865</v>
+        <v>0.1895</v>
       </c>
       <c r="L10" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M10" t="n">
         <v>204</v>
@@ -7026,7 +7026,7 @@
         <v>227</v>
       </c>
       <c r="S10" t="n">
-        <v>1531.8</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="11">
@@ -7336,31 +7336,31 @@
         <v>1181</v>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>2179.5</v>
+        <v>2183.9</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6659</v>
+        <v>3.6873</v>
       </c>
       <c r="G2" t="n">
-        <v>123.79</v>
+        <v>123.11</v>
       </c>
       <c r="H2" t="n">
-        <v>93.15000000000001</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>30.64</v>
+        <v>30.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2823</v>
+        <v>0.2884</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1519</v>
+        <v>0.1511</v>
       </c>
       <c r="L2" t="n">
-        <v>28.2</v>
+        <v>23.8</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -7381,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1692</v>
+        <v>1701.5</v>
       </c>
     </row>
     <row r="3">
@@ -7397,31 +7397,31 @@
         <v>1438</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1951.6</v>
+        <v>1956.5</v>
       </c>
       <c r="F3" t="n">
-        <v>14.014</v>
+        <v>13.4946</v>
       </c>
       <c r="G3" t="n">
-        <v>118.9</v>
+        <v>118.84</v>
       </c>
       <c r="H3" t="n">
-        <v>99.7</v>
+        <v>100.06</v>
       </c>
       <c r="I3" t="n">
-        <v>19.2</v>
+        <v>18.77</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3157</v>
+        <v>0.3168</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1519</v>
+        <v>0.1532</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>17</v>
@@ -7442,7 +7442,7 @@
         <v>14</v>
       </c>
       <c r="S3" t="n">
-        <v>1635.8</v>
+        <v>1639.2</v>
       </c>
     </row>
     <row r="4">
@@ -7458,31 +7458,31 @@
         <v>1274</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1775.8</v>
+        <v>1761</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7773</v>
+        <v>12.4806</v>
       </c>
       <c r="G4" t="n">
-        <v>117.09</v>
+        <v>118.15</v>
       </c>
       <c r="H4" t="n">
-        <v>99.90000000000001</v>
+        <v>101.88</v>
       </c>
       <c r="I4" t="n">
-        <v>17.19</v>
+        <v>16.27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3061</v>
+        <v>0.3077</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1624</v>
+        <v>0.1596</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
@@ -7503,7 +7503,7 @@
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>1609.3</v>
+        <v>1617.1</v>
       </c>
     </row>
     <row r="5">
@@ -7519,31 +7519,31 @@
         <v>1314</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1921.9</v>
+        <v>1917.6</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4321</v>
+        <v>2.3735</v>
       </c>
       <c r="G5" t="n">
-        <v>115.82</v>
+        <v>115.09</v>
       </c>
       <c r="H5" t="n">
-        <v>102.6</v>
+        <v>103.39</v>
       </c>
       <c r="I5" t="n">
-        <v>13.22</v>
+        <v>11.71</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2692</v>
+        <v>0.2653</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1364</v>
+        <v>0.14</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
@@ -7564,7 +7564,7 @@
         <v>25</v>
       </c>
       <c r="S5" t="n">
-        <v>1655.6</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="6">
@@ -7580,31 +7580,31 @@
         <v>1155</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1836.4</v>
+        <v>1838.2</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8425</v>
+        <v>3.3876</v>
       </c>
       <c r="G6" t="n">
-        <v>112.26</v>
+        <v>112.83</v>
       </c>
       <c r="H6" t="n">
-        <v>99.90000000000001</v>
+        <v>100.58</v>
       </c>
       <c r="I6" t="n">
-        <v>12.36</v>
+        <v>12.25</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2417</v>
+        <v>0.2488</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1398</v>
+        <v>0.1395</v>
       </c>
       <c r="L6" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="M6" t="n">
         <v>36</v>
@@ -7625,7 +7625,7 @@
         <v>35</v>
       </c>
       <c r="S6" t="n">
-        <v>1652.4</v>
+        <v>1641.6</v>
       </c>
     </row>
     <row r="7">
@@ -7641,31 +7641,31 @@
         <v>1257</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1830.4</v>
+        <v>1845.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0745</v>
+        <v>-2.9919</v>
       </c>
       <c r="G7" t="n">
-        <v>119.03</v>
+        <v>120.19</v>
       </c>
       <c r="H7" t="n">
-        <v>100.17</v>
+        <v>101.95</v>
       </c>
       <c r="I7" t="n">
-        <v>18.86</v>
+        <v>18.24</v>
       </c>
       <c r="J7" t="n">
-        <v>0.29</v>
+        <v>0.2897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1596</v>
+        <v>0.1578</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="M7" t="n">
         <v>19</v>
@@ -7686,7 +7686,7 @@
         <v>17</v>
       </c>
       <c r="S7" t="n">
-        <v>1677.2</v>
+        <v>1682.1</v>
       </c>
     </row>
     <row r="8">
@@ -7702,28 +7702,28 @@
         <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1751.7</v>
+        <v>1735.9</v>
       </c>
       <c r="F8" t="n">
-        <v>8.052099999999999</v>
+        <v>7.7247</v>
       </c>
       <c r="G8" t="n">
-        <v>118.51</v>
+        <v>118.75</v>
       </c>
       <c r="H8" t="n">
-        <v>107.99</v>
+        <v>108.16</v>
       </c>
       <c r="I8" t="n">
-        <v>10.52</v>
+        <v>10.59</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2827</v>
+        <v>0.2829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1274</v>
+        <v>0.1296</v>
       </c>
       <c r="L8" t="n">
         <v>-8.199999999999999</v>
@@ -7747,7 +7747,7 @@
         <v>29</v>
       </c>
       <c r="S8" t="n">
-        <v>1678.3</v>
+        <v>1675.6</v>
       </c>
     </row>
     <row r="9">
@@ -7763,31 +7763,31 @@
         <v>1199</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1607.5</v>
+        <v>1621.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2916</v>
+        <v>-0.8284</v>
       </c>
       <c r="G9" t="n">
-        <v>110.66</v>
+        <v>111.16</v>
       </c>
       <c r="H9" t="n">
-        <v>107.46</v>
+        <v>107.31</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3177</v>
+        <v>0.3133</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1509</v>
+        <v>0.1507</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
         <v>71</v>
@@ -7808,7 +7808,7 @@
         <v>77</v>
       </c>
       <c r="S9" t="n">
-        <v>1650</v>
+        <v>1656.1</v>
       </c>
     </row>
     <row r="10">
@@ -7824,31 +7824,31 @@
         <v>1143</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1730.3</v>
+        <v>1717.3</v>
       </c>
       <c r="F10" t="n">
-        <v>8.0456</v>
+        <v>7.7033</v>
       </c>
       <c r="G10" t="n">
-        <v>109.41</v>
+        <v>109.18</v>
       </c>
       <c r="H10" t="n">
-        <v>102.71</v>
+        <v>103.34</v>
       </c>
       <c r="I10" t="n">
-        <v>6.7</v>
+        <v>5.84</v>
       </c>
       <c r="J10" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1448</v>
+        <v>0.143</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>-0.4</v>
       </c>
       <c r="M10" t="n">
         <v>73</v>
@@ -7869,7 +7869,7 @@
         <v>64</v>
       </c>
       <c r="S10" t="n">
-        <v>1600</v>
+        <v>1603.3</v>
       </c>
     </row>
     <row r="11">
@@ -7885,31 +7885,31 @@
         <v>1390</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1734.2</v>
+        <v>1750</v>
       </c>
       <c r="F11" t="n">
-        <v>2.838</v>
+        <v>2.6234</v>
       </c>
       <c r="G11" t="n">
-        <v>111.86</v>
+        <v>112.31</v>
       </c>
       <c r="H11" t="n">
-        <v>106.91</v>
+        <v>107.61</v>
       </c>
       <c r="I11" t="n">
-        <v>4.95</v>
+        <v>4.71</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3137</v>
+        <v>0.3189</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1439</v>
+        <v>0.1433</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="M11" t="n">
         <v>65</v>
@@ -7930,7 +7930,7 @@
         <v>65</v>
       </c>
       <c r="S11" t="n">
-        <v>1622.2</v>
+        <v>1628.4</v>
       </c>
     </row>
     <row r="12">
@@ -7946,31 +7946,31 @@
         <v>1374</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1752.7</v>
+        <v>1738.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.268</v>
+        <v>0.9109</v>
       </c>
       <c r="G12" t="n">
-        <v>118.53</v>
+        <v>118.28</v>
       </c>
       <c r="H12" t="n">
-        <v>109.67</v>
+        <v>110.33</v>
       </c>
       <c r="I12" t="n">
-        <v>8.859999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3029</v>
+        <v>0.3064</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1516</v>
+        <v>0.1528</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>-4.2</v>
       </c>
       <c r="M12" t="n">
         <v>39</v>
@@ -7991,7 +7991,7 @@
         <v>36</v>
       </c>
       <c r="S12" t="n">
-        <v>1646.2</v>
+        <v>1643.1</v>
       </c>
     </row>
     <row r="13">
@@ -8007,31 +8007,31 @@
         <v>1439</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>1718.5</v>
+        <v>1713.5</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1973</v>
+        <v>5.7826</v>
       </c>
       <c r="G13" t="n">
-        <v>112.42</v>
+        <v>112.34</v>
       </c>
       <c r="H13" t="n">
-        <v>106.23</v>
+        <v>106.8</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>5.54</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2914</v>
+        <v>0.2975</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1461</v>
+        <v>0.1458</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6</v>
+        <v>3.2</v>
       </c>
       <c r="M13" t="n">
         <v>57</v>
@@ -8052,7 +8052,7 @@
         <v>54</v>
       </c>
       <c r="S13" t="n">
-        <v>1648.5</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="14">
@@ -8068,31 +8068,31 @@
         <v>1448</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>1637.9</v>
+        <v>1650.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1375</v>
+        <v>-3.0285</v>
       </c>
       <c r="G14" t="n">
-        <v>112.06</v>
+        <v>112.13</v>
       </c>
       <c r="H14" t="n">
-        <v>109.8</v>
+        <v>109.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2923</v>
+        <v>0.2909</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1475</v>
+        <v>0.1488</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="M14" t="n">
         <v>78</v>
@@ -8113,7 +8113,7 @@
         <v>69</v>
       </c>
       <c r="S14" t="n">
-        <v>1670.9</v>
+        <v>1669.7</v>
       </c>
     </row>
     <row r="15">
@@ -8129,31 +8129,31 @@
         <v>1393</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E15" t="n">
-        <v>1593.4</v>
+        <v>1583.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2389</v>
+        <v>1.0611</v>
       </c>
       <c r="G15" t="n">
-        <v>108.18</v>
+        <v>108.11</v>
       </c>
       <c r="H15" t="n">
-        <v>106.44</v>
+        <v>106.28</v>
       </c>
       <c r="I15" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2761</v>
+        <v>0.2758</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1528</v>
+        <v>0.1525</v>
       </c>
       <c r="L15" t="n">
-        <v>-13.8</v>
+        <v>-14.4</v>
       </c>
       <c r="M15" t="n">
         <v>77</v>
@@ -8174,7 +8174,7 @@
         <v>79</v>
       </c>
       <c r="S15" t="n">
-        <v>1667.8</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="16">
@@ -8190,31 +8190,31 @@
         <v>1338</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E16" t="n">
-        <v>1510.7</v>
+        <v>1521</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.4665</v>
+        <v>-5.1919</v>
       </c>
       <c r="G16" t="n">
-        <v>106.74</v>
+        <v>106.56</v>
       </c>
       <c r="H16" t="n">
-        <v>109.24</v>
+        <v>108.83</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5</v>
+        <v>-2.27</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3257</v>
+        <v>0.323</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1677</v>
+        <v>0.1679</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
         <v>99</v>
@@ -8235,7 +8235,7 @@
         <v>110</v>
       </c>
       <c r="S16" t="n">
-        <v>1660.9</v>
+        <v>1658.7</v>
       </c>
     </row>
   </sheetData>
@@ -8416,59 +8416,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1409</v>
+        <v>1455</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1676.2</v>
+        <v>1620</v>
       </c>
       <c r="F3" t="n">
-        <v>9.632899999999999</v>
+        <v>1.5141</v>
       </c>
       <c r="G3" t="n">
-        <v>122.85</v>
+        <v>112.55</v>
       </c>
       <c r="H3" t="n">
-        <v>105.68</v>
+        <v>102</v>
       </c>
       <c r="I3" t="n">
-        <v>17.17</v>
+        <v>10.54</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2706</v>
+        <v>0.3477</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1461</v>
+        <v>0.1417</v>
       </c>
       <c r="L3" t="n">
-        <v>17.6</v>
+        <v>11.2</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="N3" t="n">
+        <v>93</v>
+      </c>
+      <c r="O3" t="n">
+        <v>93</v>
+      </c>
+      <c r="P3" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>89</v>
+      </c>
+      <c r="R3" t="n">
         <v>83</v>
       </c>
-      <c r="O3" t="n">
-        <v>58</v>
-      </c>
-      <c r="P3" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>60</v>
-      </c>
-      <c r="R3" t="n">
-        <v>50</v>
-      </c>
       <c r="S3" t="n">
-        <v>1502.5</v>
+        <v>1534.8</v>
       </c>
     </row>
     <row r="4">
@@ -8477,59 +8477,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wichita St</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1455</v>
+        <v>1409</v>
       </c>
       <c r="D4" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E4" t="n">
-        <v>1613.3</v>
+        <v>1676.2</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3577</v>
+        <v>9.632899999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>112.04</v>
+        <v>122.85</v>
       </c>
       <c r="H4" t="n">
-        <v>102.02</v>
+        <v>105.68</v>
       </c>
       <c r="I4" t="n">
-        <v>10.02</v>
+        <v>17.17</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3484</v>
+        <v>0.2706</v>
       </c>
       <c r="K4" t="n">
-        <v>0.143</v>
+        <v>0.1461</v>
       </c>
       <c r="L4" t="n">
-        <v>8.4</v>
+        <v>17.6</v>
       </c>
       <c r="M4" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="N4" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="O4" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="P4" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="Q4" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="R4" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>1529.6</v>
+        <v>1502.5</v>
       </c>
     </row>
     <row r="5">
@@ -8599,59 +8599,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FL Atlantic</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1577.3</v>
+        <v>1439.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2377</v>
+        <v>1.3639</v>
       </c>
       <c r="G6" t="n">
-        <v>109.09</v>
+        <v>112.74</v>
       </c>
       <c r="H6" t="n">
-        <v>105.62</v>
+        <v>113.57</v>
       </c>
       <c r="I6" t="n">
-        <v>3.47</v>
+        <v>-0.83</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2929</v>
+        <v>0.2964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.166</v>
+        <v>0.1665</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="N6" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="O6" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="P6" t="n">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="Q6" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="R6" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="S6" t="n">
-        <v>1558</v>
+        <v>1491.9</v>
       </c>
     </row>
     <row r="7">
@@ -8660,59 +8660,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1150</v>
+        <v>1317</v>
       </c>
       <c r="D7" t="n">
         <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1439.3</v>
+        <v>1536.7</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3639</v>
+        <v>-5.3186</v>
       </c>
       <c r="G7" t="n">
-        <v>112.74</v>
+        <v>104.14</v>
       </c>
       <c r="H7" t="n">
-        <v>113.57</v>
+        <v>102.05</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.83</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2964</v>
+        <v>0.3367</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1665</v>
+        <v>0.157</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="N7" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="O7" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="P7" t="n">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="Q7" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="R7" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="S7" t="n">
-        <v>1491.9</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="8">
@@ -8721,59 +8721,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>FL Atlantic</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1317</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1570.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.3127</v>
+      </c>
+      <c r="G8" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>106.62</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>121</v>
       </c>
-      <c r="E8" t="n">
-        <v>1536.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-5.3186</v>
-      </c>
-      <c r="G8" t="n">
-        <v>104.14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>102.05</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.3367</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>139</v>
-      </c>
       <c r="N8" t="n">
+        <v>119</v>
+      </c>
+      <c r="O8" t="n">
+        <v>106</v>
+      </c>
+      <c r="P8" t="n">
         <v>120</v>
       </c>
-      <c r="O8" t="n">
-        <v>145</v>
-      </c>
-      <c r="P8" t="n">
-        <v>146</v>
-      </c>
       <c r="Q8" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="R8" t="n">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="S8" t="n">
-        <v>1505</v>
+        <v>1561.9</v>
       </c>
     </row>
     <row r="9">
@@ -9083,31 +9083,31 @@
         <v>1112</v>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>2252.6</v>
+        <v>2253.6</v>
       </c>
       <c r="F2" t="n">
-        <v>8.169700000000001</v>
+        <v>7.7769</v>
       </c>
       <c r="G2" t="n">
-        <v>120.84</v>
+        <v>121.09</v>
       </c>
       <c r="H2" t="n">
-        <v>95.38</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>25.46</v>
+        <v>24.99</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2935</v>
+        <v>0.291</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1524</v>
+        <v>0.1505</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -9128,7 +9128,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1751.1</v>
+        <v>1742.6</v>
       </c>
     </row>
     <row r="3">
@@ -9144,31 +9144,31 @@
         <v>1222</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>2099.2</v>
+        <v>2102.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9173</v>
+        <v>1.6401</v>
       </c>
       <c r="G3" t="n">
-        <v>117.81</v>
+        <v>117.95</v>
       </c>
       <c r="H3" t="n">
-        <v>94.78</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>23.03</v>
+        <v>22.51</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3414</v>
+        <v>0.3379</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1193</v>
+        <v>0.1199</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -9189,7 +9189,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1706</v>
+        <v>1706.6</v>
       </c>
     </row>
     <row r="4">
@@ -9198,59 +9198,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1403</v>
+        <v>1242</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>2044.2</v>
+        <v>1973.7</v>
       </c>
       <c r="F4" t="n">
-        <v>10.5951</v>
+        <v>11.337</v>
       </c>
       <c r="G4" t="n">
-        <v>118.24</v>
+        <v>111.61</v>
       </c>
       <c r="H4" t="n">
-        <v>105.38</v>
+        <v>100.9</v>
       </c>
       <c r="I4" t="n">
-        <v>12.86</v>
+        <v>10.71</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2929</v>
+        <v>0.2487</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1562</v>
+        <v>0.1523</v>
       </c>
       <c r="L4" t="n">
-        <v>7.2</v>
+        <v>-3.4</v>
       </c>
       <c r="M4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
         <v>13</v>
       </c>
-      <c r="N4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O4" t="n">
-        <v>11</v>
-      </c>
-      <c r="P4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>15</v>
       </c>
-      <c r="R4" t="n">
-        <v>13</v>
-      </c>
       <c r="S4" t="n">
-        <v>1756.8</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="5">
@@ -9259,59 +9259,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1235</v>
+        <v>1403</v>
       </c>
       <c r="D5" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>2024.5</v>
+        <v>2025.5</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6605</v>
+        <v>10.1327</v>
       </c>
       <c r="G5" t="n">
-        <v>118.09</v>
+        <v>118.86</v>
       </c>
       <c r="H5" t="n">
-        <v>96.43000000000001</v>
+        <v>106.69</v>
       </c>
       <c r="I5" t="n">
-        <v>21.66</v>
+        <v>12.16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3174</v>
+        <v>0.2944</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1477</v>
+        <v>0.155</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.2</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S5" t="n">
-        <v>1693</v>
+        <v>1762.7</v>
       </c>
     </row>
     <row r="6">
@@ -9320,59 +9320,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1971.6</v>
+        <v>2027.4</v>
       </c>
       <c r="F6" t="n">
-        <v>11.9283</v>
+        <v>3.1622</v>
       </c>
       <c r="G6" t="n">
-        <v>110.16</v>
+        <v>118.43</v>
       </c>
       <c r="H6" t="n">
-        <v>100.46</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>9.699999999999999</v>
+        <v>22.42</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2509</v>
+        <v>0.3184</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1535</v>
+        <v>0.1465</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.8</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>1779.6</v>
+        <v>1686.9</v>
       </c>
     </row>
     <row r="7">
@@ -9388,31 +9388,31 @@
         <v>1395</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1827.5</v>
+        <v>1836.3</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8987</v>
+        <v>6.8916</v>
       </c>
       <c r="G7" t="n">
-        <v>110.58</v>
+        <v>110.72</v>
       </c>
       <c r="H7" t="n">
-        <v>101.35</v>
+        <v>101.25</v>
       </c>
       <c r="I7" t="n">
-        <v>9.23</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3181</v>
+        <v>0.3192</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1536</v>
+        <v>0.1507</v>
       </c>
       <c r="L7" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
@@ -9433,7 +9433,7 @@
         <v>45</v>
       </c>
       <c r="S7" t="n">
-        <v>1681.1</v>
+        <v>1679.3</v>
       </c>
     </row>
     <row r="8">
@@ -9442,59 +9442,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>1452</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1733</v>
+        <v>1710.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4193</v>
+        <v>0.4911</v>
       </c>
       <c r="G8" t="n">
-        <v>105.76</v>
+        <v>107.75</v>
       </c>
       <c r="H8" t="n">
-        <v>97.33</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>8.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2897</v>
+        <v>0.2866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1583</v>
+        <v>0.163</v>
       </c>
       <c r="L8" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="N8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="P8" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R8" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S8" t="n">
-        <v>1713.8</v>
+        <v>1659.8</v>
       </c>
     </row>
     <row r="9">
@@ -9503,59 +9503,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1452</v>
+        <v>1416</v>
       </c>
       <c r="D9" t="n">
         <v>123</v>
       </c>
       <c r="E9" t="n">
-        <v>1710.3</v>
+        <v>1820.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4911</v>
+        <v>7.025</v>
       </c>
       <c r="G9" t="n">
-        <v>107.75</v>
+        <v>114.77</v>
       </c>
       <c r="H9" t="n">
-        <v>99.54000000000001</v>
+        <v>110.49</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.28</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2866</v>
+        <v>0.3115</v>
       </c>
       <c r="K9" t="n">
-        <v>0.163</v>
+        <v>0.1546</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O9" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P9" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
-        <v>1659.8</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="10">
@@ -9564,59 +9564,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1416</v>
+        <v>1153</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1820.5</v>
+        <v>1724.3</v>
       </c>
       <c r="F10" t="n">
-        <v>7.025</v>
+        <v>0.956</v>
       </c>
       <c r="G10" t="n">
-        <v>114.77</v>
+        <v>105.28</v>
       </c>
       <c r="H10" t="n">
-        <v>110.49</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>4.28</v>
+        <v>7.09</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3115</v>
+        <v>0.2902</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1546</v>
+        <v>0.1653</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6</v>
+        <v>7.8</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O10" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S10" t="n">
-        <v>1687.9</v>
+        <v>1716.2</v>
       </c>
     </row>
     <row r="11">
@@ -9632,31 +9632,31 @@
         <v>1140</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1905.8</v>
+        <v>1924.5</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2762</v>
+        <v>1.6354</v>
       </c>
       <c r="G11" t="n">
-        <v>117.49</v>
+        <v>118.39</v>
       </c>
       <c r="H11" t="n">
-        <v>106.29</v>
+        <v>106.82</v>
       </c>
       <c r="I11" t="n">
-        <v>11.21</v>
+        <v>11.57</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2953</v>
+        <v>0.3034</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1466</v>
+        <v>0.1419</v>
       </c>
       <c r="L11" t="n">
-        <v>-8</v>
+        <v>-5.4</v>
       </c>
       <c r="M11" t="n">
         <v>23</v>
@@ -9677,7 +9677,7 @@
         <v>23</v>
       </c>
       <c r="S11" t="n">
-        <v>1713.1</v>
+        <v>1726.9</v>
       </c>
     </row>
     <row r="12">
@@ -9693,31 +9693,31 @@
         <v>1160</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1614.1</v>
+        <v>1613.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.609</v>
+        <v>-4.3802</v>
       </c>
       <c r="G12" t="n">
-        <v>114.63</v>
+        <v>113.99</v>
       </c>
       <c r="H12" t="n">
-        <v>113.03</v>
+        <v>113.32</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>0.68</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2808</v>
+        <v>0.2829</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1415</v>
+        <v>0.1411</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="M12" t="n">
         <v>72</v>
@@ -9738,7 +9738,7 @@
         <v>78</v>
       </c>
       <c r="S12" t="n">
-        <v>1668.4</v>
+        <v>1695.4</v>
       </c>
     </row>
     <row r="13">
@@ -9754,31 +9754,31 @@
         <v>1113</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>1681.5</v>
+        <v>1678.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7205</v>
+        <v>-1.4683</v>
       </c>
       <c r="G13" t="n">
-        <v>108.88</v>
+        <v>108.23</v>
       </c>
       <c r="H13" t="n">
-        <v>108.27</v>
+        <v>109.09</v>
       </c>
       <c r="I13" t="n">
-        <v>0.61</v>
+        <v>-0.85</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2847</v>
+        <v>0.2778</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1535</v>
+        <v>0.1602</v>
       </c>
       <c r="L13" t="n">
-        <v>2.2</v>
+        <v>-3</v>
       </c>
       <c r="M13" t="n">
         <v>66</v>
@@ -9799,7 +9799,7 @@
         <v>73</v>
       </c>
       <c r="S13" t="n">
-        <v>1725.8</v>
+        <v>1735.5</v>
       </c>
     </row>
     <row r="14">
@@ -9808,59 +9808,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oklahoma St</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1329</v>
+        <v>1124</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>1711.9</v>
+        <v>1678.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0529</v>
+        <v>-6.2439</v>
       </c>
       <c r="G14" t="n">
-        <v>110.48</v>
+        <v>116.97</v>
       </c>
       <c r="H14" t="n">
-        <v>109.05</v>
+        <v>111.54</v>
       </c>
       <c r="I14" t="n">
-        <v>1.43</v>
+        <v>5.42</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2757</v>
+        <v>0.3301</v>
       </c>
       <c r="K14" t="n">
-        <v>0.156</v>
+        <v>0.1604</v>
       </c>
       <c r="L14" t="n">
-        <v>-7</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="N14" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="P14" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="R14" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="S14" t="n">
-        <v>1677.8</v>
+        <v>1727.4</v>
       </c>
     </row>
     <row r="15">
@@ -9869,59 +9869,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Oklahoma St</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1124</v>
+        <v>1329</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E15" t="n">
-        <v>1674.1</v>
+        <v>1708.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.5504</v>
+        <v>-1.1004</v>
       </c>
       <c r="G15" t="n">
-        <v>114.76</v>
+        <v>110.43</v>
       </c>
       <c r="H15" t="n">
-        <v>111.24</v>
+        <v>109.61</v>
       </c>
       <c r="I15" t="n">
-        <v>3.51</v>
+        <v>0.82</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3244</v>
+        <v>0.2792</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1668</v>
+        <v>0.1571</v>
       </c>
       <c r="L15" t="n">
         <v>-6</v>
       </c>
       <c r="M15" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="N15" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O15" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="P15" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q15" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="R15" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="S15" t="n">
-        <v>1740.6</v>
+        <v>1693.9</v>
       </c>
     </row>
     <row r="16">
@@ -9937,31 +9937,31 @@
         <v>1243</v>
       </c>
       <c r="D16" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E16" t="n">
-        <v>1579.8</v>
+        <v>1577.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.1262</v>
+        <v>-4.9402</v>
       </c>
       <c r="G16" t="n">
-        <v>106.53</v>
+        <v>106.78</v>
       </c>
       <c r="H16" t="n">
-        <v>108.89</v>
+        <v>110.18</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.37</v>
+        <v>-3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.291</v>
+        <v>0.2892</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1721</v>
+        <v>0.1683</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.6</v>
+        <v>-12.6</v>
       </c>
       <c r="M16" t="n">
         <v>102</v>
@@ -9982,7 +9982,7 @@
         <v>102</v>
       </c>
       <c r="S16" t="n">
-        <v>1692.2</v>
+        <v>1704.2</v>
       </c>
     </row>
     <row r="17">
@@ -9998,31 +9998,31 @@
         <v>1428</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E17" t="n">
-        <v>1525.9</v>
+        <v>1521.6</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.671</v>
+        <v>-4.5566</v>
       </c>
       <c r="G17" t="n">
-        <v>108.53</v>
+        <v>108.84</v>
       </c>
       <c r="H17" t="n">
-        <v>114.69</v>
+        <v>116.37</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.15</v>
+        <v>-7.53</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2793</v>
+        <v>0.28</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1575</v>
+        <v>0.162</v>
       </c>
       <c r="L17" t="n">
-        <v>-8</v>
+        <v>-14.2</v>
       </c>
       <c r="M17" t="n">
         <v>116</v>
@@ -10043,7 +10043,7 @@
         <v>123</v>
       </c>
       <c r="S17" t="n">
-        <v>1690.3</v>
+        <v>1690.8</v>
       </c>
     </row>
   </sheetData>
@@ -10231,31 +10231,31 @@
         <v>1163</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>2092.8</v>
+        <v>2064.2</v>
       </c>
       <c r="F3" t="n">
-        <v>9.4907</v>
+        <v>8.950200000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>117.38</v>
+        <v>116.34</v>
       </c>
       <c r="H3" t="n">
-        <v>97.34999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>20.03</v>
+        <v>18.93</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2903</v>
+        <v>0.2937</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1532</v>
+        <v>0.1558</v>
       </c>
       <c r="L3" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -10276,7 +10276,7 @@
         <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>1667.4</v>
+        <v>1660.9</v>
       </c>
     </row>
     <row r="4">
@@ -10292,31 +10292,31 @@
         <v>1437</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1821.5</v>
+        <v>1825.7</v>
       </c>
       <c r="F4" t="n">
-        <v>6.4146</v>
+        <v>6.1267</v>
       </c>
       <c r="G4" t="n">
-        <v>114.74</v>
+        <v>115.45</v>
       </c>
       <c r="H4" t="n">
-        <v>103.88</v>
+        <v>104.42</v>
       </c>
       <c r="I4" t="n">
-        <v>10.87</v>
+        <v>11.03</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3148</v>
+        <v>0.3111</v>
       </c>
       <c r="K4" t="n">
-        <v>0.141</v>
+        <v>0.1421</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2</v>
+        <v>-0.2</v>
       </c>
       <c r="M4" t="n">
         <v>34</v>
@@ -10337,7 +10337,7 @@
         <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>1645.7</v>
+        <v>1644.1</v>
       </c>
     </row>
     <row r="5">
@@ -10475,31 +10475,31 @@
         <v>1177</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1587.5</v>
+        <v>1577.8</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7347</v>
+        <v>5.5995</v>
       </c>
       <c r="G7" t="n">
-        <v>104.54</v>
+        <v>104.5</v>
       </c>
       <c r="H7" t="n">
-        <v>103.2</v>
+        <v>103.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2937</v>
+        <v>0.3029</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1724</v>
+        <v>0.1707</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>-4</v>
       </c>
       <c r="M7" t="n">
         <v>95</v>
@@ -10520,7 +10520,7 @@
         <v>97</v>
       </c>
       <c r="S7" t="n">
-        <v>1608.9</v>
+        <v>1606.7</v>
       </c>
     </row>
     <row r="8">
@@ -10529,59 +10529,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1344</v>
+        <v>1266</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1570.2</v>
+        <v>1544.3</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9346</v>
+        <v>-6.9692</v>
       </c>
       <c r="G8" t="n">
-        <v>114.76</v>
+        <v>104.74</v>
       </c>
       <c r="H8" t="n">
-        <v>112.81</v>
+        <v>105.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.94</v>
+        <v>-0.37</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2627</v>
+        <v>0.2957</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1612</v>
+        <v>0.1591</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2</v>
+        <v>5.4</v>
       </c>
       <c r="M8" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="P8" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="Q8" t="n">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="R8" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="S8" t="n">
-        <v>1639.9</v>
+        <v>1680.7</v>
       </c>
     </row>
     <row r="9">
@@ -10597,31 +10597,31 @@
         <v>1139</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1616.6</v>
+        <v>1626.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0682</v>
+        <v>0.8502</v>
       </c>
       <c r="G9" t="n">
-        <v>110.53</v>
+        <v>110.93</v>
       </c>
       <c r="H9" t="n">
-        <v>108.8</v>
+        <v>108.36</v>
       </c>
       <c r="I9" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3033</v>
+        <v>0.308</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1524</v>
+        <v>0.1547</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.8</v>
+        <v>-1.4</v>
       </c>
       <c r="M9" t="n">
         <v>83</v>
@@ -10642,7 +10642,7 @@
         <v>80</v>
       </c>
       <c r="S9" t="n">
-        <v>1624.9</v>
+        <v>1622.8</v>
       </c>
     </row>
     <row r="10">
@@ -10651,59 +10651,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1462</v>
+        <v>1344</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1595.9</v>
+        <v>1563.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7714</v>
+        <v>1.8938</v>
       </c>
       <c r="G10" t="n">
-        <v>108.69</v>
+        <v>115.02</v>
       </c>
       <c r="H10" t="n">
-        <v>110.81</v>
+        <v>112.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.13</v>
+        <v>2.27</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2695</v>
+        <v>0.266</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1378</v>
+        <v>0.1661</v>
       </c>
       <c r="L10" t="n">
-        <v>-4</v>
+        <v>-1.4</v>
       </c>
       <c r="M10" t="n">
+        <v>63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>76</v>
+      </c>
+      <c r="O10" t="n">
+        <v>60</v>
+      </c>
+      <c r="P10" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q10" t="n">
         <v>93</v>
       </c>
-      <c r="N10" t="n">
-        <v>75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>94</v>
-      </c>
-      <c r="P10" t="n">
-        <v>91</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>97</v>
-      </c>
       <c r="R10" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="S10" t="n">
-        <v>1631</v>
+        <v>1637.8</v>
       </c>
     </row>
     <row r="11">
@@ -10712,59 +10712,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1266</v>
+        <v>1462</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1515.7</v>
+        <v>1591.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.4748</v>
+        <v>-2.8435</v>
       </c>
       <c r="G11" t="n">
-        <v>104.9</v>
+        <v>108.76</v>
       </c>
       <c r="H11" t="n">
-        <v>105.24</v>
+        <v>111.44</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.35</v>
+        <v>-2.69</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2997</v>
+        <v>0.2684</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1579</v>
+        <v>0.1355</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>-6</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="N11" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O11" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P11" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q11" t="n">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="R11" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="S11" t="n">
-        <v>1659.8</v>
+        <v>1639.3</v>
       </c>
     </row>
     <row r="12">
@@ -10780,31 +10780,31 @@
         <v>1207</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1551.2</v>
+        <v>1558.3</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0089</v>
+        <v>-4.9029</v>
       </c>
       <c r="G12" t="n">
-        <v>109.71</v>
+        <v>109.84</v>
       </c>
       <c r="H12" t="n">
-        <v>109.01</v>
+        <v>109.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3048</v>
+        <v>0.3014</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1487</v>
+        <v>0.1488</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.8</v>
+        <v>-5.8</v>
       </c>
       <c r="M12" t="n">
         <v>90</v>
@@ -10825,7 +10825,7 @@
         <v>99</v>
       </c>
       <c r="S12" t="n">
-        <v>1646.4</v>
+        <v>1640.1</v>
       </c>
     </row>
   </sheetData>
@@ -10952,31 +10952,31 @@
         <v>1219</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>1618</v>
+        <v>1620.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2011</v>
+        <v>-1.0234</v>
       </c>
       <c r="G2" t="n">
-        <v>121.43</v>
+        <v>121.05</v>
       </c>
       <c r="H2" t="n">
-        <v>99.78</v>
+        <v>100.19</v>
       </c>
       <c r="I2" t="n">
-        <v>21.65</v>
+        <v>20.86</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3136</v>
+        <v>0.3114</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1281</v>
+        <v>0.128</v>
       </c>
       <c r="L2" t="n">
-        <v>16.2</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>91</v>
@@ -10997,7 +10997,7 @@
         <v>76</v>
       </c>
       <c r="S2" t="n">
-        <v>1375.9</v>
+        <v>1377.7</v>
       </c>
     </row>
     <row r="3">
@@ -11013,31 +11013,31 @@
         <v>1457</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1494.9</v>
+        <v>1493.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7613</v>
+        <v>1.7807</v>
       </c>
       <c r="G3" t="n">
-        <v>113.46</v>
+        <v>113.16</v>
       </c>
       <c r="H3" t="n">
-        <v>107.15</v>
+        <v>107</v>
       </c>
       <c r="I3" t="n">
-        <v>6.32</v>
+        <v>6.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3148</v>
+        <v>0.313</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1389</v>
+        <v>0.1421</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>141</v>
@@ -11058,7 +11058,7 @@
         <v>129</v>
       </c>
       <c r="S3" t="n">
-        <v>1430.2</v>
+        <v>1427.2</v>
       </c>
     </row>
     <row r="4">
@@ -11135,31 +11135,31 @@
         <v>1421</v>
       </c>
       <c r="D5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1383.4</v>
+        <v>1380.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0778</v>
+        <v>-3.8502</v>
       </c>
       <c r="G5" t="n">
-        <v>106.7</v>
+        <v>106.65</v>
       </c>
       <c r="H5" t="n">
-        <v>109.86</v>
+        <v>110.02</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.16</v>
+        <v>-3.37</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2837</v>
+        <v>0.2855</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1605</v>
+        <v>0.1613</v>
       </c>
       <c r="L5" t="n">
-        <v>-6.6</v>
+        <v>-2.2</v>
       </c>
       <c r="M5" t="n">
         <v>253</v>
@@ -11180,7 +11180,7 @@
         <v>242</v>
       </c>
       <c r="S5" t="n">
-        <v>1419.1</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="6">
@@ -11257,31 +11257,31 @@
         <v>1342</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1333.2</v>
+        <v>1331.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.8899</v>
       </c>
       <c r="G7" t="n">
-        <v>105.31</v>
+        <v>105.19</v>
       </c>
       <c r="H7" t="n">
-        <v>109.56</v>
+        <v>109.54</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.25</v>
+        <v>-4.35</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3092</v>
+        <v>0.3059</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1832</v>
+        <v>0.1843</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="M7" t="n">
         <v>278</v>
@@ -11302,7 +11302,7 @@
         <v>266</v>
       </c>
       <c r="S7" t="n">
-        <v>1408</v>
+        <v>1412.3</v>
       </c>
     </row>
     <row r="8">
@@ -11321,7 +11321,7 @@
         <v>123</v>
       </c>
       <c r="E8" t="n">
-        <v>1319.9</v>
+        <v>1322.9</v>
       </c>
       <c r="F8" t="n">
         <v>0.9741</v>
@@ -11849,59 +11849,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1345</v>
+        <v>1458</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1978.1</v>
+        <v>1859.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7736</v>
+        <v>1.6302</v>
       </c>
       <c r="G6" t="n">
-        <v>123.88</v>
+        <v>119.64</v>
       </c>
       <c r="H6" t="n">
-        <v>105.93</v>
+        <v>108.42</v>
       </c>
       <c r="I6" t="n">
-        <v>17.95</v>
+        <v>11.21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2977</v>
+        <v>0.276</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1374</v>
+        <v>0.1244</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4</v>
+        <v>10.6</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="S6" t="n">
-        <v>1741</v>
+        <v>1701.3</v>
       </c>
     </row>
     <row r="7">
@@ -11910,59 +11910,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1458</v>
+        <v>1417</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1837</v>
+        <v>1859.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4688</v>
+        <v>2.2498</v>
       </c>
       <c r="G7" t="n">
-        <v>118.38</v>
+        <v>117.64</v>
       </c>
       <c r="H7" t="n">
-        <v>106.47</v>
+        <v>107.04</v>
       </c>
       <c r="I7" t="n">
-        <v>11.91</v>
+        <v>10.59</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2733</v>
+        <v>0.2985</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1236</v>
+        <v>0.1288</v>
       </c>
       <c r="L7" t="n">
-        <v>6.4</v>
+        <v>11.2</v>
       </c>
       <c r="M7" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="P7" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R7" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
-        <v>1688.3</v>
+        <v>1689.3</v>
       </c>
     </row>
     <row r="8">
@@ -11971,59 +11971,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1417</v>
+        <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1845.8</v>
+        <v>1955.6</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0997</v>
+        <v>0.3963</v>
       </c>
       <c r="G8" t="n">
-        <v>116.51</v>
+        <v>124.64</v>
       </c>
       <c r="H8" t="n">
-        <v>106.69</v>
+        <v>107.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9.82</v>
+        <v>17.04</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2986</v>
+        <v>0.3051</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1302</v>
+        <v>0.1348</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="O8" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="S8" t="n">
-        <v>1689.8</v>
+        <v>1746.9</v>
       </c>
     </row>
     <row r="9">
@@ -12039,31 +12039,31 @@
         <v>1326</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1789.2</v>
+        <v>1799.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4042</v>
+        <v>1.5472</v>
       </c>
       <c r="G9" t="n">
-        <v>118.28</v>
+        <v>118.74</v>
       </c>
       <c r="H9" t="n">
-        <v>107.42</v>
+        <v>107.91</v>
       </c>
       <c r="I9" t="n">
-        <v>10.87</v>
+        <v>10.83</v>
       </c>
       <c r="J9" t="n">
-        <v>0.255</v>
+        <v>0.2524</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1501</v>
+        <v>0.1503</v>
       </c>
       <c r="L9" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
         <v>35</v>
@@ -12084,7 +12084,7 @@
         <v>34</v>
       </c>
       <c r="S9" t="n">
-        <v>1696.1</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="10">
@@ -12161,31 +12161,31 @@
         <v>1231</v>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1752.6</v>
+        <v>1741.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4765</v>
+        <v>-2.3683</v>
       </c>
       <c r="G11" t="n">
-        <v>116.39</v>
+        <v>116.27</v>
       </c>
       <c r="H11" t="n">
-        <v>106.14</v>
+        <v>107.64</v>
       </c>
       <c r="I11" t="n">
-        <v>10.26</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.234</v>
+        <v>0.2347</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1415</v>
+        <v>0.1428</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.2</v>
+        <v>-5.8</v>
       </c>
       <c r="M11" t="n">
         <v>43</v>
@@ -12206,7 +12206,7 @@
         <v>41</v>
       </c>
       <c r="S11" t="n">
-        <v>1696.5</v>
+        <v>1701.1</v>
       </c>
     </row>
     <row r="12">
@@ -12215,59 +12215,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1449</v>
+        <v>1278</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1655.8</v>
+        <v>1624.1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1181</v>
+        <v>0.236</v>
       </c>
       <c r="G12" t="n">
-        <v>111.56</v>
+        <v>110.8</v>
       </c>
       <c r="H12" t="n">
-        <v>105.96</v>
+        <v>108.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.61</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3009</v>
+        <v>0.2481</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1501</v>
+        <v>0.1582</v>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>-3</v>
       </c>
       <c r="M12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="O12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="Q12" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="R12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="S12" t="n">
-        <v>1691.3</v>
+        <v>1674.6</v>
       </c>
     </row>
     <row r="13">
@@ -12276,59 +12276,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1425</v>
+        <v>1449</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>1756.3</v>
+        <v>1645.7</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6277</v>
+        <v>2.0254</v>
       </c>
       <c r="G13" t="n">
-        <v>107.92</v>
+        <v>111.97</v>
       </c>
       <c r="H13" t="n">
-        <v>108.19</v>
+        <v>107.18</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.27</v>
+        <v>4.78</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2952</v>
+        <v>0.2998</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1712</v>
+        <v>0.1497</v>
       </c>
       <c r="L13" t="n">
-        <v>-18</v>
+        <v>-0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O13" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="R13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="S13" t="n">
-        <v>1685.7</v>
+        <v>1686.4</v>
       </c>
     </row>
     <row r="14">
@@ -12337,59 +12337,59 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1278</v>
+        <v>1425</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>1616.9</v>
+        <v>1743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1361</v>
+        <v>1.0281</v>
       </c>
       <c r="G14" t="n">
-        <v>109.88</v>
+        <v>108.15</v>
       </c>
       <c r="H14" t="n">
-        <v>108.2</v>
+        <v>109.62</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>-1.46</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2483</v>
+        <v>0.2937</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1566</v>
+        <v>0.1679</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>-15</v>
       </c>
       <c r="M14" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N14" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="O14" t="n">
+        <v>82</v>
+      </c>
+      <c r="P14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>52</v>
+      </c>
+      <c r="R14" t="n">
         <v>63</v>
       </c>
-      <c r="P14" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>96</v>
-      </c>
-      <c r="R14" t="n">
-        <v>68</v>
-      </c>
       <c r="S14" t="n">
-        <v>1679.2</v>
+        <v>1693.6</v>
       </c>
     </row>
     <row r="15">
@@ -12466,31 +12466,31 @@
         <v>1321</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E16" t="n">
-        <v>1592.4</v>
+        <v>1585.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.7578</v>
+        <v>-4.3422</v>
       </c>
       <c r="G16" t="n">
-        <v>110.63</v>
+        <v>111</v>
       </c>
       <c r="H16" t="n">
-        <v>109.75</v>
+        <v>110.17</v>
       </c>
       <c r="I16" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2719</v>
+        <v>0.28</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1268</v>
+        <v>0.1277</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.8</v>
+        <v>0.8</v>
       </c>
       <c r="M16" t="n">
         <v>68</v>
@@ -12511,7 +12511,7 @@
         <v>72</v>
       </c>
       <c r="S16" t="n">
-        <v>1706.7</v>
+        <v>1700.2</v>
       </c>
     </row>
     <row r="17">
@@ -12527,31 +12527,31 @@
         <v>1332</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E17" t="n">
-        <v>1593.2</v>
+        <v>1603.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.597300000000001</v>
+        <v>-9.083399999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>104.34</v>
+        <v>105.7</v>
       </c>
       <c r="H17" t="n">
-        <v>110.1</v>
+        <v>110.42</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.77</v>
+        <v>-4.72</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3119</v>
+        <v>0.3115</v>
       </c>
       <c r="K17" t="n">
-        <v>0.172</v>
+        <v>0.1704</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.8</v>
+        <v>-1.2</v>
       </c>
       <c r="M17" t="n">
         <v>98</v>
@@ -12572,7 +12572,7 @@
         <v>107</v>
       </c>
       <c r="S17" t="n">
-        <v>1738.3</v>
+        <v>1731.6</v>
       </c>
     </row>
     <row r="18">
@@ -13065,31 +13065,31 @@
         <v>1180</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1420.9</v>
+        <v>1423.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0564</v>
+        <v>0.0412</v>
       </c>
       <c r="G6" t="n">
-        <v>103.41</v>
+        <v>104.38</v>
       </c>
       <c r="H6" t="n">
-        <v>103.55</v>
+        <v>103.89</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.15</v>
+        <v>0.49</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2868</v>
+        <v>0.2871</v>
       </c>
       <c r="K6" t="n">
-        <v>0.18</v>
+        <v>0.1804</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
         <v>220</v>
@@ -13110,7 +13110,7 @@
         <v>211</v>
       </c>
       <c r="S6" t="n">
-        <v>1439.6</v>
+        <v>1435.1</v>
       </c>
     </row>
     <row r="7">
@@ -13126,31 +13126,31 @@
         <v>1456</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1525.9</v>
+        <v>1530.8</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8777</v>
+        <v>2.6755</v>
       </c>
       <c r="G7" t="n">
-        <v>112.99</v>
+        <v>112.39</v>
       </c>
       <c r="H7" t="n">
-        <v>107.55</v>
+        <v>106.61</v>
       </c>
       <c r="I7" t="n">
-        <v>5.44</v>
+        <v>5.78</v>
       </c>
       <c r="J7" t="n">
-        <v>0.233</v>
+        <v>0.2357</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1619</v>
+        <v>0.1618</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="M7" t="n">
         <v>133</v>
@@ -13171,7 +13171,7 @@
         <v>124</v>
       </c>
       <c r="S7" t="n">
-        <v>1462.6</v>
+        <v>1464.2</v>
       </c>
     </row>
     <row r="8">
@@ -13187,31 +13187,31 @@
         <v>1406</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1546.2</v>
+        <v>1548.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9255</v>
+        <v>-2.8635</v>
       </c>
       <c r="G8" t="n">
-        <v>102.64</v>
+        <v>102.84</v>
       </c>
       <c r="H8" t="n">
-        <v>102.78</v>
+        <v>102.8</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.13</v>
+        <v>0.04</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3347</v>
+        <v>0.3319</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1517</v>
+        <v>0.1529</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
         <v>177</v>
@@ -13232,7 +13232,7 @@
         <v>180</v>
       </c>
       <c r="S8" t="n">
-        <v>1527.1</v>
+        <v>1520.2</v>
       </c>
     </row>
     <row r="9">
@@ -13248,31 +13248,31 @@
         <v>1392</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1447.1</v>
+        <v>1443</v>
       </c>
       <c r="F9" t="n">
-        <v>3.303</v>
+        <v>3.1388</v>
       </c>
       <c r="G9" t="n">
-        <v>102.98</v>
+        <v>104.12</v>
       </c>
       <c r="H9" t="n">
-        <v>105.86</v>
+        <v>107.14</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.87</v>
+        <v>-3.02</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2665</v>
+        <v>0.2683</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1555</v>
+        <v>0.1568</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.8</v>
+        <v>-6.8</v>
       </c>
       <c r="M9" t="n">
         <v>222</v>
@@ -13293,7 +13293,7 @@
         <v>219</v>
       </c>
       <c r="S9" t="n">
-        <v>1463.7</v>
+        <v>1459.9</v>
       </c>
     </row>
     <row r="10">
@@ -13309,31 +13309,31 @@
         <v>1144</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1389.5</v>
+        <v>1393.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1605</v>
+        <v>0.154</v>
       </c>
       <c r="G10" t="n">
-        <v>108.08</v>
+        <v>108.93</v>
       </c>
       <c r="H10" t="n">
-        <v>112.67</v>
+        <v>113.24</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.59</v>
+        <v>-4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3356</v>
+        <v>0.3392</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1612</v>
+        <v>0.1599</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
         <v>192</v>
@@ -13354,7 +13354,7 @@
         <v>208</v>
       </c>
       <c r="S10" t="n">
-        <v>1516.7</v>
+        <v>1515.7</v>
       </c>
     </row>
     <row r="11">
@@ -13370,31 +13370,31 @@
         <v>1214</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1350.9</v>
+        <v>1348.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3858</v>
+        <v>0.3488</v>
       </c>
       <c r="G11" t="n">
-        <v>101.86</v>
+        <v>101.66</v>
       </c>
       <c r="H11" t="n">
-        <v>108.23</v>
+        <v>108.07</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.37</v>
+        <v>-6.42</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3199</v>
+        <v>0.3246</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1566</v>
+        <v>0.1569</v>
       </c>
       <c r="L11" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="M11" t="n">
         <v>273</v>
@@ -13415,7 +13415,7 @@
         <v>268</v>
       </c>
       <c r="S11" t="n">
-        <v>1451.2</v>
+        <v>1454.5</v>
       </c>
     </row>
     <row r="12">
@@ -13431,31 +13431,31 @@
         <v>1189</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>1464.6</v>
+        <v>1459.8</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8972</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>111.77</v>
+        <v>111.23</v>
       </c>
       <c r="H12" t="n">
-        <v>115.04</v>
+        <v>114.76</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.27</v>
+        <v>-3.53</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3229</v>
+        <v>0.3239</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1512</v>
+        <v>0.1564</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.8</v>
+        <v>-13.4</v>
       </c>
       <c r="M12" t="n">
         <v>219</v>
@@ -13476,7 +13476,7 @@
         <v>210</v>
       </c>
       <c r="S12" t="n">
-        <v>1489.3</v>
+        <v>1489.2</v>
       </c>
     </row>
     <row r="13">
@@ -13553,31 +13553,31 @@
         <v>1318</v>
       </c>
       <c r="D14" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>1362.3</v>
+        <v>1360</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.5491</v>
+        <v>-3.4993</v>
       </c>
       <c r="G14" t="n">
-        <v>106.52</v>
+        <v>106.61</v>
       </c>
       <c r="H14" t="n">
-        <v>114.9</v>
+        <v>115.4</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.28</v>
+        <v>0.2853</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1592</v>
+        <v>0.1564</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.4</v>
+        <v>-3</v>
       </c>
       <c r="M14" t="n">
         <v>288</v>
@@ -13598,7 +13598,7 @@
         <v>288</v>
       </c>
       <c r="S14" t="n">
-        <v>1477.6</v>
+        <v>1476.8</v>
       </c>
     </row>
   </sheetData>
@@ -13725,31 +13725,31 @@
         <v>1251</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>1729</v>
+        <v>1733.1</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4996</v>
+        <v>3.2041</v>
       </c>
       <c r="G2" t="n">
-        <v>117.41</v>
+        <v>117.83</v>
       </c>
       <c r="H2" t="n">
-        <v>110.66</v>
+        <v>110.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6.75</v>
+        <v>7.08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1701</v>
+        <v>0.1699</v>
       </c>
       <c r="K2" t="n">
         <v>0.1316</v>
       </c>
       <c r="L2" t="n">
-        <v>-6.2</v>
+        <v>-5</v>
       </c>
       <c r="M2" t="n">
         <v>111</v>
@@ -13770,7 +13770,7 @@
         <v>94</v>
       </c>
       <c r="S2" t="n">
-        <v>1482.9</v>
+        <v>1485.6</v>
       </c>
     </row>
     <row r="3">
@@ -13786,31 +13786,31 @@
         <v>1358</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1544.3</v>
+        <v>1540.1</v>
       </c>
       <c r="F3" t="n">
-        <v>4.758</v>
+        <v>4.6115</v>
       </c>
       <c r="G3" t="n">
-        <v>113.42</v>
+        <v>113.61</v>
       </c>
       <c r="H3" t="n">
-        <v>106.57</v>
+        <v>107.46</v>
       </c>
       <c r="I3" t="n">
-        <v>6.86</v>
+        <v>6.14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3054</v>
+        <v>0.3092</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1609</v>
+        <v>0.1597</v>
       </c>
       <c r="L3" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>103</v>
@@ -13831,7 +13831,7 @@
         <v>96</v>
       </c>
       <c r="S3" t="n">
-        <v>1491.4</v>
+        <v>1503.4</v>
       </c>
     </row>
     <row r="4">
@@ -13847,31 +13847,31 @@
         <v>1443</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>1487.9</v>
+        <v>1483.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.5819</v>
+        <v>-3.316</v>
       </c>
       <c r="G4" t="n">
-        <v>108.56</v>
+        <v>107.79</v>
       </c>
       <c r="H4" t="n">
-        <v>105.71</v>
+        <v>106.34</v>
       </c>
       <c r="I4" t="n">
-        <v>2.85</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3082</v>
+        <v>0.3081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1356</v>
+        <v>0.1373</v>
       </c>
       <c r="L4" t="n">
-        <v>12.8</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
         <v>138</v>
@@ -13892,7 +13892,7 @@
         <v>133</v>
       </c>
       <c r="S4" t="n">
-        <v>1486.4</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="5">
@@ -13908,31 +13908,31 @@
         <v>1292</v>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1485.8</v>
+        <v>1489.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.0291</v>
+        <v>-3.8936</v>
       </c>
       <c r="G5" t="n">
-        <v>107.77</v>
+        <v>107.97</v>
       </c>
       <c r="H5" t="n">
-        <v>109.25</v>
+        <v>108.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.48</v>
+        <v>-0.71</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2864</v>
+        <v>0.2792</v>
       </c>
       <c r="K5" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>180</v>
@@ -13953,7 +13953,7 @@
         <v>161</v>
       </c>
       <c r="S5" t="n">
-        <v>1528.1</v>
+        <v>1523.7</v>
       </c>
     </row>
     <row r="6">
@@ -13969,31 +13969,31 @@
         <v>1244</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1507.3</v>
+        <v>1501.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4075</v>
+        <v>-0.3344</v>
       </c>
       <c r="G6" t="n">
-        <v>110.23</v>
+        <v>110.51</v>
       </c>
       <c r="H6" t="n">
-        <v>108.23</v>
+        <v>108.69</v>
       </c>
       <c r="I6" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="J6" t="n">
-        <v>0.334</v>
+        <v>0.3343</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1655</v>
+        <v>0.1639</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>170</v>
@@ -14014,7 +14014,7 @@
         <v>160</v>
       </c>
       <c r="S6" t="n">
-        <v>1469.7</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="7">
@@ -14030,31 +14030,31 @@
         <v>1256</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1502.7</v>
+        <v>1506</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0079</v>
+        <v>-1.7753</v>
       </c>
       <c r="G7" t="n">
-        <v>101.77</v>
+        <v>102.77</v>
       </c>
       <c r="H7" t="n">
-        <v>104.39</v>
+        <v>102.38</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.62</v>
+        <v>0.39</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3308</v>
+        <v>0.3278</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1764</v>
+        <v>0.176</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>7.8</v>
       </c>
       <c r="M7" t="n">
         <v>246</v>
@@ -14075,7 +14075,7 @@
         <v>248</v>
       </c>
       <c r="S7" t="n">
-        <v>1470.5</v>
+        <v>1464.3</v>
       </c>
     </row>
     <row r="8">
@@ -14091,31 +14091,31 @@
         <v>1240</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" t="n">
-        <v>1459.1</v>
+        <v>1462.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0599</v>
+        <v>-0.0476</v>
       </c>
       <c r="G8" t="n">
-        <v>106.71</v>
+        <v>106.29</v>
       </c>
       <c r="H8" t="n">
-        <v>107.51</v>
+        <v>106.84</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8</v>
+        <v>-0.55</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2818</v>
+        <v>0.2799</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1568</v>
+        <v>0.16</v>
       </c>
       <c r="L8" t="n">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
         <v>205</v>
@@ -14136,7 +14136,7 @@
         <v>214</v>
       </c>
       <c r="S8" t="n">
-        <v>1469.2</v>
+        <v>1466.3</v>
       </c>
     </row>
     <row r="9">
@@ -14152,31 +14152,31 @@
         <v>1283</v>
       </c>
       <c r="D9" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1398.8</v>
+        <v>1395</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4406</v>
+        <v>1.3277</v>
       </c>
       <c r="G9" t="n">
-        <v>108.1</v>
+        <v>107.51</v>
       </c>
       <c r="H9" t="n">
-        <v>109.45</v>
+        <v>109.72</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.35</v>
+        <v>-2.21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3227</v>
+        <v>0.3194</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1613</v>
+        <v>0.1608</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="M9" t="n">
         <v>212</v>
@@ -14197,7 +14197,7 @@
         <v>218</v>
       </c>
       <c r="S9" t="n">
-        <v>1474.3</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="10">
@@ -14213,31 +14213,31 @@
         <v>1198</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1380.8</v>
+        <v>1385.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3979</v>
+        <v>1.345</v>
       </c>
       <c r="G10" t="n">
-        <v>106.61</v>
+        <v>107.53</v>
       </c>
       <c r="H10" t="n">
-        <v>109.43</v>
+        <v>108.75</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.82</v>
+        <v>-1.22</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3246</v>
+        <v>0.3239</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1739</v>
+        <v>0.1733</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.8</v>
+        <v>-0.6</v>
       </c>
       <c r="M10" t="n">
         <v>198</v>
@@ -14258,7 +14258,7 @@
         <v>200</v>
       </c>
       <c r="S10" t="n">
-        <v>1494.4</v>
+        <v>1494.2</v>
       </c>
     </row>
     <row r="11">
@@ -14274,31 +14274,31 @@
         <v>1308</v>
       </c>
       <c r="D11" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
-        <v>1456</v>
+        <v>1461.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.1896</v>
+        <v>-7.7933</v>
       </c>
       <c r="G11" t="n">
-        <v>108.64</v>
+        <v>109.22</v>
       </c>
       <c r="H11" t="n">
-        <v>108.29</v>
+        <v>108.7</v>
       </c>
       <c r="I11" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3043</v>
+        <v>0.3089</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1412</v>
+        <v>0.1419</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8</v>
+        <v>-3</v>
       </c>
       <c r="M11" t="n">
         <v>181</v>
@@ -14319,7 +14319,7 @@
         <v>186</v>
       </c>
       <c r="S11" t="n">
-        <v>1487.2</v>
+        <v>1488.4</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -14686,59 +14686,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Chr</t>
+          <t>Northwestern LA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1223</v>
+        <v>1322</v>
       </c>
       <c r="D8" t="n">
         <v>119</v>
       </c>
       <c r="E8" t="n">
-        <v>1276.5</v>
+        <v>1288.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8273</v>
+        <v>-1.681</v>
       </c>
       <c r="G8" t="n">
-        <v>103.46</v>
+        <v>102.39</v>
       </c>
       <c r="H8" t="n">
-        <v>112.17</v>
+        <v>112.41</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.710000000000001</v>
+        <v>-10.02</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3045</v>
+        <v>0.2622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1803</v>
+        <v>0.1709</v>
       </c>
       <c r="L8" t="n">
         <v>-2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="N8" t="n">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="O8" t="n">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="P8" t="n">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="Q8" t="n">
+        <v>292</v>
+      </c>
+      <c r="R8" t="n">
         <v>294</v>
       </c>
-      <c r="R8" t="n">
-        <v>301</v>
-      </c>
       <c r="S8" t="n">
-        <v>1424.2</v>
+        <v>1441.7</v>
       </c>
     </row>
     <row r="9">
@@ -14747,59 +14747,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northwestern LA</t>
+          <t>Houston Chr</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1322</v>
+        <v>1223</v>
       </c>
       <c r="D9" t="n">
         <v>119</v>
       </c>
       <c r="E9" t="n">
-        <v>1288.1</v>
+        <v>1276.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.681</v>
+        <v>-0.8273</v>
       </c>
       <c r="G9" t="n">
-        <v>102.39</v>
+        <v>103.46</v>
       </c>
       <c r="H9" t="n">
-        <v>112.41</v>
+        <v>112.17</v>
       </c>
       <c r="I9" t="n">
-        <v>-10.02</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2622</v>
+        <v>0.3045</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1709</v>
+        <v>0.1803</v>
       </c>
       <c r="L9" t="n">
         <v>-2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="N9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="O9" t="n">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="P9" t="n">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="Q9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="R9" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="S9" t="n">
-        <v>1441.7</v>
+        <v>1424.2</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -1521,31 +1521,31 @@
         <v>1276</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>2181.2</v>
+        <v>2189.2</v>
       </c>
       <c r="F2" t="n">
-        <v>7.6139</v>
+        <v>7.2681</v>
       </c>
       <c r="G2" t="n">
-        <v>121.54</v>
+        <v>121.97</v>
       </c>
       <c r="H2" t="n">
-        <v>95.23</v>
+        <v>95.94</v>
       </c>
       <c r="I2" t="n">
-        <v>26.31</v>
+        <v>26.03</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2642</v>
+        <v>0.2632</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1678</v>
+        <v>0.1657</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1758.2</v>
+        <v>1769.7</v>
       </c>
     </row>
     <row r="3">
@@ -1582,31 +1582,31 @@
         <v>1304</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1992.1</v>
+        <v>1999.6</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5554</v>
+        <v>10.6735</v>
       </c>
       <c r="G3" t="n">
-        <v>115.07</v>
+        <v>115.4</v>
       </c>
       <c r="H3" t="n">
-        <v>98.04000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="I3" t="n">
-        <v>17.03</v>
+        <v>17.45</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2419</v>
+        <v>0.2379</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1401</v>
+        <v>0.1402</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -1627,7 +1627,7 @@
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>1659.3</v>
+        <v>1665.7</v>
       </c>
     </row>
     <row r="4">
@@ -1643,31 +1643,31 @@
         <v>1277</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>2057.8</v>
+        <v>2049.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2001</v>
+        <v>0.2376</v>
       </c>
       <c r="G4" t="n">
-        <v>117.41</v>
+        <v>117.05</v>
       </c>
       <c r="H4" t="n">
-        <v>100.06</v>
+        <v>100.92</v>
       </c>
       <c r="I4" t="n">
-        <v>17.36</v>
+        <v>16.13</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2989</v>
+        <v>0.2993</v>
       </c>
       <c r="K4" t="n">
-        <v>0.165</v>
+        <v>0.1615</v>
       </c>
       <c r="L4" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
@@ -1688,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>1707.1</v>
+        <v>1729.6</v>
       </c>
     </row>
     <row r="5">
@@ -1704,31 +1704,31 @@
         <v>1228</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>1999.8</v>
+        <v>2003.3</v>
       </c>
       <c r="F5" t="n">
-        <v>8.6837</v>
+        <v>8.2525</v>
       </c>
       <c r="G5" t="n">
-        <v>125.29</v>
+        <v>125.48</v>
       </c>
       <c r="H5" t="n">
-        <v>102.13</v>
+        <v>103.07</v>
       </c>
       <c r="I5" t="n">
-        <v>23.17</v>
+        <v>22.41</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3216</v>
+        <v>0.3238</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1296</v>
+        <v>0.1295</v>
       </c>
       <c r="L5" t="n">
-        <v>13.4</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -1749,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1712.9</v>
+        <v>1709.5</v>
       </c>
     </row>
     <row r="6">
@@ -2009,31 +2009,31 @@
         <v>1234</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10" t="n">
-        <v>1851.2</v>
+        <v>1843.7</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4379</v>
+        <v>4.0673</v>
       </c>
       <c r="G10" t="n">
-        <v>119.28</v>
+        <v>118.63</v>
       </c>
       <c r="H10" t="n">
-        <v>103.76</v>
+        <v>104.06</v>
       </c>
       <c r="I10" t="n">
-        <v>15.52</v>
+        <v>14.56</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2925</v>
+        <v>0.288</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1388</v>
+        <v>0.1446</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>-2</v>
       </c>
       <c r="M10" t="n">
         <v>24</v>
@@ -2054,7 +2054,7 @@
         <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1708.5</v>
+        <v>1715.1</v>
       </c>
     </row>
     <row r="11">
@@ -2314,31 +2314,31 @@
         <v>1353</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
-        <v>1551.6</v>
+        <v>1557.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1062</v>
+        <v>-2.9475</v>
       </c>
       <c r="G15" t="n">
-        <v>104.86</v>
+        <v>104.8</v>
       </c>
       <c r="H15" t="n">
-        <v>112.84</v>
+        <v>111.67</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.98</v>
+        <v>-6.86</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3247</v>
+        <v>0.318</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1469</v>
+        <v>0.1454</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="M15" t="n">
         <v>144</v>
@@ -2359,7 +2359,7 @@
         <v>158</v>
       </c>
       <c r="S15" t="n">
-        <v>1697.1</v>
+        <v>1684.5</v>
       </c>
     </row>
     <row r="16">
@@ -2497,31 +2497,31 @@
         <v>1268</v>
       </c>
       <c r="D18" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E18" t="n">
-        <v>1601.6</v>
+        <v>1598.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.364800000000001</v>
+        <v>-8.074299999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>102.77</v>
+        <v>103.93</v>
       </c>
       <c r="H18" t="n">
-        <v>114.81</v>
+        <v>115.23</v>
       </c>
       <c r="I18" t="n">
-        <v>-12.04</v>
+        <v>-11.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3181</v>
+        <v>0.3204</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1773</v>
+        <v>0.1754</v>
       </c>
       <c r="L18" t="n">
-        <v>-10</v>
+        <v>-10.4</v>
       </c>
       <c r="M18" t="n">
         <v>130</v>
@@ -2542,7 +2542,7 @@
         <v>146</v>
       </c>
       <c r="S18" t="n">
-        <v>1713.6</v>
+        <v>1724.9</v>
       </c>
     </row>
     <row r="19">
@@ -2558,31 +2558,31 @@
         <v>1336</v>
       </c>
       <c r="D19" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E19" t="n">
-        <v>1532.8</v>
+        <v>1526.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.5578</v>
+        <v>-7.224</v>
       </c>
       <c r="G19" t="n">
-        <v>110.14</v>
+        <v>109.42</v>
       </c>
       <c r="H19" t="n">
-        <v>118.59</v>
+        <v>117.68</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.44</v>
+        <v>-8.26</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2617</v>
+        <v>0.2614</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1492</v>
+        <v>0.1489</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.4</v>
+        <v>-15.6</v>
       </c>
       <c r="M19" t="n">
         <v>128</v>
@@ -2603,7 +2603,7 @@
         <v>125</v>
       </c>
       <c r="S19" t="n">
-        <v>1671.8</v>
+        <v>1664.7</v>
       </c>
     </row>
   </sheetData>
@@ -3329,31 +3329,31 @@
         <v>1423</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1681</v>
+        <v>1669.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0383</v>
+        <v>1.9449</v>
       </c>
       <c r="G2" t="n">
-        <v>115.35</v>
+        <v>114.72</v>
       </c>
       <c r="H2" t="n">
-        <v>102.31</v>
+        <v>103.36</v>
       </c>
       <c r="I2" t="n">
-        <v>13.04</v>
+        <v>11.37</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3159</v>
+        <v>0.313</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1414</v>
+        <v>0.1394</v>
       </c>
       <c r="L2" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="M2" t="n">
         <v>104</v>
@@ -3374,7 +3374,7 @@
         <v>93</v>
       </c>
       <c r="S2" t="n">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="3">
@@ -3390,31 +3390,31 @@
         <v>1158</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1578.3</v>
+        <v>1569.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6342</v>
+        <v>1.7549</v>
       </c>
       <c r="G3" t="n">
-        <v>109.21</v>
+        <v>108.39</v>
       </c>
       <c r="H3" t="n">
-        <v>105.84</v>
+        <v>107</v>
       </c>
       <c r="I3" t="n">
-        <v>3.37</v>
+        <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2563</v>
+        <v>0.2607</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1533</v>
+        <v>0.154</v>
       </c>
       <c r="L3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
         <v>147</v>
@@ -3435,7 +3435,7 @@
         <v>145</v>
       </c>
       <c r="S3" t="n">
-        <v>1482.2</v>
+        <v>1482.5</v>
       </c>
     </row>
     <row r="4">
@@ -3451,31 +3451,31 @@
         <v>1220</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1567.8</v>
+        <v>1574.5</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0005</v>
+        <v>3.7174</v>
       </c>
       <c r="G4" t="n">
-        <v>112.7</v>
+        <v>113.98</v>
       </c>
       <c r="H4" t="n">
-        <v>102.71</v>
+        <v>102.46</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>11.53</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3013</v>
+        <v>0.3039</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1549</v>
+        <v>0.1512</v>
       </c>
       <c r="L4" t="n">
-        <v>13.2</v>
+        <v>20.2</v>
       </c>
       <c r="M4" t="n">
         <v>92</v>
@@ -3496,7 +3496,7 @@
         <v>92</v>
       </c>
       <c r="S4" t="n">
-        <v>1478.9</v>
+        <v>1481.7</v>
       </c>
     </row>
     <row r="5">
@@ -3512,31 +3512,31 @@
         <v>1284</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>1443.6</v>
+        <v>1447.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1405</v>
+        <v>1.1918</v>
       </c>
       <c r="G5" t="n">
-        <v>106.98</v>
+        <v>106.48</v>
       </c>
       <c r="H5" t="n">
-        <v>105.89</v>
+        <v>105</v>
       </c>
       <c r="I5" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3102</v>
+        <v>0.3065</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1625</v>
+        <v>0.1656</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
         <v>190</v>
@@ -3557,7 +3557,7 @@
         <v>179</v>
       </c>
       <c r="S5" t="n">
-        <v>1459</v>
+        <v>1458.5</v>
       </c>
     </row>
     <row r="6">
@@ -3573,31 +3573,31 @@
         <v>1180</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1423.2</v>
+        <v>1419.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0412</v>
+        <v>0.1348</v>
       </c>
       <c r="G6" t="n">
-        <v>104.38</v>
+        <v>103.57</v>
       </c>
       <c r="H6" t="n">
-        <v>103.89</v>
+        <v>103.69</v>
       </c>
       <c r="I6" t="n">
-        <v>0.49</v>
+        <v>-0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2871</v>
+        <v>0.291</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1804</v>
+        <v>0.1824</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>-0.2</v>
       </c>
       <c r="M6" t="n">
         <v>220</v>
@@ -3618,7 +3618,7 @@
         <v>211</v>
       </c>
       <c r="S6" t="n">
-        <v>1435.1</v>
+        <v>1436.1</v>
       </c>
     </row>
     <row r="7">
@@ -3634,31 +3634,31 @@
         <v>1456</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>1530.8</v>
+        <v>1524.1</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6755</v>
+        <v>2.5272</v>
       </c>
       <c r="G7" t="n">
-        <v>112.39</v>
+        <v>111.68</v>
       </c>
       <c r="H7" t="n">
-        <v>106.61</v>
+        <v>108.49</v>
       </c>
       <c r="I7" t="n">
-        <v>5.78</v>
+        <v>3.19</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2357</v>
+        <v>0.2372</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1618</v>
+        <v>0.163</v>
       </c>
       <c r="L7" t="n">
-        <v>5.6</v>
+        <v>-0.4</v>
       </c>
       <c r="M7" t="n">
         <v>133</v>
@@ -3679,7 +3679,7 @@
         <v>124</v>
       </c>
       <c r="S7" t="n">
-        <v>1464.2</v>
+        <v>1468.9</v>
       </c>
     </row>
     <row r="8">
@@ -3695,31 +3695,31 @@
         <v>1406</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1548.4</v>
+        <v>1556.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8635</v>
+        <v>-2.7806</v>
       </c>
       <c r="G8" t="n">
-        <v>102.84</v>
+        <v>104.06</v>
       </c>
       <c r="H8" t="n">
-        <v>102.8</v>
+        <v>102.39</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04</v>
+        <v>1.67</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3319</v>
+        <v>0.3357</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1529</v>
+        <v>0.1517</v>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>177</v>
@@ -3740,7 +3740,7 @@
         <v>180</v>
       </c>
       <c r="S8" t="n">
-        <v>1520.2</v>
+        <v>1524.4</v>
       </c>
     </row>
     <row r="9">
@@ -3817,31 +3817,31 @@
         <v>1144</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" t="n">
-        <v>1393.6</v>
+        <v>1405.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.154</v>
+        <v>0.1743</v>
       </c>
       <c r="G10" t="n">
-        <v>108.93</v>
+        <v>109.09</v>
       </c>
       <c r="H10" t="n">
-        <v>113.24</v>
+        <v>112.48</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3</v>
+        <v>-3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3392</v>
+        <v>0.3406</v>
       </c>
       <c r="K10" t="n">
         <v>0.1599</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
         <v>192</v>
@@ -3862,7 +3862,7 @@
         <v>208</v>
       </c>
       <c r="S10" t="n">
-        <v>1515.7</v>
+        <v>1523.3</v>
       </c>
     </row>
     <row r="11">
@@ -5198,31 +5198,31 @@
         <v>1453</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1381.1</v>
+        <v>1378.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6336</v>
+        <v>3.5571</v>
       </c>
       <c r="G6" t="n">
-        <v>114.38</v>
+        <v>114.49</v>
       </c>
       <c r="H6" t="n">
-        <v>115.91</v>
+        <v>117.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.53</v>
+        <v>-2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2218</v>
+        <v>0.2297</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1462</v>
+        <v>0.1429</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
         <v>195</v>
@@ -5243,7 +5243,7 @@
         <v>209</v>
       </c>
       <c r="S6" t="n">
-        <v>1448.1</v>
+        <v>1447.2</v>
       </c>
     </row>
     <row r="7">
@@ -5320,31 +5320,31 @@
         <v>1297</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1436.3</v>
+        <v>1439</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2764</v>
+        <v>0.2239</v>
       </c>
       <c r="G8" t="n">
-        <v>111.93</v>
+        <v>113.32</v>
       </c>
       <c r="H8" t="n">
-        <v>108.72</v>
+        <v>108.95</v>
       </c>
       <c r="I8" t="n">
-        <v>3.21</v>
+        <v>4.37</v>
       </c>
       <c r="J8" t="n">
-        <v>0.32</v>
+        <v>0.3154</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1598</v>
+        <v>0.1594</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>178</v>
@@ -5365,7 +5365,7 @@
         <v>189</v>
       </c>
       <c r="S8" t="n">
-        <v>1430.7</v>
+        <v>1427.9</v>
       </c>
     </row>
     <row r="9">
@@ -6091,31 +6091,31 @@
         <v>1467</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1515.6</v>
+        <v>1521.4</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9427</v>
+        <v>3.9296</v>
       </c>
       <c r="G2" t="n">
-        <v>107.67</v>
+        <v>107.03</v>
       </c>
       <c r="H2" t="n">
-        <v>102.86</v>
+        <v>102.73</v>
       </c>
       <c r="I2" t="n">
-        <v>4.81</v>
+        <v>4.29</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2665</v>
+        <v>0.2687</v>
       </c>
       <c r="K2" t="n">
         <v>0.1436</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="M2" t="n">
         <v>172</v>
@@ -6136,7 +6136,7 @@
         <v>185</v>
       </c>
       <c r="S2" t="n">
-        <v>1452.7</v>
+        <v>1455.8</v>
       </c>
     </row>
     <row r="3">
@@ -6213,31 +6213,31 @@
         <v>1373</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>1471.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9509</v>
+        <v>0.9399</v>
       </c>
       <c r="G4" t="n">
-        <v>109.69</v>
+        <v>110.16</v>
       </c>
       <c r="H4" t="n">
-        <v>102.56</v>
+        <v>102.35</v>
       </c>
       <c r="I4" t="n">
-        <v>7.14</v>
+        <v>7.81</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2822</v>
+        <v>0.2799</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1527</v>
+        <v>0.1532</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>206</v>
@@ -6258,7 +6258,7 @@
         <v>194</v>
       </c>
       <c r="S4" t="n">
-        <v>1425.6</v>
+        <v>1426.7</v>
       </c>
     </row>
     <row r="5">
@@ -6335,31 +6335,31 @@
         <v>1265</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1497.5</v>
+        <v>1491.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0359</v>
+        <v>0.0074</v>
       </c>
       <c r="G6" t="n">
-        <v>104.47</v>
+        <v>103.77</v>
       </c>
       <c r="H6" t="n">
-        <v>96.89</v>
+        <v>96.52</v>
       </c>
       <c r="I6" t="n">
-        <v>7.59</v>
+        <v>7.26</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2682</v>
+        <v>0.2704</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1596</v>
+        <v>0.1654</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>201</v>
@@ -6380,7 +6380,7 @@
         <v>182</v>
       </c>
       <c r="S6" t="n">
-        <v>1420.3</v>
+        <v>1423.5</v>
       </c>
     </row>
     <row r="7">
@@ -6457,31 +6457,31 @@
         <v>1193</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1442.9</v>
+        <v>1438.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>1.624</v>
       </c>
       <c r="G8" t="n">
-        <v>107.86</v>
+        <v>107.31</v>
       </c>
       <c r="H8" t="n">
-        <v>105.35</v>
+        <v>106.13</v>
       </c>
       <c r="I8" t="n">
-        <v>2.51</v>
+        <v>1.17</v>
       </c>
       <c r="J8" t="n">
-        <v>0.347</v>
+        <v>0.3479</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1561</v>
+        <v>0.1524</v>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>270</v>
@@ -6502,7 +6502,7 @@
         <v>245</v>
       </c>
       <c r="S8" t="n">
-        <v>1403.8</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="9">
@@ -8193,31 +8193,31 @@
         <v>1227</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1535.5</v>
+        <v>1528.6</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1038</v>
+        <v>2.2588</v>
       </c>
       <c r="G6" t="n">
-        <v>108.47</v>
+        <v>108.83</v>
       </c>
       <c r="H6" t="n">
-        <v>102.47</v>
+        <v>104.27</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4.56</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3429</v>
+        <v>0.3406</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1641</v>
+        <v>0.1647</v>
       </c>
       <c r="L6" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>110</v>
@@ -8238,7 +8238,7 @@
         <v>116</v>
       </c>
       <c r="S6" t="n">
-        <v>1506.5</v>
+        <v>1508.7</v>
       </c>
     </row>
     <row r="7">
@@ -8254,31 +8254,31 @@
         <v>1320</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>1567</v>
+        <v>1573.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9617</v>
+        <v>-3.696</v>
       </c>
       <c r="G7" t="n">
-        <v>107.53</v>
+        <v>108.74</v>
       </c>
       <c r="H7" t="n">
-        <v>96.87</v>
+        <v>97.5</v>
       </c>
       <c r="I7" t="n">
-        <v>10.66</v>
+        <v>11.25</v>
       </c>
       <c r="J7" t="n">
-        <v>0.214</v>
+        <v>0.225</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1374</v>
+        <v>0.1354</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>14.4</v>
       </c>
       <c r="M7" t="n">
         <v>80</v>
@@ -8299,7 +8299,7 @@
         <v>81</v>
       </c>
       <c r="S7" t="n">
-        <v>1516</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="8">
@@ -11798,31 +11798,31 @@
         <v>1298</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1430.4</v>
+        <v>1426.7</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2549</v>
+        <v>3.2284</v>
       </c>
       <c r="G2" t="n">
-        <v>113.28</v>
+        <v>113.4</v>
       </c>
       <c r="H2" t="n">
-        <v>98.59</v>
+        <v>99.34</v>
       </c>
       <c r="I2" t="n">
-        <v>14.69</v>
+        <v>14.06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2673</v>
+        <v>0.2769</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1673</v>
+        <v>0.1624</v>
       </c>
       <c r="L2" t="n">
-        <v>17.8</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>136</v>
@@ -11843,7 +11843,7 @@
         <v>127</v>
       </c>
       <c r="S2" t="n">
-        <v>1375.2</v>
+        <v>1374.6</v>
       </c>
     </row>
     <row r="3">
@@ -11859,31 +11859,31 @@
         <v>1250</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1320.1</v>
+        <v>1323.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7048</v>
+        <v>-0.5849</v>
       </c>
       <c r="G3" t="n">
-        <v>104.37</v>
+        <v>104.76</v>
       </c>
       <c r="H3" t="n">
-        <v>108.74</v>
+        <v>108.58</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.37</v>
+        <v>-3.82</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2183</v>
+        <v>0.214</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1735</v>
+        <v>0.1729</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4</v>
+        <v>5.6</v>
       </c>
       <c r="M3" t="n">
         <v>295</v>
@@ -11904,7 +11904,7 @@
         <v>290</v>
       </c>
       <c r="S3" t="n">
-        <v>1399.1</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="4">
@@ -11920,31 +11920,31 @@
         <v>1159</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1421.8</v>
+        <v>1418.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2169</v>
+        <v>0.1631</v>
       </c>
       <c r="G4" t="n">
-        <v>111.41</v>
+        <v>110.53</v>
       </c>
       <c r="H4" t="n">
-        <v>111.99</v>
+        <v>111.79</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.58</v>
+        <v>-1.26</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2495</v>
+        <v>0.2486</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1441</v>
+        <v>0.1425</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.6</v>
+        <v>-1.6</v>
       </c>
       <c r="M4" t="n">
         <v>254</v>
@@ -11965,7 +11965,7 @@
         <v>228</v>
       </c>
       <c r="S4" t="n">
-        <v>1422</v>
+        <v>1419.5</v>
       </c>
     </row>
     <row r="5">
@@ -11981,31 +11981,31 @@
         <v>1131</v>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>1343.2</v>
+        <v>1346.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6522</v>
+        <v>-2.4681</v>
       </c>
       <c r="G5" t="n">
-        <v>115.3</v>
+        <v>115.45</v>
       </c>
       <c r="H5" t="n">
-        <v>114.06</v>
+        <v>114.22</v>
       </c>
       <c r="I5" t="n">
         <v>1.24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2381</v>
+        <v>0.2355</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1682</v>
+        <v>0.1697</v>
       </c>
       <c r="L5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
         <v>259</v>
@@ -12026,7 +12026,7 @@
         <v>265</v>
       </c>
       <c r="S5" t="n">
-        <v>1377.3</v>
+        <v>1379.2</v>
       </c>
     </row>
     <row r="6">
@@ -13606,31 +13606,31 @@
         <v>1190</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1515.6</v>
+        <v>1518.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4929</v>
       </c>
       <c r="G2" t="n">
-        <v>116.98</v>
+        <v>116.45</v>
       </c>
       <c r="H2" t="n">
-        <v>105.72</v>
+        <v>105.53</v>
       </c>
       <c r="I2" t="n">
-        <v>11.26</v>
+        <v>10.92</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2696</v>
+        <v>0.268</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1444</v>
+        <v>0.1456</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
         <v>140</v>
@@ -13651,7 +13651,7 @@
         <v>128</v>
       </c>
       <c r="S2" t="n">
-        <v>1416.1</v>
+        <v>1416.5</v>
       </c>
     </row>
     <row r="3">
@@ -13850,31 +13850,31 @@
         <v>1441</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1381.5</v>
+        <v>1378.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2151</v>
       </c>
       <c r="G6" t="n">
-        <v>110.75</v>
+        <v>110.36</v>
       </c>
       <c r="H6" t="n">
-        <v>113.08</v>
+        <v>112.81</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.33</v>
+        <v>-2.44</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3281</v>
+        <v>0.3286</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1487</v>
+        <v>0.1523</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>236</v>
@@ -13895,7 +13895,7 @@
         <v>235</v>
       </c>
       <c r="S6" t="n">
-        <v>1471.4</v>
+        <v>1473.5</v>
       </c>
     </row>
     <row r="7">
@@ -13911,31 +13911,31 @@
         <v>1202</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>1533.7</v>
+        <v>1536.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0135</v>
+        <v>0.9002</v>
       </c>
       <c r="G7" t="n">
-        <v>111.25</v>
+        <v>111.68</v>
       </c>
       <c r="H7" t="n">
-        <v>107.48</v>
+        <v>107.71</v>
       </c>
       <c r="I7" t="n">
-        <v>3.77</v>
+        <v>3.97</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2564</v>
+        <v>0.2563</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1709</v>
+        <v>0.1715</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="M7" t="n">
         <v>200</v>
@@ -13956,7 +13956,7 @@
         <v>198</v>
       </c>
       <c r="S7" t="n">
-        <v>1419.8</v>
+        <v>1417.8</v>
       </c>
     </row>
     <row r="8">
@@ -13972,31 +13972,31 @@
         <v>1422</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1376.6</v>
+        <v>1374</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5542</v>
+        <v>-2.3898</v>
       </c>
       <c r="G8" t="n">
-        <v>110.35</v>
+        <v>110.54</v>
       </c>
       <c r="H8" t="n">
-        <v>117.35</v>
+        <v>117.8</v>
       </c>
       <c r="I8" t="n">
-        <v>-7</v>
+        <v>-7.26</v>
       </c>
       <c r="J8" t="n">
-        <v>0.272</v>
+        <v>0.2707</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1391</v>
+        <v>0.1419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>304</v>
@@ -14017,7 +14017,7 @@
         <v>298</v>
       </c>
       <c r="S8" t="n">
-        <v>1424.1</v>
+        <v>1428.1</v>
       </c>
     </row>
     <row r="9">
@@ -14571,31 +14571,31 @@
         <v>1309</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1339.8</v>
+        <v>1342</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5343</v>
+        <v>0.5805</v>
       </c>
       <c r="G6" t="n">
-        <v>106.23</v>
+        <v>106.17</v>
       </c>
       <c r="H6" t="n">
-        <v>111.08</v>
+        <v>110.07</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.85</v>
+        <v>-3.91</v>
       </c>
       <c r="J6" t="n">
-        <v>0.294</v>
+        <v>0.2927</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1965</v>
+        <v>0.1967</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
         <v>176</v>
@@ -14616,7 +14616,7 @@
         <v>203</v>
       </c>
       <c r="S6" t="n">
-        <v>1459</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="7">
@@ -14632,31 +14632,31 @@
         <v>1311</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>1362.2</v>
+        <v>1364.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5128</v>
+        <v>-1.4633</v>
       </c>
       <c r="G7" t="n">
-        <v>104.43</v>
+        <v>104.33</v>
       </c>
       <c r="H7" t="n">
-        <v>111.13</v>
+        <v>109.7</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.7</v>
+        <v>-5.37</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3234</v>
+        <v>0.322</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1678</v>
+        <v>0.168</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>240</v>
@@ -14677,7 +14677,7 @@
         <v>251</v>
       </c>
       <c r="S7" t="n">
-        <v>1434.9</v>
+        <v>1425.9</v>
       </c>
     </row>
     <row r="8">
@@ -14693,31 +14693,31 @@
         <v>1322</v>
       </c>
       <c r="D8" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1288.1</v>
+        <v>1286</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.681</v>
+        <v>-1.6046</v>
       </c>
       <c r="G8" t="n">
-        <v>102.39</v>
+        <v>101.62</v>
       </c>
       <c r="H8" t="n">
-        <v>112.41</v>
+        <v>112.18</v>
       </c>
       <c r="I8" t="n">
-        <v>-10.02</v>
+        <v>-10.55</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2622</v>
+        <v>0.2687</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1709</v>
+        <v>0.1738</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="M8" t="n">
         <v>276</v>
@@ -14738,7 +14738,7 @@
         <v>294</v>
       </c>
       <c r="S8" t="n">
-        <v>1441.7</v>
+        <v>1438.9</v>
       </c>
     </row>
     <row r="9">
@@ -14754,31 +14754,31 @@
         <v>1223</v>
       </c>
       <c r="D9" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E9" t="n">
-        <v>1276.5</v>
+        <v>1274.3</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8273</v>
+        <v>-0.7502</v>
       </c>
       <c r="G9" t="n">
-        <v>103.46</v>
+        <v>102.64</v>
       </c>
       <c r="H9" t="n">
-        <v>112.17</v>
+        <v>112.14</v>
       </c>
       <c r="I9" t="n">
-        <v>-8.710000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3045</v>
+        <v>0.2972</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1803</v>
+        <v>0.1797</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4</v>
+        <v>-5.8</v>
       </c>
       <c r="M9" t="n">
         <v>300</v>
@@ -14799,7 +14799,7 @@
         <v>301</v>
       </c>
       <c r="S9" t="n">
-        <v>1424.2</v>
+        <v>1421.3</v>
       </c>
     </row>
   </sheetData>
@@ -14926,31 +14926,31 @@
         <v>1295</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1591.4</v>
+        <v>1593.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6609</v>
+        <v>3.5257</v>
       </c>
       <c r="G2" t="n">
-        <v>114.4</v>
+        <v>114.28</v>
       </c>
       <c r="H2" t="n">
-        <v>102.12</v>
+        <v>102.18</v>
       </c>
       <c r="I2" t="n">
-        <v>12.28</v>
+        <v>12.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3105</v>
+        <v>0.3104</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1495</v>
+        <v>0.1506</v>
       </c>
       <c r="L2" t="n">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="M2" t="n">
         <v>118</v>
@@ -14971,7 +14971,7 @@
         <v>117</v>
       </c>
       <c r="S2" t="n">
-        <v>1412</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="3">
@@ -15048,31 +15048,31 @@
         <v>1315</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1369.2</v>
+        <v>1366.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>0.9359</v>
       </c>
       <c r="G4" t="n">
-        <v>107.08</v>
+        <v>106.64</v>
       </c>
       <c r="H4" t="n">
-        <v>114.49</v>
+        <v>114.37</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.42</v>
+        <v>-7.73</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3107</v>
+        <v>0.3048</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1353</v>
+        <v>0.1348</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.8</v>
+        <v>-6.4</v>
       </c>
       <c r="M4" t="n">
         <v>290</v>
@@ -15093,7 +15093,7 @@
         <v>284</v>
       </c>
       <c r="S4" t="n">
-        <v>1464.7</v>
+        <v>1468.8</v>
       </c>
     </row>
     <row r="5">
@@ -15586,31 +15586,31 @@
         <v>1407</v>
       </c>
       <c r="D2" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1593.7</v>
+        <v>1597</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3343</v>
+        <v>1.2134</v>
       </c>
       <c r="G2" t="n">
-        <v>112.11</v>
+        <v>111.85</v>
       </c>
       <c r="H2" t="n">
-        <v>106.85</v>
+        <v>106.58</v>
       </c>
       <c r="I2" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3162</v>
+        <v>0.3163</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1601</v>
+        <v>0.1636</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="M2" t="n">
         <v>156</v>
@@ -15631,7 +15631,7 @@
         <v>138</v>
       </c>
       <c r="S2" t="n">
-        <v>1464.1</v>
+        <v>1466.1</v>
       </c>
     </row>
     <row r="3">
@@ -15647,31 +15647,31 @@
         <v>1267</v>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1505</v>
+        <v>1498.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6916</v>
+        <v>-0.6787</v>
       </c>
       <c r="G3" t="n">
-        <v>114.1</v>
+        <v>113.86</v>
       </c>
       <c r="H3" t="n">
-        <v>111.78</v>
+        <v>111.61</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2915</v>
+        <v>0.2973</v>
       </c>
       <c r="K3" t="n">
         <v>0.158</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4</v>
+        <v>-3</v>
       </c>
       <c r="M3" t="n">
         <v>197</v>
@@ -15692,7 +15692,7 @@
         <v>162</v>
       </c>
       <c r="S3" t="n">
-        <v>1448.1</v>
+        <v>1448.2</v>
       </c>
     </row>
     <row r="4">
@@ -16013,31 +16013,31 @@
         <v>1379</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" t="n">
-        <v>1417.3</v>
+        <v>1414</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8704</v>
+        <v>0.977</v>
       </c>
       <c r="G9" t="n">
-        <v>106.66</v>
+        <v>106.26</v>
       </c>
       <c r="H9" t="n">
-        <v>107.26</v>
+        <v>107.36</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2968</v>
+        <v>0.3037</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1758</v>
+        <v>0.1757</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="M9" t="n">
         <v>225</v>
@@ -16058,7 +16058,7 @@
         <v>224</v>
       </c>
       <c r="S9" t="n">
-        <v>1466.6</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="10">
@@ -16135,31 +16135,31 @@
         <v>1204</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" t="n">
-        <v>1442.3</v>
+        <v>1448.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7056</v>
+        <v>0.7301</v>
       </c>
       <c r="G11" t="n">
-        <v>111.7</v>
+        <v>111.54</v>
       </c>
       <c r="H11" t="n">
-        <v>111.37</v>
+        <v>111.35</v>
       </c>
       <c r="I11" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3157</v>
+        <v>0.3152</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1465</v>
+        <v>0.1479</v>
       </c>
       <c r="L11" t="n">
-        <v>11.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>265</v>
@@ -16180,7 +16180,7 @@
         <v>254</v>
       </c>
       <c r="S11" t="n">
-        <v>1441.9</v>
+        <v>1444.4</v>
       </c>
     </row>
     <row r="12">
@@ -17394,31 +17394,31 @@
         <v>1378</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1709.5</v>
+        <v>1711.8</v>
       </c>
       <c r="F2" t="n">
-        <v>9.3651</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>115.67</v>
+        <v>116.06</v>
       </c>
       <c r="H2" t="n">
-        <v>102.39</v>
+        <v>101.73</v>
       </c>
       <c r="I2" t="n">
-        <v>13.28</v>
+        <v>14.32</v>
       </c>
       <c r="J2" t="n">
-        <v>0.336</v>
+        <v>0.3392</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1478</v>
+        <v>0.1453</v>
       </c>
       <c r="L2" t="n">
-        <v>15.4</v>
+        <v>19.6</v>
       </c>
       <c r="M2" t="n">
         <v>52</v>
@@ -17439,7 +17439,7 @@
         <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>1558.8</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="3">
@@ -17455,31 +17455,31 @@
         <v>1409</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1676.2</v>
+        <v>1679.9</v>
       </c>
       <c r="F3" t="n">
-        <v>9.632899999999999</v>
+        <v>9.1937</v>
       </c>
       <c r="G3" t="n">
-        <v>122.85</v>
+        <v>122.52</v>
       </c>
       <c r="H3" t="n">
-        <v>105.68</v>
+        <v>106.2</v>
       </c>
       <c r="I3" t="n">
-        <v>17.17</v>
+        <v>16.32</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2706</v>
+        <v>0.2712</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1461</v>
+        <v>0.1456</v>
       </c>
       <c r="L3" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="M3" t="n">
         <v>56</v>
@@ -17500,7 +17500,7 @@
         <v>50</v>
       </c>
       <c r="S3" t="n">
-        <v>1502.5</v>
+        <v>1503.5</v>
       </c>
     </row>
     <row r="4">
@@ -17577,31 +17577,31 @@
         <v>1412</v>
       </c>
       <c r="D5" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>1597.5</v>
+        <v>1599.6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5946</v>
+        <v>0.5782</v>
       </c>
       <c r="G5" t="n">
-        <v>108.59</v>
+        <v>108.91</v>
       </c>
       <c r="H5" t="n">
-        <v>102.99</v>
+        <v>103.19</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.72</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3073</v>
+        <v>0.3013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1245</v>
+        <v>0.1241</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
         <v>124</v>
@@ -17622,7 +17622,7 @@
         <v>114</v>
       </c>
       <c r="S5" t="n">
-        <v>1504.4</v>
+        <v>1499.7</v>
       </c>
     </row>
     <row r="6">
@@ -17641,7 +17641,7 @@
         <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1536.7</v>
+        <v>1532.3</v>
       </c>
       <c r="F6" t="n">
         <v>-5.3186</v>
@@ -17760,31 +17760,31 @@
         <v>1150</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1439.3</v>
+        <v>1437.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3639</v>
+        <v>1.3871</v>
       </c>
       <c r="G8" t="n">
-        <v>112.74</v>
+        <v>111.71</v>
       </c>
       <c r="H8" t="n">
-        <v>113.57</v>
+        <v>113.99</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.83</v>
+        <v>-2.27</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2964</v>
+        <v>0.298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1665</v>
+        <v>0.1699</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>-3.4</v>
       </c>
       <c r="M8" t="n">
         <v>183</v>
@@ -17805,7 +17805,7 @@
         <v>169</v>
       </c>
       <c r="S8" t="n">
-        <v>1491.9</v>
+        <v>1500.4</v>
       </c>
     </row>
     <row r="9">
@@ -17821,31 +17821,31 @@
         <v>1272</v>
       </c>
       <c r="D9" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E9" t="n">
-        <v>1560.2</v>
+        <v>1567</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.242</v>
+        <v>-5.2285</v>
       </c>
       <c r="G9" t="n">
-        <v>103.89</v>
+        <v>104.68</v>
       </c>
       <c r="H9" t="n">
-        <v>105.68</v>
+        <v>106.29</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.79</v>
+        <v>-1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.339</v>
+        <v>0.3397</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1823</v>
+        <v>0.1824</v>
       </c>
       <c r="L9" t="n">
-        <v>-12.2</v>
+        <v>-7.8</v>
       </c>
       <c r="M9" t="n">
         <v>131</v>
@@ -17866,7 +17866,7 @@
         <v>130</v>
       </c>
       <c r="S9" t="n">
-        <v>1612.9</v>
+        <v>1607.8</v>
       </c>
     </row>
     <row r="10">
@@ -17882,31 +17882,31 @@
         <v>1408</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10" t="n">
-        <v>1493.5</v>
+        <v>1495.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8307</v>
+        <v>-1.8275</v>
       </c>
       <c r="G10" t="n">
-        <v>104.53</v>
+        <v>105.57</v>
       </c>
       <c r="H10" t="n">
-        <v>110.32</v>
+        <v>110.65</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.79</v>
+        <v>-5.08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2272</v>
+        <v>0.2346</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1535</v>
+        <v>0.1519</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.8</v>
+        <v>-17.2</v>
       </c>
       <c r="M10" t="n">
         <v>196</v>
@@ -17927,7 +17927,7 @@
         <v>197</v>
       </c>
       <c r="S10" t="n">
-        <v>1529.8</v>
+        <v>1531.6</v>
       </c>
     </row>
     <row r="11">
@@ -17943,31 +17943,31 @@
         <v>1396</v>
       </c>
       <c r="D11" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E11" t="n">
-        <v>1508.2</v>
+        <v>1495.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6583</v>
+        <v>-1.6989</v>
       </c>
       <c r="G11" t="n">
-        <v>111.93</v>
+        <v>111.7</v>
       </c>
       <c r="H11" t="n">
-        <v>108.29</v>
+        <v>108.98</v>
       </c>
       <c r="I11" t="n">
-        <v>3.64</v>
+        <v>2.71</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2717</v>
+        <v>0.2698</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1294</v>
+        <v>0.1289</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>174</v>
@@ -17988,7 +17988,7 @@
         <v>177</v>
       </c>
       <c r="S11" t="n">
-        <v>1492</v>
+        <v>1500.5</v>
       </c>
     </row>
   </sheetData>
@@ -18775,31 +18775,31 @@
         <v>1365</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1765.9</v>
+        <v>1768.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7176</v>
+        <v>-0.4727</v>
       </c>
       <c r="G4" t="n">
-        <v>117.4</v>
+        <v>117.67</v>
       </c>
       <c r="H4" t="n">
-        <v>102.2</v>
+        <v>102.69</v>
       </c>
       <c r="I4" t="n">
-        <v>15.2</v>
+        <v>14.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3448</v>
+        <v>0.3472</v>
       </c>
       <c r="K4" t="n">
         <v>0.1494</v>
       </c>
       <c r="L4" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
         <v>37</v>
@@ -18820,7 +18820,7 @@
         <v>40</v>
       </c>
       <c r="S4" t="n">
-        <v>1571.8</v>
+        <v>1566.6</v>
       </c>
     </row>
     <row r="5">
@@ -18836,31 +18836,31 @@
         <v>1333</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>1543.3</v>
+        <v>1551.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0737</v>
+        <v>-2.8876</v>
       </c>
       <c r="G5" t="n">
-        <v>106.94</v>
+        <v>107.33</v>
       </c>
       <c r="H5" t="n">
-        <v>111.94</v>
+        <v>111.75</v>
       </c>
       <c r="I5" t="n">
-        <v>-5</v>
+        <v>-4.42</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2448</v>
+        <v>0.2465</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1687</v>
+        <v>0.1704</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>-2</v>
       </c>
       <c r="M5" t="n">
         <v>184</v>
@@ -18881,7 +18881,7 @@
         <v>175</v>
       </c>
       <c r="S5" t="n">
-        <v>1539.5</v>
+        <v>1538.2</v>
       </c>
     </row>
     <row r="6">
@@ -18897,31 +18897,31 @@
         <v>1362</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1568.1</v>
+        <v>1559.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.0664</v>
+        <v>-3.9344</v>
       </c>
       <c r="G6" t="n">
-        <v>109.57</v>
+        <v>109.83</v>
       </c>
       <c r="H6" t="n">
-        <v>108.89</v>
+        <v>109.48</v>
       </c>
       <c r="I6" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2747</v>
+        <v>0.2789</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1548</v>
+        <v>0.1547</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2</v>
+        <v>-3</v>
       </c>
       <c r="M6" t="n">
         <v>122</v>
@@ -18942,7 +18942,7 @@
         <v>122</v>
       </c>
       <c r="S6" t="n">
-        <v>1568.4</v>
+        <v>1568.8</v>
       </c>
     </row>
     <row r="7">
@@ -18958,31 +18958,31 @@
         <v>1334</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>1440.5</v>
+        <v>1438.1</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9361</v>
+        <v>3.8121</v>
       </c>
       <c r="G7" t="n">
-        <v>107.78</v>
+        <v>108.28</v>
       </c>
       <c r="H7" t="n">
-        <v>104.75</v>
+        <v>105.96</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04</v>
+        <v>2.32</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2727</v>
+        <v>0.2808</v>
       </c>
       <c r="K7" t="n">
-        <v>0.189</v>
+        <v>0.1875</v>
       </c>
       <c r="L7" t="n">
-        <v>-9</v>
+        <v>-8.4</v>
       </c>
       <c r="M7" t="n">
         <v>112</v>
@@ -19003,7 +19003,7 @@
         <v>115</v>
       </c>
       <c r="S7" t="n">
-        <v>1523.4</v>
+        <v>1533.2</v>
       </c>
     </row>
     <row r="8">
@@ -20095,31 +20095,31 @@
         <v>1146</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1369.9</v>
+        <v>1367.5</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1128</v>
+        <v>3.1174</v>
       </c>
       <c r="G2" t="n">
-        <v>112.04</v>
+        <v>112.34</v>
       </c>
       <c r="H2" t="n">
-        <v>106.14</v>
+        <v>107</v>
       </c>
       <c r="I2" t="n">
-        <v>5.91</v>
+        <v>5.34</v>
       </c>
       <c r="J2" t="n">
-        <v>0.271</v>
+        <v>0.2747</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1505</v>
+        <v>0.1536</v>
       </c>
       <c r="L2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M2" t="n">
         <v>154</v>
@@ -20140,7 +20140,7 @@
         <v>164</v>
       </c>
       <c r="S2" t="n">
-        <v>1437.1</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="3">
@@ -20217,31 +20217,31 @@
         <v>1474</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1424.9</v>
+        <v>1427.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9866</v>
+        <v>1.0039</v>
       </c>
       <c r="G4" t="n">
-        <v>119.08</v>
+        <v>119.17</v>
       </c>
       <c r="H4" t="n">
-        <v>116.55</v>
+        <v>116.56</v>
       </c>
       <c r="I4" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2802</v>
+        <v>0.2859</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1443</v>
+        <v>0.1441</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
         <v>191</v>
@@ -20262,7 +20262,7 @@
         <v>201</v>
       </c>
       <c r="S4" t="n">
-        <v>1433.6</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="5">
@@ -22807,31 +22807,31 @@
         <v>1340</v>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1458.3</v>
+        <v>1460.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.128</v>
+        <v>2.001</v>
       </c>
       <c r="G2" t="n">
-        <v>105.36</v>
+        <v>105.77</v>
       </c>
       <c r="H2" t="n">
-        <v>101.08</v>
+        <v>101.47</v>
       </c>
       <c r="I2" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2592</v>
+        <v>0.2576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1706</v>
+        <v>0.1661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="M2" t="n">
         <v>159</v>
@@ -22852,7 +22852,7 @@
         <v>151</v>
       </c>
       <c r="S2" t="n">
-        <v>1416.6</v>
+        <v>1413.3</v>
       </c>
     </row>
     <row r="3">
@@ -22868,31 +22868,31 @@
         <v>1286</v>
       </c>
       <c r="D3" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1436.3</v>
+        <v>1432.4</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2578</v>
+        <v>3.1402</v>
       </c>
       <c r="G3" t="n">
-        <v>112.04</v>
+        <v>111.83</v>
       </c>
       <c r="H3" t="n">
-        <v>108.25</v>
+        <v>108.61</v>
       </c>
       <c r="I3" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2625</v>
+        <v>0.2564</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1417</v>
+        <v>0.141</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M3" t="n">
         <v>135</v>
@@ -22913,7 +22913,7 @@
         <v>134</v>
       </c>
       <c r="S3" t="n">
-        <v>1437.7</v>
+        <v>1437.1</v>
       </c>
     </row>
     <row r="4">
@@ -23173,31 +23173,31 @@
         <v>1225</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" t="n">
-        <v>1399.2</v>
+        <v>1403.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3774</v>
+        <v>-0.3924</v>
       </c>
       <c r="G8" t="n">
-        <v>110.21</v>
+        <v>110.57</v>
       </c>
       <c r="H8" t="n">
-        <v>107.26</v>
+        <v>107.71</v>
       </c>
       <c r="I8" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2761</v>
+        <v>0.2754</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1488</v>
+        <v>0.1463</v>
       </c>
       <c r="L8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M8" t="n">
         <v>173</v>
@@ -23218,7 +23218,7 @@
         <v>172</v>
       </c>
       <c r="S8" t="n">
-        <v>1414.5</v>
+        <v>1416.4</v>
       </c>
     </row>
     <row r="9">
@@ -23295,31 +23295,31 @@
         <v>1226</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" t="n">
-        <v>1332.5</v>
+        <v>1330.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6577</v>
+        <v>-1.6311</v>
       </c>
       <c r="G10" t="n">
-        <v>110.74</v>
+        <v>110.59</v>
       </c>
       <c r="H10" t="n">
-        <v>116.75</v>
+        <v>116.92</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.01</v>
+        <v>-6.33</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3229</v>
+        <v>0.3184</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1668</v>
+        <v>0.1667</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="M10" t="n">
         <v>238</v>
@@ -23340,7 +23340,7 @@
         <v>229</v>
       </c>
       <c r="S10" t="n">
-        <v>1424.5</v>
+        <v>1426.8</v>
       </c>
     </row>
     <row r="11">
@@ -23528,31 +23528,31 @@
         <v>1219</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E2" t="n">
-        <v>1620.5</v>
+        <v>1625.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0234</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>121.05</v>
+        <v>121.16</v>
       </c>
       <c r="H2" t="n">
         <v>100.19</v>
       </c>
       <c r="I2" t="n">
-        <v>20.86</v>
+        <v>20.97</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3114</v>
+        <v>0.3061</v>
       </c>
       <c r="K2" t="n">
-        <v>0.128</v>
+        <v>0.1276</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>91</v>
@@ -23573,7 +23573,7 @@
         <v>76</v>
       </c>
       <c r="S2" t="n">
-        <v>1377.7</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="3">
@@ -23589,31 +23589,31 @@
         <v>1457</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>1493.8</v>
+        <v>1488.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7807</v>
+        <v>1.7975</v>
       </c>
       <c r="G3" t="n">
-        <v>113.16</v>
+        <v>112.45</v>
       </c>
       <c r="H3" t="n">
-        <v>107</v>
+        <v>107.39</v>
       </c>
       <c r="I3" t="n">
-        <v>6.15</v>
+        <v>5.06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.313</v>
+        <v>0.3163</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1421</v>
+        <v>0.1424</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="M3" t="n">
         <v>141</v>
@@ -23634,7 +23634,7 @@
         <v>129</v>
       </c>
       <c r="S3" t="n">
-        <v>1427.2</v>
+        <v>1437.4</v>
       </c>
     </row>
     <row r="4">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -9994,59 +9994,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1129</v>
+        <v>1305</v>
       </c>
       <c r="D6" t="n">
         <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1737.5</v>
+        <v>1736.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1403</v>
+        <v>6.7862</v>
       </c>
       <c r="G6" t="n">
-        <v>114.39</v>
+        <v>112.99</v>
       </c>
       <c r="H6" t="n">
-        <v>107.18</v>
+        <v>106.43</v>
       </c>
       <c r="I6" t="n">
-        <v>7.21</v>
+        <v>6.56</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2847</v>
+        <v>0.3038</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1604</v>
+        <v>0.1419</v>
       </c>
       <c r="L6" t="n">
-        <v>12.2</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O6" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P6" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="S6" t="n">
-        <v>1622.1</v>
+        <v>1598.1</v>
       </c>
     </row>
     <row r="7">
@@ -10055,59 +10055,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1305</v>
+        <v>1129</v>
       </c>
       <c r="D7" t="n">
         <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1736.5</v>
+        <v>1737.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.7862</v>
+        <v>-2.1403</v>
       </c>
       <c r="G7" t="n">
-        <v>112.99</v>
+        <v>114.39</v>
       </c>
       <c r="H7" t="n">
-        <v>106.43</v>
+        <v>107.18</v>
       </c>
       <c r="I7" t="n">
-        <v>6.56</v>
+        <v>7.21</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3038</v>
+        <v>0.2847</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1419</v>
+        <v>0.1604</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>12.2</v>
       </c>
       <c r="M7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N7" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O7" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="R7" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="S7" t="n">
-        <v>1598.1</v>
+        <v>1622.1</v>
       </c>
     </row>
     <row r="8">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -583,22 +583,22 @@
         <v>-0.4</v>
       </c>
       <c r="M2" t="n">
+        <v>40</v>
+      </c>
+      <c r="N2" t="n">
+        <v>46</v>
+      </c>
+      <c r="O2" t="n">
+        <v>36</v>
+      </c>
+      <c r="P2" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>28</v>
+      </c>
+      <c r="R2" t="n">
         <v>27</v>
-      </c>
-      <c r="N2" t="n">
-        <v>40</v>
-      </c>
-      <c r="O2" t="n">
-        <v>25</v>
-      </c>
-      <c r="P2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>26</v>
-      </c>
-      <c r="R2" t="n">
-        <v>24</v>
       </c>
       <c r="S2" t="n">
         <v>1512.1</v>
@@ -647,19 +647,19 @@
         <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R3" t="n">
         <v>44</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>43</v>
-      </c>
-      <c r="R3" t="n">
-        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>1554.6</v>
@@ -705,22 +705,22 @@
         <v>10.6</v>
       </c>
       <c r="M4" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="N4" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="O4" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="P4" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="Q4" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="R4" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="S4" t="n">
         <v>1506.8</v>
@@ -766,22 +766,22 @@
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
+        <v>79</v>
+      </c>
+      <c r="N5" t="n">
+        <v>82</v>
+      </c>
+      <c r="O5" t="n">
+        <v>79</v>
+      </c>
+      <c r="P5" t="n">
         <v>75</v>
       </c>
-      <c r="N5" t="n">
-        <v>78</v>
-      </c>
-      <c r="O5" t="n">
-        <v>72</v>
-      </c>
-      <c r="P5" t="n">
-        <v>76</v>
-      </c>
       <c r="Q5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="S5" t="n">
         <v>1562.3</v>
@@ -827,22 +827,22 @@
         <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="N6" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O6" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="P6" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R6" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="S6" t="n">
         <v>1517.3</v>
@@ -888,22 +888,22 @@
         <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N7" t="n">
         <v>115</v>
       </c>
       <c r="O7" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P7" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q7" t="n">
         <v>108</v>
       </c>
-      <c r="Q7" t="n">
-        <v>98</v>
-      </c>
       <c r="R7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S7" t="n">
         <v>1541</v>
@@ -949,22 +949,22 @@
         <v>-9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="N8" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O8" t="n">
         <v>132</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="Q8" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R8" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="S8" t="n">
         <v>1537.9</v>
@@ -1013,19 +1013,19 @@
         <v>168</v>
       </c>
       <c r="N9" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q9" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="R9" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="S9" t="n">
         <v>1499</v>
@@ -1071,22 +1071,22 @@
         <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N10" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O10" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="P10" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q10" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="R10" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="S10" t="n">
         <v>1531.5</v>
@@ -1132,22 +1132,22 @@
         <v>-7.4</v>
       </c>
       <c r="M11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N11" t="n">
         <v>150</v>
       </c>
       <c r="O11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q11" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="R11" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="S11" t="n">
         <v>1516.7</v>
@@ -1193,22 +1193,22 @@
         <v>-1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q12" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="R12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="S12" t="n">
         <v>1510.8</v>
@@ -1254,22 +1254,22 @@
         <v>-6</v>
       </c>
       <c r="M13" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="N13" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="O13" t="n">
         <v>205</v>
       </c>
       <c r="P13" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q13" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="R13" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="S13" t="n">
         <v>1566.1</v>
@@ -1315,22 +1315,22 @@
         <v>-2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="N14" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O14" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="P14" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="R14" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="S14" t="n">
         <v>1531.2</v>
@@ -1376,22 +1376,22 @@
         <v>-4.4</v>
       </c>
       <c r="M15" t="n">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N15" t="n">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="O15" t="n">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="P15" t="n">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="Q15" t="n">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="R15" t="n">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="S15" t="n">
         <v>1557.5</v>
@@ -1609,19 +1609,19 @@
         <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
         <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
         <v>12</v>
@@ -1673,16 +1673,16 @@
         <v>9</v>
       </c>
       <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="O4" t="n">
-        <v>8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
         <v>11</v>
@@ -1734,10 +1734,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>7</v>
@@ -1746,7 +1746,7 @@
         <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
         <v>1709.5</v>
@@ -1792,22 +1792,22 @@
         <v>10.6</v>
       </c>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N6" t="n">
+        <v>22</v>
+      </c>
+      <c r="O6" t="n">
+        <v>23</v>
+      </c>
+      <c r="P6" t="n">
         <v>25</v>
       </c>
-      <c r="O6" t="n">
-        <v>28</v>
-      </c>
-      <c r="P6" t="n">
-        <v>28</v>
-      </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="S6" t="n">
         <v>1701.3</v>
@@ -1853,22 +1853,22 @@
         <v>11.2</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O7" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="P7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="S7" t="n">
         <v>1689.3</v>
@@ -1920,16 +1920,16 @@
         <v>12</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
         <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>1746.9</v>
@@ -1975,22 +1975,22 @@
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S9" t="n">
         <v>1700.1</v>
@@ -2039,19 +2039,19 @@
         <v>24</v>
       </c>
       <c r="N10" t="n">
+        <v>33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>30</v>
+      </c>
+      <c r="P10" t="n">
         <v>28</v>
       </c>
-      <c r="O10" t="n">
-        <v>32</v>
-      </c>
-      <c r="P10" t="n">
-        <v>29</v>
-      </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S10" t="n">
         <v>1715.1</v>
@@ -2097,22 +2097,22 @@
         <v>-5.8</v>
       </c>
       <c r="M11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="O11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S11" t="n">
         <v>1701.1</v>
@@ -2158,22 +2158,22 @@
         <v>-3</v>
       </c>
       <c r="M12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="N12" t="n">
+        <v>72</v>
+      </c>
+      <c r="O12" t="n">
         <v>74</v>
       </c>
-      <c r="O12" t="n">
-        <v>63</v>
-      </c>
       <c r="P12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="R12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="S12" t="n">
         <v>1674.6</v>
@@ -2222,16 +2222,16 @@
         <v>54</v>
       </c>
       <c r="N13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O13" t="n">
+        <v>58</v>
+      </c>
+      <c r="P13" t="n">
         <v>59</v>
       </c>
-      <c r="P13" t="n">
-        <v>58</v>
-      </c>
       <c r="Q13" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R13" t="n">
         <v>61</v>
@@ -2280,22 +2280,22 @@
         <v>-15</v>
       </c>
       <c r="M14" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O14" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="Q14" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="R14" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="S14" t="n">
         <v>1693.6</v>
@@ -2341,22 +2341,22 @@
         <v>-2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="N15" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O15" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="P15" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="R15" t="n">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="S15" t="n">
         <v>1684.5</v>
@@ -2402,22 +2402,22 @@
         <v>0.8</v>
       </c>
       <c r="M16" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N16" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O16" t="n">
         <v>65</v>
       </c>
       <c r="P16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S16" t="n">
         <v>1700.2</v>
@@ -2463,22 +2463,22 @@
         <v>-1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N17" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O17" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P17" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q17" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R17" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="S17" t="n">
         <v>1731.6</v>
@@ -2524,22 +2524,22 @@
         <v>-10.4</v>
       </c>
       <c r="M18" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N18" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O18" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P18" t="n">
         <v>121</v>
       </c>
       <c r="Q18" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="R18" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="S18" t="n">
         <v>1724.9</v>
@@ -2585,22 +2585,22 @@
         <v>-15.6</v>
       </c>
       <c r="M19" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="N19" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O19" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="P19" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="Q19" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="R19" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="S19" t="n">
         <v>1664.7</v>
@@ -2757,22 +2757,22 @@
         <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N2" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O2" t="n">
+        <v>105</v>
+      </c>
+      <c r="P2" t="n">
         <v>110</v>
       </c>
-      <c r="P2" t="n">
-        <v>115</v>
-      </c>
       <c r="Q2" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="R2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S2" t="n">
         <v>1471.2</v>
@@ -2818,22 +2818,22 @@
         <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N3" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O3" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="P3" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R3" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="S3" t="n">
         <v>1444.6</v>
@@ -2879,22 +2879,22 @@
         <v>4.8</v>
       </c>
       <c r="M4" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N4" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="O4" t="n">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="P4" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q4" t="n">
+        <v>169</v>
+      </c>
+      <c r="R4" t="n">
         <v>180</v>
-      </c>
-      <c r="R4" t="n">
-        <v>193</v>
       </c>
       <c r="S4" t="n">
         <v>1480.3</v>
@@ -2940,22 +2940,22 @@
         <v>-4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="N5" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="O5" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="P5" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="Q5" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="R5" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="S5" t="n">
         <v>1451.3</v>
@@ -3004,16 +3004,16 @@
         <v>113</v>
       </c>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O6" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q6" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R6" t="n">
         <v>120</v>
@@ -3065,19 +3065,19 @@
         <v>155</v>
       </c>
       <c r="N7" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O7" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P7" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q7" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="R7" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="S7" t="n">
         <v>1456.9</v>
@@ -3123,22 +3123,22 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N8" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="O8" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P8" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="Q8" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="R8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S8" t="n">
         <v>1456.2</v>
@@ -3184,22 +3184,22 @@
         <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N9" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O9" t="n">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="P9" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q9" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="R9" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="S9" t="n">
         <v>1490.1</v>
@@ -3356,22 +3356,22 @@
         <v>5.8</v>
       </c>
       <c r="M2" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N2" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="O2" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P2" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>79</v>
+      </c>
+      <c r="R2" t="n">
         <v>96</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>65</v>
-      </c>
-      <c r="R2" t="n">
-        <v>93</v>
       </c>
       <c r="S2" t="n">
         <v>1427</v>
@@ -3417,22 +3417,22 @@
         <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="N3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="P3" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="Q3" t="n">
         <v>114</v>
       </c>
       <c r="R3" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="S3" t="n">
         <v>1482.5</v>
@@ -3478,22 +3478,22 @@
         <v>20.2</v>
       </c>
       <c r="M4" t="n">
+        <v>84</v>
+      </c>
+      <c r="N4" t="n">
+        <v>125</v>
+      </c>
+      <c r="O4" t="n">
+        <v>84</v>
+      </c>
+      <c r="P4" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q4" t="n">
         <v>92</v>
       </c>
-      <c r="N4" t="n">
-        <v>127</v>
-      </c>
-      <c r="O4" t="n">
-        <v>95</v>
-      </c>
-      <c r="P4" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>104</v>
-      </c>
       <c r="R4" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="S4" t="n">
         <v>1481.7</v>
@@ -3539,22 +3539,22 @@
         <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="N5" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="O5" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="Q5" t="n">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="R5" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="S5" t="n">
         <v>1458.5</v>
@@ -3600,22 +3600,22 @@
         <v>-0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N6" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O6" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P6" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Q6" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R6" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S6" t="n">
         <v>1436.1</v>
@@ -3661,22 +3661,22 @@
         <v>-0.4</v>
       </c>
       <c r="M7" t="n">
+        <v>145</v>
+      </c>
+      <c r="N7" t="n">
+        <v>173</v>
+      </c>
+      <c r="O7" t="n">
+        <v>128</v>
+      </c>
+      <c r="P7" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q7" t="n">
         <v>133</v>
       </c>
-      <c r="N7" t="n">
-        <v>169</v>
-      </c>
-      <c r="O7" t="n">
-        <v>112</v>
-      </c>
-      <c r="P7" t="n">
-        <v>125</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>145</v>
-      </c>
       <c r="R7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="S7" t="n">
         <v>1468.9</v>
@@ -3722,22 +3722,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="N8" t="n">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="O8" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="P8" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="Q8" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="R8" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="S8" t="n">
         <v>1524.4</v>
@@ -3783,22 +3783,22 @@
         <v>-6.8</v>
       </c>
       <c r="M9" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="N9" t="n">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="O9" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="P9" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="Q9" t="n">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="R9" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="S9" t="n">
         <v>1459.9</v>
@@ -3844,22 +3844,22 @@
         <v>6.2</v>
       </c>
       <c r="M10" t="n">
+        <v>177</v>
+      </c>
+      <c r="N10" t="n">
+        <v>199</v>
+      </c>
+      <c r="O10" t="n">
+        <v>136</v>
+      </c>
+      <c r="P10" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>189</v>
+      </c>
+      <c r="R10" t="n">
         <v>192</v>
-      </c>
-      <c r="N10" t="n">
-        <v>217</v>
-      </c>
-      <c r="O10" t="n">
-        <v>164</v>
-      </c>
-      <c r="P10" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>199</v>
-      </c>
-      <c r="R10" t="n">
-        <v>208</v>
       </c>
       <c r="S10" t="n">
         <v>1523.3</v>
@@ -3905,22 +3905,22 @@
         <v>-5</v>
       </c>
       <c r="M11" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N11" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O11" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q11" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="R11" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S11" t="n">
         <v>1454.5</v>
@@ -3966,22 +3966,22 @@
         <v>-13.4</v>
       </c>
       <c r="M12" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="N12" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="O12" t="n">
+        <v>218</v>
+      </c>
+      <c r="P12" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>236</v>
+      </c>
+      <c r="R12" t="n">
         <v>222</v>
-      </c>
-      <c r="P12" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>218</v>
-      </c>
-      <c r="R12" t="n">
-        <v>210</v>
       </c>
       <c r="S12" t="n">
         <v>1489.2</v>
@@ -4027,22 +4027,22 @@
         <v>-8</v>
       </c>
       <c r="M13" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="N13" t="n">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="O13" t="n">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="P13" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="Q13" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="R13" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="S13" t="n">
         <v>1450.1</v>
@@ -4088,22 +4088,22 @@
         <v>-3</v>
       </c>
       <c r="M14" t="n">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N14" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O14" t="n">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="P14" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q14" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="R14" t="n">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="S14" t="n">
         <v>1476.8</v>
@@ -4260,22 +4260,22 @@
         <v>-5</v>
       </c>
       <c r="M2" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="N2" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O2" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="P2" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Q2" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="S2" t="n">
         <v>1485.6</v>
@@ -4321,22 +4321,22 @@
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N3" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="O3" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P3" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="R3" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="S3" t="n">
         <v>1503.4</v>
@@ -4382,22 +4382,22 @@
         <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="N4" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="O4" t="n">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="P4" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="Q4" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R4" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="S4" t="n">
         <v>1482.7</v>
@@ -4443,22 +4443,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="N5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="O5" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="P5" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="Q5" t="n">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="R5" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="S5" t="n">
         <v>1523.7</v>
@@ -4504,22 +4504,22 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
+        <v>178</v>
+      </c>
+      <c r="N6" t="n">
+        <v>159</v>
+      </c>
+      <c r="O6" t="n">
+        <v>149</v>
+      </c>
+      <c r="P6" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q6" t="n">
         <v>170</v>
       </c>
-      <c r="N6" t="n">
-        <v>146</v>
-      </c>
-      <c r="O6" t="n">
-        <v>134</v>
-      </c>
-      <c r="P6" t="n">
-        <v>169</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>174</v>
-      </c>
       <c r="R6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="S6" t="n">
         <v>1469.9</v>
@@ -4565,22 +4565,22 @@
         <v>7.8</v>
       </c>
       <c r="M7" t="n">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="N7" t="n">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="O7" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="Q7" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="R7" t="n">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="S7" t="n">
         <v>1464.3</v>
@@ -4626,22 +4626,22 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N8" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="O8" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P8" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q8" t="n">
         <v>233</v>
       </c>
       <c r="R8" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="S8" t="n">
         <v>1466.3</v>
@@ -4687,22 +4687,22 @@
         <v>-1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N9" t="n">
+        <v>204</v>
+      </c>
+      <c r="O9" t="n">
         <v>201</v>
       </c>
-      <c r="O9" t="n">
-        <v>209</v>
-      </c>
       <c r="P9" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="Q9" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="R9" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="S9" t="n">
         <v>1474.6</v>
@@ -4748,22 +4748,22 @@
         <v>-0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="N10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O10" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="P10" t="n">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="Q10" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R10" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="S10" t="n">
         <v>1494.2</v>
@@ -4809,19 +4809,19 @@
         <v>-3</v>
       </c>
       <c r="M11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N11" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="O11" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="P11" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="Q11" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="R11" t="n">
         <v>186</v>
@@ -4981,22 +4981,22 @@
         <v>6.6</v>
       </c>
       <c r="M2" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="N2" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O2" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="P2" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="Q2" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="R2" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="S2" t="n">
         <v>1435.1</v>
@@ -5042,22 +5042,22 @@
         <v>16.4</v>
       </c>
       <c r="M3" t="n">
+        <v>139</v>
+      </c>
+      <c r="N3" t="n">
         <v>146</v>
       </c>
-      <c r="N3" t="n">
-        <v>151</v>
-      </c>
       <c r="O3" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="P3" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="Q3" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="R3" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="S3" t="n">
         <v>1429.2</v>
@@ -5103,22 +5103,22 @@
         <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="N4" t="n">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="O4" t="n">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="P4" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Q4" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="R4" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="S4" t="n">
         <v>1449.2</v>
@@ -5164,22 +5164,22 @@
         <v>2.2</v>
       </c>
       <c r="M5" t="n">
+        <v>170</v>
+      </c>
+      <c r="N5" t="n">
+        <v>176</v>
+      </c>
+      <c r="O5" t="n">
+        <v>155</v>
+      </c>
+      <c r="P5" t="n">
         <v>161</v>
       </c>
-      <c r="N5" t="n">
-        <v>166</v>
-      </c>
-      <c r="O5" t="n">
-        <v>153</v>
-      </c>
-      <c r="P5" t="n">
-        <v>153</v>
-      </c>
       <c r="Q5" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="R5" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="S5" t="n">
         <v>1491.6</v>
@@ -5225,22 +5225,22 @@
         <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="N6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O6" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="P6" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q6" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="R6" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="S6" t="n">
         <v>1447.2</v>
@@ -5286,22 +5286,22 @@
         <v>-3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N7" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="O7" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="P7" t="n">
         <v>242</v>
       </c>
       <c r="Q7" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="R7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S7" t="n">
         <v>1440.7</v>
@@ -5347,22 +5347,22 @@
         <v>5</v>
       </c>
       <c r="M8" t="n">
+        <v>172</v>
+      </c>
+      <c r="N8" t="n">
+        <v>183</v>
+      </c>
+      <c r="O8" t="n">
+        <v>173</v>
+      </c>
+      <c r="P8" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>187</v>
+      </c>
+      <c r="R8" t="n">
         <v>178</v>
-      </c>
-      <c r="N8" t="n">
-        <v>194</v>
-      </c>
-      <c r="O8" t="n">
-        <v>186</v>
-      </c>
-      <c r="P8" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>200</v>
-      </c>
-      <c r="R8" t="n">
-        <v>189</v>
       </c>
       <c r="S8" t="n">
         <v>1427.9</v>
@@ -5408,22 +5408,22 @@
         <v>-4.2</v>
       </c>
       <c r="M9" t="n">
+        <v>268</v>
+      </c>
+      <c r="N9" t="n">
+        <v>253</v>
+      </c>
+      <c r="O9" t="n">
+        <v>239</v>
+      </c>
+      <c r="P9" t="n">
         <v>262</v>
-      </c>
-      <c r="N9" t="n">
-        <v>249</v>
-      </c>
-      <c r="O9" t="n">
-        <v>215</v>
-      </c>
-      <c r="P9" t="n">
-        <v>254</v>
       </c>
       <c r="Q9" t="n">
         <v>259</v>
       </c>
       <c r="R9" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="S9" t="n">
         <v>1455</v>
@@ -5469,22 +5469,22 @@
         <v>-4</v>
       </c>
       <c r="M10" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="O10" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="P10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q10" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="R10" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="S10" t="n">
         <v>1429.8</v>
@@ -5530,22 +5530,22 @@
         <v>-11.4</v>
       </c>
       <c r="M11" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N11" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O11" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="P11" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q11" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="R11" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="S11" t="n">
         <v>1460</v>
@@ -5591,22 +5591,22 @@
         <v>-8.6</v>
       </c>
       <c r="M12" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="N12" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O12" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="P12" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q12" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="R12" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="S12" t="n">
         <v>1424.7</v>
@@ -5763,19 +5763,19 @@
         <v>6.6</v>
       </c>
       <c r="M2" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N2" t="n">
         <v>89</v>
       </c>
       <c r="O2" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="P2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="R2" t="n">
         <v>66</v>
@@ -5824,22 +5824,22 @@
         <v>5.4</v>
       </c>
       <c r="M3" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="N3" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O3" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="P3" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="Q3" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R3" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="S3" t="n">
         <v>1467.8</v>
@@ -5885,22 +5885,22 @@
         <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="N4" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="O4" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="P4" t="n">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="Q4" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="R4" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="S4" t="n">
         <v>1479.6</v>
@@ -5946,22 +5946,22 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="N5" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O5" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="P5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="Q5" t="n">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="R5" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="S5" t="n">
         <v>1488.6</v>
@@ -6118,22 +6118,22 @@
         <v>5.4</v>
       </c>
       <c r="M2" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N2" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O2" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="Q2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R2" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="S2" t="n">
         <v>1455.8</v>
@@ -6179,22 +6179,22 @@
         <v>-3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="N3" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="O3" t="n">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="P3" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="Q3" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="R3" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="S3" t="n">
         <v>1428.7</v>
@@ -6240,22 +6240,22 @@
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="N4" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="O4" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="P4" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Q4" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="R4" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="S4" t="n">
         <v>1426.7</v>
@@ -6304,16 +6304,16 @@
         <v>218</v>
       </c>
       <c r="N5" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="O5" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="P5" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q5" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="R5" t="n">
         <v>212</v>
@@ -6362,19 +6362,19 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N6" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O6" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="P6" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q6" t="n">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="R6" t="n">
         <v>182</v>
@@ -6423,19 +6423,19 @@
         <v>8.6</v>
       </c>
       <c r="M7" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N7" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="O7" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="P7" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q7" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="R7" t="n">
         <v>279</v>
@@ -6484,22 +6484,22 @@
         <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N8" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="O8" t="n">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="P8" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Q8" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="R8" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="S8" t="n">
         <v>1406</v>
@@ -6545,22 +6545,22 @@
         <v>4.2</v>
       </c>
       <c r="M9" t="n">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="N9" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="O9" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="P9" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="Q9" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="R9" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="S9" t="n">
         <v>1426</v>
@@ -6606,22 +6606,22 @@
         <v>-3</v>
       </c>
       <c r="M10" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N10" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O10" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="P10" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q10" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="R10" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S10" t="n">
         <v>1436.3</v>
@@ -6667,19 +6667,19 @@
         <v>-7</v>
       </c>
       <c r="M11" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N11" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O11" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="P11" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q11" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="R11" t="n">
         <v>329</v>
@@ -6839,19 +6839,19 @@
         <v>23.6</v>
       </c>
       <c r="M2" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N2" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="O2" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P2" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q2" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R2" t="n">
         <v>202</v>
@@ -6900,22 +6900,22 @@
         <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N3" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="O3" t="n">
         <v>358</v>
       </c>
       <c r="P3" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Q3" t="n">
         <v>326</v>
       </c>
       <c r="R3" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="S3" t="n">
         <v>1359.2</v>
@@ -6961,22 +6961,22 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="N4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O4" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P4" t="n">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Q4" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="R4" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="S4" t="n">
         <v>1390.3</v>
@@ -7022,22 +7022,22 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
+        <v>321</v>
+      </c>
+      <c r="N5" t="n">
+        <v>309</v>
+      </c>
+      <c r="O5" t="n">
+        <v>340</v>
+      </c>
+      <c r="P5" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>323</v>
+      </c>
+      <c r="R5" t="n">
         <v>313</v>
-      </c>
-      <c r="N5" t="n">
-        <v>299</v>
-      </c>
-      <c r="O5" t="n">
-        <v>336</v>
-      </c>
-      <c r="P5" t="n">
-        <v>298</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>314</v>
-      </c>
-      <c r="R5" t="n">
-        <v>308</v>
       </c>
       <c r="S5" t="n">
         <v>1377.4</v>
@@ -7083,22 +7083,22 @@
         <v>-4</v>
       </c>
       <c r="M6" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N6" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="O6" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P6" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q6" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="R6" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="S6" t="n">
         <v>1393</v>
@@ -7144,22 +7144,22 @@
         <v>-0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="N7" t="n">
+        <v>353</v>
+      </c>
+      <c r="O7" t="n">
+        <v>345</v>
+      </c>
+      <c r="P7" t="n">
+        <v>337</v>
+      </c>
+      <c r="Q7" t="n">
         <v>351</v>
       </c>
-      <c r="O7" t="n">
-        <v>340</v>
-      </c>
-      <c r="P7" t="n">
-        <v>333</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>352</v>
-      </c>
       <c r="R7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="S7" t="n">
         <v>1406.3</v>
@@ -7214,10 +7214,10 @@
         <v>365</v>
       </c>
       <c r="P8" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q8" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="R8" t="n">
         <v>362</v>
@@ -7377,22 +7377,22 @@
         <v>6</v>
       </c>
       <c r="M2" t="n">
+        <v>91</v>
+      </c>
+      <c r="N2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O2" t="n">
         <v>87</v>
       </c>
-      <c r="N2" t="n">
-        <v>52</v>
-      </c>
-      <c r="O2" t="n">
-        <v>83</v>
-      </c>
       <c r="P2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>1414.6</v>
@@ -7441,19 +7441,19 @@
         <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O3" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P3" t="n">
         <v>54</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="R3" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="S3" t="n">
         <v>1476.4</v>
@@ -7499,22 +7499,22 @@
         <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="N4" t="n">
+        <v>123</v>
+      </c>
+      <c r="O4" t="n">
+        <v>145</v>
+      </c>
+      <c r="P4" t="n">
         <v>125</v>
       </c>
-      <c r="O4" t="n">
-        <v>159</v>
-      </c>
-      <c r="P4" t="n">
-        <v>131</v>
-      </c>
       <c r="Q4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R4" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="S4" t="n">
         <v>1468.3</v>
@@ -7560,22 +7560,22 @@
         <v>11.8</v>
       </c>
       <c r="M5" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="N5" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="P5" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="Q5" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R5" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="S5" t="n">
         <v>1496.5</v>
@@ -7621,22 +7621,22 @@
         <v>-0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N6" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P6" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="Q6" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="R6" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S6" t="n">
         <v>1462.9</v>
@@ -7685,19 +7685,19 @@
         <v>227</v>
       </c>
       <c r="N7" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="O7" t="n">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="P7" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q7" t="n">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="R7" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="S7" t="n">
         <v>1513.3</v>
@@ -7743,22 +7743,22 @@
         <v>-6</v>
       </c>
       <c r="M8" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N8" t="n">
         <v>224</v>
       </c>
       <c r="O8" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P8" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q8" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="R8" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="S8" t="n">
         <v>1459.6</v>
@@ -7804,22 +7804,22 @@
         <v>-4.2</v>
       </c>
       <c r="M9" t="n">
+        <v>201</v>
+      </c>
+      <c r="N9" t="n">
+        <v>202</v>
+      </c>
+      <c r="O9" t="n">
+        <v>192</v>
+      </c>
+      <c r="P9" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>210</v>
+      </c>
+      <c r="R9" t="n">
         <v>203</v>
-      </c>
-      <c r="N9" t="n">
-        <v>204</v>
-      </c>
-      <c r="O9" t="n">
-        <v>206</v>
-      </c>
-      <c r="P9" t="n">
-        <v>190</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>204</v>
-      </c>
-      <c r="R9" t="n">
-        <v>204</v>
       </c>
       <c r="S9" t="n">
         <v>1451.3</v>
@@ -7976,22 +7976,22 @@
         <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="N2" t="n">
+        <v>69</v>
+      </c>
+      <c r="O2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P2" t="n">
         <v>61</v>
       </c>
-      <c r="O2" t="n">
-        <v>67</v>
-      </c>
-      <c r="P2" t="n">
-        <v>53</v>
-      </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="S2" t="n">
         <v>1485.7</v>
@@ -8040,19 +8040,19 @@
         <v>123</v>
       </c>
       <c r="N3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S3" t="n">
         <v>1524.5</v>
@@ -8098,22 +8098,22 @@
         <v>-2</v>
       </c>
       <c r="M4" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="N4" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O4" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q4" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R4" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="S4" t="n">
         <v>1504.8</v>
@@ -8159,22 +8159,22 @@
         <v>-8.6</v>
       </c>
       <c r="M5" t="n">
+        <v>120</v>
+      </c>
+      <c r="N5" t="n">
+        <v>119</v>
+      </c>
+      <c r="O5" t="n">
         <v>117</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>113</v>
       </c>
-      <c r="O5" t="n">
-        <v>116</v>
-      </c>
-      <c r="P5" t="n">
-        <v>107</v>
-      </c>
       <c r="Q5" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="S5" t="n">
         <v>1504.1</v>
@@ -8220,22 +8220,22 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N6" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="O6" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="P6" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q6" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="R6" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="S6" t="n">
         <v>1508.7</v>
@@ -8281,22 +8281,22 @@
         <v>14.4</v>
       </c>
       <c r="M7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N7" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
+        <v>72</v>
+      </c>
+      <c r="P7" t="n">
         <v>76</v>
       </c>
-      <c r="P7" t="n">
-        <v>86</v>
-      </c>
       <c r="Q7" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="R7" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="S7" t="n">
         <v>1515.8</v>
@@ -8342,22 +8342,22 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="N8" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O8" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>151</v>
+      </c>
+      <c r="R8" t="n">
         <v>157</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>139</v>
-      </c>
-      <c r="R8" t="n">
-        <v>155</v>
       </c>
       <c r="S8" t="n">
         <v>1523.8</v>
@@ -8403,22 +8403,22 @@
         <v>5.6</v>
       </c>
       <c r="M9" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="N9" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O9" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="P9" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="Q9" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="R9" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="S9" t="n">
         <v>1517.4</v>
@@ -8464,22 +8464,22 @@
         <v>-4.2</v>
       </c>
       <c r="M10" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="N10" t="n">
+        <v>160</v>
+      </c>
+      <c r="O10" t="n">
         <v>171</v>
       </c>
-      <c r="O10" t="n">
-        <v>176</v>
-      </c>
       <c r="P10" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="Q10" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="R10" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="S10" t="n">
         <v>1528.6</v>
@@ -8525,22 +8525,22 @@
         <v>-6.8</v>
       </c>
       <c r="M11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N11" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="O11" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="P11" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q11" t="n">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="R11" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S11" t="n">
         <v>1522.9</v>
@@ -8586,22 +8586,22 @@
         <v>-13.8</v>
       </c>
       <c r="M12" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="N12" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O12" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="P12" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q12" t="n">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="R12" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S12" t="n">
         <v>1566.8</v>
@@ -8767,10 +8767,10 @@
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -8819,22 +8819,22 @@
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
         <v>19</v>
       </c>
-      <c r="O3" t="n">
-        <v>15</v>
-      </c>
-      <c r="P3" t="n">
-        <v>18</v>
-      </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S3" t="n">
         <v>1639.2</v>
@@ -8880,22 +8880,22 @@
         <v>6.8</v>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N4" t="n">
         <v>38</v>
       </c>
       <c r="O4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P4" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="n">
         <v>26</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>32</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>30</v>
-      </c>
-      <c r="R4" t="n">
-        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1617.1</v>
@@ -8941,22 +8941,22 @@
         <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N5" t="n">
         <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S5" t="n">
         <v>1676</v>
@@ -9002,22 +9002,22 @@
         <v>-1.8</v>
       </c>
       <c r="M6" t="n">
+        <v>38</v>
+      </c>
+      <c r="N6" t="n">
+        <v>34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>32</v>
+      </c>
+      <c r="P6" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>34</v>
+      </c>
+      <c r="R6" t="n">
         <v>36</v>
-      </c>
-      <c r="N6" t="n">
-        <v>33</v>
-      </c>
-      <c r="O6" t="n">
-        <v>29</v>
-      </c>
-      <c r="P6" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>37</v>
-      </c>
-      <c r="R6" t="n">
-        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1641.6</v>
@@ -9063,13 +9063,13 @@
         <v>5.4</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
         <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
         <v>21</v>
@@ -9078,7 +9078,7 @@
         <v>27</v>
       </c>
       <c r="R7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="S7" t="n">
         <v>1682.1</v>
@@ -9124,22 +9124,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S8" t="n">
         <v>1675.6</v>
@@ -9185,22 +9185,22 @@
         <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N9" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O9" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="P9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R9" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="S9" t="n">
         <v>1656.1</v>
@@ -9246,22 +9246,22 @@
         <v>-0.4</v>
       </c>
       <c r="M10" t="n">
+        <v>71</v>
+      </c>
+      <c r="N10" t="n">
+        <v>65</v>
+      </c>
+      <c r="O10" t="n">
         <v>73</v>
-      </c>
-      <c r="N10" t="n">
-        <v>66</v>
-      </c>
-      <c r="O10" t="n">
-        <v>71</v>
       </c>
       <c r="P10" t="n">
         <v>71</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S10" t="n">
         <v>1603.3</v>
@@ -9307,22 +9307,22 @@
         <v>6.2</v>
       </c>
       <c r="M11" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="N11" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="O11" t="n">
         <v>56</v>
       </c>
       <c r="P11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q11" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="R11" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="S11" t="n">
         <v>1628.4</v>
@@ -9368,22 +9368,22 @@
         <v>-4.2</v>
       </c>
       <c r="M12" t="n">
+        <v>43</v>
+      </c>
+      <c r="N12" t="n">
+        <v>49</v>
+      </c>
+      <c r="O12" t="n">
         <v>39</v>
       </c>
-      <c r="N12" t="n">
-        <v>45</v>
-      </c>
-      <c r="O12" t="n">
-        <v>37</v>
-      </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S12" t="n">
         <v>1643.1</v>
@@ -9429,22 +9429,22 @@
         <v>3.2</v>
       </c>
       <c r="M13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N13" t="n">
         <v>56</v>
       </c>
       <c r="O13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S13" t="n">
         <v>1665</v>
@@ -9490,22 +9490,22 @@
         <v>-2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N14" t="n">
+        <v>67</v>
+      </c>
+      <c r="O14" t="n">
+        <v>59</v>
+      </c>
+      <c r="P14" t="n">
         <v>70</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
+        <v>80</v>
+      </c>
+      <c r="R14" t="n">
         <v>64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>83</v>
-      </c>
-      <c r="R14" t="n">
-        <v>69</v>
       </c>
       <c r="S14" t="n">
         <v>1669.7</v>
@@ -9551,22 +9551,22 @@
         <v>-14.4</v>
       </c>
       <c r="M15" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q15" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="R15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="S15" t="n">
         <v>1659</v>
@@ -9618,16 +9618,16 @@
         <v>99</v>
       </c>
       <c r="O16" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q16" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="R16" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S16" t="n">
         <v>1658.7</v>
@@ -9784,22 +9784,22 @@
         <v>-7.6</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="n">
+        <v>30</v>
+      </c>
+      <c r="R2" t="n">
         <v>29</v>
-      </c>
-      <c r="R2" t="n">
-        <v>26</v>
       </c>
       <c r="S2" t="n">
         <v>1599.2</v>
@@ -9845,22 +9845,22 @@
         <v>-0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
         <v>52</v>
       </c>
       <c r="P3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>1652.6</v>
@@ -9906,22 +9906,22 @@
         <v>-2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1598.9</v>
@@ -9967,22 +9967,22 @@
         <v>10.8</v>
       </c>
       <c r="M5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N5" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="P5" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="R5" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="S5" t="n">
         <v>1572.8</v>
@@ -10028,22 +10028,22 @@
         <v>2.6</v>
       </c>
       <c r="M6" t="n">
+        <v>76</v>
+      </c>
+      <c r="N6" t="n">
+        <v>73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>88</v>
+      </c>
+      <c r="P6" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q6" t="n">
         <v>70</v>
       </c>
-      <c r="N6" t="n">
-        <v>68</v>
-      </c>
-      <c r="O6" t="n">
-        <v>84</v>
-      </c>
-      <c r="P6" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>56</v>
-      </c>
       <c r="R6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="S6" t="n">
         <v>1598.1</v>
@@ -10089,22 +10089,22 @@
         <v>12.2</v>
       </c>
       <c r="M7" t="n">
+        <v>55</v>
+      </c>
+      <c r="N7" t="n">
         <v>60</v>
       </c>
-      <c r="N7" t="n">
-        <v>63</v>
-      </c>
       <c r="O7" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P7" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="R7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="S7" t="n">
         <v>1622.1</v>
@@ -10150,22 +10150,22 @@
         <v>4.4</v>
       </c>
       <c r="M8" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N8" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O8" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="R8" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S8" t="n">
         <v>1561.4</v>
@@ -10211,22 +10211,22 @@
         <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N9" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="O9" t="n">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="P9" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="Q9" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="R9" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="S9" t="n">
         <v>1623.2</v>
@@ -10272,22 +10272,22 @@
         <v>3.8</v>
       </c>
       <c r="M10" t="n">
+        <v>98</v>
+      </c>
+      <c r="N10" t="n">
+        <v>108</v>
+      </c>
+      <c r="O10" t="n">
+        <v>102</v>
+      </c>
+      <c r="P10" t="n">
         <v>101</v>
       </c>
-      <c r="N10" t="n">
-        <v>118</v>
-      </c>
-      <c r="O10" t="n">
-        <v>108</v>
-      </c>
-      <c r="P10" t="n">
-        <v>105</v>
-      </c>
       <c r="Q10" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S10" t="n">
         <v>1558</v>
@@ -10333,22 +10333,22 @@
         <v>-6.6</v>
       </c>
       <c r="M11" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="N11" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O11" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="P11" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="R11" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="S11" t="n">
         <v>1589</v>
@@ -10394,19 +10394,19 @@
         <v>-9</v>
       </c>
       <c r="M12" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N12" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="O12" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P12" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q12" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="R12" t="n">
         <v>256</v>
@@ -10455,19 +10455,19 @@
         <v>-15.2</v>
       </c>
       <c r="M13" t="n">
+        <v>344</v>
+      </c>
+      <c r="N13" t="n">
+        <v>336</v>
+      </c>
+      <c r="O13" t="n">
+        <v>341</v>
+      </c>
+      <c r="P13" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q13" t="n">
         <v>346</v>
-      </c>
-      <c r="N13" t="n">
-        <v>334</v>
-      </c>
-      <c r="O13" t="n">
-        <v>342</v>
-      </c>
-      <c r="P13" t="n">
-        <v>353</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>344</v>
       </c>
       <c r="R13" t="n">
         <v>349</v>
@@ -10627,22 +10627,22 @@
         <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="N2" t="n">
         <v>228</v>
       </c>
       <c r="O2" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P2" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="Q2" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="R2" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="S2" t="n">
         <v>1378.3</v>
@@ -10688,22 +10688,22 @@
         <v>-4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="N3" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="O3" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="P3" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q3" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R3" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="S3" t="n">
         <v>1359.6</v>
@@ -10749,22 +10749,22 @@
         <v>4.6</v>
       </c>
       <c r="M4" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N4" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="O4" t="n">
+        <v>267</v>
+      </c>
+      <c r="P4" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>295</v>
+      </c>
+      <c r="R4" t="n">
         <v>275</v>
-      </c>
-      <c r="P4" t="n">
-        <v>268</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>303</v>
-      </c>
-      <c r="R4" t="n">
-        <v>278</v>
       </c>
       <c r="S4" t="n">
         <v>1376.8</v>
@@ -10810,22 +10810,22 @@
         <v>-2</v>
       </c>
       <c r="M5" t="n">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N5" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="O5" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P5" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q5" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="R5" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="S5" t="n">
         <v>1378.3</v>
@@ -10871,22 +10871,22 @@
         <v>7.4</v>
       </c>
       <c r="M6" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="N6" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O6" t="n">
+        <v>324</v>
+      </c>
+      <c r="P6" t="n">
         <v>326</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
+        <v>341</v>
+      </c>
+      <c r="R6" t="n">
         <v>332</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>342</v>
-      </c>
-      <c r="R6" t="n">
-        <v>335</v>
       </c>
       <c r="S6" t="n">
         <v>1382.7</v>
@@ -10932,22 +10932,22 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N7" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O7" t="n">
         <v>339</v>
       </c>
       <c r="P7" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q7" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="R7" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S7" t="n">
         <v>1387.9</v>
@@ -10993,22 +10993,22 @@
         <v>6.6</v>
       </c>
       <c r="M8" t="n">
+        <v>306</v>
+      </c>
+      <c r="N8" t="n">
+        <v>326</v>
+      </c>
+      <c r="O8" t="n">
+        <v>328</v>
+      </c>
+      <c r="P8" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q8" t="n">
         <v>316</v>
       </c>
-      <c r="N8" t="n">
-        <v>329</v>
-      </c>
-      <c r="O8" t="n">
-        <v>325</v>
-      </c>
-      <c r="P8" t="n">
-        <v>315</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>328</v>
-      </c>
       <c r="R8" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="S8" t="n">
         <v>1390.5</v>
@@ -11054,22 +11054,22 @@
         <v>-4.4</v>
       </c>
       <c r="M9" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O9" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P9" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q9" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="R9" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="S9" t="n">
         <v>1420</v>
@@ -11226,22 +11226,22 @@
         <v>19.8</v>
       </c>
       <c r="M2" t="n">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="N2" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="O2" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="P2" t="n">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="Q2" t="n">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="R2" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="S2" t="n">
         <v>1407.8</v>
@@ -11290,19 +11290,19 @@
         <v>282</v>
       </c>
       <c r="N3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O3" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="P3" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="R3" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="S3" t="n">
         <v>1402</v>
@@ -11348,22 +11348,22 @@
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="N4" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="O4" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="P4" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q4" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="R4" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="S4" t="n">
         <v>1408.8</v>
@@ -11409,22 +11409,22 @@
         <v>-4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N5" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="O5" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P5" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q5" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="R5" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="S5" t="n">
         <v>1377.9</v>
@@ -11470,22 +11470,22 @@
         <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="N6" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="O6" t="n">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="P6" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Q6" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="S6" t="n">
         <v>1379.3</v>
@@ -11531,19 +11531,19 @@
         <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N7" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O7" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="P7" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q7" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="R7" t="n">
         <v>263</v>
@@ -11592,22 +11592,22 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O8" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="Q8" t="n">
+        <v>311</v>
+      </c>
+      <c r="R8" t="n">
         <v>309</v>
-      </c>
-      <c r="R8" t="n">
-        <v>306</v>
       </c>
       <c r="S8" t="n">
         <v>1400.2</v>
@@ -11653,22 +11653,22 @@
         <v>-4.4</v>
       </c>
       <c r="M9" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="N9" t="n">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O9" t="n">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="P9" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q9" t="n">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="R9" t="n">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="S9" t="n">
         <v>1439.7</v>
@@ -11825,22 +11825,22 @@
         <v>13</v>
       </c>
       <c r="M2" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="N2" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="O2" t="n">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="P2" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="Q2" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="R2" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="S2" t="n">
         <v>1374.6</v>
@@ -11886,22 +11886,22 @@
         <v>5.6</v>
       </c>
       <c r="M3" t="n">
+        <v>290</v>
+      </c>
+      <c r="N3" t="n">
         <v>295</v>
       </c>
-      <c r="N3" t="n">
-        <v>301</v>
-      </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="P3" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="Q3" t="n">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="R3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="S3" t="n">
         <v>1401.7</v>
@@ -11947,22 +11947,22 @@
         <v>-1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N4" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O4" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="P4" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q4" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="R4" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="S4" t="n">
         <v>1419.5</v>
@@ -12008,22 +12008,22 @@
         <v>3.6</v>
       </c>
       <c r="M5" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N5" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="O5" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="P5" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="Q5" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="R5" t="n">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="S5" t="n">
         <v>1379.2</v>
@@ -12069,19 +12069,19 @@
         <v>4.4</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N6" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O6" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P6" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q6" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="R6" t="n">
         <v>259</v>
@@ -12130,19 +12130,19 @@
         <v>-7.8</v>
       </c>
       <c r="M7" t="n">
+        <v>323</v>
+      </c>
+      <c r="N7" t="n">
+        <v>332</v>
+      </c>
+      <c r="O7" t="n">
+        <v>297</v>
+      </c>
+      <c r="P7" t="n">
         <v>322</v>
       </c>
-      <c r="N7" t="n">
-        <v>331</v>
-      </c>
-      <c r="O7" t="n">
-        <v>293</v>
-      </c>
-      <c r="P7" t="n">
-        <v>321</v>
-      </c>
       <c r="Q7" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="R7" t="n">
         <v>328</v>
@@ -12191,22 +12191,22 @@
         <v>-1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N8" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O8" t="n">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="P8" t="n">
         <v>325</v>
       </c>
       <c r="Q8" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R8" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="S8" t="n">
         <v>1388.5</v>
@@ -12252,22 +12252,22 @@
         <v>-2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="N9" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O9" t="n">
+        <v>325</v>
+      </c>
+      <c r="P9" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>329</v>
+      </c>
+      <c r="R9" t="n">
         <v>333</v>
-      </c>
-      <c r="P9" t="n">
-        <v>336</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>331</v>
-      </c>
-      <c r="R9" t="n">
-        <v>337</v>
       </c>
       <c r="S9" t="n">
         <v>1410.7</v>
@@ -12313,22 +12313,22 @@
         <v>-5.2</v>
       </c>
       <c r="M10" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N10" t="n">
+        <v>339</v>
+      </c>
+      <c r="O10" t="n">
+        <v>334</v>
+      </c>
+      <c r="P10" t="n">
         <v>338</v>
       </c>
-      <c r="O10" t="n">
-        <v>327</v>
-      </c>
-      <c r="P10" t="n">
-        <v>337</v>
-      </c>
       <c r="Q10" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="R10" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S10" t="n">
         <v>1381.7</v>
@@ -12374,22 +12374,22 @@
         <v>-3.6</v>
       </c>
       <c r="M11" t="n">
+        <v>330</v>
+      </c>
+      <c r="N11" t="n">
+        <v>337</v>
+      </c>
+      <c r="O11" t="n">
+        <v>338</v>
+      </c>
+      <c r="P11" t="n">
         <v>332</v>
       </c>
-      <c r="N11" t="n">
-        <v>340</v>
-      </c>
-      <c r="O11" t="n">
-        <v>341</v>
-      </c>
-      <c r="P11" t="n">
-        <v>334</v>
-      </c>
       <c r="Q11" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R11" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S11" t="n">
         <v>1382.1</v>
@@ -12549,7 +12549,7 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -12558,7 +12558,7 @@
         <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
         <v>4</v>
@@ -12613,16 +12613,16 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
         <v>14</v>
       </c>
-      <c r="Q3" t="n">
-        <v>16</v>
-      </c>
       <c r="R3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S3" t="n">
         <v>1772.1</v>
@@ -12668,22 +12668,22 @@
         <v>2.6</v>
       </c>
       <c r="M4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>21</v>
+      </c>
+      <c r="R4" t="n">
         <v>18</v>
-      </c>
-      <c r="O4" t="n">
-        <v>24</v>
-      </c>
-      <c r="P4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R4" t="n">
-        <v>19</v>
       </c>
       <c r="S4" t="n">
         <v>1728.7</v>
@@ -12729,22 +12729,22 @@
         <v>-0.6</v>
       </c>
       <c r="M5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>19</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
         <v>14</v>
       </c>
-      <c r="N5" t="n">
-        <v>20</v>
-      </c>
-      <c r="O5" t="n">
-        <v>18</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>22</v>
+      </c>
+      <c r="R5" t="n">
         <v>16</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>18</v>
-      </c>
-      <c r="R5" t="n">
-        <v>18</v>
       </c>
       <c r="S5" t="n">
         <v>1694.9</v>
@@ -12790,13 +12790,13 @@
         <v>2.6</v>
       </c>
       <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17</v>
+      </c>
+      <c r="O6" t="n">
         <v>18</v>
-      </c>
-      <c r="N6" t="n">
-        <v>16</v>
-      </c>
-      <c r="O6" t="n">
-        <v>20</v>
       </c>
       <c r="P6" t="n">
         <v>20</v>
@@ -12805,7 +12805,7 @@
         <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S6" t="n">
         <v>1706.1</v>
@@ -12851,16 +12851,16 @@
         <v>-0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q7" t="n">
         <v>41</v>
@@ -12912,19 +12912,19 @@
         <v>7.6</v>
       </c>
       <c r="M8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>31</v>
@@ -12973,22 +12973,22 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O9" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="S9" t="n">
         <v>1651.9</v>
@@ -13034,22 +13034,22 @@
         <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="R10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S10" t="n">
         <v>1728.4</v>
@@ -13095,22 +13095,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="O11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="R11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1699.4</v>
@@ -13156,22 +13156,22 @@
         <v>8.6</v>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P12" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q12" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="R12" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="S12" t="n">
         <v>1663.6</v>
@@ -13217,19 +13217,19 @@
         <v>-3</v>
       </c>
       <c r="M13" t="n">
+        <v>39</v>
+      </c>
+      <c r="N13" t="n">
+        <v>31</v>
+      </c>
+      <c r="O13" t="n">
+        <v>44</v>
+      </c>
+      <c r="P13" t="n">
         <v>40</v>
       </c>
-      <c r="N13" t="n">
-        <v>29</v>
-      </c>
-      <c r="O13" t="n">
-        <v>42</v>
-      </c>
-      <c r="P13" t="n">
-        <v>41</v>
-      </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R13" t="n">
         <v>38</v>
@@ -13278,22 +13278,22 @@
         <v>-19.4</v>
       </c>
       <c r="M14" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O14" t="n">
         <v>91</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q14" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="S14" t="n">
         <v>1703.2</v>
@@ -13339,22 +13339,22 @@
         <v>-7.2</v>
       </c>
       <c r="M15" t="n">
+        <v>95</v>
+      </c>
+      <c r="N15" t="n">
+        <v>96</v>
+      </c>
+      <c r="O15" t="n">
         <v>94</v>
       </c>
-      <c r="N15" t="n">
-        <v>97</v>
-      </c>
-      <c r="O15" t="n">
-        <v>99</v>
-      </c>
       <c r="P15" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="R15" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S15" t="n">
         <v>1653.5</v>
@@ -13400,22 +13400,22 @@
         <v>-5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N16" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="O16" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P16" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="Q16" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="R16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S16" t="n">
         <v>1688.2</v>
@@ -13461,22 +13461,22 @@
         <v>-6.6</v>
       </c>
       <c r="M17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N17" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O17" t="n">
+        <v>66</v>
+      </c>
+      <c r="P17" t="n">
         <v>68</v>
       </c>
-      <c r="P17" t="n">
-        <v>63</v>
-      </c>
       <c r="Q17" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R17" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="S17" t="n">
         <v>1660.6</v>
@@ -13633,7 +13633,7 @@
         <v>2.4</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="N2" t="n">
         <v>149</v>
@@ -13642,13 +13642,13 @@
         <v>162</v>
       </c>
       <c r="P2" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R2" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S2" t="n">
         <v>1416.5</v>
@@ -13694,22 +13694,22 @@
         <v>-0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N3" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="O3" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="P3" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="Q3" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R3" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="S3" t="n">
         <v>1450.7</v>
@@ -13755,22 +13755,22 @@
         <v>-1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="N4" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="O4" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="P4" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="R4" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="S4" t="n">
         <v>1426</v>
@@ -13816,22 +13816,22 @@
         <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N5" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="O5" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P5" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q5" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R5" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="S5" t="n">
         <v>1439.5</v>
@@ -13877,22 +13877,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="N6" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O6" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="P6" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="Q6" t="n">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="R6" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="S6" t="n">
         <v>1473.5</v>
@@ -13938,22 +13938,22 @@
         <v>4.4</v>
       </c>
       <c r="M7" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N7" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="O7" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="P7" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q7" t="n">
         <v>192</v>
       </c>
-      <c r="Q7" t="n">
-        <v>189</v>
-      </c>
       <c r="R7" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="S7" t="n">
         <v>1417.8</v>
@@ -13999,22 +13999,22 @@
         <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N8" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O8" t="n">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="P8" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q8" t="n">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="R8" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="S8" t="n">
         <v>1428.1</v>
@@ -14060,22 +14060,22 @@
         <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N9" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="O9" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="P9" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q9" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="R9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S9" t="n">
         <v>1422.3</v>
@@ -14121,22 +14121,22 @@
         <v>-8.6</v>
       </c>
       <c r="M10" t="n">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="N10" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="P10" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="Q10" t="n">
+        <v>336</v>
+      </c>
+      <c r="R10" t="n">
         <v>345</v>
-      </c>
-      <c r="R10" t="n">
-        <v>350</v>
       </c>
       <c r="S10" t="n">
         <v>1419.9</v>
@@ -14185,19 +14185,19 @@
         <v>360</v>
       </c>
       <c r="N11" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O11" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q11" t="n">
         <v>358</v>
       </c>
       <c r="R11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S11" t="n">
         <v>1429.4</v>
@@ -14354,22 +14354,22 @@
         <v>7.6</v>
       </c>
       <c r="M2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N2" t="n">
         <v>102</v>
       </c>
       <c r="O2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S2" t="n">
         <v>1383.2</v>
@@ -14415,22 +14415,22 @@
         <v>9.4</v>
       </c>
       <c r="M3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O3" t="n">
         <v>62</v>
       </c>
       <c r="P3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S3" t="n">
         <v>1423</v>
@@ -14476,22 +14476,22 @@
         <v>7.8</v>
       </c>
       <c r="M4" t="n">
+        <v>124</v>
+      </c>
+      <c r="N4" t="n">
+        <v>186</v>
+      </c>
+      <c r="O4" t="n">
         <v>127</v>
       </c>
-      <c r="N4" t="n">
-        <v>185</v>
-      </c>
-      <c r="O4" t="n">
-        <v>128</v>
-      </c>
       <c r="P4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R4" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="S4" t="n">
         <v>1426.5</v>
@@ -14537,19 +14537,19 @@
         <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="N5" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O5" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="P5" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q5" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="R5" t="n">
         <v>196</v>
@@ -14598,22 +14598,22 @@
         <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="N6" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="O6" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="P6" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="Q6" t="n">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="R6" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="S6" t="n">
         <v>1453</v>
@@ -14659,22 +14659,22 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="N7" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="O7" t="n">
+        <v>227</v>
+      </c>
+      <c r="P7" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>235</v>
+      </c>
+      <c r="R7" t="n">
         <v>246</v>
-      </c>
-      <c r="P7" t="n">
-        <v>249</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>238</v>
-      </c>
-      <c r="R7" t="n">
-        <v>251</v>
       </c>
       <c r="S7" t="n">
         <v>1425.9</v>
@@ -14720,22 +14720,22 @@
         <v>-3</v>
       </c>
       <c r="M8" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="N8" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="O8" t="n">
         <v>278</v>
       </c>
       <c r="P8" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="Q8" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="R8" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="S8" t="n">
         <v>1438.9</v>
@@ -14781,22 +14781,22 @@
         <v>-5.8</v>
       </c>
       <c r="M9" t="n">
+        <v>289</v>
+      </c>
+      <c r="N9" t="n">
         <v>300</v>
       </c>
-      <c r="N9" t="n">
-        <v>306</v>
-      </c>
       <c r="O9" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="P9" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="Q9" t="n">
+        <v>293</v>
+      </c>
+      <c r="R9" t="n">
         <v>294</v>
-      </c>
-      <c r="R9" t="n">
-        <v>301</v>
       </c>
       <c r="S9" t="n">
         <v>1421.3</v>
@@ -14953,22 +14953,22 @@
         <v>10.8</v>
       </c>
       <c r="M2" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N2" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="O2" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P2" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="Q2" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R2" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S2" t="n">
         <v>1410.6</v>
@@ -15014,22 +15014,22 @@
         <v>9.4</v>
       </c>
       <c r="M3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N3" t="n">
         <v>129</v>
       </c>
       <c r="O3" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="R3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S3" t="n">
         <v>1395</v>
@@ -15075,22 +15075,22 @@
         <v>-6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="N4" t="n">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="O4" t="n">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="P4" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="Q4" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="R4" t="n">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="S4" t="n">
         <v>1468.8</v>
@@ -15139,19 +15139,19 @@
         <v>281</v>
       </c>
       <c r="N5" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O5" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="P5" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q5" t="n">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="R5" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="S5" t="n">
         <v>1423.8</v>
@@ -15197,19 +15197,19 @@
         <v>-6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N6" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P6" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q6" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R6" t="n">
         <v>258</v>
@@ -15258,22 +15258,22 @@
         <v>-4.6</v>
       </c>
       <c r="M7" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N7" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O7" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="P7" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>243</v>
+      </c>
+      <c r="R7" t="n">
         <v>241</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>225</v>
-      </c>
-      <c r="R7" t="n">
-        <v>234</v>
       </c>
       <c r="S7" t="n">
         <v>1449.1</v>
@@ -15319,22 +15319,22 @@
         <v>-0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N8" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O8" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P8" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q8" t="n">
         <v>256</v>
       </c>
       <c r="R8" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="S8" t="n">
         <v>1460.2</v>
@@ -15380,22 +15380,22 @@
         <v>12.4</v>
       </c>
       <c r="M9" t="n">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N9" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O9" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P9" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="Q9" t="n">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="R9" t="n">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="S9" t="n">
         <v>1440.1</v>
@@ -15441,22 +15441,22 @@
         <v>-22.2</v>
       </c>
       <c r="M10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N10" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O10" t="n">
+        <v>362</v>
+      </c>
+      <c r="P10" t="n">
         <v>361</v>
       </c>
-      <c r="P10" t="n">
-        <v>360</v>
-      </c>
       <c r="Q10" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="R10" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S10" t="n">
         <v>1432</v>
@@ -15613,22 +15613,22 @@
         <v>6.4</v>
       </c>
       <c r="M2" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N2" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O2" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P2" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="R2" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S2" t="n">
         <v>1466.1</v>
@@ -15674,22 +15674,22 @@
         <v>-3</v>
       </c>
       <c r="M3" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N3" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="O3" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P3" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="R3" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="S3" t="n">
         <v>1448.2</v>
@@ -15735,22 +15735,22 @@
         <v>-3.2</v>
       </c>
       <c r="M4" t="n">
+        <v>247</v>
+      </c>
+      <c r="N4" t="n">
+        <v>201</v>
+      </c>
+      <c r="O4" t="n">
+        <v>236</v>
+      </c>
+      <c r="P4" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>178</v>
+      </c>
+      <c r="R4" t="n">
         <v>231</v>
-      </c>
-      <c r="N4" t="n">
-        <v>187</v>
-      </c>
-      <c r="O4" t="n">
-        <v>213</v>
-      </c>
-      <c r="P4" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>179</v>
-      </c>
-      <c r="R4" t="n">
-        <v>217</v>
       </c>
       <c r="S4" t="n">
         <v>1429.2</v>
@@ -15796,22 +15796,22 @@
         <v>-2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N5" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="O5" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="P5" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="Q5" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="R5" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="S5" t="n">
         <v>1423.8</v>
@@ -15857,22 +15857,22 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="N6" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="O6" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="P6" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q6" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="R6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S6" t="n">
         <v>1425.5</v>
@@ -15918,22 +15918,22 @@
         <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="O7" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P7" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>156</v>
+      </c>
+      <c r="R7" t="n">
         <v>185</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>134</v>
-      </c>
-      <c r="R7" t="n">
-        <v>176</v>
       </c>
       <c r="S7" t="n">
         <v>1442.8</v>
@@ -15979,22 +15979,22 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
+        <v>148</v>
+      </c>
+      <c r="N8" t="n">
+        <v>142</v>
+      </c>
+      <c r="O8" t="n">
+        <v>172</v>
+      </c>
+      <c r="P8" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q8" t="n">
         <v>143</v>
       </c>
-      <c r="N8" t="n">
-        <v>137</v>
-      </c>
-      <c r="O8" t="n">
-        <v>151</v>
-      </c>
-      <c r="P8" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>140</v>
-      </c>
       <c r="R8" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="S8" t="n">
         <v>1449.7</v>
@@ -16040,22 +16040,22 @@
         <v>5.6</v>
       </c>
       <c r="M9" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N9" t="n">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="O9" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="P9" t="n">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="Q9" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="R9" t="n">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="S9" t="n">
         <v>1471</v>
@@ -16101,19 +16101,19 @@
         <v>7.8</v>
       </c>
       <c r="M10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N10" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="O10" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="P10" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q10" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="R10" t="n">
         <v>207</v>
@@ -16162,22 +16162,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="N11" t="n">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="O11" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="P11" t="n">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="Q11" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="R11" t="n">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="S11" t="n">
         <v>1444.4</v>
@@ -16223,22 +16223,22 @@
         <v>-0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="N12" t="n">
+        <v>258</v>
+      </c>
+      <c r="O12" t="n">
+        <v>237</v>
+      </c>
+      <c r="P12" t="n">
         <v>255</v>
       </c>
-      <c r="O12" t="n">
-        <v>235</v>
-      </c>
-      <c r="P12" t="n">
-        <v>250</v>
-      </c>
       <c r="Q12" t="n">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="R12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S12" t="n">
         <v>1469.1</v>
@@ -16284,22 +16284,22 @@
         <v>-7</v>
       </c>
       <c r="M13" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N13" t="n">
         <v>281</v>
       </c>
       <c r="O13" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P13" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q13" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R13" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="S13" t="n">
         <v>1467.5</v>
@@ -16345,22 +16345,22 @@
         <v>-7</v>
       </c>
       <c r="M14" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="N14" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="O14" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P14" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="Q14" t="n">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="R14" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="S14" t="n">
         <v>1454.5</v>
@@ -16406,13 +16406,13 @@
         <v>-13.2</v>
       </c>
       <c r="M15" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N15" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O15" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="P15" t="n">
         <v>355</v>
@@ -16578,22 +16578,22 @@
         <v>4.8</v>
       </c>
       <c r="M2" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N2" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O2" t="n">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="P2" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q2" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="R2" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="S2" t="n">
         <v>1436.6</v>
@@ -16639,22 +16639,22 @@
         <v>6.6</v>
       </c>
       <c r="M3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N3" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="O3" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P3" t="n">
         <v>320</v>
       </c>
       <c r="Q3" t="n">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="R3" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="S3" t="n">
         <v>1379.3</v>
@@ -16700,22 +16700,22 @@
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N4" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="O4" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P4" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Q4" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="R4" t="n">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="S4" t="n">
         <v>1401.7</v>
@@ -16761,22 +16761,22 @@
         <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="N5" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O5" t="n">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="P5" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="Q5" t="n">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="R5" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="S5" t="n">
         <v>1389.8</v>
@@ -16822,22 +16822,22 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N6" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O6" t="n">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P6" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="Q6" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R6" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="S6" t="n">
         <v>1362.1</v>
@@ -16883,22 +16883,22 @@
         <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="N7" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O7" t="n">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="P7" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>299</v>
+      </c>
+      <c r="R7" t="n">
         <v>317</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>276</v>
-      </c>
-      <c r="R7" t="n">
-        <v>324</v>
       </c>
       <c r="S7" t="n">
         <v>1388.9</v>
@@ -16944,22 +16944,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="N8" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O8" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P8" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="Q8" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="R8" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="S8" t="n">
         <v>1425.2</v>
@@ -17005,22 +17005,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="N9" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="O9" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="P9" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="Q9" t="n">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="R9" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="S9" t="n">
         <v>1390.4</v>
@@ -17066,22 +17066,22 @@
         <v>-0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="N10" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O10" t="n">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="P10" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q10" t="n">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="R10" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="S10" t="n">
         <v>1363.2</v>
@@ -17127,22 +17127,22 @@
         <v>-6.4</v>
       </c>
       <c r="M11" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N11" t="n">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="O11" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="P11" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="Q11" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R11" t="n">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="S11" t="n">
         <v>1386.1</v>
@@ -17188,22 +17188,22 @@
         <v>-8</v>
       </c>
       <c r="M12" t="n">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="N12" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="O12" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="P12" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="Q12" t="n">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="R12" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="S12" t="n">
         <v>1413.6</v>
@@ -17255,7 +17255,7 @@
         <v>365</v>
       </c>
       <c r="O13" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P13" t="n">
         <v>365</v>
@@ -17421,22 +17421,22 @@
         <v>19.6</v>
       </c>
       <c r="M2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N2" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O2" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="P2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="R2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>1553.3</v>
@@ -17482,16 +17482,16 @@
         <v>18.8</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N3" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q3" t="n">
         <v>60</v>
@@ -17543,22 +17543,22 @@
         <v>11.2</v>
       </c>
       <c r="M4" t="n">
+        <v>88</v>
+      </c>
+      <c r="N4" t="n">
+        <v>91</v>
+      </c>
+      <c r="O4" t="n">
         <v>89</v>
       </c>
-      <c r="N4" t="n">
-        <v>93</v>
-      </c>
-      <c r="O4" t="n">
-        <v>93</v>
-      </c>
       <c r="P4" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Q4" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="R4" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="S4" t="n">
         <v>1534.8</v>
@@ -17604,22 +17604,22 @@
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N5" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="O5" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P5" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="Q5" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="R5" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="S5" t="n">
         <v>1499.7</v>
@@ -17665,22 +17665,22 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O6" t="n">
+        <v>152</v>
+      </c>
+      <c r="P6" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>136</v>
+      </c>
+      <c r="R6" t="n">
         <v>145</v>
-      </c>
-      <c r="P6" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>156</v>
-      </c>
-      <c r="R6" t="n">
-        <v>143</v>
       </c>
       <c r="S6" t="n">
         <v>1505</v>
@@ -17726,22 +17726,22 @@
         <v>-1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N7" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O7" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="P7" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="Q7" t="n">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="R7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="S7" t="n">
         <v>1561.9</v>
@@ -17787,22 +17787,22 @@
         <v>-3.4</v>
       </c>
       <c r="M8" t="n">
+        <v>191</v>
+      </c>
+      <c r="N8" t="n">
+        <v>171</v>
+      </c>
+      <c r="O8" t="n">
+        <v>189</v>
+      </c>
+      <c r="P8" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>193</v>
+      </c>
+      <c r="R8" t="n">
         <v>183</v>
-      </c>
-      <c r="N8" t="n">
-        <v>162</v>
-      </c>
-      <c r="O8" t="n">
-        <v>178</v>
-      </c>
-      <c r="P8" t="n">
-        <v>193</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>169</v>
-      </c>
-      <c r="R8" t="n">
-        <v>169</v>
       </c>
       <c r="S8" t="n">
         <v>1500.4</v>
@@ -17848,22 +17848,22 @@
         <v>-7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O9" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="P9" t="n">
         <v>130</v>
       </c>
       <c r="Q9" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="R9" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="S9" t="n">
         <v>1607.8</v>
@@ -17909,22 +17909,22 @@
         <v>-17.2</v>
       </c>
       <c r="M10" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="N10" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P10" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="Q10" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="R10" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="S10" t="n">
         <v>1531.6</v>
@@ -17970,22 +17970,22 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="N11" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="O11" t="n">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="P11" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="Q11" t="n">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="R11" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="S11" t="n">
         <v>1500.5</v>
@@ -18142,13 +18142,13 @@
         <v>6.6</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O2" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P2" t="n">
         <v>82</v>
@@ -18157,7 +18157,7 @@
         <v>77</v>
       </c>
       <c r="R2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S2" t="n">
         <v>1455.5</v>
@@ -18203,22 +18203,22 @@
         <v>10.8</v>
       </c>
       <c r="M3" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="N3" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="O3" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="P3" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="Q3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="R3" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="S3" t="n">
         <v>1455.6</v>
@@ -18264,22 +18264,22 @@
         <v>-3.6</v>
       </c>
       <c r="M4" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N4" t="n">
         <v>180</v>
       </c>
       <c r="O4" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="P4" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q4" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="R4" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="S4" t="n">
         <v>1495.6</v>
@@ -18325,22 +18325,22 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
+        <v>156</v>
+      </c>
+      <c r="N5" t="n">
+        <v>155</v>
+      </c>
+      <c r="O5" t="n">
+        <v>156</v>
+      </c>
+      <c r="P5" t="n">
         <v>163</v>
       </c>
-      <c r="N5" t="n">
-        <v>168</v>
-      </c>
-      <c r="O5" t="n">
-        <v>165</v>
-      </c>
-      <c r="P5" t="n">
-        <v>170</v>
-      </c>
       <c r="Q5" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="R5" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="S5" t="n">
         <v>1461.3</v>
@@ -18386,22 +18386,22 @@
         <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N6" t="n">
         <v>264</v>
       </c>
       <c r="O6" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P6" t="n">
         <v>267</v>
       </c>
       <c r="Q6" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="R6" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S6" t="n">
         <v>1496.9</v>
@@ -18447,22 +18447,22 @@
         <v>-10.6</v>
       </c>
       <c r="M7" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="N7" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="O7" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="P7" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="Q7" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="R7" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="S7" t="n">
         <v>1497.3</v>
@@ -18508,22 +18508,22 @@
         <v>-6.2</v>
       </c>
       <c r="M8" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="N8" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O8" t="n">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="P8" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q8" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="R8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="S8" t="n">
         <v>1470.7</v>
@@ -18680,22 +18680,22 @@
         <v>13.6</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1597.9</v>
@@ -18747,16 +18747,16 @@
         <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
         <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S3" t="n">
         <v>1595.3</v>
@@ -18805,19 +18805,19 @@
         <v>37</v>
       </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="n">
         <v>36</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1566.6</v>
@@ -18863,22 +18863,22 @@
         <v>-2</v>
       </c>
       <c r="M5" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N5" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O5" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="P5" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q5" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="R5" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="S5" t="n">
         <v>1538.2</v>
@@ -18924,22 +18924,22 @@
         <v>-3</v>
       </c>
       <c r="M6" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O6" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="P6" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="Q6" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="R6" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="S6" t="n">
         <v>1568.8</v>
@@ -18985,22 +18985,22 @@
         <v>-8.4</v>
       </c>
       <c r="M7" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N7" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="O7" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P7" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="Q7" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="R7" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S7" t="n">
         <v>1533.2</v>
@@ -19046,22 +19046,22 @@
         <v>4.6</v>
       </c>
       <c r="M8" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N8" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O8" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="P8" t="n">
         <v>116</v>
       </c>
       <c r="Q8" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R8" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="S8" t="n">
         <v>1521.6</v>
@@ -19107,22 +19107,22 @@
         <v>-3</v>
       </c>
       <c r="M9" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P9" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Q9" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="R9" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="S9" t="n">
         <v>1564</v>
@@ -19168,22 +19168,22 @@
         <v>-6</v>
       </c>
       <c r="M10" t="n">
+        <v>196</v>
+      </c>
+      <c r="N10" t="n">
+        <v>194</v>
+      </c>
+      <c r="O10" t="n">
+        <v>250</v>
+      </c>
+      <c r="P10" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q10" t="n">
         <v>204</v>
       </c>
-      <c r="N10" t="n">
-        <v>207</v>
-      </c>
-      <c r="O10" t="n">
-        <v>244</v>
-      </c>
-      <c r="P10" t="n">
-        <v>225</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>214</v>
-      </c>
       <c r="R10" t="n">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="S10" t="n">
         <v>1534</v>
@@ -19229,22 +19229,22 @@
         <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N11" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="O11" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P11" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="Q11" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="R11" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="S11" t="n">
         <v>1515.5</v>
@@ -19290,22 +19290,22 @@
         <v>-6.6</v>
       </c>
       <c r="M12" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="N12" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="O12" t="n">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="P12" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="Q12" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="R12" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="S12" t="n">
         <v>1529.1</v>
@@ -19351,22 +19351,22 @@
         <v>-1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N13" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="O13" t="n">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="P13" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q13" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="R13" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S13" t="n">
         <v>1523.1</v>
@@ -19523,22 +19523,22 @@
         <v>18.8</v>
       </c>
       <c r="M2" t="n">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="N2" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="O2" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="P2" t="n">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="Q2" t="n">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="R2" t="n">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="S2" t="n">
         <v>1364.8</v>
@@ -19584,22 +19584,22 @@
         <v>5.6</v>
       </c>
       <c r="M3" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="N3" t="n">
+        <v>215</v>
+      </c>
+      <c r="O3" t="n">
+        <v>199</v>
+      </c>
+      <c r="P3" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>227</v>
+      </c>
+      <c r="R3" t="n">
         <v>223</v>
-      </c>
-      <c r="O3" t="n">
-        <v>220</v>
-      </c>
-      <c r="P3" t="n">
-        <v>227</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>228</v>
-      </c>
-      <c r="R3" t="n">
-        <v>226</v>
       </c>
       <c r="S3" t="n">
         <v>1392.4</v>
@@ -19645,22 +19645,22 @@
         <v>-15.6</v>
       </c>
       <c r="M4" t="n">
+        <v>332</v>
+      </c>
+      <c r="N4" t="n">
+        <v>313</v>
+      </c>
+      <c r="O4" t="n">
+        <v>337</v>
+      </c>
+      <c r="P4" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>281</v>
+      </c>
+      <c r="R4" t="n">
         <v>327</v>
-      </c>
-      <c r="N4" t="n">
-        <v>311</v>
-      </c>
-      <c r="O4" t="n">
-        <v>335</v>
-      </c>
-      <c r="P4" t="n">
-        <v>306</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>264</v>
-      </c>
-      <c r="R4" t="n">
-        <v>317</v>
       </c>
       <c r="S4" t="n">
         <v>1398.5</v>
@@ -19706,22 +19706,22 @@
         <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N5" t="n">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="O5" t="n">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="P5" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="Q5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R5" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="S5" t="n">
         <v>1402.9</v>
@@ -19767,22 +19767,22 @@
         <v>-2</v>
       </c>
       <c r="M6" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="N6" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O6" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="P6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q6" t="n">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="R6" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S6" t="n">
         <v>1413.3</v>
@@ -19831,19 +19831,19 @@
         <v>347</v>
       </c>
       <c r="N7" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="O7" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P7" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R7" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S7" t="n">
         <v>1378</v>
@@ -19892,19 +19892,19 @@
         <v>355</v>
       </c>
       <c r="N8" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O8" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="P8" t="n">
         <v>349</v>
       </c>
       <c r="Q8" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="S8" t="n">
         <v>1400.3</v>
@@ -19950,22 +19950,22 @@
         <v>-7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N9" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O9" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P9" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q9" t="n">
+        <v>348</v>
+      </c>
+      <c r="R9" t="n">
         <v>346</v>
-      </c>
-      <c r="R9" t="n">
-        <v>347</v>
       </c>
       <c r="S9" t="n">
         <v>1416.5</v>
@@ -20122,22 +20122,22 @@
         <v>5.6</v>
       </c>
       <c r="M2" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N2" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="P2" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q2" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="R2" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="S2" t="n">
         <v>1437</v>
@@ -20183,22 +20183,22 @@
         <v>-2.6</v>
       </c>
       <c r="M3" t="n">
+        <v>175</v>
+      </c>
+      <c r="N3" t="n">
+        <v>164</v>
+      </c>
+      <c r="O3" t="n">
+        <v>153</v>
+      </c>
+      <c r="P3" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>137</v>
+      </c>
+      <c r="R3" t="n">
         <v>165</v>
-      </c>
-      <c r="N3" t="n">
-        <v>157</v>
-      </c>
-      <c r="O3" t="n">
-        <v>144</v>
-      </c>
-      <c r="P3" t="n">
-        <v>143</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>115</v>
-      </c>
-      <c r="R3" t="n">
-        <v>156</v>
       </c>
       <c r="S3" t="n">
         <v>1405.9</v>
@@ -20244,22 +20244,22 @@
         <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N4" t="n">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="O4" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="P4" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="Q4" t="n">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="R4" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="S4" t="n">
         <v>1430.9</v>
@@ -20305,22 +20305,22 @@
         <v>-0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="N5" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="O5" t="n">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="P5" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="Q5" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="R5" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="S5" t="n">
         <v>1421.3</v>
@@ -20366,22 +20366,22 @@
         <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="N6" t="n">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="O6" t="n">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="P6" t="n">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="Q6" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="R6" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="S6" t="n">
         <v>1431.6</v>
@@ -20427,22 +20427,22 @@
         <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N7" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="O7" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="P7" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q7" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="R7" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S7" t="n">
         <v>1406.5</v>
@@ -20488,22 +20488,22 @@
         <v>-6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N8" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="O8" t="n">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="P8" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="Q8" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="R8" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="S8" t="n">
         <v>1422.5</v>
@@ -20549,19 +20549,19 @@
         <v>-0.8</v>
       </c>
       <c r="M9" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N9" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O9" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="P9" t="n">
         <v>272</v>
       </c>
       <c r="Q9" t="n">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="R9" t="n">
         <v>285</v>
@@ -20613,19 +20613,19 @@
         <v>294</v>
       </c>
       <c r="N10" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O10" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="P10" t="n">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="Q10" t="n">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="R10" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S10" t="n">
         <v>1398.5</v>
@@ -20671,22 +20671,22 @@
         <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="N11" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="O11" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P11" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="Q11" t="n">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="R11" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="S11" t="n">
         <v>1413.5</v>
@@ -20732,22 +20732,22 @@
         <v>-6.4</v>
       </c>
       <c r="M12" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N12" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O12" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P12" t="n">
         <v>340</v>
       </c>
       <c r="Q12" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S12" t="n">
         <v>1460.8</v>
@@ -20796,19 +20796,19 @@
         <v>341</v>
       </c>
       <c r="N13" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="O13" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="P13" t="n">
         <v>347</v>
       </c>
       <c r="Q13" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="R13" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="S13" t="n">
         <v>1410.7</v>
@@ -20974,10 +20974,10 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
@@ -21032,13 +21032,13 @@
         <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>7</v>
@@ -21087,22 +21087,22 @@
         <v>-3.4</v>
       </c>
       <c r="M4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q4" t="n">
         <v>16</v>
       </c>
-      <c r="N4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>19</v>
-      </c>
-      <c r="P4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>15</v>
       </c>
       <c r="S4" t="n">
         <v>1772.3</v>
@@ -21148,22 +21148,22 @@
         <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
+        <v>17</v>
+      </c>
+      <c r="R5" t="n">
         <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>13</v>
       </c>
       <c r="S5" t="n">
         <v>1762.7</v>
@@ -21215,16 +21215,16 @@
         <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
         <v>1686.9</v>
@@ -21270,22 +21270,22 @@
         <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q7" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="R7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1679.3</v>
@@ -21331,19 +21331,19 @@
         <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N8" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O8" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R8" t="n">
         <v>58</v>
@@ -21392,22 +21392,22 @@
         <v>-1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="P9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="R9" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="S9" t="n">
         <v>1687.9</v>
@@ -21453,22 +21453,22 @@
         <v>7.8</v>
       </c>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P10" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="R10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S10" t="n">
         <v>1716.2</v>
@@ -21514,10 +21514,10 @@
         <v>-5.4</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
         <v>22</v>
@@ -21526,10 +21526,10 @@
         <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S11" t="n">
         <v>1726.9</v>
@@ -21575,22 +21575,22 @@
         <v>-2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="N12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O12" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q12" t="n">
         <v>67</v>
       </c>
       <c r="R12" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="S12" t="n">
         <v>1695.4</v>
@@ -21636,22 +21636,22 @@
         <v>-3</v>
       </c>
       <c r="M13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P13" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="Q13" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="R13" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="S13" t="n">
         <v>1735.5</v>
@@ -21697,22 +21697,22 @@
         <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O14" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="R14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="S14" t="n">
         <v>1727.4</v>
@@ -21758,22 +21758,22 @@
         <v>-6</v>
       </c>
       <c r="M15" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O15" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P15" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Q15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R15" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="S15" t="n">
         <v>1693.9</v>
@@ -21819,10 +21819,10 @@
         <v>-12.6</v>
       </c>
       <c r="M16" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N16" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O16" t="n">
         <v>98</v>
@@ -21834,7 +21834,7 @@
         <v>112</v>
       </c>
       <c r="R16" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S16" t="n">
         <v>1704.2</v>
@@ -21880,22 +21880,22 @@
         <v>-14.2</v>
       </c>
       <c r="M17" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="N17" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="O17" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="P17" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="Q17" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="R17" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="S17" t="n">
         <v>1690.8</v>
@@ -22055,16 +22055,16 @@
         <v>21</v>
       </c>
       <c r="N2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O2" t="n">
         <v>17</v>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
       </c>
       <c r="P2" t="n">
         <v>17</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R2" t="n">
         <v>22</v>
@@ -22113,22 +22113,22 @@
         <v>6.6</v>
       </c>
       <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P3" t="n">
         <v>10</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>16</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
         <v>1660.9</v>
@@ -22174,19 +22174,19 @@
         <v>-0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N4" t="n">
         <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R4" t="n">
         <v>33</v>
@@ -22235,19 +22235,19 @@
         <v>-2</v>
       </c>
       <c r="M5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P5" t="n">
         <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R5" t="n">
         <v>56</v>
@@ -22296,22 +22296,22 @@
         <v>-1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O6" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="n">
         <v>84</v>
       </c>
       <c r="R6" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="S6" t="n">
         <v>1664.3</v>
@@ -22357,22 +22357,22 @@
         <v>-4</v>
       </c>
       <c r="M7" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="N7" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="O7" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="P7" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="Q7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R7" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="S7" t="n">
         <v>1606.7</v>
@@ -22418,22 +22418,22 @@
         <v>5.4</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="N8" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="O8" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="P8" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="Q8" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="R8" t="n">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="S8" t="n">
         <v>1680.7</v>
@@ -22479,22 +22479,22 @@
         <v>-1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N9" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S9" t="n">
         <v>1622.8</v>
@@ -22540,22 +22540,22 @@
         <v>-1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="P10" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="Q10" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R10" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S10" t="n">
         <v>1637.8</v>
@@ -22601,22 +22601,22 @@
         <v>-6</v>
       </c>
       <c r="M11" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N11" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O11" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="P11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="Q11" t="n">
+        <v>99</v>
+      </c>
+      <c r="R11" t="n">
         <v>97</v>
-      </c>
-      <c r="R11" t="n">
-        <v>95</v>
       </c>
       <c r="S11" t="n">
         <v>1639.3</v>
@@ -22662,22 +22662,22 @@
         <v>-5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N12" t="n">
         <v>95</v>
       </c>
       <c r="O12" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="P12" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>111</v>
+      </c>
+      <c r="R12" t="n">
         <v>95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>101</v>
-      </c>
-      <c r="R12" t="n">
-        <v>99</v>
       </c>
       <c r="S12" t="n">
         <v>1640.1</v>
@@ -22834,22 +22834,22 @@
         <v>-0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="N2" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="O2" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="P2" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="Q2" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="R2" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="S2" t="n">
         <v>1413.3</v>
@@ -22895,22 +22895,22 @@
         <v>5.6</v>
       </c>
       <c r="M3" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N3" t="n">
         <v>163</v>
       </c>
       <c r="O3" t="n">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q3" t="n">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="R3" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="S3" t="n">
         <v>1437.1</v>
@@ -22956,22 +22956,22 @@
         <v>11.4</v>
       </c>
       <c r="M4" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="N4" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="O4" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="P4" t="n">
         <v>204</v>
       </c>
       <c r="Q4" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="R4" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S4" t="n">
         <v>1454.6</v>
@@ -23017,22 +23017,22 @@
         <v>-7.6</v>
       </c>
       <c r="M5" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N5" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O5" t="n">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="P5" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="Q5" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="R5" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="S5" t="n">
         <v>1432.7</v>
@@ -23078,22 +23078,22 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="O6" t="n">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="P6" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="Q6" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="R6" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="S6" t="n">
         <v>1399.2</v>
@@ -23139,22 +23139,22 @@
         <v>-1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N7" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="O7" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="P7" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q7" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R7" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="S7" t="n">
         <v>1423.8</v>
@@ -23200,22 +23200,22 @@
         <v>8.4</v>
       </c>
       <c r="M8" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="O8" t="n">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="P8" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="Q8" t="n">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="R8" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="S8" t="n">
         <v>1416.4</v>
@@ -23261,22 +23261,22 @@
         <v>-8</v>
       </c>
       <c r="M9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N9" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="O9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P9" t="n">
         <v>303</v>
       </c>
       <c r="Q9" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="R9" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="S9" t="n">
         <v>1444.3</v>
@@ -23322,22 +23322,22 @@
         <v>-2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="N10" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O10" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q10" t="n">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="S10" t="n">
         <v>1426.8</v>
@@ -23383,22 +23383,22 @@
         <v>-14.2</v>
       </c>
       <c r="M11" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N11" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O11" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P11" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q11" t="n">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="R11" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="S11" t="n">
         <v>1433.8</v>
@@ -23555,19 +23555,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N2" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R2" t="n">
         <v>76</v>
@@ -23616,22 +23616,22 @@
         <v>-1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="N3" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O3" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="P3" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Q3" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="R3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S3" t="n">
         <v>1437.4</v>
@@ -23677,22 +23677,22 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N4" t="n">
+        <v>257</v>
+      </c>
+      <c r="O4" t="n">
+        <v>277</v>
+      </c>
+      <c r="P4" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>263</v>
+      </c>
+      <c r="R4" t="n">
         <v>251</v>
-      </c>
-      <c r="O4" t="n">
-        <v>281</v>
-      </c>
-      <c r="P4" t="n">
-        <v>252</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>258</v>
-      </c>
-      <c r="R4" t="n">
-        <v>250</v>
       </c>
       <c r="S4" t="n">
         <v>1419.6</v>
@@ -23738,22 +23738,22 @@
         <v>-2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="N5" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="O5" t="n">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="P5" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q5" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="R5" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="S5" t="n">
         <v>1428.4</v>
@@ -23799,22 +23799,22 @@
         <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N6" t="n">
+        <v>265</v>
+      </c>
+      <c r="O6" t="n">
+        <v>289</v>
+      </c>
+      <c r="P6" t="n">
         <v>266</v>
       </c>
-      <c r="O6" t="n">
-        <v>283</v>
-      </c>
-      <c r="P6" t="n">
-        <v>262</v>
-      </c>
       <c r="Q6" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="R6" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="S6" t="n">
         <v>1389.4</v>
@@ -23860,22 +23860,22 @@
         <v>-1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="N7" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="O7" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="P7" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Q7" t="n">
         <v>273</v>
       </c>
       <c r="R7" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="S7" t="n">
         <v>1412.3</v>
@@ -23921,22 +23921,22 @@
         <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N8" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O8" t="n">
+        <v>254</v>
+      </c>
+      <c r="P8" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>274</v>
+      </c>
+      <c r="R8" t="n">
         <v>243</v>
-      </c>
-      <c r="P8" t="n">
-        <v>257</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>304</v>
-      </c>
-      <c r="R8" t="n">
-        <v>241</v>
       </c>
       <c r="S8" t="n">
         <v>1394.8</v>
@@ -23982,22 +23982,22 @@
         <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N9" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="O9" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="P9" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q9" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="R9" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="S9" t="n">
         <v>1417.1</v>
@@ -24046,16 +24046,16 @@
         <v>361</v>
       </c>
       <c r="N10" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O10" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P10" t="n">
         <v>364</v>
       </c>
       <c r="Q10" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="R10" t="n">
         <v>361</v>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -17448,59 +17448,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1409</v>
+        <v>1455</v>
       </c>
       <c r="D3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>1679.9</v>
+        <v>1620</v>
       </c>
       <c r="F3" t="n">
-        <v>9.1937</v>
+        <v>1.5141</v>
       </c>
       <c r="G3" t="n">
-        <v>122.52</v>
+        <v>112.55</v>
       </c>
       <c r="H3" t="n">
-        <v>106.2</v>
+        <v>102</v>
       </c>
       <c r="I3" t="n">
-        <v>16.32</v>
+        <v>10.54</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2712</v>
+        <v>0.3477</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1456</v>
+        <v>0.1417</v>
       </c>
       <c r="L3" t="n">
-        <v>18.8</v>
+        <v>11.2</v>
       </c>
       <c r="M3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N3" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="O3" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="P3" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="R3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="S3" t="n">
-        <v>1503.5</v>
+        <v>1534.8</v>
       </c>
     </row>
     <row r="4">
@@ -17509,59 +17509,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wichita St</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1455</v>
+        <v>1409</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>1620</v>
+        <v>1679.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5141</v>
+        <v>9.1937</v>
       </c>
       <c r="G4" t="n">
-        <v>112.55</v>
+        <v>122.52</v>
       </c>
       <c r="H4" t="n">
-        <v>102</v>
+        <v>106.2</v>
       </c>
       <c r="I4" t="n">
-        <v>10.54</v>
+        <v>16.32</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3477</v>
+        <v>0.2712</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1417</v>
+        <v>0.1456</v>
       </c>
       <c r="L4" t="n">
-        <v>11.2</v>
+        <v>18.8</v>
       </c>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="N4" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="O4" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="R4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>1534.8</v>
+        <v>1503.5</v>
       </c>
     </row>
     <row r="5">
@@ -17631,59 +17631,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1317</v>
+        <v>1150</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E6" t="n">
-        <v>1532.3</v>
+        <v>1437.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.3186</v>
+        <v>1.3871</v>
       </c>
       <c r="G6" t="n">
-        <v>104.14</v>
+        <v>111.71</v>
       </c>
       <c r="H6" t="n">
-        <v>102.05</v>
+        <v>113.99</v>
       </c>
       <c r="I6" t="n">
-        <v>2.08</v>
+        <v>-2.27</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3367</v>
+        <v>0.298</v>
       </c>
       <c r="K6" t="n">
-        <v>0.157</v>
+        <v>0.1699</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>-3.4</v>
       </c>
       <c r="M6" t="n">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="N6" t="n">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="O6" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="P6" t="n">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="Q6" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="R6" t="n">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="S6" t="n">
-        <v>1505</v>
+        <v>1500.4</v>
       </c>
     </row>
     <row r="7">
@@ -17692,59 +17692,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FL Atlantic</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1194</v>
+        <v>1317</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>1570.6</v>
+        <v>1532.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3127</v>
+        <v>-5.3186</v>
       </c>
       <c r="G7" t="n">
-        <v>108.77</v>
+        <v>104.14</v>
       </c>
       <c r="H7" t="n">
-        <v>106.62</v>
+        <v>102.05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2933</v>
+        <v>0.3367</v>
       </c>
       <c r="K7" t="n">
-        <v>0.169</v>
+        <v>0.157</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="N7" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O7" t="n">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="P7" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="Q7" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="R7" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="S7" t="n">
-        <v>1561.9</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="8">
@@ -17753,59 +17753,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FL Atlantic</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1150</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1570.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.3127</v>
+      </c>
+      <c r="G8" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>106.62</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>125</v>
       </c>
-      <c r="E8" t="n">
-        <v>1437.1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.3871</v>
-      </c>
-      <c r="G8" t="n">
-        <v>111.71</v>
-      </c>
-      <c r="H8" t="n">
-        <v>113.99</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.1699</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>191</v>
-      </c>
       <c r="N8" t="n">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="O8" t="n">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="P8" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="Q8" t="n">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="R8" t="n">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="S8" t="n">
-        <v>1500.4</v>
+        <v>1561.9</v>
       </c>
     </row>
     <row r="9">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -4409,59 +4409,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MTSU</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1292</v>
+        <v>1256</v>
       </c>
       <c r="D5" t="n">
         <v>124</v>
       </c>
       <c r="E5" t="n">
-        <v>1489.7</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.8936</v>
+        <v>-1.7753</v>
       </c>
       <c r="G5" t="n">
-        <v>107.97</v>
+        <v>102.77</v>
       </c>
       <c r="H5" t="n">
-        <v>108.68</v>
+        <v>102.38</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.71</v>
+        <v>0.39</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2792</v>
+        <v>0.3278</v>
       </c>
       <c r="K5" t="n">
-        <v>0.158</v>
+        <v>0.176</v>
       </c>
       <c r="L5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="M5" t="n">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="N5" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="O5" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="P5" t="n">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="Q5" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="R5" t="n">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="S5" t="n">
-        <v>1523.7</v>
+        <v>1464.3</v>
       </c>
     </row>
     <row r="6">
@@ -4470,59 +4470,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kennesaw</t>
+          <t>MTSU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1244</v>
+        <v>1292</v>
       </c>
       <c r="D6" t="n">
         <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>1501.9</v>
+        <v>1489.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3344</v>
+        <v>-3.8936</v>
       </c>
       <c r="G6" t="n">
-        <v>110.51</v>
+        <v>107.97</v>
       </c>
       <c r="H6" t="n">
-        <v>108.69</v>
+        <v>108.68</v>
       </c>
       <c r="I6" t="n">
-        <v>1.82</v>
+        <v>-0.71</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3343</v>
+        <v>0.2792</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1639</v>
+        <v>0.158</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M6" t="n">
+        <v>171</v>
+      </c>
+      <c r="N6" t="n">
+        <v>143</v>
+      </c>
+      <c r="O6" t="n">
+        <v>135</v>
+      </c>
+      <c r="P6" t="n">
         <v>178</v>
       </c>
-      <c r="N6" t="n">
-        <v>159</v>
-      </c>
-      <c r="O6" t="n">
-        <v>149</v>
-      </c>
-      <c r="P6" t="n">
-        <v>184</v>
-      </c>
       <c r="Q6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="R6" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="S6" t="n">
-        <v>1469.9</v>
+        <v>1523.7</v>
       </c>
     </row>
     <row r="7">
@@ -4531,59 +4531,59 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louisiana Tech</t>
+          <t>Kennesaw</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1256</v>
+        <v>1244</v>
       </c>
       <c r="D7" t="n">
         <v>124</v>
       </c>
       <c r="E7" t="n">
-        <v>1506</v>
+        <v>1501.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7753</v>
+        <v>-0.3344</v>
       </c>
       <c r="G7" t="n">
-        <v>102.77</v>
+        <v>110.51</v>
       </c>
       <c r="H7" t="n">
-        <v>102.38</v>
+        <v>108.69</v>
       </c>
       <c r="I7" t="n">
-        <v>0.39</v>
+        <v>1.82</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3278</v>
+        <v>0.3343</v>
       </c>
       <c r="K7" t="n">
-        <v>0.176</v>
+        <v>0.1639</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="N7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O7" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="P7" t="n">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="Q7" t="n">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="R7" t="n">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="S7" t="n">
-        <v>1464.3</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="8">
@@ -4653,59 +4653,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Missouri St</t>
+          <t>Florida Intl</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1283</v>
+        <v>1198</v>
       </c>
       <c r="D9" t="n">
         <v>124</v>
       </c>
       <c r="E9" t="n">
-        <v>1395</v>
+        <v>1385.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3277</v>
+        <v>1.345</v>
       </c>
       <c r="G9" t="n">
-        <v>107.51</v>
+        <v>107.53</v>
       </c>
       <c r="H9" t="n">
-        <v>109.72</v>
+        <v>108.75</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.21</v>
+        <v>-1.22</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3194</v>
+        <v>0.3239</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1608</v>
+        <v>0.1733</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="N9" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O9" t="n">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="P9" t="n">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="Q9" t="n">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="R9" t="n">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="S9" t="n">
-        <v>1474.6</v>
+        <v>1494.2</v>
       </c>
     </row>
     <row r="10">
@@ -4714,59 +4714,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Florida Intl</t>
+          <t>Missouri St</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1198</v>
+        <v>1283</v>
       </c>
       <c r="D10" t="n">
         <v>124</v>
       </c>
       <c r="E10" t="n">
-        <v>1385.5</v>
+        <v>1395</v>
       </c>
       <c r="F10" t="n">
-        <v>1.345</v>
+        <v>1.3277</v>
       </c>
       <c r="G10" t="n">
-        <v>107.53</v>
+        <v>107.51</v>
       </c>
       <c r="H10" t="n">
-        <v>108.75</v>
+        <v>109.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.22</v>
+        <v>-2.21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3239</v>
+        <v>0.3194</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1733</v>
+        <v>0.1608</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="N10" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O10" t="n">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="P10" t="n">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="Q10" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="R10" t="n">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="S10" t="n">
-        <v>1494.2</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="11">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -3451,31 +3451,31 @@
         <v>1220</v>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>1574.5</v>
+        <v>1582</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7174</v>
+        <v>3.5064</v>
       </c>
       <c r="G4" t="n">
-        <v>113.98</v>
+        <v>113.54</v>
       </c>
       <c r="H4" t="n">
-        <v>102.46</v>
+        <v>102.66</v>
       </c>
       <c r="I4" t="n">
-        <v>11.53</v>
+        <v>10.88</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3039</v>
+        <v>0.3074</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1512</v>
+        <v>0.1523</v>
       </c>
       <c r="L4" t="n">
-        <v>20.2</v>
+        <v>13.6</v>
       </c>
       <c r="M4" t="n">
         <v>84</v>
@@ -3496,7 +3496,7 @@
         <v>88</v>
       </c>
       <c r="S4" t="n">
-        <v>1481.7</v>
+        <v>1484.4</v>
       </c>
     </row>
     <row r="5">
@@ -3512,31 +3512,31 @@
         <v>1284</v>
       </c>
       <c r="D5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E5" t="n">
-        <v>1447.4</v>
+        <v>1450.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1918</v>
+        <v>1.2494</v>
       </c>
       <c r="G5" t="n">
-        <v>106.48</v>
+        <v>106.72</v>
       </c>
       <c r="H5" t="n">
-        <v>105</v>
+        <v>104.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3065</v>
+        <v>0.3125</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1656</v>
+        <v>0.1626</v>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
         <v>181</v>
@@ -3557,7 +3557,7 @@
         <v>169</v>
       </c>
       <c r="S5" t="n">
-        <v>1458.5</v>
+        <v>1456.7</v>
       </c>
     </row>
     <row r="6">
@@ -3695,31 +3695,31 @@
         <v>1406</v>
       </c>
       <c r="D8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" t="n">
-        <v>1556.9</v>
+        <v>1549.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7806</v>
+        <v>-2.6439</v>
       </c>
       <c r="G8" t="n">
-        <v>104.06</v>
+        <v>103.89</v>
       </c>
       <c r="H8" t="n">
-        <v>102.39</v>
+        <v>102.85</v>
       </c>
       <c r="I8" t="n">
-        <v>1.67</v>
+        <v>1.03</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3357</v>
+        <v>0.3383</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1517</v>
+        <v>0.1498</v>
       </c>
       <c r="L8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>157</v>
@@ -3740,7 +3740,7 @@
         <v>160</v>
       </c>
       <c r="S8" t="n">
-        <v>1524.4</v>
+        <v>1525.9</v>
       </c>
     </row>
     <row r="9">
@@ -3817,31 +3817,31 @@
         <v>1144</v>
       </c>
       <c r="D10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E10" t="n">
-        <v>1405.6</v>
+        <v>1402.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1743</v>
+        <v>0.2622</v>
       </c>
       <c r="G10" t="n">
-        <v>109.09</v>
+        <v>108.49</v>
       </c>
       <c r="H10" t="n">
-        <v>112.48</v>
+        <v>112.58</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4</v>
+        <v>-4.09</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3406</v>
+        <v>0.3394</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1599</v>
+        <v>0.1674</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="M10" t="n">
         <v>177</v>
@@ -3862,7 +3862,7 @@
         <v>192</v>
       </c>
       <c r="S10" t="n">
-        <v>1523.3</v>
+        <v>1518.8</v>
       </c>
     </row>
     <row r="11">
@@ -4954,31 +4954,31 @@
         <v>1460</v>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E2" t="n">
-        <v>1464.5</v>
+        <v>1468.7</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7711</v>
+        <v>2.7502</v>
       </c>
       <c r="G2" t="n">
-        <v>115.65</v>
+        <v>116.22</v>
       </c>
       <c r="H2" t="n">
-        <v>109.07</v>
+        <v>109.52</v>
       </c>
       <c r="I2" t="n">
-        <v>6.58</v>
+        <v>6.7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2992</v>
+        <v>0.2952</v>
       </c>
       <c r="K2" t="n">
-        <v>0.158</v>
+        <v>0.1569</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="M2" t="n">
         <v>144</v>
@@ -4999,7 +4999,7 @@
         <v>133</v>
       </c>
       <c r="S2" t="n">
-        <v>1435.1</v>
+        <v>1435.9</v>
       </c>
     </row>
     <row r="3">
@@ -5015,31 +5015,31 @@
         <v>1352</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E3" t="n">
-        <v>1538.8</v>
+        <v>1532.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3441</v>
+        <v>-1.224</v>
       </c>
       <c r="G3" t="n">
-        <v>115.3</v>
+        <v>114.92</v>
       </c>
       <c r="H3" t="n">
-        <v>108.92</v>
+        <v>109.41</v>
       </c>
       <c r="I3" t="n">
-        <v>6.38</v>
+        <v>5.51</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3338</v>
+        <v>0.3375</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1748</v>
+        <v>0.1723</v>
       </c>
       <c r="L3" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="M3" t="n">
         <v>139</v>
@@ -5060,7 +5060,7 @@
         <v>135</v>
       </c>
       <c r="S3" t="n">
-        <v>1429.2</v>
+        <v>1424.9</v>
       </c>
     </row>
     <row r="4">
@@ -5076,31 +5076,31 @@
         <v>1178</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>1321.6</v>
+        <v>1327.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5666</v>
+        <v>1.6095</v>
       </c>
       <c r="G4" t="n">
-        <v>109.83</v>
+        <v>109.63</v>
       </c>
       <c r="H4" t="n">
-        <v>112.82</v>
+        <v>112.46</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.98</v>
+        <v>-2.83</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3117</v>
+        <v>0.3161</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1566</v>
+        <v>0.1604</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="M4" t="n">
         <v>222</v>
@@ -5121,7 +5121,7 @@
         <v>229</v>
       </c>
       <c r="S4" t="n">
-        <v>1449.2</v>
+        <v>1453.9</v>
       </c>
     </row>
     <row r="5">
@@ -5320,31 +5320,31 @@
         <v>1297</v>
       </c>
       <c r="D8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" t="n">
-        <v>1439</v>
+        <v>1434.8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2239</v>
+        <v>0.1976</v>
       </c>
       <c r="G8" t="n">
-        <v>113.32</v>
+        <v>113.17</v>
       </c>
       <c r="H8" t="n">
-        <v>108.95</v>
+        <v>109.87</v>
       </c>
       <c r="I8" t="n">
-        <v>4.37</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3154</v>
+        <v>0.3204</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1594</v>
+        <v>0.1609</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
         <v>172</v>
@@ -5365,7 +5365,7 @@
         <v>178</v>
       </c>
       <c r="S8" t="n">
-        <v>1427.9</v>
+        <v>1429.8</v>
       </c>
     </row>
     <row r="9">
@@ -13606,31 +13606,31 @@
         <v>1190</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" t="n">
-        <v>1518.5</v>
+        <v>1512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4929</v>
+        <v>0.4694</v>
       </c>
       <c r="G2" t="n">
-        <v>116.45</v>
+        <v>115.9</v>
       </c>
       <c r="H2" t="n">
-        <v>105.53</v>
+        <v>106.33</v>
       </c>
       <c r="I2" t="n">
-        <v>10.92</v>
+        <v>9.57</v>
       </c>
       <c r="J2" t="n">
-        <v>0.268</v>
+        <v>0.2698</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1456</v>
+        <v>0.1474</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4</v>
+        <v>-3</v>
       </c>
       <c r="M2" t="n">
         <v>147</v>
@@ -13651,7 +13651,7 @@
         <v>126</v>
       </c>
       <c r="S2" t="n">
-        <v>1416.5</v>
+        <v>1421.6</v>
       </c>
     </row>
     <row r="3">
@@ -13911,31 +13911,31 @@
         <v>1202</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
-        <v>1536.4</v>
+        <v>1542.9</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9002</v>
+        <v>0.8197</v>
       </c>
       <c r="G7" t="n">
-        <v>111.68</v>
+        <v>112.01</v>
       </c>
       <c r="H7" t="n">
-        <v>107.71</v>
+        <v>107.28</v>
       </c>
       <c r="I7" t="n">
-        <v>3.97</v>
+        <v>4.73</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2563</v>
+        <v>0.2562</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1715</v>
+        <v>0.171</v>
       </c>
       <c r="L7" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="M7" t="n">
         <v>199</v>
@@ -13956,7 +13956,7 @@
         <v>194</v>
       </c>
       <c r="S7" t="n">
-        <v>1417.8</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="8">
@@ -14449,31 +14449,31 @@
         <v>1410</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>1395</v>
+        <v>1397.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1.606</v>
+        <v>1.648</v>
       </c>
       <c r="G4" t="n">
-        <v>109.77</v>
+        <v>110.55</v>
       </c>
       <c r="H4" t="n">
-        <v>105.08</v>
+        <v>105.06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.69</v>
+        <v>5.49</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2419</v>
+        <v>0.2398</v>
       </c>
       <c r="K4" t="n">
-        <v>0.17</v>
+        <v>0.1713</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="M4" t="n">
         <v>124</v>
@@ -14494,7 +14494,7 @@
         <v>134</v>
       </c>
       <c r="S4" t="n">
-        <v>1426.5</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="5">
@@ -14510,31 +14510,31 @@
         <v>1394</v>
       </c>
       <c r="D5" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E5" t="n">
-        <v>1376.2</v>
+        <v>1378.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.451</v>
+        <v>-0.4106</v>
       </c>
       <c r="G5" t="n">
-        <v>102.17</v>
+        <v>103</v>
       </c>
       <c r="H5" t="n">
-        <v>103.54</v>
+        <v>103.53</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.38</v>
+        <v>-0.53</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2912</v>
+        <v>0.2959</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1805</v>
+        <v>0.1852</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="M5" t="n">
         <v>180</v>
@@ -14555,7 +14555,7 @@
         <v>196</v>
       </c>
       <c r="S5" t="n">
-        <v>1426.5</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6">
@@ -14571,31 +14571,31 @@
         <v>1309</v>
       </c>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
-        <v>1342</v>
+        <v>1339.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5805</v>
+        <v>0.6274</v>
       </c>
       <c r="G6" t="n">
-        <v>106.17</v>
+        <v>106.27</v>
       </c>
       <c r="H6" t="n">
-        <v>110.07</v>
+        <v>111.11</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.91</v>
+        <v>-4.84</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2927</v>
+        <v>0.3056</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1967</v>
+        <v>0.1946</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="M6" t="n">
         <v>182</v>
@@ -14616,7 +14616,7 @@
         <v>208</v>
       </c>
       <c r="S6" t="n">
-        <v>1453</v>
+        <v>1451.6</v>
       </c>
     </row>
     <row r="7">
@@ -14632,31 +14632,31 @@
         <v>1311</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
-        <v>1364.3</v>
+        <v>1361.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4633</v>
+        <v>-1.4014</v>
       </c>
       <c r="G7" t="n">
-        <v>104.33</v>
+        <v>104.28</v>
       </c>
       <c r="H7" t="n">
-        <v>109.7</v>
+        <v>110.79</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.37</v>
+        <v>-6.51</v>
       </c>
       <c r="J7" t="n">
-        <v>0.322</v>
+        <v>0.3239</v>
       </c>
       <c r="K7" t="n">
-        <v>0.168</v>
+        <v>0.1694</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="M7" t="n">
         <v>232</v>
@@ -14677,7 +14677,7 @@
         <v>246</v>
       </c>
       <c r="S7" t="n">
-        <v>1425.9</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="8">
@@ -15586,31 +15586,31 @@
         <v>1407</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" t="n">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2134</v>
+        <v>1.1284</v>
       </c>
       <c r="G2" t="n">
-        <v>111.85</v>
+        <v>112.28</v>
       </c>
       <c r="H2" t="n">
-        <v>106.58</v>
+        <v>106.19</v>
       </c>
       <c r="I2" t="n">
-        <v>5.27</v>
+        <v>6.08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3163</v>
+        <v>0.316</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1636</v>
+        <v>0.1667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="M2" t="n">
         <v>153</v>
@@ -15631,7 +15631,7 @@
         <v>132</v>
       </c>
       <c r="S2" t="n">
-        <v>1466.1</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="3">
@@ -16135,31 +16135,31 @@
         <v>1204</v>
       </c>
       <c r="D11" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11" t="n">
-        <v>1448.4</v>
+        <v>1444.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7301</v>
+        <v>0.7778</v>
       </c>
       <c r="G11" t="n">
-        <v>111.54</v>
+        <v>111.05</v>
       </c>
       <c r="H11" t="n">
-        <v>111.35</v>
+        <v>111.87</v>
       </c>
       <c r="I11" t="n">
-        <v>0.19</v>
+        <v>-0.83</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3152</v>
+        <v>0.3138</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1479</v>
+        <v>0.1492</v>
       </c>
       <c r="L11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
         <v>230</v>
@@ -16180,7 +16180,7 @@
         <v>219</v>
       </c>
       <c r="S11" t="n">
-        <v>1444.4</v>
+        <v>1449.5</v>
       </c>
     </row>
     <row r="12">
@@ -17039,31 +17039,31 @@
         <v>1212</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E10" t="n">
-        <v>1310.9</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5341</v>
+        <v>-0.5671</v>
       </c>
       <c r="G10" t="n">
-        <v>99.77</v>
+        <v>100.56</v>
       </c>
       <c r="H10" t="n">
-        <v>104.05</v>
+        <v>103.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.27</v>
+        <v>-2.53</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2971</v>
+        <v>0.2974</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2051</v>
+        <v>0.2044</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
         <v>298</v>
@@ -17084,7 +17084,7 @@
         <v>301</v>
       </c>
       <c r="S10" t="n">
-        <v>1363.2</v>
+        <v>1352.3</v>
       </c>
     </row>
     <row r="11">
@@ -17100,31 +17100,31 @@
         <v>1106</v>
       </c>
       <c r="D11" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E11" t="n">
-        <v>1291.5</v>
+        <v>1288.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5457</v>
+        <v>-2.4613</v>
       </c>
       <c r="G11" t="n">
-        <v>100.63</v>
+        <v>100.34</v>
       </c>
       <c r="H11" t="n">
-        <v>109.07</v>
+        <v>109.18</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.43</v>
+        <v>-8.84</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3236</v>
+        <v>0.3182</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1794</v>
+        <v>0.1776</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="M11" t="n">
         <v>317</v>
@@ -17145,7 +17145,7 @@
         <v>321</v>
       </c>
       <c r="S11" t="n">
-        <v>1386.1</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="12">
@@ -17161,31 +17161,31 @@
         <v>1108</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E12" t="n">
-        <v>1267.3</v>
+        <v>1270.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4578</v>
+        <v>-1.4276</v>
       </c>
       <c r="G12" t="n">
-        <v>95.94</v>
+        <v>97.17</v>
       </c>
       <c r="H12" t="n">
-        <v>115.85</v>
+        <v>114.96</v>
       </c>
       <c r="I12" t="n">
-        <v>-19.91</v>
+        <v>-17.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3027</v>
+        <v>0.3063</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1888</v>
+        <v>0.1856</v>
       </c>
       <c r="L12" t="n">
-        <v>-8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>351</v>
@@ -17206,7 +17206,7 @@
         <v>352</v>
       </c>
       <c r="S12" t="n">
-        <v>1413.6</v>
+        <v>1410.3</v>
       </c>
     </row>
     <row r="13">
@@ -17222,31 +17222,31 @@
         <v>1290</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E13" t="n">
-        <v>1094.9</v>
+        <v>1093.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9612</v>
+        <v>-2.8469</v>
       </c>
       <c r="G13" t="n">
-        <v>91.2</v>
+        <v>90.48</v>
       </c>
       <c r="H13" t="n">
-        <v>119.19</v>
+        <v>119.09</v>
       </c>
       <c r="I13" t="n">
-        <v>-27.98</v>
+        <v>-28.61</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2856</v>
+        <v>0.291</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2073</v>
+        <v>0.2104</v>
       </c>
       <c r="L13" t="n">
-        <v>-6</v>
+        <v>-11.2</v>
       </c>
       <c r="M13" t="n">
         <v>365</v>
@@ -17267,7 +17267,7 @@
         <v>365</v>
       </c>
       <c r="S13" t="n">
-        <v>1372.9</v>
+        <v>1371.1</v>
       </c>
     </row>
   </sheetData>
@@ -18653,31 +18653,31 @@
         <v>1211</v>
       </c>
       <c r="D2" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E2" t="n">
-        <v>2061.6</v>
+        <v>2063.2</v>
       </c>
       <c r="F2" t="n">
-        <v>6.7538</v>
+        <v>6.2559</v>
       </c>
       <c r="G2" t="n">
-        <v>120.35</v>
+        <v>120.06</v>
       </c>
       <c r="H2" t="n">
-        <v>93.25</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>27.1</v>
+        <v>27.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2992</v>
+        <v>0.2963</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1329</v>
+        <v>0.1337</v>
       </c>
       <c r="L2" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -18698,7 +18698,7 @@
         <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>1597.9</v>
+        <v>1593.1</v>
       </c>
     </row>
     <row r="3">
@@ -18714,31 +18714,31 @@
         <v>1388</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E3" t="n">
-        <v>1877.4</v>
+        <v>1857.8</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5286</v>
+        <v>-0.2818</v>
       </c>
       <c r="G3" t="n">
-        <v>118.87</v>
+        <v>118.73</v>
       </c>
       <c r="H3" t="n">
-        <v>98.81999999999999</v>
+        <v>99.88</v>
       </c>
       <c r="I3" t="n">
-        <v>20.05</v>
+        <v>18.85</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2966</v>
+        <v>0.2975</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1557</v>
+        <v>0.1525</v>
       </c>
       <c r="L3" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="M3" t="n">
         <v>22</v>
@@ -18759,7 +18759,7 @@
         <v>20</v>
       </c>
       <c r="S3" t="n">
-        <v>1595.3</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="4">
@@ -18775,31 +18775,31 @@
         <v>1365</v>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>1768.3</v>
+        <v>1787.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4727</v>
+        <v>-0.2548</v>
       </c>
       <c r="G4" t="n">
-        <v>117.67</v>
+        <v>117.9</v>
       </c>
       <c r="H4" t="n">
-        <v>102.69</v>
+        <v>103.18</v>
       </c>
       <c r="I4" t="n">
-        <v>14.97</v>
+        <v>14.72</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3472</v>
+        <v>0.3445</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1494</v>
+        <v>0.15</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="M4" t="n">
         <v>37</v>
@@ -18820,7 +18820,7 @@
         <v>42</v>
       </c>
       <c r="S4" t="n">
-        <v>1566.6</v>
+        <v>1580.2</v>
       </c>
     </row>
     <row r="5">
@@ -18836,31 +18836,31 @@
         <v>1333</v>
       </c>
       <c r="D5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E5" t="n">
-        <v>1551.5</v>
+        <v>1550</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8876</v>
+        <v>-2.6712</v>
       </c>
       <c r="G5" t="n">
-        <v>107.33</v>
+        <v>106.46</v>
       </c>
       <c r="H5" t="n">
-        <v>111.75</v>
+        <v>111.33</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.42</v>
+        <v>-4.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2465</v>
+        <v>0.2493</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1704</v>
+        <v>0.1707</v>
       </c>
       <c r="L5" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="M5" t="n">
         <v>179</v>
@@ -18881,7 +18881,7 @@
         <v>171</v>
       </c>
       <c r="S5" t="n">
-        <v>1538.2</v>
+        <v>1558.8</v>
       </c>
     </row>
     <row r="6">
@@ -22929,31 +22929,31 @@
         <v>1186</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.332</v>
+        <v>-1.1643</v>
       </c>
       <c r="G4" t="n">
-        <v>111.77</v>
+        <v>112.14</v>
       </c>
       <c r="H4" t="n">
-        <v>113.13</v>
+        <v>113.12</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.36</v>
+        <v>-0.98</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2923</v>
+        <v>0.2929</v>
       </c>
       <c r="K4" t="n">
         <v>0.1707</v>
       </c>
       <c r="L4" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="M4" t="n">
         <v>166</v>
@@ -22974,7 +22974,7 @@
         <v>201</v>
       </c>
       <c r="S4" t="n">
-        <v>1454.6</v>
+        <v>1451.5</v>
       </c>
     </row>
     <row r="5">
@@ -22990,31 +22990,31 @@
         <v>1285</v>
       </c>
       <c r="D5" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E5" t="n">
-        <v>1458.8</v>
+        <v>1464.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7046</v>
+        <v>-1.6217</v>
       </c>
       <c r="G5" t="n">
-        <v>106.42</v>
+        <v>107.79</v>
       </c>
       <c r="H5" t="n">
-        <v>109.34</v>
+        <v>109.83</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.92</v>
+        <v>-2.04</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1835</v>
+        <v>0.1846</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1926</v>
+        <v>0.1896</v>
       </c>
       <c r="L5" t="n">
-        <v>-7.6</v>
+        <v>-5.6</v>
       </c>
       <c r="M5" t="n">
         <v>187</v>
@@ -23035,7 +23035,7 @@
         <v>199</v>
       </c>
       <c r="S5" t="n">
-        <v>1432.7</v>
+        <v>1434.8</v>
       </c>
     </row>
     <row r="6">
@@ -23051,31 +23051,31 @@
         <v>1294</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
-        <v>1492.8</v>
+        <v>1487</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3144</v>
+        <v>-2.1857</v>
       </c>
       <c r="G6" t="n">
-        <v>112.56</v>
+        <v>112.83</v>
       </c>
       <c r="H6" t="n">
-        <v>107.84</v>
+        <v>108.91</v>
       </c>
       <c r="I6" t="n">
-        <v>4.72</v>
+        <v>3.92</v>
       </c>
       <c r="J6" t="n">
-        <v>0.22</v>
+        <v>0.2249</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1533</v>
+        <v>0.1497</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="M6" t="n">
         <v>136</v>
@@ -23096,7 +23096,7 @@
         <v>139</v>
       </c>
       <c r="S6" t="n">
-        <v>1399.2</v>
+        <v>1401.2</v>
       </c>
     </row>
     <row r="7">
@@ -23112,31 +23112,31 @@
         <v>1451</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
-        <v>1362.9</v>
+        <v>1359.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0298</v>
+        <v>-0.0016</v>
       </c>
       <c r="G7" t="n">
-        <v>111.29</v>
+        <v>111.69</v>
       </c>
       <c r="H7" t="n">
-        <v>111.44</v>
+        <v>111.82</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3076</v>
+        <v>0.305</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1552</v>
+        <v>0.1538</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
         <v>193</v>
@@ -23157,7 +23157,7 @@
         <v>197</v>
       </c>
       <c r="S7" t="n">
-        <v>1423.8</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="8">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -2375,31 +2375,31 @@
         <v>1321</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E16" t="n">
-        <v>1585.2</v>
+        <v>1591.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.3422</v>
+        <v>-4.0194</v>
       </c>
       <c r="G16" t="n">
-        <v>111</v>
+        <v>111.47</v>
       </c>
       <c r="H16" t="n">
-        <v>110.17</v>
+        <v>109.98</v>
       </c>
       <c r="I16" t="n">
-        <v>0.84</v>
+        <v>1.49</v>
       </c>
       <c r="J16" t="n">
-        <v>0.28</v>
+        <v>0.2813</v>
       </c>
       <c r="K16" t="n">
         <v>0.1277</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>66</v>
@@ -2420,7 +2420,7 @@
         <v>70</v>
       </c>
       <c r="S16" t="n">
-        <v>1700.2</v>
+        <v>1694.1</v>
       </c>
     </row>
     <row r="17">
@@ -2436,31 +2436,31 @@
         <v>1332</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E17" t="n">
-        <v>1603.3</v>
+        <v>1594.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.083399999999999</v>
+        <v>-8.546799999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>105.7</v>
+        <v>105.07</v>
       </c>
       <c r="H17" t="n">
         <v>110.42</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.72</v>
+        <v>-5.35</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3115</v>
+        <v>0.3131</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1704</v>
+        <v>0.1706</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2</v>
+        <v>-3.4</v>
       </c>
       <c r="M17" t="n">
         <v>96</v>
@@ -2481,7 +2481,7 @@
         <v>102</v>
       </c>
       <c r="S17" t="n">
-        <v>1731.6</v>
+        <v>1726.9</v>
       </c>
     </row>
     <row r="18">
@@ -2497,31 +2497,31 @@
         <v>1268</v>
       </c>
       <c r="D18" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E18" t="n">
-        <v>1598.1</v>
+        <v>1607.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.074299999999999</v>
+        <v>-7.8093</v>
       </c>
       <c r="G18" t="n">
-        <v>103.93</v>
+        <v>104.08</v>
       </c>
       <c r="H18" t="n">
-        <v>115.23</v>
+        <v>114.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-11.3</v>
+        <v>-10.12</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3204</v>
+        <v>0.3167</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1754</v>
+        <v>0.1739</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M18" t="n">
         <v>128</v>
@@ -2542,7 +2542,7 @@
         <v>151</v>
       </c>
       <c r="S18" t="n">
-        <v>1724.9</v>
+        <v>1715.9</v>
       </c>
     </row>
     <row r="19">
@@ -2558,31 +2558,31 @@
         <v>1336</v>
       </c>
       <c r="D19" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E19" t="n">
-        <v>1526.9</v>
+        <v>1520.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.224</v>
+        <v>-6.9424</v>
       </c>
       <c r="G19" t="n">
-        <v>109.42</v>
+        <v>109.32</v>
       </c>
       <c r="H19" t="n">
-        <v>117.68</v>
+        <v>117.76</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.26</v>
+        <v>-8.44</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2614</v>
+        <v>0.2608</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1489</v>
+        <v>0.1538</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.6</v>
+        <v>-15</v>
       </c>
       <c r="M19" t="n">
         <v>138</v>
@@ -2603,7 +2603,7 @@
         <v>131</v>
       </c>
       <c r="S19" t="n">
-        <v>1664.7</v>
+        <v>1662.7</v>
       </c>
     </row>
   </sheetData>
@@ -3451,31 +3451,31 @@
         <v>1220</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1582</v>
+        <v>1586.2</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5064</v>
+        <v>3.3583</v>
       </c>
       <c r="G4" t="n">
-        <v>113.54</v>
+        <v>113.56</v>
       </c>
       <c r="H4" t="n">
-        <v>102.66</v>
+        <v>102.69</v>
       </c>
       <c r="I4" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3074</v>
+        <v>0.3081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1523</v>
+        <v>0.1527</v>
       </c>
       <c r="L4" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
         <v>84</v>
@@ -3496,7 +3496,7 @@
         <v>88</v>
       </c>
       <c r="S4" t="n">
-        <v>1484.4</v>
+        <v>1482.3</v>
       </c>
     </row>
     <row r="5">
@@ -3512,31 +3512,31 @@
         <v>1284</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
-        <v>1450.7</v>
+        <v>1446.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2494</v>
+        <v>1.3087</v>
       </c>
       <c r="G5" t="n">
-        <v>106.72</v>
+        <v>106.67</v>
       </c>
       <c r="H5" t="n">
-        <v>104.8</v>
+        <v>105.29</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3125</v>
+        <v>0.3093</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1626</v>
+        <v>0.1622</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="M5" t="n">
         <v>181</v>
@@ -3557,7 +3557,7 @@
         <v>169</v>
       </c>
       <c r="S5" t="n">
-        <v>1456.7</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="6">
@@ -4599,31 +4599,31 @@
         <v>1240</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" t="n">
-        <v>1462.8</v>
+        <v>1458</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0476</v>
+        <v>-0.0097</v>
       </c>
       <c r="G8" t="n">
-        <v>106.29</v>
+        <v>106.04</v>
       </c>
       <c r="H8" t="n">
-        <v>106.84</v>
+        <v>106.93</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.55</v>
+        <v>-0.89</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2799</v>
+        <v>0.2826</v>
       </c>
       <c r="K8" t="n">
-        <v>0.16</v>
+        <v>0.1593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
         <v>204</v>
@@ -4644,7 +4644,7 @@
         <v>211</v>
       </c>
       <c r="S8" t="n">
-        <v>1466.3</v>
+        <v>1466.6</v>
       </c>
     </row>
     <row r="9">
@@ -4660,31 +4660,31 @@
         <v>1198</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E9" t="n">
-        <v>1385.5</v>
+        <v>1382.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.345</v>
+        <v>1.3273</v>
       </c>
       <c r="G9" t="n">
-        <v>107.53</v>
+        <v>107.63</v>
       </c>
       <c r="H9" t="n">
-        <v>108.75</v>
+        <v>109.21</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.22</v>
+        <v>-1.57</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3239</v>
+        <v>0.3212</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1733</v>
+        <v>0.1739</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="M9" t="n">
         <v>190</v>
@@ -4705,7 +4705,7 @@
         <v>191</v>
       </c>
       <c r="S9" t="n">
-        <v>1494.2</v>
+        <v>1490.2</v>
       </c>
     </row>
     <row r="10">
@@ -4721,31 +4721,31 @@
         <v>1283</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E10" t="n">
-        <v>1395</v>
+        <v>1397.6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3277</v>
+        <v>1.1993</v>
       </c>
       <c r="G10" t="n">
-        <v>107.51</v>
+        <v>107.89</v>
       </c>
       <c r="H10" t="n">
-        <v>109.72</v>
+        <v>109.73</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.21</v>
+        <v>-1.84</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3194</v>
+        <v>0.324</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1608</v>
+        <v>0.1631</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="M10" t="n">
         <v>215</v>
@@ -4766,7 +4766,7 @@
         <v>214</v>
       </c>
       <c r="S10" t="n">
-        <v>1474.6</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="11">
@@ -4782,31 +4782,31 @@
         <v>1308</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E11" t="n">
-        <v>1461.5</v>
+        <v>1466.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.7933</v>
+        <v>-7.3735</v>
       </c>
       <c r="G11" t="n">
-        <v>109.22</v>
+        <v>109.08</v>
       </c>
       <c r="H11" t="n">
-        <v>108.7</v>
+        <v>108.28</v>
       </c>
       <c r="I11" t="n">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3089</v>
+        <v>0.3037</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1419</v>
+        <v>0.1447</v>
       </c>
       <c r="L11" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="M11" t="n">
         <v>185</v>
@@ -4827,7 +4827,7 @@
         <v>186</v>
       </c>
       <c r="S11" t="n">
-        <v>1488.4</v>
+        <v>1487.1</v>
       </c>
     </row>
   </sheetData>
@@ -4954,31 +4954,31 @@
         <v>1460</v>
       </c>
       <c r="D2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>1468.7</v>
+        <v>1470.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7502</v>
+        <v>2.7419</v>
       </c>
       <c r="G2" t="n">
-        <v>116.22</v>
+        <v>115.44</v>
       </c>
       <c r="H2" t="n">
-        <v>109.52</v>
+        <v>108.91</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7</v>
+        <v>6.53</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2952</v>
+        <v>0.2971</v>
       </c>
       <c r="K2" t="n">
         <v>0.1569</v>
       </c>
       <c r="L2" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>144</v>
@@ -4999,7 +4999,7 @@
         <v>133</v>
       </c>
       <c r="S2" t="n">
-        <v>1435.9</v>
+        <v>1431.7</v>
       </c>
     </row>
     <row r="3">
@@ -5076,31 +5076,31 @@
         <v>1178</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1327.7</v>
+        <v>1325.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6095</v>
+        <v>1.6749</v>
       </c>
       <c r="G4" t="n">
-        <v>109.63</v>
+        <v>108.87</v>
       </c>
       <c r="H4" t="n">
-        <v>112.46</v>
+        <v>111.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.83</v>
+        <v>-3.03</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3161</v>
+        <v>0.3151</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1604</v>
+        <v>0.1602</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="M4" t="n">
         <v>222</v>
@@ -5121,7 +5121,7 @@
         <v>229</v>
       </c>
       <c r="S4" t="n">
-        <v>1453.9</v>
+        <v>1453.7</v>
       </c>
     </row>
     <row r="5">
@@ -6091,31 +6091,31 @@
         <v>1467</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>1521.4</v>
+        <v>1514.7</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9296</v>
+        <v>3.9292</v>
       </c>
       <c r="G2" t="n">
-        <v>107.03</v>
+        <v>106.31</v>
       </c>
       <c r="H2" t="n">
-        <v>102.73</v>
+        <v>102.79</v>
       </c>
       <c r="I2" t="n">
-        <v>4.29</v>
+        <v>3.52</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2687</v>
+        <v>0.269</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1436</v>
+        <v>0.1467</v>
       </c>
       <c r="L2" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>174</v>
@@ -6136,7 +6136,7 @@
         <v>173</v>
       </c>
       <c r="S2" t="n">
-        <v>1455.8</v>
+        <v>1455.9</v>
       </c>
     </row>
     <row r="3">
@@ -6213,31 +6213,31 @@
         <v>1373</v>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1471.3</v>
+        <v>1478</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9399</v>
+        <v>0.9489</v>
       </c>
       <c r="G4" t="n">
-        <v>110.16</v>
+        <v>109.73</v>
       </c>
       <c r="H4" t="n">
-        <v>102.35</v>
+        <v>101.77</v>
       </c>
       <c r="I4" t="n">
-        <v>7.81</v>
+        <v>7.95</v>
       </c>
       <c r="J4" t="n">
         <v>0.2799</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1532</v>
+        <v>0.1508</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="M4" t="n">
         <v>195</v>
@@ -6258,7 +6258,7 @@
         <v>188</v>
       </c>
       <c r="S4" t="n">
-        <v>1426.7</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="5">
@@ -9280,31 +9280,31 @@
         <v>1390</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E11" t="n">
-        <v>1750</v>
+        <v>1734.2</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6234</v>
+        <v>2.5276</v>
       </c>
       <c r="G11" t="n">
-        <v>112.31</v>
+        <v>111.9</v>
       </c>
       <c r="H11" t="n">
-        <v>107.61</v>
+        <v>107.42</v>
       </c>
       <c r="I11" t="n">
-        <v>4.71</v>
+        <v>4.48</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3189</v>
+        <v>0.3248</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1433</v>
+        <v>0.1439</v>
       </c>
       <c r="L11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="M11" t="n">
         <v>59</v>
@@ -9325,7 +9325,7 @@
         <v>59</v>
       </c>
       <c r="S11" t="n">
-        <v>1628.4</v>
+        <v>1622.5</v>
       </c>
     </row>
     <row r="12">
@@ -9341,31 +9341,31 @@
         <v>1374</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E12" t="n">
-        <v>1738.3</v>
+        <v>1744.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9109</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>118.28</v>
+        <v>119.02</v>
       </c>
       <c r="H12" t="n">
-        <v>110.33</v>
+        <v>110.02</v>
       </c>
       <c r="I12" t="n">
-        <v>7.95</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3064</v>
+        <v>0.3105</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1528</v>
+        <v>0.1505</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.2</v>
+        <v>-5.6</v>
       </c>
       <c r="M12" t="n">
         <v>43</v>
@@ -9386,7 +9386,7 @@
         <v>39</v>
       </c>
       <c r="S12" t="n">
-        <v>1643.1</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="13">
@@ -9402,31 +9402,31 @@
         <v>1439</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E13" t="n">
-        <v>1713.5</v>
+        <v>1700</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7826</v>
+        <v>5.3784</v>
       </c>
       <c r="G13" t="n">
-        <v>112.34</v>
+        <v>112.71</v>
       </c>
       <c r="H13" t="n">
-        <v>106.8</v>
+        <v>107.62</v>
       </c>
       <c r="I13" t="n">
-        <v>5.54</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2975</v>
+        <v>0.2942</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1458</v>
+        <v>0.1447</v>
       </c>
       <c r="L13" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
         <v>56</v>
@@ -9447,7 +9447,7 @@
         <v>53</v>
       </c>
       <c r="S13" t="n">
-        <v>1665</v>
+        <v>1660.6</v>
       </c>
     </row>
     <row r="14">
@@ -9463,31 +9463,31 @@
         <v>1448</v>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E14" t="n">
-        <v>1650.8</v>
+        <v>1664.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0285</v>
+        <v>-2.8429</v>
       </c>
       <c r="G14" t="n">
-        <v>112.13</v>
+        <v>112.87</v>
       </c>
       <c r="H14" t="n">
-        <v>109.4</v>
+        <v>110</v>
       </c>
       <c r="I14" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2909</v>
+        <v>0.2991</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1488</v>
+        <v>0.1498</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
         <v>74</v>
@@ -9508,7 +9508,7 @@
         <v>64</v>
       </c>
       <c r="S14" t="n">
-        <v>1669.7</v>
+        <v>1670.8</v>
       </c>
     </row>
     <row r="15">
@@ -9524,31 +9524,31 @@
         <v>1393</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E15" t="n">
-        <v>1583.1</v>
+        <v>1576.8</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0611</v>
+        <v>0.8467</v>
       </c>
       <c r="G15" t="n">
-        <v>108.11</v>
+        <v>107.95</v>
       </c>
       <c r="H15" t="n">
-        <v>106.28</v>
+        <v>107.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.83</v>
+        <v>0.75</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2758</v>
+        <v>0.2779</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1525</v>
+        <v>0.153</v>
       </c>
       <c r="L15" t="n">
-        <v>-14.4</v>
+        <v>-10.4</v>
       </c>
       <c r="M15" t="n">
         <v>80</v>
@@ -9569,7 +9569,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="n">
-        <v>1659</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="16">
@@ -9585,31 +9585,31 @@
         <v>1338</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E16" t="n">
-        <v>1521</v>
+        <v>1536.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.1919</v>
+        <v>-4.8733</v>
       </c>
       <c r="G16" t="n">
-        <v>106.56</v>
+        <v>106.77</v>
       </c>
       <c r="H16" t="n">
-        <v>108.83</v>
+        <v>108.94</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.27</v>
+        <v>-2.17</v>
       </c>
       <c r="J16" t="n">
-        <v>0.323</v>
+        <v>0.3203</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1679</v>
+        <v>0.1682</v>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>99</v>
@@ -9630,7 +9630,7 @@
         <v>109</v>
       </c>
       <c r="S16" t="n">
-        <v>1658.7</v>
+        <v>1663.6</v>
       </c>
     </row>
   </sheetData>
@@ -10600,31 +10600,31 @@
         <v>1254</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>1416</v>
+        <v>1418.2</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4057</v>
+        <v>2.3581</v>
       </c>
       <c r="G2" t="n">
-        <v>108.81</v>
+        <v>109.38</v>
       </c>
       <c r="H2" t="n">
-        <v>104.08</v>
+        <v>104.38</v>
       </c>
       <c r="I2" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3167</v>
+        <v>0.3119</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1861</v>
+        <v>0.183</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>10.4</v>
       </c>
       <c r="M2" t="n">
         <v>217</v>
@@ -10645,7 +10645,7 @@
         <v>200</v>
       </c>
       <c r="S2" t="n">
-        <v>1378.3</v>
+        <v>1378.8</v>
       </c>
     </row>
     <row r="3">
@@ -10722,31 +10722,31 @@
         <v>1479</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1378.3</v>
+        <v>1376.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.056</v>
+        <v>-0.9555</v>
       </c>
       <c r="G4" t="n">
-        <v>104.02</v>
+        <v>104.23</v>
       </c>
       <c r="H4" t="n">
-        <v>104.43</v>
+        <v>105.25</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.41</v>
+        <v>-1.01</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2604</v>
+        <v>0.2585</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1364</v>
+        <v>0.1357</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
         <v>284</v>
@@ -10767,7 +10767,7 @@
         <v>275</v>
       </c>
       <c r="S4" t="n">
-        <v>1376.8</v>
+        <v>1379.2</v>
       </c>
     </row>
     <row r="5">
@@ -14327,31 +14327,31 @@
         <v>1372</v>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>1563.2</v>
+        <v>1565.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2741</v>
+        <v>3.2279</v>
       </c>
       <c r="G2" t="n">
-        <v>113.58</v>
+        <v>112.79</v>
       </c>
       <c r="H2" t="n">
-        <v>98.86</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>14.72</v>
+        <v>14.26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.311</v>
+        <v>0.3083</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1336</v>
+        <v>0.1321</v>
       </c>
       <c r="L2" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>89</v>
@@ -14372,7 +14372,7 @@
         <v>86</v>
       </c>
       <c r="S2" t="n">
-        <v>1383.2</v>
+        <v>1383.6</v>
       </c>
     </row>
     <row r="3">
@@ -14388,31 +14388,31 @@
         <v>1270</v>
       </c>
       <c r="D3" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E3" t="n">
-        <v>1718.7</v>
+        <v>1720.8</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9617</v>
+        <v>2.8141</v>
       </c>
       <c r="G3" t="n">
-        <v>115.41</v>
+        <v>114.82</v>
       </c>
       <c r="H3" t="n">
-        <v>100.48</v>
+        <v>100.31</v>
       </c>
       <c r="I3" t="n">
-        <v>14.93</v>
+        <v>14.51</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3477</v>
+        <v>0.3513</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1376</v>
+        <v>0.1369</v>
       </c>
       <c r="L3" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>68</v>
@@ -14433,7 +14433,7 @@
         <v>62</v>
       </c>
       <c r="S3" t="n">
-        <v>1423</v>
+        <v>1422.5</v>
       </c>
     </row>
     <row r="4">
@@ -14449,31 +14449,31 @@
         <v>1410</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1397.4</v>
+        <v>1395.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.648</v>
+        <v>1.687</v>
       </c>
       <c r="G4" t="n">
-        <v>110.55</v>
+        <v>109.78</v>
       </c>
       <c r="H4" t="n">
-        <v>105.06</v>
+        <v>104.83</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49</v>
+        <v>4.95</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2398</v>
+        <v>0.2375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1713</v>
+        <v>0.1754</v>
       </c>
       <c r="L4" t="n">
-        <v>10.4</v>
+        <v>5.4</v>
       </c>
       <c r="M4" t="n">
         <v>124</v>
@@ -14494,7 +14494,7 @@
         <v>134</v>
       </c>
       <c r="S4" t="n">
-        <v>1425</v>
+        <v>1436.7</v>
       </c>
     </row>
     <row r="5">
@@ -14510,31 +14510,31 @@
         <v>1394</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
-        <v>1378.5</v>
+        <v>1375.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4106</v>
+        <v>-0.3578</v>
       </c>
       <c r="G5" t="n">
-        <v>103</v>
+        <v>102.53</v>
       </c>
       <c r="H5" t="n">
-        <v>103.53</v>
+        <v>103.35</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.53</v>
+        <v>-0.82</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2959</v>
+        <v>0.2896</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1852</v>
+        <v>0.1883</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>180</v>
@@ -14555,7 +14555,7 @@
         <v>196</v>
       </c>
       <c r="S5" t="n">
-        <v>1424</v>
+        <v>1430.4</v>
       </c>
     </row>
     <row r="6">
@@ -16917,31 +16917,31 @@
         <v>1238</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E8" t="n">
-        <v>1300.9</v>
+        <v>1303.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.469</v>
+        <v>-1.4112</v>
       </c>
       <c r="G8" t="n">
-        <v>98.83</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>117.73</v>
+        <v>116.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-18.9</v>
+        <v>-18.29</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3036</v>
+        <v>0.3056</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1825</v>
+        <v>0.1838</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-4</v>
       </c>
       <c r="M8" t="n">
         <v>342</v>
@@ -16962,7 +16962,7 @@
         <v>348</v>
       </c>
       <c r="S8" t="n">
-        <v>1425.2</v>
+        <v>1424.2</v>
       </c>
     </row>
     <row r="9">
@@ -16978,31 +16978,31 @@
         <v>1341</v>
       </c>
       <c r="D9" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E9" t="n">
-        <v>1254.2</v>
+        <v>1256.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9032</v>
+        <v>-0.8365</v>
       </c>
       <c r="G9" t="n">
-        <v>103.81</v>
+        <v>103.47</v>
       </c>
       <c r="H9" t="n">
-        <v>108.99</v>
+        <v>108.04</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.19</v>
+        <v>-4.57</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2766</v>
+        <v>0.2769</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1553</v>
+        <v>0.1529</v>
       </c>
       <c r="L9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="M9" t="n">
         <v>312</v>
@@ -17023,7 +17023,7 @@
         <v>316</v>
       </c>
       <c r="S9" t="n">
-        <v>1390.4</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="10">
@@ -17039,31 +17039,31 @@
         <v>1212</v>
       </c>
       <c r="D10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1309.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5671</v>
+        <v>-0.5826</v>
       </c>
       <c r="G10" t="n">
-        <v>100.56</v>
+        <v>100.19</v>
       </c>
       <c r="H10" t="n">
-        <v>103.09</v>
+        <v>103.21</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.53</v>
+        <v>-3.02</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2974</v>
+        <v>0.2968</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2044</v>
+        <v>0.2047</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
         <v>298</v>
@@ -17084,7 +17084,7 @@
         <v>301</v>
       </c>
       <c r="S10" t="n">
-        <v>1352.3</v>
+        <v>1352.7</v>
       </c>
     </row>
     <row r="11">
@@ -17161,31 +17161,31 @@
         <v>1108</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E12" t="n">
-        <v>1270.1</v>
+        <v>1267.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4276</v>
+        <v>-1.3772</v>
       </c>
       <c r="G12" t="n">
-        <v>97.17</v>
+        <v>96.52</v>
       </c>
       <c r="H12" t="n">
-        <v>114.96</v>
+        <v>114.62</v>
       </c>
       <c r="I12" t="n">
-        <v>-17.8</v>
+        <v>-18.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3063</v>
+        <v>0.3013</v>
       </c>
       <c r="K12" t="n">
         <v>0.1856</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10</v>
       </c>
       <c r="M12" t="n">
         <v>351</v>
@@ -17206,7 +17206,7 @@
         <v>352</v>
       </c>
       <c r="S12" t="n">
-        <v>1410.3</v>
+        <v>1405.1</v>
       </c>
     </row>
     <row r="13">
@@ -18653,31 +18653,31 @@
         <v>1211</v>
       </c>
       <c r="D2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>2063.2</v>
+        <v>2068.3</v>
       </c>
       <c r="F2" t="n">
-        <v>6.2559</v>
+        <v>5.8188</v>
       </c>
       <c r="G2" t="n">
-        <v>120.06</v>
+        <v>120.75</v>
       </c>
       <c r="H2" t="n">
-        <v>92.98999999999999</v>
+        <v>93.89</v>
       </c>
       <c r="I2" t="n">
-        <v>27.07</v>
+        <v>26.86</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2963</v>
+        <v>0.2992</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1337</v>
+        <v>0.1335</v>
       </c>
       <c r="L2" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -18698,7 +18698,7 @@
         <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>1593.1</v>
+        <v>1601.3</v>
       </c>
     </row>
     <row r="3">
@@ -18775,31 +18775,31 @@
         <v>1365</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1787.9</v>
+        <v>1782.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2548</v>
+        <v>0.0374</v>
       </c>
       <c r="G4" t="n">
-        <v>117.9</v>
+        <v>117.62</v>
       </c>
       <c r="H4" t="n">
-        <v>103.18</v>
+        <v>104.11</v>
       </c>
       <c r="I4" t="n">
-        <v>14.72</v>
+        <v>13.51</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3445</v>
+        <v>0.3504</v>
       </c>
       <c r="K4" t="n">
-        <v>0.15</v>
+        <v>0.1498</v>
       </c>
       <c r="L4" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
         <v>37</v>
@@ -18820,7 +18820,7 @@
         <v>42</v>
       </c>
       <c r="S4" t="n">
-        <v>1580.2</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="5">
@@ -19496,31 +19496,31 @@
         <v>1420</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>1391.7</v>
+        <v>1393.7</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2162</v>
+        <v>1.2859</v>
       </c>
       <c r="G2" t="n">
-        <v>112.51</v>
+        <v>113.44</v>
       </c>
       <c r="H2" t="n">
-        <v>102.24</v>
+        <v>102.32</v>
       </c>
       <c r="I2" t="n">
-        <v>10.26</v>
+        <v>11.13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2126</v>
+        <v>0.2168</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1361</v>
+        <v>0.1344</v>
       </c>
       <c r="L2" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="M2" t="n">
         <v>198</v>
@@ -19557,31 +19557,31 @@
         <v>1436</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E3" t="n">
-        <v>1468.7</v>
+        <v>1470</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6744</v>
+        <v>-1.5409</v>
       </c>
       <c r="G3" t="n">
-        <v>112.14</v>
+        <v>111.42</v>
       </c>
       <c r="H3" t="n">
-        <v>105.78</v>
+        <v>105.02</v>
       </c>
       <c r="I3" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2415</v>
+        <v>0.241</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1398</v>
+        <v>0.1406</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>235</v>
@@ -19602,7 +19602,7 @@
         <v>223</v>
       </c>
       <c r="S3" t="n">
-        <v>1392.4</v>
+        <v>1389.6</v>
       </c>
     </row>
     <row r="4">
@@ -19618,31 +19618,31 @@
         <v>1312</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1310</v>
+        <v>1308.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3892</v>
+        <v>0.4078</v>
       </c>
       <c r="G4" t="n">
-        <v>98.15000000000001</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>108.47</v>
+        <v>108.42</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.32</v>
+        <v>-10.68</v>
       </c>
       <c r="J4" t="n">
-        <v>0.25</v>
+        <v>0.2537</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1627</v>
+        <v>0.1629</v>
       </c>
       <c r="L4" t="n">
-        <v>-15.6</v>
+        <v>-13.8</v>
       </c>
       <c r="M4" t="n">
         <v>332</v>
@@ -19663,7 +19663,7 @@
         <v>327</v>
       </c>
       <c r="S4" t="n">
-        <v>1398.5</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="5">
@@ -19679,31 +19679,31 @@
         <v>1262</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
-        <v>1350.1</v>
+        <v>1348.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5201</v>
+        <v>-2.3753</v>
       </c>
       <c r="G5" t="n">
-        <v>104.97</v>
+        <v>104.61</v>
       </c>
       <c r="H5" t="n">
-        <v>111.75</v>
+        <v>112.64</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.78</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3097</v>
+        <v>0.3157</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1714</v>
+        <v>0.1717</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>-6.4</v>
       </c>
       <c r="M5" t="n">
         <v>319</v>
@@ -19724,7 +19724,7 @@
         <v>318</v>
       </c>
       <c r="S5" t="n">
-        <v>1402.9</v>
+        <v>1403.6</v>
       </c>
     </row>
     <row r="6">
@@ -21426,31 +21426,31 @@
         <v>1153</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E10" t="n">
-        <v>1724.3</v>
+        <v>1728.9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.956</v>
+        <v>1.3367</v>
       </c>
       <c r="G10" t="n">
-        <v>105.28</v>
+        <v>105.7</v>
       </c>
       <c r="H10" t="n">
-        <v>98.18000000000001</v>
+        <v>98.19</v>
       </c>
       <c r="I10" t="n">
-        <v>7.09</v>
+        <v>7.51</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2902</v>
+        <v>0.2894</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1653</v>
+        <v>0.1614</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
         <v>42</v>
@@ -21471,7 +21471,7 @@
         <v>46</v>
       </c>
       <c r="S10" t="n">
-        <v>1716.2</v>
+        <v>1706.8</v>
       </c>
     </row>
     <row r="11">
@@ -21487,31 +21487,31 @@
         <v>1140</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E11" t="n">
-        <v>1924.5</v>
+        <v>1927.8</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6354</v>
+        <v>1.2144</v>
       </c>
       <c r="G11" t="n">
-        <v>118.39</v>
+        <v>118.9</v>
       </c>
       <c r="H11" t="n">
-        <v>106.82</v>
+        <v>107.06</v>
       </c>
       <c r="I11" t="n">
-        <v>11.57</v>
+        <v>11.85</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3034</v>
+        <v>0.3035</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1419</v>
+        <v>0.1427</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.4</v>
+        <v>-4.6</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
@@ -21532,7 +21532,7 @@
         <v>24</v>
       </c>
       <c r="S11" t="n">
-        <v>1726.9</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="12">
@@ -21548,31 +21548,31 @@
         <v>1160</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E12" t="n">
-        <v>1613.1</v>
+        <v>1605.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3802</v>
+        <v>-4.1723</v>
       </c>
       <c r="G12" t="n">
-        <v>113.99</v>
+        <v>114.14</v>
       </c>
       <c r="H12" t="n">
-        <v>113.32</v>
+        <v>113.85</v>
       </c>
       <c r="I12" t="n">
-        <v>0.68</v>
+        <v>0.28</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2829</v>
+        <v>0.285</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1411</v>
+        <v>0.1395</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6</v>
+        <v>-7.2</v>
       </c>
       <c r="M12" t="n">
         <v>64</v>
@@ -21593,7 +21593,7 @@
         <v>71</v>
       </c>
       <c r="S12" t="n">
-        <v>1695.4</v>
+        <v>1689.7</v>
       </c>
     </row>
     <row r="13">
@@ -21609,31 +21609,31 @@
         <v>1113</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E13" t="n">
-        <v>1678.6</v>
+        <v>1690</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4683</v>
+        <v>-1.2702</v>
       </c>
       <c r="G13" t="n">
-        <v>108.23</v>
+        <v>108.88</v>
       </c>
       <c r="H13" t="n">
-        <v>109.09</v>
+        <v>109.14</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2778</v>
+        <v>0.2792</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1602</v>
+        <v>0.1607</v>
       </c>
       <c r="L13" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
       <c r="M13" t="n">
         <v>63</v>
@@ -21654,7 +21654,7 @@
         <v>67</v>
       </c>
       <c r="S13" t="n">
-        <v>1735.5</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="14">
@@ -21670,31 +21670,31 @@
         <v>1124</v>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E14" t="n">
-        <v>1678.5</v>
+        <v>1667.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.2439</v>
+        <v>-5.9263</v>
       </c>
       <c r="G14" t="n">
-        <v>116.97</v>
+        <v>116.31</v>
       </c>
       <c r="H14" t="n">
-        <v>111.54</v>
+        <v>111.72</v>
       </c>
       <c r="I14" t="n">
-        <v>5.42</v>
+        <v>4.59</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3301</v>
+        <v>0.3335</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1604</v>
+        <v>0.162</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="M14" t="n">
         <v>48</v>
@@ -21731,31 +21731,31 @@
         <v>1329</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E15" t="n">
-        <v>1708.2</v>
+        <v>1716.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1004</v>
+        <v>-1.1554</v>
       </c>
       <c r="G15" t="n">
-        <v>110.43</v>
+        <v>111.03</v>
       </c>
       <c r="H15" t="n">
-        <v>109.61</v>
+        <v>109.6</v>
       </c>
       <c r="I15" t="n">
-        <v>0.82</v>
+        <v>1.43</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2792</v>
+        <v>0.2789</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1571</v>
+        <v>0.155</v>
       </c>
       <c r="L15" t="n">
-        <v>-6</v>
+        <v>-1.4</v>
       </c>
       <c r="M15" t="n">
         <v>69</v>
@@ -21776,7 +21776,7 @@
         <v>79</v>
       </c>
       <c r="S15" t="n">
-        <v>1693.9</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="16">
@@ -21792,31 +21792,31 @@
         <v>1243</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E16" t="n">
-        <v>1577.8</v>
+        <v>1574.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.9402</v>
+        <v>-4.7707</v>
       </c>
       <c r="G16" t="n">
-        <v>106.78</v>
+        <v>107.27</v>
       </c>
       <c r="H16" t="n">
-        <v>110.18</v>
+        <v>111.05</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4</v>
+        <v>-3.78</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2892</v>
+        <v>0.2905</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1683</v>
+        <v>0.1691</v>
       </c>
       <c r="L16" t="n">
-        <v>-12.6</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>101</v>
@@ -21837,7 +21837,7 @@
         <v>99</v>
       </c>
       <c r="S16" t="n">
-        <v>1704.2</v>
+        <v>1710.3</v>
       </c>
     </row>
     <row r="17">
@@ -21853,31 +21853,31 @@
         <v>1428</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E17" t="n">
-        <v>1521.6</v>
+        <v>1517</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.5566</v>
+        <v>-4.4618</v>
       </c>
       <c r="G17" t="n">
-        <v>108.84</v>
+        <v>108.31</v>
       </c>
       <c r="H17" t="n">
-        <v>116.37</v>
+        <v>115.53</v>
       </c>
       <c r="I17" t="n">
-        <v>-7.53</v>
+        <v>-7.22</v>
       </c>
       <c r="J17" t="n">
-        <v>0.28</v>
+        <v>0.2803</v>
       </c>
       <c r="K17" t="n">
-        <v>0.162</v>
+        <v>0.159</v>
       </c>
       <c r="L17" t="n">
-        <v>-14.2</v>
+        <v>-15.2</v>
       </c>
       <c r="M17" t="n">
         <v>127</v>
@@ -21898,7 +21898,7 @@
         <v>129</v>
       </c>
       <c r="S17" t="n">
-        <v>1690.8</v>
+        <v>1692.4</v>
       </c>
     </row>
   </sheetData>
@@ -22807,31 +22807,31 @@
         <v>1340</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>1460.1</v>
+        <v>1455.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.001</v>
+        <v>1.8991</v>
       </c>
       <c r="G2" t="n">
-        <v>105.77</v>
+        <v>105.47</v>
       </c>
       <c r="H2" t="n">
-        <v>101.47</v>
+        <v>101.56</v>
       </c>
       <c r="I2" t="n">
-        <v>4.29</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2576</v>
+        <v>0.2508</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1661</v>
+        <v>0.1703</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>141</v>
@@ -22852,7 +22852,7 @@
         <v>136</v>
       </c>
       <c r="S2" t="n">
-        <v>1413.3</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="3">
@@ -22929,31 +22929,31 @@
         <v>1186</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1643</v>
+        <v>-1.0019</v>
       </c>
       <c r="G4" t="n">
-        <v>112.14</v>
+        <v>111.6</v>
       </c>
       <c r="H4" t="n">
-        <v>113.12</v>
+        <v>113.34</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.98</v>
+        <v>-1.74</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2929</v>
+        <v>0.287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1707</v>
+        <v>0.1681</v>
       </c>
       <c r="L4" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="M4" t="n">
         <v>166</v>
@@ -22974,7 +22974,7 @@
         <v>201</v>
       </c>
       <c r="S4" t="n">
-        <v>1451.5</v>
+        <v>1450.3</v>
       </c>
     </row>
     <row r="5">
@@ -22990,31 +22990,31 @@
         <v>1285</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
-        <v>1464.6</v>
+        <v>1469.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6217</v>
+        <v>-1.5005</v>
       </c>
       <c r="G5" t="n">
-        <v>107.79</v>
+        <v>107.3</v>
       </c>
       <c r="H5" t="n">
-        <v>109.83</v>
+        <v>109.17</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.04</v>
+        <v>-1.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1846</v>
+        <v>0.1941</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1896</v>
+        <v>0.1861</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.6</v>
+        <v>-1</v>
       </c>
       <c r="M5" t="n">
         <v>187</v>
@@ -23035,7 +23035,7 @@
         <v>199</v>
       </c>
       <c r="S5" t="n">
-        <v>1434.8</v>
+        <v>1435.4</v>
       </c>
     </row>
     <row r="6">
@@ -23173,31 +23173,31 @@
         <v>1225</v>
       </c>
       <c r="D8" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" t="n">
-        <v>1403.1</v>
+        <v>1405.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3924</v>
+        <v>-0.3769</v>
       </c>
       <c r="G8" t="n">
-        <v>110.57</v>
+        <v>110.53</v>
       </c>
       <c r="H8" t="n">
-        <v>107.71</v>
+        <v>107.11</v>
       </c>
       <c r="I8" t="n">
-        <v>2.87</v>
+        <v>3.42</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2754</v>
+        <v>0.2756</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1463</v>
+        <v>0.1458</v>
       </c>
       <c r="L8" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>165</v>
@@ -23218,7 +23218,7 @@
         <v>161</v>
       </c>
       <c r="S8" t="n">
-        <v>1416.4</v>
+        <v>1412.5</v>
       </c>
     </row>
     <row r="9">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -1166,31 +1166,31 @@
         <v>1350</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E12" t="n">
-        <v>1466.9</v>
+        <v>1462.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4968</v>
+        <v>-0.6217</v>
       </c>
       <c r="G12" t="n">
-        <v>111.48</v>
+        <v>111.37</v>
       </c>
       <c r="H12" t="n">
-        <v>108.68</v>
+        <v>109.17</v>
       </c>
       <c r="I12" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2419</v>
+        <v>0.2398</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1397</v>
+        <v>0.1417</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="M12" t="n">
         <v>143</v>
@@ -1211,7 +1211,7 @@
         <v>152</v>
       </c>
       <c r="S12" t="n">
-        <v>1510.8</v>
+        <v>1506.6</v>
       </c>
     </row>
     <row r="13">
@@ -1227,31 +1227,31 @@
         <v>1247</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E13" t="n">
-        <v>1398.3</v>
+        <v>1395.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0204</v>
+        <v>-1.8721</v>
       </c>
       <c r="G13" t="n">
-        <v>99.75</v>
+        <v>100.2</v>
       </c>
       <c r="H13" t="n">
-        <v>111.11</v>
+        <v>112.17</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.36</v>
+        <v>-11.97</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3303</v>
+        <v>0.3331</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1752</v>
+        <v>0.1774</v>
       </c>
       <c r="L13" t="n">
-        <v>-6</v>
+        <v>-12.4</v>
       </c>
       <c r="M13" t="n">
         <v>225</v>
@@ -1272,7 +1272,7 @@
         <v>235</v>
       </c>
       <c r="S13" t="n">
-        <v>1566.1</v>
+        <v>1564.2</v>
       </c>
     </row>
     <row r="14">
@@ -1288,31 +1288,31 @@
         <v>1382</v>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E14" t="n">
-        <v>1533.9</v>
+        <v>1537</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.699299999999999</v>
+        <v>-8.5665</v>
       </c>
       <c r="G14" t="n">
-        <v>111.12</v>
+        <v>112.49</v>
       </c>
       <c r="H14" t="n">
-        <v>110.83</v>
+        <v>110.94</v>
       </c>
       <c r="I14" t="n">
-        <v>0.29</v>
+        <v>1.54</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3183</v>
+        <v>0.3278</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1633</v>
+        <v>0.1628</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.8</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>160</v>
@@ -1333,7 +1333,7 @@
         <v>158</v>
       </c>
       <c r="S14" t="n">
-        <v>1531.2</v>
+        <v>1525.6</v>
       </c>
     </row>
     <row r="15">
@@ -1349,31 +1349,31 @@
         <v>1260</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E15" t="n">
-        <v>1397.4</v>
+        <v>1402.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.1654</v>
+        <v>-3.9937</v>
       </c>
       <c r="G15" t="n">
-        <v>100.55</v>
+        <v>101.2</v>
       </c>
       <c r="H15" t="n">
-        <v>114.66</v>
+        <v>114.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-14.11</v>
+        <v>-13.26</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2832</v>
+        <v>0.2855</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1903</v>
+        <v>0.1854</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.4</v>
+        <v>-2.2</v>
       </c>
       <c r="M15" t="n">
         <v>293</v>
@@ -1394,7 +1394,7 @@
         <v>289</v>
       </c>
       <c r="S15" t="n">
-        <v>1557.5</v>
+        <v>1553.9</v>
       </c>
     </row>
   </sheetData>
@@ -2009,31 +2009,31 @@
         <v>1234</v>
       </c>
       <c r="D10" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1843.7</v>
+        <v>1848.9</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0673</v>
+        <v>3.6941</v>
       </c>
       <c r="G10" t="n">
-        <v>118.63</v>
+        <v>118.64</v>
       </c>
       <c r="H10" t="n">
-        <v>104.06</v>
+        <v>103.68</v>
       </c>
       <c r="I10" t="n">
-        <v>14.56</v>
+        <v>14.95</v>
       </c>
       <c r="J10" t="n">
-        <v>0.288</v>
+        <v>0.2884</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1446</v>
+        <v>0.1443</v>
       </c>
       <c r="L10" t="n">
-        <v>-2</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
         <v>24</v>
@@ -2054,7 +2054,7 @@
         <v>25</v>
       </c>
       <c r="S10" t="n">
-        <v>1715.1</v>
+        <v>1707.5</v>
       </c>
     </row>
     <row r="11">
@@ -2070,31 +2070,31 @@
         <v>1231</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1741.9</v>
+        <v>1726.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3683</v>
+        <v>-2.3299</v>
       </c>
       <c r="G11" t="n">
-        <v>116.27</v>
+        <v>115.61</v>
       </c>
       <c r="H11" t="n">
-        <v>107.64</v>
+        <v>107.91</v>
       </c>
       <c r="I11" t="n">
-        <v>8.619999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2347</v>
+        <v>0.2371</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1428</v>
+        <v>0.1407</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.8</v>
+        <v>-2.6</v>
       </c>
       <c r="M11" t="n">
         <v>41</v>
@@ -2115,7 +2115,7 @@
         <v>37</v>
       </c>
       <c r="S11" t="n">
-        <v>1701.1</v>
+        <v>1695.9</v>
       </c>
     </row>
     <row r="12">
@@ -2131,31 +2131,31 @@
         <v>1278</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E12" t="n">
-        <v>1624.1</v>
+        <v>1613.7</v>
       </c>
       <c r="F12" t="n">
-        <v>0.236</v>
+        <v>0.3599</v>
       </c>
       <c r="G12" t="n">
-        <v>110.8</v>
+        <v>110.46</v>
       </c>
       <c r="H12" t="n">
-        <v>108.5</v>
+        <v>108.58</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2481</v>
+        <v>0.2499</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1582</v>
+        <v>0.1577</v>
       </c>
       <c r="L12" t="n">
-        <v>-3</v>
+        <v>-7.8</v>
       </c>
       <c r="M12" t="n">
         <v>72</v>
@@ -2176,7 +2176,7 @@
         <v>74</v>
       </c>
       <c r="S12" t="n">
-        <v>1674.6</v>
+        <v>1670.6</v>
       </c>
     </row>
     <row r="13">
@@ -2192,31 +2192,31 @@
         <v>1449</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E13" t="n">
-        <v>1645.7</v>
+        <v>1660.8</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0254</v>
+        <v>1.8763</v>
       </c>
       <c r="G13" t="n">
-        <v>111.97</v>
+        <v>111.56</v>
       </c>
       <c r="H13" t="n">
-        <v>107.18</v>
+        <v>106.64</v>
       </c>
       <c r="I13" t="n">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2998</v>
+        <v>0.2978</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1497</v>
+        <v>0.1494</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>54</v>
@@ -2237,7 +2237,7 @@
         <v>61</v>
       </c>
       <c r="S13" t="n">
-        <v>1686.4</v>
+        <v>1689.5</v>
       </c>
     </row>
     <row r="14">
@@ -2253,31 +2253,31 @@
         <v>1425</v>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E14" t="n">
-        <v>1743</v>
+        <v>1727.9</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0281</v>
+        <v>0.4482</v>
       </c>
       <c r="G14" t="n">
-        <v>108.15</v>
+        <v>107.68</v>
       </c>
       <c r="H14" t="n">
-        <v>109.62</v>
+        <v>108.9</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2937</v>
+        <v>0.2905</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1679</v>
+        <v>0.1685</v>
       </c>
       <c r="L14" t="n">
-        <v>-15</v>
+        <v>-15.6</v>
       </c>
       <c r="M14" t="n">
         <v>77</v>
@@ -2298,7 +2298,7 @@
         <v>78</v>
       </c>
       <c r="S14" t="n">
-        <v>1693.6</v>
+        <v>1689.6</v>
       </c>
     </row>
     <row r="15">
@@ -2314,31 +2314,31 @@
         <v>1353</v>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E15" t="n">
-        <v>1557.5</v>
+        <v>1567.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9475</v>
+        <v>-2.7645</v>
       </c>
       <c r="G15" t="n">
-        <v>104.8</v>
+        <v>105.15</v>
       </c>
       <c r="H15" t="n">
-        <v>111.67</v>
+        <v>111.69</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.86</v>
+        <v>-6.54</v>
       </c>
       <c r="J15" t="n">
-        <v>0.318</v>
+        <v>0.3141</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1454</v>
+        <v>0.1499</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.8</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>129</v>
@@ -2359,7 +2359,7 @@
         <v>143</v>
       </c>
       <c r="S15" t="n">
-        <v>1684.5</v>
+        <v>1683.9</v>
       </c>
     </row>
     <row r="16">
@@ -2375,31 +2375,31 @@
         <v>1321</v>
       </c>
       <c r="D16" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E16" t="n">
-        <v>1591.6</v>
+        <v>1607</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.0194</v>
+        <v>-3.6942</v>
       </c>
       <c r="G16" t="n">
-        <v>111.47</v>
+        <v>111.92</v>
       </c>
       <c r="H16" t="n">
-        <v>109.98</v>
+        <v>109.76</v>
       </c>
       <c r="I16" t="n">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2813</v>
+        <v>0.2792</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1277</v>
+        <v>0.1299</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="M16" t="n">
         <v>66</v>
@@ -2420,7 +2420,7 @@
         <v>70</v>
       </c>
       <c r="S16" t="n">
-        <v>1694.1</v>
+        <v>1697.4</v>
       </c>
     </row>
     <row r="17">
@@ -2497,31 +2497,31 @@
         <v>1268</v>
       </c>
       <c r="D18" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" t="n">
-        <v>1607.2</v>
+        <v>1602</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.8093</v>
+        <v>-7.4945</v>
       </c>
       <c r="G18" t="n">
-        <v>104.08</v>
+        <v>103.79</v>
       </c>
       <c r="H18" t="n">
-        <v>114.2</v>
+        <v>114.53</v>
       </c>
       <c r="I18" t="n">
-        <v>-10.12</v>
+        <v>-10.73</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3167</v>
+        <v>0.319</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1739</v>
+        <v>0.1776</v>
       </c>
       <c r="L18" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M18" t="n">
         <v>128</v>
@@ -2542,7 +2542,7 @@
         <v>151</v>
       </c>
       <c r="S18" t="n">
-        <v>1715.9</v>
+        <v>1722.6</v>
       </c>
     </row>
     <row r="19">
@@ -2974,31 +2974,31 @@
         <v>1471</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" t="n">
-        <v>1609.6</v>
+        <v>1612.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.5106</v>
+        <v>-8.2102</v>
       </c>
       <c r="G6" t="n">
-        <v>107.44</v>
+        <v>107.17</v>
       </c>
       <c r="H6" t="n">
-        <v>101.11</v>
+        <v>100.89</v>
       </c>
       <c r="I6" t="n">
-        <v>6.32</v>
+        <v>6.28</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2366</v>
+        <v>0.2341</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1569</v>
+        <v>0.1584</v>
       </c>
       <c r="L6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="M6" t="n">
         <v>113</v>
@@ -3019,7 +3019,7 @@
         <v>120</v>
       </c>
       <c r="S6" t="n">
-        <v>1452.2</v>
+        <v>1449.6</v>
       </c>
     </row>
     <row r="7">
@@ -3035,31 +3035,31 @@
         <v>1413</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>1472.7</v>
+        <v>1478.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3306</v>
+        <v>-0.3411</v>
       </c>
       <c r="G7" t="n">
-        <v>106.71</v>
+        <v>106.92</v>
       </c>
       <c r="H7" t="n">
-        <v>106.16</v>
+        <v>105.91</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2542</v>
+        <v>0.25</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1753</v>
+        <v>0.1741</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M7" t="n">
         <v>155</v>
@@ -3080,7 +3080,7 @@
         <v>176</v>
       </c>
       <c r="S7" t="n">
-        <v>1456.9</v>
+        <v>1457.1</v>
       </c>
     </row>
     <row r="8">
@@ -3096,31 +3096,31 @@
         <v>1364</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1493.9</v>
+        <v>1488.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0793</v>
+        <v>1.0199</v>
       </c>
       <c r="G8" t="n">
-        <v>113.55</v>
+        <v>113.08</v>
       </c>
       <c r="H8" t="n">
-        <v>108.54</v>
+        <v>108.57</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4.51</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2751</v>
+        <v>0.2763</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1833</v>
+        <v>0.1817</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="M8" t="n">
         <v>126</v>
@@ -3141,7 +3141,7 @@
         <v>137</v>
       </c>
       <c r="S8" t="n">
-        <v>1456.2</v>
+        <v>1455.5</v>
       </c>
     </row>
     <row r="9">
@@ -3157,31 +3157,31 @@
         <v>1142</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1400.2</v>
+        <v>1397.3</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2454</v>
+        <v>-0.1798</v>
       </c>
       <c r="G9" t="n">
-        <v>106.57</v>
+        <v>105.82</v>
       </c>
       <c r="H9" t="n">
-        <v>111.69</v>
+        <v>111.34</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.12</v>
+        <v>-5.52</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2804</v>
+        <v>0.2798</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1916</v>
+        <v>0.1913</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
         <v>211</v>
@@ -3202,7 +3202,7 @@
         <v>228</v>
       </c>
       <c r="S9" t="n">
-        <v>1490.1</v>
+        <v>1496.9</v>
       </c>
     </row>
   </sheetData>
@@ -4233,31 +4233,31 @@
         <v>1251</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E2" t="n">
-        <v>1733.1</v>
+        <v>1719.2</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2041</v>
+        <v>2.9746</v>
       </c>
       <c r="G2" t="n">
-        <v>117.83</v>
+        <v>117.43</v>
       </c>
       <c r="H2" t="n">
-        <v>110.75</v>
+        <v>111.22</v>
       </c>
       <c r="I2" t="n">
-        <v>7.08</v>
+        <v>6.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1699</v>
+        <v>0.1712</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1316</v>
+        <v>0.1328</v>
       </c>
       <c r="L2" t="n">
-        <v>-5</v>
+        <v>-2.4</v>
       </c>
       <c r="M2" t="n">
         <v>116</v>
@@ -4278,7 +4278,7 @@
         <v>100</v>
       </c>
       <c r="S2" t="n">
-        <v>1485.6</v>
+        <v>1481.5</v>
       </c>
     </row>
     <row r="3">
@@ -4294,31 +4294,31 @@
         <v>1358</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>1540.1</v>
+        <v>1545</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6115</v>
+        <v>4.4295</v>
       </c>
       <c r="G3" t="n">
-        <v>113.61</v>
+        <v>112.95</v>
       </c>
       <c r="H3" t="n">
-        <v>107.46</v>
+        <v>106.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6.14</v>
+        <v>6.55</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3092</v>
+        <v>0.3122</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1597</v>
+        <v>0.1587</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
         <v>109</v>
@@ -4339,7 +4339,7 @@
         <v>104</v>
       </c>
       <c r="S3" t="n">
-        <v>1503.4</v>
+        <v>1499.6</v>
       </c>
     </row>
     <row r="4">
@@ -4721,31 +4721,31 @@
         <v>1283</v>
       </c>
       <c r="D10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1397.6</v>
+        <v>1411.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1993</v>
+        <v>1.1057</v>
       </c>
       <c r="G10" t="n">
-        <v>107.89</v>
+        <v>108.33</v>
       </c>
       <c r="H10" t="n">
-        <v>109.73</v>
+        <v>109.65</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.84</v>
+        <v>-1.32</v>
       </c>
       <c r="J10" t="n">
-        <v>0.324</v>
+        <v>0.3251</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1631</v>
+        <v>0.1614</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>215</v>
@@ -4766,7 +4766,7 @@
         <v>214</v>
       </c>
       <c r="S10" t="n">
-        <v>1471</v>
+        <v>1481.6</v>
       </c>
     </row>
     <row r="11">
@@ -4782,31 +4782,31 @@
         <v>1308</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1466.3</v>
+        <v>1461.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.3735</v>
+        <v>-6.9468</v>
       </c>
       <c r="G11" t="n">
-        <v>109.08</v>
+        <v>108.1</v>
       </c>
       <c r="H11" t="n">
-        <v>108.28</v>
+        <v>107.85</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="J11" t="n">
         <v>0.3037</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1447</v>
+        <v>0.1463</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
         <v>185</v>
@@ -4827,7 +4827,7 @@
         <v>186</v>
       </c>
       <c r="S11" t="n">
-        <v>1487.1</v>
+        <v>1489.5</v>
       </c>
     </row>
   </sheetData>
@@ -6873,31 +6873,31 @@
         <v>1288</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>1276.6</v>
+        <v>1266.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1495</v>
+        <v>-0.0021</v>
       </c>
       <c r="G3" t="n">
-        <v>100.03</v>
+        <v>99.73</v>
       </c>
       <c r="H3" t="n">
-        <v>111.79</v>
+        <v>111.49</v>
       </c>
       <c r="I3" t="n">
         <v>-11.76</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2945</v>
+        <v>0.294</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1709</v>
+        <v>0.1706</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="M3" t="n">
         <v>352</v>
@@ -6918,7 +6918,7 @@
         <v>351</v>
       </c>
       <c r="S3" t="n">
-        <v>1359.2</v>
+        <v>1356.2</v>
       </c>
     </row>
     <row r="4">
@@ -7178,31 +7178,31 @@
         <v>1175</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1256</v>
+        <v>1258.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1819</v>
+        <v>-3.1046</v>
       </c>
       <c r="G8" t="n">
-        <v>90.25</v>
+        <v>90.7</v>
       </c>
       <c r="H8" t="n">
-        <v>108.68</v>
+        <v>108.13</v>
       </c>
       <c r="I8" t="n">
-        <v>-18.43</v>
+        <v>-17.43</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3059</v>
+        <v>0.3064</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1858</v>
+        <v>0.1821</v>
       </c>
       <c r="L8" t="n">
-        <v>-12.2</v>
+        <v>-4.8</v>
       </c>
       <c r="M8" t="n">
         <v>362</v>
@@ -7223,7 +7223,7 @@
         <v>362</v>
       </c>
       <c r="S8" t="n">
-        <v>1357.2</v>
+        <v>1354.6</v>
       </c>
     </row>
   </sheetData>
@@ -8975,31 +8975,31 @@
         <v>1155</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" t="n">
-        <v>1838.2</v>
+        <v>1845.5</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3876</v>
+        <v>3.0058</v>
       </c>
       <c r="G6" t="n">
-        <v>112.83</v>
+        <v>113.18</v>
       </c>
       <c r="H6" t="n">
-        <v>100.58</v>
+        <v>100.7</v>
       </c>
       <c r="I6" t="n">
-        <v>12.25</v>
+        <v>12.47</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2488</v>
+        <v>0.2545</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1395</v>
+        <v>0.1366</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
         <v>38</v>
@@ -9020,7 +9020,7 @@
         <v>36</v>
       </c>
       <c r="S6" t="n">
-        <v>1641.6</v>
+        <v>1644.4</v>
       </c>
     </row>
     <row r="7">
@@ -9036,31 +9036,31 @@
         <v>1257</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>1845.2</v>
+        <v>1855.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9919</v>
+        <v>-2.8167</v>
       </c>
       <c r="G7" t="n">
-        <v>120.19</v>
+        <v>119.15</v>
       </c>
       <c r="H7" t="n">
-        <v>101.95</v>
+        <v>101.26</v>
       </c>
       <c r="I7" t="n">
-        <v>18.24</v>
+        <v>17.89</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2897</v>
+        <v>0.2908</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1578</v>
+        <v>0.1584</v>
       </c>
       <c r="L7" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
@@ -9081,7 +9081,7 @@
         <v>14</v>
       </c>
       <c r="S7" t="n">
-        <v>1682.1</v>
+        <v>1683.7</v>
       </c>
     </row>
     <row r="8">
@@ -9097,31 +9097,31 @@
         <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1735.9</v>
+        <v>1740.7</v>
       </c>
       <c r="F8" t="n">
-        <v>7.7247</v>
+        <v>7.3141</v>
       </c>
       <c r="G8" t="n">
-        <v>118.75</v>
+        <v>120.03</v>
       </c>
       <c r="H8" t="n">
-        <v>108.16</v>
+        <v>109.14</v>
       </c>
       <c r="I8" t="n">
-        <v>10.59</v>
+        <v>10.89</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2829</v>
+        <v>0.2784</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1296</v>
+        <v>0.1277</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="M8" t="n">
         <v>36</v>
@@ -9142,7 +9142,7 @@
         <v>35</v>
       </c>
       <c r="S8" t="n">
-        <v>1675.6</v>
+        <v>1669.5</v>
       </c>
     </row>
     <row r="9">
@@ -9158,31 +9158,31 @@
         <v>1199</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1621.9</v>
+        <v>1636</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8284</v>
+        <v>-0.3568</v>
       </c>
       <c r="G9" t="n">
-        <v>111.16</v>
+        <v>112.09</v>
       </c>
       <c r="H9" t="n">
-        <v>107.31</v>
+        <v>108.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3133</v>
+        <v>0.3111</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1507</v>
+        <v>0.148</v>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="M9" t="n">
         <v>65</v>
@@ -9203,7 +9203,7 @@
         <v>69</v>
       </c>
       <c r="S9" t="n">
-        <v>1656.1</v>
+        <v>1657.6</v>
       </c>
     </row>
     <row r="10">
@@ -9219,31 +9219,31 @@
         <v>1143</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1717.3</v>
+        <v>1703.3</v>
       </c>
       <c r="F10" t="n">
-        <v>7.7033</v>
+        <v>7.292</v>
       </c>
       <c r="G10" t="n">
-        <v>109.18</v>
+        <v>110.16</v>
       </c>
       <c r="H10" t="n">
-        <v>103.34</v>
+        <v>104.76</v>
       </c>
       <c r="I10" t="n">
-        <v>5.84</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.228</v>
+        <v>0.2351</v>
       </c>
       <c r="K10" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4</v>
+        <v>-2.8</v>
       </c>
       <c r="M10" t="n">
         <v>71</v>
@@ -9264,7 +9264,7 @@
         <v>65</v>
       </c>
       <c r="S10" t="n">
-        <v>1603.3</v>
+        <v>1603.7</v>
       </c>
     </row>
     <row r="11">
@@ -9341,28 +9341,28 @@
         <v>1374</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12" t="n">
-        <v>1744.5</v>
+        <v>1733.9</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.2411</v>
       </c>
       <c r="G12" t="n">
-        <v>119.02</v>
+        <v>117.96</v>
       </c>
       <c r="H12" t="n">
-        <v>110.02</v>
+        <v>109.76</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3105</v>
+        <v>0.3098</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1505</v>
+        <v>0.1542</v>
       </c>
       <c r="L12" t="n">
         <v>-5.6</v>
@@ -9386,7 +9386,7 @@
         <v>39</v>
       </c>
       <c r="S12" t="n">
-        <v>1641</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="13">
@@ -9463,31 +9463,31 @@
         <v>1448</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" t="n">
-        <v>1664.3</v>
+        <v>1657</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8429</v>
+        <v>-2.5969</v>
       </c>
       <c r="G14" t="n">
-        <v>112.87</v>
+        <v>112.23</v>
       </c>
       <c r="H14" t="n">
-        <v>110</v>
+        <v>110.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2991</v>
+        <v>0.2935</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1498</v>
+        <v>0.1514</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
         <v>74</v>
@@ -9508,7 +9508,7 @@
         <v>64</v>
       </c>
       <c r="S14" t="n">
-        <v>1670.8</v>
+        <v>1677.2</v>
       </c>
     </row>
     <row r="15">
@@ -9585,31 +9585,31 @@
         <v>1338</v>
       </c>
       <c r="D16" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E16" t="n">
-        <v>1536.9</v>
+        <v>1532</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.8733</v>
+        <v>-4.4929</v>
       </c>
       <c r="G16" t="n">
-        <v>106.77</v>
+        <v>107.91</v>
       </c>
       <c r="H16" t="n">
-        <v>108.94</v>
+        <v>110.68</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.17</v>
+        <v>-2.76</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3203</v>
+        <v>0.3187</v>
       </c>
       <c r="K16" t="n">
         <v>0.1682</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
         <v>99</v>
@@ -9630,7 +9630,7 @@
         <v>109</v>
       </c>
       <c r="S16" t="n">
-        <v>1663.6</v>
+        <v>1665.5</v>
       </c>
     </row>
   </sheetData>
@@ -10001,31 +10001,31 @@
         <v>1305</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" t="n">
-        <v>1736.5</v>
+        <v>1737.2</v>
       </c>
       <c r="F6" t="n">
-        <v>6.7862</v>
+        <v>6.361</v>
       </c>
       <c r="G6" t="n">
-        <v>112.99</v>
+        <v>112.93</v>
       </c>
       <c r="H6" t="n">
-        <v>106.43</v>
+        <v>104.74</v>
       </c>
       <c r="I6" t="n">
-        <v>6.56</v>
+        <v>8.19</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3038</v>
+        <v>0.3029</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1419</v>
+        <v>0.1435</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
         <v>76</v>
@@ -10046,7 +10046,7 @@
         <v>73</v>
       </c>
       <c r="S6" t="n">
-        <v>1598.1</v>
+        <v>1587.8</v>
       </c>
     </row>
     <row r="7">
@@ -10062,31 +10062,31 @@
         <v>1129</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>1737.5</v>
+        <v>1724.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1403</v>
+        <v>-1.8566</v>
       </c>
       <c r="G7" t="n">
-        <v>114.39</v>
+        <v>113.98</v>
       </c>
       <c r="H7" t="n">
-        <v>107.18</v>
+        <v>107.78</v>
       </c>
       <c r="I7" t="n">
-        <v>7.21</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2847</v>
+        <v>0.2839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1604</v>
+        <v>0.1571</v>
       </c>
       <c r="L7" t="n">
-        <v>12.2</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
         <v>55</v>
@@ -10107,7 +10107,7 @@
         <v>57</v>
       </c>
       <c r="S7" t="n">
-        <v>1622.1</v>
+        <v>1610.8</v>
       </c>
     </row>
     <row r="8">
@@ -10123,31 +10123,31 @@
         <v>1161</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1661.3</v>
+        <v>1664.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.2805</v>
+        <v>-4.9476</v>
       </c>
       <c r="G8" t="n">
-        <v>119.17</v>
+        <v>118.83</v>
       </c>
       <c r="H8" t="n">
-        <v>113.56</v>
+        <v>112.9</v>
       </c>
       <c r="I8" t="n">
-        <v>5.61</v>
+        <v>5.93</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2593</v>
+        <v>0.2638</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1744</v>
+        <v>0.1735</v>
       </c>
       <c r="L8" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
         <v>85</v>
@@ -10168,7 +10168,7 @@
         <v>87</v>
       </c>
       <c r="S8" t="n">
-        <v>1561.4</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="9">
@@ -10184,31 +10184,31 @@
         <v>1424</v>
       </c>
       <c r="D9" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1644.6</v>
+        <v>1650.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6162</v>
+        <v>1.6984</v>
       </c>
       <c r="G9" t="n">
-        <v>112.14</v>
+        <v>111.95</v>
       </c>
       <c r="H9" t="n">
-        <v>111.68</v>
+        <v>111.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.294</v>
+        <v>0.2937</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1598</v>
+        <v>0.1604</v>
       </c>
       <c r="L9" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="M9" t="n">
         <v>104</v>
@@ -10229,7 +10229,7 @@
         <v>111</v>
       </c>
       <c r="S9" t="n">
-        <v>1623.2</v>
+        <v>1617.1</v>
       </c>
     </row>
     <row r="10">
@@ -10245,31 +10245,31 @@
         <v>1461</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1526.8</v>
+        <v>1521.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2647</v>
+        <v>-0.1434</v>
       </c>
       <c r="G10" t="n">
-        <v>113.84</v>
+        <v>113.42</v>
       </c>
       <c r="H10" t="n">
-        <v>109.09</v>
+        <v>109.18</v>
       </c>
       <c r="I10" t="n">
-        <v>4.75</v>
+        <v>4.24</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3231</v>
+        <v>0.3287</v>
       </c>
       <c r="K10" t="n">
-        <v>0.159</v>
+        <v>0.1553</v>
       </c>
       <c r="L10" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
         <v>98</v>
@@ -10290,7 +10290,7 @@
         <v>98</v>
       </c>
       <c r="S10" t="n">
-        <v>1558</v>
+        <v>1563.6</v>
       </c>
     </row>
     <row r="11">
@@ -10306,31 +10306,31 @@
         <v>1201</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1420.6</v>
+        <v>1417.7</v>
       </c>
       <c r="F11" t="n">
-        <v>2.37</v>
+        <v>2.2387</v>
       </c>
       <c r="G11" t="n">
-        <v>104.39</v>
+        <v>104.44</v>
       </c>
       <c r="H11" t="n">
-        <v>106.19</v>
+        <v>106.05</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2609</v>
+        <v>0.2568</v>
       </c>
       <c r="K11" t="n">
-        <v>0.17</v>
+        <v>0.1713</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.6</v>
+        <v>-7</v>
       </c>
       <c r="M11" t="n">
         <v>131</v>
@@ -10351,7 +10351,7 @@
         <v>149</v>
       </c>
       <c r="S11" t="n">
-        <v>1589</v>
+        <v>1590.6</v>
       </c>
     </row>
     <row r="12">
@@ -10367,31 +10367,31 @@
         <v>1363</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E12" t="n">
-        <v>1361.4</v>
+        <v>1374.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1738</v>
+        <v>-3.063</v>
       </c>
       <c r="G12" t="n">
-        <v>107.12</v>
+        <v>107.46</v>
       </c>
       <c r="H12" t="n">
-        <v>120.72</v>
+        <v>119.84</v>
       </c>
       <c r="I12" t="n">
-        <v>-13.59</v>
+        <v>-12.39</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3383</v>
+        <v>0.3361</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1413</v>
+        <v>0.1432</v>
       </c>
       <c r="L12" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="M12" t="n">
         <v>237</v>
@@ -10412,7 +10412,7 @@
         <v>256</v>
       </c>
       <c r="S12" t="n">
-        <v>1584.5</v>
+        <v>1591.5</v>
       </c>
     </row>
     <row r="13">
@@ -10428,31 +10428,31 @@
         <v>1102</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E13" t="n">
-        <v>1256.6</v>
+        <v>1255.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3635</v>
+        <v>-2.3202</v>
       </c>
       <c r="G13" t="n">
-        <v>93.43000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="H13" t="n">
-        <v>120.31</v>
+        <v>120.13</v>
       </c>
       <c r="I13" t="n">
-        <v>-26.88</v>
+        <v>-27.93</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2222</v>
+        <v>0.2263</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2048</v>
+        <v>0.2074</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.2</v>
+        <v>-17.2</v>
       </c>
       <c r="M13" t="n">
         <v>344</v>
@@ -10473,7 +10473,7 @@
         <v>349</v>
       </c>
       <c r="S13" t="n">
-        <v>1567.3</v>
+        <v>1572.4</v>
       </c>
     </row>
   </sheetData>
@@ -11859,31 +11859,31 @@
         <v>1250</v>
       </c>
       <c r="D3" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>1323.1</v>
+        <v>1325.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5849</v>
+        <v>-0.465</v>
       </c>
       <c r="G3" t="n">
-        <v>104.76</v>
+        <v>105.58</v>
       </c>
       <c r="H3" t="n">
-        <v>108.58</v>
+        <v>108.39</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.82</v>
+        <v>-2.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.214</v>
+        <v>0.2229</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1729</v>
+        <v>0.1707</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="M3" t="n">
         <v>290</v>
@@ -11904,7 +11904,7 @@
         <v>282</v>
       </c>
       <c r="S3" t="n">
-        <v>1401.7</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="4">
@@ -11981,31 +11981,31 @@
         <v>1131</v>
       </c>
       <c r="D5" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E5" t="n">
-        <v>1346.8</v>
+        <v>1344.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4681</v>
+        <v>-2.282</v>
       </c>
       <c r="G5" t="n">
-        <v>115.45</v>
+        <v>114.64</v>
       </c>
       <c r="H5" t="n">
-        <v>114.22</v>
+        <v>114.36</v>
       </c>
       <c r="I5" t="n">
-        <v>1.24</v>
+        <v>0.28</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2355</v>
+        <v>0.2396</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1697</v>
+        <v>0.1682</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>254</v>
@@ -12026,7 +12026,7 @@
         <v>257</v>
       </c>
       <c r="S5" t="n">
-        <v>1379.2</v>
+        <v>1376.4</v>
       </c>
     </row>
     <row r="6">
@@ -13007,31 +13007,31 @@
         <v>1246</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1881.8</v>
+        <v>1887.4</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4881</v>
+        <v>5.1867</v>
       </c>
       <c r="G10" t="n">
-        <v>116.58</v>
+        <v>117.12</v>
       </c>
       <c r="H10" t="n">
-        <v>106.11</v>
+        <v>106.56</v>
       </c>
       <c r="I10" t="n">
-        <v>10.47</v>
+        <v>10.57</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3117</v>
+        <v>0.3122</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1455</v>
+        <v>0.1426</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>27</v>
@@ -13052,7 +13052,7 @@
         <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1728.4</v>
+        <v>1721.6</v>
       </c>
     </row>
     <row r="11">
@@ -13068,31 +13068,31 @@
         <v>1400</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1757.7</v>
+        <v>1741.7</v>
       </c>
       <c r="F11" t="n">
-        <v>2.865</v>
+        <v>2.8164</v>
       </c>
       <c r="G11" t="n">
-        <v>120.37</v>
+        <v>119.5</v>
       </c>
       <c r="H11" t="n">
         <v>111.34</v>
       </c>
       <c r="I11" t="n">
-        <v>9.02</v>
+        <v>8.16</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3098</v>
+        <v>0.3072</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1494</v>
+        <v>0.145</v>
       </c>
       <c r="L11" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="M11" t="n">
         <v>33</v>
@@ -13113,7 +13113,7 @@
         <v>41</v>
       </c>
       <c r="S11" t="n">
-        <v>1699.4</v>
+        <v>1696.4</v>
       </c>
     </row>
     <row r="12">
@@ -13129,31 +13129,31 @@
         <v>1328</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E12" t="n">
-        <v>1703.7</v>
+        <v>1709.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4994</v>
+        <v>-2.1526</v>
       </c>
       <c r="G12" t="n">
-        <v>119.56</v>
+        <v>120.33</v>
       </c>
       <c r="H12" t="n">
-        <v>111.75</v>
+        <v>112.01</v>
       </c>
       <c r="I12" t="n">
-        <v>7.8</v>
+        <v>8.32</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3111</v>
+        <v>0.3072</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1412</v>
+        <v>0.1408</v>
       </c>
       <c r="L12" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
         <v>46</v>
@@ -13174,7 +13174,7 @@
         <v>54</v>
       </c>
       <c r="S12" t="n">
-        <v>1663.6</v>
+        <v>1657.6</v>
       </c>
     </row>
     <row r="13">
@@ -13190,31 +13190,31 @@
         <v>1120</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E13" t="n">
-        <v>1831.7</v>
+        <v>1837.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.7196</v>
+        <v>-7.6154</v>
       </c>
       <c r="G13" t="n">
-        <v>119.16</v>
+        <v>118.87</v>
       </c>
       <c r="H13" t="n">
-        <v>114.92</v>
+        <v>113.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.25</v>
+        <v>5.37</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3497</v>
+        <v>0.3462</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1459</v>
+        <v>0.1435</v>
       </c>
       <c r="L13" t="n">
-        <v>-3</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
         <v>39</v>
@@ -13235,7 +13235,7 @@
         <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>1758.3</v>
+        <v>1750.3</v>
       </c>
     </row>
     <row r="14">
@@ -13251,31 +13251,31 @@
         <v>1280</v>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E14" t="n">
-        <v>1621.6</v>
+        <v>1615.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5779</v>
+        <v>-1.6216</v>
       </c>
       <c r="G14" t="n">
-        <v>107.61</v>
+        <v>106.64</v>
       </c>
       <c r="H14" t="n">
-        <v>112.47</v>
+        <v>112.3</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.86</v>
+        <v>-5.67</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2773</v>
+        <v>0.278</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1559</v>
+        <v>0.1555</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.4</v>
+        <v>-21.4</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -13296,7 +13296,7 @@
         <v>110</v>
       </c>
       <c r="S14" t="n">
-        <v>1703.2</v>
+        <v>1707.4</v>
       </c>
     </row>
     <row r="15">
@@ -13312,31 +13312,31 @@
         <v>1376</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E15" t="n">
-        <v>1550</v>
+        <v>1544.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5273</v>
+        <v>-2.3515</v>
       </c>
       <c r="G15" t="n">
-        <v>108.93</v>
+        <v>109.38</v>
       </c>
       <c r="H15" t="n">
-        <v>110.37</v>
+        <v>111.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.44</v>
+        <v>-2.23</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2616</v>
+        <v>0.2706</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1372</v>
+        <v>0.1382</v>
       </c>
       <c r="L15" t="n">
-        <v>-7.2</v>
+        <v>-11.2</v>
       </c>
       <c r="M15" t="n">
         <v>95</v>
@@ -13357,7 +13357,7 @@
         <v>107</v>
       </c>
       <c r="S15" t="n">
-        <v>1653.5</v>
+        <v>1655.8</v>
       </c>
     </row>
     <row r="16">
@@ -13373,31 +13373,31 @@
         <v>1279</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E16" t="n">
-        <v>1624.5</v>
+        <v>1640.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.4802</v>
+        <v>-8.1568</v>
       </c>
       <c r="G16" t="n">
-        <v>108.77</v>
+        <v>108.94</v>
       </c>
       <c r="H16" t="n">
-        <v>109.59</v>
+        <v>109.08</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2818</v>
+        <v>0.2802</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1343</v>
+        <v>0.1362</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.2</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
         <v>81</v>
@@ -13418,7 +13418,7 @@
         <v>92</v>
       </c>
       <c r="S16" t="n">
-        <v>1688.2</v>
+        <v>1692.8</v>
       </c>
     </row>
     <row r="17">
@@ -13434,31 +13434,31 @@
         <v>1261</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E17" t="n">
-        <v>1640.5</v>
+        <v>1635</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2644</v>
+        <v>-1.5391</v>
       </c>
       <c r="G17" t="n">
-        <v>115.45</v>
+        <v>115.62</v>
       </c>
       <c r="H17" t="n">
-        <v>111.34</v>
+        <v>111.89</v>
       </c>
       <c r="I17" t="n">
-        <v>4.11</v>
+        <v>3.73</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2976</v>
+        <v>0.2988</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1541</v>
+        <v>0.1522</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.6</v>
+        <v>-6.2</v>
       </c>
       <c r="M17" t="n">
         <v>62</v>
@@ -13479,7 +13479,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="n">
-        <v>1660.6</v>
+        <v>1667.8</v>
       </c>
     </row>
   </sheetData>
@@ -14327,31 +14327,31 @@
         <v>1372</v>
       </c>
       <c r="D2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" t="n">
-        <v>1565.8</v>
+        <v>1559.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2279</v>
+        <v>3.1865</v>
       </c>
       <c r="G2" t="n">
-        <v>112.79</v>
+        <v>112.19</v>
       </c>
       <c r="H2" t="n">
-        <v>98.54000000000001</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>14.26</v>
+        <v>12.69</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3083</v>
+        <v>0.3073</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1321</v>
+        <v>0.1354</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>89</v>
@@ -14372,7 +14372,7 @@
         <v>86</v>
       </c>
       <c r="S2" t="n">
-        <v>1383.6</v>
+        <v>1397.1</v>
       </c>
     </row>
     <row r="3">
@@ -14388,31 +14388,31 @@
         <v>1270</v>
       </c>
       <c r="D3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>1720.8</v>
+        <v>1726.8</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8141</v>
+        <v>2.6895</v>
       </c>
       <c r="G3" t="n">
-        <v>114.82</v>
+        <v>115.07</v>
       </c>
       <c r="H3" t="n">
-        <v>100.31</v>
+        <v>100.01</v>
       </c>
       <c r="I3" t="n">
-        <v>14.51</v>
+        <v>15.06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3513</v>
+        <v>0.3483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1369</v>
+        <v>0.139</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>68</v>
@@ -14433,7 +14433,7 @@
         <v>62</v>
       </c>
       <c r="S3" t="n">
-        <v>1422.5</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="4">
@@ -16551,31 +16551,31 @@
         <v>1126</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E2" t="n">
-        <v>1375.4</v>
+        <v>1371.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9205</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>104.96</v>
+        <v>104.97</v>
       </c>
       <c r="H2" t="n">
-        <v>108.7</v>
+        <v>108.8</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.74</v>
+        <v>-3.83</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2778</v>
+        <v>0.2792</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1862</v>
+        <v>0.186</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
         <v>238</v>
@@ -16596,7 +16596,7 @@
         <v>255</v>
       </c>
       <c r="S2" t="n">
-        <v>1436.6</v>
+        <v>1430.6</v>
       </c>
     </row>
     <row r="3">
@@ -16612,31 +16612,31 @@
         <v>1197</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>1294.9</v>
+        <v>1297.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.222</v>
+        <v>-0.1581</v>
       </c>
       <c r="G3" t="n">
-        <v>99.59</v>
+        <v>99.55</v>
       </c>
       <c r="H3" t="n">
-        <v>106.67</v>
+        <v>105.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-7.07</v>
+        <v>-6.24</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2982</v>
+        <v>0.3027</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2043</v>
+        <v>0.2062</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
         <v>315</v>
@@ -16657,7 +16657,7 @@
         <v>315</v>
       </c>
       <c r="S3" t="n">
-        <v>1379.3</v>
+        <v>1376.1</v>
       </c>
     </row>
     <row r="4">
@@ -16917,31 +16917,31 @@
         <v>1238</v>
       </c>
       <c r="D8" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1303.6</v>
+        <v>1300.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4112</v>
+        <v>-1.3402</v>
       </c>
       <c r="G8" t="n">
-        <v>98.51000000000001</v>
+        <v>97.97</v>
       </c>
       <c r="H8" t="n">
-        <v>116.79</v>
+        <v>116.33</v>
       </c>
       <c r="I8" t="n">
-        <v>-18.29</v>
+        <v>-18.36</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3056</v>
+        <v>0.3094</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1838</v>
+        <v>0.1877</v>
       </c>
       <c r="L8" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
       <c r="M8" t="n">
         <v>342</v>
@@ -16962,7 +16962,7 @@
         <v>348</v>
       </c>
       <c r="S8" t="n">
-        <v>1424.2</v>
+        <v>1420.2</v>
       </c>
     </row>
     <row r="9">
@@ -16978,31 +16978,31 @@
         <v>1341</v>
       </c>
       <c r="D9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1256.9</v>
+        <v>1260.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8365</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>103.47</v>
+        <v>103.68</v>
       </c>
       <c r="H9" t="n">
-        <v>108.04</v>
+        <v>107.97</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.57</v>
+        <v>-4.29</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2769</v>
+        <v>0.2812</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1529</v>
+        <v>0.1546</v>
       </c>
       <c r="L9" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="M9" t="n">
         <v>312</v>
@@ -17023,7 +17023,7 @@
         <v>316</v>
       </c>
       <c r="S9" t="n">
-        <v>1386</v>
+        <v>1386.7</v>
       </c>
     </row>
     <row r="10">
@@ -17760,31 +17760,31 @@
         <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1570.6</v>
+        <v>1576.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3127</v>
+        <v>-1.4104</v>
       </c>
       <c r="G8" t="n">
-        <v>108.77</v>
+        <v>108.51</v>
       </c>
       <c r="H8" t="n">
-        <v>106.62</v>
+        <v>105.87</v>
       </c>
       <c r="I8" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2933</v>
+        <v>0.2922</v>
       </c>
       <c r="K8" t="n">
-        <v>0.169</v>
+        <v>0.173</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
       <c r="M8" t="n">
         <v>125</v>
@@ -17805,7 +17805,7 @@
         <v>123</v>
       </c>
       <c r="S8" t="n">
-        <v>1561.9</v>
+        <v>1558.4</v>
       </c>
     </row>
     <row r="9">
@@ -17821,31 +17821,31 @@
         <v>1272</v>
       </c>
       <c r="D9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1567</v>
+        <v>1558.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.2285</v>
+        <v>-5.1449</v>
       </c>
       <c r="G9" t="n">
-        <v>104.68</v>
+        <v>104.32</v>
       </c>
       <c r="H9" t="n">
-        <v>106.29</v>
+        <v>106.55</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6</v>
+        <v>-2.23</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3397</v>
+        <v>0.3408</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1824</v>
+        <v>0.181</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.8</v>
+        <v>-8</v>
       </c>
       <c r="M9" t="n">
         <v>130</v>
@@ -17866,7 +17866,7 @@
         <v>125</v>
       </c>
       <c r="S9" t="n">
-        <v>1607.8</v>
+        <v>1604.3</v>
       </c>
     </row>
     <row r="10">
@@ -17882,31 +17882,31 @@
         <v>1408</v>
       </c>
       <c r="D10" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1495.7</v>
+        <v>1504</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8275</v>
+        <v>-1.8568</v>
       </c>
       <c r="G10" t="n">
-        <v>105.57</v>
+        <v>105.81</v>
       </c>
       <c r="H10" t="n">
-        <v>110.65</v>
+        <v>109.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.08</v>
+        <v>-4.16</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2346</v>
+        <v>0.2381</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1519</v>
+        <v>0.1533</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.2</v>
+        <v>-16</v>
       </c>
       <c r="M10" t="n">
         <v>210</v>
@@ -17927,7 +17927,7 @@
         <v>206</v>
       </c>
       <c r="S10" t="n">
-        <v>1531.6</v>
+        <v>1532.8</v>
       </c>
     </row>
     <row r="11">
@@ -17943,31 +17943,31 @@
         <v>1396</v>
       </c>
       <c r="D11" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1495.5</v>
+        <v>1490</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6989</v>
+        <v>-1.7447</v>
       </c>
       <c r="G11" t="n">
-        <v>111.7</v>
+        <v>110.66</v>
       </c>
       <c r="H11" t="n">
-        <v>108.98</v>
+        <v>108.26</v>
       </c>
       <c r="I11" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2698</v>
+        <v>0.2764</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1289</v>
+        <v>0.13</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
         <v>162</v>
@@ -17988,7 +17988,7 @@
         <v>164</v>
       </c>
       <c r="S11" t="n">
-        <v>1500.5</v>
+        <v>1501.2</v>
       </c>
     </row>
   </sheetData>
@@ -18420,31 +18420,31 @@
         <v>1101</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>1405.5</v>
+        <v>1408.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.049</v>
+        <v>-0.1959</v>
       </c>
       <c r="G7" t="n">
-        <v>97.48</v>
+        <v>98.2</v>
       </c>
       <c r="H7" t="n">
-        <v>106.33</v>
+        <v>106.3</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.85</v>
+        <v>-8.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3302</v>
+        <v>0.3251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1986</v>
+        <v>0.1992</v>
       </c>
       <c r="L7" t="n">
-        <v>-10.6</v>
+        <v>-10.2</v>
       </c>
       <c r="M7" t="n">
         <v>246</v>
@@ -18465,7 +18465,7 @@
         <v>248</v>
       </c>
       <c r="S7" t="n">
-        <v>1497.3</v>
+        <v>1493.1</v>
       </c>
     </row>
     <row r="8">
@@ -18481,31 +18481,31 @@
         <v>1470</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1383.6</v>
+        <v>1386.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9969</v>
+        <v>-1.08</v>
       </c>
       <c r="G8" t="n">
-        <v>100.84</v>
+        <v>100.94</v>
       </c>
       <c r="H8" t="n">
-        <v>105.74</v>
+        <v>105.94</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3225</v>
+        <v>0.3211</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1921</v>
+        <v>0.1912</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>216</v>
@@ -18526,7 +18526,7 @@
         <v>224</v>
       </c>
       <c r="S8" t="n">
-        <v>1470.7</v>
+        <v>1467.7</v>
       </c>
     </row>
   </sheetData>
@@ -21182,31 +21182,31 @@
         <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" t="n">
-        <v>2027.4</v>
+        <v>2031.1</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1622</v>
+        <v>2.7523</v>
       </c>
       <c r="G6" t="n">
-        <v>118.43</v>
+        <v>118.89</v>
       </c>
       <c r="H6" t="n">
-        <v>96.01000000000001</v>
+        <v>94.63</v>
       </c>
       <c r="I6" t="n">
-        <v>22.42</v>
+        <v>24.26</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3184</v>
+        <v>0.3199</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1465</v>
+        <v>0.1454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>12.2</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
@@ -21227,7 +21227,7 @@
         <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1686.9</v>
+        <v>1687.1</v>
       </c>
     </row>
     <row r="7">
@@ -21243,31 +21243,31 @@
         <v>1395</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>1836.3</v>
+        <v>1845.8</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8916</v>
+        <v>6.897</v>
       </c>
       <c r="G7" t="n">
-        <v>110.72</v>
+        <v>111.93</v>
       </c>
       <c r="H7" t="n">
-        <v>101.25</v>
+        <v>102.48</v>
       </c>
       <c r="I7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3192</v>
+        <v>0.3255</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1507</v>
+        <v>0.1494</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>44</v>
@@ -21288,7 +21288,7 @@
         <v>40</v>
       </c>
       <c r="S7" t="n">
-        <v>1679.3</v>
+        <v>1680.3</v>
       </c>
     </row>
     <row r="8">
@@ -21304,31 +21304,31 @@
         <v>1452</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1710.3</v>
+        <v>1703.6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4911</v>
+        <v>0.6918</v>
       </c>
       <c r="G8" t="n">
-        <v>107.75</v>
+        <v>106.36</v>
       </c>
       <c r="H8" t="n">
-        <v>99.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.36</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2866</v>
+        <v>0.2952</v>
       </c>
       <c r="K8" t="n">
-        <v>0.163</v>
+        <v>0.1655</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="M8" t="n">
         <v>57</v>
@@ -21349,7 +21349,7 @@
         <v>58</v>
       </c>
       <c r="S8" t="n">
-        <v>1659.8</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="9">
@@ -21365,31 +21365,31 @@
         <v>1416</v>
       </c>
       <c r="D9" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1820.5</v>
+        <v>1831.1</v>
       </c>
       <c r="F9" t="n">
-        <v>7.025</v>
+        <v>6.3402</v>
       </c>
       <c r="G9" t="n">
-        <v>114.77</v>
+        <v>113.8</v>
       </c>
       <c r="H9" t="n">
-        <v>110.49</v>
+        <v>109.32</v>
       </c>
       <c r="I9" t="n">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3115</v>
+        <v>0.3133</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1546</v>
+        <v>0.1536</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="M9" t="n">
         <v>53</v>
@@ -21410,7 +21410,7 @@
         <v>51</v>
       </c>
       <c r="S9" t="n">
-        <v>1687.9</v>
+        <v>1689.6</v>
       </c>
     </row>
     <row r="10">
@@ -21426,31 +21426,31 @@
         <v>1153</v>
       </c>
       <c r="D10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1728.9</v>
+        <v>1718.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3367</v>
+        <v>1.6688</v>
       </c>
       <c r="G10" t="n">
-        <v>105.7</v>
+        <v>104.83</v>
       </c>
       <c r="H10" t="n">
-        <v>98.19</v>
+        <v>97.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7.51</v>
+        <v>7.12</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2894</v>
+        <v>0.2867</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1614</v>
+        <v>0.1656</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>42</v>
@@ -21471,7 +21471,7 @@
         <v>46</v>
       </c>
       <c r="S10" t="n">
-        <v>1706.8</v>
+        <v>1713.3</v>
       </c>
     </row>
     <row r="11">
@@ -21487,31 +21487,31 @@
         <v>1140</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1927.8</v>
+        <v>1934.4</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2144</v>
+        <v>0.879</v>
       </c>
       <c r="G11" t="n">
-        <v>118.9</v>
+        <v>118.42</v>
       </c>
       <c r="H11" t="n">
-        <v>107.06</v>
+        <v>105.83</v>
       </c>
       <c r="I11" t="n">
-        <v>11.85</v>
+        <v>12.58</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3035</v>
+        <v>0.3042</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1427</v>
+        <v>0.1509</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.6</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
@@ -21532,7 +21532,7 @@
         <v>24</v>
       </c>
       <c r="S11" t="n">
-        <v>1718</v>
+        <v>1718.9</v>
       </c>
     </row>
     <row r="12">
@@ -21609,31 +21609,31 @@
         <v>1113</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" t="n">
-        <v>1690</v>
+        <v>1686.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2702</v>
+        <v>-1.0352</v>
       </c>
       <c r="G13" t="n">
-        <v>108.88</v>
+        <v>106.95</v>
       </c>
       <c r="H13" t="n">
-        <v>109.14</v>
+        <v>110.22</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.26</v>
+        <v>-3.27</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2792</v>
+        <v>0.2793</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1607</v>
+        <v>0.1676</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2</v>
+        <v>-8.6</v>
       </c>
       <c r="M13" t="n">
         <v>63</v>
@@ -21654,7 +21654,7 @@
         <v>67</v>
       </c>
       <c r="S13" t="n">
-        <v>1729.9</v>
+        <v>1742.3</v>
       </c>
     </row>
     <row r="14">
@@ -21731,31 +21731,31 @@
         <v>1329</v>
       </c>
       <c r="D15" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E15" t="n">
-        <v>1716.1</v>
+        <v>1706.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1554</v>
+        <v>-1.149</v>
       </c>
       <c r="G15" t="n">
-        <v>111.03</v>
+        <v>111.5</v>
       </c>
       <c r="H15" t="n">
-        <v>109.6</v>
+        <v>110.64</v>
       </c>
       <c r="I15" t="n">
-        <v>1.43</v>
+        <v>0.86</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2789</v>
+        <v>0.2847</v>
       </c>
       <c r="K15" t="n">
-        <v>0.155</v>
+        <v>0.1538</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="M15" t="n">
         <v>69</v>
@@ -21776,7 +21776,7 @@
         <v>79</v>
       </c>
       <c r="S15" t="n">
-        <v>1686</v>
+        <v>1692.8</v>
       </c>
     </row>
     <row r="16">
@@ -22330,31 +22330,31 @@
         <v>1177</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>1577.8</v>
+        <v>1569.4</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5995</v>
+        <v>5.3969</v>
       </c>
       <c r="G7" t="n">
-        <v>104.5</v>
+        <v>104</v>
       </c>
       <c r="H7" t="n">
-        <v>103.47</v>
+        <v>103.31</v>
       </c>
       <c r="I7" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3029</v>
+        <v>0.3003</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1707</v>
+        <v>0.1706</v>
       </c>
       <c r="L7" t="n">
-        <v>-4</v>
+        <v>-4.8</v>
       </c>
       <c r="M7" t="n">
         <v>102</v>
@@ -22375,7 +22375,7 @@
         <v>101</v>
       </c>
       <c r="S7" t="n">
-        <v>1606.7</v>
+        <v>1604.6</v>
       </c>
     </row>
     <row r="8">
@@ -22391,31 +22391,31 @@
         <v>1266</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1544.3</v>
+        <v>1537.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.9692</v>
+        <v>-6.3402</v>
       </c>
       <c r="G8" t="n">
-        <v>104.74</v>
+        <v>105.22</v>
       </c>
       <c r="H8" t="n">
-        <v>105.1</v>
+        <v>105.81</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.37</v>
+        <v>-0.59</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2957</v>
+        <v>0.2923</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1591</v>
+        <v>0.158</v>
       </c>
       <c r="L8" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="M8" t="n">
         <v>86</v>
@@ -22436,7 +22436,7 @@
         <v>91</v>
       </c>
       <c r="S8" t="n">
-        <v>1680.7</v>
+        <v>1671.3</v>
       </c>
     </row>
     <row r="9">
@@ -22452,31 +22452,31 @@
         <v>1139</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1626.2</v>
+        <v>1615.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8502</v>
+        <v>0.7248</v>
       </c>
       <c r="G9" t="n">
-        <v>110.93</v>
+        <v>111.07</v>
       </c>
       <c r="H9" t="n">
-        <v>108.36</v>
+        <v>109.32</v>
       </c>
       <c r="I9" t="n">
-        <v>2.57</v>
+        <v>1.75</v>
       </c>
       <c r="J9" t="n">
-        <v>0.308</v>
+        <v>0.3045</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1547</v>
+        <v>0.1528</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="M9" t="n">
         <v>82</v>
@@ -22497,7 +22497,7 @@
         <v>82</v>
       </c>
       <c r="S9" t="n">
-        <v>1622.8</v>
+        <v>1620.7</v>
       </c>
     </row>
     <row r="10">
@@ -22513,31 +22513,31 @@
         <v>1344</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E10" t="n">
-        <v>1563.1</v>
+        <v>1573.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8938</v>
+        <v>1.8058</v>
       </c>
       <c r="G10" t="n">
-        <v>115.02</v>
+        <v>115.49</v>
       </c>
       <c r="H10" t="n">
-        <v>112.74</v>
+        <v>112.67</v>
       </c>
       <c r="I10" t="n">
-        <v>2.27</v>
+        <v>2.82</v>
       </c>
       <c r="J10" t="n">
-        <v>0.266</v>
+        <v>0.265</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1661</v>
+        <v>0.1618</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>73</v>
@@ -22558,7 +22558,7 @@
         <v>84</v>
       </c>
       <c r="S10" t="n">
-        <v>1637.8</v>
+        <v>1638.4</v>
       </c>
     </row>
     <row r="11">
@@ -22574,31 +22574,31 @@
         <v>1462</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>1591.8</v>
+        <v>1598.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8435</v>
+        <v>-2.9105</v>
       </c>
       <c r="G11" t="n">
-        <v>108.76</v>
+        <v>109.08</v>
       </c>
       <c r="H11" t="n">
-        <v>111.44</v>
+        <v>111.34</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.69</v>
+        <v>-2.25</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2684</v>
+        <v>0.2721</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1355</v>
+        <v>0.1352</v>
       </c>
       <c r="L11" t="n">
-        <v>-6</v>
+        <v>-4.6</v>
       </c>
       <c r="M11" t="n">
         <v>97</v>
@@ -22619,7 +22619,7 @@
         <v>97</v>
       </c>
       <c r="S11" t="n">
-        <v>1639.3</v>
+        <v>1632.7</v>
       </c>
     </row>
     <row r="12">
@@ -22635,31 +22635,31 @@
         <v>1207</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E12" t="n">
-        <v>1558.3</v>
+        <v>1566.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9029</v>
+        <v>-4.7434</v>
       </c>
       <c r="G12" t="n">
-        <v>109.84</v>
+        <v>109.45</v>
       </c>
       <c r="H12" t="n">
-        <v>109.06</v>
+        <v>108.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.78</v>
+        <v>1.19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3014</v>
+        <v>0.3023</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1488</v>
+        <v>0.1484</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.8</v>
+        <v>-3.6</v>
       </c>
       <c r="M12" t="n">
         <v>87</v>
@@ -22680,7 +22680,7 @@
         <v>95</v>
       </c>
       <c r="S12" t="n">
-        <v>1640.1</v>
+        <v>1638.3</v>
       </c>
     </row>
   </sheetData>
@@ -22990,31 +22990,31 @@
         <v>1285</v>
       </c>
       <c r="D5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E5" t="n">
-        <v>1469.4</v>
+        <v>1464.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5005</v>
+        <v>-1.3592</v>
       </c>
       <c r="G5" t="n">
-        <v>107.3</v>
+        <v>106.92</v>
       </c>
       <c r="H5" t="n">
-        <v>109.17</v>
+        <v>109.44</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.87</v>
+        <v>-2.52</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1941</v>
+        <v>0.197</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1861</v>
+        <v>0.1841</v>
       </c>
       <c r="L5" t="n">
-        <v>-1</v>
+        <v>-4.8</v>
       </c>
       <c r="M5" t="n">
         <v>187</v>
@@ -23035,7 +23035,7 @@
         <v>199</v>
       </c>
       <c r="S5" t="n">
-        <v>1435.4</v>
+        <v>1433.9</v>
       </c>
     </row>
     <row r="6">
@@ -23173,31 +23173,31 @@
         <v>1225</v>
       </c>
       <c r="D8" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>1405.1</v>
+        <v>1410</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3769</v>
+        <v>-0.3498</v>
       </c>
       <c r="G8" t="n">
-        <v>110.53</v>
+        <v>110.28</v>
       </c>
       <c r="H8" t="n">
-        <v>107.11</v>
+        <v>106.53</v>
       </c>
       <c r="I8" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2756</v>
+        <v>0.2693</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1458</v>
+        <v>0.1475</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>165</v>
@@ -23218,7 +23218,7 @@
         <v>161</v>
       </c>
       <c r="S8" t="n">
-        <v>1412.5</v>
+        <v>1415.2</v>
       </c>
     </row>
     <row r="9">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -47,13 +47,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -72,12 +75,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,97 +459,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -800,31 +812,31 @@
         <v>1206</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1724.1</v>
+        <v>1709.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0204</v>
+        <v>-1.2025</v>
       </c>
       <c r="G6" t="n">
-        <v>113.12</v>
+        <v>111.94</v>
       </c>
       <c r="H6" t="n">
-        <v>104.31</v>
+        <v>104.41</v>
       </c>
       <c r="I6" t="n">
-        <v>8.81</v>
+        <v>7.53</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2641</v>
+        <v>0.2628</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1547</v>
+        <v>0.1529</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
         <v>94</v>
@@ -845,7 +857,7 @@
         <v>89</v>
       </c>
       <c r="S6" t="n">
-        <v>1517.3</v>
+        <v>1514.4</v>
       </c>
     </row>
     <row r="7">
@@ -861,31 +873,31 @@
         <v>1172</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1530.7</v>
+        <v>1533.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7149</v>
+        <v>-2.5567</v>
       </c>
       <c r="G7" t="n">
-        <v>108.86</v>
+        <v>108.41</v>
       </c>
       <c r="H7" t="n">
-        <v>105.24</v>
+        <v>104.66</v>
       </c>
       <c r="I7" t="n">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2859</v>
+        <v>0.2841</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1553</v>
+        <v>0.1548</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
         <v>107</v>
@@ -906,7 +918,7 @@
         <v>106</v>
       </c>
       <c r="S7" t="n">
-        <v>1541</v>
+        <v>1535.2</v>
       </c>
     </row>
     <row r="8">
@@ -922,31 +934,31 @@
         <v>1182</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1481.5</v>
+        <v>1489.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2564</v>
+        <v>-2.0712</v>
       </c>
       <c r="G8" t="n">
-        <v>108.87</v>
+        <v>109.05</v>
       </c>
       <c r="H8" t="n">
-        <v>107.5</v>
+        <v>107.32</v>
       </c>
       <c r="I8" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2905</v>
+        <v>0.2938</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1742</v>
+        <v>0.1676</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.6</v>
+        <v>-6</v>
       </c>
       <c r="M8" t="n">
         <v>133</v>
@@ -967,7 +979,7 @@
         <v>140</v>
       </c>
       <c r="S8" t="n">
-        <v>1537.9</v>
+        <v>1539.9</v>
       </c>
     </row>
     <row r="9">
@@ -983,31 +995,31 @@
         <v>1200</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1464.9</v>
+        <v>1460</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1637</v>
+        <v>1.265</v>
       </c>
       <c r="G9" t="n">
-        <v>104.6</v>
+        <v>104.45</v>
       </c>
       <c r="H9" t="n">
-        <v>102.16</v>
+        <v>102.55</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3135</v>
+        <v>0.3126</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1649</v>
+        <v>0.1658</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
       <c r="M9" t="n">
         <v>168</v>
@@ -1028,7 +1040,7 @@
         <v>174</v>
       </c>
       <c r="S9" t="n">
-        <v>1499</v>
+        <v>1499.4</v>
       </c>
     </row>
     <row r="10">
@@ -1044,31 +1056,31 @@
         <v>1203</v>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E10" t="n">
-        <v>1524.7</v>
+        <v>1529.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0633</v>
+        <v>-3.9222</v>
       </c>
       <c r="G10" t="n">
-        <v>115.25</v>
+        <v>114.99</v>
       </c>
       <c r="H10" t="n">
-        <v>105.33</v>
+        <v>104.97</v>
       </c>
       <c r="I10" t="n">
-        <v>9.92</v>
+        <v>10.02</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3298</v>
+        <v>0.3187</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1749</v>
+        <v>0.1742</v>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="M10" t="n">
         <v>83</v>
@@ -1089,7 +1101,7 @@
         <v>90</v>
       </c>
       <c r="S10" t="n">
-        <v>1531.5</v>
+        <v>1530.4</v>
       </c>
     </row>
     <row r="11">
@@ -1105,31 +1117,31 @@
         <v>1348</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E11" t="n">
-        <v>1565.4</v>
+        <v>1557.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7602</v>
+        <v>0.6788</v>
       </c>
       <c r="G11" t="n">
-        <v>104.48</v>
+        <v>104.75</v>
       </c>
       <c r="H11" t="n">
-        <v>101.92</v>
+        <v>102.46</v>
       </c>
       <c r="I11" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3041</v>
+        <v>0.3039</v>
       </c>
       <c r="K11" t="n">
-        <v>0.181</v>
+        <v>0.1824</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.4</v>
+        <v>-6</v>
       </c>
       <c r="M11" t="n">
         <v>134</v>
@@ -1150,7 +1162,7 @@
         <v>144</v>
       </c>
       <c r="S11" t="n">
-        <v>1516.7</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="12">
@@ -1288,31 +1300,31 @@
         <v>1382</v>
       </c>
       <c r="D14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" t="n">
-        <v>1537</v>
+        <v>1551.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.5665</v>
+        <v>-8.3871</v>
       </c>
       <c r="G14" t="n">
-        <v>112.49</v>
+        <v>111.9</v>
       </c>
       <c r="H14" t="n">
-        <v>110.94</v>
+        <v>110.28</v>
       </c>
       <c r="I14" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3278</v>
+        <v>0.3237</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1628</v>
+        <v>0.1631</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>-0.4</v>
       </c>
       <c r="M14" t="n">
         <v>160</v>
@@ -1333,7 +1345,7 @@
         <v>158</v>
       </c>
       <c r="S14" t="n">
-        <v>1525.6</v>
+        <v>1535.3</v>
       </c>
     </row>
     <row r="15">
@@ -1349,31 +1361,31 @@
         <v>1260</v>
       </c>
       <c r="D15" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" t="n">
-        <v>1402.1</v>
+        <v>1398.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.9937</v>
+        <v>-3.8026</v>
       </c>
       <c r="G15" t="n">
-        <v>101.2</v>
+        <v>100.52</v>
       </c>
       <c r="H15" t="n">
-        <v>114.47</v>
+        <v>113.86</v>
       </c>
       <c r="I15" t="n">
-        <v>-13.26</v>
+        <v>-13.35</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2855</v>
+        <v>0.2861</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1854</v>
+        <v>0.1872</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="M15" t="n">
         <v>293</v>
@@ -1394,7 +1406,7 @@
         <v>289</v>
       </c>
       <c r="S15" t="n">
-        <v>1553.9</v>
+        <v>1554</v>
       </c>
     </row>
   </sheetData>
@@ -1412,97 +1424,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -1765,31 +1777,31 @@
         <v>1458</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1859.5</v>
+        <v>1866.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6302</v>
+        <v>1.8886</v>
       </c>
       <c r="G6" t="n">
-        <v>119.64</v>
+        <v>119.65</v>
       </c>
       <c r="H6" t="n">
-        <v>108.42</v>
+        <v>108.66</v>
       </c>
       <c r="I6" t="n">
-        <v>11.21</v>
+        <v>10.99</v>
       </c>
       <c r="J6" t="n">
-        <v>0.276</v>
+        <v>0.2811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1244</v>
+        <v>0.123</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="M6" t="n">
         <v>23</v>
@@ -1810,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="S6" t="n">
-        <v>1701.3</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="7">
@@ -1826,31 +1838,31 @@
         <v>1417</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1859.1</v>
+        <v>1863</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2498</v>
+        <v>2.4395</v>
       </c>
       <c r="G7" t="n">
-        <v>117.64</v>
+        <v>116.91</v>
       </c>
       <c r="H7" t="n">
-        <v>107.04</v>
+        <v>106.2</v>
       </c>
       <c r="I7" t="n">
-        <v>10.59</v>
+        <v>10.71</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2985</v>
+        <v>0.2986</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1288</v>
+        <v>0.1298</v>
       </c>
       <c r="L7" t="n">
-        <v>11.2</v>
+        <v>13.6</v>
       </c>
       <c r="M7" t="n">
         <v>28</v>
@@ -1871,7 +1883,7 @@
         <v>34</v>
       </c>
       <c r="S7" t="n">
-        <v>1689.3</v>
+        <v>1683.8</v>
       </c>
     </row>
     <row r="8">
@@ -1887,31 +1899,31 @@
         <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1955.6</v>
+        <v>1959</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3963</v>
+        <v>-0.051</v>
       </c>
       <c r="G8" t="n">
-        <v>124.64</v>
+        <v>124.95</v>
       </c>
       <c r="H8" t="n">
-        <v>107.6</v>
+        <v>107.45</v>
       </c>
       <c r="I8" t="n">
-        <v>17.04</v>
+        <v>17.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3051</v>
+        <v>0.3095</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1348</v>
+        <v>0.1344</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
@@ -1932,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>1746.9</v>
+        <v>1740.1</v>
       </c>
     </row>
     <row r="9">
@@ -1948,31 +1960,31 @@
         <v>1326</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1799.9</v>
+        <v>1817</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5472</v>
+        <v>1.7194</v>
       </c>
       <c r="G9" t="n">
-        <v>118.74</v>
+        <v>118.68</v>
       </c>
       <c r="H9" t="n">
-        <v>107.91</v>
+        <v>108.16</v>
       </c>
       <c r="I9" t="n">
-        <v>10.83</v>
+        <v>10.52</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2524</v>
+        <v>0.2526</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1503</v>
+        <v>0.1502</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
         <v>26</v>
@@ -1993,7 +2005,7 @@
         <v>30</v>
       </c>
       <c r="S9" t="n">
-        <v>1700.1</v>
+        <v>1705.5</v>
       </c>
     </row>
     <row r="10">
@@ -2009,31 +2021,31 @@
         <v>1234</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" t="n">
-        <v>1848.9</v>
+        <v>1831.8</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6941</v>
+        <v>3.3952</v>
       </c>
       <c r="G10" t="n">
-        <v>118.64</v>
+        <v>118.92</v>
       </c>
       <c r="H10" t="n">
-        <v>103.68</v>
+        <v>104.81</v>
       </c>
       <c r="I10" t="n">
-        <v>14.95</v>
+        <v>14.12</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2884</v>
+        <v>0.2886</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1443</v>
+        <v>0.1455</v>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>-1.2</v>
       </c>
       <c r="M10" t="n">
         <v>24</v>
@@ -2054,7 +2066,7 @@
         <v>25</v>
       </c>
       <c r="S10" t="n">
-        <v>1707.5</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="11">
@@ -2192,31 +2204,31 @@
         <v>1449</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E13" t="n">
-        <v>1660.8</v>
+        <v>1654.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8763</v>
+        <v>1.8284</v>
       </c>
       <c r="G13" t="n">
-        <v>111.56</v>
+        <v>112.2</v>
       </c>
       <c r="H13" t="n">
-        <v>106.64</v>
+        <v>107.64</v>
       </c>
       <c r="I13" t="n">
-        <v>4.93</v>
+        <v>4.56</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2978</v>
+        <v>0.3038</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1494</v>
+        <v>0.1484</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="M13" t="n">
         <v>54</v>
@@ -2237,7 +2249,7 @@
         <v>61</v>
       </c>
       <c r="S13" t="n">
-        <v>1689.5</v>
+        <v>1695.6</v>
       </c>
     </row>
     <row r="14">
@@ -2314,31 +2326,31 @@
         <v>1353</v>
       </c>
       <c r="D15" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" t="n">
-        <v>1567.8</v>
+        <v>1563.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7645</v>
+        <v>-2.5391</v>
       </c>
       <c r="G15" t="n">
-        <v>105.15</v>
+        <v>104.26</v>
       </c>
       <c r="H15" t="n">
-        <v>111.69</v>
+        <v>111.5</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.54</v>
+        <v>-7.24</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3141</v>
+        <v>0.3123</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1499</v>
+        <v>0.1506</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M15" t="n">
         <v>129</v>
@@ -2359,7 +2371,7 @@
         <v>143</v>
       </c>
       <c r="S15" t="n">
-        <v>1683.9</v>
+        <v>1691.9</v>
       </c>
     </row>
     <row r="16">
@@ -2375,31 +2387,31 @@
         <v>1321</v>
       </c>
       <c r="D16" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" t="n">
-        <v>1607</v>
+        <v>1603.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.6942</v>
+        <v>-3.3221</v>
       </c>
       <c r="G16" t="n">
-        <v>111.92</v>
+        <v>111.96</v>
       </c>
       <c r="H16" t="n">
-        <v>109.76</v>
+        <v>110.87</v>
       </c>
       <c r="I16" t="n">
-        <v>2.15</v>
+        <v>1.09</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2792</v>
+        <v>0.2804</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1299</v>
+        <v>0.1303</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>66</v>
@@ -2420,7 +2432,7 @@
         <v>70</v>
       </c>
       <c r="S16" t="n">
-        <v>1697.4</v>
+        <v>1706.6</v>
       </c>
     </row>
     <row r="17">
@@ -2621,97 +2633,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2852,31 +2864,31 @@
         <v>1168</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9192</v>
+        <v>2.9262</v>
       </c>
       <c r="G4" t="n">
-        <v>108.16</v>
+        <v>107.91</v>
       </c>
       <c r="H4" t="n">
-        <v>110.11</v>
+        <v>109.34</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.95</v>
+        <v>-1.43</v>
       </c>
       <c r="J4" t="n">
-        <v>0.256</v>
+        <v>0.2569</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1447</v>
+        <v>0.1476</v>
       </c>
       <c r="L4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>169</v>
@@ -2897,7 +2909,7 @@
         <v>180</v>
       </c>
       <c r="S4" t="n">
-        <v>1480.3</v>
+        <v>1479.9</v>
       </c>
     </row>
     <row r="5">
@@ -2913,31 +2925,31 @@
         <v>1169</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1505.9</v>
+        <v>1516</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7623</v>
+        <v>1.7017</v>
       </c>
       <c r="G5" t="n">
-        <v>104.81</v>
+        <v>105.24</v>
       </c>
       <c r="H5" t="n">
-        <v>105.37</v>
+        <v>105.09</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.57</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.277</v>
+        <v>0.274</v>
       </c>
       <c r="K5" t="n">
-        <v>0.172</v>
+        <v>0.1702</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.2</v>
+        <v>-2.6</v>
       </c>
       <c r="M5" t="n">
         <v>176</v>
@@ -2958,7 +2970,7 @@
         <v>190</v>
       </c>
       <c r="S5" t="n">
-        <v>1451.3</v>
+        <v>1458.3</v>
       </c>
     </row>
     <row r="6">
@@ -2974,31 +2986,31 @@
         <v>1471</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1612.4</v>
+        <v>1602.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.2102</v>
+        <v>-7.8974</v>
       </c>
       <c r="G6" t="n">
-        <v>107.17</v>
+        <v>106.76</v>
       </c>
       <c r="H6" t="n">
-        <v>100.89</v>
+        <v>101.25</v>
       </c>
       <c r="I6" t="n">
-        <v>6.28</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2341</v>
+        <v>0.2366</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1584</v>
+        <v>0.16</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
         <v>113</v>
@@ -3019,7 +3031,7 @@
         <v>120</v>
       </c>
       <c r="S6" t="n">
-        <v>1449.6</v>
+        <v>1452.3</v>
       </c>
     </row>
     <row r="7">
@@ -3035,31 +3047,31 @@
         <v>1413</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1478.5</v>
+        <v>1473.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3411</v>
+        <v>-0.3098</v>
       </c>
       <c r="G7" t="n">
-        <v>106.92</v>
+        <v>105.97</v>
       </c>
       <c r="H7" t="n">
-        <v>105.91</v>
+        <v>105.64</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>0.25</v>
+        <v>0.2488</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1741</v>
+        <v>0.175</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>-2.8</v>
       </c>
       <c r="M7" t="n">
         <v>155</v>
@@ -3080,7 +3092,7 @@
         <v>176</v>
       </c>
       <c r="S7" t="n">
-        <v>1457.1</v>
+        <v>1454.3</v>
       </c>
     </row>
     <row r="8">
@@ -3220,97 +3232,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4124,97 +4136,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4355,31 +4367,31 @@
         <v>1443</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1483.2</v>
+        <v>1477.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.316</v>
+        <v>-3.1109</v>
       </c>
       <c r="G4" t="n">
-        <v>107.79</v>
+        <v>108.18</v>
       </c>
       <c r="H4" t="n">
-        <v>106.34</v>
+        <v>106.95</v>
       </c>
       <c r="I4" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3081</v>
+        <v>0.3082</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1373</v>
+        <v>0.1368</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
         <v>167</v>
@@ -4400,7 +4412,7 @@
         <v>156</v>
       </c>
       <c r="S4" t="n">
-        <v>1482.7</v>
+        <v>1484.4</v>
       </c>
     </row>
     <row r="5">
@@ -4416,31 +4428,31 @@
         <v>1256</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>1511.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7753</v>
+        <v>-1.5513</v>
       </c>
       <c r="G5" t="n">
-        <v>102.77</v>
+        <v>103.46</v>
       </c>
       <c r="H5" t="n">
-        <v>102.38</v>
+        <v>102.91</v>
       </c>
       <c r="I5" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3278</v>
+        <v>0.329</v>
       </c>
       <c r="K5" t="n">
-        <v>0.176</v>
+        <v>0.1746</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
         <v>208</v>
@@ -4461,7 +4473,7 @@
         <v>213</v>
       </c>
       <c r="S5" t="n">
-        <v>1464.3</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6">
@@ -4477,31 +4489,31 @@
         <v>1292</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1489.7</v>
+        <v>1484</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.8936</v>
+        <v>-3.7282</v>
       </c>
       <c r="G6" t="n">
-        <v>107.97</v>
+        <v>107.74</v>
       </c>
       <c r="H6" t="n">
-        <v>108.68</v>
+        <v>109.32</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.71</v>
+        <v>-1.58</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2792</v>
+        <v>0.2833</v>
       </c>
       <c r="K6" t="n">
-        <v>0.158</v>
+        <v>0.1618</v>
       </c>
       <c r="L6" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
         <v>171</v>
@@ -4522,7 +4534,7 @@
         <v>154</v>
       </c>
       <c r="S6" t="n">
-        <v>1523.7</v>
+        <v>1524.2</v>
       </c>
     </row>
     <row r="7">
@@ -4538,31 +4550,31 @@
         <v>1244</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1501.9</v>
+        <v>1507.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3344</v>
+        <v>-0.3139</v>
       </c>
       <c r="G7" t="n">
-        <v>110.51</v>
+        <v>111.26</v>
       </c>
       <c r="H7" t="n">
-        <v>108.69</v>
+        <v>108.94</v>
       </c>
       <c r="I7" t="n">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3343</v>
+        <v>0.3332</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1639</v>
+        <v>0.1652</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
         <v>178</v>
@@ -4583,7 +4595,7 @@
         <v>170</v>
       </c>
       <c r="S7" t="n">
-        <v>1469.9</v>
+        <v>1470.6</v>
       </c>
     </row>
     <row r="8">
@@ -4845,97 +4857,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5627,97 +5639,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5982,97 +5994,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6703,97 +6715,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6815,7 +6827,7 @@
         <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>1409</v>
+        <v>1404.4</v>
       </c>
       <c r="F2" t="n">
         <v>3.2279</v>
@@ -6934,31 +6946,31 @@
         <v>1300</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1281.6</v>
+        <v>1293</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.603</v>
+        <v>-1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>100.54</v>
+        <v>101.79</v>
       </c>
       <c r="H4" t="n">
-        <v>116.12</v>
+        <v>115.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.57</v>
+        <v>-14.17</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3056</v>
+        <v>0.3052</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1777</v>
+        <v>0.1785</v>
       </c>
       <c r="L4" t="n">
-        <v>-8.800000000000001</v>
+        <v>-4.8</v>
       </c>
       <c r="M4" t="n">
         <v>353</v>
@@ -6979,7 +6991,7 @@
         <v>347</v>
       </c>
       <c r="S4" t="n">
-        <v>1390.3</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="5">
@@ -6995,31 +7007,31 @@
         <v>1313</v>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1364.5</v>
+        <v>1365.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.9095</v>
+        <v>-3.7209</v>
       </c>
       <c r="G5" t="n">
-        <v>102.86</v>
+        <v>103.07</v>
       </c>
       <c r="H5" t="n">
-        <v>106.82</v>
+        <v>107.13</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.96</v>
+        <v>-4.06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3057</v>
+        <v>0.3094</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1775</v>
+        <v>0.1792</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>321</v>
@@ -7040,7 +7052,7 @@
         <v>313</v>
       </c>
       <c r="S5" t="n">
-        <v>1377.4</v>
+        <v>1371.6</v>
       </c>
     </row>
     <row r="6">
@@ -7056,31 +7068,31 @@
         <v>1354</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1259.4</v>
+        <v>1257.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.2527</v>
+        <v>-3.0547</v>
       </c>
       <c r="G6" t="n">
-        <v>96.31</v>
+        <v>97.12</v>
       </c>
       <c r="H6" t="n">
-        <v>114.29</v>
+        <v>114.45</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.98</v>
+        <v>-17.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3399</v>
+        <v>0.345</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1984</v>
+        <v>0.2009</v>
       </c>
       <c r="L6" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>356</v>
@@ -7101,7 +7113,7 @@
         <v>357</v>
       </c>
       <c r="S6" t="n">
-        <v>1393</v>
+        <v>1393.4</v>
       </c>
     </row>
     <row r="7">
@@ -7117,31 +7129,31 @@
         <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1224.1</v>
+        <v>1223</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5285</v>
+        <v>-0.5586</v>
       </c>
       <c r="G7" t="n">
-        <v>94.77</v>
+        <v>95.45</v>
       </c>
       <c r="H7" t="n">
-        <v>108.39</v>
+        <v>109.09</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.62</v>
+        <v>-13.64</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3071</v>
+        <v>0.3135</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2245</v>
+        <v>0.2243</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="M7" t="n">
         <v>348</v>
@@ -7162,7 +7174,7 @@
         <v>350</v>
       </c>
       <c r="S7" t="n">
-        <v>1406.3</v>
+        <v>1403.1</v>
       </c>
     </row>
     <row r="8">
@@ -7241,97 +7253,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7350,31 +7362,31 @@
         <v>1275</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>1775.2</v>
+        <v>1758.6</v>
       </c>
       <c r="F2" t="n">
-        <v>9.651999999999999</v>
+        <v>9.362500000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>120.89</v>
+        <v>120.74</v>
       </c>
       <c r="H2" t="n">
-        <v>105.23</v>
+        <v>105.88</v>
       </c>
       <c r="I2" t="n">
-        <v>15.66</v>
+        <v>14.87</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2107</v>
+        <v>0.2186</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1402</v>
+        <v>0.1413</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
         <v>91</v>
@@ -7395,7 +7407,7 @@
         <v>55</v>
       </c>
       <c r="S2" t="n">
-        <v>1414.6</v>
+        <v>1416.9</v>
       </c>
     </row>
     <row r="3">
@@ -7411,31 +7423,31 @@
         <v>1103</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E3" t="n">
-        <v>1694.4</v>
+        <v>1696.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1.739</v>
+        <v>1.818</v>
       </c>
       <c r="G3" t="n">
-        <v>123.02</v>
+        <v>122.16</v>
       </c>
       <c r="H3" t="n">
-        <v>104.03</v>
+        <v>104.24</v>
       </c>
       <c r="I3" t="n">
-        <v>18.98</v>
+        <v>17.92</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2846</v>
+        <v>0.2856</v>
       </c>
       <c r="K3" t="n">
-        <v>0.152</v>
+        <v>0.1521</v>
       </c>
       <c r="L3" t="n">
-        <v>20.2</v>
+        <v>18.2</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
@@ -7456,7 +7468,7 @@
         <v>52</v>
       </c>
       <c r="S3" t="n">
-        <v>1476.4</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="4">
@@ -7472,31 +7484,31 @@
         <v>1245</v>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1604.4</v>
+        <v>1608.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3083</v>
+        <v>0.1871</v>
       </c>
       <c r="G4" t="n">
-        <v>112.38</v>
+        <v>112.75</v>
       </c>
       <c r="H4" t="n">
-        <v>109.12</v>
+        <v>109.04</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3198</v>
+        <v>0.3174</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1818</v>
+        <v>0.177</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
         <v>154</v>
@@ -7517,7 +7529,7 @@
         <v>147</v>
       </c>
       <c r="S4" t="n">
-        <v>1468.3</v>
+        <v>1469.5</v>
       </c>
     </row>
     <row r="5">
@@ -7533,31 +7545,31 @@
         <v>1405</v>
       </c>
       <c r="D5" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1454.8</v>
+        <v>1458.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6694</v>
+        <v>-0.6373</v>
       </c>
       <c r="G5" t="n">
-        <v>115.34</v>
+        <v>114.97</v>
       </c>
       <c r="H5" t="n">
-        <v>111.66</v>
+        <v>111.68</v>
       </c>
       <c r="I5" t="n">
-        <v>3.68</v>
+        <v>3.29</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2982</v>
+        <v>0.2985</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1389</v>
+        <v>0.1405</v>
       </c>
       <c r="L5" t="n">
-        <v>11.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>135</v>
@@ -7578,7 +7590,7 @@
         <v>146</v>
       </c>
       <c r="S5" t="n">
-        <v>1496.5</v>
+        <v>1494.4</v>
       </c>
     </row>
     <row r="6">
@@ -7594,31 +7606,31 @@
         <v>1132</v>
       </c>
       <c r="D6" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1421.6</v>
+        <v>1417.9</v>
       </c>
       <c r="F6" t="n">
-        <v>1.158</v>
+        <v>1.0539</v>
       </c>
       <c r="G6" t="n">
-        <v>108.5</v>
+        <v>108.63</v>
       </c>
       <c r="H6" t="n">
-        <v>101.55</v>
+        <v>102.12</v>
       </c>
       <c r="I6" t="n">
-        <v>6.95</v>
+        <v>6.51</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2733</v>
+        <v>0.2716</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1584</v>
+        <v>0.159</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
         <v>146</v>
@@ -7639,7 +7651,7 @@
         <v>155</v>
       </c>
       <c r="S6" t="n">
-        <v>1462.9</v>
+        <v>1463.5</v>
       </c>
     </row>
     <row r="7">
@@ -7655,31 +7667,31 @@
         <v>1325</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1462.5</v>
+        <v>1458.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3882</v>
+        <v>2.132</v>
       </c>
       <c r="G7" t="n">
-        <v>107.94</v>
+        <v>107.68</v>
       </c>
       <c r="H7" t="n">
-        <v>112.06</v>
+        <v>112.31</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.11</v>
+        <v>-4.64</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2911</v>
+        <v>0.2895</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1442</v>
+        <v>0.1461</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2</v>
+        <v>-5.8</v>
       </c>
       <c r="M7" t="n">
         <v>227</v>
@@ -7700,7 +7712,7 @@
         <v>227</v>
       </c>
       <c r="S7" t="n">
-        <v>1513.3</v>
+        <v>1514.4</v>
       </c>
     </row>
     <row r="8">
@@ -7716,31 +7728,31 @@
         <v>1138</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1384.9</v>
+        <v>1382.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3277</v>
+        <v>-0.4287</v>
       </c>
       <c r="G8" t="n">
-        <v>115.04</v>
+        <v>114.27</v>
       </c>
       <c r="H8" t="n">
-        <v>114.08</v>
+        <v>113.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2767</v>
+        <v>0.272</v>
       </c>
       <c r="K8" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="L8" t="n">
-        <v>-6</v>
+        <v>-7.4</v>
       </c>
       <c r="M8" t="n">
         <v>207</v>
@@ -7761,7 +7773,7 @@
         <v>198</v>
       </c>
       <c r="S8" t="n">
-        <v>1459.6</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="9">
@@ -7777,31 +7789,31 @@
         <v>1269</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1478.9</v>
+        <v>1495.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.058</v>
+        <v>0.8792</v>
       </c>
       <c r="G9" t="n">
-        <v>109.4</v>
+        <v>110.01</v>
       </c>
       <c r="H9" t="n">
-        <v>107.53</v>
+        <v>108.12</v>
       </c>
       <c r="I9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2938</v>
+        <v>0.2974</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1727</v>
+        <v>0.1712</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.2</v>
+        <v>-1.6</v>
       </c>
       <c r="M9" t="n">
         <v>201</v>
@@ -7822,7 +7834,7 @@
         <v>203</v>
       </c>
       <c r="S9" t="n">
-        <v>1451.3</v>
+        <v>1464.6</v>
       </c>
     </row>
   </sheetData>
@@ -7840,97 +7852,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8622,97 +8634,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8731,31 +8743,31 @@
         <v>1181</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>2183.9</v>
+        <v>2185.1</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6873</v>
+        <v>3.7089</v>
       </c>
       <c r="G2" t="n">
-        <v>123.11</v>
+        <v>123.04</v>
       </c>
       <c r="H2" t="n">
-        <v>93.04000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="I2" t="n">
-        <v>30.07</v>
+        <v>28.93</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2884</v>
+        <v>0.2948</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1511</v>
+        <v>0.1547</v>
       </c>
       <c r="L2" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -8776,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1701.5</v>
+        <v>1695.7</v>
       </c>
     </row>
     <row r="3">
@@ -8792,31 +8804,31 @@
         <v>1438</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E3" t="n">
-        <v>1956.5</v>
+        <v>1963.2</v>
       </c>
       <c r="F3" t="n">
-        <v>13.4946</v>
+        <v>13.0176</v>
       </c>
       <c r="G3" t="n">
-        <v>118.84</v>
+        <v>118.86</v>
       </c>
       <c r="H3" t="n">
-        <v>100.06</v>
+        <v>100.31</v>
       </c>
       <c r="I3" t="n">
-        <v>18.77</v>
+        <v>18.55</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3168</v>
+        <v>0.3146</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1532</v>
+        <v>0.1527</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
@@ -8837,7 +8849,7 @@
         <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>1639.2</v>
+        <v>1642.5</v>
       </c>
     </row>
     <row r="4">
@@ -8853,31 +8865,31 @@
         <v>1274</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1761</v>
+        <v>1780</v>
       </c>
       <c r="F4" t="n">
-        <v>12.4806</v>
+        <v>12.0727</v>
       </c>
       <c r="G4" t="n">
-        <v>118.15</v>
+        <v>117.75</v>
       </c>
       <c r="H4" t="n">
-        <v>101.88</v>
+        <v>101.58</v>
       </c>
       <c r="I4" t="n">
-        <v>16.27</v>
+        <v>16.16</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3077</v>
+        <v>0.3083</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1596</v>
+        <v>0.1583</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="M4" t="n">
         <v>29</v>
@@ -8898,7 +8910,7 @@
         <v>32</v>
       </c>
       <c r="S4" t="n">
-        <v>1617.1</v>
+        <v>1624.7</v>
       </c>
     </row>
     <row r="5">
@@ -8914,31 +8926,31 @@
         <v>1314</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1917.6</v>
+        <v>1899.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3735</v>
+        <v>2.2848</v>
       </c>
       <c r="G5" t="n">
-        <v>115.09</v>
+        <v>115.28</v>
       </c>
       <c r="H5" t="n">
-        <v>103.39</v>
+        <v>103.72</v>
       </c>
       <c r="I5" t="n">
-        <v>11.71</v>
+        <v>11.56</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2653</v>
+        <v>0.2596</v>
       </c>
       <c r="K5" t="n">
-        <v>0.14</v>
+        <v>0.1375</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M5" t="n">
         <v>30</v>
@@ -8959,7 +8971,7 @@
         <v>23</v>
       </c>
       <c r="S5" t="n">
-        <v>1676</v>
+        <v>1677.4</v>
       </c>
     </row>
     <row r="6">
@@ -8975,31 +8987,31 @@
         <v>1155</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1845.5</v>
+        <v>1863.6</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0058</v>
+        <v>2.7155</v>
       </c>
       <c r="G6" t="n">
-        <v>113.18</v>
+        <v>113.29</v>
       </c>
       <c r="H6" t="n">
-        <v>100.7</v>
+        <v>101.28</v>
       </c>
       <c r="I6" t="n">
-        <v>12.47</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2545</v>
+        <v>0.2541</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1366</v>
+        <v>0.1378</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
         <v>38</v>
@@ -9020,7 +9032,7 @@
         <v>36</v>
       </c>
       <c r="S6" t="n">
-        <v>1644.4</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="7">
@@ -9036,31 +9048,31 @@
         <v>1257</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1855.9</v>
+        <v>1836.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8167</v>
+        <v>-2.5958</v>
       </c>
       <c r="G7" t="n">
-        <v>119.15</v>
+        <v>118.9</v>
       </c>
       <c r="H7" t="n">
-        <v>101.26</v>
+        <v>101.88</v>
       </c>
       <c r="I7" t="n">
-        <v>17.89</v>
+        <v>17.02</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2908</v>
+        <v>0.289</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1584</v>
+        <v>0.1597</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
         <v>16</v>
@@ -9081,7 +9093,7 @@
         <v>14</v>
       </c>
       <c r="S7" t="n">
-        <v>1683.7</v>
+        <v>1686.1</v>
       </c>
     </row>
     <row r="8">
@@ -9097,31 +9109,31 @@
         <v>1301</v>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1740.7</v>
+        <v>1734</v>
       </c>
       <c r="F8" t="n">
-        <v>7.3141</v>
+        <v>6.962</v>
       </c>
       <c r="G8" t="n">
-        <v>120.03</v>
+        <v>119.36</v>
       </c>
       <c r="H8" t="n">
-        <v>109.14</v>
+        <v>109.32</v>
       </c>
       <c r="I8" t="n">
-        <v>10.89</v>
+        <v>10.04</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2784</v>
+        <v>0.2802</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1277</v>
+        <v>0.1288</v>
       </c>
       <c r="L8" t="n">
-        <v>-11</v>
+        <v>-6.6</v>
       </c>
       <c r="M8" t="n">
         <v>36</v>
@@ -9142,7 +9154,7 @@
         <v>35</v>
       </c>
       <c r="S8" t="n">
-        <v>1669.5</v>
+        <v>1681.7</v>
       </c>
     </row>
     <row r="9">
@@ -9158,31 +9170,31 @@
         <v>1199</v>
       </c>
       <c r="D9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1636</v>
+        <v>1634.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3568</v>
+        <v>0.1136</v>
       </c>
       <c r="G9" t="n">
-        <v>112.09</v>
+        <v>112.14</v>
       </c>
       <c r="H9" t="n">
-        <v>108.2</v>
+        <v>108.52</v>
       </c>
       <c r="I9" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3111</v>
+        <v>0.309</v>
       </c>
       <c r="K9" t="n">
-        <v>0.148</v>
+        <v>0.1488</v>
       </c>
       <c r="L9" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="M9" t="n">
         <v>65</v>
@@ -9203,7 +9215,7 @@
         <v>69</v>
       </c>
       <c r="S9" t="n">
-        <v>1657.6</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="10">
@@ -9648,97 +9660,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -9757,31 +9769,31 @@
         <v>1429</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>1869.8</v>
+        <v>1875.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2419</v>
+        <v>0.1664</v>
       </c>
       <c r="G2" t="n">
-        <v>120.49</v>
+        <v>120.08</v>
       </c>
       <c r="H2" t="n">
-        <v>105.01</v>
+        <v>104.01</v>
       </c>
       <c r="I2" t="n">
-        <v>15.48</v>
+        <v>16.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3065</v>
+        <v>0.305</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1487</v>
+        <v>0.1501</v>
       </c>
       <c r="L2" t="n">
-        <v>-7.6</v>
+        <v>-3</v>
       </c>
       <c r="M2" t="n">
         <v>35</v>
@@ -9802,7 +9814,7 @@
         <v>29</v>
       </c>
       <c r="S2" t="n">
-        <v>1599.2</v>
+        <v>1599.4</v>
       </c>
     </row>
     <row r="3">
@@ -9818,31 +9830,31 @@
         <v>1361</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E3" t="n">
-        <v>1788.2</v>
+        <v>1796.6</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5794</v>
+        <v>5.1383</v>
       </c>
       <c r="G3" t="n">
-        <v>110.7</v>
+        <v>110.37</v>
       </c>
       <c r="H3" t="n">
-        <v>101.58</v>
+        <v>101.04</v>
       </c>
       <c r="I3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2605</v>
+        <v>0.2637</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1642</v>
+        <v>0.1654</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>47</v>
@@ -9863,7 +9875,7 @@
         <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>1652.6</v>
+        <v>1653.1</v>
       </c>
     </row>
     <row r="4">
@@ -9879,31 +9891,31 @@
         <v>1307</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1811.2</v>
+        <v>1812.6</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4739</v>
+        <v>3.0887</v>
       </c>
       <c r="G4" t="n">
-        <v>115.21</v>
+        <v>115.92</v>
       </c>
       <c r="H4" t="n">
-        <v>103.06</v>
+        <v>103.11</v>
       </c>
       <c r="I4" t="n">
-        <v>12.14</v>
+        <v>12.81</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2768</v>
+        <v>0.2783</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1435</v>
+        <v>0.1445</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.4</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
@@ -9924,7 +9936,7 @@
         <v>45</v>
       </c>
       <c r="S4" t="n">
-        <v>1598.9</v>
+        <v>1586.9</v>
       </c>
     </row>
     <row r="5">
@@ -9940,31 +9952,31 @@
         <v>1213</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1720.3</v>
+        <v>1708.1</v>
       </c>
       <c r="F5" t="n">
-        <v>6.4863</v>
+        <v>6.2885</v>
       </c>
       <c r="G5" t="n">
-        <v>110.07</v>
+        <v>110.21</v>
       </c>
       <c r="H5" t="n">
-        <v>99.11</v>
+        <v>100.23</v>
       </c>
       <c r="I5" t="n">
-        <v>10.96</v>
+        <v>9.98</v>
       </c>
       <c r="J5" t="n">
-        <v>0.275</v>
+        <v>0.2731</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1725</v>
+        <v>0.1723</v>
       </c>
       <c r="L5" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
         <v>60</v>
@@ -9985,7 +9997,7 @@
         <v>68</v>
       </c>
       <c r="S5" t="n">
-        <v>1572.8</v>
+        <v>1581.4</v>
       </c>
     </row>
     <row r="6">
@@ -10001,31 +10013,31 @@
         <v>1305</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1737.2</v>
+        <v>1749.4</v>
       </c>
       <c r="F6" t="n">
-        <v>6.361</v>
+        <v>5.9785</v>
       </c>
       <c r="G6" t="n">
-        <v>112.93</v>
+        <v>113.3</v>
       </c>
       <c r="H6" t="n">
-        <v>104.74</v>
+        <v>105.71</v>
       </c>
       <c r="I6" t="n">
-        <v>8.19</v>
+        <v>7.59</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1435</v>
+        <v>0.1436</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="M6" t="n">
         <v>76</v>
@@ -10046,7 +10058,7 @@
         <v>73</v>
       </c>
       <c r="S6" t="n">
-        <v>1587.8</v>
+        <v>1597.4</v>
       </c>
     </row>
     <row r="7">
@@ -10123,31 +10135,31 @@
         <v>1161</v>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1664.2</v>
+        <v>1655.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.9476</v>
+        <v>-4.6276</v>
       </c>
       <c r="G8" t="n">
-        <v>118.83</v>
+        <v>117.7</v>
       </c>
       <c r="H8" t="n">
-        <v>112.9</v>
+        <v>112.56</v>
       </c>
       <c r="I8" t="n">
-        <v>5.93</v>
+        <v>5.14</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2638</v>
+        <v>0.2637</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1735</v>
+        <v>0.1761</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
         <v>85</v>
@@ -10168,7 +10180,7 @@
         <v>87</v>
       </c>
       <c r="S8" t="n">
-        <v>1553.3</v>
+        <v>1564.6</v>
       </c>
     </row>
     <row r="9">
@@ -10184,31 +10196,31 @@
         <v>1424</v>
       </c>
       <c r="D9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1650.4</v>
+        <v>1644.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6984</v>
+        <v>1.7904</v>
       </c>
       <c r="G9" t="n">
-        <v>111.95</v>
+        <v>111.01</v>
       </c>
       <c r="H9" t="n">
-        <v>111.26</v>
+        <v>111.62</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.62</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2937</v>
+        <v>0.2955</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1604</v>
+        <v>0.1654</v>
       </c>
       <c r="L9" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
         <v>104</v>
@@ -10229,7 +10241,7 @@
         <v>111</v>
       </c>
       <c r="S9" t="n">
-        <v>1617.1</v>
+        <v>1628.6</v>
       </c>
     </row>
     <row r="10">
@@ -10367,31 +10379,31 @@
         <v>1363</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E12" t="n">
-        <v>1374.8</v>
+        <v>1373.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.063</v>
+        <v>-2.8726</v>
       </c>
       <c r="G12" t="n">
-        <v>107.46</v>
+        <v>107.53</v>
       </c>
       <c r="H12" t="n">
-        <v>119.84</v>
+        <v>120.61</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.39</v>
+        <v>-13.08</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3361</v>
+        <v>0.3376</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1432</v>
+        <v>0.1448</v>
       </c>
       <c r="L12" t="n">
-        <v>-4</v>
+        <v>-8.4</v>
       </c>
       <c r="M12" t="n">
         <v>237</v>
@@ -10412,7 +10424,7 @@
         <v>256</v>
       </c>
       <c r="S12" t="n">
-        <v>1591.5</v>
+        <v>1598.9</v>
       </c>
     </row>
     <row r="13">
@@ -10491,97 +10503,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -11090,97 +11102,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -11689,97 +11701,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -12410,97 +12422,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -12763,31 +12775,31 @@
         <v>1397</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1898.6</v>
+        <v>1911</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6704</v>
+        <v>-1.5912</v>
       </c>
       <c r="G6" t="n">
-        <v>117.06</v>
+        <v>117.14</v>
       </c>
       <c r="H6" t="n">
-        <v>101.96</v>
+        <v>101.72</v>
       </c>
       <c r="I6" t="n">
-        <v>15.09</v>
+        <v>15.42</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3583</v>
+        <v>0.3527</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1671</v>
+        <v>0.1643</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -12808,7 +12820,7 @@
         <v>21</v>
       </c>
       <c r="S6" t="n">
-        <v>1706.1</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="7">
@@ -12824,31 +12836,31 @@
         <v>1401</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1843.5</v>
+        <v>1824</v>
       </c>
       <c r="F7" t="n">
-        <v>4.536</v>
+        <v>4.3608</v>
       </c>
       <c r="G7" t="n">
-        <v>117.79</v>
+        <v>117.14</v>
       </c>
       <c r="H7" t="n">
-        <v>106.34</v>
+        <v>107.43</v>
       </c>
       <c r="I7" t="n">
-        <v>11.45</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3067</v>
+        <v>0.3098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1399</v>
+        <v>0.1389</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6</v>
+        <v>-5.4</v>
       </c>
       <c r="M7" t="n">
         <v>34</v>
@@ -12869,7 +12881,7 @@
         <v>43</v>
       </c>
       <c r="S7" t="n">
-        <v>1651.1</v>
+        <v>1653.7</v>
       </c>
     </row>
     <row r="8">
@@ -12885,31 +12897,31 @@
         <v>1208</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1816.9</v>
+        <v>1798.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2065</v>
+        <v>0.2861</v>
       </c>
       <c r="G8" t="n">
-        <v>121.14</v>
+        <v>119.92</v>
       </c>
       <c r="H8" t="n">
-        <v>107.06</v>
+        <v>106.59</v>
       </c>
       <c r="I8" t="n">
-        <v>14.09</v>
+        <v>13.33</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3227</v>
+        <v>0.3181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1388</v>
+        <v>0.141</v>
       </c>
       <c r="L8" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="M8" t="n">
         <v>31</v>
@@ -12930,7 +12942,7 @@
         <v>31</v>
       </c>
       <c r="S8" t="n">
-        <v>1643</v>
+        <v>1643.1</v>
       </c>
     </row>
     <row r="9">
@@ -12946,31 +12958,31 @@
         <v>1281</v>
       </c>
       <c r="D9" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1757.5</v>
+        <v>1747.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.923</v>
+        <v>-1.7576</v>
       </c>
       <c r="G9" t="n">
-        <v>115.19</v>
+        <v>114.92</v>
       </c>
       <c r="H9" t="n">
-        <v>109.25</v>
+        <v>109.48</v>
       </c>
       <c r="I9" t="n">
-        <v>5.95</v>
+        <v>5.45</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3014</v>
+        <v>0.2996</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1701</v>
+        <v>0.1685</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
         <v>50</v>
@@ -12991,7 +13003,7 @@
         <v>60</v>
       </c>
       <c r="S9" t="n">
-        <v>1651.9</v>
+        <v>1658.3</v>
       </c>
     </row>
     <row r="10">
@@ -13007,31 +13019,31 @@
         <v>1246</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" t="n">
-        <v>1887.4</v>
+        <v>1897</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1867</v>
+        <v>4.9403</v>
       </c>
       <c r="G10" t="n">
-        <v>117.12</v>
+        <v>116.84</v>
       </c>
       <c r="H10" t="n">
-        <v>106.56</v>
+        <v>106.32</v>
       </c>
       <c r="I10" t="n">
-        <v>10.57</v>
+        <v>10.52</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3122</v>
+        <v>0.312</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1426</v>
+        <v>0.1463</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>27</v>
@@ -13052,7 +13064,7 @@
         <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1721.6</v>
+        <v>1723.9</v>
       </c>
     </row>
     <row r="11">
@@ -13129,31 +13141,31 @@
         <v>1328</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E12" t="n">
-        <v>1709.5</v>
+        <v>1729</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1526</v>
+        <v>-1.822</v>
       </c>
       <c r="G12" t="n">
-        <v>120.33</v>
+        <v>120.4</v>
       </c>
       <c r="H12" t="n">
-        <v>112.01</v>
+        <v>111.31</v>
       </c>
       <c r="I12" t="n">
-        <v>8.32</v>
+        <v>9.09</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3072</v>
+        <v>0.3094</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1408</v>
+        <v>0.1414</v>
       </c>
       <c r="L12" t="n">
-        <v>11.8</v>
+        <v>13.4</v>
       </c>
       <c r="M12" t="n">
         <v>46</v>
@@ -13174,7 +13186,7 @@
         <v>54</v>
       </c>
       <c r="S12" t="n">
-        <v>1657.6</v>
+        <v>1666.2</v>
       </c>
     </row>
     <row r="13">
@@ -13190,31 +13202,31 @@
         <v>1120</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E13" t="n">
-        <v>1837.5</v>
+        <v>1825.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.6154</v>
+        <v>-7.4529</v>
       </c>
       <c r="G13" t="n">
-        <v>118.87</v>
+        <v>118.02</v>
       </c>
       <c r="H13" t="n">
-        <v>113.5</v>
+        <v>113.69</v>
       </c>
       <c r="I13" t="n">
-        <v>5.37</v>
+        <v>4.33</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3462</v>
+        <v>0.3492</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1435</v>
+        <v>0.1457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M13" t="n">
         <v>39</v>
@@ -13235,7 +13247,7 @@
         <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>1750.3</v>
+        <v>1757.6</v>
       </c>
     </row>
     <row r="14">
@@ -13373,31 +13385,31 @@
         <v>1279</v>
       </c>
       <c r="D16" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" t="n">
-        <v>1640.5</v>
+        <v>1659.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.1568</v>
+        <v>-7.7529</v>
       </c>
       <c r="G16" t="n">
-        <v>108.94</v>
+        <v>108.81</v>
       </c>
       <c r="H16" t="n">
-        <v>109.08</v>
+        <v>108.87</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.14</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2802</v>
+        <v>0.2848</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1362</v>
+        <v>0.1363</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
         <v>81</v>
@@ -13418,7 +13430,7 @@
         <v>92</v>
       </c>
       <c r="S16" t="n">
-        <v>1692.8</v>
+        <v>1697.1</v>
       </c>
     </row>
     <row r="17">
@@ -13497,97 +13509,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -14218,97 +14230,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -14817,97 +14829,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -15477,97 +15489,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -16442,97 +16454,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -16673,31 +16685,31 @@
         <v>1380</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1374.1</v>
+        <v>1375.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5631</v>
+        <v>-2.3939</v>
       </c>
       <c r="G4" t="n">
-        <v>105.51</v>
+        <v>106.4</v>
       </c>
       <c r="H4" t="n">
-        <v>111.44</v>
+        <v>111.97</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.93</v>
+        <v>-5.57</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3235</v>
+        <v>0.322</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1584</v>
+        <v>0.159</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>-0.2</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -16718,7 +16730,7 @@
         <v>277</v>
       </c>
       <c r="S4" t="n">
-        <v>1401.7</v>
+        <v>1396.5</v>
       </c>
     </row>
     <row r="5">
@@ -16734,31 +16746,31 @@
         <v>1411</v>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1289.8</v>
+        <v>1287.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4248</v>
+        <v>-1.2868</v>
       </c>
       <c r="G5" t="n">
-        <v>103.64</v>
+        <v>103.59</v>
       </c>
       <c r="H5" t="n">
-        <v>111.36</v>
+        <v>111.54</v>
       </c>
       <c r="I5" t="n">
-        <v>-7.72</v>
+        <v>-7.96</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2722</v>
+        <v>0.2701</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1743</v>
+        <v>0.1747</v>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>308</v>
@@ -16779,7 +16791,7 @@
         <v>320</v>
       </c>
       <c r="S5" t="n">
-        <v>1389.8</v>
+        <v>1386.6</v>
       </c>
     </row>
     <row r="6">
@@ -16795,31 +16807,31 @@
         <v>1105</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1288.5</v>
+        <v>1291.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7742</v>
+        <v>0.731</v>
       </c>
       <c r="G6" t="n">
-        <v>106.26</v>
+        <v>106.44</v>
       </c>
       <c r="H6" t="n">
-        <v>109.69</v>
+        <v>109.11</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.43</v>
+        <v>-2.67</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2571</v>
+        <v>0.2602</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1595</v>
+        <v>0.161</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
         <v>301</v>
@@ -16840,7 +16852,7 @@
         <v>308</v>
       </c>
       <c r="S6" t="n">
-        <v>1362.1</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="7">
@@ -16856,31 +16868,31 @@
         <v>1115</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1256.8</v>
+        <v>1255</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5341</v>
+        <v>1.4804</v>
       </c>
       <c r="G7" t="n">
-        <v>103.5</v>
+        <v>104.37</v>
       </c>
       <c r="H7" t="n">
-        <v>113.07</v>
+        <v>114.46</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.57</v>
+        <v>-10.09</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2838</v>
+        <v>0.2904</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1827</v>
+        <v>0.1808</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>316</v>
@@ -16901,7 +16913,7 @@
         <v>317</v>
       </c>
       <c r="S7" t="n">
-        <v>1388.9</v>
+        <v>1389.8</v>
       </c>
     </row>
     <row r="8">
@@ -17285,97 +17297,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -17638,31 +17650,31 @@
         <v>1150</v>
       </c>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1437.1</v>
+        <v>1443.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3871</v>
+        <v>1.3825</v>
       </c>
       <c r="G6" t="n">
-        <v>111.71</v>
+        <v>112.43</v>
       </c>
       <c r="H6" t="n">
-        <v>113.99</v>
+        <v>113.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.27</v>
+        <v>-0.77</v>
       </c>
       <c r="J6" t="n">
-        <v>0.298</v>
+        <v>0.2995</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1699</v>
+        <v>0.1697</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
       <c r="M6" t="n">
         <v>191</v>
@@ -17683,7 +17695,7 @@
         <v>183</v>
       </c>
       <c r="S6" t="n">
-        <v>1500.4</v>
+        <v>1498.1</v>
       </c>
     </row>
     <row r="7">
@@ -17699,31 +17711,31 @@
         <v>1317</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1532.3</v>
+        <v>1540.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.3186</v>
+        <v>-5.0315</v>
       </c>
       <c r="G7" t="n">
-        <v>104.14</v>
+        <v>104.23</v>
       </c>
       <c r="H7" t="n">
-        <v>102.05</v>
+        <v>102.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3367</v>
+        <v>0.3337</v>
       </c>
       <c r="K7" t="n">
-        <v>0.157</v>
+        <v>0.1533</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
         <v>140</v>
@@ -17744,7 +17756,7 @@
         <v>145</v>
       </c>
       <c r="S7" t="n">
-        <v>1505</v>
+        <v>1509.6</v>
       </c>
     </row>
     <row r="8">
@@ -17760,31 +17772,31 @@
         <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>1576.1</v>
+        <v>1567.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4104</v>
+        <v>-1.4453</v>
       </c>
       <c r="G8" t="n">
-        <v>108.51</v>
+        <v>108.2</v>
       </c>
       <c r="H8" t="n">
-        <v>105.87</v>
+        <v>105.94</v>
       </c>
       <c r="I8" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2922</v>
+        <v>0.2867</v>
       </c>
       <c r="K8" t="n">
-        <v>0.173</v>
+        <v>0.1725</v>
       </c>
       <c r="L8" t="n">
-        <v>-2</v>
+        <v>-2.6</v>
       </c>
       <c r="M8" t="n">
         <v>125</v>
@@ -17805,7 +17817,7 @@
         <v>123</v>
       </c>
       <c r="S8" t="n">
-        <v>1558.4</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="9">
@@ -17882,31 +17894,31 @@
         <v>1408</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" t="n">
-        <v>1504</v>
+        <v>1497.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8568</v>
+        <v>-1.8191</v>
       </c>
       <c r="G10" t="n">
-        <v>105.81</v>
+        <v>105.42</v>
       </c>
       <c r="H10" t="n">
-        <v>109.97</v>
+        <v>110.61</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.16</v>
+        <v>-5.19</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2381</v>
+        <v>0.2392</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1533</v>
+        <v>0.1502</v>
       </c>
       <c r="L10" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="M10" t="n">
         <v>210</v>
@@ -17927,7 +17939,7 @@
         <v>206</v>
       </c>
       <c r="S10" t="n">
-        <v>1532.8</v>
+        <v>1528.4</v>
       </c>
     </row>
     <row r="11">
@@ -18006,97 +18018,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -18237,31 +18249,31 @@
         <v>1469</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1383.1</v>
+        <v>1386.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.399</v>
+        <v>2.4009</v>
       </c>
       <c r="G4" t="n">
-        <v>108.04</v>
+        <v>108.33</v>
       </c>
       <c r="H4" t="n">
-        <v>111.09</v>
+        <v>110.83</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.05</v>
+        <v>-2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.27</v>
+        <v>0.2668</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1665</v>
+        <v>0.17</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.6</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
         <v>184</v>
@@ -18282,7 +18294,7 @@
         <v>175</v>
       </c>
       <c r="S4" t="n">
-        <v>1495.6</v>
+        <v>1489.8</v>
       </c>
     </row>
     <row r="5">
@@ -18298,31 +18310,31 @@
         <v>1426</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1458.1</v>
+        <v>1459.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0693</v>
+        <v>0.9557</v>
       </c>
       <c r="G5" t="n">
-        <v>100.7</v>
+        <v>100.63</v>
       </c>
       <c r="H5" t="n">
-        <v>100.67</v>
+        <v>100.34</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03</v>
+        <v>0.29</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3095</v>
+        <v>0.3139</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2079</v>
+        <v>0.2045</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="M5" t="n">
         <v>156</v>
@@ -18343,7 +18355,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="n">
-        <v>1461.3</v>
+        <v>1455.6</v>
       </c>
     </row>
     <row r="6">
@@ -18359,31 +18371,31 @@
         <v>1381</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1323.1</v>
+        <v>1321.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1666</v>
+        <v>-0.1279</v>
       </c>
       <c r="G6" t="n">
-        <v>102.08</v>
+        <v>101.36</v>
       </c>
       <c r="H6" t="n">
-        <v>114.13</v>
+        <v>113.27</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.05</v>
+        <v>-11.91</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2768</v>
+        <v>0.2767</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1972</v>
+        <v>0.198</v>
       </c>
       <c r="L6" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="M6" t="n">
         <v>252</v>
@@ -18404,7 +18416,7 @@
         <v>271</v>
       </c>
       <c r="S6" t="n">
-        <v>1496.9</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="7">
@@ -18420,31 +18432,31 @@
         <v>1101</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1408.3</v>
+        <v>1405.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1959</v>
+        <v>-0.2938</v>
       </c>
       <c r="G7" t="n">
-        <v>98.2</v>
+        <v>98.31</v>
       </c>
       <c r="H7" t="n">
-        <v>106.3</v>
+        <v>106.57</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.1</v>
+        <v>-8.26</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3251</v>
+        <v>0.3276</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1992</v>
+        <v>0.1985</v>
       </c>
       <c r="L7" t="n">
-        <v>-10.2</v>
+        <v>-10.6</v>
       </c>
       <c r="M7" t="n">
         <v>246</v>
@@ -18465,7 +18477,7 @@
         <v>248</v>
       </c>
       <c r="S7" t="n">
-        <v>1493.1</v>
+        <v>1489.4</v>
       </c>
     </row>
     <row r="8">
@@ -18544,97 +18556,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -19387,97 +19399,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -19986,97 +19998,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -20829,97 +20841,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -20938,31 +20950,31 @@
         <v>1112</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>2253.6</v>
+        <v>2256</v>
       </c>
       <c r="F2" t="n">
-        <v>7.7769</v>
+        <v>7.4143</v>
       </c>
       <c r="G2" t="n">
-        <v>121.09</v>
+        <v>121.01</v>
       </c>
       <c r="H2" t="n">
-        <v>96.09999999999999</v>
+        <v>95.61</v>
       </c>
       <c r="I2" t="n">
-        <v>24.99</v>
+        <v>25.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0.291</v>
+        <v>0.2928</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1505</v>
+        <v>0.1495</v>
       </c>
       <c r="L2" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -20983,7 +20995,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1742.6</v>
+        <v>1747.3</v>
       </c>
     </row>
     <row r="3">
@@ -20999,31 +21011,31 @@
         <v>1222</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E3" t="n">
-        <v>2102.9</v>
+        <v>2111.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6401</v>
+        <v>1.4261</v>
       </c>
       <c r="G3" t="n">
-        <v>117.95</v>
+        <v>117.41</v>
       </c>
       <c r="H3" t="n">
-        <v>95.43000000000001</v>
+        <v>95.28</v>
       </c>
       <c r="I3" t="n">
-        <v>22.51</v>
+        <v>22.14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3379</v>
+        <v>0.3403</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1199</v>
+        <v>0.1244</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>10.8</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -21044,7 +21056,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1706.6</v>
+        <v>1716.1</v>
       </c>
     </row>
     <row r="4">
@@ -21060,31 +21072,31 @@
         <v>1242</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1973.7</v>
+        <v>1983.4</v>
       </c>
       <c r="F4" t="n">
-        <v>11.337</v>
+        <v>10.797</v>
       </c>
       <c r="G4" t="n">
-        <v>111.61</v>
+        <v>111.09</v>
       </c>
       <c r="H4" t="n">
-        <v>100.9</v>
+        <v>100.73</v>
       </c>
       <c r="I4" t="n">
-        <v>10.71</v>
+        <v>10.36</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2487</v>
+        <v>0.2493</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1523</v>
+        <v>0.1516</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.4</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
         <v>19</v>
@@ -21105,7 +21117,7 @@
         <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>1772.3</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="5">
@@ -21121,31 +21133,31 @@
         <v>1403</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>2025.5</v>
+        <v>2010.7</v>
       </c>
       <c r="F5" t="n">
-        <v>10.1327</v>
+        <v>9.579599999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>118.86</v>
+        <v>117.2</v>
       </c>
       <c r="H5" t="n">
-        <v>106.69</v>
+        <v>106.7</v>
       </c>
       <c r="I5" t="n">
-        <v>12.16</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2944</v>
+        <v>0.2893</v>
       </c>
       <c r="K5" t="n">
         <v>0.155</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="M5" t="n">
         <v>17</v>
@@ -21166,7 +21178,7 @@
         <v>15</v>
       </c>
       <c r="S5" t="n">
-        <v>1762.7</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="6">
@@ -21182,31 +21194,31 @@
         <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>2031.1</v>
+        <v>2045.9</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7523</v>
+        <v>2.4203</v>
       </c>
       <c r="G6" t="n">
-        <v>118.89</v>
+        <v>118.77</v>
       </c>
       <c r="H6" t="n">
-        <v>94.63</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>24.26</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3199</v>
+        <v>0.3164</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1454</v>
+        <v>0.1462</v>
       </c>
       <c r="L6" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
@@ -21227,7 +21239,7 @@
         <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1687.1</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="7">
@@ -21243,31 +21255,31 @@
         <v>1395</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1845.8</v>
+        <v>1836.1</v>
       </c>
       <c r="F7" t="n">
-        <v>6.897</v>
+        <v>6.9164</v>
       </c>
       <c r="G7" t="n">
-        <v>111.93</v>
+        <v>111.16</v>
       </c>
       <c r="H7" t="n">
-        <v>102.48</v>
+        <v>102.34</v>
       </c>
       <c r="I7" t="n">
-        <v>9.449999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3255</v>
+        <v>0.3231</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1494</v>
+        <v>0.1514</v>
       </c>
       <c r="L7" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="M7" t="n">
         <v>44</v>
@@ -21288,7 +21300,7 @@
         <v>40</v>
       </c>
       <c r="S7" t="n">
-        <v>1680.3</v>
+        <v>1691.3</v>
       </c>
     </row>
     <row r="8">
@@ -21365,31 +21377,31 @@
         <v>1416</v>
       </c>
       <c r="D9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E9" t="n">
-        <v>1831.1</v>
+        <v>1828.6</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3402</v>
+        <v>5.8051</v>
       </c>
       <c r="G9" t="n">
-        <v>113.8</v>
+        <v>113</v>
       </c>
       <c r="H9" t="n">
-        <v>109.32</v>
+        <v>110.03</v>
       </c>
       <c r="I9" t="n">
-        <v>4.47</v>
+        <v>2.97</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3133</v>
+        <v>0.3147</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1536</v>
+        <v>0.1543</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>53</v>
@@ -21410,7 +21422,7 @@
         <v>51</v>
       </c>
       <c r="S9" t="n">
-        <v>1689.6</v>
+        <v>1712.7</v>
       </c>
     </row>
     <row r="10">
@@ -21487,31 +21499,31 @@
         <v>1140</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" t="n">
-        <v>1934.4</v>
+        <v>1926.2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.879</v>
+        <v>0.632</v>
       </c>
       <c r="G11" t="n">
-        <v>118.42</v>
+        <v>117.67</v>
       </c>
       <c r="H11" t="n">
-        <v>105.83</v>
+        <v>106.1</v>
       </c>
       <c r="I11" t="n">
-        <v>12.58</v>
+        <v>11.57</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3042</v>
+        <v>0.3038</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1509</v>
+        <v>0.1534</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
@@ -21532,7 +21544,7 @@
         <v>24</v>
       </c>
       <c r="S11" t="n">
-        <v>1718.9</v>
+        <v>1733.2</v>
       </c>
     </row>
     <row r="12">
@@ -21916,97 +21928,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -22025,31 +22037,31 @@
         <v>1385</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>1961.4</v>
+        <v>1964.1</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5897</v>
+        <v>5.6344</v>
       </c>
       <c r="G2" t="n">
-        <v>113.79</v>
+        <v>113.75</v>
       </c>
       <c r="H2" t="n">
-        <v>98.7</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>15.09</v>
+        <v>15.21</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3238</v>
+        <v>0.3255</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1418</v>
+        <v>0.1408</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
@@ -22070,7 +22082,7 @@
         <v>22</v>
       </c>
       <c r="S2" t="n">
-        <v>1680.5</v>
+        <v>1676.3</v>
       </c>
     </row>
     <row r="3">
@@ -22086,31 +22098,31 @@
         <v>1163</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E3" t="n">
-        <v>2064.2</v>
+        <v>2066.1</v>
       </c>
       <c r="F3" t="n">
-        <v>8.950200000000001</v>
+        <v>8.2806</v>
       </c>
       <c r="G3" t="n">
-        <v>116.34</v>
+        <v>117.74</v>
       </c>
       <c r="H3" t="n">
-        <v>97.40000000000001</v>
+        <v>97.67</v>
       </c>
       <c r="I3" t="n">
-        <v>18.93</v>
+        <v>20.07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2937</v>
+        <v>0.2928</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1558</v>
+        <v>0.1549</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -22131,7 +22143,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>1660.9</v>
+        <v>1659.9</v>
       </c>
     </row>
     <row r="4">
@@ -22147,31 +22159,31 @@
         <v>1437</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E4" t="n">
-        <v>1825.7</v>
+        <v>1806.3</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1267</v>
+        <v>5.8793</v>
       </c>
       <c r="G4" t="n">
-        <v>115.45</v>
+        <v>114.59</v>
       </c>
       <c r="H4" t="n">
-        <v>104.42</v>
+        <v>104.94</v>
       </c>
       <c r="I4" t="n">
-        <v>11.03</v>
+        <v>9.66</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3111</v>
+        <v>0.313</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1421</v>
+        <v>0.1447</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
@@ -22192,7 +22204,7 @@
         <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>1644.1</v>
+        <v>1641.5</v>
       </c>
     </row>
     <row r="5">
@@ -22208,31 +22220,31 @@
         <v>1371</v>
       </c>
       <c r="D5" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>1662</v>
+        <v>1673.5</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9773</v>
+        <v>4.6016</v>
       </c>
       <c r="G5" t="n">
         <v>105.77</v>
       </c>
       <c r="H5" t="n">
-        <v>98.03</v>
+        <v>97.47</v>
       </c>
       <c r="I5" t="n">
-        <v>7.74</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3233</v>
+        <v>0.318</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1586</v>
+        <v>0.1565</v>
       </c>
       <c r="L5" t="n">
-        <v>-2</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
         <v>52</v>
@@ -22253,7 +22265,7 @@
         <v>56</v>
       </c>
       <c r="S5" t="n">
-        <v>1637.8</v>
+        <v>1635.8</v>
       </c>
     </row>
     <row r="6">
@@ -22269,31 +22281,31 @@
         <v>1166</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>1675</v>
+        <v>1663.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3235</v>
+        <v>-2.2846</v>
       </c>
       <c r="G6" t="n">
-        <v>110.12</v>
+        <v>109.3</v>
       </c>
       <c r="H6" t="n">
-        <v>109.57</v>
+        <v>109.72</v>
       </c>
       <c r="I6" t="n">
-        <v>0.55</v>
+        <v>-0.41</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2481</v>
+        <v>0.2485</v>
       </c>
       <c r="K6" t="n">
         <v>0.1544</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8</v>
+        <v>-5.4</v>
       </c>
       <c r="M6" t="n">
         <v>75</v>
@@ -22314,7 +22326,7 @@
         <v>81</v>
       </c>
       <c r="S6" t="n">
-        <v>1664.3</v>
+        <v>1664.6</v>
       </c>
     </row>
     <row r="7">
@@ -22513,31 +22525,31 @@
         <v>1344</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E10" t="n">
-        <v>1573.5</v>
+        <v>1570.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8058</v>
+        <v>1.7823</v>
       </c>
       <c r="G10" t="n">
-        <v>115.49</v>
+        <v>114.62</v>
       </c>
       <c r="H10" t="n">
-        <v>112.67</v>
+        <v>112.79</v>
       </c>
       <c r="I10" t="n">
-        <v>2.82</v>
+        <v>1.83</v>
       </c>
       <c r="J10" t="n">
-        <v>0.265</v>
+        <v>0.2594</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1618</v>
+        <v>0.1619</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="M10" t="n">
         <v>73</v>
@@ -22558,7 +22570,7 @@
         <v>84</v>
       </c>
       <c r="S10" t="n">
-        <v>1638.4</v>
+        <v>1652.1</v>
       </c>
     </row>
     <row r="11">
@@ -22574,31 +22586,31 @@
         <v>1462</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" t="n">
-        <v>1598.7</v>
+        <v>1596.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9105</v>
+        <v>-2.9096</v>
       </c>
       <c r="G11" t="n">
-        <v>109.08</v>
+        <v>108.98</v>
       </c>
       <c r="H11" t="n">
-        <v>111.34</v>
+        <v>112.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.25</v>
+        <v>-3.88</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2721</v>
+        <v>0.2791</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1352</v>
+        <v>0.1365</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.6</v>
+        <v>-7.6</v>
       </c>
       <c r="M11" t="n">
         <v>97</v>
@@ -22619,7 +22631,7 @@
         <v>97</v>
       </c>
       <c r="S11" t="n">
-        <v>1632.7</v>
+        <v>1651.8</v>
       </c>
     </row>
     <row r="12">
@@ -22635,31 +22647,31 @@
         <v>1207</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E12" t="n">
-        <v>1566.8</v>
+        <v>1586.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7434</v>
+        <v>-4.5368</v>
       </c>
       <c r="G12" t="n">
-        <v>109.45</v>
+        <v>109.93</v>
       </c>
       <c r="H12" t="n">
-        <v>108.26</v>
+        <v>108.05</v>
       </c>
       <c r="I12" t="n">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3023</v>
+        <v>0.3069</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1484</v>
+        <v>0.1463</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.6</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
         <v>87</v>
@@ -22680,7 +22692,7 @@
         <v>95</v>
       </c>
       <c r="S12" t="n">
-        <v>1638.3</v>
+        <v>1646</v>
       </c>
     </row>
   </sheetData>
@@ -22698,97 +22710,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -23419,97 +23431,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,97 +447,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -1424,97 +1412,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2633,97 +2621,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -3232,97 +3220,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4136,97 +4124,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4857,97 +4845,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5639,97 +5627,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5994,97 +5982,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6715,97 +6703,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7253,97 +7241,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7852,97 +7840,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8634,97 +8622,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -9660,97 +9648,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -10503,97 +10491,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -11102,97 +11090,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -11701,97 +11689,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -12422,97 +12410,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -13509,97 +13497,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -14230,97 +14218,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -14829,97 +14817,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -15489,97 +15477,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -16454,97 +16442,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -17297,97 +17285,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -18018,97 +18006,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -18556,97 +18544,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -19399,97 +19387,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -19998,97 +19986,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -20841,97 +20829,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -21928,97 +21916,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -22710,97 +22698,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -23431,97 +23419,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -556,31 +556,31 @@
         <v>1387</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>1807.8</v>
+        <v>1811.5</v>
       </c>
       <c r="F2" t="n">
-        <v>9.839</v>
+        <v>9.2125</v>
       </c>
       <c r="G2" t="n">
-        <v>120.36</v>
+        <v>120.63</v>
       </c>
       <c r="H2" t="n">
-        <v>98.52</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>21.84</v>
+        <v>22.12</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2436</v>
+        <v>0.2386</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1686</v>
+        <v>0.1675</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="M2" t="n">
         <v>40</v>
@@ -601,7 +601,7 @@
         <v>27</v>
       </c>
       <c r="S2" t="n">
-        <v>1512.1</v>
+        <v>1510.4</v>
       </c>
     </row>
     <row r="3">
@@ -617,31 +617,31 @@
         <v>1433</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1739.9</v>
+        <v>1743.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9764</v>
+        <v>3.091</v>
       </c>
       <c r="G3" t="n">
-        <v>118.46</v>
+        <v>118.25</v>
       </c>
       <c r="H3" t="n">
-        <v>103.76</v>
+        <v>103.78</v>
       </c>
       <c r="I3" t="n">
-        <v>14.7</v>
+        <v>14.46</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2979</v>
+        <v>0.2985</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1497</v>
+        <v>0.1511</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
@@ -662,7 +662,7 @@
         <v>44</v>
       </c>
       <c r="S3" t="n">
-        <v>1554.6</v>
+        <v>1550.6</v>
       </c>
     </row>
     <row r="4">
@@ -678,31 +678,31 @@
         <v>1386</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1612</v>
+        <v>1618.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9935</v>
+        <v>1.2818</v>
       </c>
       <c r="G4" t="n">
-        <v>105.94</v>
+        <v>106.15</v>
       </c>
       <c r="H4" t="n">
-        <v>102.75</v>
+        <v>102.39</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2842</v>
+        <v>0.2844</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1621</v>
+        <v>0.1631</v>
       </c>
       <c r="L4" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="M4" t="n">
         <v>121</v>
@@ -723,7 +723,7 @@
         <v>124</v>
       </c>
       <c r="S4" t="n">
-        <v>1506.8</v>
+        <v>1508.9</v>
       </c>
     </row>
     <row r="5">
@@ -739,31 +739,31 @@
         <v>1173</v>
       </c>
       <c r="D5" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1663.4</v>
+        <v>1669.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5466</v>
+        <v>-2.3756</v>
       </c>
       <c r="G5" t="n">
-        <v>109.99</v>
+        <v>109.86</v>
       </c>
       <c r="H5" t="n">
-        <v>102.29</v>
+        <v>101.93</v>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>7.93</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2531</v>
+        <v>0.2559</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1686</v>
+        <v>0.1703</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
         <v>79</v>
@@ -784,7 +784,7 @@
         <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>1562.3</v>
+        <v>1559.7</v>
       </c>
     </row>
     <row r="6">
@@ -861,31 +861,31 @@
         <v>1172</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="n">
-        <v>1533.9</v>
+        <v>1527.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5567</v>
+        <v>-2.3908</v>
       </c>
       <c r="G7" t="n">
-        <v>108.41</v>
+        <v>107.99</v>
       </c>
       <c r="H7" t="n">
-        <v>104.66</v>
+        <v>105.22</v>
       </c>
       <c r="I7" t="n">
-        <v>3.74</v>
+        <v>2.77</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2841</v>
+        <v>0.2874</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1548</v>
+        <v>0.156</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
         <v>107</v>
@@ -906,7 +906,7 @@
         <v>106</v>
       </c>
       <c r="S7" t="n">
-        <v>1535.2</v>
+        <v>1539.4</v>
       </c>
     </row>
     <row r="8">
@@ -922,31 +922,31 @@
         <v>1182</v>
       </c>
       <c r="D8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" t="n">
-        <v>1489.8</v>
+        <v>1486.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0712</v>
+        <v>-1.8538</v>
       </c>
       <c r="G8" t="n">
-        <v>109.05</v>
+        <v>108.66</v>
       </c>
       <c r="H8" t="n">
-        <v>107.32</v>
+        <v>107.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2938</v>
+        <v>0.293</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1676</v>
+        <v>0.1717</v>
       </c>
       <c r="L8" t="n">
-        <v>-6</v>
+        <v>-4.8</v>
       </c>
       <c r="M8" t="n">
         <v>133</v>
@@ -967,7 +967,7 @@
         <v>140</v>
       </c>
       <c r="S8" t="n">
-        <v>1539.9</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="9">
@@ -1044,31 +1044,31 @@
         <v>1203</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10" t="n">
-        <v>1529.5</v>
+        <v>1525.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9222</v>
+        <v>-3.7537</v>
       </c>
       <c r="G10" t="n">
         <v>114.99</v>
       </c>
       <c r="H10" t="n">
-        <v>104.97</v>
+        <v>105.77</v>
       </c>
       <c r="I10" t="n">
-        <v>10.02</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3187</v>
+        <v>0.3243</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1742</v>
+        <v>0.1728</v>
       </c>
       <c r="L10" t="n">
-        <v>6.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M10" t="n">
         <v>83</v>
@@ -1089,7 +1089,7 @@
         <v>90</v>
       </c>
       <c r="S10" t="n">
-        <v>1530.4</v>
+        <v>1543.4</v>
       </c>
     </row>
     <row r="11">
@@ -1288,31 +1288,31 @@
         <v>1382</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" t="n">
-        <v>1551.8</v>
+        <v>1545.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.3871</v>
+        <v>-8.1075</v>
       </c>
       <c r="G14" t="n">
-        <v>111.9</v>
+        <v>111.41</v>
       </c>
       <c r="H14" t="n">
-        <v>110.28</v>
+        <v>110.25</v>
       </c>
       <c r="I14" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3237</v>
+        <v>0.3195</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1631</v>
+        <v>0.164</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="M14" t="n">
         <v>160</v>
@@ -1333,7 +1333,7 @@
         <v>158</v>
       </c>
       <c r="S14" t="n">
-        <v>1535.3</v>
+        <v>1538.4</v>
       </c>
     </row>
     <row r="15">
@@ -1521,31 +1521,31 @@
         <v>1276</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>2189.2</v>
+        <v>2192.4</v>
       </c>
       <c r="F2" t="n">
-        <v>7.2681</v>
+        <v>6.99</v>
       </c>
       <c r="G2" t="n">
-        <v>121.97</v>
+        <v>121.3</v>
       </c>
       <c r="H2" t="n">
-        <v>95.94</v>
+        <v>95.95</v>
       </c>
       <c r="I2" t="n">
-        <v>26.03</v>
+        <v>25.34</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2632</v>
+        <v>0.2601</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1657</v>
+        <v>0.1647</v>
       </c>
       <c r="L2" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1769.7</v>
+        <v>1768.8</v>
       </c>
     </row>
     <row r="3">
@@ -1582,31 +1582,31 @@
         <v>1304</v>
       </c>
       <c r="D3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1999.6</v>
+        <v>1982.9</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6735</v>
+        <v>9.932399999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>115.4</v>
+        <v>114.61</v>
       </c>
       <c r="H3" t="n">
-        <v>97.95</v>
+        <v>98.94</v>
       </c>
       <c r="I3" t="n">
-        <v>17.45</v>
+        <v>15.67</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2379</v>
+        <v>0.2433</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1402</v>
+        <v>0.1403</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -1627,7 +1627,7 @@
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>1665.7</v>
+        <v>1675.8</v>
       </c>
     </row>
     <row r="4">
@@ -1643,31 +1643,31 @@
         <v>1277</v>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>2049.8</v>
+        <v>2027.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2376</v>
+        <v>0.218</v>
       </c>
       <c r="G4" t="n">
-        <v>117.05</v>
+        <v>117.66</v>
       </c>
       <c r="H4" t="n">
-        <v>100.92</v>
+        <v>102.12</v>
       </c>
       <c r="I4" t="n">
-        <v>16.13</v>
+        <v>15.54</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2993</v>
+        <v>0.2963</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1615</v>
+        <v>0.1607</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
@@ -1688,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>1729.6</v>
+        <v>1730.1</v>
       </c>
     </row>
     <row r="5">
@@ -1704,31 +1704,31 @@
         <v>1228</v>
       </c>
       <c r="D5" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>2003.3</v>
+        <v>1982.7</v>
       </c>
       <c r="F5" t="n">
-        <v>8.2525</v>
+        <v>7.8712</v>
       </c>
       <c r="G5" t="n">
-        <v>125.48</v>
+        <v>125.11</v>
       </c>
       <c r="H5" t="n">
-        <v>103.07</v>
+        <v>103.66</v>
       </c>
       <c r="I5" t="n">
-        <v>22.41</v>
+        <v>21.45</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3238</v>
+        <v>0.3222</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1295</v>
+        <v>0.1281</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -1749,7 +1749,7 @@
         <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>1709.5</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="6">
@@ -1765,31 +1765,31 @@
         <v>1458</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1866.2</v>
+        <v>1886.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8886</v>
+        <v>2.1287</v>
       </c>
       <c r="G6" t="n">
-        <v>119.65</v>
+        <v>119.67</v>
       </c>
       <c r="H6" t="n">
-        <v>108.66</v>
+        <v>108.89</v>
       </c>
       <c r="I6" t="n">
-        <v>10.99</v>
+        <v>10.78</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2811</v>
+        <v>0.2787</v>
       </c>
       <c r="K6" t="n">
-        <v>0.123</v>
+        <v>0.1222</v>
       </c>
       <c r="L6" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
         <v>23</v>
@@ -1810,7 +1810,7 @@
         <v>26</v>
       </c>
       <c r="S6" t="n">
-        <v>1697</v>
+        <v>1709.1</v>
       </c>
     </row>
     <row r="7">
@@ -1826,31 +1826,31 @@
         <v>1417</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="n">
-        <v>1863</v>
+        <v>1885.4</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4395</v>
+        <v>2.6042</v>
       </c>
       <c r="G7" t="n">
-        <v>116.91</v>
+        <v>117.52</v>
       </c>
       <c r="H7" t="n">
-        <v>106.2</v>
+        <v>107.06</v>
       </c>
       <c r="I7" t="n">
-        <v>10.71</v>
+        <v>10.46</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2986</v>
+        <v>0.3052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1298</v>
+        <v>0.1315</v>
       </c>
       <c r="L7" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="M7" t="n">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>34</v>
       </c>
       <c r="S7" t="n">
-        <v>1683.8</v>
+        <v>1698.9</v>
       </c>
     </row>
     <row r="8">
@@ -1887,31 +1887,31 @@
         <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" t="n">
-        <v>1959</v>
+        <v>1975.7</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.051</v>
+        <v>-0.3998</v>
       </c>
       <c r="G8" t="n">
-        <v>124.95</v>
+        <v>124.77</v>
       </c>
       <c r="H8" t="n">
-        <v>107.45</v>
+        <v>106.95</v>
       </c>
       <c r="I8" t="n">
-        <v>17.5</v>
+        <v>17.82</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3095</v>
+        <v>0.3094</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1344</v>
+        <v>0.1359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
@@ -1932,7 +1932,7 @@
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>1740.1</v>
+        <v>1751.8</v>
       </c>
     </row>
     <row r="9">
@@ -1948,31 +1948,31 @@
         <v>1326</v>
       </c>
       <c r="D9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>1817</v>
+        <v>1813.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7194</v>
+        <v>1.9487</v>
       </c>
       <c r="G9" t="n">
-        <v>118.68</v>
+        <v>118</v>
       </c>
       <c r="H9" t="n">
-        <v>108.16</v>
+        <v>108.07</v>
       </c>
       <c r="I9" t="n">
-        <v>10.52</v>
+        <v>9.93</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2526</v>
+        <v>0.255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1502</v>
+        <v>0.1503</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="M9" t="n">
         <v>26</v>
@@ -1993,7 +1993,7 @@
         <v>30</v>
       </c>
       <c r="S9" t="n">
-        <v>1705.5</v>
+        <v>1722.9</v>
       </c>
     </row>
     <row r="10">
@@ -2730,31 +2730,31 @@
         <v>1414</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>1614.5</v>
+        <v>1620.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2068</v>
+        <v>2.2032</v>
       </c>
       <c r="G2" t="n">
-        <v>103.59</v>
+        <v>104.72</v>
       </c>
       <c r="H2" t="n">
-        <v>96.37</v>
+        <v>96.98</v>
       </c>
       <c r="I2" t="n">
-        <v>7.22</v>
+        <v>7.74</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2658</v>
+        <v>0.2714</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1712</v>
+        <v>0.1714</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>10.4</v>
       </c>
       <c r="M2" t="n">
         <v>106</v>
@@ -2775,7 +2775,7 @@
         <v>118</v>
       </c>
       <c r="S2" t="n">
-        <v>1471.2</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="3">
@@ -2791,31 +2791,31 @@
         <v>1218</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1535.7</v>
+        <v>1538.8</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2322</v>
+        <v>3.0942</v>
       </c>
       <c r="G3" t="n">
-        <v>108.42</v>
+        <v>108.45</v>
       </c>
       <c r="H3" t="n">
-        <v>97.5</v>
+        <v>96.83</v>
       </c>
       <c r="I3" t="n">
-        <v>10.92</v>
+        <v>11.62</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2524</v>
+        <v>0.2555</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1813</v>
+        <v>0.1843</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
         <v>115</v>
@@ -2836,7 +2836,7 @@
         <v>112</v>
       </c>
       <c r="S3" t="n">
-        <v>1444.6</v>
+        <v>1444.2</v>
       </c>
     </row>
     <row r="4">
@@ -2852,31 +2852,31 @@
         <v>1168</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1399</v>
+        <v>1395.9</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9262</v>
+        <v>2.9449</v>
       </c>
       <c r="G4" t="n">
-        <v>107.91</v>
+        <v>107.12</v>
       </c>
       <c r="H4" t="n">
-        <v>109.34</v>
+        <v>109.48</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.43</v>
+        <v>-2.35</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2569</v>
+        <v>0.2559</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1476</v>
+        <v>0.1466</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
         <v>169</v>
@@ -2897,7 +2897,7 @@
         <v>180</v>
       </c>
       <c r="S4" t="n">
-        <v>1479.9</v>
+        <v>1482.1</v>
       </c>
     </row>
     <row r="5">
@@ -2913,31 +2913,31 @@
         <v>1169</v>
       </c>
       <c r="D5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1516</v>
+        <v>1510.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7017</v>
+        <v>1.7028</v>
       </c>
       <c r="G5" t="n">
-        <v>105.24</v>
+        <v>105.45</v>
       </c>
       <c r="H5" t="n">
-        <v>105.09</v>
+        <v>106.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>-0.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.274</v>
+        <v>0.2789</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1702</v>
+        <v>0.1683</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.6</v>
+        <v>-5.4</v>
       </c>
       <c r="M5" t="n">
         <v>176</v>
@@ -2958,7 +2958,7 @@
         <v>190</v>
       </c>
       <c r="S5" t="n">
-        <v>1458.3</v>
+        <v>1463.1</v>
       </c>
     </row>
     <row r="6">
@@ -4294,31 +4294,31 @@
         <v>1358</v>
       </c>
       <c r="D3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1545</v>
+        <v>1537.5</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4295</v>
+        <v>4.2853</v>
       </c>
       <c r="G3" t="n">
-        <v>112.95</v>
+        <v>112.78</v>
       </c>
       <c r="H3" t="n">
-        <v>106.4</v>
+        <v>106.92</v>
       </c>
       <c r="I3" t="n">
-        <v>6.55</v>
+        <v>5.87</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3122</v>
+        <v>0.3127</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1587</v>
+        <v>0.162</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>-0.6</v>
       </c>
       <c r="M3" t="n">
         <v>109</v>
@@ -4339,7 +4339,7 @@
         <v>104</v>
       </c>
       <c r="S3" t="n">
-        <v>1499.6</v>
+        <v>1500.3</v>
       </c>
     </row>
     <row r="4">
@@ -4416,31 +4416,31 @@
         <v>1256</v>
       </c>
       <c r="D5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1511.7</v>
+        <v>1515.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5513</v>
+        <v>-1.3208</v>
       </c>
       <c r="G5" t="n">
-        <v>103.46</v>
+        <v>104.02</v>
       </c>
       <c r="H5" t="n">
-        <v>102.91</v>
+        <v>103.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="J5" t="n">
-        <v>0.329</v>
+        <v>0.3299</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1746</v>
+        <v>0.1728</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="M5" t="n">
         <v>208</v>
@@ -4461,7 +4461,7 @@
         <v>213</v>
       </c>
       <c r="S5" t="n">
-        <v>1466</v>
+        <v>1463.6</v>
       </c>
     </row>
     <row r="6">
@@ -4538,31 +4538,31 @@
         <v>1244</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="n">
-        <v>1507.3</v>
+        <v>1514.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3139</v>
+        <v>-0.2575</v>
       </c>
       <c r="G7" t="n">
         <v>111.26</v>
       </c>
       <c r="H7" t="n">
-        <v>108.94</v>
+        <v>108.75</v>
       </c>
       <c r="I7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3332</v>
+        <v>0.3392</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1652</v>
+        <v>0.1672</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
         <v>178</v>
@@ -4583,7 +4583,7 @@
         <v>170</v>
       </c>
       <c r="S7" t="n">
-        <v>1470.6</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="8">
@@ -4721,31 +4721,31 @@
         <v>1283</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E10" t="n">
-        <v>1411.5</v>
+        <v>1408</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1057</v>
+        <v>1.1121</v>
       </c>
       <c r="G10" t="n">
-        <v>108.33</v>
+        <v>108.66</v>
       </c>
       <c r="H10" t="n">
-        <v>109.65</v>
+        <v>110.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.32</v>
+        <v>-1.54</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3251</v>
+        <v>0.3282</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1614</v>
+        <v>0.1596</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>215</v>
@@ -4766,7 +4766,7 @@
         <v>214</v>
       </c>
       <c r="S10" t="n">
-        <v>1481.6</v>
+        <v>1481.4</v>
       </c>
     </row>
     <row r="11">
@@ -6812,31 +6812,31 @@
         <v>1224</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>1404.4</v>
+        <v>1406</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2279</v>
+        <v>3.0696</v>
       </c>
       <c r="G2" t="n">
-        <v>109.08</v>
+        <v>108.81</v>
       </c>
       <c r="H2" t="n">
-        <v>98.81</v>
+        <v>97.94</v>
       </c>
       <c r="I2" t="n">
-        <v>10.27</v>
+        <v>10.87</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3126</v>
+        <v>0.3142</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1855</v>
+        <v>0.1871</v>
       </c>
       <c r="L2" t="n">
-        <v>23.6</v>
+        <v>20.6</v>
       </c>
       <c r="M2" t="n">
         <v>202</v>
@@ -6857,7 +6857,7 @@
         <v>202</v>
       </c>
       <c r="S2" t="n">
-        <v>1380.6</v>
+        <v>1374.8</v>
       </c>
     </row>
     <row r="3">
@@ -6934,31 +6934,31 @@
         <v>1300</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1293</v>
+        <v>1291.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.46</v>
+        <v>-1.3164</v>
       </c>
       <c r="G4" t="n">
-        <v>101.79</v>
+        <v>101.75</v>
       </c>
       <c r="H4" t="n">
-        <v>115.96</v>
+        <v>115.02</v>
       </c>
       <c r="I4" t="n">
-        <v>-14.17</v>
+        <v>-13.27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3052</v>
+        <v>0.3122</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1785</v>
+        <v>0.1759</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.8</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>353</v>
@@ -6979,7 +6979,7 @@
         <v>347</v>
       </c>
       <c r="S4" t="n">
-        <v>1384</v>
+        <v>1379.6</v>
       </c>
     </row>
     <row r="5">
@@ -7056,31 +7056,31 @@
         <v>1354</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1257.4</v>
+        <v>1255.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0547</v>
+        <v>-2.8499</v>
       </c>
       <c r="G6" t="n">
-        <v>97.12</v>
+        <v>96.22</v>
       </c>
       <c r="H6" t="n">
-        <v>114.45</v>
+        <v>114.16</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.33</v>
+        <v>-17.93</v>
       </c>
       <c r="J6" t="n">
-        <v>0.345</v>
+        <v>0.3451</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2009</v>
+        <v>0.2043</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="M6" t="n">
         <v>356</v>
@@ -7101,7 +7101,7 @@
         <v>357</v>
       </c>
       <c r="S6" t="n">
-        <v>1393.4</v>
+        <v>1394.2</v>
       </c>
     </row>
     <row r="7">
@@ -7120,7 +7120,7 @@
         <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>1223</v>
+        <v>1226.7</v>
       </c>
       <c r="F7" t="n">
         <v>-0.5586</v>
@@ -7178,31 +7178,31 @@
         <v>1175</v>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E8" t="n">
-        <v>1258.6</v>
+        <v>1251.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1046</v>
+        <v>-2.9934</v>
       </c>
       <c r="G8" t="n">
-        <v>90.7</v>
+        <v>90.72</v>
       </c>
       <c r="H8" t="n">
-        <v>108.13</v>
+        <v>108.11</v>
       </c>
       <c r="I8" t="n">
-        <v>-17.43</v>
+        <v>-17.39</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3064</v>
+        <v>0.3078</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1821</v>
+        <v>0.1867</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.8</v>
+        <v>-3.2</v>
       </c>
       <c r="M8" t="n">
         <v>362</v>
@@ -7223,7 +7223,7 @@
         <v>362</v>
       </c>
       <c r="S8" t="n">
-        <v>1354.6</v>
+        <v>1352.4</v>
       </c>
     </row>
   </sheetData>
@@ -7411,31 +7411,31 @@
         <v>1103</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1696.5</v>
+        <v>1704.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1.818</v>
+        <v>1.8839</v>
       </c>
       <c r="G3" t="n">
-        <v>122.16</v>
+        <v>121.82</v>
       </c>
       <c r="H3" t="n">
-        <v>104.24</v>
+        <v>104.08</v>
       </c>
       <c r="I3" t="n">
-        <v>17.92</v>
+        <v>17.74</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2856</v>
+        <v>0.2847</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1521</v>
+        <v>0.1512</v>
       </c>
       <c r="L3" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
@@ -7456,7 +7456,7 @@
         <v>52</v>
       </c>
       <c r="S3" t="n">
-        <v>1474.6</v>
+        <v>1481.1</v>
       </c>
     </row>
     <row r="4">
@@ -7472,31 +7472,31 @@
         <v>1245</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1608.7</v>
+        <v>1600.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1871</v>
+        <v>0.115</v>
       </c>
       <c r="G4" t="n">
-        <v>112.75</v>
+        <v>112.17</v>
       </c>
       <c r="H4" t="n">
-        <v>109.04</v>
+        <v>109.18</v>
       </c>
       <c r="I4" t="n">
-        <v>3.71</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3174</v>
+        <v>0.3235</v>
       </c>
       <c r="K4" t="n">
-        <v>0.177</v>
+        <v>0.1763</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
         <v>154</v>
@@ -7517,7 +7517,7 @@
         <v>147</v>
       </c>
       <c r="S4" t="n">
-        <v>1469.5</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="5">
@@ -7533,28 +7533,28 @@
         <v>1405</v>
       </c>
       <c r="D5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1458.6</v>
+        <v>1464.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6373</v>
+        <v>-0.583</v>
       </c>
       <c r="G5" t="n">
-        <v>114.97</v>
+        <v>114.81</v>
       </c>
       <c r="H5" t="n">
-        <v>111.68</v>
+        <v>111.04</v>
       </c>
       <c r="I5" t="n">
-        <v>3.29</v>
+        <v>3.78</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2985</v>
+        <v>0.2898</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1405</v>
+        <v>0.1416</v>
       </c>
       <c r="L5" t="n">
         <v>8.199999999999999</v>
@@ -7578,7 +7578,7 @@
         <v>146</v>
       </c>
       <c r="S5" t="n">
-        <v>1494.4</v>
+        <v>1495.2</v>
       </c>
     </row>
     <row r="6">
@@ -7777,31 +7777,31 @@
         <v>1269</v>
       </c>
       <c r="D9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>1495.5</v>
+        <v>1489.7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8792</v>
+        <v>0.828</v>
       </c>
       <c r="G9" t="n">
-        <v>110.01</v>
+        <v>109.25</v>
       </c>
       <c r="H9" t="n">
-        <v>108.12</v>
+        <v>108.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1.89</v>
+        <v>1.21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2974</v>
+        <v>0.2995</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1712</v>
+        <v>0.1715</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6</v>
+        <v>-2.8</v>
       </c>
       <c r="M9" t="n">
         <v>201</v>
@@ -7822,7 +7822,7 @@
         <v>203</v>
       </c>
       <c r="S9" t="n">
-        <v>1464.6</v>
+        <v>1461.5</v>
       </c>
     </row>
   </sheetData>
@@ -8731,31 +8731,31 @@
         <v>1181</v>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>2185.1</v>
+        <v>2189.2</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7089</v>
+        <v>3.7126</v>
       </c>
       <c r="G2" t="n">
-        <v>123.04</v>
+        <v>122.89</v>
       </c>
       <c r="H2" t="n">
-        <v>94.12</v>
+        <v>94.03</v>
       </c>
       <c r="I2" t="n">
-        <v>28.93</v>
+        <v>28.87</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2948</v>
+        <v>0.2894</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1547</v>
+        <v>0.1548</v>
       </c>
       <c r="L2" t="n">
-        <v>23</v>
+        <v>16.6</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1695.7</v>
+        <v>1703.5</v>
       </c>
     </row>
     <row r="3">
@@ -8792,31 +8792,31 @@
         <v>1438</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1963.2</v>
+        <v>1971</v>
       </c>
       <c r="F3" t="n">
-        <v>13.0176</v>
+        <v>12.5889</v>
       </c>
       <c r="G3" t="n">
-        <v>118.86</v>
+        <v>119.48</v>
       </c>
       <c r="H3" t="n">
-        <v>100.31</v>
+        <v>100.21</v>
       </c>
       <c r="I3" t="n">
-        <v>18.55</v>
+        <v>19.27</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3146</v>
+        <v>0.3151</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1527</v>
+        <v>0.153</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
@@ -8837,7 +8837,7 @@
         <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>1642.5</v>
+        <v>1646.9</v>
       </c>
     </row>
     <row r="4">
@@ -8853,31 +8853,31 @@
         <v>1274</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1780</v>
+        <v>1772.3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.0727</v>
+        <v>11.776</v>
       </c>
       <c r="G4" t="n">
-        <v>117.75</v>
+        <v>117.07</v>
       </c>
       <c r="H4" t="n">
-        <v>101.58</v>
+        <v>102.95</v>
       </c>
       <c r="I4" t="n">
-        <v>16.16</v>
+        <v>14.11</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3083</v>
+        <v>0.3096</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1583</v>
+        <v>0.1569</v>
       </c>
       <c r="L4" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>29</v>
@@ -8898,7 +8898,7 @@
         <v>32</v>
       </c>
       <c r="S4" t="n">
-        <v>1624.7</v>
+        <v>1635.9</v>
       </c>
     </row>
     <row r="5">
@@ -8975,31 +8975,31 @@
         <v>1155</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1863.6</v>
+        <v>1859.5</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7155</v>
+        <v>2.557</v>
       </c>
       <c r="G6" t="n">
-        <v>113.29</v>
+        <v>112.59</v>
       </c>
       <c r="H6" t="n">
-        <v>101.28</v>
+        <v>101.68</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>10.91</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2541</v>
+        <v>0.2554</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1378</v>
+        <v>0.136</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>-0.6</v>
       </c>
       <c r="M6" t="n">
         <v>38</v>
@@ -9020,7 +9020,7 @@
         <v>36</v>
       </c>
       <c r="S6" t="n">
-        <v>1655.1</v>
+        <v>1672.9</v>
       </c>
     </row>
     <row r="7">
@@ -9757,31 +9757,31 @@
         <v>1429</v>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>1875.9</v>
+        <v>1885.6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1664</v>
+        <v>0.1404</v>
       </c>
       <c r="G2" t="n">
-        <v>120.08</v>
+        <v>119.83</v>
       </c>
       <c r="H2" t="n">
-        <v>104.01</v>
+        <v>103.76</v>
       </c>
       <c r="I2" t="n">
         <v>16.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.305</v>
+        <v>0.3026</v>
       </c>
       <c r="K2" t="n">
         <v>0.1501</v>
       </c>
       <c r="L2" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>35</v>
@@ -9802,7 +9802,7 @@
         <v>29</v>
       </c>
       <c r="S2" t="n">
-        <v>1599.4</v>
+        <v>1604.7</v>
       </c>
     </row>
     <row r="3">
@@ -9818,31 +9818,31 @@
         <v>1361</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1796.6</v>
+        <v>1812.2</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1383</v>
+        <v>4.8008</v>
       </c>
       <c r="G3" t="n">
-        <v>110.37</v>
+        <v>109.86</v>
       </c>
       <c r="H3" t="n">
-        <v>101.04</v>
+        <v>100.82</v>
       </c>
       <c r="I3" t="n">
-        <v>9.34</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2637</v>
+        <v>0.2638</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1654</v>
+        <v>0.1664</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>47</v>
@@ -9863,7 +9863,7 @@
         <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>1653.1</v>
+        <v>1659.4</v>
       </c>
     </row>
     <row r="4">
@@ -9879,31 +9879,31 @@
         <v>1307</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1812.6</v>
+        <v>1796.9</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0887</v>
+        <v>2.7628</v>
       </c>
       <c r="G4" t="n">
-        <v>115.92</v>
+        <v>114.94</v>
       </c>
       <c r="H4" t="n">
-        <v>103.11</v>
+        <v>102.87</v>
       </c>
       <c r="I4" t="n">
-        <v>12.81</v>
+        <v>12.07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2783</v>
+        <v>0.284</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1445</v>
+        <v>0.1454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
@@ -9924,7 +9924,7 @@
         <v>45</v>
       </c>
       <c r="S4" t="n">
-        <v>1586.9</v>
+        <v>1597.3</v>
       </c>
     </row>
     <row r="5">
@@ -10001,31 +10001,31 @@
         <v>1305</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1749.4</v>
+        <v>1739.6</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9785</v>
+        <v>5.6949</v>
       </c>
       <c r="G6" t="n">
-        <v>113.3</v>
+        <v>112.25</v>
       </c>
       <c r="H6" t="n">
-        <v>105.71</v>
+        <v>105.65</v>
       </c>
       <c r="I6" t="n">
-        <v>7.59</v>
+        <v>6.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.303</v>
+        <v>0.3012</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1436</v>
+        <v>0.1459</v>
       </c>
       <c r="L6" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="M6" t="n">
         <v>76</v>
@@ -10046,7 +10046,7 @@
         <v>73</v>
       </c>
       <c r="S6" t="n">
-        <v>1597.4</v>
+        <v>1607.1</v>
       </c>
     </row>
     <row r="7">
@@ -12519,31 +12519,31 @@
         <v>1196</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>2014.8</v>
+        <v>2024.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8716</v>
+        <v>3.1754</v>
       </c>
       <c r="G2" t="n">
-        <v>120.95</v>
+        <v>120.02</v>
       </c>
       <c r="H2" t="n">
-        <v>99.02</v>
+        <v>98.41</v>
       </c>
       <c r="I2" t="n">
-        <v>21.92</v>
+        <v>21.61</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3329</v>
+        <v>0.3339</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1552</v>
+        <v>0.1592</v>
       </c>
       <c r="L2" t="n">
-        <v>21.4</v>
+        <v>19.2</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -12564,7 +12564,7 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1709.6</v>
+        <v>1715.4</v>
       </c>
     </row>
     <row r="3">
@@ -12580,31 +12580,31 @@
         <v>1104</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1975.1</v>
+        <v>1949.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4869</v>
+        <v>-1.3255</v>
       </c>
       <c r="G3" t="n">
-        <v>122.11</v>
+        <v>121.37</v>
       </c>
       <c r="H3" t="n">
-        <v>110.78</v>
+        <v>110.6</v>
       </c>
       <c r="I3" t="n">
-        <v>11.33</v>
+        <v>10.77</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2853</v>
+        <v>0.2809</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1289</v>
+        <v>0.1288</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -12625,7 +12625,7 @@
         <v>17</v>
       </c>
       <c r="S3" t="n">
-        <v>1772.1</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="4">
@@ -12641,31 +12641,31 @@
         <v>1116</v>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1950</v>
+        <v>1956.5</v>
       </c>
       <c r="F4" t="n">
-        <v>5.5428</v>
+        <v>5.3805</v>
       </c>
       <c r="G4" t="n">
-        <v>122.85</v>
+        <v>122.83</v>
       </c>
       <c r="H4" t="n">
-        <v>108.88</v>
+        <v>109.16</v>
       </c>
       <c r="I4" t="n">
-        <v>13.96</v>
+        <v>13.66</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3009</v>
+        <v>0.3026</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1205</v>
+        <v>0.1196</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
         <v>18</v>
@@ -12686,7 +12686,7 @@
         <v>18</v>
       </c>
       <c r="S4" t="n">
-        <v>1728.7</v>
+        <v>1728.4</v>
       </c>
     </row>
     <row r="5">
@@ -12702,31 +12702,31 @@
         <v>1435</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1935.7</v>
+        <v>1949.6</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1989</v>
+        <v>1.887</v>
       </c>
       <c r="G5" t="n">
-        <v>121.8</v>
+        <v>121.84</v>
       </c>
       <c r="H5" t="n">
-        <v>105.67</v>
+        <v>105.79</v>
       </c>
       <c r="I5" t="n">
-        <v>16.12</v>
+        <v>16.05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2802</v>
+        <v>0.2851</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1278</v>
+        <v>0.1258</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
         <v>13</v>
@@ -12747,7 +12747,7 @@
         <v>16</v>
       </c>
       <c r="S5" t="n">
-        <v>1694.9</v>
+        <v>1701.5</v>
       </c>
     </row>
     <row r="6">
@@ -12763,31 +12763,31 @@
         <v>1397</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1911</v>
+        <v>1897.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5912</v>
+        <v>-1.4465</v>
       </c>
       <c r="G6" t="n">
-        <v>117.14</v>
+        <v>116.86</v>
       </c>
       <c r="H6" t="n">
-        <v>101.72</v>
+        <v>102.57</v>
       </c>
       <c r="I6" t="n">
-        <v>15.42</v>
+        <v>14.29</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3527</v>
+        <v>0.36</v>
       </c>
       <c r="K6" t="n">
         <v>0.1643</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -12808,7 +12808,7 @@
         <v>21</v>
       </c>
       <c r="S6" t="n">
-        <v>1709</v>
+        <v>1716.9</v>
       </c>
     </row>
     <row r="7">
@@ -13007,31 +13007,31 @@
         <v>1246</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10" t="n">
-        <v>1897</v>
+        <v>1886.9</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9403</v>
+        <v>4.7611</v>
       </c>
       <c r="G10" t="n">
-        <v>116.84</v>
+        <v>115.76</v>
       </c>
       <c r="H10" t="n">
-        <v>106.32</v>
+        <v>106.05</v>
       </c>
       <c r="I10" t="n">
-        <v>10.52</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.312</v>
+        <v>0.3106</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1463</v>
+        <v>0.1465</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>-3</v>
       </c>
       <c r="M10" t="n">
         <v>27</v>
@@ -13052,7 +13052,7 @@
         <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>1723.9</v>
+        <v>1734.8</v>
       </c>
     </row>
     <row r="11">
@@ -13129,31 +13129,31 @@
         <v>1328</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" t="n">
-        <v>1729</v>
+        <v>1722.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.822</v>
+        <v>-1.4338</v>
       </c>
       <c r="G12" t="n">
-        <v>120.4</v>
+        <v>120</v>
       </c>
       <c r="H12" t="n">
-        <v>111.31</v>
+        <v>111.63</v>
       </c>
       <c r="I12" t="n">
-        <v>9.09</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3094</v>
+        <v>0.309</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1414</v>
+        <v>0.1402</v>
       </c>
       <c r="L12" t="n">
-        <v>13.4</v>
+        <v>9.6</v>
       </c>
       <c r="M12" t="n">
         <v>46</v>
@@ -13174,7 +13174,7 @@
         <v>54</v>
       </c>
       <c r="S12" t="n">
-        <v>1666.2</v>
+        <v>1675.4</v>
       </c>
     </row>
     <row r="13">
@@ -13373,31 +13373,31 @@
         <v>1279</v>
       </c>
       <c r="D16" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E16" t="n">
-        <v>1659.4</v>
+        <v>1685.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.7529</v>
+        <v>-7.2757</v>
       </c>
       <c r="G16" t="n">
-        <v>108.81</v>
+        <v>108.93</v>
       </c>
       <c r="H16" t="n">
-        <v>108.87</v>
+        <v>108.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2848</v>
+        <v>0.2814</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1363</v>
+        <v>0.1336</v>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
         <v>81</v>
@@ -13418,7 +13418,7 @@
         <v>92</v>
       </c>
       <c r="S16" t="n">
-        <v>1697.1</v>
+        <v>1706.6</v>
       </c>
     </row>
     <row r="17">
@@ -16612,31 +16612,31 @@
         <v>1197</v>
       </c>
       <c r="D3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1297.6</v>
+        <v>1295.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1581</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>99.55</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>105.79</v>
+        <v>105.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.24</v>
+        <v>-6.32</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3027</v>
+        <v>0.3042</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2062</v>
+        <v>0.2044</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
         <v>315</v>
@@ -16657,7 +16657,7 @@
         <v>315</v>
       </c>
       <c r="S3" t="n">
-        <v>1376.1</v>
+        <v>1376.6</v>
       </c>
     </row>
     <row r="4">
@@ -16673,31 +16673,31 @@
         <v>1380</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1375.9</v>
+        <v>1377.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3939</v>
+        <v>-2.2287</v>
       </c>
       <c r="G4" t="n">
-        <v>106.4</v>
+        <v>106.09</v>
       </c>
       <c r="H4" t="n">
-        <v>111.97</v>
+        <v>111.35</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.57</v>
+        <v>-5.25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.322</v>
+        <v>0.3165</v>
       </c>
       <c r="K4" t="n">
-        <v>0.159</v>
+        <v>0.1627</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -16718,7 +16718,7 @@
         <v>277</v>
       </c>
       <c r="S4" t="n">
-        <v>1396.5</v>
+        <v>1393.5</v>
       </c>
     </row>
     <row r="5">
@@ -16795,31 +16795,31 @@
         <v>1105</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1291.1</v>
+        <v>1288.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.731</v>
+        <v>0.7093</v>
       </c>
       <c r="G6" t="n">
-        <v>106.44</v>
+        <v>105.69</v>
       </c>
       <c r="H6" t="n">
-        <v>109.11</v>
+        <v>109.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.67</v>
+        <v>-3.92</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2602</v>
+        <v>0.2565</v>
       </c>
       <c r="K6" t="n">
-        <v>0.161</v>
+        <v>0.1589</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
         <v>301</v>
@@ -16840,7 +16840,7 @@
         <v>308</v>
       </c>
       <c r="S6" t="n">
-        <v>1359</v>
+        <v>1355.6</v>
       </c>
     </row>
     <row r="7">
@@ -16978,31 +16978,31 @@
         <v>1341</v>
       </c>
       <c r="D9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>1260.4</v>
+        <v>1263.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.6629</v>
       </c>
       <c r="G9" t="n">
-        <v>103.68</v>
+        <v>104.26</v>
       </c>
       <c r="H9" t="n">
-        <v>107.97</v>
+        <v>107.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.29</v>
+        <v>-2.94</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2812</v>
+        <v>0.2838</v>
       </c>
       <c r="K9" t="n">
         <v>0.1546</v>
       </c>
       <c r="L9" t="n">
-        <v>10.8</v>
+        <v>12.8</v>
       </c>
       <c r="M9" t="n">
         <v>312</v>
@@ -17023,7 +17023,7 @@
         <v>316</v>
       </c>
       <c r="S9" t="n">
-        <v>1386.7</v>
+        <v>1382.8</v>
       </c>
     </row>
     <row r="10">
@@ -17516,31 +17516,31 @@
         <v>1409</v>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1679.9</v>
+        <v>1685.7</v>
       </c>
       <c r="F4" t="n">
-        <v>9.1937</v>
+        <v>8.801299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>122.52</v>
+        <v>121.6</v>
       </c>
       <c r="H4" t="n">
-        <v>106.2</v>
+        <v>105.56</v>
       </c>
       <c r="I4" t="n">
-        <v>16.32</v>
+        <v>16.04</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2712</v>
+        <v>0.2692</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1456</v>
+        <v>0.1481</v>
       </c>
       <c r="L4" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="M4" t="n">
         <v>58</v>
@@ -17561,7 +17561,7 @@
         <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>1503.5</v>
+        <v>1505.1</v>
       </c>
     </row>
     <row r="5">
@@ -17577,31 +17577,31 @@
         <v>1412</v>
       </c>
       <c r="D5" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1599.6</v>
+        <v>1590.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5782</v>
+        <v>0.5744</v>
       </c>
       <c r="G5" t="n">
-        <v>108.91</v>
+        <v>109.21</v>
       </c>
       <c r="H5" t="n">
-        <v>103.19</v>
+        <v>104.11</v>
       </c>
       <c r="I5" t="n">
-        <v>5.72</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3013</v>
+        <v>0.3005</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1241</v>
+        <v>0.1249</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>122</v>
@@ -17622,7 +17622,7 @@
         <v>117</v>
       </c>
       <c r="S5" t="n">
-        <v>1499.7</v>
+        <v>1498.7</v>
       </c>
     </row>
     <row r="6">
@@ -17638,31 +17638,31 @@
         <v>1150</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>1443.2</v>
+        <v>1452.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3825</v>
+        <v>1.4072</v>
       </c>
       <c r="G6" t="n">
-        <v>112.43</v>
+        <v>112.83</v>
       </c>
       <c r="H6" t="n">
-        <v>113.2</v>
+        <v>113.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.77</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2995</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1697</v>
+        <v>0.1663</v>
       </c>
       <c r="L6" t="n">
-        <v>-3</v>
+        <v>-2.2</v>
       </c>
       <c r="M6" t="n">
         <v>191</v>
@@ -17683,7 +17683,7 @@
         <v>183</v>
       </c>
       <c r="S6" t="n">
-        <v>1498.1</v>
+        <v>1502.2</v>
       </c>
     </row>
     <row r="7">
@@ -17699,31 +17699,31 @@
         <v>1317</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="n">
-        <v>1540.9</v>
+        <v>1535.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.0315</v>
+        <v>-4.7102</v>
       </c>
       <c r="G7" t="n">
-        <v>104.23</v>
+        <v>103.74</v>
       </c>
       <c r="H7" t="n">
-        <v>102.04</v>
+        <v>101.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2.19</v>
+        <v>1.76</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3337</v>
+        <v>0.333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1533</v>
+        <v>0.1539</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>140</v>
@@ -17744,7 +17744,7 @@
         <v>145</v>
       </c>
       <c r="S7" t="n">
-        <v>1509.6</v>
+        <v>1516.2</v>
       </c>
     </row>
     <row r="8">
@@ -18115,31 +18115,31 @@
         <v>1430</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1528</v>
+        <v>3.0131</v>
       </c>
       <c r="G2" t="n">
-        <v>111.58</v>
+        <v>111.37</v>
       </c>
       <c r="H2" t="n">
-        <v>100.45</v>
+        <v>100.52</v>
       </c>
       <c r="I2" t="n">
-        <v>11.12</v>
+        <v>10.85</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3056</v>
+        <v>0.304</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1962</v>
+        <v>0.1971</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="M2" t="n">
         <v>90</v>
@@ -18160,7 +18160,7 @@
         <v>85</v>
       </c>
       <c r="S2" t="n">
-        <v>1455.5</v>
+        <v>1456.2</v>
       </c>
     </row>
     <row r="3">
@@ -18176,31 +18176,31 @@
         <v>1465</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>1594.5</v>
+        <v>1597.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5103</v>
+        <v>1.5316</v>
       </c>
       <c r="G3" t="n">
-        <v>107.31</v>
+        <v>107.84</v>
       </c>
       <c r="H3" t="n">
-        <v>99.48999999999999</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>7.82</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3297</v>
+        <v>0.3313</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1719</v>
+        <v>0.1718</v>
       </c>
       <c r="L3" t="n">
-        <v>10.8</v>
+        <v>17.4</v>
       </c>
       <c r="M3" t="n">
         <v>112</v>
@@ -18221,7 +18221,7 @@
         <v>103</v>
       </c>
       <c r="S3" t="n">
-        <v>1455.6</v>
+        <v>1454.2</v>
       </c>
     </row>
     <row r="4">
@@ -18237,31 +18237,31 @@
         <v>1469</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1386.1</v>
+        <v>1383.5</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4009</v>
+        <v>2.4068</v>
       </c>
       <c r="G4" t="n">
-        <v>108.33</v>
+        <v>108</v>
       </c>
       <c r="H4" t="n">
-        <v>110.83</v>
+        <v>111.41</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.5</v>
+        <v>-3.41</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2668</v>
+        <v>0.2667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.17</v>
+        <v>0.1705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>-4.2</v>
       </c>
       <c r="M4" t="n">
         <v>184</v>
@@ -18282,7 +18282,7 @@
         <v>175</v>
       </c>
       <c r="S4" t="n">
-        <v>1489.8</v>
+        <v>1495.4</v>
       </c>
     </row>
     <row r="5">
@@ -18298,31 +18298,31 @@
         <v>1426</v>
       </c>
       <c r="D5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1459.9</v>
+        <v>1455.9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9557</v>
+        <v>0.8692</v>
       </c>
       <c r="G5" t="n">
-        <v>100.63</v>
+        <v>100.87</v>
       </c>
       <c r="H5" t="n">
-        <v>100.34</v>
+        <v>100.83</v>
       </c>
       <c r="I5" t="n">
-        <v>0.29</v>
+        <v>0.04</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3139</v>
+        <v>0.3127</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2045</v>
+        <v>0.2041</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
         <v>156</v>
@@ -18343,7 +18343,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="n">
-        <v>1455.6</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="6">
@@ -20938,31 +20938,31 @@
         <v>1112</v>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>2256</v>
+        <v>2262.9</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4143</v>
+        <v>7.0872</v>
       </c>
       <c r="G2" t="n">
-        <v>121.01</v>
+        <v>121.14</v>
       </c>
       <c r="H2" t="n">
-        <v>95.61</v>
+        <v>96.66</v>
       </c>
       <c r="I2" t="n">
-        <v>25.4</v>
+        <v>24.48</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2928</v>
+        <v>0.2942</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1495</v>
+        <v>0.151</v>
       </c>
       <c r="L2" t="n">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -20983,7 +20983,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1747.3</v>
+        <v>1758.1</v>
       </c>
     </row>
     <row r="3">
@@ -20999,31 +20999,31 @@
         <v>1222</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>2111.2</v>
+        <v>2120.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4261</v>
+        <v>1.2885</v>
       </c>
       <c r="G3" t="n">
-        <v>117.41</v>
+        <v>117.48</v>
       </c>
       <c r="H3" t="n">
-        <v>95.28</v>
+        <v>94.63</v>
       </c>
       <c r="I3" t="n">
-        <v>22.14</v>
+        <v>22.86</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3403</v>
+        <v>0.3358</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1244</v>
+        <v>0.1237</v>
       </c>
       <c r="L3" t="n">
-        <v>10.8</v>
+        <v>17.8</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -21044,7 +21044,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1716.1</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="4">
@@ -21060,31 +21060,31 @@
         <v>1242</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>1983.4</v>
+        <v>1973.7</v>
       </c>
       <c r="F4" t="n">
-        <v>10.797</v>
+        <v>10.346</v>
       </c>
       <c r="G4" t="n">
-        <v>111.09</v>
+        <v>109.9</v>
       </c>
       <c r="H4" t="n">
-        <v>100.73</v>
+        <v>101.51</v>
       </c>
       <c r="I4" t="n">
-        <v>10.36</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2493</v>
+        <v>0.2556</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1516</v>
+        <v>0.1512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>-6.2</v>
       </c>
       <c r="M4" t="n">
         <v>19</v>
@@ -21105,7 +21105,7 @@
         <v>19</v>
       </c>
       <c r="S4" t="n">
-        <v>1778</v>
+        <v>1791.1</v>
       </c>
     </row>
     <row r="5">
@@ -21182,31 +21182,31 @@
         <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
-        <v>2045.9</v>
+        <v>2039</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4203</v>
+        <v>2.2111</v>
       </c>
       <c r="G6" t="n">
-        <v>118.77</v>
+        <v>118.9</v>
       </c>
       <c r="H6" t="n">
-        <v>94.51000000000001</v>
+        <v>95.73</v>
       </c>
       <c r="I6" t="n">
-        <v>24.26</v>
+        <v>23.17</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3164</v>
+        <v>0.3217</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1462</v>
+        <v>0.1469</v>
       </c>
       <c r="L6" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
@@ -21227,7 +21227,7 @@
         <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1700.1</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="7">
@@ -22025,31 +22025,31 @@
         <v>1385</v>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>1964.1</v>
+        <v>1967.8</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6344</v>
+        <v>5.6546</v>
       </c>
       <c r="G2" t="n">
-        <v>113.75</v>
+        <v>114.06</v>
       </c>
       <c r="H2" t="n">
-        <v>98.54000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>15.21</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3255</v>
+        <v>0.3244</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1408</v>
+        <v>0.1434</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
@@ -22070,7 +22070,7 @@
         <v>22</v>
       </c>
       <c r="S2" t="n">
-        <v>1676.3</v>
+        <v>1677.1</v>
       </c>
     </row>
     <row r="3">
@@ -22086,31 +22086,31 @@
         <v>1163</v>
       </c>
       <c r="D3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>2066.1</v>
+        <v>2067.9</v>
       </c>
       <c r="F3" t="n">
-        <v>8.2806</v>
+        <v>7.6929</v>
       </c>
       <c r="G3" t="n">
-        <v>117.74</v>
+        <v>117.25</v>
       </c>
       <c r="H3" t="n">
-        <v>97.67</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>20.07</v>
+        <v>20.14</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2928</v>
+        <v>0.2963</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1549</v>
+        <v>0.1567</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -22131,7 +22131,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>1659.9</v>
+        <v>1657.6</v>
       </c>
     </row>
     <row r="4">
@@ -22208,31 +22208,31 @@
         <v>1371</v>
       </c>
       <c r="D5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>1673.5</v>
+        <v>1669.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6016</v>
+        <v>4.331</v>
       </c>
       <c r="G5" t="n">
-        <v>105.77</v>
+        <v>105.59</v>
       </c>
       <c r="H5" t="n">
-        <v>97.47</v>
+        <v>98.3</v>
       </c>
       <c r="I5" t="n">
-        <v>8.300000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="J5" t="n">
-        <v>0.318</v>
+        <v>0.3263</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1565</v>
+        <v>0.1579</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>-0.2</v>
       </c>
       <c r="M5" t="n">
         <v>52</v>
@@ -22253,7 +22253,7 @@
         <v>56</v>
       </c>
       <c r="S5" t="n">
-        <v>1635.8</v>
+        <v>1648.5</v>
       </c>
     </row>
     <row r="6">
@@ -22635,31 +22635,31 @@
         <v>1207</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" t="n">
-        <v>1586.2</v>
+        <v>1584.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5368</v>
+        <v>-4.2375</v>
       </c>
       <c r="G12" t="n">
-        <v>109.93</v>
+        <v>109</v>
       </c>
       <c r="H12" t="n">
-        <v>108.05</v>
+        <v>108.36</v>
       </c>
       <c r="I12" t="n">
-        <v>1.88</v>
+        <v>0.64</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3069</v>
+        <v>0.308</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1463</v>
+        <v>0.1483</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
         <v>87</v>
@@ -22680,7 +22680,7 @@
         <v>95</v>
       </c>
       <c r="S12" t="n">
-        <v>1646</v>
+        <v>1660.1</v>
       </c>
     </row>
   </sheetData>

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -556,31 +556,31 @@
         <v>1387</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1811.5</v>
+        <v>1793.2</v>
       </c>
       <c r="F2" t="n">
-        <v>9.2125</v>
+        <v>8.666399999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>120.63</v>
+        <v>120</v>
       </c>
       <c r="H2" t="n">
-        <v>98.51000000000001</v>
+        <v>98.73</v>
       </c>
       <c r="I2" t="n">
-        <v>22.12</v>
+        <v>21.28</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2386</v>
+        <v>0.2418</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1675</v>
+        <v>0.1658</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.6</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>40</v>
@@ -601,7 +601,7 @@
         <v>27</v>
       </c>
       <c r="S2" t="n">
-        <v>1510.4</v>
+        <v>1516.9</v>
       </c>
     </row>
     <row r="3">
@@ -617,31 +617,31 @@
         <v>1433</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1743.5</v>
+        <v>1751</v>
       </c>
       <c r="F3" t="n">
-        <v>3.091</v>
+        <v>3.1884</v>
       </c>
       <c r="G3" t="n">
-        <v>118.25</v>
+        <v>118.3</v>
       </c>
       <c r="H3" t="n">
-        <v>103.78</v>
+        <v>103.55</v>
       </c>
       <c r="I3" t="n">
-        <v>14.46</v>
+        <v>14.75</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2985</v>
+        <v>0.2988</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1511</v>
+        <v>0.1491</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
@@ -662,7 +662,7 @@
         <v>44</v>
       </c>
       <c r="S3" t="n">
-        <v>1550.6</v>
+        <v>1553.9</v>
       </c>
     </row>
     <row r="4">
@@ -678,31 +678,31 @@
         <v>1386</v>
       </c>
       <c r="D4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>1618.4</v>
+        <v>1610.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2818</v>
+        <v>1.549</v>
       </c>
       <c r="G4" t="n">
-        <v>106.15</v>
+        <v>105.81</v>
       </c>
       <c r="H4" t="n">
-        <v>102.39</v>
+        <v>103.14</v>
       </c>
       <c r="I4" t="n">
-        <v>3.76</v>
+        <v>2.67</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2844</v>
+        <v>0.287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1631</v>
+        <v>0.162</v>
       </c>
       <c r="L4" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>121</v>
@@ -723,7 +723,7 @@
         <v>124</v>
       </c>
       <c r="S4" t="n">
-        <v>1508.9</v>
+        <v>1518.1</v>
       </c>
     </row>
     <row r="5">
@@ -739,31 +739,31 @@
         <v>1173</v>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" t="n">
-        <v>1669.7</v>
+        <v>1688.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3756</v>
+        <v>-2.1851</v>
       </c>
       <c r="G5" t="n">
-        <v>109.86</v>
+        <v>109.55</v>
       </c>
       <c r="H5" t="n">
-        <v>101.93</v>
+        <v>101.89</v>
       </c>
       <c r="I5" t="n">
-        <v>7.93</v>
+        <v>7.66</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2559</v>
+        <v>0.2528</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1703</v>
+        <v>0.1736</v>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>79</v>
@@ -784,7 +784,7 @@
         <v>75</v>
       </c>
       <c r="S5" t="n">
-        <v>1559.7</v>
+        <v>1570.2</v>
       </c>
     </row>
     <row r="6">
@@ -1521,31 +1521,31 @@
         <v>1276</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>2192.4</v>
+        <v>2196.8</v>
       </c>
       <c r="F2" t="n">
-        <v>6.99</v>
+        <v>6.739</v>
       </c>
       <c r="G2" t="n">
-        <v>121.3</v>
+        <v>120.64</v>
       </c>
       <c r="H2" t="n">
-        <v>95.95</v>
+        <v>95.94</v>
       </c>
       <c r="I2" t="n">
-        <v>25.34</v>
+        <v>24.71</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2601</v>
+        <v>0.2604</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1647</v>
+        <v>0.1666</v>
       </c>
       <c r="L2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1768.8</v>
+        <v>1772.9</v>
       </c>
     </row>
     <row r="3">
@@ -1765,31 +1765,31 @@
         <v>1458</v>
       </c>
       <c r="D6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" t="n">
-        <v>1886.8</v>
+        <v>1882.4</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1287</v>
+        <v>2.4266</v>
       </c>
       <c r="G6" t="n">
-        <v>119.67</v>
+        <v>118.8</v>
       </c>
       <c r="H6" t="n">
-        <v>108.89</v>
+        <v>108.53</v>
       </c>
       <c r="I6" t="n">
-        <v>10.78</v>
+        <v>10.27</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2787</v>
+        <v>0.2776</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1222</v>
+        <v>0.124</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>23</v>
@@ -1810,7 +1810,7 @@
         <v>26</v>
       </c>
       <c r="S6" t="n">
-        <v>1709.1</v>
+        <v>1724.6</v>
       </c>
     </row>
     <row r="7">
@@ -1826,31 +1826,31 @@
         <v>1417</v>
       </c>
       <c r="D7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" t="n">
-        <v>1885.4</v>
+        <v>1874.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6042</v>
+        <v>2.8463</v>
       </c>
       <c r="G7" t="n">
-        <v>117.52</v>
+        <v>117.18</v>
       </c>
       <c r="H7" t="n">
-        <v>107.06</v>
+        <v>107.51</v>
       </c>
       <c r="I7" t="n">
-        <v>10.46</v>
+        <v>9.67</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3052</v>
+        <v>0.3055</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1315</v>
+        <v>0.1325</v>
       </c>
       <c r="L7" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="M7" t="n">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>34</v>
       </c>
       <c r="S7" t="n">
-        <v>1698.9</v>
+        <v>1706.3</v>
       </c>
     </row>
     <row r="8">
@@ -1887,31 +1887,31 @@
         <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" t="n">
-        <v>1975.7</v>
+        <v>1986.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3998</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>124.77</v>
+        <v>124.76</v>
       </c>
       <c r="H8" t="n">
-        <v>106.95</v>
+        <v>107.25</v>
       </c>
       <c r="I8" t="n">
-        <v>17.82</v>
+        <v>17.51</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3094</v>
+        <v>0.3105</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1359</v>
+        <v>0.1343</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
@@ -1932,7 +1932,7 @@
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>1751.8</v>
+        <v>1754.6</v>
       </c>
     </row>
     <row r="9">
@@ -2730,31 +2730,31 @@
         <v>1414</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1620.3</v>
+        <v>1610</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2032</v>
+        <v>2.2217</v>
       </c>
       <c r="G2" t="n">
-        <v>104.72</v>
+        <v>103.96</v>
       </c>
       <c r="H2" t="n">
-        <v>96.98</v>
+        <v>97.06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.74</v>
+        <v>6.9</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2714</v>
+        <v>0.2752</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1714</v>
+        <v>0.1724</v>
       </c>
       <c r="L2" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>106</v>
@@ -2775,7 +2775,7 @@
         <v>118</v>
       </c>
       <c r="S2" t="n">
-        <v>1473</v>
+        <v>1475.3</v>
       </c>
     </row>
     <row r="3">
@@ -2791,31 +2791,31 @@
         <v>1218</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1538.8</v>
+        <v>1549.1</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0942</v>
+        <v>2.9832</v>
       </c>
       <c r="G3" t="n">
-        <v>108.45</v>
+        <v>108.14</v>
       </c>
       <c r="H3" t="n">
-        <v>96.83</v>
+        <v>96.69</v>
       </c>
       <c r="I3" t="n">
-        <v>11.62</v>
+        <v>11.45</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2555</v>
+        <v>0.2583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1843</v>
+        <v>0.1851</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="M3" t="n">
         <v>115</v>
@@ -2836,7 +2836,7 @@
         <v>112</v>
       </c>
       <c r="S3" t="n">
-        <v>1444.2</v>
+        <v>1452.3</v>
       </c>
     </row>
     <row r="4">
@@ -4416,31 +4416,31 @@
         <v>1256</v>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" t="n">
-        <v>1515.2</v>
+        <v>1508.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3208</v>
+        <v>-1.1024</v>
       </c>
       <c r="G5" t="n">
-        <v>104.02</v>
+        <v>103.62</v>
       </c>
       <c r="H5" t="n">
-        <v>103.4</v>
+        <v>103.73</v>
       </c>
       <c r="I5" t="n">
-        <v>0.62</v>
+        <v>-0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3299</v>
+        <v>0.3293</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1728</v>
+        <v>0.1715</v>
       </c>
       <c r="L5" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="M5" t="n">
         <v>208</v>
@@ -4461,7 +4461,7 @@
         <v>213</v>
       </c>
       <c r="S5" t="n">
-        <v>1463.6</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6">
@@ -4538,31 +4538,31 @@
         <v>1244</v>
       </c>
       <c r="D7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" t="n">
-        <v>1514.9</v>
+        <v>1521.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2575</v>
+        <v>-0.1615</v>
       </c>
       <c r="G7" t="n">
-        <v>111.26</v>
+        <v>111.12</v>
       </c>
       <c r="H7" t="n">
-        <v>108.75</v>
+        <v>108.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3392</v>
+        <v>0.345</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1672</v>
+        <v>0.165</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
         <v>178</v>
@@ -4583,7 +4583,7 @@
         <v>170</v>
       </c>
       <c r="S7" t="n">
-        <v>1473.6</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="8">
@@ -5736,31 +5736,31 @@
         <v>1463</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1720.2</v>
+        <v>1727.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1161</v>
+        <v>1.0257</v>
       </c>
       <c r="G2" t="n">
-        <v>120.93</v>
+        <v>122.21</v>
       </c>
       <c r="H2" t="n">
-        <v>107.17</v>
+        <v>108.54</v>
       </c>
       <c r="I2" t="n">
-        <v>13.77</v>
+        <v>13.66</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2847</v>
+        <v>0.2923</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1362</v>
+        <v>0.1356</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>78</v>
@@ -5781,7 +5781,7 @@
         <v>66</v>
       </c>
       <c r="S2" t="n">
-        <v>1457.4</v>
+        <v>1459.8</v>
       </c>
     </row>
     <row r="3">
@@ -5797,31 +5797,31 @@
         <v>1217</v>
       </c>
       <c r="D3" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1513.7</v>
+        <v>1490.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6769</v>
+        <v>2.799</v>
       </c>
       <c r="G3" t="n">
-        <v>109.39</v>
+        <v>107.97</v>
       </c>
       <c r="H3" t="n">
-        <v>104.64</v>
+        <v>103.76</v>
       </c>
       <c r="I3" t="n">
-        <v>4.75</v>
+        <v>4.21</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2416</v>
+        <v>0.2408</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1637</v>
+        <v>0.1611</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
         <v>149</v>
@@ -5842,7 +5842,7 @@
         <v>150</v>
       </c>
       <c r="S3" t="n">
-        <v>1467.8</v>
+        <v>1465.2</v>
       </c>
     </row>
     <row r="4">
@@ -5858,31 +5858,31 @@
         <v>1335</v>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>1419.8</v>
+        <v>1431.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0511</v>
+        <v>1.1135</v>
       </c>
       <c r="G4" t="n">
-        <v>108.53</v>
+        <v>107.49</v>
       </c>
       <c r="H4" t="n">
-        <v>106.51</v>
+        <v>105.83</v>
       </c>
       <c r="I4" t="n">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="J4" t="n">
-        <v>0.312</v>
+        <v>0.3084</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1496</v>
+        <v>0.1543</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="M4" t="n">
         <v>163</v>
@@ -5903,7 +5903,7 @@
         <v>148</v>
       </c>
       <c r="S4" t="n">
-        <v>1479.6</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="5">
@@ -5919,31 +5919,31 @@
         <v>1165</v>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E5" t="n">
-        <v>1493.9</v>
+        <v>1478.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2607</v>
+        <v>-1.0235</v>
       </c>
       <c r="G5" t="n">
-        <v>119.99</v>
+        <v>120.04</v>
       </c>
       <c r="H5" t="n">
-        <v>116.75</v>
+        <v>118.39</v>
       </c>
       <c r="I5" t="n">
-        <v>3.24</v>
+        <v>1.64</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2786</v>
+        <v>0.2957</v>
       </c>
       <c r="K5" t="n">
-        <v>0.158</v>
+        <v>0.1555</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>-0.2</v>
       </c>
       <c r="M5" t="n">
         <v>158</v>
@@ -5964,7 +5964,7 @@
         <v>141</v>
       </c>
       <c r="S5" t="n">
-        <v>1488.6</v>
+        <v>1502.5</v>
       </c>
     </row>
   </sheetData>
@@ -6812,31 +6812,31 @@
         <v>1224</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1406</v>
+        <v>1407.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0696</v>
+        <v>2.9318</v>
       </c>
       <c r="G2" t="n">
-        <v>108.81</v>
+        <v>109.06</v>
       </c>
       <c r="H2" t="n">
-        <v>97.94</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>10.87</v>
+        <v>10.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3142</v>
+        <v>0.3191</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1871</v>
+        <v>0.1856</v>
       </c>
       <c r="L2" t="n">
-        <v>20.6</v>
+        <v>15.4</v>
       </c>
       <c r="M2" t="n">
         <v>202</v>
@@ -6857,7 +6857,7 @@
         <v>202</v>
       </c>
       <c r="S2" t="n">
-        <v>1374.8</v>
+        <v>1372.4</v>
       </c>
     </row>
     <row r="3">
@@ -6934,31 +6934,31 @@
         <v>1300</v>
       </c>
       <c r="D4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>1291.7</v>
+        <v>1289.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3164</v>
+        <v>-1.1732</v>
       </c>
       <c r="G4" t="n">
-        <v>101.75</v>
+        <v>101.76</v>
       </c>
       <c r="H4" t="n">
-        <v>115.02</v>
+        <v>115.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-13.27</v>
+        <v>-13.44</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3122</v>
+        <v>0.3141</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1759</v>
+        <v>0.1781</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>-1.2</v>
       </c>
       <c r="M4" t="n">
         <v>353</v>
@@ -6979,7 +6979,7 @@
         <v>347</v>
       </c>
       <c r="S4" t="n">
-        <v>1379.6</v>
+        <v>1382.1</v>
       </c>
     </row>
     <row r="5">
@@ -7411,31 +7411,31 @@
         <v>1103</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1704.5</v>
+        <v>1707.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8839</v>
+        <v>1.9745</v>
       </c>
       <c r="G3" t="n">
-        <v>121.82</v>
+        <v>121.64</v>
       </c>
       <c r="H3" t="n">
-        <v>104.08</v>
+        <v>104.36</v>
       </c>
       <c r="I3" t="n">
-        <v>17.74</v>
+        <v>17.27</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2847</v>
+        <v>0.2887</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1512</v>
+        <v>0.15</v>
       </c>
       <c r="L3" t="n">
-        <v>16.8</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
@@ -7456,7 +7456,7 @@
         <v>52</v>
       </c>
       <c r="S3" t="n">
-        <v>1481.1</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="4">
@@ -7533,31 +7533,31 @@
         <v>1405</v>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" t="n">
-        <v>1464.4</v>
+        <v>1461</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.583</v>
+        <v>-0.4994</v>
       </c>
       <c r="G5" t="n">
         <v>114.81</v>
       </c>
       <c r="H5" t="n">
-        <v>111.04</v>
+        <v>111.47</v>
       </c>
       <c r="I5" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2898</v>
+        <v>0.2875</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1416</v>
+        <v>0.1423</v>
       </c>
       <c r="L5" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="M5" t="n">
         <v>135</v>
@@ -7578,7 +7578,7 @@
         <v>146</v>
       </c>
       <c r="S5" t="n">
-        <v>1495.2</v>
+        <v>1503.6</v>
       </c>
     </row>
     <row r="6">
@@ -8731,31 +8731,31 @@
         <v>1181</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>2189.2</v>
+        <v>2195.9</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7126</v>
+        <v>3.7176</v>
       </c>
       <c r="G2" t="n">
-        <v>122.89</v>
+        <v>122.74</v>
       </c>
       <c r="H2" t="n">
-        <v>94.03</v>
+        <v>94.67</v>
       </c>
       <c r="I2" t="n">
-        <v>28.87</v>
+        <v>28.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2894</v>
+        <v>0.2982</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1548</v>
+        <v>0.1541</v>
       </c>
       <c r="L2" t="n">
-        <v>16.6</v>
+        <v>12.2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1703.5</v>
+        <v>1712.3</v>
       </c>
     </row>
     <row r="3">
@@ -8792,31 +8792,31 @@
         <v>1438</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1971</v>
+        <v>1964.3</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5889</v>
+        <v>12.2076</v>
       </c>
       <c r="G3" t="n">
-        <v>119.48</v>
+        <v>119.04</v>
       </c>
       <c r="H3" t="n">
-        <v>100.21</v>
+        <v>100.85</v>
       </c>
       <c r="I3" t="n">
-        <v>19.27</v>
+        <v>18.19</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3151</v>
+        <v>0.3154</v>
       </c>
       <c r="K3" t="n">
-        <v>0.153</v>
+        <v>0.1544</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
@@ -8837,7 +8837,7 @@
         <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>1646.9</v>
+        <v>1665.9</v>
       </c>
     </row>
     <row r="4">
@@ -9757,31 +9757,31 @@
         <v>1429</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1885.6</v>
+        <v>1897.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1404</v>
+        <v>0.1736</v>
       </c>
       <c r="G2" t="n">
-        <v>119.83</v>
+        <v>119.56</v>
       </c>
       <c r="H2" t="n">
-        <v>103.76</v>
+        <v>103.49</v>
       </c>
       <c r="I2" t="n">
-        <v>16.07</v>
+        <v>16.08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3026</v>
+        <v>0.3032</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1501</v>
+        <v>0.1479</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="M2" t="n">
         <v>35</v>
@@ -9802,7 +9802,7 @@
         <v>29</v>
       </c>
       <c r="S2" t="n">
-        <v>1604.7</v>
+        <v>1611.4</v>
       </c>
     </row>
     <row r="3">
@@ -9818,31 +9818,31 @@
         <v>1361</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1812.2</v>
+        <v>1800.4</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8008</v>
+        <v>4.5904</v>
       </c>
       <c r="G3" t="n">
-        <v>109.86</v>
+        <v>109.49</v>
       </c>
       <c r="H3" t="n">
-        <v>100.82</v>
+        <v>101.41</v>
       </c>
       <c r="I3" t="n">
-        <v>9.050000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2638</v>
+        <v>0.2636</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1664</v>
+        <v>0.1682</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="M3" t="n">
         <v>47</v>
@@ -9863,7 +9863,7 @@
         <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>1659.4</v>
+        <v>1666.9</v>
       </c>
     </row>
     <row r="4">
@@ -12519,31 +12519,31 @@
         <v>1196</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>2024.9</v>
+        <v>2006.7</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1754</v>
+        <v>3.4651</v>
       </c>
       <c r="G2" t="n">
-        <v>120.02</v>
+        <v>119.99</v>
       </c>
       <c r="H2" t="n">
-        <v>98.41</v>
+        <v>100.19</v>
       </c>
       <c r="I2" t="n">
-        <v>21.61</v>
+        <v>19.81</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3339</v>
+        <v>0.3342</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1592</v>
+        <v>0.1568</v>
       </c>
       <c r="L2" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -12564,7 +12564,7 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>1715.4</v>
+        <v>1722.9</v>
       </c>
     </row>
     <row r="3">
@@ -12641,31 +12641,31 @@
         <v>1116</v>
       </c>
       <c r="D4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>1956.5</v>
+        <v>1961.7</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3805</v>
+        <v>5.2535</v>
       </c>
       <c r="G4" t="n">
-        <v>122.83</v>
+        <v>122.84</v>
       </c>
       <c r="H4" t="n">
-        <v>109.16</v>
+        <v>109.47</v>
       </c>
       <c r="I4" t="n">
-        <v>13.66</v>
+        <v>13.37</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3026</v>
+        <v>0.3045</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1196</v>
+        <v>0.1197</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="M4" t="n">
         <v>18</v>
@@ -12686,7 +12686,7 @@
         <v>18</v>
       </c>
       <c r="S4" t="n">
-        <v>1728.4</v>
+        <v>1726.7</v>
       </c>
     </row>
     <row r="5">
@@ -12702,31 +12702,31 @@
         <v>1435</v>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" t="n">
-        <v>1949.6</v>
+        <v>1967.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1.887</v>
+        <v>1.6985</v>
       </c>
       <c r="G5" t="n">
-        <v>121.84</v>
+        <v>122.92</v>
       </c>
       <c r="H5" t="n">
-        <v>105.79</v>
+        <v>106.35</v>
       </c>
       <c r="I5" t="n">
-        <v>16.05</v>
+        <v>16.57</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2851</v>
+        <v>0.2937</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1258</v>
+        <v>0.1302</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="M5" t="n">
         <v>13</v>
@@ -12747,7 +12747,7 @@
         <v>16</v>
       </c>
       <c r="S5" t="n">
-        <v>1701.5</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="6">
@@ -13373,28 +13373,28 @@
         <v>1279</v>
       </c>
       <c r="D16" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16" t="n">
-        <v>1685.2</v>
+        <v>1680</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.2757</v>
+        <v>-6.7111</v>
       </c>
       <c r="G16" t="n">
-        <v>108.93</v>
+        <v>109.14</v>
       </c>
       <c r="H16" t="n">
-        <v>108.99</v>
+        <v>109.36</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.06</v>
+        <v>-0.22</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2814</v>
+        <v>0.2823</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1336</v>
+        <v>0.1344</v>
       </c>
       <c r="L16" t="n">
         <v>1.8</v>
@@ -13418,7 +13418,7 @@
         <v>92</v>
       </c>
       <c r="S16" t="n">
-        <v>1706.6</v>
+        <v>1713.4</v>
       </c>
     </row>
     <row r="17">
@@ -16673,31 +16673,31 @@
         <v>1380</v>
       </c>
       <c r="D4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>1377.9</v>
+        <v>1374.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2287</v>
+        <v>-2.0668</v>
       </c>
       <c r="G4" t="n">
-        <v>106.09</v>
+        <v>105.92</v>
       </c>
       <c r="H4" t="n">
-        <v>111.35</v>
+        <v>111.39</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.25</v>
+        <v>-5.47</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3165</v>
+        <v>0.3169</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1627</v>
+        <v>0.1617</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -16718,7 +16718,7 @@
         <v>277</v>
       </c>
       <c r="S4" t="n">
-        <v>1393.5</v>
+        <v>1389.2</v>
       </c>
     </row>
     <row r="5">
@@ -16978,31 +16978,31 @@
         <v>1341</v>
       </c>
       <c r="D9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" t="n">
-        <v>1263.2</v>
+        <v>1266.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6629</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>104.26</v>
+        <v>104.38</v>
       </c>
       <c r="H9" t="n">
-        <v>107.2</v>
+        <v>107.11</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.94</v>
+        <v>-2.73</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2838</v>
+        <v>0.2878</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1546</v>
+        <v>0.1551</v>
       </c>
       <c r="L9" t="n">
-        <v>12.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>312</v>
@@ -17023,7 +17023,7 @@
         <v>316</v>
       </c>
       <c r="S9" t="n">
-        <v>1382.8</v>
+        <v>1383.4</v>
       </c>
     </row>
     <row r="10">
@@ -17394,31 +17394,31 @@
         <v>1378</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1711.8</v>
+        <v>1714.9</v>
       </c>
       <c r="F2" t="n">
-        <v>9.207800000000001</v>
+        <v>9.035</v>
       </c>
       <c r="G2" t="n">
-        <v>116.06</v>
+        <v>116.33</v>
       </c>
       <c r="H2" t="n">
-        <v>101.73</v>
+        <v>101.48</v>
       </c>
       <c r="I2" t="n">
-        <v>14.32</v>
+        <v>14.84</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3392</v>
+        <v>0.3412</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1453</v>
+        <v>0.1466</v>
       </c>
       <c r="L2" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="M2" t="n">
         <v>51</v>
@@ -17439,7 +17439,7 @@
         <v>49</v>
       </c>
       <c r="S2" t="n">
-        <v>1553.3</v>
+        <v>1550.3</v>
       </c>
     </row>
     <row r="3">
@@ -17455,31 +17455,31 @@
         <v>1455</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1620</v>
+        <v>1632.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5141</v>
+        <v>1.6748</v>
       </c>
       <c r="G3" t="n">
-        <v>112.55</v>
+        <v>113.01</v>
       </c>
       <c r="H3" t="n">
-        <v>102</v>
+        <v>102.22</v>
       </c>
       <c r="I3" t="n">
-        <v>10.54</v>
+        <v>10.79</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3477</v>
+        <v>0.3461</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1417</v>
+        <v>0.1427</v>
       </c>
       <c r="L3" t="n">
-        <v>11.2</v>
+        <v>13.2</v>
       </c>
       <c r="M3" t="n">
         <v>88</v>
@@ -17500,7 +17500,7 @@
         <v>80</v>
       </c>
       <c r="S3" t="n">
-        <v>1534.8</v>
+        <v>1540.9</v>
       </c>
     </row>
     <row r="4">
@@ -17516,31 +17516,31 @@
         <v>1409</v>
       </c>
       <c r="D4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>1685.7</v>
+        <v>1673.1</v>
       </c>
       <c r="F4" t="n">
-        <v>8.801299999999999</v>
+        <v>8.4628</v>
       </c>
       <c r="G4" t="n">
-        <v>121.6</v>
+        <v>121.13</v>
       </c>
       <c r="H4" t="n">
-        <v>105.56</v>
+        <v>106.46</v>
       </c>
       <c r="I4" t="n">
-        <v>16.04</v>
+        <v>14.67</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2692</v>
+        <v>0.2753</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1481</v>
+        <v>0.1473</v>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>11.2</v>
       </c>
       <c r="M4" t="n">
         <v>58</v>
@@ -17561,7 +17561,7 @@
         <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>1505.1</v>
+        <v>1509.4</v>
       </c>
     </row>
     <row r="5">
@@ -17638,31 +17638,31 @@
         <v>1150</v>
       </c>
       <c r="D6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" t="n">
-        <v>1452.6</v>
+        <v>1449.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4072</v>
+        <v>1.4733</v>
       </c>
       <c r="G6" t="n">
-        <v>112.83</v>
+        <v>112</v>
       </c>
       <c r="H6" t="n">
-        <v>113.53</v>
+        <v>114.05</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.3044</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1663</v>
+        <v>0.1687</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2</v>
+        <v>-6.4</v>
       </c>
       <c r="M6" t="n">
         <v>191</v>
@@ -17683,7 +17683,7 @@
         <v>183</v>
       </c>
       <c r="S6" t="n">
-        <v>1502.2</v>
+        <v>1509.6</v>
       </c>
     </row>
     <row r="7">
@@ -18115,31 +18115,31 @@
         <v>1430</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1641</v>
+        <v>1630.2</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0131</v>
+        <v>2.9069</v>
       </c>
       <c r="G2" t="n">
-        <v>111.37</v>
+        <v>110.64</v>
       </c>
       <c r="H2" t="n">
-        <v>100.52</v>
+        <v>100.29</v>
       </c>
       <c r="I2" t="n">
-        <v>10.85</v>
+        <v>10.35</v>
       </c>
       <c r="J2" t="n">
-        <v>0.304</v>
+        <v>0.3035</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1971</v>
+        <v>0.197</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="M2" t="n">
         <v>90</v>
@@ -18160,7 +18160,7 @@
         <v>85</v>
       </c>
       <c r="S2" t="n">
-        <v>1456.2</v>
+        <v>1461.8</v>
       </c>
     </row>
     <row r="3">
@@ -18176,31 +18176,31 @@
         <v>1465</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1597.1</v>
+        <v>1607.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5316</v>
+        <v>1.5554</v>
       </c>
       <c r="G3" t="n">
-        <v>107.84</v>
+        <v>107.22</v>
       </c>
       <c r="H3" t="n">
-        <v>99.54000000000001</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3313</v>
+        <v>0.3287</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1718</v>
+        <v>0.1735</v>
       </c>
       <c r="L3" t="n">
-        <v>17.4</v>
+        <v>15.4</v>
       </c>
       <c r="M3" t="n">
         <v>112</v>
@@ -18221,7 +18221,7 @@
         <v>103</v>
       </c>
       <c r="S3" t="n">
-        <v>1454.2</v>
+        <v>1462.4</v>
       </c>
     </row>
     <row r="4">
@@ -19496,31 +19496,31 @@
         <v>1420</v>
       </c>
       <c r="D2" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1393.7</v>
+        <v>1397.9</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2859</v>
+        <v>1.3468</v>
       </c>
       <c r="G2" t="n">
-        <v>113.44</v>
+        <v>113.39</v>
       </c>
       <c r="H2" t="n">
-        <v>102.32</v>
+        <v>101.92</v>
       </c>
       <c r="I2" t="n">
-        <v>11.13</v>
+        <v>11.47</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2168</v>
+        <v>0.2176</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1344</v>
+        <v>0.135</v>
       </c>
       <c r="L2" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="M2" t="n">
         <v>198</v>
@@ -19541,7 +19541,7 @@
         <v>205</v>
       </c>
       <c r="S2" t="n">
-        <v>1364.8</v>
+        <v>1369.1</v>
       </c>
     </row>
     <row r="3">
@@ -19557,31 +19557,31 @@
         <v>1436</v>
       </c>
       <c r="D3" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>1470</v>
+        <v>1465.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5409</v>
+        <v>-1.4149</v>
       </c>
       <c r="G3" t="n">
-        <v>111.42</v>
+        <v>110.8</v>
       </c>
       <c r="H3" t="n">
-        <v>105.02</v>
+        <v>105.67</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>5.13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.241</v>
+        <v>0.2421</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1406</v>
+        <v>0.1399</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
         <v>235</v>
@@ -19602,7 +19602,7 @@
         <v>223</v>
       </c>
       <c r="S3" t="n">
-        <v>1389.6</v>
+        <v>1390.5</v>
       </c>
     </row>
     <row r="4">
@@ -20938,31 +20938,31 @@
         <v>1112</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>2262.9</v>
+        <v>2272.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7.0872</v>
+        <v>6.8151</v>
       </c>
       <c r="G2" t="n">
         <v>121.14</v>
       </c>
       <c r="H2" t="n">
-        <v>96.66</v>
+        <v>97.11</v>
       </c>
       <c r="I2" t="n">
-        <v>24.48</v>
+        <v>24.03</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2942</v>
+        <v>0.2925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.151</v>
+        <v>0.1497</v>
       </c>
       <c r="L2" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -20983,7 +20983,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>1758.1</v>
+        <v>1769.2</v>
       </c>
     </row>
     <row r="3">
@@ -20999,31 +20999,31 @@
         <v>1222</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>2120.9</v>
+        <v>2111.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2885</v>
+        <v>1.2196</v>
       </c>
       <c r="G3" t="n">
-        <v>117.48</v>
+        <v>117.35</v>
       </c>
       <c r="H3" t="n">
-        <v>94.63</v>
+        <v>95.8</v>
       </c>
       <c r="I3" t="n">
-        <v>22.86</v>
+        <v>21.55</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3358</v>
+        <v>0.3386</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1237</v>
+        <v>0.1236</v>
       </c>
       <c r="L3" t="n">
-        <v>17.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -21044,7 +21044,7 @@
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1724.5</v>
+        <v>1742.7</v>
       </c>
     </row>
     <row r="4">
@@ -22025,31 +22025,31 @@
         <v>1385</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>1967.8</v>
+        <v>1984.9</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6546</v>
+        <v>5.6609</v>
       </c>
       <c r="G2" t="n">
-        <v>114.06</v>
+        <v>113.97</v>
       </c>
       <c r="H2" t="n">
-        <v>98.84999999999999</v>
+        <v>98.16</v>
       </c>
       <c r="I2" t="n">
-        <v>15.21</v>
+        <v>15.81</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3244</v>
+        <v>0.3224</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1434</v>
+        <v>0.1422</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
@@ -22070,7 +22070,7 @@
         <v>22</v>
       </c>
       <c r="S2" t="n">
-        <v>1677.1</v>
+        <v>1691.6</v>
       </c>
     </row>
     <row r="3">
@@ -22086,31 +22086,31 @@
         <v>1163</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" t="n">
-        <v>2067.9</v>
+        <v>2050.7</v>
       </c>
       <c r="F3" t="n">
-        <v>7.6929</v>
+        <v>7.1741</v>
       </c>
       <c r="G3" t="n">
-        <v>117.25</v>
+        <v>116.06</v>
       </c>
       <c r="H3" t="n">
-        <v>97.09999999999999</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>20.14</v>
+        <v>18.05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2963</v>
+        <v>0.3013</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1567</v>
+        <v>0.1603</v>
       </c>
       <c r="L3" t="n">
-        <v>14.2</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -22131,7 +22131,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>1657.6</v>
+        <v>1670.2</v>
       </c>
     </row>
     <row r="4">

--- a/conf_team_stats_2026.xlsx
+++ b/conf_team_stats_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,97 +447,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -610,7 +598,7 @@
         <v>30</v>
       </c>
       <c r="R2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S2" t="n">
         <v>1516.9</v>
@@ -668,9 +656,11 @@
         <v>41</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="R3" t="n">
+        <v>43</v>
+      </c>
       <c r="S3" t="n">
         <v>1558.4</v>
       </c>
@@ -730,7 +720,7 @@
         <v>89</v>
       </c>
       <c r="R4" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="S4" t="n">
         <v>1518.1</v>
@@ -788,9 +778,11 @@
         <v>72</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="R5" t="n">
+        <v>69</v>
+      </c>
       <c r="S5" t="n">
         <v>1574.7</v>
       </c>
@@ -850,7 +842,7 @@
         <v>78</v>
       </c>
       <c r="R6" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="S6" t="n">
         <v>1514.4</v>
@@ -911,7 +903,7 @@
         <v>110</v>
       </c>
       <c r="R7" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="S7" t="n">
         <v>1539.4</v>
@@ -969,10 +961,10 @@
         <v>137</v>
       </c>
       <c r="Q8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R8" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="S8" t="n">
         <v>1548</v>
@@ -1094,7 +1086,7 @@
         <v>118</v>
       </c>
       <c r="R10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S10" t="n">
         <v>1543.4</v>
@@ -1155,7 +1147,7 @@
         <v>159</v>
       </c>
       <c r="R11" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="S11" t="n">
         <v>1516</v>
@@ -1216,7 +1208,7 @@
         <v>190</v>
       </c>
       <c r="R12" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="S12" t="n">
         <v>1506.6</v>
@@ -1277,7 +1269,7 @@
         <v>243</v>
       </c>
       <c r="R13" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="S13" t="n">
         <v>1564.2</v>
@@ -1338,7 +1330,7 @@
         <v>161</v>
       </c>
       <c r="R14" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="S14" t="n">
         <v>1538.4</v>
@@ -1399,7 +1391,7 @@
         <v>276</v>
       </c>
       <c r="R15" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="S15" t="n">
         <v>1554</v>
@@ -1420,97 +1412,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -1570,7 +1562,9 @@
       <c r="Q2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
       <c r="S2" t="n">
         <v>1779.9</v>
       </c>
@@ -1630,7 +1624,7 @@
         <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S3" t="n">
         <v>1675.8</v>
@@ -1752,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
         <v>1717.2</v>
@@ -1813,7 +1807,7 @@
         <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S6" t="n">
         <v>1724.6</v>
@@ -1874,7 +1868,7 @@
         <v>33</v>
       </c>
       <c r="R7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S7" t="n">
         <v>1706.3</v>
@@ -1934,7 +1928,9 @@
       <c r="Q8" t="n">
         <v>12</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
       <c r="S8" t="n">
         <v>1769.7</v>
       </c>
@@ -1994,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>1722.9</v>
@@ -2052,10 +2048,10 @@
         <v>28</v>
       </c>
       <c r="Q10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S10" t="n">
         <v>1712.2</v>
@@ -2116,7 +2112,7 @@
         <v>58</v>
       </c>
       <c r="R11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1695.9</v>
@@ -2177,7 +2173,7 @@
         <v>91</v>
       </c>
       <c r="R12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="S12" t="n">
         <v>1670.6</v>
@@ -2238,7 +2234,7 @@
         <v>82</v>
       </c>
       <c r="R13" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="S13" t="n">
         <v>1695.6</v>
@@ -2296,10 +2292,10 @@
         <v>74</v>
       </c>
       <c r="Q14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S14" t="n">
         <v>1689.6</v>
@@ -2360,7 +2356,7 @@
         <v>119</v>
       </c>
       <c r="R15" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="S15" t="n">
         <v>1691.9</v>
@@ -2421,7 +2417,7 @@
         <v>90</v>
       </c>
       <c r="R16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="S16" t="n">
         <v>1706.6</v>
@@ -2482,7 +2478,7 @@
         <v>116</v>
       </c>
       <c r="R17" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="S17" t="n">
         <v>1726.9</v>
@@ -2543,7 +2539,7 @@
         <v>121</v>
       </c>
       <c r="R18" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="S18" t="n">
         <v>1722.6</v>
@@ -2601,10 +2597,10 @@
         <v>131</v>
       </c>
       <c r="Q19" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="R19" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="S19" t="n">
         <v>1662.7</v>
@@ -2625,97 +2621,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -2776,7 +2772,7 @@
         <v>109</v>
       </c>
       <c r="R2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S2" t="n">
         <v>1475.3</v>
@@ -2837,7 +2833,7 @@
         <v>93</v>
       </c>
       <c r="R3" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="S3" t="n">
         <v>1452.3</v>
@@ -2895,10 +2891,10 @@
         <v>192</v>
       </c>
       <c r="Q4" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R4" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="S4" t="n">
         <v>1482.1</v>
@@ -2959,7 +2955,7 @@
         <v>146</v>
       </c>
       <c r="R5" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S5" t="n">
         <v>1463.1</v>
@@ -3020,7 +3016,7 @@
         <v>112</v>
       </c>
       <c r="R6" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="S6" t="n">
         <v>1452.3</v>
@@ -3081,7 +3077,7 @@
         <v>160</v>
       </c>
       <c r="R7" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="S7" t="n">
         <v>1454.3</v>
@@ -3142,7 +3138,7 @@
         <v>164</v>
       </c>
       <c r="R8" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="S8" t="n">
         <v>1455.5</v>
@@ -3203,7 +3199,7 @@
         <v>232</v>
       </c>
       <c r="R9" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="S9" t="n">
         <v>1496.9</v>
@@ -3224,97 +3220,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -3436,7 +3432,7 @@
         <v>113</v>
       </c>
       <c r="R3" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S3" t="n">
         <v>1482.5</v>
@@ -3558,7 +3554,7 @@
         <v>173</v>
       </c>
       <c r="R5" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S5" t="n">
         <v>1462</v>
@@ -3619,7 +3615,7 @@
         <v>219</v>
       </c>
       <c r="R6" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="S6" t="n">
         <v>1436.1</v>
@@ -3677,10 +3673,10 @@
         <v>135</v>
       </c>
       <c r="Q7" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S7" t="n">
         <v>1468.9</v>
@@ -3741,7 +3737,7 @@
         <v>155</v>
       </c>
       <c r="R8" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S8" t="n">
         <v>1525.9</v>
@@ -3802,7 +3798,7 @@
         <v>209</v>
       </c>
       <c r="R9" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="S9" t="n">
         <v>1459.9</v>
@@ -3863,7 +3859,7 @@
         <v>201</v>
       </c>
       <c r="R10" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="S10" t="n">
         <v>1518.8</v>
@@ -3924,7 +3920,7 @@
         <v>266</v>
       </c>
       <c r="R11" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S11" t="n">
         <v>1454.5</v>
@@ -3985,7 +3981,7 @@
         <v>236</v>
       </c>
       <c r="R12" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="S12" t="n">
         <v>1489.2</v>
@@ -4046,7 +4042,7 @@
         <v>285</v>
       </c>
       <c r="R13" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="S13" t="n">
         <v>1450.1</v>
@@ -4107,7 +4103,7 @@
         <v>323</v>
       </c>
       <c r="R14" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="S14" t="n">
         <v>1476.8</v>
@@ -4128,97 +4124,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -4279,7 +4275,7 @@
         <v>77</v>
       </c>
       <c r="R2" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="S2" t="n">
         <v>1481.5</v>
@@ -4340,7 +4336,7 @@
         <v>101</v>
       </c>
       <c r="R3" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="S3" t="n">
         <v>1500.3</v>
@@ -4401,7 +4397,7 @@
         <v>145</v>
       </c>
       <c r="R4" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="S4" t="n">
         <v>1484.4</v>
@@ -4462,7 +4458,7 @@
         <v>194</v>
       </c>
       <c r="R5" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="S5" t="n">
         <v>1466</v>
@@ -4523,7 +4519,7 @@
         <v>170</v>
       </c>
       <c r="R6" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="S6" t="n">
         <v>1524.2</v>
@@ -4584,7 +4580,7 @@
         <v>149</v>
       </c>
       <c r="R7" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="S7" t="n">
         <v>1474.6</v>
@@ -4645,7 +4641,7 @@
         <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="S8" t="n">
         <v>1466.6</v>
@@ -4706,7 +4702,7 @@
         <v>228</v>
       </c>
       <c r="R9" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="S9" t="n">
         <v>1490.2</v>
@@ -4767,7 +4763,7 @@
         <v>234</v>
       </c>
       <c r="R10" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="S10" t="n">
         <v>1481.4</v>
@@ -4828,7 +4824,7 @@
         <v>222</v>
       </c>
       <c r="R11" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="S11" t="n">
         <v>1489.5</v>
@@ -4849,97 +4845,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5000,7 +4996,7 @@
         <v>124</v>
       </c>
       <c r="R2" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="S2" t="n">
         <v>1431.7</v>
@@ -5061,7 +5057,7 @@
         <v>139</v>
       </c>
       <c r="R3" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="S3" t="n">
         <v>1424.9</v>
@@ -5122,7 +5118,7 @@
         <v>210</v>
       </c>
       <c r="R4" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="S4" t="n">
         <v>1453.7</v>
@@ -5183,7 +5179,7 @@
         <v>184</v>
       </c>
       <c r="R5" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="S5" t="n">
         <v>1491.6</v>
@@ -5244,7 +5240,7 @@
         <v>177</v>
       </c>
       <c r="R6" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="S6" t="n">
         <v>1447.2</v>
@@ -5305,7 +5301,7 @@
         <v>217</v>
       </c>
       <c r="R7" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S7" t="n">
         <v>1440.7</v>
@@ -5366,7 +5362,7 @@
         <v>195</v>
       </c>
       <c r="R8" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="S8" t="n">
         <v>1429.8</v>
@@ -5427,7 +5423,7 @@
         <v>259</v>
       </c>
       <c r="R9" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="S9" t="n">
         <v>1455</v>
@@ -5488,7 +5484,7 @@
         <v>245</v>
       </c>
       <c r="R10" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="S10" t="n">
         <v>1429.8</v>
@@ -5549,7 +5545,7 @@
         <v>308</v>
       </c>
       <c r="R11" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S11" t="n">
         <v>1460</v>
@@ -5610,7 +5606,7 @@
         <v>343</v>
       </c>
       <c r="R12" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="S12" t="n">
         <v>1424.7</v>
@@ -5631,97 +5627,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -5779,9 +5775,11 @@
         <v>73</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
+        <v>68</v>
+      </c>
       <c r="S2" t="n">
         <v>1457.5</v>
       </c>
@@ -5838,10 +5836,10 @@
         <v>151</v>
       </c>
       <c r="Q3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S3" t="n">
         <v>1465.2</v>
@@ -5899,9 +5897,11 @@
         <v>139</v>
       </c>
       <c r="Q4" t="n">
-        <v>138</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>128</v>
+      </c>
+      <c r="R4" t="n">
+        <v>139</v>
+      </c>
       <c r="S4" t="n">
         <v>1493.7</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>188</v>
       </c>
       <c r="R5" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="S5" t="n">
         <v>1502.5</v>
@@ -5982,97 +5982,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6130,10 +6130,10 @@
         <v>155</v>
       </c>
       <c r="Q2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R2" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="S2" t="n">
         <v>1455.9</v>
@@ -6191,10 +6191,10 @@
         <v>225</v>
       </c>
       <c r="Q3" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R3" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="S3" t="n">
         <v>1428.7</v>
@@ -6255,7 +6255,7 @@
         <v>172</v>
       </c>
       <c r="R4" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="S4" t="n">
         <v>1430.3</v>
@@ -6377,7 +6377,7 @@
         <v>202</v>
       </c>
       <c r="R6" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S6" t="n">
         <v>1423.5</v>
@@ -6438,7 +6438,7 @@
         <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="S7" t="n">
         <v>1437.6</v>
@@ -6499,7 +6499,7 @@
         <v>211</v>
       </c>
       <c r="R8" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="S8" t="n">
         <v>1406</v>
@@ -6560,7 +6560,7 @@
         <v>216</v>
       </c>
       <c r="R9" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="S9" t="n">
         <v>1426</v>
@@ -6703,97 +6703,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -6851,10 +6851,10 @@
         <v>196</v>
       </c>
       <c r="Q2" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S2" t="n">
         <v>1372.4</v>
@@ -6915,7 +6915,7 @@
         <v>327</v>
       </c>
       <c r="R3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S3" t="n">
         <v>1356.2</v>
@@ -6976,7 +6976,7 @@
         <v>335</v>
       </c>
       <c r="R4" t="n">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="S4" t="n">
         <v>1382.1</v>
@@ -7037,7 +7037,7 @@
         <v>325</v>
       </c>
       <c r="R5" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="S5" t="n">
         <v>1371.6</v>
@@ -7098,7 +7098,7 @@
         <v>351</v>
       </c>
       <c r="R6" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S6" t="n">
         <v>1394.2</v>
@@ -7159,7 +7159,7 @@
         <v>353</v>
       </c>
       <c r="R7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S7" t="n">
         <v>1403.1</v>
@@ -7241,97 +7241,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7392,7 +7392,7 @@
         <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="S2" t="n">
         <v>1416.9</v>
@@ -7450,10 +7450,10 @@
         <v>54</v>
       </c>
       <c r="Q3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S3" t="n">
         <v>1479.2</v>
@@ -7514,7 +7514,7 @@
         <v>87</v>
       </c>
       <c r="R4" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="S4" t="n">
         <v>1479</v>
@@ -7575,7 +7575,7 @@
         <v>148</v>
       </c>
       <c r="R5" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="S5" t="n">
         <v>1503.6</v>
@@ -7636,7 +7636,7 @@
         <v>178</v>
       </c>
       <c r="R6" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="S6" t="n">
         <v>1463.5</v>
@@ -7697,7 +7697,7 @@
         <v>214</v>
       </c>
       <c r="R7" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="S7" t="n">
         <v>1514.4</v>
@@ -7758,7 +7758,7 @@
         <v>196</v>
       </c>
       <c r="R8" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="S8" t="n">
         <v>1469.9</v>
@@ -7819,7 +7819,7 @@
         <v>208</v>
       </c>
       <c r="R9" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="S9" t="n">
         <v>1461.5</v>
@@ -7840,97 +7840,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -7988,10 +7988,10 @@
         <v>61</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="S2" t="n">
         <v>1485.7</v>
@@ -8052,7 +8052,7 @@
         <v>108</v>
       </c>
       <c r="R3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S3" t="n">
         <v>1524.5</v>
@@ -8113,7 +8113,7 @@
         <v>102</v>
       </c>
       <c r="R4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S4" t="n">
         <v>1504.8</v>
@@ -8174,7 +8174,7 @@
         <v>99</v>
       </c>
       <c r="R5" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="S5" t="n">
         <v>1504.1</v>
@@ -8232,10 +8232,10 @@
         <v>109</v>
       </c>
       <c r="Q6" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R6" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="S6" t="n">
         <v>1508.7</v>
@@ -8357,7 +8357,7 @@
         <v>151</v>
       </c>
       <c r="R8" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S8" t="n">
         <v>1523.8</v>
@@ -8418,7 +8418,7 @@
         <v>158</v>
       </c>
       <c r="R9" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="S9" t="n">
         <v>1517.4</v>
@@ -8476,10 +8476,10 @@
         <v>204</v>
       </c>
       <c r="Q10" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R10" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="S10" t="n">
         <v>1528.6</v>
@@ -8540,7 +8540,7 @@
         <v>253</v>
       </c>
       <c r="R11" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S11" t="n">
         <v>1522.9</v>
@@ -8601,7 +8601,7 @@
         <v>305</v>
       </c>
       <c r="R12" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S12" t="n">
         <v>1566.8</v>
@@ -8622,97 +8622,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -8834,7 +8834,7 @@
         <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
         <v>1665.9</v>
@@ -8892,7 +8892,7 @@
         <v>33</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R4" t="n">
         <v>32</v>
@@ -8956,7 +8956,7 @@
         <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S5" t="n">
         <v>1677.4</v>
@@ -9017,7 +9017,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S6" t="n">
         <v>1672.9</v>
@@ -9078,7 +9078,7 @@
         <v>28</v>
       </c>
       <c r="R7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S7" t="n">
         <v>1686.1</v>
@@ -9139,7 +9139,7 @@
         <v>41</v>
       </c>
       <c r="R8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S8" t="n">
         <v>1681.7</v>
@@ -9200,7 +9200,7 @@
         <v>72</v>
       </c>
       <c r="R9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="S9" t="n">
         <v>1678</v>
@@ -9261,7 +9261,7 @@
         <v>56</v>
       </c>
       <c r="R10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S10" t="n">
         <v>1603.7</v>
@@ -9322,7 +9322,7 @@
         <v>57</v>
       </c>
       <c r="R11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="S11" t="n">
         <v>1622.5</v>
@@ -9383,7 +9383,7 @@
         <v>44</v>
       </c>
       <c r="R12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1649.8</v>
@@ -9444,7 +9444,7 @@
         <v>52</v>
       </c>
       <c r="R13" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S13" t="n">
         <v>1660.6</v>
@@ -9505,7 +9505,7 @@
         <v>79</v>
       </c>
       <c r="R14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S14" t="n">
         <v>1677.2</v>
@@ -9566,7 +9566,7 @@
         <v>85</v>
       </c>
       <c r="R15" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="S15" t="n">
         <v>1664</v>
@@ -9627,7 +9627,7 @@
         <v>126</v>
       </c>
       <c r="R16" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="S16" t="n">
         <v>1665.5</v>
@@ -9648,97 +9648,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -9799,7 +9799,7 @@
         <v>29</v>
       </c>
       <c r="R2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S2" t="n">
         <v>1611.4</v>
@@ -9918,10 +9918,10 @@
         <v>51</v>
       </c>
       <c r="Q4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R4" t="n">
         <v>46</v>
-      </c>
-      <c r="R4" t="n">
-        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1597.3</v>
@@ -9982,7 +9982,7 @@
         <v>74</v>
       </c>
       <c r="R5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="S5" t="n">
         <v>1581.4</v>
@@ -10043,7 +10043,7 @@
         <v>69</v>
       </c>
       <c r="R6" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="S6" t="n">
         <v>1607.1</v>
@@ -10104,7 +10104,7 @@
         <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S7" t="n">
         <v>1610.8</v>
@@ -10287,7 +10287,7 @@
         <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S10" t="n">
         <v>1563.6</v>
@@ -10348,7 +10348,7 @@
         <v>179</v>
       </c>
       <c r="R11" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="S11" t="n">
         <v>1590.6</v>
@@ -10409,7 +10409,7 @@
         <v>244</v>
       </c>
       <c r="R12" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="S12" t="n">
         <v>1598.9</v>
@@ -10470,7 +10470,7 @@
         <v>346</v>
       </c>
       <c r="R13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="S13" t="n">
         <v>1572.4</v>
@@ -10491,97 +10491,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -10642,7 +10642,7 @@
         <v>165</v>
       </c>
       <c r="R2" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S2" t="n">
         <v>1378.8</v>
@@ -10703,7 +10703,7 @@
         <v>252</v>
       </c>
       <c r="R3" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="S3" t="n">
         <v>1359.6</v>
@@ -10764,7 +10764,7 @@
         <v>296</v>
       </c>
       <c r="R4" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S4" t="n">
         <v>1379.2</v>
@@ -10825,7 +10825,7 @@
         <v>300</v>
       </c>
       <c r="R5" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="S5" t="n">
         <v>1378.3</v>
@@ -10886,7 +10886,7 @@
         <v>341</v>
       </c>
       <c r="R6" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="S6" t="n">
         <v>1382.7</v>
@@ -10947,7 +10947,7 @@
         <v>345</v>
       </c>
       <c r="R7" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S7" t="n">
         <v>1387.9</v>
@@ -11008,7 +11008,7 @@
         <v>316</v>
       </c>
       <c r="R8" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="S8" t="n">
         <v>1390.5</v>
@@ -11069,7 +11069,7 @@
         <v>350</v>
       </c>
       <c r="R9" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="S9" t="n">
         <v>1420</v>
@@ -11090,97 +11090,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -11241,7 +11241,7 @@
         <v>152</v>
       </c>
       <c r="R2" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="S2" t="n">
         <v>1407.8</v>
@@ -11302,7 +11302,7 @@
         <v>223</v>
       </c>
       <c r="R3" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="S3" t="n">
         <v>1402</v>
@@ -11363,7 +11363,7 @@
         <v>220</v>
       </c>
       <c r="R4" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="S4" t="n">
         <v>1408.8</v>
@@ -11424,7 +11424,7 @@
         <v>192</v>
       </c>
       <c r="R5" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="S5" t="n">
         <v>1377.9</v>
@@ -11485,7 +11485,7 @@
         <v>249</v>
       </c>
       <c r="R6" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="S6" t="n">
         <v>1379.3</v>
@@ -11546,7 +11546,7 @@
         <v>251</v>
       </c>
       <c r="R7" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="S7" t="n">
         <v>1391.9</v>
@@ -11607,7 +11607,7 @@
         <v>311</v>
       </c>
       <c r="R8" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="S8" t="n">
         <v>1400.2</v>
@@ -11668,7 +11668,7 @@
         <v>314</v>
       </c>
       <c r="R9" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="S9" t="n">
         <v>1439.7</v>
@@ -11689,97 +11689,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -11840,7 +11840,7 @@
         <v>123</v>
       </c>
       <c r="R2" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S2" t="n">
         <v>1374.6</v>
@@ -11901,7 +11901,7 @@
         <v>263</v>
       </c>
       <c r="R3" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="S3" t="n">
         <v>1399</v>
@@ -11962,7 +11962,7 @@
         <v>240</v>
       </c>
       <c r="R4" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="S4" t="n">
         <v>1419.5</v>
@@ -12023,7 +12023,7 @@
         <v>270</v>
       </c>
       <c r="R5" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="S5" t="n">
         <v>1376.4</v>
@@ -12084,7 +12084,7 @@
         <v>258</v>
       </c>
       <c r="R6" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="S6" t="n">
         <v>1396.2</v>
@@ -12206,7 +12206,7 @@
         <v>330</v>
       </c>
       <c r="R8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="S8" t="n">
         <v>1388.5</v>
@@ -12267,7 +12267,7 @@
         <v>328</v>
       </c>
       <c r="R9" t="n">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="S9" t="n">
         <v>1410.7</v>
@@ -12328,7 +12328,7 @@
         <v>339</v>
       </c>
       <c r="R10" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S10" t="n">
         <v>1381.7</v>
@@ -12389,7 +12389,7 @@
         <v>337</v>
       </c>
       <c r="R11" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S11" t="n">
         <v>1382.1</v>
@@ -12410,97 +12410,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -12622,7 +12622,7 @@
         <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S3" t="n">
         <v>1767</v>
@@ -12680,9 +12680,11 @@
         <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="R4" t="n">
+        <v>15</v>
+      </c>
       <c r="S4" t="n">
         <v>1736</v>
       </c>
@@ -12739,9 +12741,11 @@
         <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="R5" t="n">
+        <v>13</v>
+      </c>
       <c r="S5" t="n">
         <v>1718.8</v>
       </c>
@@ -12798,10 +12802,10 @@
         <v>20</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S6" t="n">
         <v>1716.9</v>
@@ -12862,7 +12866,7 @@
         <v>42</v>
       </c>
       <c r="R7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S7" t="n">
         <v>1653.7</v>
@@ -12923,7 +12927,7 @@
         <v>37</v>
       </c>
       <c r="R8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S8" t="n">
         <v>1643.1</v>
@@ -12984,7 +12988,7 @@
         <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S9" t="n">
         <v>1658.3</v>
@@ -13106,7 +13110,7 @@
         <v>47</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1696.4</v>
@@ -13167,7 +13171,7 @@
         <v>67</v>
       </c>
       <c r="R12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="S12" t="n">
         <v>1675.4</v>
@@ -13225,7 +13229,7 @@
         <v>39</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R13" t="n">
         <v>38</v>
@@ -13289,7 +13293,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S14" t="n">
         <v>1707.4</v>
@@ -13350,7 +13354,7 @@
         <v>135</v>
       </c>
       <c r="R15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="S15" t="n">
         <v>1655.8</v>
@@ -13411,7 +13415,7 @@
         <v>103</v>
       </c>
       <c r="R16" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="S16" t="n">
         <v>1713.4</v>
@@ -13493,97 +13497,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -13644,7 +13648,7 @@
         <v>162</v>
       </c>
       <c r="R2" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="S2" t="n">
         <v>1421.6</v>
@@ -13705,7 +13709,7 @@
         <v>191</v>
       </c>
       <c r="R3" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="S3" t="n">
         <v>1450.7</v>
@@ -13766,7 +13770,7 @@
         <v>218</v>
       </c>
       <c r="R4" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="S4" t="n">
         <v>1426</v>
@@ -13827,7 +13831,7 @@
         <v>215</v>
       </c>
       <c r="R5" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="S5" t="n">
         <v>1439.5</v>
@@ -13888,7 +13892,7 @@
         <v>239</v>
       </c>
       <c r="R6" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S6" t="n">
         <v>1473.5</v>
@@ -13949,7 +13953,7 @@
         <v>183</v>
       </c>
       <c r="R7" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="S7" t="n">
         <v>1422.2</v>
@@ -14010,7 +14014,7 @@
         <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S8" t="n">
         <v>1428.1</v>
@@ -14071,7 +14075,7 @@
         <v>304</v>
       </c>
       <c r="R9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="S9" t="n">
         <v>1422.3</v>
@@ -14132,7 +14136,7 @@
         <v>338</v>
       </c>
       <c r="R10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="S10" t="n">
         <v>1419.9</v>
@@ -14193,7 +14197,7 @@
         <v>358</v>
       </c>
       <c r="R11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S11" t="n">
         <v>1429.4</v>
@@ -14214,97 +14218,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -14365,7 +14369,7 @@
         <v>66</v>
       </c>
       <c r="R2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S2" t="n">
         <v>1397.1</v>
@@ -14423,10 +14427,10 @@
         <v>63</v>
       </c>
       <c r="Q3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R3" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="S3" t="n">
         <v>1428.4</v>
@@ -14487,7 +14491,7 @@
         <v>167</v>
       </c>
       <c r="R4" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="S4" t="n">
         <v>1436.7</v>
@@ -14548,7 +14552,7 @@
         <v>198</v>
       </c>
       <c r="R5" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="S5" t="n">
         <v>1430.4</v>
@@ -14609,7 +14613,7 @@
         <v>213</v>
       </c>
       <c r="R6" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="S6" t="n">
         <v>1451.6</v>
@@ -14670,7 +14674,7 @@
         <v>238</v>
       </c>
       <c r="R7" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="S7" t="n">
         <v>1426</v>
@@ -14731,7 +14735,7 @@
         <v>307</v>
       </c>
       <c r="R8" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S8" t="n">
         <v>1438.9</v>
@@ -14813,97 +14817,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -14964,7 +14968,7 @@
         <v>98</v>
       </c>
       <c r="R2" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S2" t="n">
         <v>1410.6</v>
@@ -15025,7 +15029,7 @@
         <v>117</v>
       </c>
       <c r="R3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S3" t="n">
         <v>1395</v>
@@ -15086,7 +15090,7 @@
         <v>237</v>
       </c>
       <c r="R4" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S4" t="n">
         <v>1468.8</v>
@@ -15147,7 +15151,7 @@
         <v>254</v>
       </c>
       <c r="R5" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="S5" t="n">
         <v>1423.8</v>
@@ -15269,7 +15273,7 @@
         <v>242</v>
       </c>
       <c r="R7" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="S7" t="n">
         <v>1449.1</v>
@@ -15330,7 +15334,7 @@
         <v>256</v>
       </c>
       <c r="R8" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="S8" t="n">
         <v>1460.2</v>
@@ -15391,7 +15395,7 @@
         <v>326</v>
       </c>
       <c r="R9" t="n">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="S9" t="n">
         <v>1440.1</v>
@@ -15452,7 +15456,7 @@
         <v>363</v>
       </c>
       <c r="R10" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S10" t="n">
         <v>1432</v>
@@ -15473,97 +15477,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -15624,7 +15628,7 @@
         <v>120</v>
       </c>
       <c r="R2" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="S2" t="n">
         <v>1466</v>
@@ -15685,7 +15689,7 @@
         <v>157</v>
       </c>
       <c r="R3" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S3" t="n">
         <v>1448.2</v>
@@ -15746,7 +15750,7 @@
         <v>181</v>
       </c>
       <c r="R4" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="S4" t="n">
         <v>1429.2</v>
@@ -15807,7 +15811,7 @@
         <v>175</v>
       </c>
       <c r="R5" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="S5" t="n">
         <v>1423.8</v>
@@ -15868,7 +15872,7 @@
         <v>197</v>
       </c>
       <c r="R6" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S6" t="n">
         <v>1425.5</v>
@@ -15929,7 +15933,7 @@
         <v>154</v>
       </c>
       <c r="R7" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="S7" t="n">
         <v>1442.8</v>
@@ -15990,7 +15994,7 @@
         <v>142</v>
       </c>
       <c r="R8" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="S8" t="n">
         <v>1449.7</v>
@@ -16051,7 +16055,7 @@
         <v>212</v>
       </c>
       <c r="R9" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="S9" t="n">
         <v>1471</v>
@@ -16112,7 +16116,7 @@
         <v>193</v>
       </c>
       <c r="R10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S10" t="n">
         <v>1452.5</v>
@@ -16173,7 +16177,7 @@
         <v>227</v>
       </c>
       <c r="R11" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S11" t="n">
         <v>1449.5</v>
@@ -16234,7 +16238,7 @@
         <v>262</v>
       </c>
       <c r="R12" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S12" t="n">
         <v>1469.1</v>
@@ -16295,7 +16299,7 @@
         <v>291</v>
       </c>
       <c r="R13" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S13" t="n">
         <v>1467.5</v>
@@ -16356,7 +16360,7 @@
         <v>319</v>
       </c>
       <c r="R14" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="S14" t="n">
         <v>1454.5</v>
@@ -16438,97 +16442,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -16589,7 +16593,7 @@
         <v>221</v>
       </c>
       <c r="R2" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="S2" t="n">
         <v>1430.6</v>
@@ -16650,7 +16654,7 @@
         <v>289</v>
       </c>
       <c r="R3" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="S3" t="n">
         <v>1376.6</v>
@@ -16711,7 +16715,7 @@
         <v>271</v>
       </c>
       <c r="R4" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S4" t="n">
         <v>1389.2</v>
@@ -16772,7 +16776,7 @@
         <v>313</v>
       </c>
       <c r="R5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S5" t="n">
         <v>1386.6</v>
@@ -16833,7 +16837,7 @@
         <v>265</v>
       </c>
       <c r="R6" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S6" t="n">
         <v>1355.6</v>
@@ -16894,7 +16898,7 @@
         <v>301</v>
       </c>
       <c r="R7" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S7" t="n">
         <v>1389.8</v>
@@ -16955,7 +16959,7 @@
         <v>315</v>
       </c>
       <c r="R8" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S8" t="n">
         <v>1420.2</v>
@@ -17016,7 +17020,7 @@
         <v>306</v>
       </c>
       <c r="R9" t="n">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="S9" t="n">
         <v>1383.4</v>
@@ -17077,7 +17081,7 @@
         <v>320</v>
       </c>
       <c r="R10" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="S10" t="n">
         <v>1352.7</v>
@@ -17138,7 +17142,7 @@
         <v>332</v>
       </c>
       <c r="R11" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="S11" t="n">
         <v>1382</v>
@@ -17199,7 +17203,7 @@
         <v>336</v>
       </c>
       <c r="R12" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="S12" t="n">
         <v>1405.1</v>
@@ -17281,97 +17285,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -17429,9 +17433,11 @@
         <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>51</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="R2" t="n">
+        <v>45</v>
+      </c>
       <c r="S2" t="n">
         <v>1554.8</v>
       </c>
@@ -17490,7 +17496,9 @@
       <c r="Q3" t="n">
         <v>83</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>78</v>
+      </c>
       <c r="S3" t="n">
         <v>1546.5</v>
       </c>
@@ -17547,10 +17555,10 @@
         <v>59</v>
       </c>
       <c r="Q4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S4" t="n">
         <v>1509.4</v>
@@ -17611,7 +17619,7 @@
         <v>115</v>
       </c>
       <c r="R5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S5" t="n">
         <v>1498.7</v>
@@ -17672,7 +17680,7 @@
         <v>176</v>
       </c>
       <c r="R6" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="S6" t="n">
         <v>1509.6</v>
@@ -17733,7 +17741,7 @@
         <v>127</v>
       </c>
       <c r="R7" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="S7" t="n">
         <v>1516.2</v>
@@ -17791,7 +17799,7 @@
         <v>129</v>
       </c>
       <c r="Q8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R8" t="n">
         <v>123</v>
@@ -17855,7 +17863,7 @@
         <v>163</v>
       </c>
       <c r="R9" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="S9" t="n">
         <v>1604.3</v>
@@ -17913,10 +17921,10 @@
         <v>213</v>
       </c>
       <c r="Q10" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S10" t="n">
         <v>1528.4</v>
@@ -17974,10 +17982,10 @@
         <v>174</v>
       </c>
       <c r="Q11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="S11" t="n">
         <v>1501.2</v>
@@ -17998,97 +18006,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -18210,7 +18218,7 @@
         <v>81</v>
       </c>
       <c r="R3" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="S3" t="n">
         <v>1462.4</v>
@@ -18271,7 +18279,7 @@
         <v>144</v>
       </c>
       <c r="R4" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S4" t="n">
         <v>1495.4</v>
@@ -18332,7 +18340,7 @@
         <v>150</v>
       </c>
       <c r="R5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S5" t="n">
         <v>1465</v>
@@ -18393,7 +18401,7 @@
         <v>264</v>
       </c>
       <c r="R6" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S6" t="n">
         <v>1494</v>
@@ -18515,7 +18523,7 @@
         <v>231</v>
       </c>
       <c r="R8" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="S8" t="n">
         <v>1467.7</v>
@@ -18536,97 +18544,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -18684,10 +18692,10 @@
         <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>1601.3</v>
@@ -18748,7 +18756,7 @@
         <v>21</v>
       </c>
       <c r="R3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S3" t="n">
         <v>1596.9</v>
@@ -18809,7 +18817,7 @@
         <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S4" t="n">
         <v>1596.2</v>
@@ -18867,10 +18875,10 @@
         <v>166</v>
       </c>
       <c r="Q5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R5" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S5" t="n">
         <v>1558.8</v>
@@ -18989,7 +18997,7 @@
         <v>120</v>
       </c>
       <c r="Q7" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R7" t="n">
         <v>116</v>
@@ -19053,7 +19061,7 @@
         <v>114</v>
       </c>
       <c r="R8" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="S8" t="n">
         <v>1521.6</v>
@@ -19114,7 +19122,7 @@
         <v>203</v>
       </c>
       <c r="R9" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="S9" t="n">
         <v>1564</v>
@@ -19175,7 +19183,7 @@
         <v>205</v>
       </c>
       <c r="R10" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="S10" t="n">
         <v>1534</v>
@@ -19236,7 +19244,7 @@
         <v>187</v>
       </c>
       <c r="R11" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="S11" t="n">
         <v>1515.5</v>
@@ -19297,7 +19305,7 @@
         <v>247</v>
       </c>
       <c r="R12" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="S12" t="n">
         <v>1529.1</v>
@@ -19358,7 +19366,7 @@
         <v>290</v>
       </c>
       <c r="R13" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="S13" t="n">
         <v>1523.1</v>
@@ -19379,97 +19387,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -19530,7 +19538,7 @@
         <v>189</v>
       </c>
       <c r="R2" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="S2" t="n">
         <v>1369.1</v>
@@ -19591,7 +19599,7 @@
         <v>225</v>
       </c>
       <c r="R3" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="S3" t="n">
         <v>1390.5</v>
@@ -19713,7 +19721,7 @@
         <v>317</v>
       </c>
       <c r="R5" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="S5" t="n">
         <v>1403.6</v>
@@ -19835,7 +19843,7 @@
         <v>352</v>
       </c>
       <c r="R7" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S7" t="n">
         <v>1378</v>
@@ -19896,7 +19904,7 @@
         <v>349</v>
       </c>
       <c r="R8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="S8" t="n">
         <v>1400.3</v>
@@ -19957,7 +19965,7 @@
         <v>348</v>
       </c>
       <c r="R9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S9" t="n">
         <v>1416.5</v>
@@ -19978,97 +19986,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -20187,10 +20195,10 @@
         <v>147</v>
       </c>
       <c r="Q3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R3" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="S3" t="n">
         <v>1405.9</v>
@@ -20251,7 +20259,7 @@
         <v>171</v>
       </c>
       <c r="R4" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="S4" t="n">
         <v>1430.9</v>
@@ -20312,7 +20320,7 @@
         <v>182</v>
       </c>
       <c r="R5" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="S5" t="n">
         <v>1421.3</v>
@@ -20373,7 +20381,7 @@
         <v>260</v>
       </c>
       <c r="R6" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="S6" t="n">
         <v>1431.6</v>
@@ -20434,7 +20442,7 @@
         <v>269</v>
       </c>
       <c r="R7" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S7" t="n">
         <v>1406.5</v>
@@ -20495,7 +20503,7 @@
         <v>302</v>
       </c>
       <c r="R8" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="S8" t="n">
         <v>1422.5</v>
@@ -20617,7 +20625,7 @@
         <v>297</v>
       </c>
       <c r="R10" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S10" t="n">
         <v>1398.5</v>
@@ -20678,7 +20686,7 @@
         <v>303</v>
       </c>
       <c r="R11" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="S11" t="n">
         <v>1413.5</v>
@@ -20739,7 +20747,7 @@
         <v>347</v>
       </c>
       <c r="R12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S12" t="n">
         <v>1460.8</v>
@@ -20800,7 +20808,7 @@
         <v>334</v>
       </c>
       <c r="R13" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="S13" t="n">
         <v>1410.7</v>
@@ -20821,97 +20829,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -21030,10 +21038,10 @@
         <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
         <v>1742.7</v>
@@ -21094,7 +21102,7 @@
         <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S4" t="n">
         <v>1791.1</v>
@@ -21155,7 +21163,7 @@
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S5" t="n">
         <v>1772.3</v>
@@ -21216,7 +21224,7 @@
         <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
         <v>1718</v>
@@ -21277,7 +21285,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1691.3</v>
@@ -21338,7 +21346,7 @@
         <v>71</v>
       </c>
       <c r="R8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S8" t="n">
         <v>1669</v>
@@ -21457,10 +21465,10 @@
         <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S10" t="n">
         <v>1713.3</v>
@@ -21521,7 +21529,7 @@
         <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S11" t="n">
         <v>1733.2</v>
@@ -21582,7 +21590,7 @@
         <v>68</v>
       </c>
       <c r="R12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="S12" t="n">
         <v>1689.7</v>
@@ -21640,10 +21648,10 @@
         <v>64</v>
       </c>
       <c r="Q13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R13" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="S13" t="n">
         <v>1742.3</v>
@@ -21704,7 +21712,7 @@
         <v>70</v>
       </c>
       <c r="R14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S14" t="n">
         <v>1727.4</v>
@@ -21765,7 +21773,7 @@
         <v>55</v>
       </c>
       <c r="R15" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="S15" t="n">
         <v>1692.8</v>
@@ -21826,7 +21834,7 @@
         <v>111</v>
       </c>
       <c r="R16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S16" t="n">
         <v>1710.3</v>
@@ -21887,7 +21895,7 @@
         <v>147</v>
       </c>
       <c r="R17" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="S17" t="n">
         <v>1692.4</v>
@@ -21908,97 +21916,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -22059,7 +22067,7 @@
         <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="S2" t="n">
         <v>1691.6</v>
@@ -22120,7 +22128,7 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
         <v>1670.2</v>
@@ -22181,7 +22189,7 @@
         <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>1641.5</v>
@@ -22242,7 +22250,7 @@
         <v>54</v>
       </c>
       <c r="R5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="S5" t="n">
         <v>1648.5</v>
@@ -22303,7 +22311,7 @@
         <v>84</v>
       </c>
       <c r="R6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S6" t="n">
         <v>1664.6</v>
@@ -22364,7 +22372,7 @@
         <v>95</v>
       </c>
       <c r="R7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S7" t="n">
         <v>1604.6</v>
@@ -22422,10 +22430,10 @@
         <v>94</v>
       </c>
       <c r="Q8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S8" t="n">
         <v>1671.3</v>
@@ -22486,7 +22494,7 @@
         <v>86</v>
       </c>
       <c r="R9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="S9" t="n">
         <v>1620.7</v>
@@ -22547,7 +22555,7 @@
         <v>94</v>
       </c>
       <c r="R10" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S10" t="n">
         <v>1652.1</v>
@@ -22669,7 +22677,7 @@
         <v>104</v>
       </c>
       <c r="R12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="S12" t="n">
         <v>1660.1</v>
@@ -22690,97 +22698,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -22841,7 +22849,7 @@
         <v>143</v>
       </c>
       <c r="R2" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="S2" t="n">
         <v>1416</v>
@@ -22902,7 +22910,7 @@
         <v>166</v>
       </c>
       <c r="R3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S3" t="n">
         <v>1437.1</v>
@@ -22963,7 +22971,7 @@
         <v>226</v>
       </c>
       <c r="R4" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="S4" t="n">
         <v>1450.3</v>
@@ -23024,7 +23032,7 @@
         <v>186</v>
       </c>
       <c r="R5" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="S5" t="n">
         <v>1433.9</v>
@@ -23085,7 +23093,7 @@
         <v>156</v>
       </c>
       <c r="R6" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="S6" t="n">
         <v>1401.2</v>
@@ -23146,7 +23154,7 @@
         <v>224</v>
       </c>
       <c r="R7" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="S7" t="n">
         <v>1419</v>
@@ -23207,7 +23215,7 @@
         <v>174</v>
       </c>
       <c r="R8" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="S8" t="n">
         <v>1415.2</v>
@@ -23268,7 +23276,7 @@
         <v>292</v>
       </c>
       <c r="R9" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="S9" t="n">
         <v>1444.3</v>
@@ -23390,7 +23398,7 @@
         <v>322</v>
       </c>
       <c r="R11" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="S11" t="n">
         <v>1433.8</v>
@@ -23411,97 +23419,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -23562,7 +23570,7 @@
         <v>75</v>
       </c>
       <c r="R2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S2" t="n">
         <v>1382.5</v>
@@ -23623,7 +23631,7 @@
         <v>125</v>
       </c>
       <c r="R3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S3" t="n">
         <v>1437.4</v>
@@ -23684,7 +23692,7 @@
         <v>261</v>
       </c>
       <c r="R4" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S4" t="n">
         <v>1419.6</v>
@@ -23745,7 +23753,7 @@
         <v>248</v>
       </c>
       <c r="R5" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="S5" t="n">
         <v>1428.4</v>
@@ -23803,10 +23811,10 @@
         <v>264</v>
       </c>
       <c r="Q6" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R6" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S6" t="n">
         <v>1389.4</v>
@@ -23867,7 +23875,7 @@
         <v>273</v>
       </c>
       <c r="R7" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="S7" t="n">
         <v>1412.3</v>
@@ -23925,10 +23933,10 @@
         <v>255</v>
       </c>
       <c r="Q8" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R8" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S8" t="n">
         <v>1394.8</v>
@@ -23989,7 +23997,7 @@
         <v>299</v>
       </c>
       <c r="R9" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="S9" t="n">
         <v>1417.1</v>
